--- a/assets/data/bcv/excel/ove_bcv_pib_historico_anual.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_pib_historico_anual.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="datos" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="metadatos" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="datos" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="metadatos" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -97,11 +97,79 @@
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
       <col>0</col>
@@ -116,13 +184,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:blip cstate="print" r:embed="rId1"/>
+        <a:stretch>
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:prstGeom prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -131,7 +199,7 @@
 </file>
 
 <file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
       <col>0</col>
@@ -146,13 +214,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:blip cstate="print" r:embed="rId1"/>
+        <a:stretch>
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:prstGeom prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -668,7 +736,7 @@
       </c>
       <c r="S7" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -753,7 +821,7 @@
       </c>
       <c r="S8" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -838,7 +906,7 @@
       </c>
       <c r="S9" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -923,7 +991,7 @@
       </c>
       <c r="S10" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -1008,7 +1076,7 @@
       </c>
       <c r="S11" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -1093,7 +1161,7 @@
       </c>
       <c r="S12" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -1178,7 +1246,7 @@
       </c>
       <c r="S13" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -1263,7 +1331,7 @@
       </c>
       <c r="S14" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -1348,7 +1416,7 @@
       </c>
       <c r="S15" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -1433,7 +1501,7 @@
       </c>
       <c r="S16" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -1518,7 +1586,7 @@
       </c>
       <c r="S17" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -1603,7 +1671,7 @@
       </c>
       <c r="S18" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -1688,7 +1756,7 @@
       </c>
       <c r="S19" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -1773,7 +1841,7 @@
       </c>
       <c r="S20" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -1858,7 +1926,7 @@
       </c>
       <c r="S21" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -1943,7 +2011,7 @@
       </c>
       <c r="S22" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -2028,7 +2096,7 @@
       </c>
       <c r="S23" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -2113,7 +2181,7 @@
       </c>
       <c r="S24" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -2198,7 +2266,7 @@
       </c>
       <c r="S25" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -2283,7 +2351,7 @@
       </c>
       <c r="S26" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -2368,7 +2436,7 @@
       </c>
       <c r="S27" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -2453,7 +2521,7 @@
       </c>
       <c r="S28" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -2538,7 +2606,7 @@
       </c>
       <c r="S29" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -2623,7 +2691,7 @@
       </c>
       <c r="S30" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -2708,7 +2776,7 @@
       </c>
       <c r="S31" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -2793,7 +2861,7 @@
       </c>
       <c r="S32" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -2878,7 +2946,7 @@
       </c>
       <c r="S33" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -2963,7 +3031,7 @@
       </c>
       <c r="S34" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -3048,7 +3116,7 @@
       </c>
       <c r="S35" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -3133,7 +3201,7 @@
       </c>
       <c r="S36" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -3218,7 +3286,7 @@
       </c>
       <c r="S37" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -3303,7 +3371,7 @@
       </c>
       <c r="S38" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -3388,7 +3456,7 @@
       </c>
       <c r="S39" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -3473,7 +3541,7 @@
       </c>
       <c r="S40" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -3558,7 +3626,7 @@
       </c>
       <c r="S41" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -3643,7 +3711,7 @@
       </c>
       <c r="S42" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -3728,7 +3796,7 @@
       </c>
       <c r="S43" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -3813,7 +3881,7 @@
       </c>
       <c r="S44" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -3898,7 +3966,7 @@
       </c>
       <c r="S45" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -3983,7 +4051,7 @@
       </c>
       <c r="S46" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -4068,7 +4136,7 @@
       </c>
       <c r="S47" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -4153,7 +4221,7 @@
       </c>
       <c r="S48" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -4238,7 +4306,7 @@
       </c>
       <c r="S49" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -4323,7 +4391,7 @@
       </c>
       <c r="S50" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -4408,7 +4476,7 @@
       </c>
       <c r="S51" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -4493,7 +4561,7 @@
       </c>
       <c r="S52" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -4578,7 +4646,7 @@
       </c>
       <c r="S53" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -4663,7 +4731,7 @@
       </c>
       <c r="S54" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -4748,7 +4816,7 @@
       </c>
       <c r="S55" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -4833,7 +4901,7 @@
       </c>
       <c r="S56" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -4918,7 +4986,7 @@
       </c>
       <c r="S57" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -5003,7 +5071,7 @@
       </c>
       <c r="S58" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -5088,7 +5156,7 @@
       </c>
       <c r="S59" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -5173,7 +5241,7 @@
       </c>
       <c r="S60" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -5258,7 +5326,7 @@
       </c>
       <c r="S61" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -5343,7 +5411,7 @@
       </c>
       <c r="S62" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -5428,7 +5496,7 @@
       </c>
       <c r="S63" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -5513,7 +5581,7 @@
       </c>
       <c r="S64" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -5598,7 +5666,7 @@
       </c>
       <c r="S65" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -5683,7 +5751,7 @@
       </c>
       <c r="S66" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -5768,7 +5836,7 @@
       </c>
       <c r="S67" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -5853,7 +5921,7 @@
       </c>
       <c r="S68" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -5938,7 +6006,7 @@
       </c>
       <c r="S69" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -6023,7 +6091,7 @@
       </c>
       <c r="S70" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -6108,7 +6176,7 @@
       </c>
       <c r="S71" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -6193,7 +6261,7 @@
       </c>
       <c r="S72" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -6278,7 +6346,7 @@
       </c>
       <c r="S73" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -6363,7 +6431,7 @@
       </c>
       <c r="S74" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -6448,7 +6516,7 @@
       </c>
       <c r="S75" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -6533,7 +6601,7 @@
       </c>
       <c r="S76" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -6618,7 +6686,7 @@
       </c>
       <c r="S77" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -6703,7 +6771,7 @@
       </c>
       <c r="S78" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -6788,7 +6856,7 @@
       </c>
       <c r="S79" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -6873,7 +6941,7 @@
       </c>
       <c r="S80" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -6958,7 +7026,7 @@
       </c>
       <c r="S81" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -7043,7 +7111,7 @@
       </c>
       <c r="S82" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -7128,7 +7196,7 @@
       </c>
       <c r="S83" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -7213,7 +7281,7 @@
       </c>
       <c r="S84" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -7298,7 +7366,7 @@
       </c>
       <c r="S85" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -7383,7 +7451,7 @@
       </c>
       <c r="S86" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -7468,7 +7536,7 @@
       </c>
       <c r="S87" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -7553,7 +7621,7 @@
       </c>
       <c r="S88" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -7638,7 +7706,7 @@
       </c>
       <c r="S89" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -7723,7 +7791,7 @@
       </c>
       <c r="S90" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -7808,7 +7876,7 @@
       </c>
       <c r="S91" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -7893,7 +7961,7 @@
       </c>
       <c r="S92" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -7978,7 +8046,7 @@
       </c>
       <c r="S93" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -8063,7 +8131,7 @@
       </c>
       <c r="S94" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -8148,7 +8216,7 @@
       </c>
       <c r="S95" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -8233,7 +8301,7 @@
       </c>
       <c r="S96" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -8318,7 +8386,7 @@
       </c>
       <c r="S97" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -8403,7 +8471,7 @@
       </c>
       <c r="S98" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -8488,7 +8556,7 @@
       </c>
       <c r="S99" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -8573,7 +8641,7 @@
       </c>
       <c r="S100" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -8658,7 +8726,7 @@
       </c>
       <c r="S101" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -8743,7 +8811,7 @@
       </c>
       <c r="S102" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -8828,7 +8896,7 @@
       </c>
       <c r="S103" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -8913,7 +8981,7 @@
       </c>
       <c r="S104" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -8998,7 +9066,7 @@
       </c>
       <c r="S105" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -9083,7 +9151,7 @@
       </c>
       <c r="S106" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -9168,7 +9236,7 @@
       </c>
       <c r="S107" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -9253,7 +9321,7 @@
       </c>
       <c r="S108" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -9338,7 +9406,7 @@
       </c>
       <c r="S109" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -9423,7 +9491,7 @@
       </c>
       <c r="S110" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -9508,7 +9576,7 @@
       </c>
       <c r="S111" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -9593,7 +9661,7 @@
       </c>
       <c r="S112" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -9678,7 +9746,7 @@
       </c>
       <c r="S113" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -9763,7 +9831,7 @@
       </c>
       <c r="S114" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -9848,7 +9916,7 @@
       </c>
       <c r="S115" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -9933,7 +10001,7 @@
       </c>
       <c r="S116" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -10018,7 +10086,7 @@
       </c>
       <c r="S117" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -10103,7 +10171,7 @@
       </c>
       <c r="S118" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -10188,7 +10256,7 @@
       </c>
       <c r="S119" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -10273,7 +10341,7 @@
       </c>
       <c r="S120" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -10358,7 +10426,7 @@
       </c>
       <c r="S121" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -10443,7 +10511,7 @@
       </c>
       <c r="S122" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -10528,7 +10596,7 @@
       </c>
       <c r="S123" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -10613,7 +10681,7 @@
       </c>
       <c r="S124" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -10698,7 +10766,7 @@
       </c>
       <c r="S125" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -10783,7 +10851,7 @@
       </c>
       <c r="S126" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -10868,7 +10936,7 @@
       </c>
       <c r="S127" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -10953,7 +11021,7 @@
       </c>
       <c r="S128" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -11038,7 +11106,7 @@
       </c>
       <c r="S129" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -11123,7 +11191,7 @@
       </c>
       <c r="S130" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -11208,7 +11276,7 @@
       </c>
       <c r="S131" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -11293,7 +11361,7 @@
       </c>
       <c r="S132" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -11378,7 +11446,7 @@
       </c>
       <c r="S133" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -11463,7 +11531,7 @@
       </c>
       <c r="S134" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -11548,7 +11616,7 @@
       </c>
       <c r="S135" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -11633,7 +11701,7 @@
       </c>
       <c r="S136" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -11718,7 +11786,7 @@
       </c>
       <c r="S137" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -11803,7 +11871,7 @@
       </c>
       <c r="S138" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -11888,7 +11956,7 @@
       </c>
       <c r="S139" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -11973,7 +12041,7 @@
       </c>
       <c r="S140" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -12058,7 +12126,7 @@
       </c>
       <c r="S141" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -12190,7 +12258,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -12270,7 +12338,7 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>{"dataset_id": "bcv_pib_historico_anual", "title": "Producto interno bruto histórico anual", "table": "PIB histórico anual", "source_file": "7_1_14_anual.xls", "base": "1957/1968/1984/1997", "price_type": "Precios constantes", "measure": "Nivel", "frequency": "Anual", "period": "2017", "year": 2017, "quarter": null, "classification": "Total economía", "component": "Producto interno bruto", "value": 392393.12, "unit": "Millones de bolívares a precios constantes", "status": "", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/7_1_14_anual.xls", "fetched_at": "2026-07-22T10:52:06Z"}</t>
+          <t>{"dataset_id": "bcv_pib_historico_anual", "title": "Producto interno bruto histórico anual", "table": "PIB histórico anual", "source_file": "7_1_14_anual.xls", "base": "1957/1968/1984/1997", "price_type": "Precios constantes", "measure": "Nivel", "frequency": "Anual", "period": "2017", "year": 2017, "quarter": null, "classification": "Total economía", "component": "Producto interno bruto", "value": 392393.12, "unit": "Millones de bolívares a precios constantes", "status": "", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/7_1_14_anual.xls", "fetched_at": "2026-07-22T15:17:12Z"}</t>
         </is>
       </c>
     </row>

--- a/assets/data/bcv/excel/ove_bcv_pib_historico_anual.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_pib_historico_anual.xlsx
@@ -736,7 +736,7 @@
       </c>
       <c r="S7" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -821,7 +821,7 @@
       </c>
       <c r="S8" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -906,7 +906,7 @@
       </c>
       <c r="S9" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -991,7 +991,7 @@
       </c>
       <c r="S10" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="S11" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -1161,7 +1161,7 @@
       </c>
       <c r="S12" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -1246,7 +1246,7 @@
       </c>
       <c r="S13" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -1331,7 +1331,7 @@
       </c>
       <c r="S14" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -1416,7 +1416,7 @@
       </c>
       <c r="S15" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -1501,7 +1501,7 @@
       </c>
       <c r="S16" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -1586,7 +1586,7 @@
       </c>
       <c r="S17" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -1671,7 +1671,7 @@
       </c>
       <c r="S18" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -1756,7 +1756,7 @@
       </c>
       <c r="S19" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -1841,7 +1841,7 @@
       </c>
       <c r="S20" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -1926,7 +1926,7 @@
       </c>
       <c r="S21" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -2011,7 +2011,7 @@
       </c>
       <c r="S22" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="S23" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -2181,7 +2181,7 @@
       </c>
       <c r="S24" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -2266,7 +2266,7 @@
       </c>
       <c r="S25" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -2351,7 +2351,7 @@
       </c>
       <c r="S26" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -2436,7 +2436,7 @@
       </c>
       <c r="S27" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -2521,7 +2521,7 @@
       </c>
       <c r="S28" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -2606,7 +2606,7 @@
       </c>
       <c r="S29" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -2691,7 +2691,7 @@
       </c>
       <c r="S30" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -2776,7 +2776,7 @@
       </c>
       <c r="S31" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -2861,7 +2861,7 @@
       </c>
       <c r="S32" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -2946,7 +2946,7 @@
       </c>
       <c r="S33" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -3031,7 +3031,7 @@
       </c>
       <c r="S34" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -3116,7 +3116,7 @@
       </c>
       <c r="S35" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -3201,7 +3201,7 @@
       </c>
       <c r="S36" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -3286,7 +3286,7 @@
       </c>
       <c r="S37" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -3371,7 +3371,7 @@
       </c>
       <c r="S38" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -3456,7 +3456,7 @@
       </c>
       <c r="S39" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -3541,7 +3541,7 @@
       </c>
       <c r="S40" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -3626,7 +3626,7 @@
       </c>
       <c r="S41" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -3711,7 +3711,7 @@
       </c>
       <c r="S42" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -3796,7 +3796,7 @@
       </c>
       <c r="S43" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -3881,7 +3881,7 @@
       </c>
       <c r="S44" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -3966,7 +3966,7 @@
       </c>
       <c r="S45" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -4051,7 +4051,7 @@
       </c>
       <c r="S46" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -4136,7 +4136,7 @@
       </c>
       <c r="S47" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -4221,7 +4221,7 @@
       </c>
       <c r="S48" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -4306,7 +4306,7 @@
       </c>
       <c r="S49" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -4391,7 +4391,7 @@
       </c>
       <c r="S50" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -4476,7 +4476,7 @@
       </c>
       <c r="S51" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -4561,7 +4561,7 @@
       </c>
       <c r="S52" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -4646,7 +4646,7 @@
       </c>
       <c r="S53" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -4731,7 +4731,7 @@
       </c>
       <c r="S54" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -4816,7 +4816,7 @@
       </c>
       <c r="S55" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -4901,7 +4901,7 @@
       </c>
       <c r="S56" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -4986,7 +4986,7 @@
       </c>
       <c r="S57" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -5071,7 +5071,7 @@
       </c>
       <c r="S58" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -5156,7 +5156,7 @@
       </c>
       <c r="S59" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -5241,7 +5241,7 @@
       </c>
       <c r="S60" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -5326,7 +5326,7 @@
       </c>
       <c r="S61" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -5411,7 +5411,7 @@
       </c>
       <c r="S62" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -5496,7 +5496,7 @@
       </c>
       <c r="S63" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -5581,7 +5581,7 @@
       </c>
       <c r="S64" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -5666,7 +5666,7 @@
       </c>
       <c r="S65" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -5751,7 +5751,7 @@
       </c>
       <c r="S66" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -5836,7 +5836,7 @@
       </c>
       <c r="S67" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -5921,7 +5921,7 @@
       </c>
       <c r="S68" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -6006,7 +6006,7 @@
       </c>
       <c r="S69" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -6091,7 +6091,7 @@
       </c>
       <c r="S70" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -6176,7 +6176,7 @@
       </c>
       <c r="S71" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -6261,7 +6261,7 @@
       </c>
       <c r="S72" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -6346,7 +6346,7 @@
       </c>
       <c r="S73" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -6431,7 +6431,7 @@
       </c>
       <c r="S74" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -6516,7 +6516,7 @@
       </c>
       <c r="S75" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -6601,7 +6601,7 @@
       </c>
       <c r="S76" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -6686,7 +6686,7 @@
       </c>
       <c r="S77" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -6771,7 +6771,7 @@
       </c>
       <c r="S78" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -6856,7 +6856,7 @@
       </c>
       <c r="S79" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -6941,7 +6941,7 @@
       </c>
       <c r="S80" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -7026,7 +7026,7 @@
       </c>
       <c r="S81" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -7111,7 +7111,7 @@
       </c>
       <c r="S82" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -7196,7 +7196,7 @@
       </c>
       <c r="S83" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -7281,7 +7281,7 @@
       </c>
       <c r="S84" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -7366,7 +7366,7 @@
       </c>
       <c r="S85" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -7451,7 +7451,7 @@
       </c>
       <c r="S86" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -7536,7 +7536,7 @@
       </c>
       <c r="S87" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -7621,7 +7621,7 @@
       </c>
       <c r="S88" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -7706,7 +7706,7 @@
       </c>
       <c r="S89" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -7791,7 +7791,7 @@
       </c>
       <c r="S90" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -7876,7 +7876,7 @@
       </c>
       <c r="S91" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -7961,7 +7961,7 @@
       </c>
       <c r="S92" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -8046,7 +8046,7 @@
       </c>
       <c r="S93" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -8131,7 +8131,7 @@
       </c>
       <c r="S94" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -8216,7 +8216,7 @@
       </c>
       <c r="S95" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -8301,7 +8301,7 @@
       </c>
       <c r="S96" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -8386,7 +8386,7 @@
       </c>
       <c r="S97" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -8471,7 +8471,7 @@
       </c>
       <c r="S98" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -8556,7 +8556,7 @@
       </c>
       <c r="S99" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -8641,7 +8641,7 @@
       </c>
       <c r="S100" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -8726,7 +8726,7 @@
       </c>
       <c r="S101" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -8811,7 +8811,7 @@
       </c>
       <c r="S102" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -8896,7 +8896,7 @@
       </c>
       <c r="S103" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -8981,7 +8981,7 @@
       </c>
       <c r="S104" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -9066,7 +9066,7 @@
       </c>
       <c r="S105" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -9151,7 +9151,7 @@
       </c>
       <c r="S106" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -9236,7 +9236,7 @@
       </c>
       <c r="S107" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -9321,7 +9321,7 @@
       </c>
       <c r="S108" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -9406,7 +9406,7 @@
       </c>
       <c r="S109" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -9491,7 +9491,7 @@
       </c>
       <c r="S110" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -9576,7 +9576,7 @@
       </c>
       <c r="S111" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -9661,7 +9661,7 @@
       </c>
       <c r="S112" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -9746,7 +9746,7 @@
       </c>
       <c r="S113" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -9831,7 +9831,7 @@
       </c>
       <c r="S114" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -9916,7 +9916,7 @@
       </c>
       <c r="S115" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -10001,7 +10001,7 @@
       </c>
       <c r="S116" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -10086,7 +10086,7 @@
       </c>
       <c r="S117" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -10171,7 +10171,7 @@
       </c>
       <c r="S118" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -10256,7 +10256,7 @@
       </c>
       <c r="S119" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -10341,7 +10341,7 @@
       </c>
       <c r="S120" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -10426,7 +10426,7 @@
       </c>
       <c r="S121" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -10511,7 +10511,7 @@
       </c>
       <c r="S122" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -10596,7 +10596,7 @@
       </c>
       <c r="S123" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -10681,7 +10681,7 @@
       </c>
       <c r="S124" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -10766,7 +10766,7 @@
       </c>
       <c r="S125" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -10851,7 +10851,7 @@
       </c>
       <c r="S126" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -10936,7 +10936,7 @@
       </c>
       <c r="S127" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -11021,7 +11021,7 @@
       </c>
       <c r="S128" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -11106,7 +11106,7 @@
       </c>
       <c r="S129" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -11191,7 +11191,7 @@
       </c>
       <c r="S130" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -11276,7 +11276,7 @@
       </c>
       <c r="S131" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -11361,7 +11361,7 @@
       </c>
       <c r="S132" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -11446,7 +11446,7 @@
       </c>
       <c r="S133" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -11531,7 +11531,7 @@
       </c>
       <c r="S134" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -11616,7 +11616,7 @@
       </c>
       <c r="S135" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -11701,7 +11701,7 @@
       </c>
       <c r="S136" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -11786,7 +11786,7 @@
       </c>
       <c r="S137" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -11871,7 +11871,7 @@
       </c>
       <c r="S138" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -11956,7 +11956,7 @@
       </c>
       <c r="S139" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -12041,7 +12041,7 @@
       </c>
       <c r="S140" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -12126,7 +12126,7 @@
       </c>
       <c r="S141" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -12258,7 +12258,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -12338,7 +12338,7 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>{"dataset_id": "bcv_pib_historico_anual", "title": "Producto interno bruto histórico anual", "table": "PIB histórico anual", "source_file": "7_1_14_anual.xls", "base": "1957/1968/1984/1997", "price_type": "Precios constantes", "measure": "Nivel", "frequency": "Anual", "period": "2017", "year": 2017, "quarter": null, "classification": "Total economía", "component": "Producto interno bruto", "value": 392393.12, "unit": "Millones de bolívares a precios constantes", "status": "", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/7_1_14_anual.xls", "fetched_at": "2026-07-22T15:17:12Z"}</t>
+          <t>{"dataset_id": "bcv_pib_historico_anual", "title": "Producto interno bruto histórico anual", "table": "PIB histórico anual", "source_file": "7_1_14_anual.xls", "base": "1957/1968/1984/1997", "price_type": "Precios constantes", "measure": "Nivel", "frequency": "Anual", "period": "2017", "year": 2017, "quarter": null, "classification": "Total economía", "component": "Producto interno bruto", "value": 392393.12, "unit": "Millones de bolívares a precios constantes", "status": "", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/7_1_14_anual.xls", "fetched_at": "2026-07-22T21:35:45Z"}</t>
         </is>
       </c>
     </row>

--- a/assets/data/bcv/excel/ove_bcv_pib_historico_anual.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_pib_historico_anual.xlsx
@@ -736,7 +736,7 @@
       </c>
       <c r="S7" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -821,7 +821,7 @@
       </c>
       <c r="S8" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -906,7 +906,7 @@
       </c>
       <c r="S9" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -991,7 +991,7 @@
       </c>
       <c r="S10" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="S11" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -1161,7 +1161,7 @@
       </c>
       <c r="S12" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -1246,7 +1246,7 @@
       </c>
       <c r="S13" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -1331,7 +1331,7 @@
       </c>
       <c r="S14" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -1416,7 +1416,7 @@
       </c>
       <c r="S15" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -1501,7 +1501,7 @@
       </c>
       <c r="S16" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -1586,7 +1586,7 @@
       </c>
       <c r="S17" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -1671,7 +1671,7 @@
       </c>
       <c r="S18" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -1756,7 +1756,7 @@
       </c>
       <c r="S19" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -1841,7 +1841,7 @@
       </c>
       <c r="S20" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -1926,7 +1926,7 @@
       </c>
       <c r="S21" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -2011,7 +2011,7 @@
       </c>
       <c r="S22" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="S23" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -2181,7 +2181,7 @@
       </c>
       <c r="S24" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -2266,7 +2266,7 @@
       </c>
       <c r="S25" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -2351,7 +2351,7 @@
       </c>
       <c r="S26" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -2436,7 +2436,7 @@
       </c>
       <c r="S27" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -2521,7 +2521,7 @@
       </c>
       <c r="S28" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -2606,7 +2606,7 @@
       </c>
       <c r="S29" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -2691,7 +2691,7 @@
       </c>
       <c r="S30" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -2776,7 +2776,7 @@
       </c>
       <c r="S31" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -2861,7 +2861,7 @@
       </c>
       <c r="S32" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -2946,7 +2946,7 @@
       </c>
       <c r="S33" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -3031,7 +3031,7 @@
       </c>
       <c r="S34" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -3116,7 +3116,7 @@
       </c>
       <c r="S35" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -3201,7 +3201,7 @@
       </c>
       <c r="S36" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -3286,7 +3286,7 @@
       </c>
       <c r="S37" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -3371,7 +3371,7 @@
       </c>
       <c r="S38" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -3456,7 +3456,7 @@
       </c>
       <c r="S39" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -3541,7 +3541,7 @@
       </c>
       <c r="S40" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -3626,7 +3626,7 @@
       </c>
       <c r="S41" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -3711,7 +3711,7 @@
       </c>
       <c r="S42" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -3796,7 +3796,7 @@
       </c>
       <c r="S43" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -3881,7 +3881,7 @@
       </c>
       <c r="S44" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -3966,7 +3966,7 @@
       </c>
       <c r="S45" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -4051,7 +4051,7 @@
       </c>
       <c r="S46" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -4136,7 +4136,7 @@
       </c>
       <c r="S47" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -4221,7 +4221,7 @@
       </c>
       <c r="S48" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -4306,7 +4306,7 @@
       </c>
       <c r="S49" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -4391,7 +4391,7 @@
       </c>
       <c r="S50" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -4476,7 +4476,7 @@
       </c>
       <c r="S51" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -4561,7 +4561,7 @@
       </c>
       <c r="S52" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -4646,7 +4646,7 @@
       </c>
       <c r="S53" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -4731,7 +4731,7 @@
       </c>
       <c r="S54" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -4816,7 +4816,7 @@
       </c>
       <c r="S55" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -4901,7 +4901,7 @@
       </c>
       <c r="S56" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -4986,7 +4986,7 @@
       </c>
       <c r="S57" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -5071,7 +5071,7 @@
       </c>
       <c r="S58" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -5156,7 +5156,7 @@
       </c>
       <c r="S59" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -5241,7 +5241,7 @@
       </c>
       <c r="S60" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -5326,7 +5326,7 @@
       </c>
       <c r="S61" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -5411,7 +5411,7 @@
       </c>
       <c r="S62" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -5496,7 +5496,7 @@
       </c>
       <c r="S63" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -5581,7 +5581,7 @@
       </c>
       <c r="S64" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -5666,7 +5666,7 @@
       </c>
       <c r="S65" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -5751,7 +5751,7 @@
       </c>
       <c r="S66" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -5836,7 +5836,7 @@
       </c>
       <c r="S67" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -5921,7 +5921,7 @@
       </c>
       <c r="S68" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -6006,7 +6006,7 @@
       </c>
       <c r="S69" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -6091,7 +6091,7 @@
       </c>
       <c r="S70" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -6176,7 +6176,7 @@
       </c>
       <c r="S71" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -6261,7 +6261,7 @@
       </c>
       <c r="S72" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -6346,7 +6346,7 @@
       </c>
       <c r="S73" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -6431,7 +6431,7 @@
       </c>
       <c r="S74" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -6516,7 +6516,7 @@
       </c>
       <c r="S75" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -6601,7 +6601,7 @@
       </c>
       <c r="S76" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -6686,7 +6686,7 @@
       </c>
       <c r="S77" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -6771,7 +6771,7 @@
       </c>
       <c r="S78" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -6856,7 +6856,7 @@
       </c>
       <c r="S79" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -6941,7 +6941,7 @@
       </c>
       <c r="S80" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -7026,7 +7026,7 @@
       </c>
       <c r="S81" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -7111,7 +7111,7 @@
       </c>
       <c r="S82" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -7196,7 +7196,7 @@
       </c>
       <c r="S83" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -7281,7 +7281,7 @@
       </c>
       <c r="S84" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -7366,7 +7366,7 @@
       </c>
       <c r="S85" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -7451,7 +7451,7 @@
       </c>
       <c r="S86" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -7536,7 +7536,7 @@
       </c>
       <c r="S87" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -7621,7 +7621,7 @@
       </c>
       <c r="S88" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -7706,7 +7706,7 @@
       </c>
       <c r="S89" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -7791,7 +7791,7 @@
       </c>
       <c r="S90" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -7876,7 +7876,7 @@
       </c>
       <c r="S91" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -7961,7 +7961,7 @@
       </c>
       <c r="S92" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -8046,7 +8046,7 @@
       </c>
       <c r="S93" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -8131,7 +8131,7 @@
       </c>
       <c r="S94" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -8216,7 +8216,7 @@
       </c>
       <c r="S95" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -8301,7 +8301,7 @@
       </c>
       <c r="S96" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -8386,7 +8386,7 @@
       </c>
       <c r="S97" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -8471,7 +8471,7 @@
       </c>
       <c r="S98" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -8556,7 +8556,7 @@
       </c>
       <c r="S99" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -8641,7 +8641,7 @@
       </c>
       <c r="S100" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -8726,7 +8726,7 @@
       </c>
       <c r="S101" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -8811,7 +8811,7 @@
       </c>
       <c r="S102" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -8896,7 +8896,7 @@
       </c>
       <c r="S103" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -8981,7 +8981,7 @@
       </c>
       <c r="S104" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -9066,7 +9066,7 @@
       </c>
       <c r="S105" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -9151,7 +9151,7 @@
       </c>
       <c r="S106" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -9236,7 +9236,7 @@
       </c>
       <c r="S107" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -9321,7 +9321,7 @@
       </c>
       <c r="S108" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -9406,7 +9406,7 @@
       </c>
       <c r="S109" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -9491,7 +9491,7 @@
       </c>
       <c r="S110" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -9576,7 +9576,7 @@
       </c>
       <c r="S111" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -9661,7 +9661,7 @@
       </c>
       <c r="S112" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -9746,7 +9746,7 @@
       </c>
       <c r="S113" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -9831,7 +9831,7 @@
       </c>
       <c r="S114" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -9916,7 +9916,7 @@
       </c>
       <c r="S115" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -10001,7 +10001,7 @@
       </c>
       <c r="S116" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -10086,7 +10086,7 @@
       </c>
       <c r="S117" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -10171,7 +10171,7 @@
       </c>
       <c r="S118" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -10256,7 +10256,7 @@
       </c>
       <c r="S119" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -10341,7 +10341,7 @@
       </c>
       <c r="S120" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -10426,7 +10426,7 @@
       </c>
       <c r="S121" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -10511,7 +10511,7 @@
       </c>
       <c r="S122" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -10596,7 +10596,7 @@
       </c>
       <c r="S123" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -10681,7 +10681,7 @@
       </c>
       <c r="S124" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -10766,7 +10766,7 @@
       </c>
       <c r="S125" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -10851,7 +10851,7 @@
       </c>
       <c r="S126" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -10936,7 +10936,7 @@
       </c>
       <c r="S127" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -11021,7 +11021,7 @@
       </c>
       <c r="S128" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -11106,7 +11106,7 @@
       </c>
       <c r="S129" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -11191,7 +11191,7 @@
       </c>
       <c r="S130" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -11276,7 +11276,7 @@
       </c>
       <c r="S131" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -11361,7 +11361,7 @@
       </c>
       <c r="S132" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -11446,7 +11446,7 @@
       </c>
       <c r="S133" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -11531,7 +11531,7 @@
       </c>
       <c r="S134" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -11616,7 +11616,7 @@
       </c>
       <c r="S135" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -11701,7 +11701,7 @@
       </c>
       <c r="S136" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -11786,7 +11786,7 @@
       </c>
       <c r="S137" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -11871,7 +11871,7 @@
       </c>
       <c r="S138" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -11956,7 +11956,7 @@
       </c>
       <c r="S139" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -12041,7 +12041,7 @@
       </c>
       <c r="S140" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -12126,7 +12126,7 @@
       </c>
       <c r="S141" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -12258,7 +12258,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -12338,7 +12338,7 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>{"dataset_id": "bcv_pib_historico_anual", "title": "Producto interno bruto histórico anual", "table": "PIB histórico anual", "source_file": "7_1_14_anual.xls", "base": "1957/1968/1984/1997", "price_type": "Precios constantes", "measure": "Nivel", "frequency": "Anual", "period": "2017", "year": 2017, "quarter": null, "classification": "Total economía", "component": "Producto interno bruto", "value": 392393.12, "unit": "Millones de bolívares a precios constantes", "status": "", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/7_1_14_anual.xls", "fetched_at": "2026-07-22T21:35:45Z"}</t>
+          <t>{"dataset_id": "bcv_pib_historico_anual", "title": "Producto interno bruto histórico anual", "table": "PIB histórico anual", "source_file": "7_1_14_anual.xls", "base": "1957/1968/1984/1997", "price_type": "Precios constantes", "measure": "Nivel", "frequency": "Anual", "period": "2017", "year": 2017, "quarter": null, "classification": "Total economía", "component": "Producto interno bruto", "value": 392393.12, "unit": "Millones de bolívares a precios constantes", "status": "", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/7_1_14_anual.xls", "fetched_at": "2026-07-23T21:35:03Z"}</t>
         </is>
       </c>
     </row>

--- a/assets/data/bcv/excel/ove_bcv_pib_historico_anual.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_pib_historico_anual.xlsx
@@ -736,7 +736,7 @@
       </c>
       <c r="S7" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -821,7 +821,7 @@
       </c>
       <c r="S8" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -906,7 +906,7 @@
       </c>
       <c r="S9" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -991,7 +991,7 @@
       </c>
       <c r="S10" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="S11" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -1161,7 +1161,7 @@
       </c>
       <c r="S12" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -1246,7 +1246,7 @@
       </c>
       <c r="S13" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -1331,7 +1331,7 @@
       </c>
       <c r="S14" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -1416,7 +1416,7 @@
       </c>
       <c r="S15" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -1501,7 +1501,7 @@
       </c>
       <c r="S16" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -1586,7 +1586,7 @@
       </c>
       <c r="S17" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -1671,7 +1671,7 @@
       </c>
       <c r="S18" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -1756,7 +1756,7 @@
       </c>
       <c r="S19" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -1841,7 +1841,7 @@
       </c>
       <c r="S20" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -1926,7 +1926,7 @@
       </c>
       <c r="S21" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -2011,7 +2011,7 @@
       </c>
       <c r="S22" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="S23" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -2181,7 +2181,7 @@
       </c>
       <c r="S24" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -2266,7 +2266,7 @@
       </c>
       <c r="S25" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -2351,7 +2351,7 @@
       </c>
       <c r="S26" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -2436,7 +2436,7 @@
       </c>
       <c r="S27" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -2521,7 +2521,7 @@
       </c>
       <c r="S28" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -2606,7 +2606,7 @@
       </c>
       <c r="S29" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -2691,7 +2691,7 @@
       </c>
       <c r="S30" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -2776,7 +2776,7 @@
       </c>
       <c r="S31" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -2861,7 +2861,7 @@
       </c>
       <c r="S32" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -2946,7 +2946,7 @@
       </c>
       <c r="S33" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -3031,7 +3031,7 @@
       </c>
       <c r="S34" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -3116,7 +3116,7 @@
       </c>
       <c r="S35" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -3201,7 +3201,7 @@
       </c>
       <c r="S36" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -3286,7 +3286,7 @@
       </c>
       <c r="S37" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -3371,7 +3371,7 @@
       </c>
       <c r="S38" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -3456,7 +3456,7 @@
       </c>
       <c r="S39" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -3541,7 +3541,7 @@
       </c>
       <c r="S40" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -3626,7 +3626,7 @@
       </c>
       <c r="S41" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -3711,7 +3711,7 @@
       </c>
       <c r="S42" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -3796,7 +3796,7 @@
       </c>
       <c r="S43" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -3881,7 +3881,7 @@
       </c>
       <c r="S44" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -3966,7 +3966,7 @@
       </c>
       <c r="S45" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -4051,7 +4051,7 @@
       </c>
       <c r="S46" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -4136,7 +4136,7 @@
       </c>
       <c r="S47" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -4221,7 +4221,7 @@
       </c>
       <c r="S48" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -4306,7 +4306,7 @@
       </c>
       <c r="S49" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -4391,7 +4391,7 @@
       </c>
       <c r="S50" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -4476,7 +4476,7 @@
       </c>
       <c r="S51" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -4561,7 +4561,7 @@
       </c>
       <c r="S52" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -4646,7 +4646,7 @@
       </c>
       <c r="S53" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -4731,7 +4731,7 @@
       </c>
       <c r="S54" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -4816,7 +4816,7 @@
       </c>
       <c r="S55" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -4901,7 +4901,7 @@
       </c>
       <c r="S56" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -4986,7 +4986,7 @@
       </c>
       <c r="S57" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -5071,7 +5071,7 @@
       </c>
       <c r="S58" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -5156,7 +5156,7 @@
       </c>
       <c r="S59" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -5241,7 +5241,7 @@
       </c>
       <c r="S60" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -5326,7 +5326,7 @@
       </c>
       <c r="S61" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -5411,7 +5411,7 @@
       </c>
       <c r="S62" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -5496,7 +5496,7 @@
       </c>
       <c r="S63" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -5581,7 +5581,7 @@
       </c>
       <c r="S64" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -5666,7 +5666,7 @@
       </c>
       <c r="S65" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -5751,7 +5751,7 @@
       </c>
       <c r="S66" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -5836,7 +5836,7 @@
       </c>
       <c r="S67" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -5921,7 +5921,7 @@
       </c>
       <c r="S68" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -6006,7 +6006,7 @@
       </c>
       <c r="S69" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -6091,7 +6091,7 @@
       </c>
       <c r="S70" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -6176,7 +6176,7 @@
       </c>
       <c r="S71" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -6261,7 +6261,7 @@
       </c>
       <c r="S72" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -6346,7 +6346,7 @@
       </c>
       <c r="S73" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -6431,7 +6431,7 @@
       </c>
       <c r="S74" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -6516,7 +6516,7 @@
       </c>
       <c r="S75" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -6601,7 +6601,7 @@
       </c>
       <c r="S76" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -6686,7 +6686,7 @@
       </c>
       <c r="S77" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -6771,7 +6771,7 @@
       </c>
       <c r="S78" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -6856,7 +6856,7 @@
       </c>
       <c r="S79" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -6941,7 +6941,7 @@
       </c>
       <c r="S80" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -7026,7 +7026,7 @@
       </c>
       <c r="S81" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -7111,7 +7111,7 @@
       </c>
       <c r="S82" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -7196,7 +7196,7 @@
       </c>
       <c r="S83" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -7281,7 +7281,7 @@
       </c>
       <c r="S84" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -7366,7 +7366,7 @@
       </c>
       <c r="S85" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -7451,7 +7451,7 @@
       </c>
       <c r="S86" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -7536,7 +7536,7 @@
       </c>
       <c r="S87" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -7621,7 +7621,7 @@
       </c>
       <c r="S88" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -7706,7 +7706,7 @@
       </c>
       <c r="S89" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -7791,7 +7791,7 @@
       </c>
       <c r="S90" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -7876,7 +7876,7 @@
       </c>
       <c r="S91" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -7961,7 +7961,7 @@
       </c>
       <c r="S92" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -8046,7 +8046,7 @@
       </c>
       <c r="S93" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -8131,7 +8131,7 @@
       </c>
       <c r="S94" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -8216,7 +8216,7 @@
       </c>
       <c r="S95" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -8301,7 +8301,7 @@
       </c>
       <c r="S96" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -8386,7 +8386,7 @@
       </c>
       <c r="S97" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -8471,7 +8471,7 @@
       </c>
       <c r="S98" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -8556,7 +8556,7 @@
       </c>
       <c r="S99" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -8641,7 +8641,7 @@
       </c>
       <c r="S100" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -8726,7 +8726,7 @@
       </c>
       <c r="S101" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -8811,7 +8811,7 @@
       </c>
       <c r="S102" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -8896,7 +8896,7 @@
       </c>
       <c r="S103" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -8981,7 +8981,7 @@
       </c>
       <c r="S104" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -9066,7 +9066,7 @@
       </c>
       <c r="S105" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -9151,7 +9151,7 @@
       </c>
       <c r="S106" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -9236,7 +9236,7 @@
       </c>
       <c r="S107" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -9321,7 +9321,7 @@
       </c>
       <c r="S108" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -9406,7 +9406,7 @@
       </c>
       <c r="S109" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -9491,7 +9491,7 @@
       </c>
       <c r="S110" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -9576,7 +9576,7 @@
       </c>
       <c r="S111" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -9661,7 +9661,7 @@
       </c>
       <c r="S112" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -9746,7 +9746,7 @@
       </c>
       <c r="S113" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -9831,7 +9831,7 @@
       </c>
       <c r="S114" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -9916,7 +9916,7 @@
       </c>
       <c r="S115" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -10001,7 +10001,7 @@
       </c>
       <c r="S116" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -10086,7 +10086,7 @@
       </c>
       <c r="S117" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -10171,7 +10171,7 @@
       </c>
       <c r="S118" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -10256,7 +10256,7 @@
       </c>
       <c r="S119" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -10341,7 +10341,7 @@
       </c>
       <c r="S120" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -10426,7 +10426,7 @@
       </c>
       <c r="S121" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -10511,7 +10511,7 @@
       </c>
       <c r="S122" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -10596,7 +10596,7 @@
       </c>
       <c r="S123" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -10681,7 +10681,7 @@
       </c>
       <c r="S124" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -10766,7 +10766,7 @@
       </c>
       <c r="S125" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -10851,7 +10851,7 @@
       </c>
       <c r="S126" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -10936,7 +10936,7 @@
       </c>
       <c r="S127" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -11021,7 +11021,7 @@
       </c>
       <c r="S128" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -11106,7 +11106,7 @@
       </c>
       <c r="S129" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -11191,7 +11191,7 @@
       </c>
       <c r="S130" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -11276,7 +11276,7 @@
       </c>
       <c r="S131" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -11361,7 +11361,7 @@
       </c>
       <c r="S132" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -11446,7 +11446,7 @@
       </c>
       <c r="S133" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -11531,7 +11531,7 @@
       </c>
       <c r="S134" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -11616,7 +11616,7 @@
       </c>
       <c r="S135" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -11701,7 +11701,7 @@
       </c>
       <c r="S136" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -11786,7 +11786,7 @@
       </c>
       <c r="S137" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -11871,7 +11871,7 @@
       </c>
       <c r="S138" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -11956,7 +11956,7 @@
       </c>
       <c r="S139" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -12041,7 +12041,7 @@
       </c>
       <c r="S140" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -12126,7 +12126,7 @@
       </c>
       <c r="S141" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -12258,7 +12258,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -12338,7 +12338,7 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>{"dataset_id": "bcv_pib_historico_anual", "title": "Producto interno bruto histórico anual", "table": "PIB histórico anual", "source_file": "7_1_14_anual.xls", "base": "1957/1968/1984/1997", "price_type": "Precios constantes", "measure": "Nivel", "frequency": "Anual", "period": "2017", "year": 2017, "quarter": null, "classification": "Total economía", "component": "Producto interno bruto", "value": 392393.12, "unit": "Millones de bolívares a precios constantes", "status": "", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/7_1_14_anual.xls", "fetched_at": "2026-07-23T21:35:03Z"}</t>
+          <t>{"dataset_id": "bcv_pib_historico_anual", "title": "Producto interno bruto histórico anual", "table": "PIB histórico anual", "source_file": "7_1_14_anual.xls", "base": "1957/1968/1984/1997", "price_type": "Precios constantes", "measure": "Nivel", "frequency": "Anual", "period": "2017", "year": 2017, "quarter": null, "classification": "Total economía", "component": "Producto interno bruto", "value": 392393.12, "unit": "Millones de bolívares a precios constantes", "status": "", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/7_1_14_anual.xls", "fetched_at": "2026-07-24T21:36:09Z"}</t>
         </is>
       </c>
     </row>

--- a/assets/data/bcv/excel/ove_bcv_pib_historico_anual.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_pib_historico_anual.xlsx
@@ -736,7 +736,7 @@
       </c>
       <c r="S7" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -821,7 +821,7 @@
       </c>
       <c r="S8" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -906,7 +906,7 @@
       </c>
       <c r="S9" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -991,7 +991,7 @@
       </c>
       <c r="S10" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="S11" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -1161,7 +1161,7 @@
       </c>
       <c r="S12" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -1246,7 +1246,7 @@
       </c>
       <c r="S13" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -1331,7 +1331,7 @@
       </c>
       <c r="S14" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -1416,7 +1416,7 @@
       </c>
       <c r="S15" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -1501,7 +1501,7 @@
       </c>
       <c r="S16" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -1586,7 +1586,7 @@
       </c>
       <c r="S17" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -1671,7 +1671,7 @@
       </c>
       <c r="S18" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -1756,7 +1756,7 @@
       </c>
       <c r="S19" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -1841,7 +1841,7 @@
       </c>
       <c r="S20" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -1926,7 +1926,7 @@
       </c>
       <c r="S21" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -2011,7 +2011,7 @@
       </c>
       <c r="S22" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="S23" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -2181,7 +2181,7 @@
       </c>
       <c r="S24" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -2266,7 +2266,7 @@
       </c>
       <c r="S25" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -2351,7 +2351,7 @@
       </c>
       <c r="S26" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -2436,7 +2436,7 @@
       </c>
       <c r="S27" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -2521,7 +2521,7 @@
       </c>
       <c r="S28" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -2606,7 +2606,7 @@
       </c>
       <c r="S29" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -2691,7 +2691,7 @@
       </c>
       <c r="S30" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -2776,7 +2776,7 @@
       </c>
       <c r="S31" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -2861,7 +2861,7 @@
       </c>
       <c r="S32" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -2946,7 +2946,7 @@
       </c>
       <c r="S33" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -3031,7 +3031,7 @@
       </c>
       <c r="S34" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -3116,7 +3116,7 @@
       </c>
       <c r="S35" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -3201,7 +3201,7 @@
       </c>
       <c r="S36" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -3286,7 +3286,7 @@
       </c>
       <c r="S37" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -3371,7 +3371,7 @@
       </c>
       <c r="S38" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -3456,7 +3456,7 @@
       </c>
       <c r="S39" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -3541,7 +3541,7 @@
       </c>
       <c r="S40" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -3626,7 +3626,7 @@
       </c>
       <c r="S41" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -3711,7 +3711,7 @@
       </c>
       <c r="S42" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -3796,7 +3796,7 @@
       </c>
       <c r="S43" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -3881,7 +3881,7 @@
       </c>
       <c r="S44" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -3966,7 +3966,7 @@
       </c>
       <c r="S45" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -4051,7 +4051,7 @@
       </c>
       <c r="S46" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -4136,7 +4136,7 @@
       </c>
       <c r="S47" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -4221,7 +4221,7 @@
       </c>
       <c r="S48" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -4306,7 +4306,7 @@
       </c>
       <c r="S49" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -4391,7 +4391,7 @@
       </c>
       <c r="S50" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -4476,7 +4476,7 @@
       </c>
       <c r="S51" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -4561,7 +4561,7 @@
       </c>
       <c r="S52" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -4646,7 +4646,7 @@
       </c>
       <c r="S53" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -4731,7 +4731,7 @@
       </c>
       <c r="S54" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -4816,7 +4816,7 @@
       </c>
       <c r="S55" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -4901,7 +4901,7 @@
       </c>
       <c r="S56" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -4986,7 +4986,7 @@
       </c>
       <c r="S57" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -5071,7 +5071,7 @@
       </c>
       <c r="S58" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -5156,7 +5156,7 @@
       </c>
       <c r="S59" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -5241,7 +5241,7 @@
       </c>
       <c r="S60" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -5326,7 +5326,7 @@
       </c>
       <c r="S61" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -5411,7 +5411,7 @@
       </c>
       <c r="S62" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -5496,7 +5496,7 @@
       </c>
       <c r="S63" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -5581,7 +5581,7 @@
       </c>
       <c r="S64" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -5666,7 +5666,7 @@
       </c>
       <c r="S65" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -5751,7 +5751,7 @@
       </c>
       <c r="S66" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -5836,7 +5836,7 @@
       </c>
       <c r="S67" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -5921,7 +5921,7 @@
       </c>
       <c r="S68" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -6006,7 +6006,7 @@
       </c>
       <c r="S69" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -6091,7 +6091,7 @@
       </c>
       <c r="S70" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -6176,7 +6176,7 @@
       </c>
       <c r="S71" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -6261,7 +6261,7 @@
       </c>
       <c r="S72" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -6346,7 +6346,7 @@
       </c>
       <c r="S73" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -6431,7 +6431,7 @@
       </c>
       <c r="S74" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -6516,7 +6516,7 @@
       </c>
       <c r="S75" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -6601,7 +6601,7 @@
       </c>
       <c r="S76" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -6686,7 +6686,7 @@
       </c>
       <c r="S77" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -6771,7 +6771,7 @@
       </c>
       <c r="S78" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -6856,7 +6856,7 @@
       </c>
       <c r="S79" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -6941,7 +6941,7 @@
       </c>
       <c r="S80" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -7026,7 +7026,7 @@
       </c>
       <c r="S81" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -7111,7 +7111,7 @@
       </c>
       <c r="S82" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -7196,7 +7196,7 @@
       </c>
       <c r="S83" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -7281,7 +7281,7 @@
       </c>
       <c r="S84" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -7366,7 +7366,7 @@
       </c>
       <c r="S85" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -7451,7 +7451,7 @@
       </c>
       <c r="S86" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -7536,7 +7536,7 @@
       </c>
       <c r="S87" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -7621,7 +7621,7 @@
       </c>
       <c r="S88" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -7706,7 +7706,7 @@
       </c>
       <c r="S89" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -7791,7 +7791,7 @@
       </c>
       <c r="S90" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -7876,7 +7876,7 @@
       </c>
       <c r="S91" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -7961,7 +7961,7 @@
       </c>
       <c r="S92" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -8046,7 +8046,7 @@
       </c>
       <c r="S93" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -8131,7 +8131,7 @@
       </c>
       <c r="S94" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -8216,7 +8216,7 @@
       </c>
       <c r="S95" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -8301,7 +8301,7 @@
       </c>
       <c r="S96" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -8386,7 +8386,7 @@
       </c>
       <c r="S97" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -8471,7 +8471,7 @@
       </c>
       <c r="S98" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -8556,7 +8556,7 @@
       </c>
       <c r="S99" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -8641,7 +8641,7 @@
       </c>
       <c r="S100" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -8726,7 +8726,7 @@
       </c>
       <c r="S101" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -8811,7 +8811,7 @@
       </c>
       <c r="S102" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -8896,7 +8896,7 @@
       </c>
       <c r="S103" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -8981,7 +8981,7 @@
       </c>
       <c r="S104" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -9066,7 +9066,7 @@
       </c>
       <c r="S105" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -9151,7 +9151,7 @@
       </c>
       <c r="S106" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -9236,7 +9236,7 @@
       </c>
       <c r="S107" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -9321,7 +9321,7 @@
       </c>
       <c r="S108" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -9406,7 +9406,7 @@
       </c>
       <c r="S109" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -9491,7 +9491,7 @@
       </c>
       <c r="S110" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -9576,7 +9576,7 @@
       </c>
       <c r="S111" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -9661,7 +9661,7 @@
       </c>
       <c r="S112" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -9746,7 +9746,7 @@
       </c>
       <c r="S113" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -9831,7 +9831,7 @@
       </c>
       <c r="S114" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -9916,7 +9916,7 @@
       </c>
       <c r="S115" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -10001,7 +10001,7 @@
       </c>
       <c r="S116" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -10086,7 +10086,7 @@
       </c>
       <c r="S117" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -10171,7 +10171,7 @@
       </c>
       <c r="S118" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -10256,7 +10256,7 @@
       </c>
       <c r="S119" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -10341,7 +10341,7 @@
       </c>
       <c r="S120" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -10426,7 +10426,7 @@
       </c>
       <c r="S121" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -10511,7 +10511,7 @@
       </c>
       <c r="S122" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -10596,7 +10596,7 @@
       </c>
       <c r="S123" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -10681,7 +10681,7 @@
       </c>
       <c r="S124" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -10766,7 +10766,7 @@
       </c>
       <c r="S125" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -10851,7 +10851,7 @@
       </c>
       <c r="S126" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -10936,7 +10936,7 @@
       </c>
       <c r="S127" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -11021,7 +11021,7 @@
       </c>
       <c r="S128" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -11106,7 +11106,7 @@
       </c>
       <c r="S129" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -11191,7 +11191,7 @@
       </c>
       <c r="S130" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -11276,7 +11276,7 @@
       </c>
       <c r="S131" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -11361,7 +11361,7 @@
       </c>
       <c r="S132" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -11446,7 +11446,7 @@
       </c>
       <c r="S133" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -11531,7 +11531,7 @@
       </c>
       <c r="S134" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -11616,7 +11616,7 @@
       </c>
       <c r="S135" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -11701,7 +11701,7 @@
       </c>
       <c r="S136" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -11786,7 +11786,7 @@
       </c>
       <c r="S137" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -11871,7 +11871,7 @@
       </c>
       <c r="S138" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -11956,7 +11956,7 @@
       </c>
       <c r="S139" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -12041,7 +12041,7 @@
       </c>
       <c r="S140" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -12126,7 +12126,7 @@
       </c>
       <c r="S141" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -12258,7 +12258,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -12338,7 +12338,7 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>{"dataset_id": "bcv_pib_historico_anual", "title": "Producto interno bruto histórico anual", "table": "PIB histórico anual", "source_file": "7_1_14_anual.xls", "base": "1957/1968/1984/1997", "price_type": "Precios constantes", "measure": "Nivel", "frequency": "Anual", "period": "2017", "year": 2017, "quarter": null, "classification": "Total economía", "component": "Producto interno bruto", "value": 392393.12, "unit": "Millones de bolívares a precios constantes", "status": "", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/7_1_14_anual.xls", "fetched_at": "2026-07-24T21:36:09Z"}</t>
+          <t>{"dataset_id": "bcv_pib_historico_anual", "title": "Producto interno bruto histórico anual", "table": "PIB histórico anual", "source_file": "7_1_14_anual.xls", "base": "1957/1968/1984/1997", "price_type": "Precios constantes", "measure": "Nivel", "frequency": "Anual", "period": "2017", "year": 2017, "quarter": null, "classification": "Total economía", "component": "Producto interno bruto", "value": 392393.12, "unit": "Millones de bolívares a precios constantes", "status": "", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/7_1_14_anual.xls", "fetched_at": "2026-07-25T21:23:58Z"}</t>
         </is>
       </c>
     </row>

--- a/assets/data/bcv/excel/ove_bcv_pib_historico_anual.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_pib_historico_anual.xlsx
@@ -736,7 +736,7 @@
       </c>
       <c r="S7" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -821,7 +821,7 @@
       </c>
       <c r="S8" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -906,7 +906,7 @@
       </c>
       <c r="S9" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -991,7 +991,7 @@
       </c>
       <c r="S10" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="S11" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -1161,7 +1161,7 @@
       </c>
       <c r="S12" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -1246,7 +1246,7 @@
       </c>
       <c r="S13" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -1331,7 +1331,7 @@
       </c>
       <c r="S14" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -1416,7 +1416,7 @@
       </c>
       <c r="S15" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -1501,7 +1501,7 @@
       </c>
       <c r="S16" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -1586,7 +1586,7 @@
       </c>
       <c r="S17" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -1671,7 +1671,7 @@
       </c>
       <c r="S18" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -1756,7 +1756,7 @@
       </c>
       <c r="S19" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -1841,7 +1841,7 @@
       </c>
       <c r="S20" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -1926,7 +1926,7 @@
       </c>
       <c r="S21" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -2011,7 +2011,7 @@
       </c>
       <c r="S22" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="S23" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -2181,7 +2181,7 @@
       </c>
       <c r="S24" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -2266,7 +2266,7 @@
       </c>
       <c r="S25" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -2351,7 +2351,7 @@
       </c>
       <c r="S26" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -2436,7 +2436,7 @@
       </c>
       <c r="S27" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -2521,7 +2521,7 @@
       </c>
       <c r="S28" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -2606,7 +2606,7 @@
       </c>
       <c r="S29" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -2691,7 +2691,7 @@
       </c>
       <c r="S30" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -2776,7 +2776,7 @@
       </c>
       <c r="S31" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -2861,7 +2861,7 @@
       </c>
       <c r="S32" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -2946,7 +2946,7 @@
       </c>
       <c r="S33" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -3031,7 +3031,7 @@
       </c>
       <c r="S34" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -3116,7 +3116,7 @@
       </c>
       <c r="S35" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -3201,7 +3201,7 @@
       </c>
       <c r="S36" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -3286,7 +3286,7 @@
       </c>
       <c r="S37" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -3371,7 +3371,7 @@
       </c>
       <c r="S38" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -3456,7 +3456,7 @@
       </c>
       <c r="S39" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -3541,7 +3541,7 @@
       </c>
       <c r="S40" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -3626,7 +3626,7 @@
       </c>
       <c r="S41" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -3711,7 +3711,7 @@
       </c>
       <c r="S42" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -3796,7 +3796,7 @@
       </c>
       <c r="S43" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -3881,7 +3881,7 @@
       </c>
       <c r="S44" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -3966,7 +3966,7 @@
       </c>
       <c r="S45" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -4051,7 +4051,7 @@
       </c>
       <c r="S46" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -4136,7 +4136,7 @@
       </c>
       <c r="S47" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -4221,7 +4221,7 @@
       </c>
       <c r="S48" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -4306,7 +4306,7 @@
       </c>
       <c r="S49" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -4391,7 +4391,7 @@
       </c>
       <c r="S50" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -4476,7 +4476,7 @@
       </c>
       <c r="S51" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -4561,7 +4561,7 @@
       </c>
       <c r="S52" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -4646,7 +4646,7 @@
       </c>
       <c r="S53" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -4731,7 +4731,7 @@
       </c>
       <c r="S54" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -4816,7 +4816,7 @@
       </c>
       <c r="S55" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -4901,7 +4901,7 @@
       </c>
       <c r="S56" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -4986,7 +4986,7 @@
       </c>
       <c r="S57" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -5071,7 +5071,7 @@
       </c>
       <c r="S58" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -5156,7 +5156,7 @@
       </c>
       <c r="S59" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -5241,7 +5241,7 @@
       </c>
       <c r="S60" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -5326,7 +5326,7 @@
       </c>
       <c r="S61" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -5411,7 +5411,7 @@
       </c>
       <c r="S62" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -5496,7 +5496,7 @@
       </c>
       <c r="S63" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -5581,7 +5581,7 @@
       </c>
       <c r="S64" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -5666,7 +5666,7 @@
       </c>
       <c r="S65" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -5751,7 +5751,7 @@
       </c>
       <c r="S66" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -5836,7 +5836,7 @@
       </c>
       <c r="S67" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -5921,7 +5921,7 @@
       </c>
       <c r="S68" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -6006,7 +6006,7 @@
       </c>
       <c r="S69" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -6091,7 +6091,7 @@
       </c>
       <c r="S70" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -6176,7 +6176,7 @@
       </c>
       <c r="S71" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -6261,7 +6261,7 @@
       </c>
       <c r="S72" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -6346,7 +6346,7 @@
       </c>
       <c r="S73" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -6431,7 +6431,7 @@
       </c>
       <c r="S74" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -6516,7 +6516,7 @@
       </c>
       <c r="S75" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -6601,7 +6601,7 @@
       </c>
       <c r="S76" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -6686,7 +6686,7 @@
       </c>
       <c r="S77" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -6771,7 +6771,7 @@
       </c>
       <c r="S78" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -6856,7 +6856,7 @@
       </c>
       <c r="S79" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -6941,7 +6941,7 @@
       </c>
       <c r="S80" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -7026,7 +7026,7 @@
       </c>
       <c r="S81" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -7111,7 +7111,7 @@
       </c>
       <c r="S82" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -7196,7 +7196,7 @@
       </c>
       <c r="S83" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -7281,7 +7281,7 @@
       </c>
       <c r="S84" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -7366,7 +7366,7 @@
       </c>
       <c r="S85" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -7451,7 +7451,7 @@
       </c>
       <c r="S86" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -7536,7 +7536,7 @@
       </c>
       <c r="S87" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -7621,7 +7621,7 @@
       </c>
       <c r="S88" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -7706,7 +7706,7 @@
       </c>
       <c r="S89" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -7791,7 +7791,7 @@
       </c>
       <c r="S90" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -7876,7 +7876,7 @@
       </c>
       <c r="S91" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -7961,7 +7961,7 @@
       </c>
       <c r="S92" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -8046,7 +8046,7 @@
       </c>
       <c r="S93" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -8131,7 +8131,7 @@
       </c>
       <c r="S94" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -8216,7 +8216,7 @@
       </c>
       <c r="S95" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -8301,7 +8301,7 @@
       </c>
       <c r="S96" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -8386,7 +8386,7 @@
       </c>
       <c r="S97" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -8471,7 +8471,7 @@
       </c>
       <c r="S98" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -8556,7 +8556,7 @@
       </c>
       <c r="S99" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -8641,7 +8641,7 @@
       </c>
       <c r="S100" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -8726,7 +8726,7 @@
       </c>
       <c r="S101" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -8811,7 +8811,7 @@
       </c>
       <c r="S102" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -8896,7 +8896,7 @@
       </c>
       <c r="S103" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -8981,7 +8981,7 @@
       </c>
       <c r="S104" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -9066,7 +9066,7 @@
       </c>
       <c r="S105" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -9151,7 +9151,7 @@
       </c>
       <c r="S106" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -9236,7 +9236,7 @@
       </c>
       <c r="S107" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -9321,7 +9321,7 @@
       </c>
       <c r="S108" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -9406,7 +9406,7 @@
       </c>
       <c r="S109" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -9491,7 +9491,7 @@
       </c>
       <c r="S110" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -9576,7 +9576,7 @@
       </c>
       <c r="S111" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -9661,7 +9661,7 @@
       </c>
       <c r="S112" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -9746,7 +9746,7 @@
       </c>
       <c r="S113" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -9831,7 +9831,7 @@
       </c>
       <c r="S114" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -9916,7 +9916,7 @@
       </c>
       <c r="S115" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -10001,7 +10001,7 @@
       </c>
       <c r="S116" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -10086,7 +10086,7 @@
       </c>
       <c r="S117" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -10171,7 +10171,7 @@
       </c>
       <c r="S118" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -10256,7 +10256,7 @@
       </c>
       <c r="S119" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -10341,7 +10341,7 @@
       </c>
       <c r="S120" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -10426,7 +10426,7 @@
       </c>
       <c r="S121" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -10511,7 +10511,7 @@
       </c>
       <c r="S122" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -10596,7 +10596,7 @@
       </c>
       <c r="S123" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -10681,7 +10681,7 @@
       </c>
       <c r="S124" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -10766,7 +10766,7 @@
       </c>
       <c r="S125" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -10851,7 +10851,7 @@
       </c>
       <c r="S126" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -10936,7 +10936,7 @@
       </c>
       <c r="S127" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -11021,7 +11021,7 @@
       </c>
       <c r="S128" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -11106,7 +11106,7 @@
       </c>
       <c r="S129" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -11191,7 +11191,7 @@
       </c>
       <c r="S130" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -11276,7 +11276,7 @@
       </c>
       <c r="S131" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -11361,7 +11361,7 @@
       </c>
       <c r="S132" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -11446,7 +11446,7 @@
       </c>
       <c r="S133" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -11531,7 +11531,7 @@
       </c>
       <c r="S134" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -11616,7 +11616,7 @@
       </c>
       <c r="S135" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -11701,7 +11701,7 @@
       </c>
       <c r="S136" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -11786,7 +11786,7 @@
       </c>
       <c r="S137" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -11871,7 +11871,7 @@
       </c>
       <c r="S138" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -11956,7 +11956,7 @@
       </c>
       <c r="S139" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -12041,7 +12041,7 @@
       </c>
       <c r="S140" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -12126,7 +12126,7 @@
       </c>
       <c r="S141" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -12258,7 +12258,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -12338,7 +12338,7 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>{"dataset_id": "bcv_pib_historico_anual", "title": "Producto interno bruto histórico anual", "table": "PIB histórico anual", "source_file": "7_1_14_anual.xls", "base": "1957/1968/1984/1997", "price_type": "Precios constantes", "measure": "Nivel", "frequency": "Anual", "period": "2017", "year": 2017, "quarter": null, "classification": "Total economía", "component": "Producto interno bruto", "value": 392393.12, "unit": "Millones de bolívares a precios constantes", "status": "", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/7_1_14_anual.xls", "fetched_at": "2026-07-25T21:23:58Z"}</t>
+          <t>{"dataset_id": "bcv_pib_historico_anual", "title": "Producto interno bruto histórico anual", "table": "PIB histórico anual", "source_file": "7_1_14_anual.xls", "base": "1957/1968/1984/1997", "price_type": "Precios constantes", "measure": "Nivel", "frequency": "Anual", "period": "2017", "year": 2017, "quarter": null, "classification": "Total economía", "component": "Producto interno bruto", "value": 392393.12, "unit": "Millones de bolívares a precios constantes", "status": "", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/7_1_14_anual.xls", "fetched_at": "2026-07-26T21:25:47Z"}</t>
         </is>
       </c>
     </row>

--- a/assets/data/bcv/excel/ove_bcv_pib_historico_anual.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_pib_historico_anual.xlsx
@@ -736,7 +736,7 @@
       </c>
       <c r="S7" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -821,7 +821,7 @@
       </c>
       <c r="S8" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -906,7 +906,7 @@
       </c>
       <c r="S9" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -991,7 +991,7 @@
       </c>
       <c r="S10" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="S11" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -1161,7 +1161,7 @@
       </c>
       <c r="S12" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -1246,7 +1246,7 @@
       </c>
       <c r="S13" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -1331,7 +1331,7 @@
       </c>
       <c r="S14" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -1416,7 +1416,7 @@
       </c>
       <c r="S15" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -1501,7 +1501,7 @@
       </c>
       <c r="S16" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -1586,7 +1586,7 @@
       </c>
       <c r="S17" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -1671,7 +1671,7 @@
       </c>
       <c r="S18" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -1756,7 +1756,7 @@
       </c>
       <c r="S19" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -1841,7 +1841,7 @@
       </c>
       <c r="S20" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -1926,7 +1926,7 @@
       </c>
       <c r="S21" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -2011,7 +2011,7 @@
       </c>
       <c r="S22" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="S23" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -2181,7 +2181,7 @@
       </c>
       <c r="S24" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -2266,7 +2266,7 @@
       </c>
       <c r="S25" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -2351,7 +2351,7 @@
       </c>
       <c r="S26" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -2436,7 +2436,7 @@
       </c>
       <c r="S27" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -2521,7 +2521,7 @@
       </c>
       <c r="S28" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -2606,7 +2606,7 @@
       </c>
       <c r="S29" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -2691,7 +2691,7 @@
       </c>
       <c r="S30" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -2776,7 +2776,7 @@
       </c>
       <c r="S31" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -2861,7 +2861,7 @@
       </c>
       <c r="S32" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -2946,7 +2946,7 @@
       </c>
       <c r="S33" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -3031,7 +3031,7 @@
       </c>
       <c r="S34" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -3116,7 +3116,7 @@
       </c>
       <c r="S35" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -3201,7 +3201,7 @@
       </c>
       <c r="S36" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -3286,7 +3286,7 @@
       </c>
       <c r="S37" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -3371,7 +3371,7 @@
       </c>
       <c r="S38" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -3456,7 +3456,7 @@
       </c>
       <c r="S39" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -3541,7 +3541,7 @@
       </c>
       <c r="S40" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -3626,7 +3626,7 @@
       </c>
       <c r="S41" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -3711,7 +3711,7 @@
       </c>
       <c r="S42" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -3796,7 +3796,7 @@
       </c>
       <c r="S43" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -3881,7 +3881,7 @@
       </c>
       <c r="S44" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -3966,7 +3966,7 @@
       </c>
       <c r="S45" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -4051,7 +4051,7 @@
       </c>
       <c r="S46" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -4136,7 +4136,7 @@
       </c>
       <c r="S47" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -4221,7 +4221,7 @@
       </c>
       <c r="S48" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -4306,7 +4306,7 @@
       </c>
       <c r="S49" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -4391,7 +4391,7 @@
       </c>
       <c r="S50" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -4476,7 +4476,7 @@
       </c>
       <c r="S51" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -4561,7 +4561,7 @@
       </c>
       <c r="S52" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -4646,7 +4646,7 @@
       </c>
       <c r="S53" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -4731,7 +4731,7 @@
       </c>
       <c r="S54" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -4816,7 +4816,7 @@
       </c>
       <c r="S55" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -4901,7 +4901,7 @@
       </c>
       <c r="S56" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -4986,7 +4986,7 @@
       </c>
       <c r="S57" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -5071,7 +5071,7 @@
       </c>
       <c r="S58" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -5156,7 +5156,7 @@
       </c>
       <c r="S59" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -5241,7 +5241,7 @@
       </c>
       <c r="S60" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -5326,7 +5326,7 @@
       </c>
       <c r="S61" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -5411,7 +5411,7 @@
       </c>
       <c r="S62" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -5496,7 +5496,7 @@
       </c>
       <c r="S63" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -5581,7 +5581,7 @@
       </c>
       <c r="S64" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -5666,7 +5666,7 @@
       </c>
       <c r="S65" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -5751,7 +5751,7 @@
       </c>
       <c r="S66" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -5836,7 +5836,7 @@
       </c>
       <c r="S67" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -5921,7 +5921,7 @@
       </c>
       <c r="S68" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -6006,7 +6006,7 @@
       </c>
       <c r="S69" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -6091,7 +6091,7 @@
       </c>
       <c r="S70" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -6176,7 +6176,7 @@
       </c>
       <c r="S71" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -6261,7 +6261,7 @@
       </c>
       <c r="S72" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -6346,7 +6346,7 @@
       </c>
       <c r="S73" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -6431,7 +6431,7 @@
       </c>
       <c r="S74" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -6516,7 +6516,7 @@
       </c>
       <c r="S75" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -6601,7 +6601,7 @@
       </c>
       <c r="S76" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -6686,7 +6686,7 @@
       </c>
       <c r="S77" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -6771,7 +6771,7 @@
       </c>
       <c r="S78" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -6856,7 +6856,7 @@
       </c>
       <c r="S79" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -6941,7 +6941,7 @@
       </c>
       <c r="S80" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -7026,7 +7026,7 @@
       </c>
       <c r="S81" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -7111,7 +7111,7 @@
       </c>
       <c r="S82" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -7196,7 +7196,7 @@
       </c>
       <c r="S83" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -7281,7 +7281,7 @@
       </c>
       <c r="S84" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -7366,7 +7366,7 @@
       </c>
       <c r="S85" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -7451,7 +7451,7 @@
       </c>
       <c r="S86" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -7536,7 +7536,7 @@
       </c>
       <c r="S87" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -7621,7 +7621,7 @@
       </c>
       <c r="S88" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -7706,7 +7706,7 @@
       </c>
       <c r="S89" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -7791,7 +7791,7 @@
       </c>
       <c r="S90" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -7876,7 +7876,7 @@
       </c>
       <c r="S91" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -7961,7 +7961,7 @@
       </c>
       <c r="S92" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -8046,7 +8046,7 @@
       </c>
       <c r="S93" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -8131,7 +8131,7 @@
       </c>
       <c r="S94" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -8216,7 +8216,7 @@
       </c>
       <c r="S95" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -8301,7 +8301,7 @@
       </c>
       <c r="S96" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -8386,7 +8386,7 @@
       </c>
       <c r="S97" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -8471,7 +8471,7 @@
       </c>
       <c r="S98" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -8556,7 +8556,7 @@
       </c>
       <c r="S99" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -8641,7 +8641,7 @@
       </c>
       <c r="S100" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -8726,7 +8726,7 @@
       </c>
       <c r="S101" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -8811,7 +8811,7 @@
       </c>
       <c r="S102" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -8896,7 +8896,7 @@
       </c>
       <c r="S103" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -8981,7 +8981,7 @@
       </c>
       <c r="S104" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -9066,7 +9066,7 @@
       </c>
       <c r="S105" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -9151,7 +9151,7 @@
       </c>
       <c r="S106" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -9236,7 +9236,7 @@
       </c>
       <c r="S107" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -9321,7 +9321,7 @@
       </c>
       <c r="S108" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -9406,7 +9406,7 @@
       </c>
       <c r="S109" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -9491,7 +9491,7 @@
       </c>
       <c r="S110" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -9576,7 +9576,7 @@
       </c>
       <c r="S111" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -9661,7 +9661,7 @@
       </c>
       <c r="S112" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -9746,7 +9746,7 @@
       </c>
       <c r="S113" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -9831,7 +9831,7 @@
       </c>
       <c r="S114" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -9916,7 +9916,7 @@
       </c>
       <c r="S115" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -10001,7 +10001,7 @@
       </c>
       <c r="S116" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -10086,7 +10086,7 @@
       </c>
       <c r="S117" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -10171,7 +10171,7 @@
       </c>
       <c r="S118" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -10256,7 +10256,7 @@
       </c>
       <c r="S119" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -10341,7 +10341,7 @@
       </c>
       <c r="S120" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -10426,7 +10426,7 @@
       </c>
       <c r="S121" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -10511,7 +10511,7 @@
       </c>
       <c r="S122" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -10596,7 +10596,7 @@
       </c>
       <c r="S123" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -10681,7 +10681,7 @@
       </c>
       <c r="S124" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -10766,7 +10766,7 @@
       </c>
       <c r="S125" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -10851,7 +10851,7 @@
       </c>
       <c r="S126" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -10936,7 +10936,7 @@
       </c>
       <c r="S127" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -11021,7 +11021,7 @@
       </c>
       <c r="S128" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -11106,7 +11106,7 @@
       </c>
       <c r="S129" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -11191,7 +11191,7 @@
       </c>
       <c r="S130" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -11276,7 +11276,7 @@
       </c>
       <c r="S131" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -11361,7 +11361,7 @@
       </c>
       <c r="S132" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -11446,7 +11446,7 @@
       </c>
       <c r="S133" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -11531,7 +11531,7 @@
       </c>
       <c r="S134" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -11616,7 +11616,7 @@
       </c>
       <c r="S135" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -11701,7 +11701,7 @@
       </c>
       <c r="S136" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -11786,7 +11786,7 @@
       </c>
       <c r="S137" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -11871,7 +11871,7 @@
       </c>
       <c r="S138" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -11956,7 +11956,7 @@
       </c>
       <c r="S139" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -12041,7 +12041,7 @@
       </c>
       <c r="S140" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -12126,7 +12126,7 @@
       </c>
       <c r="S141" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -12258,7 +12258,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -12338,7 +12338,7 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>{"dataset_id": "bcv_pib_historico_anual", "title": "Producto interno bruto histórico anual", "table": "PIB histórico anual", "source_file": "7_1_14_anual.xls", "base": "1957/1968/1984/1997", "price_type": "Precios constantes", "measure": "Nivel", "frequency": "Anual", "period": "2017", "year": 2017, "quarter": null, "classification": "Total economía", "component": "Producto interno bruto", "value": 392393.12, "unit": "Millones de bolívares a precios constantes", "status": "", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/7_1_14_anual.xls", "fetched_at": "2026-07-26T21:25:47Z"}</t>
+          <t>{"dataset_id": "bcv_pib_historico_anual", "title": "Producto interno bruto histórico anual", "table": "PIB histórico anual", "source_file": "7_1_14_anual.xls", "base": "1957/1968/1984/1997", "price_type": "Precios constantes", "measure": "Nivel", "frequency": "Anual", "period": "2017", "year": 2017, "quarter": null, "classification": "Total economía", "component": "Producto interno bruto", "value": 392393.12, "unit": "Millones de bolívares a precios constantes", "status": "", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/7_1_14_anual.xls", "fetched_at": "2026-07-27T21:37:28Z"}</t>
         </is>
       </c>
     </row>

--- a/assets/data/bcv/excel/ove_bcv_pib_historico_anual.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_pib_historico_anual.xlsx
@@ -736,7 +736,7 @@
       </c>
       <c r="S7" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -821,7 +821,7 @@
       </c>
       <c r="S8" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -906,7 +906,7 @@
       </c>
       <c r="S9" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -991,7 +991,7 @@
       </c>
       <c r="S10" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="S11" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -1161,7 +1161,7 @@
       </c>
       <c r="S12" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -1246,7 +1246,7 @@
       </c>
       <c r="S13" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -1331,7 +1331,7 @@
       </c>
       <c r="S14" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -1416,7 +1416,7 @@
       </c>
       <c r="S15" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -1501,7 +1501,7 @@
       </c>
       <c r="S16" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -1586,7 +1586,7 @@
       </c>
       <c r="S17" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -1671,7 +1671,7 @@
       </c>
       <c r="S18" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -1756,7 +1756,7 @@
       </c>
       <c r="S19" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -1841,7 +1841,7 @@
       </c>
       <c r="S20" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -1926,7 +1926,7 @@
       </c>
       <c r="S21" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -2011,7 +2011,7 @@
       </c>
       <c r="S22" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="S23" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -2181,7 +2181,7 @@
       </c>
       <c r="S24" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -2266,7 +2266,7 @@
       </c>
       <c r="S25" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -2351,7 +2351,7 @@
       </c>
       <c r="S26" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -2436,7 +2436,7 @@
       </c>
       <c r="S27" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -2521,7 +2521,7 @@
       </c>
       <c r="S28" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -2606,7 +2606,7 @@
       </c>
       <c r="S29" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -2691,7 +2691,7 @@
       </c>
       <c r="S30" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -2776,7 +2776,7 @@
       </c>
       <c r="S31" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -2861,7 +2861,7 @@
       </c>
       <c r="S32" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -2946,7 +2946,7 @@
       </c>
       <c r="S33" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -3031,7 +3031,7 @@
       </c>
       <c r="S34" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -3116,7 +3116,7 @@
       </c>
       <c r="S35" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -3201,7 +3201,7 @@
       </c>
       <c r="S36" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -3286,7 +3286,7 @@
       </c>
       <c r="S37" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -3371,7 +3371,7 @@
       </c>
       <c r="S38" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -3456,7 +3456,7 @@
       </c>
       <c r="S39" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -3541,7 +3541,7 @@
       </c>
       <c r="S40" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -3626,7 +3626,7 @@
       </c>
       <c r="S41" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -3711,7 +3711,7 @@
       </c>
       <c r="S42" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -3796,7 +3796,7 @@
       </c>
       <c r="S43" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -3881,7 +3881,7 @@
       </c>
       <c r="S44" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -3966,7 +3966,7 @@
       </c>
       <c r="S45" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -4051,7 +4051,7 @@
       </c>
       <c r="S46" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -4136,7 +4136,7 @@
       </c>
       <c r="S47" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -4221,7 +4221,7 @@
       </c>
       <c r="S48" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -4306,7 +4306,7 @@
       </c>
       <c r="S49" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -4391,7 +4391,7 @@
       </c>
       <c r="S50" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -4476,7 +4476,7 @@
       </c>
       <c r="S51" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -4561,7 +4561,7 @@
       </c>
       <c r="S52" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -4646,7 +4646,7 @@
       </c>
       <c r="S53" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -4731,7 +4731,7 @@
       </c>
       <c r="S54" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -4816,7 +4816,7 @@
       </c>
       <c r="S55" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -4901,7 +4901,7 @@
       </c>
       <c r="S56" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -4986,7 +4986,7 @@
       </c>
       <c r="S57" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -5071,7 +5071,7 @@
       </c>
       <c r="S58" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -5156,7 +5156,7 @@
       </c>
       <c r="S59" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -5241,7 +5241,7 @@
       </c>
       <c r="S60" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -5326,7 +5326,7 @@
       </c>
       <c r="S61" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -5411,7 +5411,7 @@
       </c>
       <c r="S62" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -5496,7 +5496,7 @@
       </c>
       <c r="S63" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -5581,7 +5581,7 @@
       </c>
       <c r="S64" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -5666,7 +5666,7 @@
       </c>
       <c r="S65" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -5751,7 +5751,7 @@
       </c>
       <c r="S66" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -5836,7 +5836,7 @@
       </c>
       <c r="S67" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -5921,7 +5921,7 @@
       </c>
       <c r="S68" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -6006,7 +6006,7 @@
       </c>
       <c r="S69" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -6091,7 +6091,7 @@
       </c>
       <c r="S70" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -6176,7 +6176,7 @@
       </c>
       <c r="S71" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -6261,7 +6261,7 @@
       </c>
       <c r="S72" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -6346,7 +6346,7 @@
       </c>
       <c r="S73" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -6431,7 +6431,7 @@
       </c>
       <c r="S74" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -6516,7 +6516,7 @@
       </c>
       <c r="S75" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -6601,7 +6601,7 @@
       </c>
       <c r="S76" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -6686,7 +6686,7 @@
       </c>
       <c r="S77" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -6771,7 +6771,7 @@
       </c>
       <c r="S78" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -6856,7 +6856,7 @@
       </c>
       <c r="S79" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -6941,7 +6941,7 @@
       </c>
       <c r="S80" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -7026,7 +7026,7 @@
       </c>
       <c r="S81" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -7111,7 +7111,7 @@
       </c>
       <c r="S82" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -7196,7 +7196,7 @@
       </c>
       <c r="S83" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -7281,7 +7281,7 @@
       </c>
       <c r="S84" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -7366,7 +7366,7 @@
       </c>
       <c r="S85" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -7451,7 +7451,7 @@
       </c>
       <c r="S86" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -7536,7 +7536,7 @@
       </c>
       <c r="S87" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -7621,7 +7621,7 @@
       </c>
       <c r="S88" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -7706,7 +7706,7 @@
       </c>
       <c r="S89" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -7791,7 +7791,7 @@
       </c>
       <c r="S90" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -7876,7 +7876,7 @@
       </c>
       <c r="S91" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -7961,7 +7961,7 @@
       </c>
       <c r="S92" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -8046,7 +8046,7 @@
       </c>
       <c r="S93" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -8131,7 +8131,7 @@
       </c>
       <c r="S94" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -8216,7 +8216,7 @@
       </c>
       <c r="S95" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -8301,7 +8301,7 @@
       </c>
       <c r="S96" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -8386,7 +8386,7 @@
       </c>
       <c r="S97" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -8471,7 +8471,7 @@
       </c>
       <c r="S98" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -8556,7 +8556,7 @@
       </c>
       <c r="S99" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -8641,7 +8641,7 @@
       </c>
       <c r="S100" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -8726,7 +8726,7 @@
       </c>
       <c r="S101" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -8811,7 +8811,7 @@
       </c>
       <c r="S102" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -8896,7 +8896,7 @@
       </c>
       <c r="S103" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -8981,7 +8981,7 @@
       </c>
       <c r="S104" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -9066,7 +9066,7 @@
       </c>
       <c r="S105" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -9151,7 +9151,7 @@
       </c>
       <c r="S106" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -9236,7 +9236,7 @@
       </c>
       <c r="S107" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -9321,7 +9321,7 @@
       </c>
       <c r="S108" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -9406,7 +9406,7 @@
       </c>
       <c r="S109" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -9491,7 +9491,7 @@
       </c>
       <c r="S110" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -9576,7 +9576,7 @@
       </c>
       <c r="S111" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -9661,7 +9661,7 @@
       </c>
       <c r="S112" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -9746,7 +9746,7 @@
       </c>
       <c r="S113" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -9831,7 +9831,7 @@
       </c>
       <c r="S114" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -9916,7 +9916,7 @@
       </c>
       <c r="S115" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -10001,7 +10001,7 @@
       </c>
       <c r="S116" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -10086,7 +10086,7 @@
       </c>
       <c r="S117" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -10171,7 +10171,7 @@
       </c>
       <c r="S118" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -10256,7 +10256,7 @@
       </c>
       <c r="S119" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -10341,7 +10341,7 @@
       </c>
       <c r="S120" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -10426,7 +10426,7 @@
       </c>
       <c r="S121" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -10511,7 +10511,7 @@
       </c>
       <c r="S122" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -10596,7 +10596,7 @@
       </c>
       <c r="S123" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -10681,7 +10681,7 @@
       </c>
       <c r="S124" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -10766,7 +10766,7 @@
       </c>
       <c r="S125" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -10851,7 +10851,7 @@
       </c>
       <c r="S126" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -10936,7 +10936,7 @@
       </c>
       <c r="S127" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -11021,7 +11021,7 @@
       </c>
       <c r="S128" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -11106,7 +11106,7 @@
       </c>
       <c r="S129" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -11191,7 +11191,7 @@
       </c>
       <c r="S130" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -11276,7 +11276,7 @@
       </c>
       <c r="S131" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -11361,7 +11361,7 @@
       </c>
       <c r="S132" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -11446,7 +11446,7 @@
       </c>
       <c r="S133" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -11531,7 +11531,7 @@
       </c>
       <c r="S134" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -11616,7 +11616,7 @@
       </c>
       <c r="S135" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -11701,7 +11701,7 @@
       </c>
       <c r="S136" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -11786,7 +11786,7 @@
       </c>
       <c r="S137" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -11871,7 +11871,7 @@
       </c>
       <c r="S138" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -11956,7 +11956,7 @@
       </c>
       <c r="S139" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -12041,7 +12041,7 @@
       </c>
       <c r="S140" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -12126,7 +12126,7 @@
       </c>
       <c r="S141" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -12258,7 +12258,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -12338,7 +12338,7 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>{"dataset_id": "bcv_pib_historico_anual", "title": "Producto interno bruto histórico anual", "table": "PIB histórico anual", "source_file": "7_1_14_anual.xls", "base": "1957/1968/1984/1997", "price_type": "Precios constantes", "measure": "Nivel", "frequency": "Anual", "period": "2017", "year": 2017, "quarter": null, "classification": "Total economía", "component": "Producto interno bruto", "value": 392393.12, "unit": "Millones de bolívares a precios constantes", "status": "", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/7_1_14_anual.xls", "fetched_at": "2026-07-27T21:37:28Z"}</t>
+          <t>{"dataset_id": "bcv_pib_historico_anual", "title": "Producto interno bruto histórico anual", "table": "PIB histórico anual", "source_file": "7_1_14_anual.xls", "base": "1957/1968/1984/1997", "price_type": "Precios constantes", "measure": "Nivel", "frequency": "Anual", "period": "2017", "year": 2017, "quarter": null, "classification": "Total economía", "component": "Producto interno bruto", "value": 392393.12, "unit": "Millones de bolívares a precios constantes", "status": "", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/7_1_14_anual.xls", "fetched_at": "2026-07-28T21:37:48Z"}</t>
         </is>
       </c>
     </row>

--- a/assets/data/bcv/excel/ove_bcv_pib_historico_anual.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_pib_historico_anual.xlsx
@@ -736,7 +736,7 @@
       </c>
       <c r="S7" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -821,7 +821,7 @@
       </c>
       <c r="S8" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -906,7 +906,7 @@
       </c>
       <c r="S9" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -991,7 +991,7 @@
       </c>
       <c r="S10" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="S11" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -1161,7 +1161,7 @@
       </c>
       <c r="S12" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -1246,7 +1246,7 @@
       </c>
       <c r="S13" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -1331,7 +1331,7 @@
       </c>
       <c r="S14" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -1416,7 +1416,7 @@
       </c>
       <c r="S15" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -1501,7 +1501,7 @@
       </c>
       <c r="S16" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -1586,7 +1586,7 @@
       </c>
       <c r="S17" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -1671,7 +1671,7 @@
       </c>
       <c r="S18" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -1756,7 +1756,7 @@
       </c>
       <c r="S19" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -1841,7 +1841,7 @@
       </c>
       <c r="S20" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -1926,7 +1926,7 @@
       </c>
       <c r="S21" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -2011,7 +2011,7 @@
       </c>
       <c r="S22" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="S23" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -2181,7 +2181,7 @@
       </c>
       <c r="S24" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -2266,7 +2266,7 @@
       </c>
       <c r="S25" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -2351,7 +2351,7 @@
       </c>
       <c r="S26" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -2436,7 +2436,7 @@
       </c>
       <c r="S27" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -2521,7 +2521,7 @@
       </c>
       <c r="S28" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -2606,7 +2606,7 @@
       </c>
       <c r="S29" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -2691,7 +2691,7 @@
       </c>
       <c r="S30" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -2776,7 +2776,7 @@
       </c>
       <c r="S31" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -2861,7 +2861,7 @@
       </c>
       <c r="S32" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -2946,7 +2946,7 @@
       </c>
       <c r="S33" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -3031,7 +3031,7 @@
       </c>
       <c r="S34" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -3116,7 +3116,7 @@
       </c>
       <c r="S35" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -3201,7 +3201,7 @@
       </c>
       <c r="S36" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -3286,7 +3286,7 @@
       </c>
       <c r="S37" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -3371,7 +3371,7 @@
       </c>
       <c r="S38" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -3456,7 +3456,7 @@
       </c>
       <c r="S39" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -3541,7 +3541,7 @@
       </c>
       <c r="S40" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -3626,7 +3626,7 @@
       </c>
       <c r="S41" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -3711,7 +3711,7 @@
       </c>
       <c r="S42" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -3796,7 +3796,7 @@
       </c>
       <c r="S43" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -3881,7 +3881,7 @@
       </c>
       <c r="S44" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -3966,7 +3966,7 @@
       </c>
       <c r="S45" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -4051,7 +4051,7 @@
       </c>
       <c r="S46" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -4136,7 +4136,7 @@
       </c>
       <c r="S47" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -4221,7 +4221,7 @@
       </c>
       <c r="S48" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -4306,7 +4306,7 @@
       </c>
       <c r="S49" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -4391,7 +4391,7 @@
       </c>
       <c r="S50" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -4476,7 +4476,7 @@
       </c>
       <c r="S51" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -4561,7 +4561,7 @@
       </c>
       <c r="S52" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -4646,7 +4646,7 @@
       </c>
       <c r="S53" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -4731,7 +4731,7 @@
       </c>
       <c r="S54" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -4816,7 +4816,7 @@
       </c>
       <c r="S55" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -4901,7 +4901,7 @@
       </c>
       <c r="S56" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -4986,7 +4986,7 @@
       </c>
       <c r="S57" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -5071,7 +5071,7 @@
       </c>
       <c r="S58" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -5156,7 +5156,7 @@
       </c>
       <c r="S59" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -5241,7 +5241,7 @@
       </c>
       <c r="S60" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -5326,7 +5326,7 @@
       </c>
       <c r="S61" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -5411,7 +5411,7 @@
       </c>
       <c r="S62" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -5496,7 +5496,7 @@
       </c>
       <c r="S63" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -5581,7 +5581,7 @@
       </c>
       <c r="S64" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -5666,7 +5666,7 @@
       </c>
       <c r="S65" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -5751,7 +5751,7 @@
       </c>
       <c r="S66" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -5836,7 +5836,7 @@
       </c>
       <c r="S67" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -5921,7 +5921,7 @@
       </c>
       <c r="S68" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -6006,7 +6006,7 @@
       </c>
       <c r="S69" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -6091,7 +6091,7 @@
       </c>
       <c r="S70" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -6176,7 +6176,7 @@
       </c>
       <c r="S71" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -6261,7 +6261,7 @@
       </c>
       <c r="S72" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -6346,7 +6346,7 @@
       </c>
       <c r="S73" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -6431,7 +6431,7 @@
       </c>
       <c r="S74" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -6516,7 +6516,7 @@
       </c>
       <c r="S75" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -6601,7 +6601,7 @@
       </c>
       <c r="S76" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -6686,7 +6686,7 @@
       </c>
       <c r="S77" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -6771,7 +6771,7 @@
       </c>
       <c r="S78" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -6856,7 +6856,7 @@
       </c>
       <c r="S79" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -6941,7 +6941,7 @@
       </c>
       <c r="S80" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -7026,7 +7026,7 @@
       </c>
       <c r="S81" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -7111,7 +7111,7 @@
       </c>
       <c r="S82" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -7196,7 +7196,7 @@
       </c>
       <c r="S83" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -7281,7 +7281,7 @@
       </c>
       <c r="S84" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -7366,7 +7366,7 @@
       </c>
       <c r="S85" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -7451,7 +7451,7 @@
       </c>
       <c r="S86" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -7536,7 +7536,7 @@
       </c>
       <c r="S87" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -7621,7 +7621,7 @@
       </c>
       <c r="S88" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -7706,7 +7706,7 @@
       </c>
       <c r="S89" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -7791,7 +7791,7 @@
       </c>
       <c r="S90" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -7876,7 +7876,7 @@
       </c>
       <c r="S91" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -7961,7 +7961,7 @@
       </c>
       <c r="S92" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -8046,7 +8046,7 @@
       </c>
       <c r="S93" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -8131,7 +8131,7 @@
       </c>
       <c r="S94" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -8216,7 +8216,7 @@
       </c>
       <c r="S95" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -8301,7 +8301,7 @@
       </c>
       <c r="S96" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -8386,7 +8386,7 @@
       </c>
       <c r="S97" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -8471,7 +8471,7 @@
       </c>
       <c r="S98" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -8556,7 +8556,7 @@
       </c>
       <c r="S99" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -8641,7 +8641,7 @@
       </c>
       <c r="S100" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -8726,7 +8726,7 @@
       </c>
       <c r="S101" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -8811,7 +8811,7 @@
       </c>
       <c r="S102" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -8896,7 +8896,7 @@
       </c>
       <c r="S103" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -8981,7 +8981,7 @@
       </c>
       <c r="S104" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -9066,7 +9066,7 @@
       </c>
       <c r="S105" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -9151,7 +9151,7 @@
       </c>
       <c r="S106" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -9236,7 +9236,7 @@
       </c>
       <c r="S107" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -9321,7 +9321,7 @@
       </c>
       <c r="S108" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -9406,7 +9406,7 @@
       </c>
       <c r="S109" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -9491,7 +9491,7 @@
       </c>
       <c r="S110" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -9576,7 +9576,7 @@
       </c>
       <c r="S111" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -9661,7 +9661,7 @@
       </c>
       <c r="S112" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -9746,7 +9746,7 @@
       </c>
       <c r="S113" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -9831,7 +9831,7 @@
       </c>
       <c r="S114" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -9916,7 +9916,7 @@
       </c>
       <c r="S115" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -10001,7 +10001,7 @@
       </c>
       <c r="S116" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -10086,7 +10086,7 @@
       </c>
       <c r="S117" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -10171,7 +10171,7 @@
       </c>
       <c r="S118" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -10256,7 +10256,7 @@
       </c>
       <c r="S119" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -10341,7 +10341,7 @@
       </c>
       <c r="S120" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -10426,7 +10426,7 @@
       </c>
       <c r="S121" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -10511,7 +10511,7 @@
       </c>
       <c r="S122" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -10596,7 +10596,7 @@
       </c>
       <c r="S123" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -10681,7 +10681,7 @@
       </c>
       <c r="S124" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -10766,7 +10766,7 @@
       </c>
       <c r="S125" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -10851,7 +10851,7 @@
       </c>
       <c r="S126" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -10936,7 +10936,7 @@
       </c>
       <c r="S127" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -11021,7 +11021,7 @@
       </c>
       <c r="S128" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -11106,7 +11106,7 @@
       </c>
       <c r="S129" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -11191,7 +11191,7 @@
       </c>
       <c r="S130" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -11276,7 +11276,7 @@
       </c>
       <c r="S131" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -11361,7 +11361,7 @@
       </c>
       <c r="S132" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -11446,7 +11446,7 @@
       </c>
       <c r="S133" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -11531,7 +11531,7 @@
       </c>
       <c r="S134" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -11616,7 +11616,7 @@
       </c>
       <c r="S135" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -11701,7 +11701,7 @@
       </c>
       <c r="S136" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -11786,7 +11786,7 @@
       </c>
       <c r="S137" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -11871,7 +11871,7 @@
       </c>
       <c r="S138" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -11956,7 +11956,7 @@
       </c>
       <c r="S139" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -12041,7 +12041,7 @@
       </c>
       <c r="S140" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -12126,7 +12126,7 @@
       </c>
       <c r="S141" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -12258,7 +12258,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -12338,7 +12338,7 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>{"dataset_id": "bcv_pib_historico_anual", "title": "Producto interno bruto histórico anual", "table": "PIB histórico anual", "source_file": "7_1_14_anual.xls", "base": "1957/1968/1984/1997", "price_type": "Precios constantes", "measure": "Nivel", "frequency": "Anual", "period": "2017", "year": 2017, "quarter": null, "classification": "Total economía", "component": "Producto interno bruto", "value": 392393.12, "unit": "Millones de bolívares a precios constantes", "status": "", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/7_1_14_anual.xls", "fetched_at": "2026-07-28T21:37:48Z"}</t>
+          <t>{"dataset_id": "bcv_pib_historico_anual", "title": "Producto interno bruto histórico anual", "table": "PIB histórico anual", "source_file": "7_1_14_anual.xls", "base": "1957/1968/1984/1997", "price_type": "Precios constantes", "measure": "Nivel", "frequency": "Anual", "period": "2017", "year": 2017, "quarter": null, "classification": "Total economía", "component": "Producto interno bruto", "value": 392393.12, "unit": "Millones de bolívares a precios constantes", "status": "", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/7_1_14_anual.xls", "fetched_at": "2026-07-29T21:26:22Z"}</t>
         </is>
       </c>
     </row>

--- a/assets/data/bcv/excel/ove_bcv_pib_historico_anual.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_pib_historico_anual.xlsx
@@ -736,7 +736,7 @@
       </c>
       <c r="S7" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -821,7 +821,7 @@
       </c>
       <c r="S8" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -906,7 +906,7 @@
       </c>
       <c r="S9" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -991,7 +991,7 @@
       </c>
       <c r="S10" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="S11" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -1161,7 +1161,7 @@
       </c>
       <c r="S12" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -1246,7 +1246,7 @@
       </c>
       <c r="S13" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -1331,7 +1331,7 @@
       </c>
       <c r="S14" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -1416,7 +1416,7 @@
       </c>
       <c r="S15" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -1501,7 +1501,7 @@
       </c>
       <c r="S16" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -1586,7 +1586,7 @@
       </c>
       <c r="S17" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -1671,7 +1671,7 @@
       </c>
       <c r="S18" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -1756,7 +1756,7 @@
       </c>
       <c r="S19" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -1841,7 +1841,7 @@
       </c>
       <c r="S20" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -1926,7 +1926,7 @@
       </c>
       <c r="S21" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -2011,7 +2011,7 @@
       </c>
       <c r="S22" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="S23" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -2181,7 +2181,7 @@
       </c>
       <c r="S24" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -2266,7 +2266,7 @@
       </c>
       <c r="S25" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -2351,7 +2351,7 @@
       </c>
       <c r="S26" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -2436,7 +2436,7 @@
       </c>
       <c r="S27" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -2521,7 +2521,7 @@
       </c>
       <c r="S28" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -2606,7 +2606,7 @@
       </c>
       <c r="S29" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -2691,7 +2691,7 @@
       </c>
       <c r="S30" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -2776,7 +2776,7 @@
       </c>
       <c r="S31" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -2861,7 +2861,7 @@
       </c>
       <c r="S32" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -2946,7 +2946,7 @@
       </c>
       <c r="S33" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -3031,7 +3031,7 @@
       </c>
       <c r="S34" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -3116,7 +3116,7 @@
       </c>
       <c r="S35" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -3201,7 +3201,7 @@
       </c>
       <c r="S36" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -3286,7 +3286,7 @@
       </c>
       <c r="S37" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -3371,7 +3371,7 @@
       </c>
       <c r="S38" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -3456,7 +3456,7 @@
       </c>
       <c r="S39" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -3541,7 +3541,7 @@
       </c>
       <c r="S40" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -3626,7 +3626,7 @@
       </c>
       <c r="S41" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -3711,7 +3711,7 @@
       </c>
       <c r="S42" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -3796,7 +3796,7 @@
       </c>
       <c r="S43" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -3881,7 +3881,7 @@
       </c>
       <c r="S44" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -3966,7 +3966,7 @@
       </c>
       <c r="S45" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -4051,7 +4051,7 @@
       </c>
       <c r="S46" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -4136,7 +4136,7 @@
       </c>
       <c r="S47" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -4221,7 +4221,7 @@
       </c>
       <c r="S48" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -4306,7 +4306,7 @@
       </c>
       <c r="S49" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -4391,7 +4391,7 @@
       </c>
       <c r="S50" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -4476,7 +4476,7 @@
       </c>
       <c r="S51" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -4561,7 +4561,7 @@
       </c>
       <c r="S52" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -4646,7 +4646,7 @@
       </c>
       <c r="S53" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -4731,7 +4731,7 @@
       </c>
       <c r="S54" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -4816,7 +4816,7 @@
       </c>
       <c r="S55" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -4901,7 +4901,7 @@
       </c>
       <c r="S56" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -4986,7 +4986,7 @@
       </c>
       <c r="S57" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -5071,7 +5071,7 @@
       </c>
       <c r="S58" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -5156,7 +5156,7 @@
       </c>
       <c r="S59" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -5241,7 +5241,7 @@
       </c>
       <c r="S60" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -5326,7 +5326,7 @@
       </c>
       <c r="S61" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -5411,7 +5411,7 @@
       </c>
       <c r="S62" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -5496,7 +5496,7 @@
       </c>
       <c r="S63" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -5581,7 +5581,7 @@
       </c>
       <c r="S64" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -5666,7 +5666,7 @@
       </c>
       <c r="S65" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -5751,7 +5751,7 @@
       </c>
       <c r="S66" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -5836,7 +5836,7 @@
       </c>
       <c r="S67" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -5921,7 +5921,7 @@
       </c>
       <c r="S68" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -6006,7 +6006,7 @@
       </c>
       <c r="S69" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -6091,7 +6091,7 @@
       </c>
       <c r="S70" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -6176,7 +6176,7 @@
       </c>
       <c r="S71" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -6261,7 +6261,7 @@
       </c>
       <c r="S72" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -6346,7 +6346,7 @@
       </c>
       <c r="S73" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -6431,7 +6431,7 @@
       </c>
       <c r="S74" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -6516,7 +6516,7 @@
       </c>
       <c r="S75" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -6601,7 +6601,7 @@
       </c>
       <c r="S76" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -6686,7 +6686,7 @@
       </c>
       <c r="S77" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -6771,7 +6771,7 @@
       </c>
       <c r="S78" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -6856,7 +6856,7 @@
       </c>
       <c r="S79" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -6941,7 +6941,7 @@
       </c>
       <c r="S80" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -7026,7 +7026,7 @@
       </c>
       <c r="S81" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -7111,7 +7111,7 @@
       </c>
       <c r="S82" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -7196,7 +7196,7 @@
       </c>
       <c r="S83" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -7281,7 +7281,7 @@
       </c>
       <c r="S84" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -7366,7 +7366,7 @@
       </c>
       <c r="S85" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -7451,7 +7451,7 @@
       </c>
       <c r="S86" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -7536,7 +7536,7 @@
       </c>
       <c r="S87" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -7621,7 +7621,7 @@
       </c>
       <c r="S88" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -7706,7 +7706,7 @@
       </c>
       <c r="S89" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -7791,7 +7791,7 @@
       </c>
       <c r="S90" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -7876,7 +7876,7 @@
       </c>
       <c r="S91" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -7961,7 +7961,7 @@
       </c>
       <c r="S92" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -8046,7 +8046,7 @@
       </c>
       <c r="S93" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -8131,7 +8131,7 @@
       </c>
       <c r="S94" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -8216,7 +8216,7 @@
       </c>
       <c r="S95" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -8301,7 +8301,7 @@
       </c>
       <c r="S96" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -8386,7 +8386,7 @@
       </c>
       <c r="S97" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -8471,7 +8471,7 @@
       </c>
       <c r="S98" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -8556,7 +8556,7 @@
       </c>
       <c r="S99" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -8641,7 +8641,7 @@
       </c>
       <c r="S100" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -8726,7 +8726,7 @@
       </c>
       <c r="S101" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -8811,7 +8811,7 @@
       </c>
       <c r="S102" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -8896,7 +8896,7 @@
       </c>
       <c r="S103" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -8981,7 +8981,7 @@
       </c>
       <c r="S104" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -9066,7 +9066,7 @@
       </c>
       <c r="S105" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -9151,7 +9151,7 @@
       </c>
       <c r="S106" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -9236,7 +9236,7 @@
       </c>
       <c r="S107" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -9321,7 +9321,7 @@
       </c>
       <c r="S108" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -9406,7 +9406,7 @@
       </c>
       <c r="S109" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -9491,7 +9491,7 @@
       </c>
       <c r="S110" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -9576,7 +9576,7 @@
       </c>
       <c r="S111" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -9661,7 +9661,7 @@
       </c>
       <c r="S112" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -9746,7 +9746,7 @@
       </c>
       <c r="S113" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -9831,7 +9831,7 @@
       </c>
       <c r="S114" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -9916,7 +9916,7 @@
       </c>
       <c r="S115" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -10001,7 +10001,7 @@
       </c>
       <c r="S116" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -10086,7 +10086,7 @@
       </c>
       <c r="S117" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -10171,7 +10171,7 @@
       </c>
       <c r="S118" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -10256,7 +10256,7 @@
       </c>
       <c r="S119" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -10341,7 +10341,7 @@
       </c>
       <c r="S120" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -10426,7 +10426,7 @@
       </c>
       <c r="S121" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -10511,7 +10511,7 @@
       </c>
       <c r="S122" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -10596,7 +10596,7 @@
       </c>
       <c r="S123" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -10681,7 +10681,7 @@
       </c>
       <c r="S124" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -10766,7 +10766,7 @@
       </c>
       <c r="S125" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -10851,7 +10851,7 @@
       </c>
       <c r="S126" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -10936,7 +10936,7 @@
       </c>
       <c r="S127" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -11021,7 +11021,7 @@
       </c>
       <c r="S128" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -11106,7 +11106,7 @@
       </c>
       <c r="S129" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -11191,7 +11191,7 @@
       </c>
       <c r="S130" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -11276,7 +11276,7 @@
       </c>
       <c r="S131" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -11361,7 +11361,7 @@
       </c>
       <c r="S132" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -11446,7 +11446,7 @@
       </c>
       <c r="S133" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -11531,7 +11531,7 @@
       </c>
       <c r="S134" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -11616,7 +11616,7 @@
       </c>
       <c r="S135" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -11701,7 +11701,7 @@
       </c>
       <c r="S136" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -11786,7 +11786,7 @@
       </c>
       <c r="S137" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -11871,7 +11871,7 @@
       </c>
       <c r="S138" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -11956,7 +11956,7 @@
       </c>
       <c r="S139" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -12041,7 +12041,7 @@
       </c>
       <c r="S140" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -12126,7 +12126,7 @@
       </c>
       <c r="S141" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -12258,7 +12258,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -12338,7 +12338,7 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>{"dataset_id": "bcv_pib_historico_anual", "title": "Producto interno bruto histórico anual", "table": "PIB histórico anual", "source_file": "7_1_14_anual.xls", "base": "1957/1968/1984/1997", "price_type": "Precios constantes", "measure": "Nivel", "frequency": "Anual", "period": "2017", "year": 2017, "quarter": null, "classification": "Total economía", "component": "Producto interno bruto", "value": 392393.12, "unit": "Millones de bolívares a precios constantes", "status": "", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/7_1_14_anual.xls", "fetched_at": "2026-07-29T21:26:22Z"}</t>
+          <t>{"dataset_id": "bcv_pib_historico_anual", "title": "Producto interno bruto histórico anual", "table": "PIB histórico anual", "source_file": "7_1_14_anual.xls", "base": "1957/1968/1984/1997", "price_type": "Precios constantes", "measure": "Nivel", "frequency": "Anual", "period": "2017", "year": 2017, "quarter": null, "classification": "Total economía", "component": "Producto interno bruto", "value": 392393.12, "unit": "Millones de bolívares a precios constantes", "status": "", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/7_1_14_anual.xls", "fetched_at": "2026-07-30T21:40:55Z"}</t>
         </is>
       </c>
     </row>

--- a/assets/data/bcv/excel/ove_bcv_pib_historico_anual.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_pib_historico_anual.xlsx
@@ -736,7 +736,7 @@
       </c>
       <c r="S7" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -821,7 +821,7 @@
       </c>
       <c r="S8" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -906,7 +906,7 @@
       </c>
       <c r="S9" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -991,7 +991,7 @@
       </c>
       <c r="S10" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="S11" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -1161,7 +1161,7 @@
       </c>
       <c r="S12" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -1246,7 +1246,7 @@
       </c>
       <c r="S13" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -1331,7 +1331,7 @@
       </c>
       <c r="S14" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -1416,7 +1416,7 @@
       </c>
       <c r="S15" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -1501,7 +1501,7 @@
       </c>
       <c r="S16" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -1586,7 +1586,7 @@
       </c>
       <c r="S17" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -1671,7 +1671,7 @@
       </c>
       <c r="S18" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -1756,7 +1756,7 @@
       </c>
       <c r="S19" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -1841,7 +1841,7 @@
       </c>
       <c r="S20" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -1926,7 +1926,7 @@
       </c>
       <c r="S21" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -2011,7 +2011,7 @@
       </c>
       <c r="S22" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="S23" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -2181,7 +2181,7 @@
       </c>
       <c r="S24" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -2266,7 +2266,7 @@
       </c>
       <c r="S25" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -2351,7 +2351,7 @@
       </c>
       <c r="S26" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -2436,7 +2436,7 @@
       </c>
       <c r="S27" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -2521,7 +2521,7 @@
       </c>
       <c r="S28" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -2606,7 +2606,7 @@
       </c>
       <c r="S29" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -2691,7 +2691,7 @@
       </c>
       <c r="S30" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -2776,7 +2776,7 @@
       </c>
       <c r="S31" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -2861,7 +2861,7 @@
       </c>
       <c r="S32" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -2946,7 +2946,7 @@
       </c>
       <c r="S33" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -3031,7 +3031,7 @@
       </c>
       <c r="S34" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -3116,7 +3116,7 @@
       </c>
       <c r="S35" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -3201,7 +3201,7 @@
       </c>
       <c r="S36" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -3286,7 +3286,7 @@
       </c>
       <c r="S37" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -3371,7 +3371,7 @@
       </c>
       <c r="S38" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -3456,7 +3456,7 @@
       </c>
       <c r="S39" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -3541,7 +3541,7 @@
       </c>
       <c r="S40" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -3626,7 +3626,7 @@
       </c>
       <c r="S41" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -3711,7 +3711,7 @@
       </c>
       <c r="S42" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -3796,7 +3796,7 @@
       </c>
       <c r="S43" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -3881,7 +3881,7 @@
       </c>
       <c r="S44" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -3966,7 +3966,7 @@
       </c>
       <c r="S45" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -4051,7 +4051,7 @@
       </c>
       <c r="S46" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -4136,7 +4136,7 @@
       </c>
       <c r="S47" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -4221,7 +4221,7 @@
       </c>
       <c r="S48" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -4306,7 +4306,7 @@
       </c>
       <c r="S49" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -4391,7 +4391,7 @@
       </c>
       <c r="S50" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -4476,7 +4476,7 @@
       </c>
       <c r="S51" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -4561,7 +4561,7 @@
       </c>
       <c r="S52" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -4646,7 +4646,7 @@
       </c>
       <c r="S53" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -4731,7 +4731,7 @@
       </c>
       <c r="S54" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -4816,7 +4816,7 @@
       </c>
       <c r="S55" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -4901,7 +4901,7 @@
       </c>
       <c r="S56" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -4986,7 +4986,7 @@
       </c>
       <c r="S57" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -5071,7 +5071,7 @@
       </c>
       <c r="S58" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -5156,7 +5156,7 @@
       </c>
       <c r="S59" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -5241,7 +5241,7 @@
       </c>
       <c r="S60" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -5326,7 +5326,7 @@
       </c>
       <c r="S61" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -5411,7 +5411,7 @@
       </c>
       <c r="S62" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -5496,7 +5496,7 @@
       </c>
       <c r="S63" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -5581,7 +5581,7 @@
       </c>
       <c r="S64" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -5666,7 +5666,7 @@
       </c>
       <c r="S65" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -5751,7 +5751,7 @@
       </c>
       <c r="S66" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -5836,7 +5836,7 @@
       </c>
       <c r="S67" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -5921,7 +5921,7 @@
       </c>
       <c r="S68" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -6006,7 +6006,7 @@
       </c>
       <c r="S69" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -6091,7 +6091,7 @@
       </c>
       <c r="S70" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -6176,7 +6176,7 @@
       </c>
       <c r="S71" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -6261,7 +6261,7 @@
       </c>
       <c r="S72" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -6346,7 +6346,7 @@
       </c>
       <c r="S73" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -6431,7 +6431,7 @@
       </c>
       <c r="S74" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -6516,7 +6516,7 @@
       </c>
       <c r="S75" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -6601,7 +6601,7 @@
       </c>
       <c r="S76" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -6686,7 +6686,7 @@
       </c>
       <c r="S77" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -6771,7 +6771,7 @@
       </c>
       <c r="S78" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -6856,7 +6856,7 @@
       </c>
       <c r="S79" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -6941,7 +6941,7 @@
       </c>
       <c r="S80" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -7026,7 +7026,7 @@
       </c>
       <c r="S81" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -7111,7 +7111,7 @@
       </c>
       <c r="S82" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -7196,7 +7196,7 @@
       </c>
       <c r="S83" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -7281,7 +7281,7 @@
       </c>
       <c r="S84" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -7366,7 +7366,7 @@
       </c>
       <c r="S85" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -7451,7 +7451,7 @@
       </c>
       <c r="S86" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -7536,7 +7536,7 @@
       </c>
       <c r="S87" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -7621,7 +7621,7 @@
       </c>
       <c r="S88" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -7706,7 +7706,7 @@
       </c>
       <c r="S89" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -7791,7 +7791,7 @@
       </c>
       <c r="S90" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -7876,7 +7876,7 @@
       </c>
       <c r="S91" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -7961,7 +7961,7 @@
       </c>
       <c r="S92" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -8046,7 +8046,7 @@
       </c>
       <c r="S93" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -8131,7 +8131,7 @@
       </c>
       <c r="S94" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -8216,7 +8216,7 @@
       </c>
       <c r="S95" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -8301,7 +8301,7 @@
       </c>
       <c r="S96" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -8386,7 +8386,7 @@
       </c>
       <c r="S97" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -8471,7 +8471,7 @@
       </c>
       <c r="S98" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -8556,7 +8556,7 @@
       </c>
       <c r="S99" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -8641,7 +8641,7 @@
       </c>
       <c r="S100" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -8726,7 +8726,7 @@
       </c>
       <c r="S101" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -8811,7 +8811,7 @@
       </c>
       <c r="S102" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -8896,7 +8896,7 @@
       </c>
       <c r="S103" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -8981,7 +8981,7 @@
       </c>
       <c r="S104" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -9066,7 +9066,7 @@
       </c>
       <c r="S105" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -9151,7 +9151,7 @@
       </c>
       <c r="S106" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -9236,7 +9236,7 @@
       </c>
       <c r="S107" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -9321,7 +9321,7 @@
       </c>
       <c r="S108" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -9406,7 +9406,7 @@
       </c>
       <c r="S109" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -9491,7 +9491,7 @@
       </c>
       <c r="S110" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -9576,7 +9576,7 @@
       </c>
       <c r="S111" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -9661,7 +9661,7 @@
       </c>
       <c r="S112" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -9746,7 +9746,7 @@
       </c>
       <c r="S113" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -9831,7 +9831,7 @@
       </c>
       <c r="S114" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -9916,7 +9916,7 @@
       </c>
       <c r="S115" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -10001,7 +10001,7 @@
       </c>
       <c r="S116" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -10086,7 +10086,7 @@
       </c>
       <c r="S117" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -10171,7 +10171,7 @@
       </c>
       <c r="S118" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -10256,7 +10256,7 @@
       </c>
       <c r="S119" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -10341,7 +10341,7 @@
       </c>
       <c r="S120" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -10426,7 +10426,7 @@
       </c>
       <c r="S121" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -10511,7 +10511,7 @@
       </c>
       <c r="S122" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -10596,7 +10596,7 @@
       </c>
       <c r="S123" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -10681,7 +10681,7 @@
       </c>
       <c r="S124" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -10766,7 +10766,7 @@
       </c>
       <c r="S125" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -10851,7 +10851,7 @@
       </c>
       <c r="S126" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -10936,7 +10936,7 @@
       </c>
       <c r="S127" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -11021,7 +11021,7 @@
       </c>
       <c r="S128" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -11106,7 +11106,7 @@
       </c>
       <c r="S129" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -11191,7 +11191,7 @@
       </c>
       <c r="S130" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -11276,7 +11276,7 @@
       </c>
       <c r="S131" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -11361,7 +11361,7 @@
       </c>
       <c r="S132" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -11446,7 +11446,7 @@
       </c>
       <c r="S133" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -11531,7 +11531,7 @@
       </c>
       <c r="S134" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -11616,7 +11616,7 @@
       </c>
       <c r="S135" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -11701,7 +11701,7 @@
       </c>
       <c r="S136" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -11786,7 +11786,7 @@
       </c>
       <c r="S137" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -11871,7 +11871,7 @@
       </c>
       <c r="S138" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -11956,7 +11956,7 @@
       </c>
       <c r="S139" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -12041,7 +12041,7 @@
       </c>
       <c r="S140" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -12126,7 +12126,7 @@
       </c>
       <c r="S141" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -12258,7 +12258,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -12338,7 +12338,7 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>{"dataset_id": "bcv_pib_historico_anual", "title": "Producto interno bruto histórico anual", "table": "PIB histórico anual", "source_file": "7_1_14_anual.xls", "base": "1957/1968/1984/1997", "price_type": "Precios constantes", "measure": "Nivel", "frequency": "Anual", "period": "2017", "year": 2017, "quarter": null, "classification": "Total economía", "component": "Producto interno bruto", "value": 392393.12, "unit": "Millones de bolívares a precios constantes", "status": "", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/7_1_14_anual.xls", "fetched_at": "2026-07-30T21:40:55Z"}</t>
+          <t>{"dataset_id": "bcv_pib_historico_anual", "title": "Producto interno bruto histórico anual", "table": "PIB histórico anual", "source_file": "7_1_14_anual.xls", "base": "1957/1968/1984/1997", "price_type": "Precios constantes", "measure": "Nivel", "frequency": "Anual", "period": "2017", "year": 2017, "quarter": null, "classification": "Total economía", "component": "Producto interno bruto", "value": 392393.12, "unit": "Millones de bolívares a precios constantes", "status": "", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/7_1_14_anual.xls", "fetched_at": "2026-07-31T21:36:46Z"}</t>
         </is>
       </c>
     </row>

--- a/assets/data/bcv/excel/ove_bcv_pib_historico_anual.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_pib_historico_anual.xlsx
@@ -736,7 +736,7 @@
       </c>
       <c r="S7" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -821,7 +821,7 @@
       </c>
       <c r="S8" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -906,7 +906,7 @@
       </c>
       <c r="S9" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -991,7 +991,7 @@
       </c>
       <c r="S10" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="S11" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -1161,7 +1161,7 @@
       </c>
       <c r="S12" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -1246,7 +1246,7 @@
       </c>
       <c r="S13" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -1331,7 +1331,7 @@
       </c>
       <c r="S14" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -1416,7 +1416,7 @@
       </c>
       <c r="S15" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -1501,7 +1501,7 @@
       </c>
       <c r="S16" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -1586,7 +1586,7 @@
       </c>
       <c r="S17" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -1671,7 +1671,7 @@
       </c>
       <c r="S18" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -1756,7 +1756,7 @@
       </c>
       <c r="S19" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -1841,7 +1841,7 @@
       </c>
       <c r="S20" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -1926,7 +1926,7 @@
       </c>
       <c r="S21" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -2011,7 +2011,7 @@
       </c>
       <c r="S22" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="S23" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -2181,7 +2181,7 @@
       </c>
       <c r="S24" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -2266,7 +2266,7 @@
       </c>
       <c r="S25" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -2351,7 +2351,7 @@
       </c>
       <c r="S26" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -2436,7 +2436,7 @@
       </c>
       <c r="S27" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -2521,7 +2521,7 @@
       </c>
       <c r="S28" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -2606,7 +2606,7 @@
       </c>
       <c r="S29" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -2691,7 +2691,7 @@
       </c>
       <c r="S30" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -2776,7 +2776,7 @@
       </c>
       <c r="S31" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -2861,7 +2861,7 @@
       </c>
       <c r="S32" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -2946,7 +2946,7 @@
       </c>
       <c r="S33" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -3031,7 +3031,7 @@
       </c>
       <c r="S34" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -3116,7 +3116,7 @@
       </c>
       <c r="S35" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -3201,7 +3201,7 @@
       </c>
       <c r="S36" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -3286,7 +3286,7 @@
       </c>
       <c r="S37" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -3371,7 +3371,7 @@
       </c>
       <c r="S38" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -3456,7 +3456,7 @@
       </c>
       <c r="S39" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -3541,7 +3541,7 @@
       </c>
       <c r="S40" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -3626,7 +3626,7 @@
       </c>
       <c r="S41" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -3711,7 +3711,7 @@
       </c>
       <c r="S42" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -3796,7 +3796,7 @@
       </c>
       <c r="S43" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -3881,7 +3881,7 @@
       </c>
       <c r="S44" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -3966,7 +3966,7 @@
       </c>
       <c r="S45" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -4051,7 +4051,7 @@
       </c>
       <c r="S46" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -4136,7 +4136,7 @@
       </c>
       <c r="S47" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -4221,7 +4221,7 @@
       </c>
       <c r="S48" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -4306,7 +4306,7 @@
       </c>
       <c r="S49" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -4391,7 +4391,7 @@
       </c>
       <c r="S50" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -4476,7 +4476,7 @@
       </c>
       <c r="S51" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -4561,7 +4561,7 @@
       </c>
       <c r="S52" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -4646,7 +4646,7 @@
       </c>
       <c r="S53" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -4731,7 +4731,7 @@
       </c>
       <c r="S54" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -4816,7 +4816,7 @@
       </c>
       <c r="S55" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -4901,7 +4901,7 @@
       </c>
       <c r="S56" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -4986,7 +4986,7 @@
       </c>
       <c r="S57" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -5071,7 +5071,7 @@
       </c>
       <c r="S58" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -5156,7 +5156,7 @@
       </c>
       <c r="S59" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -5241,7 +5241,7 @@
       </c>
       <c r="S60" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -5326,7 +5326,7 @@
       </c>
       <c r="S61" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -5411,7 +5411,7 @@
       </c>
       <c r="S62" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -5496,7 +5496,7 @@
       </c>
       <c r="S63" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -5581,7 +5581,7 @@
       </c>
       <c r="S64" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -5666,7 +5666,7 @@
       </c>
       <c r="S65" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -5751,7 +5751,7 @@
       </c>
       <c r="S66" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -5836,7 +5836,7 @@
       </c>
       <c r="S67" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -5921,7 +5921,7 @@
       </c>
       <c r="S68" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -6006,7 +6006,7 @@
       </c>
       <c r="S69" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -6091,7 +6091,7 @@
       </c>
       <c r="S70" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -6176,7 +6176,7 @@
       </c>
       <c r="S71" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -6261,7 +6261,7 @@
       </c>
       <c r="S72" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -6346,7 +6346,7 @@
       </c>
       <c r="S73" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -6431,7 +6431,7 @@
       </c>
       <c r="S74" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -6516,7 +6516,7 @@
       </c>
       <c r="S75" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -6601,7 +6601,7 @@
       </c>
       <c r="S76" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -6686,7 +6686,7 @@
       </c>
       <c r="S77" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -6771,7 +6771,7 @@
       </c>
       <c r="S78" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -6856,7 +6856,7 @@
       </c>
       <c r="S79" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -6941,7 +6941,7 @@
       </c>
       <c r="S80" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -7026,7 +7026,7 @@
       </c>
       <c r="S81" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -7111,7 +7111,7 @@
       </c>
       <c r="S82" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -7196,7 +7196,7 @@
       </c>
       <c r="S83" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -7281,7 +7281,7 @@
       </c>
       <c r="S84" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -7366,7 +7366,7 @@
       </c>
       <c r="S85" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -7451,7 +7451,7 @@
       </c>
       <c r="S86" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -7536,7 +7536,7 @@
       </c>
       <c r="S87" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -7621,7 +7621,7 @@
       </c>
       <c r="S88" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -7706,7 +7706,7 @@
       </c>
       <c r="S89" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -7791,7 +7791,7 @@
       </c>
       <c r="S90" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -7876,7 +7876,7 @@
       </c>
       <c r="S91" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -7961,7 +7961,7 @@
       </c>
       <c r="S92" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -8046,7 +8046,7 @@
       </c>
       <c r="S93" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -8131,7 +8131,7 @@
       </c>
       <c r="S94" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -8216,7 +8216,7 @@
       </c>
       <c r="S95" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -8301,7 +8301,7 @@
       </c>
       <c r="S96" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -8386,7 +8386,7 @@
       </c>
       <c r="S97" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -8471,7 +8471,7 @@
       </c>
       <c r="S98" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -8556,7 +8556,7 @@
       </c>
       <c r="S99" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -8641,7 +8641,7 @@
       </c>
       <c r="S100" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -8726,7 +8726,7 @@
       </c>
       <c r="S101" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -8811,7 +8811,7 @@
       </c>
       <c r="S102" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -8896,7 +8896,7 @@
       </c>
       <c r="S103" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -8981,7 +8981,7 @@
       </c>
       <c r="S104" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -9066,7 +9066,7 @@
       </c>
       <c r="S105" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -9151,7 +9151,7 @@
       </c>
       <c r="S106" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -9236,7 +9236,7 @@
       </c>
       <c r="S107" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -9321,7 +9321,7 @@
       </c>
       <c r="S108" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -9406,7 +9406,7 @@
       </c>
       <c r="S109" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -9491,7 +9491,7 @@
       </c>
       <c r="S110" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -9576,7 +9576,7 @@
       </c>
       <c r="S111" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -9661,7 +9661,7 @@
       </c>
       <c r="S112" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -9746,7 +9746,7 @@
       </c>
       <c r="S113" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -9831,7 +9831,7 @@
       </c>
       <c r="S114" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -9916,7 +9916,7 @@
       </c>
       <c r="S115" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -10001,7 +10001,7 @@
       </c>
       <c r="S116" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -10086,7 +10086,7 @@
       </c>
       <c r="S117" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -10171,7 +10171,7 @@
       </c>
       <c r="S118" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -10256,7 +10256,7 @@
       </c>
       <c r="S119" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -10341,7 +10341,7 @@
       </c>
       <c r="S120" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -10426,7 +10426,7 @@
       </c>
       <c r="S121" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -10511,7 +10511,7 @@
       </c>
       <c r="S122" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -10596,7 +10596,7 @@
       </c>
       <c r="S123" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -10681,7 +10681,7 @@
       </c>
       <c r="S124" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -10766,7 +10766,7 @@
       </c>
       <c r="S125" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -10851,7 +10851,7 @@
       </c>
       <c r="S126" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -10936,7 +10936,7 @@
       </c>
       <c r="S127" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -11021,7 +11021,7 @@
       </c>
       <c r="S128" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -11106,7 +11106,7 @@
       </c>
       <c r="S129" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -11191,7 +11191,7 @@
       </c>
       <c r="S130" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -11276,7 +11276,7 @@
       </c>
       <c r="S131" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -11361,7 +11361,7 @@
       </c>
       <c r="S132" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -11446,7 +11446,7 @@
       </c>
       <c r="S133" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -11531,7 +11531,7 @@
       </c>
       <c r="S134" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -11616,7 +11616,7 @@
       </c>
       <c r="S135" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -11701,7 +11701,7 @@
       </c>
       <c r="S136" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -11786,7 +11786,7 @@
       </c>
       <c r="S137" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -11871,7 +11871,7 @@
       </c>
       <c r="S138" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -11956,7 +11956,7 @@
       </c>
       <c r="S139" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -12041,7 +12041,7 @@
       </c>
       <c r="S140" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -12126,7 +12126,7 @@
       </c>
       <c r="S141" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -12258,7 +12258,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -12338,7 +12338,7 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>{"dataset_id": "bcv_pib_historico_anual", "title": "Producto interno bruto histórico anual", "table": "PIB histórico anual", "source_file": "7_1_14_anual.xls", "base": "1957/1968/1984/1997", "price_type": "Precios constantes", "measure": "Nivel", "frequency": "Anual", "period": "2017", "year": 2017, "quarter": null, "classification": "Total economía", "component": "Producto interno bruto", "value": 392393.12, "unit": "Millones de bolívares a precios constantes", "status": "", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/7_1_14_anual.xls", "fetched_at": "2026-07-31T21:36:46Z"}</t>
+          <t>{"dataset_id": "bcv_pib_historico_anual", "title": "Producto interno bruto histórico anual", "table": "PIB histórico anual", "source_file": "7_1_14_anual.xls", "base": "1957/1968/1984/1997", "price_type": "Precios constantes", "measure": "Nivel", "frequency": "Anual", "period": "2017", "year": 2017, "quarter": null, "classification": "Total economía", "component": "Producto interno bruto", "value": 392393.12, "unit": "Millones de bolívares a precios constantes", "status": "", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/7_1_14_anual.xls", "fetched_at": "2026-08-01T21:23:57Z"}</t>
         </is>
       </c>
     </row>

--- a/assets/data/bcv/excel/ove_bcv_pib_historico_anual.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_pib_historico_anual.xlsx
@@ -736,7 +736,7 @@
       </c>
       <c r="S7" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -821,7 +821,7 @@
       </c>
       <c r="S8" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -906,7 +906,7 @@
       </c>
       <c r="S9" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -991,7 +991,7 @@
       </c>
       <c r="S10" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="S11" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -1161,7 +1161,7 @@
       </c>
       <c r="S12" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -1246,7 +1246,7 @@
       </c>
       <c r="S13" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -1331,7 +1331,7 @@
       </c>
       <c r="S14" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -1416,7 +1416,7 @@
       </c>
       <c r="S15" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -1501,7 +1501,7 @@
       </c>
       <c r="S16" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -1586,7 +1586,7 @@
       </c>
       <c r="S17" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -1671,7 +1671,7 @@
       </c>
       <c r="S18" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -1756,7 +1756,7 @@
       </c>
       <c r="S19" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -1841,7 +1841,7 @@
       </c>
       <c r="S20" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -1926,7 +1926,7 @@
       </c>
       <c r="S21" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -2011,7 +2011,7 @@
       </c>
       <c r="S22" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="S23" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -2181,7 +2181,7 @@
       </c>
       <c r="S24" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -2266,7 +2266,7 @@
       </c>
       <c r="S25" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -2351,7 +2351,7 @@
       </c>
       <c r="S26" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -2436,7 +2436,7 @@
       </c>
       <c r="S27" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -2521,7 +2521,7 @@
       </c>
       <c r="S28" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -2606,7 +2606,7 @@
       </c>
       <c r="S29" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -2691,7 +2691,7 @@
       </c>
       <c r="S30" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -2776,7 +2776,7 @@
       </c>
       <c r="S31" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -2861,7 +2861,7 @@
       </c>
       <c r="S32" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -2946,7 +2946,7 @@
       </c>
       <c r="S33" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -3031,7 +3031,7 @@
       </c>
       <c r="S34" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -3116,7 +3116,7 @@
       </c>
       <c r="S35" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -3201,7 +3201,7 @@
       </c>
       <c r="S36" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -3286,7 +3286,7 @@
       </c>
       <c r="S37" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -3371,7 +3371,7 @@
       </c>
       <c r="S38" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -3456,7 +3456,7 @@
       </c>
       <c r="S39" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -3541,7 +3541,7 @@
       </c>
       <c r="S40" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -3626,7 +3626,7 @@
       </c>
       <c r="S41" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -3711,7 +3711,7 @@
       </c>
       <c r="S42" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -3796,7 +3796,7 @@
       </c>
       <c r="S43" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -3881,7 +3881,7 @@
       </c>
       <c r="S44" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -3966,7 +3966,7 @@
       </c>
       <c r="S45" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -4051,7 +4051,7 @@
       </c>
       <c r="S46" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -4136,7 +4136,7 @@
       </c>
       <c r="S47" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -4221,7 +4221,7 @@
       </c>
       <c r="S48" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -4306,7 +4306,7 @@
       </c>
       <c r="S49" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -4391,7 +4391,7 @@
       </c>
       <c r="S50" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -4476,7 +4476,7 @@
       </c>
       <c r="S51" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -4561,7 +4561,7 @@
       </c>
       <c r="S52" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -4646,7 +4646,7 @@
       </c>
       <c r="S53" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -4731,7 +4731,7 @@
       </c>
       <c r="S54" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -4816,7 +4816,7 @@
       </c>
       <c r="S55" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -4901,7 +4901,7 @@
       </c>
       <c r="S56" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -4986,7 +4986,7 @@
       </c>
       <c r="S57" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -5071,7 +5071,7 @@
       </c>
       <c r="S58" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -5156,7 +5156,7 @@
       </c>
       <c r="S59" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -5241,7 +5241,7 @@
       </c>
       <c r="S60" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -5326,7 +5326,7 @@
       </c>
       <c r="S61" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -5411,7 +5411,7 @@
       </c>
       <c r="S62" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -5496,7 +5496,7 @@
       </c>
       <c r="S63" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -5581,7 +5581,7 @@
       </c>
       <c r="S64" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -5666,7 +5666,7 @@
       </c>
       <c r="S65" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -5751,7 +5751,7 @@
       </c>
       <c r="S66" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -5836,7 +5836,7 @@
       </c>
       <c r="S67" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -5921,7 +5921,7 @@
       </c>
       <c r="S68" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -6006,7 +6006,7 @@
       </c>
       <c r="S69" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -6091,7 +6091,7 @@
       </c>
       <c r="S70" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -6176,7 +6176,7 @@
       </c>
       <c r="S71" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -6261,7 +6261,7 @@
       </c>
       <c r="S72" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -6346,7 +6346,7 @@
       </c>
       <c r="S73" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -6431,7 +6431,7 @@
       </c>
       <c r="S74" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -6516,7 +6516,7 @@
       </c>
       <c r="S75" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -6601,7 +6601,7 @@
       </c>
       <c r="S76" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -6686,7 +6686,7 @@
       </c>
       <c r="S77" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -6771,7 +6771,7 @@
       </c>
       <c r="S78" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -6856,7 +6856,7 @@
       </c>
       <c r="S79" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -6941,7 +6941,7 @@
       </c>
       <c r="S80" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -7026,7 +7026,7 @@
       </c>
       <c r="S81" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -7111,7 +7111,7 @@
       </c>
       <c r="S82" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -7196,7 +7196,7 @@
       </c>
       <c r="S83" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -7281,7 +7281,7 @@
       </c>
       <c r="S84" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -7366,7 +7366,7 @@
       </c>
       <c r="S85" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -7451,7 +7451,7 @@
       </c>
       <c r="S86" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -7536,7 +7536,7 @@
       </c>
       <c r="S87" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -7621,7 +7621,7 @@
       </c>
       <c r="S88" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -7706,7 +7706,7 @@
       </c>
       <c r="S89" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -7791,7 +7791,7 @@
       </c>
       <c r="S90" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -7876,7 +7876,7 @@
       </c>
       <c r="S91" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -7961,7 +7961,7 @@
       </c>
       <c r="S92" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -8046,7 +8046,7 @@
       </c>
       <c r="S93" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -8131,7 +8131,7 @@
       </c>
       <c r="S94" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -8216,7 +8216,7 @@
       </c>
       <c r="S95" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -8301,7 +8301,7 @@
       </c>
       <c r="S96" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -8386,7 +8386,7 @@
       </c>
       <c r="S97" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -8471,7 +8471,7 @@
       </c>
       <c r="S98" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -8556,7 +8556,7 @@
       </c>
       <c r="S99" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -8641,7 +8641,7 @@
       </c>
       <c r="S100" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -8726,7 +8726,7 @@
       </c>
       <c r="S101" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -8811,7 +8811,7 @@
       </c>
       <c r="S102" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -8896,7 +8896,7 @@
       </c>
       <c r="S103" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -8981,7 +8981,7 @@
       </c>
       <c r="S104" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -9066,7 +9066,7 @@
       </c>
       <c r="S105" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -9151,7 +9151,7 @@
       </c>
       <c r="S106" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -9236,7 +9236,7 @@
       </c>
       <c r="S107" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -9321,7 +9321,7 @@
       </c>
       <c r="S108" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -9406,7 +9406,7 @@
       </c>
       <c r="S109" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -9491,7 +9491,7 @@
       </c>
       <c r="S110" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -9576,7 +9576,7 @@
       </c>
       <c r="S111" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -9661,7 +9661,7 @@
       </c>
       <c r="S112" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -9746,7 +9746,7 @@
       </c>
       <c r="S113" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -9831,7 +9831,7 @@
       </c>
       <c r="S114" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -9916,7 +9916,7 @@
       </c>
       <c r="S115" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -10001,7 +10001,7 @@
       </c>
       <c r="S116" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -10086,7 +10086,7 @@
       </c>
       <c r="S117" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -10171,7 +10171,7 @@
       </c>
       <c r="S118" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -10256,7 +10256,7 @@
       </c>
       <c r="S119" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -10341,7 +10341,7 @@
       </c>
       <c r="S120" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -10426,7 +10426,7 @@
       </c>
       <c r="S121" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -10511,7 +10511,7 @@
       </c>
       <c r="S122" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -10596,7 +10596,7 @@
       </c>
       <c r="S123" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -10681,7 +10681,7 @@
       </c>
       <c r="S124" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -10766,7 +10766,7 @@
       </c>
       <c r="S125" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -10851,7 +10851,7 @@
       </c>
       <c r="S126" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -10936,7 +10936,7 @@
       </c>
       <c r="S127" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -11021,7 +11021,7 @@
       </c>
       <c r="S128" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -11106,7 +11106,7 @@
       </c>
       <c r="S129" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -11191,7 +11191,7 @@
       </c>
       <c r="S130" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -11276,7 +11276,7 @@
       </c>
       <c r="S131" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -11361,7 +11361,7 @@
       </c>
       <c r="S132" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -11446,7 +11446,7 @@
       </c>
       <c r="S133" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -11531,7 +11531,7 @@
       </c>
       <c r="S134" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -11616,7 +11616,7 @@
       </c>
       <c r="S135" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -11701,7 +11701,7 @@
       </c>
       <c r="S136" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -11786,7 +11786,7 @@
       </c>
       <c r="S137" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -11871,7 +11871,7 @@
       </c>
       <c r="S138" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -11956,7 +11956,7 @@
       </c>
       <c r="S139" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -12041,7 +12041,7 @@
       </c>
       <c r="S140" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -12126,7 +12126,7 @@
       </c>
       <c r="S141" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -12258,7 +12258,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -12338,7 +12338,7 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>{"dataset_id": "bcv_pib_historico_anual", "title": "Producto interno bruto histórico anual", "table": "PIB histórico anual", "source_file": "7_1_14_anual.xls", "base": "1957/1968/1984/1997", "price_type": "Precios constantes", "measure": "Nivel", "frequency": "Anual", "period": "2017", "year": 2017, "quarter": null, "classification": "Total economía", "component": "Producto interno bruto", "value": 392393.12, "unit": "Millones de bolívares a precios constantes", "status": "", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/7_1_14_anual.xls", "fetched_at": "2026-08-01T21:23:57Z"}</t>
+          <t>{"dataset_id": "bcv_pib_historico_anual", "title": "Producto interno bruto histórico anual", "table": "PIB histórico anual", "source_file": "7_1_14_anual.xls", "base": "1957/1968/1984/1997", "price_type": "Precios constantes", "measure": "Nivel", "frequency": "Anual", "period": "2017", "year": 2017, "quarter": null, "classification": "Total economía", "component": "Producto interno bruto", "value": 392393.12, "unit": "Millones de bolívares a precios constantes", "status": "", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/7_1_14_anual.xls", "fetched_at": "2026-08-02T14:43:06Z"}</t>
         </is>
       </c>
     </row>

--- a/assets/data/bcv/excel/ove_bcv_pib_historico_anual.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_pib_historico_anual.xlsx
@@ -736,7 +736,7 @@
       </c>
       <c r="S7" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -821,7 +821,7 @@
       </c>
       <c r="S8" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -906,7 +906,7 @@
       </c>
       <c r="S9" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -991,7 +991,7 @@
       </c>
       <c r="S10" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="S11" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -1161,7 +1161,7 @@
       </c>
       <c r="S12" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -1246,7 +1246,7 @@
       </c>
       <c r="S13" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -1331,7 +1331,7 @@
       </c>
       <c r="S14" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -1416,7 +1416,7 @@
       </c>
       <c r="S15" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -1501,7 +1501,7 @@
       </c>
       <c r="S16" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -1586,7 +1586,7 @@
       </c>
       <c r="S17" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -1671,7 +1671,7 @@
       </c>
       <c r="S18" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -1756,7 +1756,7 @@
       </c>
       <c r="S19" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -1841,7 +1841,7 @@
       </c>
       <c r="S20" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -1926,7 +1926,7 @@
       </c>
       <c r="S21" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -2011,7 +2011,7 @@
       </c>
       <c r="S22" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="S23" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -2181,7 +2181,7 @@
       </c>
       <c r="S24" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -2266,7 +2266,7 @@
       </c>
       <c r="S25" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -2351,7 +2351,7 @@
       </c>
       <c r="S26" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -2436,7 +2436,7 @@
       </c>
       <c r="S27" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -2521,7 +2521,7 @@
       </c>
       <c r="S28" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -2606,7 +2606,7 @@
       </c>
       <c r="S29" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -2691,7 +2691,7 @@
       </c>
       <c r="S30" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -2776,7 +2776,7 @@
       </c>
       <c r="S31" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -2861,7 +2861,7 @@
       </c>
       <c r="S32" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -2946,7 +2946,7 @@
       </c>
       <c r="S33" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -3031,7 +3031,7 @@
       </c>
       <c r="S34" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -3116,7 +3116,7 @@
       </c>
       <c r="S35" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -3201,7 +3201,7 @@
       </c>
       <c r="S36" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -3286,7 +3286,7 @@
       </c>
       <c r="S37" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -3371,7 +3371,7 @@
       </c>
       <c r="S38" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -3456,7 +3456,7 @@
       </c>
       <c r="S39" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -3541,7 +3541,7 @@
       </c>
       <c r="S40" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -3626,7 +3626,7 @@
       </c>
       <c r="S41" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -3711,7 +3711,7 @@
       </c>
       <c r="S42" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -3796,7 +3796,7 @@
       </c>
       <c r="S43" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -3881,7 +3881,7 @@
       </c>
       <c r="S44" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -3966,7 +3966,7 @@
       </c>
       <c r="S45" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -4051,7 +4051,7 @@
       </c>
       <c r="S46" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -4136,7 +4136,7 @@
       </c>
       <c r="S47" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -4221,7 +4221,7 @@
       </c>
       <c r="S48" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -4306,7 +4306,7 @@
       </c>
       <c r="S49" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -4391,7 +4391,7 @@
       </c>
       <c r="S50" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -4476,7 +4476,7 @@
       </c>
       <c r="S51" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -4561,7 +4561,7 @@
       </c>
       <c r="S52" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -4646,7 +4646,7 @@
       </c>
       <c r="S53" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -4731,7 +4731,7 @@
       </c>
       <c r="S54" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -4816,7 +4816,7 @@
       </c>
       <c r="S55" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -4901,7 +4901,7 @@
       </c>
       <c r="S56" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -4986,7 +4986,7 @@
       </c>
       <c r="S57" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -5071,7 +5071,7 @@
       </c>
       <c r="S58" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -5156,7 +5156,7 @@
       </c>
       <c r="S59" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -5241,7 +5241,7 @@
       </c>
       <c r="S60" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -5326,7 +5326,7 @@
       </c>
       <c r="S61" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -5411,7 +5411,7 @@
       </c>
       <c r="S62" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -5496,7 +5496,7 @@
       </c>
       <c r="S63" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -5581,7 +5581,7 @@
       </c>
       <c r="S64" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -5666,7 +5666,7 @@
       </c>
       <c r="S65" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -5751,7 +5751,7 @@
       </c>
       <c r="S66" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -5836,7 +5836,7 @@
       </c>
       <c r="S67" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -5921,7 +5921,7 @@
       </c>
       <c r="S68" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -6006,7 +6006,7 @@
       </c>
       <c r="S69" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -6091,7 +6091,7 @@
       </c>
       <c r="S70" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -6176,7 +6176,7 @@
       </c>
       <c r="S71" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -6261,7 +6261,7 @@
       </c>
       <c r="S72" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -6346,7 +6346,7 @@
       </c>
       <c r="S73" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -6431,7 +6431,7 @@
       </c>
       <c r="S74" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -6516,7 +6516,7 @@
       </c>
       <c r="S75" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -6601,7 +6601,7 @@
       </c>
       <c r="S76" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -6686,7 +6686,7 @@
       </c>
       <c r="S77" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -6771,7 +6771,7 @@
       </c>
       <c r="S78" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -6856,7 +6856,7 @@
       </c>
       <c r="S79" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -6941,7 +6941,7 @@
       </c>
       <c r="S80" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -7026,7 +7026,7 @@
       </c>
       <c r="S81" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -7111,7 +7111,7 @@
       </c>
       <c r="S82" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -7196,7 +7196,7 @@
       </c>
       <c r="S83" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -7281,7 +7281,7 @@
       </c>
       <c r="S84" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -7366,7 +7366,7 @@
       </c>
       <c r="S85" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -7451,7 +7451,7 @@
       </c>
       <c r="S86" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -7536,7 +7536,7 @@
       </c>
       <c r="S87" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -7621,7 +7621,7 @@
       </c>
       <c r="S88" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -7706,7 +7706,7 @@
       </c>
       <c r="S89" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -7791,7 +7791,7 @@
       </c>
       <c r="S90" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -7876,7 +7876,7 @@
       </c>
       <c r="S91" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -7961,7 +7961,7 @@
       </c>
       <c r="S92" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -8046,7 +8046,7 @@
       </c>
       <c r="S93" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -8131,7 +8131,7 @@
       </c>
       <c r="S94" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -8216,7 +8216,7 @@
       </c>
       <c r="S95" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -8301,7 +8301,7 @@
       </c>
       <c r="S96" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -8386,7 +8386,7 @@
       </c>
       <c r="S97" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -8471,7 +8471,7 @@
       </c>
       <c r="S98" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -8556,7 +8556,7 @@
       </c>
       <c r="S99" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -8641,7 +8641,7 @@
       </c>
       <c r="S100" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -8726,7 +8726,7 @@
       </c>
       <c r="S101" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -8811,7 +8811,7 @@
       </c>
       <c r="S102" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -8896,7 +8896,7 @@
       </c>
       <c r="S103" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -8981,7 +8981,7 @@
       </c>
       <c r="S104" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -9066,7 +9066,7 @@
       </c>
       <c r="S105" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -9151,7 +9151,7 @@
       </c>
       <c r="S106" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -9236,7 +9236,7 @@
       </c>
       <c r="S107" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -9321,7 +9321,7 @@
       </c>
       <c r="S108" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -9406,7 +9406,7 @@
       </c>
       <c r="S109" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -9491,7 +9491,7 @@
       </c>
       <c r="S110" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -9576,7 +9576,7 @@
       </c>
       <c r="S111" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -9661,7 +9661,7 @@
       </c>
       <c r="S112" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -9746,7 +9746,7 @@
       </c>
       <c r="S113" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -9831,7 +9831,7 @@
       </c>
       <c r="S114" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -9916,7 +9916,7 @@
       </c>
       <c r="S115" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -10001,7 +10001,7 @@
       </c>
       <c r="S116" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -10086,7 +10086,7 @@
       </c>
       <c r="S117" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -10171,7 +10171,7 @@
       </c>
       <c r="S118" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -10256,7 +10256,7 @@
       </c>
       <c r="S119" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -10341,7 +10341,7 @@
       </c>
       <c r="S120" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -10426,7 +10426,7 @@
       </c>
       <c r="S121" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -10511,7 +10511,7 @@
       </c>
       <c r="S122" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -10596,7 +10596,7 @@
       </c>
       <c r="S123" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -10681,7 +10681,7 @@
       </c>
       <c r="S124" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -10766,7 +10766,7 @@
       </c>
       <c r="S125" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -10851,7 +10851,7 @@
       </c>
       <c r="S126" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -10936,7 +10936,7 @@
       </c>
       <c r="S127" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -11021,7 +11021,7 @@
       </c>
       <c r="S128" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -11106,7 +11106,7 @@
       </c>
       <c r="S129" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -11191,7 +11191,7 @@
       </c>
       <c r="S130" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -11276,7 +11276,7 @@
       </c>
       <c r="S131" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -11361,7 +11361,7 @@
       </c>
       <c r="S132" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -11446,7 +11446,7 @@
       </c>
       <c r="S133" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -11531,7 +11531,7 @@
       </c>
       <c r="S134" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -11616,7 +11616,7 @@
       </c>
       <c r="S135" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -11701,7 +11701,7 @@
       </c>
       <c r="S136" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -11786,7 +11786,7 @@
       </c>
       <c r="S137" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -11871,7 +11871,7 @@
       </c>
       <c r="S138" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -11956,7 +11956,7 @@
       </c>
       <c r="S139" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -12041,7 +12041,7 @@
       </c>
       <c r="S140" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -12126,7 +12126,7 @@
       </c>
       <c r="S141" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -12258,7 +12258,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -12338,7 +12338,7 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>{"dataset_id": "bcv_pib_historico_anual", "title": "Producto interno bruto histórico anual", "table": "PIB histórico anual", "source_file": "7_1_14_anual.xls", "base": "1957/1968/1984/1997", "price_type": "Precios constantes", "measure": "Nivel", "frequency": "Anual", "period": "2017", "year": 2017, "quarter": null, "classification": "Total economía", "component": "Producto interno bruto", "value": 392393.12, "unit": "Millones de bolívares a precios constantes", "status": "", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/7_1_14_anual.xls", "fetched_at": "2026-08-02T14:43:06Z"}</t>
+          <t>{"dataset_id": "bcv_pib_historico_anual", "title": "Producto interno bruto histórico anual", "table": "PIB histórico anual", "source_file": "7_1_14_anual.xls", "base": "1957/1968/1984/1997", "price_type": "Precios constantes", "measure": "Nivel", "frequency": "Anual", "period": "2017", "year": 2017, "quarter": null, "classification": "Total economía", "component": "Producto interno bruto", "value": 392393.12, "unit": "Millones de bolívares a precios constantes", "status": "", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/7_1_14_anual.xls", "fetched_at": "2026-08-02T21:23:58Z"}</t>
         </is>
       </c>
     </row>

--- a/assets/data/bcv/excel/ove_bcv_pib_historico_anual.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_pib_historico_anual.xlsx
@@ -736,7 +736,7 @@
       </c>
       <c r="S7" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -821,7 +821,7 @@
       </c>
       <c r="S8" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -906,7 +906,7 @@
       </c>
       <c r="S9" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -991,7 +991,7 @@
       </c>
       <c r="S10" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="S11" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -1161,7 +1161,7 @@
       </c>
       <c r="S12" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -1246,7 +1246,7 @@
       </c>
       <c r="S13" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -1331,7 +1331,7 @@
       </c>
       <c r="S14" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -1416,7 +1416,7 @@
       </c>
       <c r="S15" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -1501,7 +1501,7 @@
       </c>
       <c r="S16" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -1586,7 +1586,7 @@
       </c>
       <c r="S17" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -1671,7 +1671,7 @@
       </c>
       <c r="S18" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -1756,7 +1756,7 @@
       </c>
       <c r="S19" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -1841,7 +1841,7 @@
       </c>
       <c r="S20" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -1926,7 +1926,7 @@
       </c>
       <c r="S21" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -2011,7 +2011,7 @@
       </c>
       <c r="S22" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="S23" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -2181,7 +2181,7 @@
       </c>
       <c r="S24" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -2266,7 +2266,7 @@
       </c>
       <c r="S25" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -2351,7 +2351,7 @@
       </c>
       <c r="S26" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -2436,7 +2436,7 @@
       </c>
       <c r="S27" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -2521,7 +2521,7 @@
       </c>
       <c r="S28" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -2606,7 +2606,7 @@
       </c>
       <c r="S29" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -2691,7 +2691,7 @@
       </c>
       <c r="S30" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -2776,7 +2776,7 @@
       </c>
       <c r="S31" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -2861,7 +2861,7 @@
       </c>
       <c r="S32" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -2946,7 +2946,7 @@
       </c>
       <c r="S33" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -3031,7 +3031,7 @@
       </c>
       <c r="S34" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -3116,7 +3116,7 @@
       </c>
       <c r="S35" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -3201,7 +3201,7 @@
       </c>
       <c r="S36" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -3286,7 +3286,7 @@
       </c>
       <c r="S37" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -3371,7 +3371,7 @@
       </c>
       <c r="S38" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -3456,7 +3456,7 @@
       </c>
       <c r="S39" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -3541,7 +3541,7 @@
       </c>
       <c r="S40" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -3626,7 +3626,7 @@
       </c>
       <c r="S41" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -3711,7 +3711,7 @@
       </c>
       <c r="S42" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -3796,7 +3796,7 @@
       </c>
       <c r="S43" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -3881,7 +3881,7 @@
       </c>
       <c r="S44" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -3966,7 +3966,7 @@
       </c>
       <c r="S45" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -4051,7 +4051,7 @@
       </c>
       <c r="S46" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -4136,7 +4136,7 @@
       </c>
       <c r="S47" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -4221,7 +4221,7 @@
       </c>
       <c r="S48" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -4306,7 +4306,7 @@
       </c>
       <c r="S49" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -4391,7 +4391,7 @@
       </c>
       <c r="S50" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -4476,7 +4476,7 @@
       </c>
       <c r="S51" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -4561,7 +4561,7 @@
       </c>
       <c r="S52" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -4646,7 +4646,7 @@
       </c>
       <c r="S53" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -4731,7 +4731,7 @@
       </c>
       <c r="S54" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -4816,7 +4816,7 @@
       </c>
       <c r="S55" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -4901,7 +4901,7 @@
       </c>
       <c r="S56" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -4986,7 +4986,7 @@
       </c>
       <c r="S57" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -5071,7 +5071,7 @@
       </c>
       <c r="S58" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -5156,7 +5156,7 @@
       </c>
       <c r="S59" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -5241,7 +5241,7 @@
       </c>
       <c r="S60" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -5326,7 +5326,7 @@
       </c>
       <c r="S61" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -5411,7 +5411,7 @@
       </c>
       <c r="S62" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -5496,7 +5496,7 @@
       </c>
       <c r="S63" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -5581,7 +5581,7 @@
       </c>
       <c r="S64" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -5666,7 +5666,7 @@
       </c>
       <c r="S65" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -5751,7 +5751,7 @@
       </c>
       <c r="S66" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -5836,7 +5836,7 @@
       </c>
       <c r="S67" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -5921,7 +5921,7 @@
       </c>
       <c r="S68" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -6006,7 +6006,7 @@
       </c>
       <c r="S69" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -6091,7 +6091,7 @@
       </c>
       <c r="S70" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -6176,7 +6176,7 @@
       </c>
       <c r="S71" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -6261,7 +6261,7 @@
       </c>
       <c r="S72" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -6346,7 +6346,7 @@
       </c>
       <c r="S73" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -6431,7 +6431,7 @@
       </c>
       <c r="S74" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -6516,7 +6516,7 @@
       </c>
       <c r="S75" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -6601,7 +6601,7 @@
       </c>
       <c r="S76" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -6686,7 +6686,7 @@
       </c>
       <c r="S77" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -6771,7 +6771,7 @@
       </c>
       <c r="S78" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -6856,7 +6856,7 @@
       </c>
       <c r="S79" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -6941,7 +6941,7 @@
       </c>
       <c r="S80" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -7026,7 +7026,7 @@
       </c>
       <c r="S81" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -7111,7 +7111,7 @@
       </c>
       <c r="S82" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -7196,7 +7196,7 @@
       </c>
       <c r="S83" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -7281,7 +7281,7 @@
       </c>
       <c r="S84" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -7366,7 +7366,7 @@
       </c>
       <c r="S85" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -7451,7 +7451,7 @@
       </c>
       <c r="S86" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -7536,7 +7536,7 @@
       </c>
       <c r="S87" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -7621,7 +7621,7 @@
       </c>
       <c r="S88" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -7706,7 +7706,7 @@
       </c>
       <c r="S89" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -7791,7 +7791,7 @@
       </c>
       <c r="S90" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -7876,7 +7876,7 @@
       </c>
       <c r="S91" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -7961,7 +7961,7 @@
       </c>
       <c r="S92" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -8046,7 +8046,7 @@
       </c>
       <c r="S93" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -8131,7 +8131,7 @@
       </c>
       <c r="S94" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -8216,7 +8216,7 @@
       </c>
       <c r="S95" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -8301,7 +8301,7 @@
       </c>
       <c r="S96" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -8386,7 +8386,7 @@
       </c>
       <c r="S97" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -8471,7 +8471,7 @@
       </c>
       <c r="S98" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -8556,7 +8556,7 @@
       </c>
       <c r="S99" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -8641,7 +8641,7 @@
       </c>
       <c r="S100" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -8726,7 +8726,7 @@
       </c>
       <c r="S101" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -8811,7 +8811,7 @@
       </c>
       <c r="S102" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -8896,7 +8896,7 @@
       </c>
       <c r="S103" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -8981,7 +8981,7 @@
       </c>
       <c r="S104" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -9066,7 +9066,7 @@
       </c>
       <c r="S105" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -9151,7 +9151,7 @@
       </c>
       <c r="S106" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -9236,7 +9236,7 @@
       </c>
       <c r="S107" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -9321,7 +9321,7 @@
       </c>
       <c r="S108" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -9406,7 +9406,7 @@
       </c>
       <c r="S109" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -9491,7 +9491,7 @@
       </c>
       <c r="S110" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -9576,7 +9576,7 @@
       </c>
       <c r="S111" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -9661,7 +9661,7 @@
       </c>
       <c r="S112" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -9746,7 +9746,7 @@
       </c>
       <c r="S113" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -9831,7 +9831,7 @@
       </c>
       <c r="S114" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -9916,7 +9916,7 @@
       </c>
       <c r="S115" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -10001,7 +10001,7 @@
       </c>
       <c r="S116" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -10086,7 +10086,7 @@
       </c>
       <c r="S117" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -10171,7 +10171,7 @@
       </c>
       <c r="S118" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -10256,7 +10256,7 @@
       </c>
       <c r="S119" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -10341,7 +10341,7 @@
       </c>
       <c r="S120" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -10426,7 +10426,7 @@
       </c>
       <c r="S121" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -10511,7 +10511,7 @@
       </c>
       <c r="S122" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -10596,7 +10596,7 @@
       </c>
       <c r="S123" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -10681,7 +10681,7 @@
       </c>
       <c r="S124" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -10766,7 +10766,7 @@
       </c>
       <c r="S125" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -10851,7 +10851,7 @@
       </c>
       <c r="S126" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -10936,7 +10936,7 @@
       </c>
       <c r="S127" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -11021,7 +11021,7 @@
       </c>
       <c r="S128" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -11106,7 +11106,7 @@
       </c>
       <c r="S129" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -11191,7 +11191,7 @@
       </c>
       <c r="S130" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -11276,7 +11276,7 @@
       </c>
       <c r="S131" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -11361,7 +11361,7 @@
       </c>
       <c r="S132" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -11446,7 +11446,7 @@
       </c>
       <c r="S133" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -11531,7 +11531,7 @@
       </c>
       <c r="S134" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -11616,7 +11616,7 @@
       </c>
       <c r="S135" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -11701,7 +11701,7 @@
       </c>
       <c r="S136" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -11786,7 +11786,7 @@
       </c>
       <c r="S137" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -11871,7 +11871,7 @@
       </c>
       <c r="S138" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -11956,7 +11956,7 @@
       </c>
       <c r="S139" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -12041,7 +12041,7 @@
       </c>
       <c r="S140" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -12126,7 +12126,7 @@
       </c>
       <c r="S141" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -12258,7 +12258,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -12338,7 +12338,7 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>{"dataset_id": "bcv_pib_historico_anual", "title": "Producto interno bruto histórico anual", "table": "PIB histórico anual", "source_file": "7_1_14_anual.xls", "base": "1957/1968/1984/1997", "price_type": "Precios constantes", "measure": "Nivel", "frequency": "Anual", "period": "2017", "year": 2017, "quarter": null, "classification": "Total economía", "component": "Producto interno bruto", "value": 392393.12, "unit": "Millones de bolívares a precios constantes", "status": "", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/7_1_14_anual.xls", "fetched_at": "2026-08-02T21:23:58Z"}</t>
+          <t>{"dataset_id": "bcv_pib_historico_anual", "title": "Producto interno bruto histórico anual", "table": "PIB histórico anual", "source_file": "7_1_14_anual.xls", "base": "1957/1968/1984/1997", "price_type": "Precios constantes", "measure": "Nivel", "frequency": "Anual", "period": "2017", "year": 2017, "quarter": null, "classification": "Total economía", "component": "Producto interno bruto", "value": 392393.12, "unit": "Millones de bolívares a precios constantes", "status": "", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/7_1_14_anual.xls", "fetched_at": "2026-08-03T21:38:53Z"}</t>
         </is>
       </c>
     </row>

--- a/assets/data/bcv/excel/ove_bcv_pib_historico_anual.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_pib_historico_anual.xlsx
@@ -736,7 +736,7 @@
       </c>
       <c r="S7" s="4" t="inlineStr">
         <is>
-          <t>2026-08-03T21:38:53Z</t>
+          <t>2026-08-04T21:47:55Z</t>
         </is>
       </c>
     </row>
@@ -821,7 +821,7 @@
       </c>
       <c r="S8" s="4" t="inlineStr">
         <is>
-          <t>2026-08-03T21:38:53Z</t>
+          <t>2026-08-04T21:47:55Z</t>
         </is>
       </c>
     </row>
@@ -906,7 +906,7 @@
       </c>
       <c r="S9" s="4" t="inlineStr">
         <is>
-          <t>2026-08-03T21:38:53Z</t>
+          <t>2026-08-04T21:47:55Z</t>
         </is>
       </c>
     </row>
@@ -991,7 +991,7 @@
       </c>
       <c r="S10" s="4" t="inlineStr">
         <is>
-          <t>2026-08-03T21:38:53Z</t>
+          <t>2026-08-04T21:47:55Z</t>
         </is>
       </c>
     </row>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="S11" s="4" t="inlineStr">
         <is>
-          <t>2026-08-03T21:38:53Z</t>
+          <t>2026-08-04T21:47:55Z</t>
         </is>
       </c>
     </row>
@@ -1161,7 +1161,7 @@
       </c>
       <c r="S12" s="4" t="inlineStr">
         <is>
-          <t>2026-08-03T21:38:53Z</t>
+          <t>2026-08-04T21:47:55Z</t>
         </is>
       </c>
     </row>
@@ -1246,7 +1246,7 @@
       </c>
       <c r="S13" s="4" t="inlineStr">
         <is>
-          <t>2026-08-03T21:38:53Z</t>
+          <t>2026-08-04T21:47:55Z</t>
         </is>
       </c>
     </row>
@@ -1331,7 +1331,7 @@
       </c>
       <c r="S14" s="4" t="inlineStr">
         <is>
-          <t>2026-08-03T21:38:53Z</t>
+          <t>2026-08-04T21:47:55Z</t>
         </is>
       </c>
     </row>
@@ -1416,7 +1416,7 @@
       </c>
       <c r="S15" s="4" t="inlineStr">
         <is>
-          <t>2026-08-03T21:38:53Z</t>
+          <t>2026-08-04T21:47:55Z</t>
         </is>
       </c>
     </row>
@@ -1501,7 +1501,7 @@
       </c>
       <c r="S16" s="4" t="inlineStr">
         <is>
-          <t>2026-08-03T21:38:53Z</t>
+          <t>2026-08-04T21:47:55Z</t>
         </is>
       </c>
     </row>
@@ -1586,7 +1586,7 @@
       </c>
       <c r="S17" s="4" t="inlineStr">
         <is>
-          <t>2026-08-03T21:38:53Z</t>
+          <t>2026-08-04T21:47:55Z</t>
         </is>
       </c>
     </row>
@@ -1671,7 +1671,7 @@
       </c>
       <c r="S18" s="4" t="inlineStr">
         <is>
-          <t>2026-08-03T21:38:53Z</t>
+          <t>2026-08-04T21:47:55Z</t>
         </is>
       </c>
     </row>
@@ -1756,7 +1756,7 @@
       </c>
       <c r="S19" s="4" t="inlineStr">
         <is>
-          <t>2026-08-03T21:38:53Z</t>
+          <t>2026-08-04T21:47:55Z</t>
         </is>
       </c>
     </row>
@@ -1841,7 +1841,7 @@
       </c>
       <c r="S20" s="4" t="inlineStr">
         <is>
-          <t>2026-08-03T21:38:53Z</t>
+          <t>2026-08-04T21:47:55Z</t>
         </is>
       </c>
     </row>
@@ -1926,7 +1926,7 @@
       </c>
       <c r="S21" s="4" t="inlineStr">
         <is>
-          <t>2026-08-03T21:38:53Z</t>
+          <t>2026-08-04T21:47:55Z</t>
         </is>
       </c>
     </row>
@@ -2011,7 +2011,7 @@
       </c>
       <c r="S22" s="4" t="inlineStr">
         <is>
-          <t>2026-08-03T21:38:53Z</t>
+          <t>2026-08-04T21:47:55Z</t>
         </is>
       </c>
     </row>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="S23" s="4" t="inlineStr">
         <is>
-          <t>2026-08-03T21:38:53Z</t>
+          <t>2026-08-04T21:47:55Z</t>
         </is>
       </c>
     </row>
@@ -2181,7 +2181,7 @@
       </c>
       <c r="S24" s="4" t="inlineStr">
         <is>
-          <t>2026-08-03T21:38:53Z</t>
+          <t>2026-08-04T21:47:55Z</t>
         </is>
       </c>
     </row>
@@ -2266,7 +2266,7 @@
       </c>
       <c r="S25" s="4" t="inlineStr">
         <is>
-          <t>2026-08-03T21:38:53Z</t>
+          <t>2026-08-04T21:47:55Z</t>
         </is>
       </c>
     </row>
@@ -2351,7 +2351,7 @@
       </c>
       <c r="S26" s="4" t="inlineStr">
         <is>
-          <t>2026-08-03T21:38:53Z</t>
+          <t>2026-08-04T21:47:55Z</t>
         </is>
       </c>
     </row>
@@ -2436,7 +2436,7 @@
       </c>
       <c r="S27" s="4" t="inlineStr">
         <is>
-          <t>2026-08-03T21:38:53Z</t>
+          <t>2026-08-04T21:47:55Z</t>
         </is>
       </c>
     </row>
@@ -2521,7 +2521,7 @@
       </c>
       <c r="S28" s="4" t="inlineStr">
         <is>
-          <t>2026-08-03T21:38:53Z</t>
+          <t>2026-08-04T21:47:55Z</t>
         </is>
       </c>
     </row>
@@ -2606,7 +2606,7 @@
       </c>
       <c r="S29" s="4" t="inlineStr">
         <is>
-          <t>2026-08-03T21:38:53Z</t>
+          <t>2026-08-04T21:47:55Z</t>
         </is>
       </c>
     </row>
@@ -2691,7 +2691,7 @@
       </c>
       <c r="S30" s="4" t="inlineStr">
         <is>
-          <t>2026-08-03T21:38:53Z</t>
+          <t>2026-08-04T21:47:55Z</t>
         </is>
       </c>
     </row>
@@ -2776,7 +2776,7 @@
       </c>
       <c r="S31" s="4" t="inlineStr">
         <is>
-          <t>2026-08-03T21:38:53Z</t>
+          <t>2026-08-04T21:47:55Z</t>
         </is>
       </c>
     </row>
@@ -2861,7 +2861,7 @@
       </c>
       <c r="S32" s="4" t="inlineStr">
         <is>
-          <t>2026-08-03T21:38:53Z</t>
+          <t>2026-08-04T21:47:55Z</t>
         </is>
       </c>
     </row>
@@ -2946,7 +2946,7 @@
       </c>
       <c r="S33" s="4" t="inlineStr">
         <is>
-          <t>2026-08-03T21:38:53Z</t>
+          <t>2026-08-04T21:47:55Z</t>
         </is>
       </c>
     </row>
@@ -3031,7 +3031,7 @@
       </c>
       <c r="S34" s="4" t="inlineStr">
         <is>
-          <t>2026-08-03T21:38:53Z</t>
+          <t>2026-08-04T21:47:55Z</t>
         </is>
       </c>
     </row>
@@ -3116,7 +3116,7 @@
       </c>
       <c r="S35" s="4" t="inlineStr">
         <is>
-          <t>2026-08-03T21:38:53Z</t>
+          <t>2026-08-04T21:47:55Z</t>
         </is>
       </c>
     </row>
@@ -3201,7 +3201,7 @@
       </c>
       <c r="S36" s="4" t="inlineStr">
         <is>
-          <t>2026-08-03T21:38:53Z</t>
+          <t>2026-08-04T21:47:55Z</t>
         </is>
       </c>
     </row>
@@ -3286,7 +3286,7 @@
       </c>
       <c r="S37" s="4" t="inlineStr">
         <is>
-          <t>2026-08-03T21:38:53Z</t>
+          <t>2026-08-04T21:47:55Z</t>
         </is>
       </c>
     </row>
@@ -3371,7 +3371,7 @@
       </c>
       <c r="S38" s="4" t="inlineStr">
         <is>
-          <t>2026-08-03T21:38:53Z</t>
+          <t>2026-08-04T21:47:55Z</t>
         </is>
       </c>
     </row>
@@ -3456,7 +3456,7 @@
       </c>
       <c r="S39" s="4" t="inlineStr">
         <is>
-          <t>2026-08-03T21:38:53Z</t>
+          <t>2026-08-04T21:47:55Z</t>
         </is>
       </c>
     </row>
@@ -3541,7 +3541,7 @@
       </c>
       <c r="S40" s="4" t="inlineStr">
         <is>
-          <t>2026-08-03T21:38:53Z</t>
+          <t>2026-08-04T21:47:55Z</t>
         </is>
       </c>
     </row>
@@ -3626,7 +3626,7 @@
       </c>
       <c r="S41" s="4" t="inlineStr">
         <is>
-          <t>2026-08-03T21:38:53Z</t>
+          <t>2026-08-04T21:47:55Z</t>
         </is>
       </c>
     </row>
@@ -3711,7 +3711,7 @@
       </c>
       <c r="S42" s="4" t="inlineStr">
         <is>
-          <t>2026-08-03T21:38:53Z</t>
+          <t>2026-08-04T21:47:55Z</t>
         </is>
       </c>
     </row>
@@ -3796,7 +3796,7 @@
       </c>
       <c r="S43" s="4" t="inlineStr">
         <is>
-          <t>2026-08-03T21:38:53Z</t>
+          <t>2026-08-04T21:47:55Z</t>
         </is>
       </c>
     </row>
@@ -3881,7 +3881,7 @@
       </c>
       <c r="S44" s="4" t="inlineStr">
         <is>
-          <t>2026-08-03T21:38:53Z</t>
+          <t>2026-08-04T21:47:55Z</t>
         </is>
       </c>
     </row>
@@ -3966,7 +3966,7 @@
       </c>
       <c r="S45" s="4" t="inlineStr">
         <is>
-          <t>2026-08-03T21:38:53Z</t>
+          <t>2026-08-04T21:47:55Z</t>
         </is>
       </c>
     </row>
@@ -4051,7 +4051,7 @@
       </c>
       <c r="S46" s="4" t="inlineStr">
         <is>
-          <t>2026-08-03T21:38:53Z</t>
+          <t>2026-08-04T21:47:55Z</t>
         </is>
       </c>
     </row>
@@ -4136,7 +4136,7 @@
       </c>
       <c r="S47" s="4" t="inlineStr">
         <is>
-          <t>2026-08-03T21:38:53Z</t>
+          <t>2026-08-04T21:47:55Z</t>
         </is>
       </c>
     </row>
@@ -4221,7 +4221,7 @@
       </c>
       <c r="S48" s="4" t="inlineStr">
         <is>
-          <t>2026-08-03T21:38:53Z</t>
+          <t>2026-08-04T21:47:55Z</t>
         </is>
       </c>
     </row>
@@ -4306,7 +4306,7 @@
       </c>
       <c r="S49" s="4" t="inlineStr">
         <is>
-          <t>2026-08-03T21:38:53Z</t>
+          <t>2026-08-04T21:47:55Z</t>
         </is>
       </c>
     </row>
@@ -4391,7 +4391,7 @@
       </c>
       <c r="S50" s="4" t="inlineStr">
         <is>
-          <t>2026-08-03T21:38:53Z</t>
+          <t>2026-08-04T21:47:55Z</t>
         </is>
       </c>
     </row>
@@ -4476,7 +4476,7 @@
       </c>
       <c r="S51" s="4" t="inlineStr">
         <is>
-          <t>2026-08-03T21:38:53Z</t>
+          <t>2026-08-04T21:47:55Z</t>
         </is>
       </c>
     </row>
@@ -4561,7 +4561,7 @@
       </c>
       <c r="S52" s="4" t="inlineStr">
         <is>
-          <t>2026-08-03T21:38:53Z</t>
+          <t>2026-08-04T21:47:55Z</t>
         </is>
       </c>
     </row>
@@ -4646,7 +4646,7 @@
       </c>
       <c r="S53" s="4" t="inlineStr">
         <is>
-          <t>2026-08-03T21:38:53Z</t>
+          <t>2026-08-04T21:47:55Z</t>
         </is>
       </c>
     </row>
@@ -4731,7 +4731,7 @@
       </c>
       <c r="S54" s="4" t="inlineStr">
         <is>
-          <t>2026-08-03T21:38:53Z</t>
+          <t>2026-08-04T21:47:55Z</t>
         </is>
       </c>
     </row>
@@ -4816,7 +4816,7 @@
       </c>
       <c r="S55" s="4" t="inlineStr">
         <is>
-          <t>2026-08-03T21:38:53Z</t>
+          <t>2026-08-04T21:47:55Z</t>
         </is>
       </c>
     </row>
@@ -4901,7 +4901,7 @@
       </c>
       <c r="S56" s="4" t="inlineStr">
         <is>
-          <t>2026-08-03T21:38:53Z</t>
+          <t>2026-08-04T21:47:55Z</t>
         </is>
       </c>
     </row>
@@ -4986,7 +4986,7 @@
       </c>
       <c r="S57" s="4" t="inlineStr">
         <is>
-          <t>2026-08-03T21:38:53Z</t>
+          <t>2026-08-04T21:47:55Z</t>
         </is>
       </c>
     </row>
@@ -5071,7 +5071,7 @@
       </c>
       <c r="S58" s="4" t="inlineStr">
         <is>
-          <t>2026-08-03T21:38:53Z</t>
+          <t>2026-08-04T21:47:55Z</t>
         </is>
       </c>
     </row>
@@ -5156,7 +5156,7 @@
       </c>
       <c r="S59" s="4" t="inlineStr">
         <is>
-          <t>2026-08-03T21:38:53Z</t>
+          <t>2026-08-04T21:47:55Z</t>
         </is>
       </c>
     </row>
@@ -5241,7 +5241,7 @@
       </c>
       <c r="S60" s="4" t="inlineStr">
         <is>
-          <t>2026-08-03T21:38:53Z</t>
+          <t>2026-08-04T21:47:55Z</t>
         </is>
       </c>
     </row>
@@ -5326,7 +5326,7 @@
       </c>
       <c r="S61" s="4" t="inlineStr">
         <is>
-          <t>2026-08-03T21:38:53Z</t>
+          <t>2026-08-04T21:47:55Z</t>
         </is>
       </c>
     </row>
@@ -5411,7 +5411,7 @@
       </c>
       <c r="S62" s="4" t="inlineStr">
         <is>
-          <t>2026-08-03T21:38:53Z</t>
+          <t>2026-08-04T21:47:55Z</t>
         </is>
       </c>
     </row>
@@ -5496,7 +5496,7 @@
       </c>
       <c r="S63" s="4" t="inlineStr">
         <is>
-          <t>2026-08-03T21:38:53Z</t>
+          <t>2026-08-04T21:47:55Z</t>
         </is>
       </c>
     </row>
@@ -5581,7 +5581,7 @@
       </c>
       <c r="S64" s="4" t="inlineStr">
         <is>
-          <t>2026-08-03T21:38:53Z</t>
+          <t>2026-08-04T21:47:55Z</t>
         </is>
       </c>
     </row>
@@ -5666,7 +5666,7 @@
       </c>
       <c r="S65" s="4" t="inlineStr">
         <is>
-          <t>2026-08-03T21:38:53Z</t>
+          <t>2026-08-04T21:47:55Z</t>
         </is>
       </c>
     </row>
@@ -5751,7 +5751,7 @@
       </c>
       <c r="S66" s="4" t="inlineStr">
         <is>
-          <t>2026-08-03T21:38:53Z</t>
+          <t>2026-08-04T21:47:55Z</t>
         </is>
       </c>
     </row>
@@ -5836,7 +5836,7 @@
       </c>
       <c r="S67" s="4" t="inlineStr">
         <is>
-          <t>2026-08-03T21:38:53Z</t>
+          <t>2026-08-04T21:47:55Z</t>
         </is>
       </c>
     </row>
@@ -5921,7 +5921,7 @@
       </c>
       <c r="S68" s="4" t="inlineStr">
         <is>
-          <t>2026-08-03T21:38:53Z</t>
+          <t>2026-08-04T21:47:55Z</t>
         </is>
       </c>
     </row>
@@ -6006,7 +6006,7 @@
       </c>
       <c r="S69" s="4" t="inlineStr">
         <is>
-          <t>2026-08-03T21:38:53Z</t>
+          <t>2026-08-04T21:47:55Z</t>
         </is>
       </c>
     </row>
@@ -6091,7 +6091,7 @@
       </c>
       <c r="S70" s="4" t="inlineStr">
         <is>
-          <t>2026-08-03T21:38:53Z</t>
+          <t>2026-08-04T21:47:55Z</t>
         </is>
       </c>
     </row>
@@ -6176,7 +6176,7 @@
       </c>
       <c r="S71" s="4" t="inlineStr">
         <is>
-          <t>2026-08-03T21:38:53Z</t>
+          <t>2026-08-04T21:47:55Z</t>
         </is>
       </c>
     </row>
@@ -6261,7 +6261,7 @@
       </c>
       <c r="S72" s="4" t="inlineStr">
         <is>
-          <t>2026-08-03T21:38:53Z</t>
+          <t>2026-08-04T21:47:55Z</t>
         </is>
       </c>
     </row>
@@ -6346,7 +6346,7 @@
       </c>
       <c r="S73" s="4" t="inlineStr">
         <is>
-          <t>2026-08-03T21:38:53Z</t>
+          <t>2026-08-04T21:47:55Z</t>
         </is>
       </c>
     </row>
@@ -6431,7 +6431,7 @@
       </c>
       <c r="S74" s="4" t="inlineStr">
         <is>
-          <t>2026-08-03T21:38:53Z</t>
+          <t>2026-08-04T21:47:55Z</t>
         </is>
       </c>
     </row>
@@ -6516,7 +6516,7 @@
       </c>
       <c r="S75" s="4" t="inlineStr">
         <is>
-          <t>2026-08-03T21:38:53Z</t>
+          <t>2026-08-04T21:47:55Z</t>
         </is>
       </c>
     </row>
@@ -6601,7 +6601,7 @@
       </c>
       <c r="S76" s="4" t="inlineStr">
         <is>
-          <t>2026-08-03T21:38:53Z</t>
+          <t>2026-08-04T21:47:55Z</t>
         </is>
       </c>
     </row>
@@ -6686,7 +6686,7 @@
       </c>
       <c r="S77" s="4" t="inlineStr">
         <is>
-          <t>2026-08-03T21:38:53Z</t>
+          <t>2026-08-04T21:47:55Z</t>
         </is>
       </c>
     </row>
@@ -6771,7 +6771,7 @@
       </c>
       <c r="S78" s="4" t="inlineStr">
         <is>
-          <t>2026-08-03T21:38:53Z</t>
+          <t>2026-08-04T21:47:55Z</t>
         </is>
       </c>
     </row>
@@ -6856,7 +6856,7 @@
       </c>
       <c r="S79" s="4" t="inlineStr">
         <is>
-          <t>2026-08-03T21:38:53Z</t>
+          <t>2026-08-04T21:47:55Z</t>
         </is>
       </c>
     </row>
@@ -6941,7 +6941,7 @@
       </c>
       <c r="S80" s="4" t="inlineStr">
         <is>
-          <t>2026-08-03T21:38:53Z</t>
+          <t>2026-08-04T21:47:55Z</t>
         </is>
       </c>
     </row>
@@ -7026,7 +7026,7 @@
       </c>
       <c r="S81" s="4" t="inlineStr">
         <is>
-          <t>2026-08-03T21:38:53Z</t>
+          <t>2026-08-04T21:47:55Z</t>
         </is>
       </c>
     </row>
@@ -7111,7 +7111,7 @@
       </c>
       <c r="S82" s="4" t="inlineStr">
         <is>
-          <t>2026-08-03T21:38:53Z</t>
+          <t>2026-08-04T21:47:55Z</t>
         </is>
       </c>
     </row>
@@ -7196,7 +7196,7 @@
       </c>
       <c r="S83" s="4" t="inlineStr">
         <is>
-          <t>2026-08-03T21:38:53Z</t>
+          <t>2026-08-04T21:47:55Z</t>
         </is>
       </c>
     </row>
@@ -7281,7 +7281,7 @@
       </c>
       <c r="S84" s="4" t="inlineStr">
         <is>
-          <t>2026-08-03T21:38:53Z</t>
+          <t>2026-08-04T21:47:55Z</t>
         </is>
       </c>
     </row>
@@ -7366,7 +7366,7 @@
       </c>
       <c r="S85" s="4" t="inlineStr">
         <is>
-          <t>2026-08-03T21:38:53Z</t>
+          <t>2026-08-04T21:47:55Z</t>
         </is>
       </c>
     </row>
@@ -7451,7 +7451,7 @@
       </c>
       <c r="S86" s="4" t="inlineStr">
         <is>
-          <t>2026-08-03T21:38:53Z</t>
+          <t>2026-08-04T21:47:55Z</t>
         </is>
       </c>
     </row>
@@ -7536,7 +7536,7 @@
       </c>
       <c r="S87" s="4" t="inlineStr">
         <is>
-          <t>2026-08-03T21:38:53Z</t>
+          <t>2026-08-04T21:47:55Z</t>
         </is>
       </c>
     </row>
@@ -7621,7 +7621,7 @@
       </c>
       <c r="S88" s="4" t="inlineStr">
         <is>
-          <t>2026-08-03T21:38:53Z</t>
+          <t>2026-08-04T21:47:55Z</t>
         </is>
       </c>
     </row>
@@ -7706,7 +7706,7 @@
       </c>
       <c r="S89" s="4" t="inlineStr">
         <is>
-          <t>2026-08-03T21:38:53Z</t>
+          <t>2026-08-04T21:47:55Z</t>
         </is>
       </c>
     </row>
@@ -7791,7 +7791,7 @@
       </c>
       <c r="S90" s="4" t="inlineStr">
         <is>
-          <t>2026-08-03T21:38:53Z</t>
+          <t>2026-08-04T21:47:55Z</t>
         </is>
       </c>
     </row>
@@ -7876,7 +7876,7 @@
       </c>
       <c r="S91" s="4" t="inlineStr">
         <is>
-          <t>2026-08-03T21:38:53Z</t>
+          <t>2026-08-04T21:47:55Z</t>
         </is>
       </c>
     </row>
@@ -7961,7 +7961,7 @@
       </c>
       <c r="S92" s="4" t="inlineStr">
         <is>
-          <t>2026-08-03T21:38:53Z</t>
+          <t>2026-08-04T21:47:55Z</t>
         </is>
       </c>
     </row>
@@ -8046,7 +8046,7 @@
       </c>
       <c r="S93" s="4" t="inlineStr">
         <is>
-          <t>2026-08-03T21:38:53Z</t>
+          <t>2026-08-04T21:47:55Z</t>
         </is>
       </c>
     </row>
@@ -8131,7 +8131,7 @@
       </c>
       <c r="S94" s="4" t="inlineStr">
         <is>
-          <t>2026-08-03T21:38:53Z</t>
+          <t>2026-08-04T21:47:55Z</t>
         </is>
       </c>
     </row>
@@ -8216,7 +8216,7 @@
       </c>
       <c r="S95" s="4" t="inlineStr">
         <is>
-          <t>2026-08-03T21:38:53Z</t>
+          <t>2026-08-04T21:47:55Z</t>
         </is>
       </c>
     </row>
@@ -8301,7 +8301,7 @@
       </c>
       <c r="S96" s="4" t="inlineStr">
         <is>
-          <t>2026-08-03T21:38:53Z</t>
+          <t>2026-08-04T21:47:55Z</t>
         </is>
       </c>
     </row>
@@ -8386,7 +8386,7 @@
       </c>
       <c r="S97" s="4" t="inlineStr">
         <is>
-          <t>2026-08-03T21:38:53Z</t>
+          <t>2026-08-04T21:47:55Z</t>
         </is>
       </c>
     </row>
@@ -8471,7 +8471,7 @@
       </c>
       <c r="S98" s="4" t="inlineStr">
         <is>
-          <t>2026-08-03T21:38:53Z</t>
+          <t>2026-08-04T21:47:55Z</t>
         </is>
       </c>
     </row>
@@ -8556,7 +8556,7 @@
       </c>
       <c r="S99" s="4" t="inlineStr">
         <is>
-          <t>2026-08-03T21:38:53Z</t>
+          <t>2026-08-04T21:47:55Z</t>
         </is>
       </c>
     </row>
@@ -8641,7 +8641,7 @@
       </c>
       <c r="S100" s="4" t="inlineStr">
         <is>
-          <t>2026-08-03T21:38:53Z</t>
+          <t>2026-08-04T21:47:55Z</t>
         </is>
       </c>
     </row>
@@ -8726,7 +8726,7 @@
       </c>
       <c r="S101" s="4" t="inlineStr">
         <is>
-          <t>2026-08-03T21:38:53Z</t>
+          <t>2026-08-04T21:47:55Z</t>
         </is>
       </c>
     </row>
@@ -8811,7 +8811,7 @@
       </c>
       <c r="S102" s="4" t="inlineStr">
         <is>
-          <t>2026-08-03T21:38:53Z</t>
+          <t>2026-08-04T21:47:55Z</t>
         </is>
       </c>
     </row>
@@ -8896,7 +8896,7 @@
       </c>
       <c r="S103" s="4" t="inlineStr">
         <is>
-          <t>2026-08-03T21:38:53Z</t>
+          <t>2026-08-04T21:47:55Z</t>
         </is>
       </c>
     </row>
@@ -8981,7 +8981,7 @@
       </c>
       <c r="S104" s="4" t="inlineStr">
         <is>
-          <t>2026-08-03T21:38:53Z</t>
+          <t>2026-08-04T21:47:55Z</t>
         </is>
       </c>
     </row>
@@ -9066,7 +9066,7 @@
       </c>
       <c r="S105" s="4" t="inlineStr">
         <is>
-          <t>2026-08-03T21:38:53Z</t>
+          <t>2026-08-04T21:47:55Z</t>
         </is>
       </c>
     </row>
@@ -9151,7 +9151,7 @@
       </c>
       <c r="S106" s="4" t="inlineStr">
         <is>
-          <t>2026-08-03T21:38:53Z</t>
+          <t>2026-08-04T21:47:55Z</t>
         </is>
       </c>
     </row>
@@ -9236,7 +9236,7 @@
       </c>
       <c r="S107" s="4" t="inlineStr">
         <is>
-          <t>2026-08-03T21:38:53Z</t>
+          <t>2026-08-04T21:47:55Z</t>
         </is>
       </c>
     </row>
@@ -9321,7 +9321,7 @@
       </c>
       <c r="S108" s="4" t="inlineStr">
         <is>
-          <t>2026-08-03T21:38:53Z</t>
+          <t>2026-08-04T21:47:55Z</t>
         </is>
       </c>
     </row>
@@ -9406,7 +9406,7 @@
       </c>
       <c r="S109" s="4" t="inlineStr">
         <is>
-          <t>2026-08-03T21:38:53Z</t>
+          <t>2026-08-04T21:47:55Z</t>
         </is>
       </c>
     </row>
@@ -9491,7 +9491,7 @@
       </c>
       <c r="S110" s="4" t="inlineStr">
         <is>
-          <t>2026-08-03T21:38:53Z</t>
+          <t>2026-08-04T21:47:55Z</t>
         </is>
       </c>
     </row>
@@ -9576,7 +9576,7 @@
       </c>
       <c r="S111" s="4" t="inlineStr">
         <is>
-          <t>2026-08-03T21:38:53Z</t>
+          <t>2026-08-04T21:47:55Z</t>
         </is>
       </c>
     </row>
@@ -9661,7 +9661,7 @@
       </c>
       <c r="S112" s="4" t="inlineStr">
         <is>
-          <t>2026-08-03T21:38:53Z</t>
+          <t>2026-08-04T21:47:55Z</t>
         </is>
       </c>
     </row>
@@ -9746,7 +9746,7 @@
       </c>
       <c r="S113" s="4" t="inlineStr">
         <is>
-          <t>2026-08-03T21:38:53Z</t>
+          <t>2026-08-04T21:47:55Z</t>
         </is>
       </c>
     </row>
@@ -9831,7 +9831,7 @@
       </c>
       <c r="S114" s="4" t="inlineStr">
         <is>
-          <t>2026-08-03T21:38:53Z</t>
+          <t>2026-08-04T21:47:55Z</t>
         </is>
       </c>
     </row>
@@ -9916,7 +9916,7 @@
       </c>
       <c r="S115" s="4" t="inlineStr">
         <is>
-          <t>2026-08-03T21:38:53Z</t>
+          <t>2026-08-04T21:47:55Z</t>
         </is>
       </c>
     </row>
@@ -10001,7 +10001,7 @@
       </c>
       <c r="S116" s="4" t="inlineStr">
         <is>
-          <t>2026-08-03T21:38:53Z</t>
+          <t>2026-08-04T21:47:55Z</t>
         </is>
       </c>
     </row>
@@ -10086,7 +10086,7 @@
       </c>
       <c r="S117" s="4" t="inlineStr">
         <is>
-          <t>2026-08-03T21:38:53Z</t>
+          <t>2026-08-04T21:47:55Z</t>
         </is>
       </c>
     </row>
@@ -10171,7 +10171,7 @@
       </c>
       <c r="S118" s="4" t="inlineStr">
         <is>
-          <t>2026-08-03T21:38:53Z</t>
+          <t>2026-08-04T21:47:55Z</t>
         </is>
       </c>
     </row>
@@ -10256,7 +10256,7 @@
       </c>
       <c r="S119" s="4" t="inlineStr">
         <is>
-          <t>2026-08-03T21:38:53Z</t>
+          <t>2026-08-04T21:47:55Z</t>
         </is>
       </c>
     </row>
@@ -10341,7 +10341,7 @@
       </c>
       <c r="S120" s="4" t="inlineStr">
         <is>
-          <t>2026-08-03T21:38:53Z</t>
+          <t>2026-08-04T21:47:55Z</t>
         </is>
       </c>
     </row>
@@ -10426,7 +10426,7 @@
       </c>
       <c r="S121" s="4" t="inlineStr">
         <is>
-          <t>2026-08-03T21:38:53Z</t>
+          <t>2026-08-04T21:47:55Z</t>
         </is>
       </c>
     </row>
@@ -10511,7 +10511,7 @@
       </c>
       <c r="S122" s="4" t="inlineStr">
         <is>
-          <t>2026-08-03T21:38:53Z</t>
+          <t>2026-08-04T21:47:55Z</t>
         </is>
       </c>
     </row>
@@ -10596,7 +10596,7 @@
       </c>
       <c r="S123" s="4" t="inlineStr">
         <is>
-          <t>2026-08-03T21:38:53Z</t>
+          <t>2026-08-04T21:47:55Z</t>
         </is>
       </c>
     </row>
@@ -10681,7 +10681,7 @@
       </c>
       <c r="S124" s="4" t="inlineStr">
         <is>
-          <t>2026-08-03T21:38:53Z</t>
+          <t>2026-08-04T21:47:55Z</t>
         </is>
       </c>
     </row>
@@ -10766,7 +10766,7 @@
       </c>
       <c r="S125" s="4" t="inlineStr">
         <is>
-          <t>2026-08-03T21:38:53Z</t>
+          <t>2026-08-04T21:47:55Z</t>
         </is>
       </c>
     </row>
@@ -10851,7 +10851,7 @@
       </c>
       <c r="S126" s="4" t="inlineStr">
         <is>
-          <t>2026-08-03T21:38:53Z</t>
+          <t>2026-08-04T21:47:55Z</t>
         </is>
       </c>
     </row>
@@ -10936,7 +10936,7 @@
       </c>
       <c r="S127" s="4" t="inlineStr">
         <is>
-          <t>2026-08-03T21:38:53Z</t>
+          <t>2026-08-04T21:47:55Z</t>
         </is>
       </c>
     </row>
@@ -11021,7 +11021,7 @@
       </c>
       <c r="S128" s="4" t="inlineStr">
         <is>
-          <t>2026-08-03T21:38:53Z</t>
+          <t>2026-08-04T21:47:55Z</t>
         </is>
       </c>
     </row>
@@ -11106,7 +11106,7 @@
       </c>
       <c r="S129" s="4" t="inlineStr">
         <is>
-          <t>2026-08-03T21:38:53Z</t>
+          <t>2026-08-04T21:47:55Z</t>
         </is>
       </c>
     </row>
@@ -11191,7 +11191,7 @@
       </c>
       <c r="S130" s="4" t="inlineStr">
         <is>
-          <t>2026-08-03T21:38:53Z</t>
+          <t>2026-08-04T21:47:55Z</t>
         </is>
       </c>
     </row>
@@ -11276,7 +11276,7 @@
       </c>
       <c r="S131" s="4" t="inlineStr">
         <is>
-          <t>2026-08-03T21:38:53Z</t>
+          <t>2026-08-04T21:47:55Z</t>
         </is>
       </c>
     </row>
@@ -11361,7 +11361,7 @@
       </c>
       <c r="S132" s="4" t="inlineStr">
         <is>
-          <t>2026-08-03T21:38:53Z</t>
+          <t>2026-08-04T21:47:55Z</t>
         </is>
       </c>
     </row>
@@ -11446,7 +11446,7 @@
       </c>
       <c r="S133" s="4" t="inlineStr">
         <is>
-          <t>2026-08-03T21:38:53Z</t>
+          <t>2026-08-04T21:47:55Z</t>
         </is>
       </c>
     </row>
@@ -11531,7 +11531,7 @@
       </c>
       <c r="S134" s="4" t="inlineStr">
         <is>
-          <t>2026-08-03T21:38:53Z</t>
+          <t>2026-08-04T21:47:55Z</t>
         </is>
       </c>
     </row>
@@ -11616,7 +11616,7 @@
       </c>
       <c r="S135" s="4" t="inlineStr">
         <is>
-          <t>2026-08-03T21:38:53Z</t>
+          <t>2026-08-04T21:47:55Z</t>
         </is>
       </c>
     </row>
@@ -11701,7 +11701,7 @@
       </c>
       <c r="S136" s="4" t="inlineStr">
         <is>
-          <t>2026-08-03T21:38:53Z</t>
+          <t>2026-08-04T21:47:55Z</t>
         </is>
       </c>
     </row>
@@ -11786,7 +11786,7 @@
       </c>
       <c r="S137" s="4" t="inlineStr">
         <is>
-          <t>2026-08-03T21:38:53Z</t>
+          <t>2026-08-04T21:47:55Z</t>
         </is>
       </c>
     </row>
@@ -11871,7 +11871,7 @@
       </c>
       <c r="S138" s="4" t="inlineStr">
         <is>
-          <t>2026-08-03T21:38:53Z</t>
+          <t>2026-08-04T21:47:55Z</t>
         </is>
       </c>
     </row>
@@ -11956,7 +11956,7 @@
       </c>
       <c r="S139" s="4" t="inlineStr">
         <is>
-          <t>2026-08-03T21:38:53Z</t>
+          <t>2026-08-04T21:47:55Z</t>
         </is>
       </c>
     </row>
@@ -12041,7 +12041,7 @@
       </c>
       <c r="S140" s="4" t="inlineStr">
         <is>
-          <t>2026-08-03T21:38:53Z</t>
+          <t>2026-08-04T21:47:55Z</t>
         </is>
       </c>
     </row>
@@ -12126,7 +12126,7 @@
       </c>
       <c r="S141" s="4" t="inlineStr">
         <is>
-          <t>2026-08-03T21:38:53Z</t>
+          <t>2026-08-04T21:47:55Z</t>
         </is>
       </c>
     </row>
@@ -12258,7 +12258,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>2026-08-03T21:38:53Z</t>
+          <t>2026-08-04T21:47:55Z</t>
         </is>
       </c>
     </row>
@@ -12338,7 +12338,7 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>{"dataset_id": "bcv_pib_historico_anual", "title": "Producto interno bruto histórico anual", "table": "PIB histórico anual", "source_file": "7_1_14_anual.xls", "base": "1957/1968/1984/1997", "price_type": "Precios constantes", "measure": "Nivel", "frequency": "Anual", "period": "2017", "year": 2017, "quarter": null, "classification": "Total economía", "component": "Producto interno bruto", "value": 392393.12, "unit": "Millones de bolívares a precios constantes", "status": "", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/7_1_14_anual.xls", "fetched_at": "2026-08-03T21:38:53Z"}</t>
+          <t>{"dataset_id": "bcv_pib_historico_anual", "title": "Producto interno bruto histórico anual", "table": "PIB histórico anual", "source_file": "7_1_14_anual.xls", "base": "1957/1968/1984/1997", "price_type": "Precios constantes", "measure": "Nivel", "frequency": "Anual", "period": "2017", "year": 2017, "quarter": null, "classification": "Total economía", "component": "Producto interno bruto", "value": 392393.12, "unit": "Millones de bolívares a precios constantes", "status": "", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/7_1_14_anual.xls", "fetched_at": "2026-08-04T21:47:55Z"}</t>
         </is>
       </c>
     </row>

--- a/assets/data/bcv/excel/ove_bcv_pib_historico_anual.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_pib_historico_anual.xlsx
@@ -736,7 +736,7 @@
       </c>
       <c r="S7" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04T21:47:55Z</t>
+          <t>2026-08-05T21:44:21Z</t>
         </is>
       </c>
     </row>
@@ -821,7 +821,7 @@
       </c>
       <c r="S8" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04T21:47:55Z</t>
+          <t>2026-08-05T21:44:21Z</t>
         </is>
       </c>
     </row>
@@ -906,7 +906,7 @@
       </c>
       <c r="S9" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04T21:47:55Z</t>
+          <t>2026-08-05T21:44:21Z</t>
         </is>
       </c>
     </row>
@@ -991,7 +991,7 @@
       </c>
       <c r="S10" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04T21:47:55Z</t>
+          <t>2026-08-05T21:44:21Z</t>
         </is>
       </c>
     </row>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="S11" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04T21:47:55Z</t>
+          <t>2026-08-05T21:44:21Z</t>
         </is>
       </c>
     </row>
@@ -1161,7 +1161,7 @@
       </c>
       <c r="S12" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04T21:47:55Z</t>
+          <t>2026-08-05T21:44:21Z</t>
         </is>
       </c>
     </row>
@@ -1246,7 +1246,7 @@
       </c>
       <c r="S13" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04T21:47:55Z</t>
+          <t>2026-08-05T21:44:21Z</t>
         </is>
       </c>
     </row>
@@ -1331,7 +1331,7 @@
       </c>
       <c r="S14" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04T21:47:55Z</t>
+          <t>2026-08-05T21:44:21Z</t>
         </is>
       </c>
     </row>
@@ -1416,7 +1416,7 @@
       </c>
       <c r="S15" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04T21:47:55Z</t>
+          <t>2026-08-05T21:44:21Z</t>
         </is>
       </c>
     </row>
@@ -1501,7 +1501,7 @@
       </c>
       <c r="S16" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04T21:47:55Z</t>
+          <t>2026-08-05T21:44:21Z</t>
         </is>
       </c>
     </row>
@@ -1586,7 +1586,7 @@
       </c>
       <c r="S17" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04T21:47:55Z</t>
+          <t>2026-08-05T21:44:21Z</t>
         </is>
       </c>
     </row>
@@ -1671,7 +1671,7 @@
       </c>
       <c r="S18" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04T21:47:55Z</t>
+          <t>2026-08-05T21:44:21Z</t>
         </is>
       </c>
     </row>
@@ -1756,7 +1756,7 @@
       </c>
       <c r="S19" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04T21:47:55Z</t>
+          <t>2026-08-05T21:44:21Z</t>
         </is>
       </c>
     </row>
@@ -1841,7 +1841,7 @@
       </c>
       <c r="S20" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04T21:47:55Z</t>
+          <t>2026-08-05T21:44:21Z</t>
         </is>
       </c>
     </row>
@@ -1926,7 +1926,7 @@
       </c>
       <c r="S21" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04T21:47:55Z</t>
+          <t>2026-08-05T21:44:21Z</t>
         </is>
       </c>
     </row>
@@ -2011,7 +2011,7 @@
       </c>
       <c r="S22" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04T21:47:55Z</t>
+          <t>2026-08-05T21:44:21Z</t>
         </is>
       </c>
     </row>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="S23" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04T21:47:55Z</t>
+          <t>2026-08-05T21:44:21Z</t>
         </is>
       </c>
     </row>
@@ -2181,7 +2181,7 @@
       </c>
       <c r="S24" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04T21:47:55Z</t>
+          <t>2026-08-05T21:44:21Z</t>
         </is>
       </c>
     </row>
@@ -2266,7 +2266,7 @@
       </c>
       <c r="S25" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04T21:47:55Z</t>
+          <t>2026-08-05T21:44:21Z</t>
         </is>
       </c>
     </row>
@@ -2351,7 +2351,7 @@
       </c>
       <c r="S26" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04T21:47:55Z</t>
+          <t>2026-08-05T21:44:21Z</t>
         </is>
       </c>
     </row>
@@ -2436,7 +2436,7 @@
       </c>
       <c r="S27" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04T21:47:55Z</t>
+          <t>2026-08-05T21:44:21Z</t>
         </is>
       </c>
     </row>
@@ -2521,7 +2521,7 @@
       </c>
       <c r="S28" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04T21:47:55Z</t>
+          <t>2026-08-05T21:44:21Z</t>
         </is>
       </c>
     </row>
@@ -2606,7 +2606,7 @@
       </c>
       <c r="S29" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04T21:47:55Z</t>
+          <t>2026-08-05T21:44:21Z</t>
         </is>
       </c>
     </row>
@@ -2691,7 +2691,7 @@
       </c>
       <c r="S30" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04T21:47:55Z</t>
+          <t>2026-08-05T21:44:21Z</t>
         </is>
       </c>
     </row>
@@ -2776,7 +2776,7 @@
       </c>
       <c r="S31" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04T21:47:55Z</t>
+          <t>2026-08-05T21:44:21Z</t>
         </is>
       </c>
     </row>
@@ -2861,7 +2861,7 @@
       </c>
       <c r="S32" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04T21:47:55Z</t>
+          <t>2026-08-05T21:44:21Z</t>
         </is>
       </c>
     </row>
@@ -2946,7 +2946,7 @@
       </c>
       <c r="S33" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04T21:47:55Z</t>
+          <t>2026-08-05T21:44:21Z</t>
         </is>
       </c>
     </row>
@@ -3031,7 +3031,7 @@
       </c>
       <c r="S34" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04T21:47:55Z</t>
+          <t>2026-08-05T21:44:21Z</t>
         </is>
       </c>
     </row>
@@ -3116,7 +3116,7 @@
       </c>
       <c r="S35" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04T21:47:55Z</t>
+          <t>2026-08-05T21:44:21Z</t>
         </is>
       </c>
     </row>
@@ -3201,7 +3201,7 @@
       </c>
       <c r="S36" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04T21:47:55Z</t>
+          <t>2026-08-05T21:44:21Z</t>
         </is>
       </c>
     </row>
@@ -3286,7 +3286,7 @@
       </c>
       <c r="S37" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04T21:47:55Z</t>
+          <t>2026-08-05T21:44:21Z</t>
         </is>
       </c>
     </row>
@@ -3371,7 +3371,7 @@
       </c>
       <c r="S38" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04T21:47:55Z</t>
+          <t>2026-08-05T21:44:21Z</t>
         </is>
       </c>
     </row>
@@ -3456,7 +3456,7 @@
       </c>
       <c r="S39" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04T21:47:55Z</t>
+          <t>2026-08-05T21:44:21Z</t>
         </is>
       </c>
     </row>
@@ -3541,7 +3541,7 @@
       </c>
       <c r="S40" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04T21:47:55Z</t>
+          <t>2026-08-05T21:44:21Z</t>
         </is>
       </c>
     </row>
@@ -3626,7 +3626,7 @@
       </c>
       <c r="S41" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04T21:47:55Z</t>
+          <t>2026-08-05T21:44:21Z</t>
         </is>
       </c>
     </row>
@@ -3711,7 +3711,7 @@
       </c>
       <c r="S42" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04T21:47:55Z</t>
+          <t>2026-08-05T21:44:21Z</t>
         </is>
       </c>
     </row>
@@ -3796,7 +3796,7 @@
       </c>
       <c r="S43" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04T21:47:55Z</t>
+          <t>2026-08-05T21:44:21Z</t>
         </is>
       </c>
     </row>
@@ -3881,7 +3881,7 @@
       </c>
       <c r="S44" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04T21:47:55Z</t>
+          <t>2026-08-05T21:44:21Z</t>
         </is>
       </c>
     </row>
@@ -3966,7 +3966,7 @@
       </c>
       <c r="S45" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04T21:47:55Z</t>
+          <t>2026-08-05T21:44:21Z</t>
         </is>
       </c>
     </row>
@@ -4051,7 +4051,7 @@
       </c>
       <c r="S46" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04T21:47:55Z</t>
+          <t>2026-08-05T21:44:21Z</t>
         </is>
       </c>
     </row>
@@ -4136,7 +4136,7 @@
       </c>
       <c r="S47" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04T21:47:55Z</t>
+          <t>2026-08-05T21:44:21Z</t>
         </is>
       </c>
     </row>
@@ -4221,7 +4221,7 @@
       </c>
       <c r="S48" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04T21:47:55Z</t>
+          <t>2026-08-05T21:44:21Z</t>
         </is>
       </c>
     </row>
@@ -4306,7 +4306,7 @@
       </c>
       <c r="S49" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04T21:47:55Z</t>
+          <t>2026-08-05T21:44:21Z</t>
         </is>
       </c>
     </row>
@@ -4391,7 +4391,7 @@
       </c>
       <c r="S50" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04T21:47:55Z</t>
+          <t>2026-08-05T21:44:21Z</t>
         </is>
       </c>
     </row>
@@ -4476,7 +4476,7 @@
       </c>
       <c r="S51" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04T21:47:55Z</t>
+          <t>2026-08-05T21:44:21Z</t>
         </is>
       </c>
     </row>
@@ -4561,7 +4561,7 @@
       </c>
       <c r="S52" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04T21:47:55Z</t>
+          <t>2026-08-05T21:44:21Z</t>
         </is>
       </c>
     </row>
@@ -4646,7 +4646,7 @@
       </c>
       <c r="S53" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04T21:47:55Z</t>
+          <t>2026-08-05T21:44:21Z</t>
         </is>
       </c>
     </row>
@@ -4731,7 +4731,7 @@
       </c>
       <c r="S54" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04T21:47:55Z</t>
+          <t>2026-08-05T21:44:21Z</t>
         </is>
       </c>
     </row>
@@ -4816,7 +4816,7 @@
       </c>
       <c r="S55" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04T21:47:55Z</t>
+          <t>2026-08-05T21:44:21Z</t>
         </is>
       </c>
     </row>
@@ -4901,7 +4901,7 @@
       </c>
       <c r="S56" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04T21:47:55Z</t>
+          <t>2026-08-05T21:44:21Z</t>
         </is>
       </c>
     </row>
@@ -4986,7 +4986,7 @@
       </c>
       <c r="S57" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04T21:47:55Z</t>
+          <t>2026-08-05T21:44:21Z</t>
         </is>
       </c>
     </row>
@@ -5071,7 +5071,7 @@
       </c>
       <c r="S58" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04T21:47:55Z</t>
+          <t>2026-08-05T21:44:21Z</t>
         </is>
       </c>
     </row>
@@ -5156,7 +5156,7 @@
       </c>
       <c r="S59" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04T21:47:55Z</t>
+          <t>2026-08-05T21:44:21Z</t>
         </is>
       </c>
     </row>
@@ -5241,7 +5241,7 @@
       </c>
       <c r="S60" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04T21:47:55Z</t>
+          <t>2026-08-05T21:44:21Z</t>
         </is>
       </c>
     </row>
@@ -5326,7 +5326,7 @@
       </c>
       <c r="S61" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04T21:47:55Z</t>
+          <t>2026-08-05T21:44:21Z</t>
         </is>
       </c>
     </row>
@@ -5411,7 +5411,7 @@
       </c>
       <c r="S62" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04T21:47:55Z</t>
+          <t>2026-08-05T21:44:21Z</t>
         </is>
       </c>
     </row>
@@ -5496,7 +5496,7 @@
       </c>
       <c r="S63" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04T21:47:55Z</t>
+          <t>2026-08-05T21:44:21Z</t>
         </is>
       </c>
     </row>
@@ -5581,7 +5581,7 @@
       </c>
       <c r="S64" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04T21:47:55Z</t>
+          <t>2026-08-05T21:44:21Z</t>
         </is>
       </c>
     </row>
@@ -5666,7 +5666,7 @@
       </c>
       <c r="S65" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04T21:47:55Z</t>
+          <t>2026-08-05T21:44:21Z</t>
         </is>
       </c>
     </row>
@@ -5751,7 +5751,7 @@
       </c>
       <c r="S66" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04T21:47:55Z</t>
+          <t>2026-08-05T21:44:21Z</t>
         </is>
       </c>
     </row>
@@ -5836,7 +5836,7 @@
       </c>
       <c r="S67" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04T21:47:55Z</t>
+          <t>2026-08-05T21:44:21Z</t>
         </is>
       </c>
     </row>
@@ -5921,7 +5921,7 @@
       </c>
       <c r="S68" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04T21:47:55Z</t>
+          <t>2026-08-05T21:44:21Z</t>
         </is>
       </c>
     </row>
@@ -6006,7 +6006,7 @@
       </c>
       <c r="S69" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04T21:47:55Z</t>
+          <t>2026-08-05T21:44:21Z</t>
         </is>
       </c>
     </row>
@@ -6091,7 +6091,7 @@
       </c>
       <c r="S70" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04T21:47:55Z</t>
+          <t>2026-08-05T21:44:21Z</t>
         </is>
       </c>
     </row>
@@ -6176,7 +6176,7 @@
       </c>
       <c r="S71" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04T21:47:55Z</t>
+          <t>2026-08-05T21:44:21Z</t>
         </is>
       </c>
     </row>
@@ -6261,7 +6261,7 @@
       </c>
       <c r="S72" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04T21:47:55Z</t>
+          <t>2026-08-05T21:44:21Z</t>
         </is>
       </c>
     </row>
@@ -6346,7 +6346,7 @@
       </c>
       <c r="S73" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04T21:47:55Z</t>
+          <t>2026-08-05T21:44:21Z</t>
         </is>
       </c>
     </row>
@@ -6431,7 +6431,7 @@
       </c>
       <c r="S74" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04T21:47:55Z</t>
+          <t>2026-08-05T21:44:21Z</t>
         </is>
       </c>
     </row>
@@ -6516,7 +6516,7 @@
       </c>
       <c r="S75" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04T21:47:55Z</t>
+          <t>2026-08-05T21:44:21Z</t>
         </is>
       </c>
     </row>
@@ -6601,7 +6601,7 @@
       </c>
       <c r="S76" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04T21:47:55Z</t>
+          <t>2026-08-05T21:44:21Z</t>
         </is>
       </c>
     </row>
@@ -6686,7 +6686,7 @@
       </c>
       <c r="S77" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04T21:47:55Z</t>
+          <t>2026-08-05T21:44:21Z</t>
         </is>
       </c>
     </row>
@@ -6771,7 +6771,7 @@
       </c>
       <c r="S78" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04T21:47:55Z</t>
+          <t>2026-08-05T21:44:21Z</t>
         </is>
       </c>
     </row>
@@ -6856,7 +6856,7 @@
       </c>
       <c r="S79" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04T21:47:55Z</t>
+          <t>2026-08-05T21:44:21Z</t>
         </is>
       </c>
     </row>
@@ -6941,7 +6941,7 @@
       </c>
       <c r="S80" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04T21:47:55Z</t>
+          <t>2026-08-05T21:44:21Z</t>
         </is>
       </c>
     </row>
@@ -7026,7 +7026,7 @@
       </c>
       <c r="S81" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04T21:47:55Z</t>
+          <t>2026-08-05T21:44:21Z</t>
         </is>
       </c>
     </row>
@@ -7111,7 +7111,7 @@
       </c>
       <c r="S82" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04T21:47:55Z</t>
+          <t>2026-08-05T21:44:21Z</t>
         </is>
       </c>
     </row>
@@ -7196,7 +7196,7 @@
       </c>
       <c r="S83" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04T21:47:55Z</t>
+          <t>2026-08-05T21:44:21Z</t>
         </is>
       </c>
     </row>
@@ -7281,7 +7281,7 @@
       </c>
       <c r="S84" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04T21:47:55Z</t>
+          <t>2026-08-05T21:44:21Z</t>
         </is>
       </c>
     </row>
@@ -7366,7 +7366,7 @@
       </c>
       <c r="S85" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04T21:47:55Z</t>
+          <t>2026-08-05T21:44:21Z</t>
         </is>
       </c>
     </row>
@@ -7451,7 +7451,7 @@
       </c>
       <c r="S86" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04T21:47:55Z</t>
+          <t>2026-08-05T21:44:21Z</t>
         </is>
       </c>
     </row>
@@ -7536,7 +7536,7 @@
       </c>
       <c r="S87" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04T21:47:55Z</t>
+          <t>2026-08-05T21:44:21Z</t>
         </is>
       </c>
     </row>
@@ -7621,7 +7621,7 @@
       </c>
       <c r="S88" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04T21:47:55Z</t>
+          <t>2026-08-05T21:44:21Z</t>
         </is>
       </c>
     </row>
@@ -7706,7 +7706,7 @@
       </c>
       <c r="S89" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04T21:47:55Z</t>
+          <t>2026-08-05T21:44:21Z</t>
         </is>
       </c>
     </row>
@@ -7791,7 +7791,7 @@
       </c>
       <c r="S90" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04T21:47:55Z</t>
+          <t>2026-08-05T21:44:21Z</t>
         </is>
       </c>
     </row>
@@ -7876,7 +7876,7 @@
       </c>
       <c r="S91" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04T21:47:55Z</t>
+          <t>2026-08-05T21:44:21Z</t>
         </is>
       </c>
     </row>
@@ -7961,7 +7961,7 @@
       </c>
       <c r="S92" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04T21:47:55Z</t>
+          <t>2026-08-05T21:44:21Z</t>
         </is>
       </c>
     </row>
@@ -8046,7 +8046,7 @@
       </c>
       <c r="S93" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04T21:47:55Z</t>
+          <t>2026-08-05T21:44:21Z</t>
         </is>
       </c>
     </row>
@@ -8131,7 +8131,7 @@
       </c>
       <c r="S94" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04T21:47:55Z</t>
+          <t>2026-08-05T21:44:21Z</t>
         </is>
       </c>
     </row>
@@ -8216,7 +8216,7 @@
       </c>
       <c r="S95" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04T21:47:55Z</t>
+          <t>2026-08-05T21:44:21Z</t>
         </is>
       </c>
     </row>
@@ -8301,7 +8301,7 @@
       </c>
       <c r="S96" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04T21:47:55Z</t>
+          <t>2026-08-05T21:44:21Z</t>
         </is>
       </c>
     </row>
@@ -8386,7 +8386,7 @@
       </c>
       <c r="S97" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04T21:47:55Z</t>
+          <t>2026-08-05T21:44:21Z</t>
         </is>
       </c>
     </row>
@@ -8471,7 +8471,7 @@
       </c>
       <c r="S98" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04T21:47:55Z</t>
+          <t>2026-08-05T21:44:21Z</t>
         </is>
       </c>
     </row>
@@ -8556,7 +8556,7 @@
       </c>
       <c r="S99" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04T21:47:55Z</t>
+          <t>2026-08-05T21:44:21Z</t>
         </is>
       </c>
     </row>
@@ -8641,7 +8641,7 @@
       </c>
       <c r="S100" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04T21:47:55Z</t>
+          <t>2026-08-05T21:44:21Z</t>
         </is>
       </c>
     </row>
@@ -8726,7 +8726,7 @@
       </c>
       <c r="S101" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04T21:47:55Z</t>
+          <t>2026-08-05T21:44:21Z</t>
         </is>
       </c>
     </row>
@@ -8811,7 +8811,7 @@
       </c>
       <c r="S102" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04T21:47:55Z</t>
+          <t>2026-08-05T21:44:21Z</t>
         </is>
       </c>
     </row>
@@ -8896,7 +8896,7 @@
       </c>
       <c r="S103" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04T21:47:55Z</t>
+          <t>2026-08-05T21:44:21Z</t>
         </is>
       </c>
     </row>
@@ -8981,7 +8981,7 @@
       </c>
       <c r="S104" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04T21:47:55Z</t>
+          <t>2026-08-05T21:44:21Z</t>
         </is>
       </c>
     </row>
@@ -9066,7 +9066,7 @@
       </c>
       <c r="S105" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04T21:47:55Z</t>
+          <t>2026-08-05T21:44:21Z</t>
         </is>
       </c>
     </row>
@@ -9151,7 +9151,7 @@
       </c>
       <c r="S106" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04T21:47:55Z</t>
+          <t>2026-08-05T21:44:21Z</t>
         </is>
       </c>
     </row>
@@ -9236,7 +9236,7 @@
       </c>
       <c r="S107" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04T21:47:55Z</t>
+          <t>2026-08-05T21:44:21Z</t>
         </is>
       </c>
     </row>
@@ -9321,7 +9321,7 @@
       </c>
       <c r="S108" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04T21:47:55Z</t>
+          <t>2026-08-05T21:44:21Z</t>
         </is>
       </c>
     </row>
@@ -9406,7 +9406,7 @@
       </c>
       <c r="S109" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04T21:47:55Z</t>
+          <t>2026-08-05T21:44:21Z</t>
         </is>
       </c>
     </row>
@@ -9491,7 +9491,7 @@
       </c>
       <c r="S110" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04T21:47:55Z</t>
+          <t>2026-08-05T21:44:21Z</t>
         </is>
       </c>
     </row>
@@ -9576,7 +9576,7 @@
       </c>
       <c r="S111" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04T21:47:55Z</t>
+          <t>2026-08-05T21:44:21Z</t>
         </is>
       </c>
     </row>
@@ -9661,7 +9661,7 @@
       </c>
       <c r="S112" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04T21:47:55Z</t>
+          <t>2026-08-05T21:44:21Z</t>
         </is>
       </c>
     </row>
@@ -9746,7 +9746,7 @@
       </c>
       <c r="S113" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04T21:47:55Z</t>
+          <t>2026-08-05T21:44:21Z</t>
         </is>
       </c>
     </row>
@@ -9831,7 +9831,7 @@
       </c>
       <c r="S114" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04T21:47:55Z</t>
+          <t>2026-08-05T21:44:21Z</t>
         </is>
       </c>
     </row>
@@ -9916,7 +9916,7 @@
       </c>
       <c r="S115" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04T21:47:55Z</t>
+          <t>2026-08-05T21:44:21Z</t>
         </is>
       </c>
     </row>
@@ -10001,7 +10001,7 @@
       </c>
       <c r="S116" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04T21:47:55Z</t>
+          <t>2026-08-05T21:44:21Z</t>
         </is>
       </c>
     </row>
@@ -10086,7 +10086,7 @@
       </c>
       <c r="S117" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04T21:47:55Z</t>
+          <t>2026-08-05T21:44:21Z</t>
         </is>
       </c>
     </row>
@@ -10171,7 +10171,7 @@
       </c>
       <c r="S118" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04T21:47:55Z</t>
+          <t>2026-08-05T21:44:21Z</t>
         </is>
       </c>
     </row>
@@ -10256,7 +10256,7 @@
       </c>
       <c r="S119" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04T21:47:55Z</t>
+          <t>2026-08-05T21:44:21Z</t>
         </is>
       </c>
     </row>
@@ -10341,7 +10341,7 @@
       </c>
       <c r="S120" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04T21:47:55Z</t>
+          <t>2026-08-05T21:44:21Z</t>
         </is>
       </c>
     </row>
@@ -10426,7 +10426,7 @@
       </c>
       <c r="S121" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04T21:47:55Z</t>
+          <t>2026-08-05T21:44:21Z</t>
         </is>
       </c>
     </row>
@@ -10511,7 +10511,7 @@
       </c>
       <c r="S122" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04T21:47:55Z</t>
+          <t>2026-08-05T21:44:21Z</t>
         </is>
       </c>
     </row>
@@ -10596,7 +10596,7 @@
       </c>
       <c r="S123" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04T21:47:55Z</t>
+          <t>2026-08-05T21:44:21Z</t>
         </is>
       </c>
     </row>
@@ -10681,7 +10681,7 @@
       </c>
       <c r="S124" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04T21:47:55Z</t>
+          <t>2026-08-05T21:44:21Z</t>
         </is>
       </c>
     </row>
@@ -10766,7 +10766,7 @@
       </c>
       <c r="S125" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04T21:47:55Z</t>
+          <t>2026-08-05T21:44:21Z</t>
         </is>
       </c>
     </row>
@@ -10851,7 +10851,7 @@
       </c>
       <c r="S126" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04T21:47:55Z</t>
+          <t>2026-08-05T21:44:21Z</t>
         </is>
       </c>
     </row>
@@ -10936,7 +10936,7 @@
       </c>
       <c r="S127" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04T21:47:55Z</t>
+          <t>2026-08-05T21:44:21Z</t>
         </is>
       </c>
     </row>
@@ -11021,7 +11021,7 @@
       </c>
       <c r="S128" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04T21:47:55Z</t>
+          <t>2026-08-05T21:44:21Z</t>
         </is>
       </c>
     </row>
@@ -11106,7 +11106,7 @@
       </c>
       <c r="S129" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04T21:47:55Z</t>
+          <t>2026-08-05T21:44:21Z</t>
         </is>
       </c>
     </row>
@@ -11191,7 +11191,7 @@
       </c>
       <c r="S130" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04T21:47:55Z</t>
+          <t>2026-08-05T21:44:21Z</t>
         </is>
       </c>
     </row>
@@ -11276,7 +11276,7 @@
       </c>
       <c r="S131" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04T21:47:55Z</t>
+          <t>2026-08-05T21:44:21Z</t>
         </is>
       </c>
     </row>
@@ -11361,7 +11361,7 @@
       </c>
       <c r="S132" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04T21:47:55Z</t>
+          <t>2026-08-05T21:44:21Z</t>
         </is>
       </c>
     </row>
@@ -11446,7 +11446,7 @@
       </c>
       <c r="S133" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04T21:47:55Z</t>
+          <t>2026-08-05T21:44:21Z</t>
         </is>
       </c>
     </row>
@@ -11531,7 +11531,7 @@
       </c>
       <c r="S134" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04T21:47:55Z</t>
+          <t>2026-08-05T21:44:21Z</t>
         </is>
       </c>
     </row>
@@ -11616,7 +11616,7 @@
       </c>
       <c r="S135" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04T21:47:55Z</t>
+          <t>2026-08-05T21:44:21Z</t>
         </is>
       </c>
     </row>
@@ -11701,7 +11701,7 @@
       </c>
       <c r="S136" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04T21:47:55Z</t>
+          <t>2026-08-05T21:44:21Z</t>
         </is>
       </c>
     </row>
@@ -11786,7 +11786,7 @@
       </c>
       <c r="S137" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04T21:47:55Z</t>
+          <t>2026-08-05T21:44:21Z</t>
         </is>
       </c>
     </row>
@@ -11871,7 +11871,7 @@
       </c>
       <c r="S138" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04T21:47:55Z</t>
+          <t>2026-08-05T21:44:21Z</t>
         </is>
       </c>
     </row>
@@ -11956,7 +11956,7 @@
       </c>
       <c r="S139" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04T21:47:55Z</t>
+          <t>2026-08-05T21:44:21Z</t>
         </is>
       </c>
     </row>
@@ -12041,7 +12041,7 @@
       </c>
       <c r="S140" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04T21:47:55Z</t>
+          <t>2026-08-05T21:44:21Z</t>
         </is>
       </c>
     </row>
@@ -12126,7 +12126,7 @@
       </c>
       <c r="S141" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04T21:47:55Z</t>
+          <t>2026-08-05T21:44:21Z</t>
         </is>
       </c>
     </row>
@@ -12258,7 +12258,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04T21:47:55Z</t>
+          <t>2026-08-05T21:44:21Z</t>
         </is>
       </c>
     </row>
@@ -12338,7 +12338,7 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>{"dataset_id": "bcv_pib_historico_anual", "title": "Producto interno bruto histórico anual", "table": "PIB histórico anual", "source_file": "7_1_14_anual.xls", "base": "1957/1968/1984/1997", "price_type": "Precios constantes", "measure": "Nivel", "frequency": "Anual", "period": "2017", "year": 2017, "quarter": null, "classification": "Total economía", "component": "Producto interno bruto", "value": 392393.12, "unit": "Millones de bolívares a precios constantes", "status": "", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/7_1_14_anual.xls", "fetched_at": "2026-08-04T21:47:55Z"}</t>
+          <t>{"dataset_id": "bcv_pib_historico_anual", "title": "Producto interno bruto histórico anual", "table": "PIB histórico anual", "source_file": "7_1_14_anual.xls", "base": "1957/1968/1984/1997", "price_type": "Precios constantes", "measure": "Nivel", "frequency": "Anual", "period": "2017", "year": 2017, "quarter": null, "classification": "Total economía", "component": "Producto interno bruto", "value": 392393.12, "unit": "Millones de bolívares a precios constantes", "status": "", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/7_1_14_anual.xls", "fetched_at": "2026-08-05T21:44:21Z"}</t>
         </is>
       </c>
     </row>

--- a/assets/data/bcv/excel/ove_bcv_pib_historico_anual.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_pib_historico_anual.xlsx
@@ -736,7 +736,7 @@
       </c>
       <c r="S7" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05T21:44:21Z</t>
+          <t>2026-08-07T00:56:56Z</t>
         </is>
       </c>
     </row>
@@ -821,7 +821,7 @@
       </c>
       <c r="S8" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05T21:44:21Z</t>
+          <t>2026-08-07T00:56:56Z</t>
         </is>
       </c>
     </row>
@@ -906,7 +906,7 @@
       </c>
       <c r="S9" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05T21:44:21Z</t>
+          <t>2026-08-07T00:56:56Z</t>
         </is>
       </c>
     </row>
@@ -991,7 +991,7 @@
       </c>
       <c r="S10" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05T21:44:21Z</t>
+          <t>2026-08-07T00:56:56Z</t>
         </is>
       </c>
     </row>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="S11" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05T21:44:21Z</t>
+          <t>2026-08-07T00:56:56Z</t>
         </is>
       </c>
     </row>
@@ -1161,7 +1161,7 @@
       </c>
       <c r="S12" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05T21:44:21Z</t>
+          <t>2026-08-07T00:56:56Z</t>
         </is>
       </c>
     </row>
@@ -1246,7 +1246,7 @@
       </c>
       <c r="S13" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05T21:44:21Z</t>
+          <t>2026-08-07T00:56:56Z</t>
         </is>
       </c>
     </row>
@@ -1331,7 +1331,7 @@
       </c>
       <c r="S14" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05T21:44:21Z</t>
+          <t>2026-08-07T00:56:56Z</t>
         </is>
       </c>
     </row>
@@ -1416,7 +1416,7 @@
       </c>
       <c r="S15" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05T21:44:21Z</t>
+          <t>2026-08-07T00:56:56Z</t>
         </is>
       </c>
     </row>
@@ -1501,7 +1501,7 @@
       </c>
       <c r="S16" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05T21:44:21Z</t>
+          <t>2026-08-07T00:56:56Z</t>
         </is>
       </c>
     </row>
@@ -1586,7 +1586,7 @@
       </c>
       <c r="S17" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05T21:44:21Z</t>
+          <t>2026-08-07T00:56:56Z</t>
         </is>
       </c>
     </row>
@@ -1671,7 +1671,7 @@
       </c>
       <c r="S18" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05T21:44:21Z</t>
+          <t>2026-08-07T00:56:56Z</t>
         </is>
       </c>
     </row>
@@ -1756,7 +1756,7 @@
       </c>
       <c r="S19" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05T21:44:21Z</t>
+          <t>2026-08-07T00:56:56Z</t>
         </is>
       </c>
     </row>
@@ -1841,7 +1841,7 @@
       </c>
       <c r="S20" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05T21:44:21Z</t>
+          <t>2026-08-07T00:56:56Z</t>
         </is>
       </c>
     </row>
@@ -1926,7 +1926,7 @@
       </c>
       <c r="S21" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05T21:44:21Z</t>
+          <t>2026-08-07T00:56:56Z</t>
         </is>
       </c>
     </row>
@@ -2011,7 +2011,7 @@
       </c>
       <c r="S22" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05T21:44:21Z</t>
+          <t>2026-08-07T00:56:56Z</t>
         </is>
       </c>
     </row>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="S23" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05T21:44:21Z</t>
+          <t>2026-08-07T00:56:56Z</t>
         </is>
       </c>
     </row>
@@ -2181,7 +2181,7 @@
       </c>
       <c r="S24" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05T21:44:21Z</t>
+          <t>2026-08-07T00:56:56Z</t>
         </is>
       </c>
     </row>
@@ -2266,7 +2266,7 @@
       </c>
       <c r="S25" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05T21:44:21Z</t>
+          <t>2026-08-07T00:56:56Z</t>
         </is>
       </c>
     </row>
@@ -2351,7 +2351,7 @@
       </c>
       <c r="S26" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05T21:44:21Z</t>
+          <t>2026-08-07T00:56:56Z</t>
         </is>
       </c>
     </row>
@@ -2436,7 +2436,7 @@
       </c>
       <c r="S27" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05T21:44:21Z</t>
+          <t>2026-08-07T00:56:56Z</t>
         </is>
       </c>
     </row>
@@ -2521,7 +2521,7 @@
       </c>
       <c r="S28" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05T21:44:21Z</t>
+          <t>2026-08-07T00:56:56Z</t>
         </is>
       </c>
     </row>
@@ -2606,7 +2606,7 @@
       </c>
       <c r="S29" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05T21:44:21Z</t>
+          <t>2026-08-07T00:56:56Z</t>
         </is>
       </c>
     </row>
@@ -2691,7 +2691,7 @@
       </c>
       <c r="S30" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05T21:44:21Z</t>
+          <t>2026-08-07T00:56:56Z</t>
         </is>
       </c>
     </row>
@@ -2776,7 +2776,7 @@
       </c>
       <c r="S31" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05T21:44:21Z</t>
+          <t>2026-08-07T00:56:56Z</t>
         </is>
       </c>
     </row>
@@ -2861,7 +2861,7 @@
       </c>
       <c r="S32" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05T21:44:21Z</t>
+          <t>2026-08-07T00:56:56Z</t>
         </is>
       </c>
     </row>
@@ -2946,7 +2946,7 @@
       </c>
       <c r="S33" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05T21:44:21Z</t>
+          <t>2026-08-07T00:56:56Z</t>
         </is>
       </c>
     </row>
@@ -3031,7 +3031,7 @@
       </c>
       <c r="S34" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05T21:44:21Z</t>
+          <t>2026-08-07T00:56:56Z</t>
         </is>
       </c>
     </row>
@@ -3116,7 +3116,7 @@
       </c>
       <c r="S35" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05T21:44:21Z</t>
+          <t>2026-08-07T00:56:56Z</t>
         </is>
       </c>
     </row>
@@ -3201,7 +3201,7 @@
       </c>
       <c r="S36" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05T21:44:21Z</t>
+          <t>2026-08-07T00:56:56Z</t>
         </is>
       </c>
     </row>
@@ -3286,7 +3286,7 @@
       </c>
       <c r="S37" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05T21:44:21Z</t>
+          <t>2026-08-07T00:56:56Z</t>
         </is>
       </c>
     </row>
@@ -3371,7 +3371,7 @@
       </c>
       <c r="S38" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05T21:44:21Z</t>
+          <t>2026-08-07T00:56:56Z</t>
         </is>
       </c>
     </row>
@@ -3456,7 +3456,7 @@
       </c>
       <c r="S39" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05T21:44:21Z</t>
+          <t>2026-08-07T00:56:56Z</t>
         </is>
       </c>
     </row>
@@ -3541,7 +3541,7 @@
       </c>
       <c r="S40" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05T21:44:21Z</t>
+          <t>2026-08-07T00:56:56Z</t>
         </is>
       </c>
     </row>
@@ -3626,7 +3626,7 @@
       </c>
       <c r="S41" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05T21:44:21Z</t>
+          <t>2026-08-07T00:56:56Z</t>
         </is>
       </c>
     </row>
@@ -3711,7 +3711,7 @@
       </c>
       <c r="S42" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05T21:44:21Z</t>
+          <t>2026-08-07T00:56:56Z</t>
         </is>
       </c>
     </row>
@@ -3796,7 +3796,7 @@
       </c>
       <c r="S43" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05T21:44:21Z</t>
+          <t>2026-08-07T00:56:56Z</t>
         </is>
       </c>
     </row>
@@ -3881,7 +3881,7 @@
       </c>
       <c r="S44" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05T21:44:21Z</t>
+          <t>2026-08-07T00:56:56Z</t>
         </is>
       </c>
     </row>
@@ -3966,7 +3966,7 @@
       </c>
       <c r="S45" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05T21:44:21Z</t>
+          <t>2026-08-07T00:56:56Z</t>
         </is>
       </c>
     </row>
@@ -4051,7 +4051,7 @@
       </c>
       <c r="S46" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05T21:44:21Z</t>
+          <t>2026-08-07T00:56:56Z</t>
         </is>
       </c>
     </row>
@@ -4136,7 +4136,7 @@
       </c>
       <c r="S47" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05T21:44:21Z</t>
+          <t>2026-08-07T00:56:56Z</t>
         </is>
       </c>
     </row>
@@ -4221,7 +4221,7 @@
       </c>
       <c r="S48" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05T21:44:21Z</t>
+          <t>2026-08-07T00:56:56Z</t>
         </is>
       </c>
     </row>
@@ -4306,7 +4306,7 @@
       </c>
       <c r="S49" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05T21:44:21Z</t>
+          <t>2026-08-07T00:56:56Z</t>
         </is>
       </c>
     </row>
@@ -4391,7 +4391,7 @@
       </c>
       <c r="S50" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05T21:44:21Z</t>
+          <t>2026-08-07T00:56:56Z</t>
         </is>
       </c>
     </row>
@@ -4476,7 +4476,7 @@
       </c>
       <c r="S51" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05T21:44:21Z</t>
+          <t>2026-08-07T00:56:56Z</t>
         </is>
       </c>
     </row>
@@ -4561,7 +4561,7 @@
       </c>
       <c r="S52" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05T21:44:21Z</t>
+          <t>2026-08-07T00:56:56Z</t>
         </is>
       </c>
     </row>
@@ -4646,7 +4646,7 @@
       </c>
       <c r="S53" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05T21:44:21Z</t>
+          <t>2026-08-07T00:56:56Z</t>
         </is>
       </c>
     </row>
@@ -4731,7 +4731,7 @@
       </c>
       <c r="S54" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05T21:44:21Z</t>
+          <t>2026-08-07T00:56:56Z</t>
         </is>
       </c>
     </row>
@@ -4816,7 +4816,7 @@
       </c>
       <c r="S55" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05T21:44:21Z</t>
+          <t>2026-08-07T00:56:56Z</t>
         </is>
       </c>
     </row>
@@ -4901,7 +4901,7 @@
       </c>
       <c r="S56" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05T21:44:21Z</t>
+          <t>2026-08-07T00:56:56Z</t>
         </is>
       </c>
     </row>
@@ -4986,7 +4986,7 @@
       </c>
       <c r="S57" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05T21:44:21Z</t>
+          <t>2026-08-07T00:56:56Z</t>
         </is>
       </c>
     </row>
@@ -5071,7 +5071,7 @@
       </c>
       <c r="S58" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05T21:44:21Z</t>
+          <t>2026-08-07T00:56:56Z</t>
         </is>
       </c>
     </row>
@@ -5156,7 +5156,7 @@
       </c>
       <c r="S59" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05T21:44:21Z</t>
+          <t>2026-08-07T00:56:56Z</t>
         </is>
       </c>
     </row>
@@ -5241,7 +5241,7 @@
       </c>
       <c r="S60" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05T21:44:21Z</t>
+          <t>2026-08-07T00:56:56Z</t>
         </is>
       </c>
     </row>
@@ -5326,7 +5326,7 @@
       </c>
       <c r="S61" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05T21:44:21Z</t>
+          <t>2026-08-07T00:56:56Z</t>
         </is>
       </c>
     </row>
@@ -5411,7 +5411,7 @@
       </c>
       <c r="S62" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05T21:44:21Z</t>
+          <t>2026-08-07T00:56:56Z</t>
         </is>
       </c>
     </row>
@@ -5496,7 +5496,7 @@
       </c>
       <c r="S63" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05T21:44:21Z</t>
+          <t>2026-08-07T00:56:56Z</t>
         </is>
       </c>
     </row>
@@ -5581,7 +5581,7 @@
       </c>
       <c r="S64" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05T21:44:21Z</t>
+          <t>2026-08-07T00:56:56Z</t>
         </is>
       </c>
     </row>
@@ -5666,7 +5666,7 @@
       </c>
       <c r="S65" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05T21:44:21Z</t>
+          <t>2026-08-07T00:56:56Z</t>
         </is>
       </c>
     </row>
@@ -5751,7 +5751,7 @@
       </c>
       <c r="S66" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05T21:44:21Z</t>
+          <t>2026-08-07T00:56:56Z</t>
         </is>
       </c>
     </row>
@@ -5836,7 +5836,7 @@
       </c>
       <c r="S67" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05T21:44:21Z</t>
+          <t>2026-08-07T00:56:56Z</t>
         </is>
       </c>
     </row>
@@ -5921,7 +5921,7 @@
       </c>
       <c r="S68" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05T21:44:21Z</t>
+          <t>2026-08-07T00:56:56Z</t>
         </is>
       </c>
     </row>
@@ -6006,7 +6006,7 @@
       </c>
       <c r="S69" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05T21:44:21Z</t>
+          <t>2026-08-07T00:56:56Z</t>
         </is>
       </c>
     </row>
@@ -6091,7 +6091,7 @@
       </c>
       <c r="S70" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05T21:44:21Z</t>
+          <t>2026-08-07T00:56:56Z</t>
         </is>
       </c>
     </row>
@@ -6176,7 +6176,7 @@
       </c>
       <c r="S71" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05T21:44:21Z</t>
+          <t>2026-08-07T00:56:56Z</t>
         </is>
       </c>
     </row>
@@ -6261,7 +6261,7 @@
       </c>
       <c r="S72" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05T21:44:21Z</t>
+          <t>2026-08-07T00:56:56Z</t>
         </is>
       </c>
     </row>
@@ -6346,7 +6346,7 @@
       </c>
       <c r="S73" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05T21:44:21Z</t>
+          <t>2026-08-07T00:56:56Z</t>
         </is>
       </c>
     </row>
@@ -6431,7 +6431,7 @@
       </c>
       <c r="S74" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05T21:44:21Z</t>
+          <t>2026-08-07T00:56:56Z</t>
         </is>
       </c>
     </row>
@@ -6516,7 +6516,7 @@
       </c>
       <c r="S75" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05T21:44:21Z</t>
+          <t>2026-08-07T00:56:56Z</t>
         </is>
       </c>
     </row>
@@ -6601,7 +6601,7 @@
       </c>
       <c r="S76" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05T21:44:21Z</t>
+          <t>2026-08-07T00:56:56Z</t>
         </is>
       </c>
     </row>
@@ -6686,7 +6686,7 @@
       </c>
       <c r="S77" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05T21:44:21Z</t>
+          <t>2026-08-07T00:56:56Z</t>
         </is>
       </c>
     </row>
@@ -6771,7 +6771,7 @@
       </c>
       <c r="S78" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05T21:44:21Z</t>
+          <t>2026-08-07T00:56:56Z</t>
         </is>
       </c>
     </row>
@@ -6856,7 +6856,7 @@
       </c>
       <c r="S79" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05T21:44:21Z</t>
+          <t>2026-08-07T00:56:56Z</t>
         </is>
       </c>
     </row>
@@ -6941,7 +6941,7 @@
       </c>
       <c r="S80" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05T21:44:21Z</t>
+          <t>2026-08-07T00:56:56Z</t>
         </is>
       </c>
     </row>
@@ -7026,7 +7026,7 @@
       </c>
       <c r="S81" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05T21:44:21Z</t>
+          <t>2026-08-07T00:56:56Z</t>
         </is>
       </c>
     </row>
@@ -7111,7 +7111,7 @@
       </c>
       <c r="S82" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05T21:44:21Z</t>
+          <t>2026-08-07T00:56:56Z</t>
         </is>
       </c>
     </row>
@@ -7196,7 +7196,7 @@
       </c>
       <c r="S83" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05T21:44:21Z</t>
+          <t>2026-08-07T00:56:56Z</t>
         </is>
       </c>
     </row>
@@ -7281,7 +7281,7 @@
       </c>
       <c r="S84" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05T21:44:21Z</t>
+          <t>2026-08-07T00:56:56Z</t>
         </is>
       </c>
     </row>
@@ -7366,7 +7366,7 @@
       </c>
       <c r="S85" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05T21:44:21Z</t>
+          <t>2026-08-07T00:56:56Z</t>
         </is>
       </c>
     </row>
@@ -7451,7 +7451,7 @@
       </c>
       <c r="S86" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05T21:44:21Z</t>
+          <t>2026-08-07T00:56:56Z</t>
         </is>
       </c>
     </row>
@@ -7536,7 +7536,7 @@
       </c>
       <c r="S87" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05T21:44:21Z</t>
+          <t>2026-08-07T00:56:56Z</t>
         </is>
       </c>
     </row>
@@ -7621,7 +7621,7 @@
       </c>
       <c r="S88" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05T21:44:21Z</t>
+          <t>2026-08-07T00:56:56Z</t>
         </is>
       </c>
     </row>
@@ -7706,7 +7706,7 @@
       </c>
       <c r="S89" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05T21:44:21Z</t>
+          <t>2026-08-07T00:56:56Z</t>
         </is>
       </c>
     </row>
@@ -7791,7 +7791,7 @@
       </c>
       <c r="S90" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05T21:44:21Z</t>
+          <t>2026-08-07T00:56:56Z</t>
         </is>
       </c>
     </row>
@@ -7876,7 +7876,7 @@
       </c>
       <c r="S91" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05T21:44:21Z</t>
+          <t>2026-08-07T00:56:56Z</t>
         </is>
       </c>
     </row>
@@ -7961,7 +7961,7 @@
       </c>
       <c r="S92" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05T21:44:21Z</t>
+          <t>2026-08-07T00:56:56Z</t>
         </is>
       </c>
     </row>
@@ -8046,7 +8046,7 @@
       </c>
       <c r="S93" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05T21:44:21Z</t>
+          <t>2026-08-07T00:56:56Z</t>
         </is>
       </c>
     </row>
@@ -8131,7 +8131,7 @@
       </c>
       <c r="S94" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05T21:44:21Z</t>
+          <t>2026-08-07T00:56:56Z</t>
         </is>
       </c>
     </row>
@@ -8216,7 +8216,7 @@
       </c>
       <c r="S95" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05T21:44:21Z</t>
+          <t>2026-08-07T00:56:56Z</t>
         </is>
       </c>
     </row>
@@ -8301,7 +8301,7 @@
       </c>
       <c r="S96" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05T21:44:21Z</t>
+          <t>2026-08-07T00:56:56Z</t>
         </is>
       </c>
     </row>
@@ -8386,7 +8386,7 @@
       </c>
       <c r="S97" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05T21:44:21Z</t>
+          <t>2026-08-07T00:56:56Z</t>
         </is>
       </c>
     </row>
@@ -8471,7 +8471,7 @@
       </c>
       <c r="S98" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05T21:44:21Z</t>
+          <t>2026-08-07T00:56:56Z</t>
         </is>
       </c>
     </row>
@@ -8556,7 +8556,7 @@
       </c>
       <c r="S99" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05T21:44:21Z</t>
+          <t>2026-08-07T00:56:56Z</t>
         </is>
       </c>
     </row>
@@ -8641,7 +8641,7 @@
       </c>
       <c r="S100" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05T21:44:21Z</t>
+          <t>2026-08-07T00:56:56Z</t>
         </is>
       </c>
     </row>
@@ -8726,7 +8726,7 @@
       </c>
       <c r="S101" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05T21:44:21Z</t>
+          <t>2026-08-07T00:56:56Z</t>
         </is>
       </c>
     </row>
@@ -8811,7 +8811,7 @@
       </c>
       <c r="S102" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05T21:44:21Z</t>
+          <t>2026-08-07T00:56:56Z</t>
         </is>
       </c>
     </row>
@@ -8896,7 +8896,7 @@
       </c>
       <c r="S103" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05T21:44:21Z</t>
+          <t>2026-08-07T00:56:56Z</t>
         </is>
       </c>
     </row>
@@ -8981,7 +8981,7 @@
       </c>
       <c r="S104" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05T21:44:21Z</t>
+          <t>2026-08-07T00:56:56Z</t>
         </is>
       </c>
     </row>
@@ -9066,7 +9066,7 @@
       </c>
       <c r="S105" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05T21:44:21Z</t>
+          <t>2026-08-07T00:56:56Z</t>
         </is>
       </c>
     </row>
@@ -9151,7 +9151,7 @@
       </c>
       <c r="S106" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05T21:44:21Z</t>
+          <t>2026-08-07T00:56:56Z</t>
         </is>
       </c>
     </row>
@@ -9236,7 +9236,7 @@
       </c>
       <c r="S107" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05T21:44:21Z</t>
+          <t>2026-08-07T00:56:56Z</t>
         </is>
       </c>
     </row>
@@ -9321,7 +9321,7 @@
       </c>
       <c r="S108" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05T21:44:21Z</t>
+          <t>2026-08-07T00:56:56Z</t>
         </is>
       </c>
     </row>
@@ -9406,7 +9406,7 @@
       </c>
       <c r="S109" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05T21:44:21Z</t>
+          <t>2026-08-07T00:56:56Z</t>
         </is>
       </c>
     </row>
@@ -9491,7 +9491,7 @@
       </c>
       <c r="S110" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05T21:44:21Z</t>
+          <t>2026-08-07T00:56:56Z</t>
         </is>
       </c>
     </row>
@@ -9576,7 +9576,7 @@
       </c>
       <c r="S111" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05T21:44:21Z</t>
+          <t>2026-08-07T00:56:56Z</t>
         </is>
       </c>
     </row>
@@ -9661,7 +9661,7 @@
       </c>
       <c r="S112" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05T21:44:21Z</t>
+          <t>2026-08-07T00:56:56Z</t>
         </is>
       </c>
     </row>
@@ -9746,7 +9746,7 @@
       </c>
       <c r="S113" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05T21:44:21Z</t>
+          <t>2026-08-07T00:56:56Z</t>
         </is>
       </c>
     </row>
@@ -9831,7 +9831,7 @@
       </c>
       <c r="S114" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05T21:44:21Z</t>
+          <t>2026-08-07T00:56:56Z</t>
         </is>
       </c>
     </row>
@@ -9916,7 +9916,7 @@
       </c>
       <c r="S115" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05T21:44:21Z</t>
+          <t>2026-08-07T00:56:56Z</t>
         </is>
       </c>
     </row>
@@ -10001,7 +10001,7 @@
       </c>
       <c r="S116" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05T21:44:21Z</t>
+          <t>2026-08-07T00:56:56Z</t>
         </is>
       </c>
     </row>
@@ -10086,7 +10086,7 @@
       </c>
       <c r="S117" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05T21:44:21Z</t>
+          <t>2026-08-07T00:56:56Z</t>
         </is>
       </c>
     </row>
@@ -10171,7 +10171,7 @@
       </c>
       <c r="S118" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05T21:44:21Z</t>
+          <t>2026-08-07T00:56:56Z</t>
         </is>
       </c>
     </row>
@@ -10256,7 +10256,7 @@
       </c>
       <c r="S119" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05T21:44:21Z</t>
+          <t>2026-08-07T00:56:56Z</t>
         </is>
       </c>
     </row>
@@ -10341,7 +10341,7 @@
       </c>
       <c r="S120" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05T21:44:21Z</t>
+          <t>2026-08-07T00:56:56Z</t>
         </is>
       </c>
     </row>
@@ -10426,7 +10426,7 @@
       </c>
       <c r="S121" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05T21:44:21Z</t>
+          <t>2026-08-07T00:56:56Z</t>
         </is>
       </c>
     </row>
@@ -10511,7 +10511,7 @@
       </c>
       <c r="S122" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05T21:44:21Z</t>
+          <t>2026-08-07T00:56:56Z</t>
         </is>
       </c>
     </row>
@@ -10596,7 +10596,7 @@
       </c>
       <c r="S123" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05T21:44:21Z</t>
+          <t>2026-08-07T00:56:56Z</t>
         </is>
       </c>
     </row>
@@ -10681,7 +10681,7 @@
       </c>
       <c r="S124" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05T21:44:21Z</t>
+          <t>2026-08-07T00:56:56Z</t>
         </is>
       </c>
     </row>
@@ -10766,7 +10766,7 @@
       </c>
       <c r="S125" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05T21:44:21Z</t>
+          <t>2026-08-07T00:56:56Z</t>
         </is>
       </c>
     </row>
@@ -10851,7 +10851,7 @@
       </c>
       <c r="S126" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05T21:44:21Z</t>
+          <t>2026-08-07T00:56:56Z</t>
         </is>
       </c>
     </row>
@@ -10936,7 +10936,7 @@
       </c>
       <c r="S127" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05T21:44:21Z</t>
+          <t>2026-08-07T00:56:56Z</t>
         </is>
       </c>
     </row>
@@ -11021,7 +11021,7 @@
       </c>
       <c r="S128" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05T21:44:21Z</t>
+          <t>2026-08-07T00:56:56Z</t>
         </is>
       </c>
     </row>
@@ -11106,7 +11106,7 @@
       </c>
       <c r="S129" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05T21:44:21Z</t>
+          <t>2026-08-07T00:56:56Z</t>
         </is>
       </c>
     </row>
@@ -11191,7 +11191,7 @@
       </c>
       <c r="S130" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05T21:44:21Z</t>
+          <t>2026-08-07T00:56:56Z</t>
         </is>
       </c>
     </row>
@@ -11276,7 +11276,7 @@
       </c>
       <c r="S131" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05T21:44:21Z</t>
+          <t>2026-08-07T00:56:56Z</t>
         </is>
       </c>
     </row>
@@ -11361,7 +11361,7 @@
       </c>
       <c r="S132" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05T21:44:21Z</t>
+          <t>2026-08-07T00:56:56Z</t>
         </is>
       </c>
     </row>
@@ -11446,7 +11446,7 @@
       </c>
       <c r="S133" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05T21:44:21Z</t>
+          <t>2026-08-07T00:56:56Z</t>
         </is>
       </c>
     </row>
@@ -11531,7 +11531,7 @@
       </c>
       <c r="S134" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05T21:44:21Z</t>
+          <t>2026-08-07T00:56:56Z</t>
         </is>
       </c>
     </row>
@@ -11616,7 +11616,7 @@
       </c>
       <c r="S135" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05T21:44:21Z</t>
+          <t>2026-08-07T00:56:56Z</t>
         </is>
       </c>
     </row>
@@ -11701,7 +11701,7 @@
       </c>
       <c r="S136" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05T21:44:21Z</t>
+          <t>2026-08-07T00:56:56Z</t>
         </is>
       </c>
     </row>
@@ -11786,7 +11786,7 @@
       </c>
       <c r="S137" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05T21:44:21Z</t>
+          <t>2026-08-07T00:56:56Z</t>
         </is>
       </c>
     </row>
@@ -11871,7 +11871,7 @@
       </c>
       <c r="S138" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05T21:44:21Z</t>
+          <t>2026-08-07T00:56:56Z</t>
         </is>
       </c>
     </row>
@@ -11956,7 +11956,7 @@
       </c>
       <c r="S139" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05T21:44:21Z</t>
+          <t>2026-08-07T00:56:56Z</t>
         </is>
       </c>
     </row>
@@ -12041,7 +12041,7 @@
       </c>
       <c r="S140" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05T21:44:21Z</t>
+          <t>2026-08-07T00:56:56Z</t>
         </is>
       </c>
     </row>
@@ -12126,7 +12126,7 @@
       </c>
       <c r="S141" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05T21:44:21Z</t>
+          <t>2026-08-07T00:56:56Z</t>
         </is>
       </c>
     </row>
@@ -12258,7 +12258,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05T21:44:21Z</t>
+          <t>2026-08-07T00:56:56Z</t>
         </is>
       </c>
     </row>
@@ -12338,7 +12338,7 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>{"dataset_id": "bcv_pib_historico_anual", "title": "Producto interno bruto histórico anual", "table": "PIB histórico anual", "source_file": "7_1_14_anual.xls", "base": "1957/1968/1984/1997", "price_type": "Precios constantes", "measure": "Nivel", "frequency": "Anual", "period": "2017", "year": 2017, "quarter": null, "classification": "Total economía", "component": "Producto interno bruto", "value": 392393.12, "unit": "Millones de bolívares a precios constantes", "status": "", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/7_1_14_anual.xls", "fetched_at": "2026-08-05T21:44:21Z"}</t>
+          <t>{"dataset_id": "bcv_pib_historico_anual", "title": "Producto interno bruto histórico anual", "table": "PIB histórico anual", "source_file": "7_1_14_anual.xls", "base": "1957/1968/1984/1997", "price_type": "Precios constantes", "measure": "Nivel", "frequency": "Anual", "period": "2017", "year": 2017, "quarter": null, "classification": "Total economía", "component": "Producto interno bruto", "value": 392393.12, "unit": "Millones de bolívares a precios constantes", "status": "", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/7_1_14_anual.xls", "fetched_at": "2026-08-07T00:56:56Z"}</t>
         </is>
       </c>
     </row>

--- a/assets/data/bcv/excel/ove_bcv_pib_historico_anual.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_pib_historico_anual.xlsx
@@ -736,7 +736,7 @@
       </c>
       <c r="S7" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -821,7 +821,7 @@
       </c>
       <c r="S8" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -906,7 +906,7 @@
       </c>
       <c r="S9" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -991,7 +991,7 @@
       </c>
       <c r="S10" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="S11" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -1161,7 +1161,7 @@
       </c>
       <c r="S12" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -1246,7 +1246,7 @@
       </c>
       <c r="S13" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -1331,7 +1331,7 @@
       </c>
       <c r="S14" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -1416,7 +1416,7 @@
       </c>
       <c r="S15" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -1501,7 +1501,7 @@
       </c>
       <c r="S16" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -1586,7 +1586,7 @@
       </c>
       <c r="S17" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -1671,7 +1671,7 @@
       </c>
       <c r="S18" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -1756,7 +1756,7 @@
       </c>
       <c r="S19" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -1841,7 +1841,7 @@
       </c>
       <c r="S20" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -1926,7 +1926,7 @@
       </c>
       <c r="S21" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -2011,7 +2011,7 @@
       </c>
       <c r="S22" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="S23" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -2181,7 +2181,7 @@
       </c>
       <c r="S24" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -2266,7 +2266,7 @@
       </c>
       <c r="S25" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -2351,7 +2351,7 @@
       </c>
       <c r="S26" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -2436,7 +2436,7 @@
       </c>
       <c r="S27" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -2521,7 +2521,7 @@
       </c>
       <c r="S28" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -2606,7 +2606,7 @@
       </c>
       <c r="S29" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -2691,7 +2691,7 @@
       </c>
       <c r="S30" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -2776,7 +2776,7 @@
       </c>
       <c r="S31" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -2861,7 +2861,7 @@
       </c>
       <c r="S32" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -2946,7 +2946,7 @@
       </c>
       <c r="S33" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -3031,7 +3031,7 @@
       </c>
       <c r="S34" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -3116,7 +3116,7 @@
       </c>
       <c r="S35" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -3201,7 +3201,7 @@
       </c>
       <c r="S36" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -3286,7 +3286,7 @@
       </c>
       <c r="S37" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -3371,7 +3371,7 @@
       </c>
       <c r="S38" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -3456,7 +3456,7 @@
       </c>
       <c r="S39" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -3541,7 +3541,7 @@
       </c>
       <c r="S40" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -3626,7 +3626,7 @@
       </c>
       <c r="S41" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -3711,7 +3711,7 @@
       </c>
       <c r="S42" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -3796,7 +3796,7 @@
       </c>
       <c r="S43" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -3881,7 +3881,7 @@
       </c>
       <c r="S44" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -3966,7 +3966,7 @@
       </c>
       <c r="S45" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -4051,7 +4051,7 @@
       </c>
       <c r="S46" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -4136,7 +4136,7 @@
       </c>
       <c r="S47" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -4221,7 +4221,7 @@
       </c>
       <c r="S48" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -4306,7 +4306,7 @@
       </c>
       <c r="S49" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -4391,7 +4391,7 @@
       </c>
       <c r="S50" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -4476,7 +4476,7 @@
       </c>
       <c r="S51" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -4561,7 +4561,7 @@
       </c>
       <c r="S52" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -4646,7 +4646,7 @@
       </c>
       <c r="S53" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -4731,7 +4731,7 @@
       </c>
       <c r="S54" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -4816,7 +4816,7 @@
       </c>
       <c r="S55" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -4901,7 +4901,7 @@
       </c>
       <c r="S56" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -4986,7 +4986,7 @@
       </c>
       <c r="S57" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -5071,7 +5071,7 @@
       </c>
       <c r="S58" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -5156,7 +5156,7 @@
       </c>
       <c r="S59" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -5241,7 +5241,7 @@
       </c>
       <c r="S60" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -5326,7 +5326,7 @@
       </c>
       <c r="S61" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -5411,7 +5411,7 @@
       </c>
       <c r="S62" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -5496,7 +5496,7 @@
       </c>
       <c r="S63" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -5581,7 +5581,7 @@
       </c>
       <c r="S64" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -5666,7 +5666,7 @@
       </c>
       <c r="S65" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -5751,7 +5751,7 @@
       </c>
       <c r="S66" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -5836,7 +5836,7 @@
       </c>
       <c r="S67" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -5921,7 +5921,7 @@
       </c>
       <c r="S68" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -6006,7 +6006,7 @@
       </c>
       <c r="S69" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -6091,7 +6091,7 @@
       </c>
       <c r="S70" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -6176,7 +6176,7 @@
       </c>
       <c r="S71" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -6261,7 +6261,7 @@
       </c>
       <c r="S72" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -6346,7 +6346,7 @@
       </c>
       <c r="S73" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -6431,7 +6431,7 @@
       </c>
       <c r="S74" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -6516,7 +6516,7 @@
       </c>
       <c r="S75" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -6601,7 +6601,7 @@
       </c>
       <c r="S76" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -6686,7 +6686,7 @@
       </c>
       <c r="S77" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -6771,7 +6771,7 @@
       </c>
       <c r="S78" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -6856,7 +6856,7 @@
       </c>
       <c r="S79" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -6941,7 +6941,7 @@
       </c>
       <c r="S80" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -7026,7 +7026,7 @@
       </c>
       <c r="S81" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -7111,7 +7111,7 @@
       </c>
       <c r="S82" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -7196,7 +7196,7 @@
       </c>
       <c r="S83" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -7281,7 +7281,7 @@
       </c>
       <c r="S84" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -7366,7 +7366,7 @@
       </c>
       <c r="S85" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -7451,7 +7451,7 @@
       </c>
       <c r="S86" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -7536,7 +7536,7 @@
       </c>
       <c r="S87" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -7621,7 +7621,7 @@
       </c>
       <c r="S88" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -7706,7 +7706,7 @@
       </c>
       <c r="S89" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -7791,7 +7791,7 @@
       </c>
       <c r="S90" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -7876,7 +7876,7 @@
       </c>
       <c r="S91" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -7961,7 +7961,7 @@
       </c>
       <c r="S92" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -8046,7 +8046,7 @@
       </c>
       <c r="S93" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -8131,7 +8131,7 @@
       </c>
       <c r="S94" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -8216,7 +8216,7 @@
       </c>
       <c r="S95" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -8301,7 +8301,7 @@
       </c>
       <c r="S96" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -8386,7 +8386,7 @@
       </c>
       <c r="S97" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -8471,7 +8471,7 @@
       </c>
       <c r="S98" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -8556,7 +8556,7 @@
       </c>
       <c r="S99" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -8641,7 +8641,7 @@
       </c>
       <c r="S100" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -8726,7 +8726,7 @@
       </c>
       <c r="S101" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -8811,7 +8811,7 @@
       </c>
       <c r="S102" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -8896,7 +8896,7 @@
       </c>
       <c r="S103" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -8981,7 +8981,7 @@
       </c>
       <c r="S104" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -9066,7 +9066,7 @@
       </c>
       <c r="S105" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -9151,7 +9151,7 @@
       </c>
       <c r="S106" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -9236,7 +9236,7 @@
       </c>
       <c r="S107" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -9321,7 +9321,7 @@
       </c>
       <c r="S108" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -9406,7 +9406,7 @@
       </c>
       <c r="S109" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -9491,7 +9491,7 @@
       </c>
       <c r="S110" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -9576,7 +9576,7 @@
       </c>
       <c r="S111" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -9661,7 +9661,7 @@
       </c>
       <c r="S112" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -9746,7 +9746,7 @@
       </c>
       <c r="S113" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -9831,7 +9831,7 @@
       </c>
       <c r="S114" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -9916,7 +9916,7 @@
       </c>
       <c r="S115" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -10001,7 +10001,7 @@
       </c>
       <c r="S116" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -10086,7 +10086,7 @@
       </c>
       <c r="S117" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -10171,7 +10171,7 @@
       </c>
       <c r="S118" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -10256,7 +10256,7 @@
       </c>
       <c r="S119" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -10341,7 +10341,7 @@
       </c>
       <c r="S120" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -10426,7 +10426,7 @@
       </c>
       <c r="S121" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -10511,7 +10511,7 @@
       </c>
       <c r="S122" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -10596,7 +10596,7 @@
       </c>
       <c r="S123" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -10681,7 +10681,7 @@
       </c>
       <c r="S124" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -10766,7 +10766,7 @@
       </c>
       <c r="S125" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -10851,7 +10851,7 @@
       </c>
       <c r="S126" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -10936,7 +10936,7 @@
       </c>
       <c r="S127" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -11021,7 +11021,7 @@
       </c>
       <c r="S128" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -11106,7 +11106,7 @@
       </c>
       <c r="S129" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -11191,7 +11191,7 @@
       </c>
       <c r="S130" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -11276,7 +11276,7 @@
       </c>
       <c r="S131" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -11361,7 +11361,7 @@
       </c>
       <c r="S132" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -11446,7 +11446,7 @@
       </c>
       <c r="S133" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -11531,7 +11531,7 @@
       </c>
       <c r="S134" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -11616,7 +11616,7 @@
       </c>
       <c r="S135" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -11701,7 +11701,7 @@
       </c>
       <c r="S136" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -11786,7 +11786,7 @@
       </c>
       <c r="S137" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -11871,7 +11871,7 @@
       </c>
       <c r="S138" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -11956,7 +11956,7 @@
       </c>
       <c r="S139" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -12041,7 +12041,7 @@
       </c>
       <c r="S140" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -12126,7 +12126,7 @@
       </c>
       <c r="S141" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -12258,7 +12258,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -12338,7 +12338,7 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>{"dataset_id": "bcv_pib_historico_anual", "title": "Producto interno bruto histórico anual", "table": "PIB histórico anual", "source_file": "7_1_14_anual.xls", "base": "1957/1968/1984/1997", "price_type": "Precios constantes", "measure": "Nivel", "frequency": "Anual", "period": "2017", "year": 2017, "quarter": null, "classification": "Total economía", "component": "Producto interno bruto", "value": 392393.12, "unit": "Millones de bolívares a precios constantes", "status": "", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/7_1_14_anual.xls", "fetched_at": "2026-08-07T00:56:56Z"}</t>
+          <t>{"dataset_id": "bcv_pib_historico_anual", "title": "Producto interno bruto histórico anual", "table": "PIB histórico anual", "source_file": "7_1_14_anual.xls", "base": "1957/1968/1984/1997", "price_type": "Precios constantes", "measure": "Nivel", "frequency": "Anual", "period": "2017", "year": 2017, "quarter": null, "classification": "Total economía", "component": "Producto interno bruto", "value": 392393.12, "unit": "Millones de bolívares a precios constantes", "status": "", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/7_1_14_anual.xls", "fetched_at": "2026-08-07T14:18:55Z"}</t>
         </is>
       </c>
     </row>

--- a/assets/data/bcv/excel/ove_bcv_pib_historico_anual.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_pib_historico_anual.xlsx
@@ -736,7 +736,7 @@
       </c>
       <c r="S7" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T14:18:55Z</t>
+          <t>2026-08-07T21:09:10Z</t>
         </is>
       </c>
     </row>
@@ -821,7 +821,7 @@
       </c>
       <c r="S8" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T14:18:55Z</t>
+          <t>2026-08-07T21:09:10Z</t>
         </is>
       </c>
     </row>
@@ -906,7 +906,7 @@
       </c>
       <c r="S9" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T14:18:55Z</t>
+          <t>2026-08-07T21:09:10Z</t>
         </is>
       </c>
     </row>
@@ -991,7 +991,7 @@
       </c>
       <c r="S10" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T14:18:55Z</t>
+          <t>2026-08-07T21:09:10Z</t>
         </is>
       </c>
     </row>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="S11" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T14:18:55Z</t>
+          <t>2026-08-07T21:09:10Z</t>
         </is>
       </c>
     </row>
@@ -1161,7 +1161,7 @@
       </c>
       <c r="S12" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T14:18:55Z</t>
+          <t>2026-08-07T21:09:10Z</t>
         </is>
       </c>
     </row>
@@ -1246,7 +1246,7 @@
       </c>
       <c r="S13" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T14:18:55Z</t>
+          <t>2026-08-07T21:09:10Z</t>
         </is>
       </c>
     </row>
@@ -1331,7 +1331,7 @@
       </c>
       <c r="S14" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T14:18:55Z</t>
+          <t>2026-08-07T21:09:10Z</t>
         </is>
       </c>
     </row>
@@ -1416,7 +1416,7 @@
       </c>
       <c r="S15" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T14:18:55Z</t>
+          <t>2026-08-07T21:09:10Z</t>
         </is>
       </c>
     </row>
@@ -1501,7 +1501,7 @@
       </c>
       <c r="S16" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T14:18:55Z</t>
+          <t>2026-08-07T21:09:10Z</t>
         </is>
       </c>
     </row>
@@ -1586,7 +1586,7 @@
       </c>
       <c r="S17" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T14:18:55Z</t>
+          <t>2026-08-07T21:09:10Z</t>
         </is>
       </c>
     </row>
@@ -1671,7 +1671,7 @@
       </c>
       <c r="S18" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T14:18:55Z</t>
+          <t>2026-08-07T21:09:10Z</t>
         </is>
       </c>
     </row>
@@ -1756,7 +1756,7 @@
       </c>
       <c r="S19" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T14:18:55Z</t>
+          <t>2026-08-07T21:09:10Z</t>
         </is>
       </c>
     </row>
@@ -1841,7 +1841,7 @@
       </c>
       <c r="S20" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T14:18:55Z</t>
+          <t>2026-08-07T21:09:10Z</t>
         </is>
       </c>
     </row>
@@ -1926,7 +1926,7 @@
       </c>
       <c r="S21" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T14:18:55Z</t>
+          <t>2026-08-07T21:09:10Z</t>
         </is>
       </c>
     </row>
@@ -2011,7 +2011,7 @@
       </c>
       <c r="S22" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T14:18:55Z</t>
+          <t>2026-08-07T21:09:10Z</t>
         </is>
       </c>
     </row>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="S23" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T14:18:55Z</t>
+          <t>2026-08-07T21:09:10Z</t>
         </is>
       </c>
     </row>
@@ -2181,7 +2181,7 @@
       </c>
       <c r="S24" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T14:18:55Z</t>
+          <t>2026-08-07T21:09:10Z</t>
         </is>
       </c>
     </row>
@@ -2266,7 +2266,7 @@
       </c>
       <c r="S25" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T14:18:55Z</t>
+          <t>2026-08-07T21:09:10Z</t>
         </is>
       </c>
     </row>
@@ -2351,7 +2351,7 @@
       </c>
       <c r="S26" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T14:18:55Z</t>
+          <t>2026-08-07T21:09:10Z</t>
         </is>
       </c>
     </row>
@@ -2436,7 +2436,7 @@
       </c>
       <c r="S27" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T14:18:55Z</t>
+          <t>2026-08-07T21:09:10Z</t>
         </is>
       </c>
     </row>
@@ -2521,7 +2521,7 @@
       </c>
       <c r="S28" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T14:18:55Z</t>
+          <t>2026-08-07T21:09:10Z</t>
         </is>
       </c>
     </row>
@@ -2606,7 +2606,7 @@
       </c>
       <c r="S29" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T14:18:55Z</t>
+          <t>2026-08-07T21:09:10Z</t>
         </is>
       </c>
     </row>
@@ -2691,7 +2691,7 @@
       </c>
       <c r="S30" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T14:18:55Z</t>
+          <t>2026-08-07T21:09:10Z</t>
         </is>
       </c>
     </row>
@@ -2776,7 +2776,7 @@
       </c>
       <c r="S31" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T14:18:55Z</t>
+          <t>2026-08-07T21:09:10Z</t>
         </is>
       </c>
     </row>
@@ -2861,7 +2861,7 @@
       </c>
       <c r="S32" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T14:18:55Z</t>
+          <t>2026-08-07T21:09:10Z</t>
         </is>
       </c>
     </row>
@@ -2946,7 +2946,7 @@
       </c>
       <c r="S33" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T14:18:55Z</t>
+          <t>2026-08-07T21:09:10Z</t>
         </is>
       </c>
     </row>
@@ -3031,7 +3031,7 @@
       </c>
       <c r="S34" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T14:18:55Z</t>
+          <t>2026-08-07T21:09:10Z</t>
         </is>
       </c>
     </row>
@@ -3116,7 +3116,7 @@
       </c>
       <c r="S35" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T14:18:55Z</t>
+          <t>2026-08-07T21:09:10Z</t>
         </is>
       </c>
     </row>
@@ -3201,7 +3201,7 @@
       </c>
       <c r="S36" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T14:18:55Z</t>
+          <t>2026-08-07T21:09:10Z</t>
         </is>
       </c>
     </row>
@@ -3286,7 +3286,7 @@
       </c>
       <c r="S37" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T14:18:55Z</t>
+          <t>2026-08-07T21:09:10Z</t>
         </is>
       </c>
     </row>
@@ -3371,7 +3371,7 @@
       </c>
       <c r="S38" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T14:18:55Z</t>
+          <t>2026-08-07T21:09:10Z</t>
         </is>
       </c>
     </row>
@@ -3456,7 +3456,7 @@
       </c>
       <c r="S39" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T14:18:55Z</t>
+          <t>2026-08-07T21:09:10Z</t>
         </is>
       </c>
     </row>
@@ -3541,7 +3541,7 @@
       </c>
       <c r="S40" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T14:18:55Z</t>
+          <t>2026-08-07T21:09:10Z</t>
         </is>
       </c>
     </row>
@@ -3626,7 +3626,7 @@
       </c>
       <c r="S41" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T14:18:55Z</t>
+          <t>2026-08-07T21:09:10Z</t>
         </is>
       </c>
     </row>
@@ -3711,7 +3711,7 @@
       </c>
       <c r="S42" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T14:18:55Z</t>
+          <t>2026-08-07T21:09:10Z</t>
         </is>
       </c>
     </row>
@@ -3796,7 +3796,7 @@
       </c>
       <c r="S43" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T14:18:55Z</t>
+          <t>2026-08-07T21:09:10Z</t>
         </is>
       </c>
     </row>
@@ -3881,7 +3881,7 @@
       </c>
       <c r="S44" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T14:18:55Z</t>
+          <t>2026-08-07T21:09:10Z</t>
         </is>
       </c>
     </row>
@@ -3966,7 +3966,7 @@
       </c>
       <c r="S45" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T14:18:55Z</t>
+          <t>2026-08-07T21:09:10Z</t>
         </is>
       </c>
     </row>
@@ -4051,7 +4051,7 @@
       </c>
       <c r="S46" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T14:18:55Z</t>
+          <t>2026-08-07T21:09:10Z</t>
         </is>
       </c>
     </row>
@@ -4136,7 +4136,7 @@
       </c>
       <c r="S47" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T14:18:55Z</t>
+          <t>2026-08-07T21:09:10Z</t>
         </is>
       </c>
     </row>
@@ -4221,7 +4221,7 @@
       </c>
       <c r="S48" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T14:18:55Z</t>
+          <t>2026-08-07T21:09:10Z</t>
         </is>
       </c>
     </row>
@@ -4306,7 +4306,7 @@
       </c>
       <c r="S49" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T14:18:55Z</t>
+          <t>2026-08-07T21:09:10Z</t>
         </is>
       </c>
     </row>
@@ -4391,7 +4391,7 @@
       </c>
       <c r="S50" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T14:18:55Z</t>
+          <t>2026-08-07T21:09:10Z</t>
         </is>
       </c>
     </row>
@@ -4476,7 +4476,7 @@
       </c>
       <c r="S51" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T14:18:55Z</t>
+          <t>2026-08-07T21:09:10Z</t>
         </is>
       </c>
     </row>
@@ -4561,7 +4561,7 @@
       </c>
       <c r="S52" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T14:18:55Z</t>
+          <t>2026-08-07T21:09:10Z</t>
         </is>
       </c>
     </row>
@@ -4646,7 +4646,7 @@
       </c>
       <c r="S53" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T14:18:55Z</t>
+          <t>2026-08-07T21:09:10Z</t>
         </is>
       </c>
     </row>
@@ -4731,7 +4731,7 @@
       </c>
       <c r="S54" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T14:18:55Z</t>
+          <t>2026-08-07T21:09:10Z</t>
         </is>
       </c>
     </row>
@@ -4816,7 +4816,7 @@
       </c>
       <c r="S55" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T14:18:55Z</t>
+          <t>2026-08-07T21:09:10Z</t>
         </is>
       </c>
     </row>
@@ -4901,7 +4901,7 @@
       </c>
       <c r="S56" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T14:18:55Z</t>
+          <t>2026-08-07T21:09:10Z</t>
         </is>
       </c>
     </row>
@@ -4986,7 +4986,7 @@
       </c>
       <c r="S57" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T14:18:55Z</t>
+          <t>2026-08-07T21:09:10Z</t>
         </is>
       </c>
     </row>
@@ -5071,7 +5071,7 @@
       </c>
       <c r="S58" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T14:18:55Z</t>
+          <t>2026-08-07T21:09:10Z</t>
         </is>
       </c>
     </row>
@@ -5156,7 +5156,7 @@
       </c>
       <c r="S59" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T14:18:55Z</t>
+          <t>2026-08-07T21:09:10Z</t>
         </is>
       </c>
     </row>
@@ -5241,7 +5241,7 @@
       </c>
       <c r="S60" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T14:18:55Z</t>
+          <t>2026-08-07T21:09:10Z</t>
         </is>
       </c>
     </row>
@@ -5326,7 +5326,7 @@
       </c>
       <c r="S61" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T14:18:55Z</t>
+          <t>2026-08-07T21:09:10Z</t>
         </is>
       </c>
     </row>
@@ -5411,7 +5411,7 @@
       </c>
       <c r="S62" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T14:18:55Z</t>
+          <t>2026-08-07T21:09:10Z</t>
         </is>
       </c>
     </row>
@@ -5496,7 +5496,7 @@
       </c>
       <c r="S63" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T14:18:55Z</t>
+          <t>2026-08-07T21:09:10Z</t>
         </is>
       </c>
     </row>
@@ -5581,7 +5581,7 @@
       </c>
       <c r="S64" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T14:18:55Z</t>
+          <t>2026-08-07T21:09:10Z</t>
         </is>
       </c>
     </row>
@@ -5666,7 +5666,7 @@
       </c>
       <c r="S65" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T14:18:55Z</t>
+          <t>2026-08-07T21:09:10Z</t>
         </is>
       </c>
     </row>
@@ -5751,7 +5751,7 @@
       </c>
       <c r="S66" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T14:18:55Z</t>
+          <t>2026-08-07T21:09:10Z</t>
         </is>
       </c>
     </row>
@@ -5836,7 +5836,7 @@
       </c>
       <c r="S67" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T14:18:55Z</t>
+          <t>2026-08-07T21:09:10Z</t>
         </is>
       </c>
     </row>
@@ -5921,7 +5921,7 @@
       </c>
       <c r="S68" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T14:18:55Z</t>
+          <t>2026-08-07T21:09:10Z</t>
         </is>
       </c>
     </row>
@@ -6006,7 +6006,7 @@
       </c>
       <c r="S69" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T14:18:55Z</t>
+          <t>2026-08-07T21:09:10Z</t>
         </is>
       </c>
     </row>
@@ -6091,7 +6091,7 @@
       </c>
       <c r="S70" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T14:18:55Z</t>
+          <t>2026-08-07T21:09:10Z</t>
         </is>
       </c>
     </row>
@@ -6176,7 +6176,7 @@
       </c>
       <c r="S71" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T14:18:55Z</t>
+          <t>2026-08-07T21:09:10Z</t>
         </is>
       </c>
     </row>
@@ -6261,7 +6261,7 @@
       </c>
       <c r="S72" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T14:18:55Z</t>
+          <t>2026-08-07T21:09:10Z</t>
         </is>
       </c>
     </row>
@@ -6346,7 +6346,7 @@
       </c>
       <c r="S73" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T14:18:55Z</t>
+          <t>2026-08-07T21:09:10Z</t>
         </is>
       </c>
     </row>
@@ -6431,7 +6431,7 @@
       </c>
       <c r="S74" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T14:18:55Z</t>
+          <t>2026-08-07T21:09:10Z</t>
         </is>
       </c>
     </row>
@@ -6516,7 +6516,7 @@
       </c>
       <c r="S75" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T14:18:55Z</t>
+          <t>2026-08-07T21:09:10Z</t>
         </is>
       </c>
     </row>
@@ -6601,7 +6601,7 @@
       </c>
       <c r="S76" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T14:18:55Z</t>
+          <t>2026-08-07T21:09:10Z</t>
         </is>
       </c>
     </row>
@@ -6686,7 +6686,7 @@
       </c>
       <c r="S77" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T14:18:55Z</t>
+          <t>2026-08-07T21:09:10Z</t>
         </is>
       </c>
     </row>
@@ -6771,7 +6771,7 @@
       </c>
       <c r="S78" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T14:18:55Z</t>
+          <t>2026-08-07T21:09:10Z</t>
         </is>
       </c>
     </row>
@@ -6856,7 +6856,7 @@
       </c>
       <c r="S79" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T14:18:55Z</t>
+          <t>2026-08-07T21:09:10Z</t>
         </is>
       </c>
     </row>
@@ -6941,7 +6941,7 @@
       </c>
       <c r="S80" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T14:18:55Z</t>
+          <t>2026-08-07T21:09:10Z</t>
         </is>
       </c>
     </row>
@@ -7026,7 +7026,7 @@
       </c>
       <c r="S81" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T14:18:55Z</t>
+          <t>2026-08-07T21:09:10Z</t>
         </is>
       </c>
     </row>
@@ -7111,7 +7111,7 @@
       </c>
       <c r="S82" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T14:18:55Z</t>
+          <t>2026-08-07T21:09:10Z</t>
         </is>
       </c>
     </row>
@@ -7196,7 +7196,7 @@
       </c>
       <c r="S83" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T14:18:55Z</t>
+          <t>2026-08-07T21:09:10Z</t>
         </is>
       </c>
     </row>
@@ -7281,7 +7281,7 @@
       </c>
       <c r="S84" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T14:18:55Z</t>
+          <t>2026-08-07T21:09:10Z</t>
         </is>
       </c>
     </row>
@@ -7366,7 +7366,7 @@
       </c>
       <c r="S85" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T14:18:55Z</t>
+          <t>2026-08-07T21:09:10Z</t>
         </is>
       </c>
     </row>
@@ -7451,7 +7451,7 @@
       </c>
       <c r="S86" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T14:18:55Z</t>
+          <t>2026-08-07T21:09:10Z</t>
         </is>
       </c>
     </row>
@@ -7536,7 +7536,7 @@
       </c>
       <c r="S87" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T14:18:55Z</t>
+          <t>2026-08-07T21:09:10Z</t>
         </is>
       </c>
     </row>
@@ -7621,7 +7621,7 @@
       </c>
       <c r="S88" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T14:18:55Z</t>
+          <t>2026-08-07T21:09:10Z</t>
         </is>
       </c>
     </row>
@@ -7706,7 +7706,7 @@
       </c>
       <c r="S89" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T14:18:55Z</t>
+          <t>2026-08-07T21:09:10Z</t>
         </is>
       </c>
     </row>
@@ -7791,7 +7791,7 @@
       </c>
       <c r="S90" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T14:18:55Z</t>
+          <t>2026-08-07T21:09:10Z</t>
         </is>
       </c>
     </row>
@@ -7876,7 +7876,7 @@
       </c>
       <c r="S91" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T14:18:55Z</t>
+          <t>2026-08-07T21:09:10Z</t>
         </is>
       </c>
     </row>
@@ -7961,7 +7961,7 @@
       </c>
       <c r="S92" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T14:18:55Z</t>
+          <t>2026-08-07T21:09:10Z</t>
         </is>
       </c>
     </row>
@@ -8046,7 +8046,7 @@
       </c>
       <c r="S93" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T14:18:55Z</t>
+          <t>2026-08-07T21:09:10Z</t>
         </is>
       </c>
     </row>
@@ -8131,7 +8131,7 @@
       </c>
       <c r="S94" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T14:18:55Z</t>
+          <t>2026-08-07T21:09:10Z</t>
         </is>
       </c>
     </row>
@@ -8216,7 +8216,7 @@
       </c>
       <c r="S95" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T14:18:55Z</t>
+          <t>2026-08-07T21:09:10Z</t>
         </is>
       </c>
     </row>
@@ -8301,7 +8301,7 @@
       </c>
       <c r="S96" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T14:18:55Z</t>
+          <t>2026-08-07T21:09:10Z</t>
         </is>
       </c>
     </row>
@@ -8386,7 +8386,7 @@
       </c>
       <c r="S97" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T14:18:55Z</t>
+          <t>2026-08-07T21:09:10Z</t>
         </is>
       </c>
     </row>
@@ -8471,7 +8471,7 @@
       </c>
       <c r="S98" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T14:18:55Z</t>
+          <t>2026-08-07T21:09:10Z</t>
         </is>
       </c>
     </row>
@@ -8556,7 +8556,7 @@
       </c>
       <c r="S99" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T14:18:55Z</t>
+          <t>2026-08-07T21:09:10Z</t>
         </is>
       </c>
     </row>
@@ -8641,7 +8641,7 @@
       </c>
       <c r="S100" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T14:18:55Z</t>
+          <t>2026-08-07T21:09:10Z</t>
         </is>
       </c>
     </row>
@@ -8726,7 +8726,7 @@
       </c>
       <c r="S101" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T14:18:55Z</t>
+          <t>2026-08-07T21:09:10Z</t>
         </is>
       </c>
     </row>
@@ -8811,7 +8811,7 @@
       </c>
       <c r="S102" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T14:18:55Z</t>
+          <t>2026-08-07T21:09:10Z</t>
         </is>
       </c>
     </row>
@@ -8896,7 +8896,7 @@
       </c>
       <c r="S103" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T14:18:55Z</t>
+          <t>2026-08-07T21:09:10Z</t>
         </is>
       </c>
     </row>
@@ -8981,7 +8981,7 @@
       </c>
       <c r="S104" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T14:18:55Z</t>
+          <t>2026-08-07T21:09:10Z</t>
         </is>
       </c>
     </row>
@@ -9066,7 +9066,7 @@
       </c>
       <c r="S105" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T14:18:55Z</t>
+          <t>2026-08-07T21:09:10Z</t>
         </is>
       </c>
     </row>
@@ -9151,7 +9151,7 @@
       </c>
       <c r="S106" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T14:18:55Z</t>
+          <t>2026-08-07T21:09:10Z</t>
         </is>
       </c>
     </row>
@@ -9236,7 +9236,7 @@
       </c>
       <c r="S107" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T14:18:55Z</t>
+          <t>2026-08-07T21:09:10Z</t>
         </is>
       </c>
     </row>
@@ -9321,7 +9321,7 @@
       </c>
       <c r="S108" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T14:18:55Z</t>
+          <t>2026-08-07T21:09:10Z</t>
         </is>
       </c>
     </row>
@@ -9406,7 +9406,7 @@
       </c>
       <c r="S109" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T14:18:55Z</t>
+          <t>2026-08-07T21:09:10Z</t>
         </is>
       </c>
     </row>
@@ -9491,7 +9491,7 @@
       </c>
       <c r="S110" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T14:18:55Z</t>
+          <t>2026-08-07T21:09:10Z</t>
         </is>
       </c>
     </row>
@@ -9576,7 +9576,7 @@
       </c>
       <c r="S111" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T14:18:55Z</t>
+          <t>2026-08-07T21:09:10Z</t>
         </is>
       </c>
     </row>
@@ -9661,7 +9661,7 @@
       </c>
       <c r="S112" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T14:18:55Z</t>
+          <t>2026-08-07T21:09:10Z</t>
         </is>
       </c>
     </row>
@@ -9746,7 +9746,7 @@
       </c>
       <c r="S113" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T14:18:55Z</t>
+          <t>2026-08-07T21:09:10Z</t>
         </is>
       </c>
     </row>
@@ -9831,7 +9831,7 @@
       </c>
       <c r="S114" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T14:18:55Z</t>
+          <t>2026-08-07T21:09:10Z</t>
         </is>
       </c>
     </row>
@@ -9916,7 +9916,7 @@
       </c>
       <c r="S115" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T14:18:55Z</t>
+          <t>2026-08-07T21:09:10Z</t>
         </is>
       </c>
     </row>
@@ -10001,7 +10001,7 @@
       </c>
       <c r="S116" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T14:18:55Z</t>
+          <t>2026-08-07T21:09:10Z</t>
         </is>
       </c>
     </row>
@@ -10086,7 +10086,7 @@
       </c>
       <c r="S117" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T14:18:55Z</t>
+          <t>2026-08-07T21:09:10Z</t>
         </is>
       </c>
     </row>
@@ -10171,7 +10171,7 @@
       </c>
       <c r="S118" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T14:18:55Z</t>
+          <t>2026-08-07T21:09:10Z</t>
         </is>
       </c>
     </row>
@@ -10256,7 +10256,7 @@
       </c>
       <c r="S119" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T14:18:55Z</t>
+          <t>2026-08-07T21:09:10Z</t>
         </is>
       </c>
     </row>
@@ -10341,7 +10341,7 @@
       </c>
       <c r="S120" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T14:18:55Z</t>
+          <t>2026-08-07T21:09:10Z</t>
         </is>
       </c>
     </row>
@@ -10426,7 +10426,7 @@
       </c>
       <c r="S121" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T14:18:55Z</t>
+          <t>2026-08-07T21:09:10Z</t>
         </is>
       </c>
     </row>
@@ -10511,7 +10511,7 @@
       </c>
       <c r="S122" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T14:18:55Z</t>
+          <t>2026-08-07T21:09:10Z</t>
         </is>
       </c>
     </row>
@@ -10596,7 +10596,7 @@
       </c>
       <c r="S123" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T14:18:55Z</t>
+          <t>2026-08-07T21:09:10Z</t>
         </is>
       </c>
     </row>
@@ -10681,7 +10681,7 @@
       </c>
       <c r="S124" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T14:18:55Z</t>
+          <t>2026-08-07T21:09:10Z</t>
         </is>
       </c>
     </row>
@@ -10766,7 +10766,7 @@
       </c>
       <c r="S125" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T14:18:55Z</t>
+          <t>2026-08-07T21:09:10Z</t>
         </is>
       </c>
     </row>
@@ -10851,7 +10851,7 @@
       </c>
       <c r="S126" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T14:18:55Z</t>
+          <t>2026-08-07T21:09:10Z</t>
         </is>
       </c>
     </row>
@@ -10936,7 +10936,7 @@
       </c>
       <c r="S127" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T14:18:55Z</t>
+          <t>2026-08-07T21:09:10Z</t>
         </is>
       </c>
     </row>
@@ -11021,7 +11021,7 @@
       </c>
       <c r="S128" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T14:18:55Z</t>
+          <t>2026-08-07T21:09:10Z</t>
         </is>
       </c>
     </row>
@@ -11106,7 +11106,7 @@
       </c>
       <c r="S129" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T14:18:55Z</t>
+          <t>2026-08-07T21:09:10Z</t>
         </is>
       </c>
     </row>
@@ -11191,7 +11191,7 @@
       </c>
       <c r="S130" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T14:18:55Z</t>
+          <t>2026-08-07T21:09:10Z</t>
         </is>
       </c>
     </row>
@@ -11276,7 +11276,7 @@
       </c>
       <c r="S131" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T14:18:55Z</t>
+          <t>2026-08-07T21:09:10Z</t>
         </is>
       </c>
     </row>
@@ -11361,7 +11361,7 @@
       </c>
       <c r="S132" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T14:18:55Z</t>
+          <t>2026-08-07T21:09:10Z</t>
         </is>
       </c>
     </row>
@@ -11446,7 +11446,7 @@
       </c>
       <c r="S133" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T14:18:55Z</t>
+          <t>2026-08-07T21:09:10Z</t>
         </is>
       </c>
     </row>
@@ -11531,7 +11531,7 @@
       </c>
       <c r="S134" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T14:18:55Z</t>
+          <t>2026-08-07T21:09:10Z</t>
         </is>
       </c>
     </row>
@@ -11616,7 +11616,7 @@
       </c>
       <c r="S135" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T14:18:55Z</t>
+          <t>2026-08-07T21:09:10Z</t>
         </is>
       </c>
     </row>
@@ -11701,7 +11701,7 @@
       </c>
       <c r="S136" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T14:18:55Z</t>
+          <t>2026-08-07T21:09:10Z</t>
         </is>
       </c>
     </row>
@@ -11786,7 +11786,7 @@
       </c>
       <c r="S137" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T14:18:55Z</t>
+          <t>2026-08-07T21:09:10Z</t>
         </is>
       </c>
     </row>
@@ -11871,7 +11871,7 @@
       </c>
       <c r="S138" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T14:18:55Z</t>
+          <t>2026-08-07T21:09:10Z</t>
         </is>
       </c>
     </row>
@@ -11956,7 +11956,7 @@
       </c>
       <c r="S139" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T14:18:55Z</t>
+          <t>2026-08-07T21:09:10Z</t>
         </is>
       </c>
     </row>
@@ -12041,7 +12041,7 @@
       </c>
       <c r="S140" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T14:18:55Z</t>
+          <t>2026-08-07T21:09:10Z</t>
         </is>
       </c>
     </row>
@@ -12126,7 +12126,7 @@
       </c>
       <c r="S141" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T14:18:55Z</t>
+          <t>2026-08-07T21:09:10Z</t>
         </is>
       </c>
     </row>
@@ -12258,7 +12258,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T14:18:55Z</t>
+          <t>2026-08-07T21:09:10Z</t>
         </is>
       </c>
     </row>
@@ -12338,7 +12338,7 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>{"dataset_id": "bcv_pib_historico_anual", "title": "Producto interno bruto histórico anual", "table": "PIB histórico anual", "source_file": "7_1_14_anual.xls", "base": "1957/1968/1984/1997", "price_type": "Precios constantes", "measure": "Nivel", "frequency": "Anual", "period": "2017", "year": 2017, "quarter": null, "classification": "Total economía", "component": "Producto interno bruto", "value": 392393.12, "unit": "Millones de bolívares a precios constantes", "status": "", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/7_1_14_anual.xls", "fetched_at": "2026-08-07T14:18:55Z"}</t>
+          <t>{"dataset_id": "bcv_pib_historico_anual", "title": "Producto interno bruto histórico anual", "table": "PIB histórico anual", "source_file": "7_1_14_anual.xls", "base": "1957/1968/1984/1997", "price_type": "Precios constantes", "measure": "Nivel", "frequency": "Anual", "period": "2017", "year": 2017, "quarter": null, "classification": "Total economía", "component": "Producto interno bruto", "value": 392393.12, "unit": "Millones de bolívares a precios constantes", "status": "", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/7_1_14_anual.xls", "fetched_at": "2026-08-07T21:09:10Z"}</t>
         </is>
       </c>
     </row>

--- a/assets/data/bcv/excel/ove_bcv_pib_historico_anual.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_pib_historico_anual.xlsx
@@ -736,7 +736,7 @@
       </c>
       <c r="S7" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T21:09:10Z</t>
+          <t>2026-08-08T20:57:48Z</t>
         </is>
       </c>
     </row>
@@ -821,7 +821,7 @@
       </c>
       <c r="S8" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T21:09:10Z</t>
+          <t>2026-08-08T20:57:48Z</t>
         </is>
       </c>
     </row>
@@ -906,7 +906,7 @@
       </c>
       <c r="S9" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T21:09:10Z</t>
+          <t>2026-08-08T20:57:48Z</t>
         </is>
       </c>
     </row>
@@ -991,7 +991,7 @@
       </c>
       <c r="S10" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T21:09:10Z</t>
+          <t>2026-08-08T20:57:48Z</t>
         </is>
       </c>
     </row>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="S11" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T21:09:10Z</t>
+          <t>2026-08-08T20:57:48Z</t>
         </is>
       </c>
     </row>
@@ -1161,7 +1161,7 @@
       </c>
       <c r="S12" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T21:09:10Z</t>
+          <t>2026-08-08T20:57:48Z</t>
         </is>
       </c>
     </row>
@@ -1246,7 +1246,7 @@
       </c>
       <c r="S13" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T21:09:10Z</t>
+          <t>2026-08-08T20:57:48Z</t>
         </is>
       </c>
     </row>
@@ -1331,7 +1331,7 @@
       </c>
       <c r="S14" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T21:09:10Z</t>
+          <t>2026-08-08T20:57:48Z</t>
         </is>
       </c>
     </row>
@@ -1416,7 +1416,7 @@
       </c>
       <c r="S15" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T21:09:10Z</t>
+          <t>2026-08-08T20:57:48Z</t>
         </is>
       </c>
     </row>
@@ -1501,7 +1501,7 @@
       </c>
       <c r="S16" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T21:09:10Z</t>
+          <t>2026-08-08T20:57:48Z</t>
         </is>
       </c>
     </row>
@@ -1586,7 +1586,7 @@
       </c>
       <c r="S17" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T21:09:10Z</t>
+          <t>2026-08-08T20:57:48Z</t>
         </is>
       </c>
     </row>
@@ -1671,7 +1671,7 @@
       </c>
       <c r="S18" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T21:09:10Z</t>
+          <t>2026-08-08T20:57:48Z</t>
         </is>
       </c>
     </row>
@@ -1756,7 +1756,7 @@
       </c>
       <c r="S19" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T21:09:10Z</t>
+          <t>2026-08-08T20:57:48Z</t>
         </is>
       </c>
     </row>
@@ -1841,7 +1841,7 @@
       </c>
       <c r="S20" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T21:09:10Z</t>
+          <t>2026-08-08T20:57:48Z</t>
         </is>
       </c>
     </row>
@@ -1926,7 +1926,7 @@
       </c>
       <c r="S21" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T21:09:10Z</t>
+          <t>2026-08-08T20:57:48Z</t>
         </is>
       </c>
     </row>
@@ -2011,7 +2011,7 @@
       </c>
       <c r="S22" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T21:09:10Z</t>
+          <t>2026-08-08T20:57:48Z</t>
         </is>
       </c>
     </row>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="S23" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T21:09:10Z</t>
+          <t>2026-08-08T20:57:48Z</t>
         </is>
       </c>
     </row>
@@ -2181,7 +2181,7 @@
       </c>
       <c r="S24" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T21:09:10Z</t>
+          <t>2026-08-08T20:57:48Z</t>
         </is>
       </c>
     </row>
@@ -2266,7 +2266,7 @@
       </c>
       <c r="S25" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T21:09:10Z</t>
+          <t>2026-08-08T20:57:48Z</t>
         </is>
       </c>
     </row>
@@ -2351,7 +2351,7 @@
       </c>
       <c r="S26" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T21:09:10Z</t>
+          <t>2026-08-08T20:57:48Z</t>
         </is>
       </c>
     </row>
@@ -2436,7 +2436,7 @@
       </c>
       <c r="S27" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T21:09:10Z</t>
+          <t>2026-08-08T20:57:48Z</t>
         </is>
       </c>
     </row>
@@ -2521,7 +2521,7 @@
       </c>
       <c r="S28" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T21:09:10Z</t>
+          <t>2026-08-08T20:57:48Z</t>
         </is>
       </c>
     </row>
@@ -2606,7 +2606,7 @@
       </c>
       <c r="S29" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T21:09:10Z</t>
+          <t>2026-08-08T20:57:48Z</t>
         </is>
       </c>
     </row>
@@ -2691,7 +2691,7 @@
       </c>
       <c r="S30" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T21:09:10Z</t>
+          <t>2026-08-08T20:57:48Z</t>
         </is>
       </c>
     </row>
@@ -2776,7 +2776,7 @@
       </c>
       <c r="S31" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T21:09:10Z</t>
+          <t>2026-08-08T20:57:48Z</t>
         </is>
       </c>
     </row>
@@ -2861,7 +2861,7 @@
       </c>
       <c r="S32" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T21:09:10Z</t>
+          <t>2026-08-08T20:57:48Z</t>
         </is>
       </c>
     </row>
@@ -2946,7 +2946,7 @@
       </c>
       <c r="S33" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T21:09:10Z</t>
+          <t>2026-08-08T20:57:48Z</t>
         </is>
       </c>
     </row>
@@ -3031,7 +3031,7 @@
       </c>
       <c r="S34" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T21:09:10Z</t>
+          <t>2026-08-08T20:57:48Z</t>
         </is>
       </c>
     </row>
@@ -3116,7 +3116,7 @@
       </c>
       <c r="S35" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T21:09:10Z</t>
+          <t>2026-08-08T20:57:48Z</t>
         </is>
       </c>
     </row>
@@ -3201,7 +3201,7 @@
       </c>
       <c r="S36" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T21:09:10Z</t>
+          <t>2026-08-08T20:57:48Z</t>
         </is>
       </c>
     </row>
@@ -3286,7 +3286,7 @@
       </c>
       <c r="S37" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T21:09:10Z</t>
+          <t>2026-08-08T20:57:48Z</t>
         </is>
       </c>
     </row>
@@ -3371,7 +3371,7 @@
       </c>
       <c r="S38" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T21:09:10Z</t>
+          <t>2026-08-08T20:57:48Z</t>
         </is>
       </c>
     </row>
@@ -3456,7 +3456,7 @@
       </c>
       <c r="S39" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T21:09:10Z</t>
+          <t>2026-08-08T20:57:48Z</t>
         </is>
       </c>
     </row>
@@ -3541,7 +3541,7 @@
       </c>
       <c r="S40" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T21:09:10Z</t>
+          <t>2026-08-08T20:57:48Z</t>
         </is>
       </c>
     </row>
@@ -3626,7 +3626,7 @@
       </c>
       <c r="S41" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T21:09:10Z</t>
+          <t>2026-08-08T20:57:48Z</t>
         </is>
       </c>
     </row>
@@ -3711,7 +3711,7 @@
       </c>
       <c r="S42" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T21:09:10Z</t>
+          <t>2026-08-08T20:57:48Z</t>
         </is>
       </c>
     </row>
@@ -3796,7 +3796,7 @@
       </c>
       <c r="S43" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T21:09:10Z</t>
+          <t>2026-08-08T20:57:48Z</t>
         </is>
       </c>
     </row>
@@ -3881,7 +3881,7 @@
       </c>
       <c r="S44" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T21:09:10Z</t>
+          <t>2026-08-08T20:57:48Z</t>
         </is>
       </c>
     </row>
@@ -3966,7 +3966,7 @@
       </c>
       <c r="S45" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T21:09:10Z</t>
+          <t>2026-08-08T20:57:48Z</t>
         </is>
       </c>
     </row>
@@ -4051,7 +4051,7 @@
       </c>
       <c r="S46" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T21:09:10Z</t>
+          <t>2026-08-08T20:57:48Z</t>
         </is>
       </c>
     </row>
@@ -4136,7 +4136,7 @@
       </c>
       <c r="S47" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T21:09:10Z</t>
+          <t>2026-08-08T20:57:48Z</t>
         </is>
       </c>
     </row>
@@ -4221,7 +4221,7 @@
       </c>
       <c r="S48" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T21:09:10Z</t>
+          <t>2026-08-08T20:57:48Z</t>
         </is>
       </c>
     </row>
@@ -4306,7 +4306,7 @@
       </c>
       <c r="S49" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T21:09:10Z</t>
+          <t>2026-08-08T20:57:48Z</t>
         </is>
       </c>
     </row>
@@ -4391,7 +4391,7 @@
       </c>
       <c r="S50" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T21:09:10Z</t>
+          <t>2026-08-08T20:57:48Z</t>
         </is>
       </c>
     </row>
@@ -4476,7 +4476,7 @@
       </c>
       <c r="S51" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T21:09:10Z</t>
+          <t>2026-08-08T20:57:48Z</t>
         </is>
       </c>
     </row>
@@ -4561,7 +4561,7 @@
       </c>
       <c r="S52" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T21:09:10Z</t>
+          <t>2026-08-08T20:57:48Z</t>
         </is>
       </c>
     </row>
@@ -4646,7 +4646,7 @@
       </c>
       <c r="S53" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T21:09:10Z</t>
+          <t>2026-08-08T20:57:48Z</t>
         </is>
       </c>
     </row>
@@ -4731,7 +4731,7 @@
       </c>
       <c r="S54" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T21:09:10Z</t>
+          <t>2026-08-08T20:57:48Z</t>
         </is>
       </c>
     </row>
@@ -4816,7 +4816,7 @@
       </c>
       <c r="S55" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T21:09:10Z</t>
+          <t>2026-08-08T20:57:48Z</t>
         </is>
       </c>
     </row>
@@ -4901,7 +4901,7 @@
       </c>
       <c r="S56" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T21:09:10Z</t>
+          <t>2026-08-08T20:57:48Z</t>
         </is>
       </c>
     </row>
@@ -4986,7 +4986,7 @@
       </c>
       <c r="S57" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T21:09:10Z</t>
+          <t>2026-08-08T20:57:48Z</t>
         </is>
       </c>
     </row>
@@ -5071,7 +5071,7 @@
       </c>
       <c r="S58" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T21:09:10Z</t>
+          <t>2026-08-08T20:57:48Z</t>
         </is>
       </c>
     </row>
@@ -5156,7 +5156,7 @@
       </c>
       <c r="S59" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T21:09:10Z</t>
+          <t>2026-08-08T20:57:48Z</t>
         </is>
       </c>
     </row>
@@ -5241,7 +5241,7 @@
       </c>
       <c r="S60" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T21:09:10Z</t>
+          <t>2026-08-08T20:57:48Z</t>
         </is>
       </c>
     </row>
@@ -5326,7 +5326,7 @@
       </c>
       <c r="S61" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T21:09:10Z</t>
+          <t>2026-08-08T20:57:48Z</t>
         </is>
       </c>
     </row>
@@ -5411,7 +5411,7 @@
       </c>
       <c r="S62" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T21:09:10Z</t>
+          <t>2026-08-08T20:57:48Z</t>
         </is>
       </c>
     </row>
@@ -5496,7 +5496,7 @@
       </c>
       <c r="S63" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T21:09:10Z</t>
+          <t>2026-08-08T20:57:48Z</t>
         </is>
       </c>
     </row>
@@ -5581,7 +5581,7 @@
       </c>
       <c r="S64" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T21:09:10Z</t>
+          <t>2026-08-08T20:57:48Z</t>
         </is>
       </c>
     </row>
@@ -5666,7 +5666,7 @@
       </c>
       <c r="S65" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T21:09:10Z</t>
+          <t>2026-08-08T20:57:48Z</t>
         </is>
       </c>
     </row>
@@ -5751,7 +5751,7 @@
       </c>
       <c r="S66" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T21:09:10Z</t>
+          <t>2026-08-08T20:57:48Z</t>
         </is>
       </c>
     </row>
@@ -5836,7 +5836,7 @@
       </c>
       <c r="S67" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T21:09:10Z</t>
+          <t>2026-08-08T20:57:48Z</t>
         </is>
       </c>
     </row>
@@ -5921,7 +5921,7 @@
       </c>
       <c r="S68" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T21:09:10Z</t>
+          <t>2026-08-08T20:57:48Z</t>
         </is>
       </c>
     </row>
@@ -6006,7 +6006,7 @@
       </c>
       <c r="S69" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T21:09:10Z</t>
+          <t>2026-08-08T20:57:48Z</t>
         </is>
       </c>
     </row>
@@ -6091,7 +6091,7 @@
       </c>
       <c r="S70" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T21:09:10Z</t>
+          <t>2026-08-08T20:57:48Z</t>
         </is>
       </c>
     </row>
@@ -6176,7 +6176,7 @@
       </c>
       <c r="S71" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T21:09:10Z</t>
+          <t>2026-08-08T20:57:48Z</t>
         </is>
       </c>
     </row>
@@ -6261,7 +6261,7 @@
       </c>
       <c r="S72" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T21:09:10Z</t>
+          <t>2026-08-08T20:57:48Z</t>
         </is>
       </c>
     </row>
@@ -6346,7 +6346,7 @@
       </c>
       <c r="S73" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T21:09:10Z</t>
+          <t>2026-08-08T20:57:48Z</t>
         </is>
       </c>
     </row>
@@ -6431,7 +6431,7 @@
       </c>
       <c r="S74" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T21:09:10Z</t>
+          <t>2026-08-08T20:57:48Z</t>
         </is>
       </c>
     </row>
@@ -6516,7 +6516,7 @@
       </c>
       <c r="S75" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T21:09:10Z</t>
+          <t>2026-08-08T20:57:48Z</t>
         </is>
       </c>
     </row>
@@ -6601,7 +6601,7 @@
       </c>
       <c r="S76" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T21:09:10Z</t>
+          <t>2026-08-08T20:57:48Z</t>
         </is>
       </c>
     </row>
@@ -6686,7 +6686,7 @@
       </c>
       <c r="S77" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T21:09:10Z</t>
+          <t>2026-08-08T20:57:48Z</t>
         </is>
       </c>
     </row>
@@ -6771,7 +6771,7 @@
       </c>
       <c r="S78" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T21:09:10Z</t>
+          <t>2026-08-08T20:57:48Z</t>
         </is>
       </c>
     </row>
@@ -6856,7 +6856,7 @@
       </c>
       <c r="S79" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T21:09:10Z</t>
+          <t>2026-08-08T20:57:48Z</t>
         </is>
       </c>
     </row>
@@ -6941,7 +6941,7 @@
       </c>
       <c r="S80" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T21:09:10Z</t>
+          <t>2026-08-08T20:57:48Z</t>
         </is>
       </c>
     </row>
@@ -7026,7 +7026,7 @@
       </c>
       <c r="S81" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T21:09:10Z</t>
+          <t>2026-08-08T20:57:48Z</t>
         </is>
       </c>
     </row>
@@ -7111,7 +7111,7 @@
       </c>
       <c r="S82" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T21:09:10Z</t>
+          <t>2026-08-08T20:57:48Z</t>
         </is>
       </c>
     </row>
@@ -7196,7 +7196,7 @@
       </c>
       <c r="S83" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T21:09:10Z</t>
+          <t>2026-08-08T20:57:48Z</t>
         </is>
       </c>
     </row>
@@ -7281,7 +7281,7 @@
       </c>
       <c r="S84" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T21:09:10Z</t>
+          <t>2026-08-08T20:57:48Z</t>
         </is>
       </c>
     </row>
@@ -7366,7 +7366,7 @@
       </c>
       <c r="S85" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T21:09:10Z</t>
+          <t>2026-08-08T20:57:48Z</t>
         </is>
       </c>
     </row>
@@ -7451,7 +7451,7 @@
       </c>
       <c r="S86" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T21:09:10Z</t>
+          <t>2026-08-08T20:57:48Z</t>
         </is>
       </c>
     </row>
@@ -7536,7 +7536,7 @@
       </c>
       <c r="S87" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T21:09:10Z</t>
+          <t>2026-08-08T20:57:48Z</t>
         </is>
       </c>
     </row>
@@ -7621,7 +7621,7 @@
       </c>
       <c r="S88" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T21:09:10Z</t>
+          <t>2026-08-08T20:57:48Z</t>
         </is>
       </c>
     </row>
@@ -7706,7 +7706,7 @@
       </c>
       <c r="S89" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T21:09:10Z</t>
+          <t>2026-08-08T20:57:48Z</t>
         </is>
       </c>
     </row>
@@ -7791,7 +7791,7 @@
       </c>
       <c r="S90" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T21:09:10Z</t>
+          <t>2026-08-08T20:57:48Z</t>
         </is>
       </c>
     </row>
@@ -7876,7 +7876,7 @@
       </c>
       <c r="S91" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T21:09:10Z</t>
+          <t>2026-08-08T20:57:48Z</t>
         </is>
       </c>
     </row>
@@ -7961,7 +7961,7 @@
       </c>
       <c r="S92" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T21:09:10Z</t>
+          <t>2026-08-08T20:57:48Z</t>
         </is>
       </c>
     </row>
@@ -8046,7 +8046,7 @@
       </c>
       <c r="S93" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T21:09:10Z</t>
+          <t>2026-08-08T20:57:48Z</t>
         </is>
       </c>
     </row>
@@ -8131,7 +8131,7 @@
       </c>
       <c r="S94" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T21:09:10Z</t>
+          <t>2026-08-08T20:57:48Z</t>
         </is>
       </c>
     </row>
@@ -8216,7 +8216,7 @@
       </c>
       <c r="S95" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T21:09:10Z</t>
+          <t>2026-08-08T20:57:48Z</t>
         </is>
       </c>
     </row>
@@ -8301,7 +8301,7 @@
       </c>
       <c r="S96" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T21:09:10Z</t>
+          <t>2026-08-08T20:57:48Z</t>
         </is>
       </c>
     </row>
@@ -8386,7 +8386,7 @@
       </c>
       <c r="S97" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T21:09:10Z</t>
+          <t>2026-08-08T20:57:48Z</t>
         </is>
       </c>
     </row>
@@ -8471,7 +8471,7 @@
       </c>
       <c r="S98" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T21:09:10Z</t>
+          <t>2026-08-08T20:57:48Z</t>
         </is>
       </c>
     </row>
@@ -8556,7 +8556,7 @@
       </c>
       <c r="S99" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T21:09:10Z</t>
+          <t>2026-08-08T20:57:48Z</t>
         </is>
       </c>
     </row>
@@ -8641,7 +8641,7 @@
       </c>
       <c r="S100" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T21:09:10Z</t>
+          <t>2026-08-08T20:57:48Z</t>
         </is>
       </c>
     </row>
@@ -8726,7 +8726,7 @@
       </c>
       <c r="S101" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T21:09:10Z</t>
+          <t>2026-08-08T20:57:48Z</t>
         </is>
       </c>
     </row>
@@ -8811,7 +8811,7 @@
       </c>
       <c r="S102" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T21:09:10Z</t>
+          <t>2026-08-08T20:57:48Z</t>
         </is>
       </c>
     </row>
@@ -8896,7 +8896,7 @@
       </c>
       <c r="S103" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T21:09:10Z</t>
+          <t>2026-08-08T20:57:48Z</t>
         </is>
       </c>
     </row>
@@ -8981,7 +8981,7 @@
       </c>
       <c r="S104" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T21:09:10Z</t>
+          <t>2026-08-08T20:57:48Z</t>
         </is>
       </c>
     </row>
@@ -9066,7 +9066,7 @@
       </c>
       <c r="S105" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T21:09:10Z</t>
+          <t>2026-08-08T20:57:48Z</t>
         </is>
       </c>
     </row>
@@ -9151,7 +9151,7 @@
       </c>
       <c r="S106" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T21:09:10Z</t>
+          <t>2026-08-08T20:57:48Z</t>
         </is>
       </c>
     </row>
@@ -9236,7 +9236,7 @@
       </c>
       <c r="S107" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T21:09:10Z</t>
+          <t>2026-08-08T20:57:48Z</t>
         </is>
       </c>
     </row>
@@ -9321,7 +9321,7 @@
       </c>
       <c r="S108" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T21:09:10Z</t>
+          <t>2026-08-08T20:57:48Z</t>
         </is>
       </c>
     </row>
@@ -9406,7 +9406,7 @@
       </c>
       <c r="S109" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T21:09:10Z</t>
+          <t>2026-08-08T20:57:48Z</t>
         </is>
       </c>
     </row>
@@ -9491,7 +9491,7 @@
       </c>
       <c r="S110" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T21:09:10Z</t>
+          <t>2026-08-08T20:57:48Z</t>
         </is>
       </c>
     </row>
@@ -9576,7 +9576,7 @@
       </c>
       <c r="S111" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T21:09:10Z</t>
+          <t>2026-08-08T20:57:48Z</t>
         </is>
       </c>
     </row>
@@ -9661,7 +9661,7 @@
       </c>
       <c r="S112" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T21:09:10Z</t>
+          <t>2026-08-08T20:57:48Z</t>
         </is>
       </c>
     </row>
@@ -9746,7 +9746,7 @@
       </c>
       <c r="S113" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T21:09:10Z</t>
+          <t>2026-08-08T20:57:48Z</t>
         </is>
       </c>
     </row>
@@ -9831,7 +9831,7 @@
       </c>
       <c r="S114" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T21:09:10Z</t>
+          <t>2026-08-08T20:57:48Z</t>
         </is>
       </c>
     </row>
@@ -9916,7 +9916,7 @@
       </c>
       <c r="S115" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T21:09:10Z</t>
+          <t>2026-08-08T20:57:48Z</t>
         </is>
       </c>
     </row>
@@ -10001,7 +10001,7 @@
       </c>
       <c r="S116" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T21:09:10Z</t>
+          <t>2026-08-08T20:57:48Z</t>
         </is>
       </c>
     </row>
@@ -10086,7 +10086,7 @@
       </c>
       <c r="S117" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T21:09:10Z</t>
+          <t>2026-08-08T20:57:48Z</t>
         </is>
       </c>
     </row>
@@ -10171,7 +10171,7 @@
       </c>
       <c r="S118" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T21:09:10Z</t>
+          <t>2026-08-08T20:57:48Z</t>
         </is>
       </c>
     </row>
@@ -10256,7 +10256,7 @@
       </c>
       <c r="S119" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T21:09:10Z</t>
+          <t>2026-08-08T20:57:48Z</t>
         </is>
       </c>
     </row>
@@ -10341,7 +10341,7 @@
       </c>
       <c r="S120" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T21:09:10Z</t>
+          <t>2026-08-08T20:57:48Z</t>
         </is>
       </c>
     </row>
@@ -10426,7 +10426,7 @@
       </c>
       <c r="S121" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T21:09:10Z</t>
+          <t>2026-08-08T20:57:48Z</t>
         </is>
       </c>
     </row>
@@ -10511,7 +10511,7 @@
       </c>
       <c r="S122" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T21:09:10Z</t>
+          <t>2026-08-08T20:57:48Z</t>
         </is>
       </c>
     </row>
@@ -10596,7 +10596,7 @@
       </c>
       <c r="S123" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T21:09:10Z</t>
+          <t>2026-08-08T20:57:48Z</t>
         </is>
       </c>
     </row>
@@ -10681,7 +10681,7 @@
       </c>
       <c r="S124" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T21:09:10Z</t>
+          <t>2026-08-08T20:57:48Z</t>
         </is>
       </c>
     </row>
@@ -10766,7 +10766,7 @@
       </c>
       <c r="S125" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T21:09:10Z</t>
+          <t>2026-08-08T20:57:48Z</t>
         </is>
       </c>
     </row>
@@ -10851,7 +10851,7 @@
       </c>
       <c r="S126" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T21:09:10Z</t>
+          <t>2026-08-08T20:57:48Z</t>
         </is>
       </c>
     </row>
@@ -10936,7 +10936,7 @@
       </c>
       <c r="S127" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T21:09:10Z</t>
+          <t>2026-08-08T20:57:48Z</t>
         </is>
       </c>
     </row>
@@ -11021,7 +11021,7 @@
       </c>
       <c r="S128" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T21:09:10Z</t>
+          <t>2026-08-08T20:57:48Z</t>
         </is>
       </c>
     </row>
@@ -11106,7 +11106,7 @@
       </c>
       <c r="S129" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T21:09:10Z</t>
+          <t>2026-08-08T20:57:48Z</t>
         </is>
       </c>
     </row>
@@ -11191,7 +11191,7 @@
       </c>
       <c r="S130" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T21:09:10Z</t>
+          <t>2026-08-08T20:57:48Z</t>
         </is>
       </c>
     </row>
@@ -11276,7 +11276,7 @@
       </c>
       <c r="S131" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T21:09:10Z</t>
+          <t>2026-08-08T20:57:48Z</t>
         </is>
       </c>
     </row>
@@ -11361,7 +11361,7 @@
       </c>
       <c r="S132" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T21:09:10Z</t>
+          <t>2026-08-08T20:57:48Z</t>
         </is>
       </c>
     </row>
@@ -11446,7 +11446,7 @@
       </c>
       <c r="S133" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T21:09:10Z</t>
+          <t>2026-08-08T20:57:48Z</t>
         </is>
       </c>
     </row>
@@ -11531,7 +11531,7 @@
       </c>
       <c r="S134" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T21:09:10Z</t>
+          <t>2026-08-08T20:57:48Z</t>
         </is>
       </c>
     </row>
@@ -11616,7 +11616,7 @@
       </c>
       <c r="S135" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T21:09:10Z</t>
+          <t>2026-08-08T20:57:48Z</t>
         </is>
       </c>
     </row>
@@ -11701,7 +11701,7 @@
       </c>
       <c r="S136" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T21:09:10Z</t>
+          <t>2026-08-08T20:57:48Z</t>
         </is>
       </c>
     </row>
@@ -11786,7 +11786,7 @@
       </c>
       <c r="S137" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T21:09:10Z</t>
+          <t>2026-08-08T20:57:48Z</t>
         </is>
       </c>
     </row>
@@ -11871,7 +11871,7 @@
       </c>
       <c r="S138" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T21:09:10Z</t>
+          <t>2026-08-08T20:57:48Z</t>
         </is>
       </c>
     </row>
@@ -11956,7 +11956,7 @@
       </c>
       <c r="S139" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T21:09:10Z</t>
+          <t>2026-08-08T20:57:48Z</t>
         </is>
       </c>
     </row>
@@ -12041,7 +12041,7 @@
       </c>
       <c r="S140" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T21:09:10Z</t>
+          <t>2026-08-08T20:57:48Z</t>
         </is>
       </c>
     </row>
@@ -12126,7 +12126,7 @@
       </c>
       <c r="S141" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T21:09:10Z</t>
+          <t>2026-08-08T20:57:48Z</t>
         </is>
       </c>
     </row>
@@ -12258,7 +12258,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T21:09:10Z</t>
+          <t>2026-08-08T20:57:48Z</t>
         </is>
       </c>
     </row>
@@ -12338,7 +12338,7 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>{"dataset_id": "bcv_pib_historico_anual", "title": "Producto interno bruto histórico anual", "table": "PIB histórico anual", "source_file": "7_1_14_anual.xls", "base": "1957/1968/1984/1997", "price_type": "Precios constantes", "measure": "Nivel", "frequency": "Anual", "period": "2017", "year": 2017, "quarter": null, "classification": "Total economía", "component": "Producto interno bruto", "value": 392393.12, "unit": "Millones de bolívares a precios constantes", "status": "", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/7_1_14_anual.xls", "fetched_at": "2026-08-07T21:09:10Z"}</t>
+          <t>{"dataset_id": "bcv_pib_historico_anual", "title": "Producto interno bruto histórico anual", "table": "PIB histórico anual", "source_file": "7_1_14_anual.xls", "base": "1957/1968/1984/1997", "price_type": "Precios constantes", "measure": "Nivel", "frequency": "Anual", "period": "2017", "year": 2017, "quarter": null, "classification": "Total economía", "component": "Producto interno bruto", "value": 392393.12, "unit": "Millones de bolívares a precios constantes", "status": "", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/7_1_14_anual.xls", "fetched_at": "2026-08-08T20:57:48Z"}</t>
         </is>
       </c>
     </row>

--- a/assets/data/bcv/excel/ove_bcv_pib_historico_anual.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_pib_historico_anual.xlsx
@@ -736,7 +736,7 @@
       </c>
       <c r="S7" s="4" t="inlineStr">
         <is>
-          <t>2026-08-08T20:57:48Z</t>
+          <t>2026-08-09T21:02:02Z</t>
         </is>
       </c>
     </row>
@@ -821,7 +821,7 @@
       </c>
       <c r="S8" s="4" t="inlineStr">
         <is>
-          <t>2026-08-08T20:57:48Z</t>
+          <t>2026-08-09T21:02:02Z</t>
         </is>
       </c>
     </row>
@@ -906,7 +906,7 @@
       </c>
       <c r="S9" s="4" t="inlineStr">
         <is>
-          <t>2026-08-08T20:57:48Z</t>
+          <t>2026-08-09T21:02:02Z</t>
         </is>
       </c>
     </row>
@@ -991,7 +991,7 @@
       </c>
       <c r="S10" s="4" t="inlineStr">
         <is>
-          <t>2026-08-08T20:57:48Z</t>
+          <t>2026-08-09T21:02:02Z</t>
         </is>
       </c>
     </row>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="S11" s="4" t="inlineStr">
         <is>
-          <t>2026-08-08T20:57:48Z</t>
+          <t>2026-08-09T21:02:02Z</t>
         </is>
       </c>
     </row>
@@ -1161,7 +1161,7 @@
       </c>
       <c r="S12" s="4" t="inlineStr">
         <is>
-          <t>2026-08-08T20:57:48Z</t>
+          <t>2026-08-09T21:02:02Z</t>
         </is>
       </c>
     </row>
@@ -1246,7 +1246,7 @@
       </c>
       <c r="S13" s="4" t="inlineStr">
         <is>
-          <t>2026-08-08T20:57:48Z</t>
+          <t>2026-08-09T21:02:02Z</t>
         </is>
       </c>
     </row>
@@ -1331,7 +1331,7 @@
       </c>
       <c r="S14" s="4" t="inlineStr">
         <is>
-          <t>2026-08-08T20:57:48Z</t>
+          <t>2026-08-09T21:02:02Z</t>
         </is>
       </c>
     </row>
@@ -1416,7 +1416,7 @@
       </c>
       <c r="S15" s="4" t="inlineStr">
         <is>
-          <t>2026-08-08T20:57:48Z</t>
+          <t>2026-08-09T21:02:02Z</t>
         </is>
       </c>
     </row>
@@ -1501,7 +1501,7 @@
       </c>
       <c r="S16" s="4" t="inlineStr">
         <is>
-          <t>2026-08-08T20:57:48Z</t>
+          <t>2026-08-09T21:02:02Z</t>
         </is>
       </c>
     </row>
@@ -1586,7 +1586,7 @@
       </c>
       <c r="S17" s="4" t="inlineStr">
         <is>
-          <t>2026-08-08T20:57:48Z</t>
+          <t>2026-08-09T21:02:02Z</t>
         </is>
       </c>
     </row>
@@ -1671,7 +1671,7 @@
       </c>
       <c r="S18" s="4" t="inlineStr">
         <is>
-          <t>2026-08-08T20:57:48Z</t>
+          <t>2026-08-09T21:02:02Z</t>
         </is>
       </c>
     </row>
@@ -1756,7 +1756,7 @@
       </c>
       <c r="S19" s="4" t="inlineStr">
         <is>
-          <t>2026-08-08T20:57:48Z</t>
+          <t>2026-08-09T21:02:02Z</t>
         </is>
       </c>
     </row>
@@ -1841,7 +1841,7 @@
       </c>
       <c r="S20" s="4" t="inlineStr">
         <is>
-          <t>2026-08-08T20:57:48Z</t>
+          <t>2026-08-09T21:02:02Z</t>
         </is>
       </c>
     </row>
@@ -1926,7 +1926,7 @@
       </c>
       <c r="S21" s="4" t="inlineStr">
         <is>
-          <t>2026-08-08T20:57:48Z</t>
+          <t>2026-08-09T21:02:02Z</t>
         </is>
       </c>
     </row>
@@ -2011,7 +2011,7 @@
       </c>
       <c r="S22" s="4" t="inlineStr">
         <is>
-          <t>2026-08-08T20:57:48Z</t>
+          <t>2026-08-09T21:02:02Z</t>
         </is>
       </c>
     </row>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="S23" s="4" t="inlineStr">
         <is>
-          <t>2026-08-08T20:57:48Z</t>
+          <t>2026-08-09T21:02:02Z</t>
         </is>
       </c>
     </row>
@@ -2181,7 +2181,7 @@
       </c>
       <c r="S24" s="4" t="inlineStr">
         <is>
-          <t>2026-08-08T20:57:48Z</t>
+          <t>2026-08-09T21:02:02Z</t>
         </is>
       </c>
     </row>
@@ -2266,7 +2266,7 @@
       </c>
       <c r="S25" s="4" t="inlineStr">
         <is>
-          <t>2026-08-08T20:57:48Z</t>
+          <t>2026-08-09T21:02:02Z</t>
         </is>
       </c>
     </row>
@@ -2351,7 +2351,7 @@
       </c>
       <c r="S26" s="4" t="inlineStr">
         <is>
-          <t>2026-08-08T20:57:48Z</t>
+          <t>2026-08-09T21:02:02Z</t>
         </is>
       </c>
     </row>
@@ -2436,7 +2436,7 @@
       </c>
       <c r="S27" s="4" t="inlineStr">
         <is>
-          <t>2026-08-08T20:57:48Z</t>
+          <t>2026-08-09T21:02:02Z</t>
         </is>
       </c>
     </row>
@@ -2521,7 +2521,7 @@
       </c>
       <c r="S28" s="4" t="inlineStr">
         <is>
-          <t>2026-08-08T20:57:48Z</t>
+          <t>2026-08-09T21:02:02Z</t>
         </is>
       </c>
     </row>
@@ -2606,7 +2606,7 @@
       </c>
       <c r="S29" s="4" t="inlineStr">
         <is>
-          <t>2026-08-08T20:57:48Z</t>
+          <t>2026-08-09T21:02:02Z</t>
         </is>
       </c>
     </row>
@@ -2691,7 +2691,7 @@
       </c>
       <c r="S30" s="4" t="inlineStr">
         <is>
-          <t>2026-08-08T20:57:48Z</t>
+          <t>2026-08-09T21:02:02Z</t>
         </is>
       </c>
     </row>
@@ -2776,7 +2776,7 @@
       </c>
       <c r="S31" s="4" t="inlineStr">
         <is>
-          <t>2026-08-08T20:57:48Z</t>
+          <t>2026-08-09T21:02:02Z</t>
         </is>
       </c>
     </row>
@@ -2861,7 +2861,7 @@
       </c>
       <c r="S32" s="4" t="inlineStr">
         <is>
-          <t>2026-08-08T20:57:48Z</t>
+          <t>2026-08-09T21:02:02Z</t>
         </is>
       </c>
     </row>
@@ -2946,7 +2946,7 @@
       </c>
       <c r="S33" s="4" t="inlineStr">
         <is>
-          <t>2026-08-08T20:57:48Z</t>
+          <t>2026-08-09T21:02:02Z</t>
         </is>
       </c>
     </row>
@@ -3031,7 +3031,7 @@
       </c>
       <c r="S34" s="4" t="inlineStr">
         <is>
-          <t>2026-08-08T20:57:48Z</t>
+          <t>2026-08-09T21:02:02Z</t>
         </is>
       </c>
     </row>
@@ -3116,7 +3116,7 @@
       </c>
       <c r="S35" s="4" t="inlineStr">
         <is>
-          <t>2026-08-08T20:57:48Z</t>
+          <t>2026-08-09T21:02:02Z</t>
         </is>
       </c>
     </row>
@@ -3201,7 +3201,7 @@
       </c>
       <c r="S36" s="4" t="inlineStr">
         <is>
-          <t>2026-08-08T20:57:48Z</t>
+          <t>2026-08-09T21:02:02Z</t>
         </is>
       </c>
     </row>
@@ -3286,7 +3286,7 @@
       </c>
       <c r="S37" s="4" t="inlineStr">
         <is>
-          <t>2026-08-08T20:57:48Z</t>
+          <t>2026-08-09T21:02:02Z</t>
         </is>
       </c>
     </row>
@@ -3371,7 +3371,7 @@
       </c>
       <c r="S38" s="4" t="inlineStr">
         <is>
-          <t>2026-08-08T20:57:48Z</t>
+          <t>2026-08-09T21:02:02Z</t>
         </is>
       </c>
     </row>
@@ -3456,7 +3456,7 @@
       </c>
       <c r="S39" s="4" t="inlineStr">
         <is>
-          <t>2026-08-08T20:57:48Z</t>
+          <t>2026-08-09T21:02:02Z</t>
         </is>
       </c>
     </row>
@@ -3541,7 +3541,7 @@
       </c>
       <c r="S40" s="4" t="inlineStr">
         <is>
-          <t>2026-08-08T20:57:48Z</t>
+          <t>2026-08-09T21:02:02Z</t>
         </is>
       </c>
     </row>
@@ -3626,7 +3626,7 @@
       </c>
       <c r="S41" s="4" t="inlineStr">
         <is>
-          <t>2026-08-08T20:57:48Z</t>
+          <t>2026-08-09T21:02:02Z</t>
         </is>
       </c>
     </row>
@@ -3711,7 +3711,7 @@
       </c>
       <c r="S42" s="4" t="inlineStr">
         <is>
-          <t>2026-08-08T20:57:48Z</t>
+          <t>2026-08-09T21:02:02Z</t>
         </is>
       </c>
     </row>
@@ -3796,7 +3796,7 @@
       </c>
       <c r="S43" s="4" t="inlineStr">
         <is>
-          <t>2026-08-08T20:57:48Z</t>
+          <t>2026-08-09T21:02:02Z</t>
         </is>
       </c>
     </row>
@@ -3881,7 +3881,7 @@
       </c>
       <c r="S44" s="4" t="inlineStr">
         <is>
-          <t>2026-08-08T20:57:48Z</t>
+          <t>2026-08-09T21:02:02Z</t>
         </is>
       </c>
     </row>
@@ -3966,7 +3966,7 @@
       </c>
       <c r="S45" s="4" t="inlineStr">
         <is>
-          <t>2026-08-08T20:57:48Z</t>
+          <t>2026-08-09T21:02:02Z</t>
         </is>
       </c>
     </row>
@@ -4051,7 +4051,7 @@
       </c>
       <c r="S46" s="4" t="inlineStr">
         <is>
-          <t>2026-08-08T20:57:48Z</t>
+          <t>2026-08-09T21:02:02Z</t>
         </is>
       </c>
     </row>
@@ -4136,7 +4136,7 @@
       </c>
       <c r="S47" s="4" t="inlineStr">
         <is>
-          <t>2026-08-08T20:57:48Z</t>
+          <t>2026-08-09T21:02:02Z</t>
         </is>
       </c>
     </row>
@@ -4221,7 +4221,7 @@
       </c>
       <c r="S48" s="4" t="inlineStr">
         <is>
-          <t>2026-08-08T20:57:48Z</t>
+          <t>2026-08-09T21:02:02Z</t>
         </is>
       </c>
     </row>
@@ -4306,7 +4306,7 @@
       </c>
       <c r="S49" s="4" t="inlineStr">
         <is>
-          <t>2026-08-08T20:57:48Z</t>
+          <t>2026-08-09T21:02:02Z</t>
         </is>
       </c>
     </row>
@@ -4391,7 +4391,7 @@
       </c>
       <c r="S50" s="4" t="inlineStr">
         <is>
-          <t>2026-08-08T20:57:48Z</t>
+          <t>2026-08-09T21:02:02Z</t>
         </is>
       </c>
     </row>
@@ -4476,7 +4476,7 @@
       </c>
       <c r="S51" s="4" t="inlineStr">
         <is>
-          <t>2026-08-08T20:57:48Z</t>
+          <t>2026-08-09T21:02:02Z</t>
         </is>
       </c>
     </row>
@@ -4561,7 +4561,7 @@
       </c>
       <c r="S52" s="4" t="inlineStr">
         <is>
-          <t>2026-08-08T20:57:48Z</t>
+          <t>2026-08-09T21:02:02Z</t>
         </is>
       </c>
     </row>
@@ -4646,7 +4646,7 @@
       </c>
       <c r="S53" s="4" t="inlineStr">
         <is>
-          <t>2026-08-08T20:57:48Z</t>
+          <t>2026-08-09T21:02:02Z</t>
         </is>
       </c>
     </row>
@@ -4731,7 +4731,7 @@
       </c>
       <c r="S54" s="4" t="inlineStr">
         <is>
-          <t>2026-08-08T20:57:48Z</t>
+          <t>2026-08-09T21:02:02Z</t>
         </is>
       </c>
     </row>
@@ -4816,7 +4816,7 @@
       </c>
       <c r="S55" s="4" t="inlineStr">
         <is>
-          <t>2026-08-08T20:57:48Z</t>
+          <t>2026-08-09T21:02:02Z</t>
         </is>
       </c>
     </row>
@@ -4901,7 +4901,7 @@
       </c>
       <c r="S56" s="4" t="inlineStr">
         <is>
-          <t>2026-08-08T20:57:48Z</t>
+          <t>2026-08-09T21:02:02Z</t>
         </is>
       </c>
     </row>
@@ -4986,7 +4986,7 @@
       </c>
       <c r="S57" s="4" t="inlineStr">
         <is>
-          <t>2026-08-08T20:57:48Z</t>
+          <t>2026-08-09T21:02:02Z</t>
         </is>
       </c>
     </row>
@@ -5071,7 +5071,7 @@
       </c>
       <c r="S58" s="4" t="inlineStr">
         <is>
-          <t>2026-08-08T20:57:48Z</t>
+          <t>2026-08-09T21:02:02Z</t>
         </is>
       </c>
     </row>
@@ -5156,7 +5156,7 @@
       </c>
       <c r="S59" s="4" t="inlineStr">
         <is>
-          <t>2026-08-08T20:57:48Z</t>
+          <t>2026-08-09T21:02:02Z</t>
         </is>
       </c>
     </row>
@@ -5241,7 +5241,7 @@
       </c>
       <c r="S60" s="4" t="inlineStr">
         <is>
-          <t>2026-08-08T20:57:48Z</t>
+          <t>2026-08-09T21:02:02Z</t>
         </is>
       </c>
     </row>
@@ -5326,7 +5326,7 @@
       </c>
       <c r="S61" s="4" t="inlineStr">
         <is>
-          <t>2026-08-08T20:57:48Z</t>
+          <t>2026-08-09T21:02:02Z</t>
         </is>
       </c>
     </row>
@@ -5411,7 +5411,7 @@
       </c>
       <c r="S62" s="4" t="inlineStr">
         <is>
-          <t>2026-08-08T20:57:48Z</t>
+          <t>2026-08-09T21:02:02Z</t>
         </is>
       </c>
     </row>
@@ -5496,7 +5496,7 @@
       </c>
       <c r="S63" s="4" t="inlineStr">
         <is>
-          <t>2026-08-08T20:57:48Z</t>
+          <t>2026-08-09T21:02:02Z</t>
         </is>
       </c>
     </row>
@@ -5581,7 +5581,7 @@
       </c>
       <c r="S64" s="4" t="inlineStr">
         <is>
-          <t>2026-08-08T20:57:48Z</t>
+          <t>2026-08-09T21:02:02Z</t>
         </is>
       </c>
     </row>
@@ -5666,7 +5666,7 @@
       </c>
       <c r="S65" s="4" t="inlineStr">
         <is>
-          <t>2026-08-08T20:57:48Z</t>
+          <t>2026-08-09T21:02:02Z</t>
         </is>
       </c>
     </row>
@@ -5751,7 +5751,7 @@
       </c>
       <c r="S66" s="4" t="inlineStr">
         <is>
-          <t>2026-08-08T20:57:48Z</t>
+          <t>2026-08-09T21:02:02Z</t>
         </is>
       </c>
     </row>
@@ -5836,7 +5836,7 @@
       </c>
       <c r="S67" s="4" t="inlineStr">
         <is>
-          <t>2026-08-08T20:57:48Z</t>
+          <t>2026-08-09T21:02:02Z</t>
         </is>
       </c>
     </row>
@@ -5921,7 +5921,7 @@
       </c>
       <c r="S68" s="4" t="inlineStr">
         <is>
-          <t>2026-08-08T20:57:48Z</t>
+          <t>2026-08-09T21:02:02Z</t>
         </is>
       </c>
     </row>
@@ -6006,7 +6006,7 @@
       </c>
       <c r="S69" s="4" t="inlineStr">
         <is>
-          <t>2026-08-08T20:57:48Z</t>
+          <t>2026-08-09T21:02:02Z</t>
         </is>
       </c>
     </row>
@@ -6091,7 +6091,7 @@
       </c>
       <c r="S70" s="4" t="inlineStr">
         <is>
-          <t>2026-08-08T20:57:48Z</t>
+          <t>2026-08-09T21:02:02Z</t>
         </is>
       </c>
     </row>
@@ -6176,7 +6176,7 @@
       </c>
       <c r="S71" s="4" t="inlineStr">
         <is>
-          <t>2026-08-08T20:57:48Z</t>
+          <t>2026-08-09T21:02:02Z</t>
         </is>
       </c>
     </row>
@@ -6261,7 +6261,7 @@
       </c>
       <c r="S72" s="4" t="inlineStr">
         <is>
-          <t>2026-08-08T20:57:48Z</t>
+          <t>2026-08-09T21:02:02Z</t>
         </is>
       </c>
     </row>
@@ -6346,7 +6346,7 @@
       </c>
       <c r="S73" s="4" t="inlineStr">
         <is>
-          <t>2026-08-08T20:57:48Z</t>
+          <t>2026-08-09T21:02:02Z</t>
         </is>
       </c>
     </row>
@@ -6431,7 +6431,7 @@
       </c>
       <c r="S74" s="4" t="inlineStr">
         <is>
-          <t>2026-08-08T20:57:48Z</t>
+          <t>2026-08-09T21:02:02Z</t>
         </is>
       </c>
     </row>
@@ -6516,7 +6516,7 @@
       </c>
       <c r="S75" s="4" t="inlineStr">
         <is>
-          <t>2026-08-08T20:57:48Z</t>
+          <t>2026-08-09T21:02:02Z</t>
         </is>
       </c>
     </row>
@@ -6601,7 +6601,7 @@
       </c>
       <c r="S76" s="4" t="inlineStr">
         <is>
-          <t>2026-08-08T20:57:48Z</t>
+          <t>2026-08-09T21:02:02Z</t>
         </is>
       </c>
     </row>
@@ -6686,7 +6686,7 @@
       </c>
       <c r="S77" s="4" t="inlineStr">
         <is>
-          <t>2026-08-08T20:57:48Z</t>
+          <t>2026-08-09T21:02:02Z</t>
         </is>
       </c>
     </row>
@@ -6771,7 +6771,7 @@
       </c>
       <c r="S78" s="4" t="inlineStr">
         <is>
-          <t>2026-08-08T20:57:48Z</t>
+          <t>2026-08-09T21:02:02Z</t>
         </is>
       </c>
     </row>
@@ -6856,7 +6856,7 @@
       </c>
       <c r="S79" s="4" t="inlineStr">
         <is>
-          <t>2026-08-08T20:57:48Z</t>
+          <t>2026-08-09T21:02:02Z</t>
         </is>
       </c>
     </row>
@@ -6941,7 +6941,7 @@
       </c>
       <c r="S80" s="4" t="inlineStr">
         <is>
-          <t>2026-08-08T20:57:48Z</t>
+          <t>2026-08-09T21:02:02Z</t>
         </is>
       </c>
     </row>
@@ -7026,7 +7026,7 @@
       </c>
       <c r="S81" s="4" t="inlineStr">
         <is>
-          <t>2026-08-08T20:57:48Z</t>
+          <t>2026-08-09T21:02:02Z</t>
         </is>
       </c>
     </row>
@@ -7111,7 +7111,7 @@
       </c>
       <c r="S82" s="4" t="inlineStr">
         <is>
-          <t>2026-08-08T20:57:48Z</t>
+          <t>2026-08-09T21:02:02Z</t>
         </is>
       </c>
     </row>
@@ -7196,7 +7196,7 @@
       </c>
       <c r="S83" s="4" t="inlineStr">
         <is>
-          <t>2026-08-08T20:57:48Z</t>
+          <t>2026-08-09T21:02:02Z</t>
         </is>
       </c>
     </row>
@@ -7281,7 +7281,7 @@
       </c>
       <c r="S84" s="4" t="inlineStr">
         <is>
-          <t>2026-08-08T20:57:48Z</t>
+          <t>2026-08-09T21:02:02Z</t>
         </is>
       </c>
     </row>
@@ -7366,7 +7366,7 @@
       </c>
       <c r="S85" s="4" t="inlineStr">
         <is>
-          <t>2026-08-08T20:57:48Z</t>
+          <t>2026-08-09T21:02:02Z</t>
         </is>
       </c>
     </row>
@@ -7451,7 +7451,7 @@
       </c>
       <c r="S86" s="4" t="inlineStr">
         <is>
-          <t>2026-08-08T20:57:48Z</t>
+          <t>2026-08-09T21:02:02Z</t>
         </is>
       </c>
     </row>
@@ -7536,7 +7536,7 @@
       </c>
       <c r="S87" s="4" t="inlineStr">
         <is>
-          <t>2026-08-08T20:57:48Z</t>
+          <t>2026-08-09T21:02:02Z</t>
         </is>
       </c>
     </row>
@@ -7621,7 +7621,7 @@
       </c>
       <c r="S88" s="4" t="inlineStr">
         <is>
-          <t>2026-08-08T20:57:48Z</t>
+          <t>2026-08-09T21:02:02Z</t>
         </is>
       </c>
     </row>
@@ -7706,7 +7706,7 @@
       </c>
       <c r="S89" s="4" t="inlineStr">
         <is>
-          <t>2026-08-08T20:57:48Z</t>
+          <t>2026-08-09T21:02:02Z</t>
         </is>
       </c>
     </row>
@@ -7791,7 +7791,7 @@
       </c>
       <c r="S90" s="4" t="inlineStr">
         <is>
-          <t>2026-08-08T20:57:48Z</t>
+          <t>2026-08-09T21:02:02Z</t>
         </is>
       </c>
     </row>
@@ -7876,7 +7876,7 @@
       </c>
       <c r="S91" s="4" t="inlineStr">
         <is>
-          <t>2026-08-08T20:57:48Z</t>
+          <t>2026-08-09T21:02:02Z</t>
         </is>
       </c>
     </row>
@@ -7961,7 +7961,7 @@
       </c>
       <c r="S92" s="4" t="inlineStr">
         <is>
-          <t>2026-08-08T20:57:48Z</t>
+          <t>2026-08-09T21:02:02Z</t>
         </is>
       </c>
     </row>
@@ -8046,7 +8046,7 @@
       </c>
       <c r="S93" s="4" t="inlineStr">
         <is>
-          <t>2026-08-08T20:57:48Z</t>
+          <t>2026-08-09T21:02:02Z</t>
         </is>
       </c>
     </row>
@@ -8131,7 +8131,7 @@
       </c>
       <c r="S94" s="4" t="inlineStr">
         <is>
-          <t>2026-08-08T20:57:48Z</t>
+          <t>2026-08-09T21:02:02Z</t>
         </is>
       </c>
     </row>
@@ -8216,7 +8216,7 @@
       </c>
       <c r="S95" s="4" t="inlineStr">
         <is>
-          <t>2026-08-08T20:57:48Z</t>
+          <t>2026-08-09T21:02:02Z</t>
         </is>
       </c>
     </row>
@@ -8301,7 +8301,7 @@
       </c>
       <c r="S96" s="4" t="inlineStr">
         <is>
-          <t>2026-08-08T20:57:48Z</t>
+          <t>2026-08-09T21:02:02Z</t>
         </is>
       </c>
     </row>
@@ -8386,7 +8386,7 @@
       </c>
       <c r="S97" s="4" t="inlineStr">
         <is>
-          <t>2026-08-08T20:57:48Z</t>
+          <t>2026-08-09T21:02:02Z</t>
         </is>
       </c>
     </row>
@@ -8471,7 +8471,7 @@
       </c>
       <c r="S98" s="4" t="inlineStr">
         <is>
-          <t>2026-08-08T20:57:48Z</t>
+          <t>2026-08-09T21:02:02Z</t>
         </is>
       </c>
     </row>
@@ -8556,7 +8556,7 @@
       </c>
       <c r="S99" s="4" t="inlineStr">
         <is>
-          <t>2026-08-08T20:57:48Z</t>
+          <t>2026-08-09T21:02:02Z</t>
         </is>
       </c>
     </row>
@@ -8641,7 +8641,7 @@
       </c>
       <c r="S100" s="4" t="inlineStr">
         <is>
-          <t>2026-08-08T20:57:48Z</t>
+          <t>2026-08-09T21:02:02Z</t>
         </is>
       </c>
     </row>
@@ -8726,7 +8726,7 @@
       </c>
       <c r="S101" s="4" t="inlineStr">
         <is>
-          <t>2026-08-08T20:57:48Z</t>
+          <t>2026-08-09T21:02:02Z</t>
         </is>
       </c>
     </row>
@@ -8811,7 +8811,7 @@
       </c>
       <c r="S102" s="4" t="inlineStr">
         <is>
-          <t>2026-08-08T20:57:48Z</t>
+          <t>2026-08-09T21:02:02Z</t>
         </is>
       </c>
     </row>
@@ -8896,7 +8896,7 @@
       </c>
       <c r="S103" s="4" t="inlineStr">
         <is>
-          <t>2026-08-08T20:57:48Z</t>
+          <t>2026-08-09T21:02:02Z</t>
         </is>
       </c>
     </row>
@@ -8981,7 +8981,7 @@
       </c>
       <c r="S104" s="4" t="inlineStr">
         <is>
-          <t>2026-08-08T20:57:48Z</t>
+          <t>2026-08-09T21:02:02Z</t>
         </is>
       </c>
     </row>
@@ -9066,7 +9066,7 @@
       </c>
       <c r="S105" s="4" t="inlineStr">
         <is>
-          <t>2026-08-08T20:57:48Z</t>
+          <t>2026-08-09T21:02:02Z</t>
         </is>
       </c>
     </row>
@@ -9151,7 +9151,7 @@
       </c>
       <c r="S106" s="4" t="inlineStr">
         <is>
-          <t>2026-08-08T20:57:48Z</t>
+          <t>2026-08-09T21:02:02Z</t>
         </is>
       </c>
     </row>
@@ -9236,7 +9236,7 @@
       </c>
       <c r="S107" s="4" t="inlineStr">
         <is>
-          <t>2026-08-08T20:57:48Z</t>
+          <t>2026-08-09T21:02:02Z</t>
         </is>
       </c>
     </row>
@@ -9321,7 +9321,7 @@
       </c>
       <c r="S108" s="4" t="inlineStr">
         <is>
-          <t>2026-08-08T20:57:48Z</t>
+          <t>2026-08-09T21:02:02Z</t>
         </is>
       </c>
     </row>
@@ -9406,7 +9406,7 @@
       </c>
       <c r="S109" s="4" t="inlineStr">
         <is>
-          <t>2026-08-08T20:57:48Z</t>
+          <t>2026-08-09T21:02:02Z</t>
         </is>
       </c>
     </row>
@@ -9491,7 +9491,7 @@
       </c>
       <c r="S110" s="4" t="inlineStr">
         <is>
-          <t>2026-08-08T20:57:48Z</t>
+          <t>2026-08-09T21:02:02Z</t>
         </is>
       </c>
     </row>
@@ -9576,7 +9576,7 @@
       </c>
       <c r="S111" s="4" t="inlineStr">
         <is>
-          <t>2026-08-08T20:57:48Z</t>
+          <t>2026-08-09T21:02:02Z</t>
         </is>
       </c>
     </row>
@@ -9661,7 +9661,7 @@
       </c>
       <c r="S112" s="4" t="inlineStr">
         <is>
-          <t>2026-08-08T20:57:48Z</t>
+          <t>2026-08-09T21:02:02Z</t>
         </is>
       </c>
     </row>
@@ -9746,7 +9746,7 @@
       </c>
       <c r="S113" s="4" t="inlineStr">
         <is>
-          <t>2026-08-08T20:57:48Z</t>
+          <t>2026-08-09T21:02:02Z</t>
         </is>
       </c>
     </row>
@@ -9831,7 +9831,7 @@
       </c>
       <c r="S114" s="4" t="inlineStr">
         <is>
-          <t>2026-08-08T20:57:48Z</t>
+          <t>2026-08-09T21:02:02Z</t>
         </is>
       </c>
     </row>
@@ -9916,7 +9916,7 @@
       </c>
       <c r="S115" s="4" t="inlineStr">
         <is>
-          <t>2026-08-08T20:57:48Z</t>
+          <t>2026-08-09T21:02:02Z</t>
         </is>
       </c>
     </row>
@@ -10001,7 +10001,7 @@
       </c>
       <c r="S116" s="4" t="inlineStr">
         <is>
-          <t>2026-08-08T20:57:48Z</t>
+          <t>2026-08-09T21:02:02Z</t>
         </is>
       </c>
     </row>
@@ -10086,7 +10086,7 @@
       </c>
       <c r="S117" s="4" t="inlineStr">
         <is>
-          <t>2026-08-08T20:57:48Z</t>
+          <t>2026-08-09T21:02:02Z</t>
         </is>
       </c>
     </row>
@@ -10171,7 +10171,7 @@
       </c>
       <c r="S118" s="4" t="inlineStr">
         <is>
-          <t>2026-08-08T20:57:48Z</t>
+          <t>2026-08-09T21:02:02Z</t>
         </is>
       </c>
     </row>
@@ -10256,7 +10256,7 @@
       </c>
       <c r="S119" s="4" t="inlineStr">
         <is>
-          <t>2026-08-08T20:57:48Z</t>
+          <t>2026-08-09T21:02:02Z</t>
         </is>
       </c>
     </row>
@@ -10341,7 +10341,7 @@
       </c>
       <c r="S120" s="4" t="inlineStr">
         <is>
-          <t>2026-08-08T20:57:48Z</t>
+          <t>2026-08-09T21:02:02Z</t>
         </is>
       </c>
     </row>
@@ -10426,7 +10426,7 @@
       </c>
       <c r="S121" s="4" t="inlineStr">
         <is>
-          <t>2026-08-08T20:57:48Z</t>
+          <t>2026-08-09T21:02:02Z</t>
         </is>
       </c>
     </row>
@@ -10511,7 +10511,7 @@
       </c>
       <c r="S122" s="4" t="inlineStr">
         <is>
-          <t>2026-08-08T20:57:48Z</t>
+          <t>2026-08-09T21:02:02Z</t>
         </is>
       </c>
     </row>
@@ -10596,7 +10596,7 @@
       </c>
       <c r="S123" s="4" t="inlineStr">
         <is>
-          <t>2026-08-08T20:57:48Z</t>
+          <t>2026-08-09T21:02:02Z</t>
         </is>
       </c>
     </row>
@@ -10681,7 +10681,7 @@
       </c>
       <c r="S124" s="4" t="inlineStr">
         <is>
-          <t>2026-08-08T20:57:48Z</t>
+          <t>2026-08-09T21:02:02Z</t>
         </is>
       </c>
     </row>
@@ -10766,7 +10766,7 @@
       </c>
       <c r="S125" s="4" t="inlineStr">
         <is>
-          <t>2026-08-08T20:57:48Z</t>
+          <t>2026-08-09T21:02:02Z</t>
         </is>
       </c>
     </row>
@@ -10851,7 +10851,7 @@
       </c>
       <c r="S126" s="4" t="inlineStr">
         <is>
-          <t>2026-08-08T20:57:48Z</t>
+          <t>2026-08-09T21:02:02Z</t>
         </is>
       </c>
     </row>
@@ -10936,7 +10936,7 @@
       </c>
       <c r="S127" s="4" t="inlineStr">
         <is>
-          <t>2026-08-08T20:57:48Z</t>
+          <t>2026-08-09T21:02:02Z</t>
         </is>
       </c>
     </row>
@@ -11021,7 +11021,7 @@
       </c>
       <c r="S128" s="4" t="inlineStr">
         <is>
-          <t>2026-08-08T20:57:48Z</t>
+          <t>2026-08-09T21:02:02Z</t>
         </is>
       </c>
     </row>
@@ -11106,7 +11106,7 @@
       </c>
       <c r="S129" s="4" t="inlineStr">
         <is>
-          <t>2026-08-08T20:57:48Z</t>
+          <t>2026-08-09T21:02:02Z</t>
         </is>
       </c>
     </row>
@@ -11191,7 +11191,7 @@
       </c>
       <c r="S130" s="4" t="inlineStr">
         <is>
-          <t>2026-08-08T20:57:48Z</t>
+          <t>2026-08-09T21:02:02Z</t>
         </is>
       </c>
     </row>
@@ -11276,7 +11276,7 @@
       </c>
       <c r="S131" s="4" t="inlineStr">
         <is>
-          <t>2026-08-08T20:57:48Z</t>
+          <t>2026-08-09T21:02:02Z</t>
         </is>
       </c>
     </row>
@@ -11361,7 +11361,7 @@
       </c>
       <c r="S132" s="4" t="inlineStr">
         <is>
-          <t>2026-08-08T20:57:48Z</t>
+          <t>2026-08-09T21:02:02Z</t>
         </is>
       </c>
     </row>
@@ -11446,7 +11446,7 @@
       </c>
       <c r="S133" s="4" t="inlineStr">
         <is>
-          <t>2026-08-08T20:57:48Z</t>
+          <t>2026-08-09T21:02:02Z</t>
         </is>
       </c>
     </row>
@@ -11531,7 +11531,7 @@
       </c>
       <c r="S134" s="4" t="inlineStr">
         <is>
-          <t>2026-08-08T20:57:48Z</t>
+          <t>2026-08-09T21:02:02Z</t>
         </is>
       </c>
     </row>
@@ -11616,7 +11616,7 @@
       </c>
       <c r="S135" s="4" t="inlineStr">
         <is>
-          <t>2026-08-08T20:57:48Z</t>
+          <t>2026-08-09T21:02:02Z</t>
         </is>
       </c>
     </row>
@@ -11701,7 +11701,7 @@
       </c>
       <c r="S136" s="4" t="inlineStr">
         <is>
-          <t>2026-08-08T20:57:48Z</t>
+          <t>2026-08-09T21:02:02Z</t>
         </is>
       </c>
     </row>
@@ -11786,7 +11786,7 @@
       </c>
       <c r="S137" s="4" t="inlineStr">
         <is>
-          <t>2026-08-08T20:57:48Z</t>
+          <t>2026-08-09T21:02:02Z</t>
         </is>
       </c>
     </row>
@@ -11871,7 +11871,7 @@
       </c>
       <c r="S138" s="4" t="inlineStr">
         <is>
-          <t>2026-08-08T20:57:48Z</t>
+          <t>2026-08-09T21:02:02Z</t>
         </is>
       </c>
     </row>
@@ -11956,7 +11956,7 @@
       </c>
       <c r="S139" s="4" t="inlineStr">
         <is>
-          <t>2026-08-08T20:57:48Z</t>
+          <t>2026-08-09T21:02:02Z</t>
         </is>
       </c>
     </row>
@@ -12041,7 +12041,7 @@
       </c>
       <c r="S140" s="4" t="inlineStr">
         <is>
-          <t>2026-08-08T20:57:48Z</t>
+          <t>2026-08-09T21:02:02Z</t>
         </is>
       </c>
     </row>
@@ -12126,7 +12126,7 @@
       </c>
       <c r="S141" s="4" t="inlineStr">
         <is>
-          <t>2026-08-08T20:57:48Z</t>
+          <t>2026-08-09T21:02:02Z</t>
         </is>
       </c>
     </row>
@@ -12258,7 +12258,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>2026-08-08T20:57:48Z</t>
+          <t>2026-08-09T21:02:02Z</t>
         </is>
       </c>
     </row>
@@ -12338,7 +12338,7 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>{"dataset_id": "bcv_pib_historico_anual", "title": "Producto interno bruto histórico anual", "table": "PIB histórico anual", "source_file": "7_1_14_anual.xls", "base": "1957/1968/1984/1997", "price_type": "Precios constantes", "measure": "Nivel", "frequency": "Anual", "period": "2017", "year": 2017, "quarter": null, "classification": "Total economía", "component": "Producto interno bruto", "value": 392393.12, "unit": "Millones de bolívares a precios constantes", "status": "", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/7_1_14_anual.xls", "fetched_at": "2026-08-08T20:57:48Z"}</t>
+          <t>{"dataset_id": "bcv_pib_historico_anual", "title": "Producto interno bruto histórico anual", "table": "PIB histórico anual", "source_file": "7_1_14_anual.xls", "base": "1957/1968/1984/1997", "price_type": "Precios constantes", "measure": "Nivel", "frequency": "Anual", "period": "2017", "year": 2017, "quarter": null, "classification": "Total economía", "component": "Producto interno bruto", "value": 392393.12, "unit": "Millones de bolívares a precios constantes", "status": "", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/7_1_14_anual.xls", "fetched_at": "2026-08-09T21:02:02Z"}</t>
         </is>
       </c>
     </row>

--- a/assets/data/bcv/excel/ove_bcv_pib_historico_anual.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_pib_historico_anual.xlsx
@@ -736,7 +736,7 @@
       </c>
       <c r="S7" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -821,7 +821,7 @@
       </c>
       <c r="S8" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -906,7 +906,7 @@
       </c>
       <c r="S9" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -991,7 +991,7 @@
       </c>
       <c r="S10" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="S11" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -1161,7 +1161,7 @@
       </c>
       <c r="S12" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -1246,7 +1246,7 @@
       </c>
       <c r="S13" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -1331,7 +1331,7 @@
       </c>
       <c r="S14" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -1416,7 +1416,7 @@
       </c>
       <c r="S15" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -1501,7 +1501,7 @@
       </c>
       <c r="S16" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -1586,7 +1586,7 @@
       </c>
       <c r="S17" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -1671,7 +1671,7 @@
       </c>
       <c r="S18" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -1756,7 +1756,7 @@
       </c>
       <c r="S19" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -1841,7 +1841,7 @@
       </c>
       <c r="S20" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -1926,7 +1926,7 @@
       </c>
       <c r="S21" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -2011,7 +2011,7 @@
       </c>
       <c r="S22" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="S23" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -2181,7 +2181,7 @@
       </c>
       <c r="S24" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -2266,7 +2266,7 @@
       </c>
       <c r="S25" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -2351,7 +2351,7 @@
       </c>
       <c r="S26" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -2436,7 +2436,7 @@
       </c>
       <c r="S27" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -2521,7 +2521,7 @@
       </c>
       <c r="S28" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -2606,7 +2606,7 @@
       </c>
       <c r="S29" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -2691,7 +2691,7 @@
       </c>
       <c r="S30" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -2776,7 +2776,7 @@
       </c>
       <c r="S31" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -2861,7 +2861,7 @@
       </c>
       <c r="S32" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -2946,7 +2946,7 @@
       </c>
       <c r="S33" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -3031,7 +3031,7 @@
       </c>
       <c r="S34" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -3116,7 +3116,7 @@
       </c>
       <c r="S35" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -3201,7 +3201,7 @@
       </c>
       <c r="S36" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -3286,7 +3286,7 @@
       </c>
       <c r="S37" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -3371,7 +3371,7 @@
       </c>
       <c r="S38" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -3456,7 +3456,7 @@
       </c>
       <c r="S39" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -3541,7 +3541,7 @@
       </c>
       <c r="S40" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -3626,7 +3626,7 @@
       </c>
       <c r="S41" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -3711,7 +3711,7 @@
       </c>
       <c r="S42" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -3796,7 +3796,7 @@
       </c>
       <c r="S43" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -3881,7 +3881,7 @@
       </c>
       <c r="S44" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -3966,7 +3966,7 @@
       </c>
       <c r="S45" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -4051,7 +4051,7 @@
       </c>
       <c r="S46" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -4136,7 +4136,7 @@
       </c>
       <c r="S47" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -4221,7 +4221,7 @@
       </c>
       <c r="S48" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -4306,7 +4306,7 @@
       </c>
       <c r="S49" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -4391,7 +4391,7 @@
       </c>
       <c r="S50" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -4476,7 +4476,7 @@
       </c>
       <c r="S51" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -4561,7 +4561,7 @@
       </c>
       <c r="S52" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -4646,7 +4646,7 @@
       </c>
       <c r="S53" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -4731,7 +4731,7 @@
       </c>
       <c r="S54" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -4816,7 +4816,7 @@
       </c>
       <c r="S55" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -4901,7 +4901,7 @@
       </c>
       <c r="S56" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -4986,7 +4986,7 @@
       </c>
       <c r="S57" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -5071,7 +5071,7 @@
       </c>
       <c r="S58" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -5156,7 +5156,7 @@
       </c>
       <c r="S59" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -5241,7 +5241,7 @@
       </c>
       <c r="S60" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -5326,7 +5326,7 @@
       </c>
       <c r="S61" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -5411,7 +5411,7 @@
       </c>
       <c r="S62" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -5496,7 +5496,7 @@
       </c>
       <c r="S63" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -5581,7 +5581,7 @@
       </c>
       <c r="S64" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -5666,7 +5666,7 @@
       </c>
       <c r="S65" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -5751,7 +5751,7 @@
       </c>
       <c r="S66" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -5836,7 +5836,7 @@
       </c>
       <c r="S67" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -5921,7 +5921,7 @@
       </c>
       <c r="S68" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -6006,7 +6006,7 @@
       </c>
       <c r="S69" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -6091,7 +6091,7 @@
       </c>
       <c r="S70" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -6176,7 +6176,7 @@
       </c>
       <c r="S71" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -6261,7 +6261,7 @@
       </c>
       <c r="S72" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -6346,7 +6346,7 @@
       </c>
       <c r="S73" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -6431,7 +6431,7 @@
       </c>
       <c r="S74" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -6516,7 +6516,7 @@
       </c>
       <c r="S75" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -6601,7 +6601,7 @@
       </c>
       <c r="S76" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -6686,7 +6686,7 @@
       </c>
       <c r="S77" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -6771,7 +6771,7 @@
       </c>
       <c r="S78" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -6856,7 +6856,7 @@
       </c>
       <c r="S79" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -6941,7 +6941,7 @@
       </c>
       <c r="S80" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -7026,7 +7026,7 @@
       </c>
       <c r="S81" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -7111,7 +7111,7 @@
       </c>
       <c r="S82" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -7196,7 +7196,7 @@
       </c>
       <c r="S83" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -7281,7 +7281,7 @@
       </c>
       <c r="S84" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -7366,7 +7366,7 @@
       </c>
       <c r="S85" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -7451,7 +7451,7 @@
       </c>
       <c r="S86" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -7536,7 +7536,7 @@
       </c>
       <c r="S87" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -7621,7 +7621,7 @@
       </c>
       <c r="S88" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -7706,7 +7706,7 @@
       </c>
       <c r="S89" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -7791,7 +7791,7 @@
       </c>
       <c r="S90" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -7876,7 +7876,7 @@
       </c>
       <c r="S91" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -7961,7 +7961,7 @@
       </c>
       <c r="S92" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -8046,7 +8046,7 @@
       </c>
       <c r="S93" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -8131,7 +8131,7 @@
       </c>
       <c r="S94" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -8216,7 +8216,7 @@
       </c>
       <c r="S95" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -8301,7 +8301,7 @@
       </c>
       <c r="S96" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -8386,7 +8386,7 @@
       </c>
       <c r="S97" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -8471,7 +8471,7 @@
       </c>
       <c r="S98" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -8556,7 +8556,7 @@
       </c>
       <c r="S99" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -8641,7 +8641,7 @@
       </c>
       <c r="S100" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -8726,7 +8726,7 @@
       </c>
       <c r="S101" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -8811,7 +8811,7 @@
       </c>
       <c r="S102" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -8896,7 +8896,7 @@
       </c>
       <c r="S103" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -8981,7 +8981,7 @@
       </c>
       <c r="S104" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -9066,7 +9066,7 @@
       </c>
       <c r="S105" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -9151,7 +9151,7 @@
       </c>
       <c r="S106" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -9236,7 +9236,7 @@
       </c>
       <c r="S107" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -9321,7 +9321,7 @@
       </c>
       <c r="S108" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -9406,7 +9406,7 @@
       </c>
       <c r="S109" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -9491,7 +9491,7 @@
       </c>
       <c r="S110" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -9576,7 +9576,7 @@
       </c>
       <c r="S111" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -9661,7 +9661,7 @@
       </c>
       <c r="S112" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -9746,7 +9746,7 @@
       </c>
       <c r="S113" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -9831,7 +9831,7 @@
       </c>
       <c r="S114" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -9916,7 +9916,7 @@
       </c>
       <c r="S115" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -10001,7 +10001,7 @@
       </c>
       <c r="S116" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -10086,7 +10086,7 @@
       </c>
       <c r="S117" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -10171,7 +10171,7 @@
       </c>
       <c r="S118" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -10256,7 +10256,7 @@
       </c>
       <c r="S119" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -10341,7 +10341,7 @@
       </c>
       <c r="S120" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -10426,7 +10426,7 @@
       </c>
       <c r="S121" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -10511,7 +10511,7 @@
       </c>
       <c r="S122" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -10596,7 +10596,7 @@
       </c>
       <c r="S123" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -10681,7 +10681,7 @@
       </c>
       <c r="S124" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -10766,7 +10766,7 @@
       </c>
       <c r="S125" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -10851,7 +10851,7 @@
       </c>
       <c r="S126" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -10936,7 +10936,7 @@
       </c>
       <c r="S127" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -11021,7 +11021,7 @@
       </c>
       <c r="S128" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -11106,7 +11106,7 @@
       </c>
       <c r="S129" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -11191,7 +11191,7 @@
       </c>
       <c r="S130" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -11276,7 +11276,7 @@
       </c>
       <c r="S131" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -11361,7 +11361,7 @@
       </c>
       <c r="S132" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -11446,7 +11446,7 @@
       </c>
       <c r="S133" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -11531,7 +11531,7 @@
       </c>
       <c r="S134" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -11616,7 +11616,7 @@
       </c>
       <c r="S135" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -11701,7 +11701,7 @@
       </c>
       <c r="S136" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -11786,7 +11786,7 @@
       </c>
       <c r="S137" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -11871,7 +11871,7 @@
       </c>
       <c r="S138" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -11956,7 +11956,7 @@
       </c>
       <c r="S139" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -12041,7 +12041,7 @@
       </c>
       <c r="S140" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -12126,7 +12126,7 @@
       </c>
       <c r="S141" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -12258,7 +12258,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -12338,7 +12338,7 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>{"dataset_id": "bcv_pib_historico_anual", "title": "Producto interno bruto histórico anual", "table": "PIB histórico anual", "source_file": "7_1_14_anual.xls", "base": "1957/1968/1984/1997", "price_type": "Precios constantes", "measure": "Nivel", "frequency": "Anual", "period": "2017", "year": 2017, "quarter": null, "classification": "Total economía", "component": "Producto interno bruto", "value": 392393.12, "unit": "Millones de bolívares a precios constantes", "status": "", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/7_1_14_anual.xls", "fetched_at": "2026-08-09T21:02:02Z"}</t>
+          <t>{"dataset_id": "bcv_pib_historico_anual", "title": "Producto interno bruto histórico anual", "table": "PIB histórico anual", "source_file": "7_1_14_anual.xls", "base": "1957/1968/1984/1997", "price_type": "Precios constantes", "measure": "Nivel", "frequency": "Anual", "period": "2017", "year": 2017, "quarter": null, "classification": "Total economía", "component": "Producto interno bruto", "value": 392393.12, "unit": "Millones de bolívares a precios constantes", "status": "", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/7_1_14_anual.xls", "fetched_at": "2026-08-10T21:11:07Z"}</t>
         </is>
       </c>
     </row>

--- a/assets/data/bcv/excel/ove_bcv_pib_historico_anual.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_pib_historico_anual.xlsx
@@ -736,7 +736,7 @@
       </c>
       <c r="S7" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10T21:11:07Z</t>
+          <t>2026-08-11T21:14:59Z</t>
         </is>
       </c>
     </row>
@@ -821,7 +821,7 @@
       </c>
       <c r="S8" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10T21:11:07Z</t>
+          <t>2026-08-11T21:14:59Z</t>
         </is>
       </c>
     </row>
@@ -906,7 +906,7 @@
       </c>
       <c r="S9" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10T21:11:07Z</t>
+          <t>2026-08-11T21:14:59Z</t>
         </is>
       </c>
     </row>
@@ -991,7 +991,7 @@
       </c>
       <c r="S10" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10T21:11:07Z</t>
+          <t>2026-08-11T21:14:59Z</t>
         </is>
       </c>
     </row>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="S11" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10T21:11:07Z</t>
+          <t>2026-08-11T21:14:59Z</t>
         </is>
       </c>
     </row>
@@ -1161,7 +1161,7 @@
       </c>
       <c r="S12" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10T21:11:07Z</t>
+          <t>2026-08-11T21:14:59Z</t>
         </is>
       </c>
     </row>
@@ -1246,7 +1246,7 @@
       </c>
       <c r="S13" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10T21:11:07Z</t>
+          <t>2026-08-11T21:14:59Z</t>
         </is>
       </c>
     </row>
@@ -1331,7 +1331,7 @@
       </c>
       <c r="S14" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10T21:11:07Z</t>
+          <t>2026-08-11T21:14:59Z</t>
         </is>
       </c>
     </row>
@@ -1416,7 +1416,7 @@
       </c>
       <c r="S15" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10T21:11:07Z</t>
+          <t>2026-08-11T21:14:59Z</t>
         </is>
       </c>
     </row>
@@ -1501,7 +1501,7 @@
       </c>
       <c r="S16" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10T21:11:07Z</t>
+          <t>2026-08-11T21:14:59Z</t>
         </is>
       </c>
     </row>
@@ -1586,7 +1586,7 @@
       </c>
       <c r="S17" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10T21:11:07Z</t>
+          <t>2026-08-11T21:14:59Z</t>
         </is>
       </c>
     </row>
@@ -1671,7 +1671,7 @@
       </c>
       <c r="S18" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10T21:11:07Z</t>
+          <t>2026-08-11T21:14:59Z</t>
         </is>
       </c>
     </row>
@@ -1756,7 +1756,7 @@
       </c>
       <c r="S19" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10T21:11:07Z</t>
+          <t>2026-08-11T21:14:59Z</t>
         </is>
       </c>
     </row>
@@ -1841,7 +1841,7 @@
       </c>
       <c r="S20" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10T21:11:07Z</t>
+          <t>2026-08-11T21:14:59Z</t>
         </is>
       </c>
     </row>
@@ -1926,7 +1926,7 @@
       </c>
       <c r="S21" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10T21:11:07Z</t>
+          <t>2026-08-11T21:14:59Z</t>
         </is>
       </c>
     </row>
@@ -2011,7 +2011,7 @@
       </c>
       <c r="S22" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10T21:11:07Z</t>
+          <t>2026-08-11T21:14:59Z</t>
         </is>
       </c>
     </row>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="S23" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10T21:11:07Z</t>
+          <t>2026-08-11T21:14:59Z</t>
         </is>
       </c>
     </row>
@@ -2181,7 +2181,7 @@
       </c>
       <c r="S24" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10T21:11:07Z</t>
+          <t>2026-08-11T21:14:59Z</t>
         </is>
       </c>
     </row>
@@ -2266,7 +2266,7 @@
       </c>
       <c r="S25" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10T21:11:07Z</t>
+          <t>2026-08-11T21:14:59Z</t>
         </is>
       </c>
     </row>
@@ -2351,7 +2351,7 @@
       </c>
       <c r="S26" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10T21:11:07Z</t>
+          <t>2026-08-11T21:14:59Z</t>
         </is>
       </c>
     </row>
@@ -2436,7 +2436,7 @@
       </c>
       <c r="S27" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10T21:11:07Z</t>
+          <t>2026-08-11T21:14:59Z</t>
         </is>
       </c>
     </row>
@@ -2521,7 +2521,7 @@
       </c>
       <c r="S28" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10T21:11:07Z</t>
+          <t>2026-08-11T21:14:59Z</t>
         </is>
       </c>
     </row>
@@ -2606,7 +2606,7 @@
       </c>
       <c r="S29" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10T21:11:07Z</t>
+          <t>2026-08-11T21:14:59Z</t>
         </is>
       </c>
     </row>
@@ -2691,7 +2691,7 @@
       </c>
       <c r="S30" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10T21:11:07Z</t>
+          <t>2026-08-11T21:14:59Z</t>
         </is>
       </c>
     </row>
@@ -2776,7 +2776,7 @@
       </c>
       <c r="S31" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10T21:11:07Z</t>
+          <t>2026-08-11T21:14:59Z</t>
         </is>
       </c>
     </row>
@@ -2861,7 +2861,7 @@
       </c>
       <c r="S32" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10T21:11:07Z</t>
+          <t>2026-08-11T21:14:59Z</t>
         </is>
       </c>
     </row>
@@ -2946,7 +2946,7 @@
       </c>
       <c r="S33" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10T21:11:07Z</t>
+          <t>2026-08-11T21:14:59Z</t>
         </is>
       </c>
     </row>
@@ -3031,7 +3031,7 @@
       </c>
       <c r="S34" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10T21:11:07Z</t>
+          <t>2026-08-11T21:14:59Z</t>
         </is>
       </c>
     </row>
@@ -3116,7 +3116,7 @@
       </c>
       <c r="S35" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10T21:11:07Z</t>
+          <t>2026-08-11T21:14:59Z</t>
         </is>
       </c>
     </row>
@@ -3201,7 +3201,7 @@
       </c>
       <c r="S36" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10T21:11:07Z</t>
+          <t>2026-08-11T21:14:59Z</t>
         </is>
       </c>
     </row>
@@ -3286,7 +3286,7 @@
       </c>
       <c r="S37" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10T21:11:07Z</t>
+          <t>2026-08-11T21:14:59Z</t>
         </is>
       </c>
     </row>
@@ -3371,7 +3371,7 @@
       </c>
       <c r="S38" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10T21:11:07Z</t>
+          <t>2026-08-11T21:14:59Z</t>
         </is>
       </c>
     </row>
@@ -3456,7 +3456,7 @@
       </c>
       <c r="S39" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10T21:11:07Z</t>
+          <t>2026-08-11T21:14:59Z</t>
         </is>
       </c>
     </row>
@@ -3541,7 +3541,7 @@
       </c>
       <c r="S40" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10T21:11:07Z</t>
+          <t>2026-08-11T21:14:59Z</t>
         </is>
       </c>
     </row>
@@ -3626,7 +3626,7 @@
       </c>
       <c r="S41" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10T21:11:07Z</t>
+          <t>2026-08-11T21:14:59Z</t>
         </is>
       </c>
     </row>
@@ -3711,7 +3711,7 @@
       </c>
       <c r="S42" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10T21:11:07Z</t>
+          <t>2026-08-11T21:14:59Z</t>
         </is>
       </c>
     </row>
@@ -3796,7 +3796,7 @@
       </c>
       <c r="S43" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10T21:11:07Z</t>
+          <t>2026-08-11T21:14:59Z</t>
         </is>
       </c>
     </row>
@@ -3881,7 +3881,7 @@
       </c>
       <c r="S44" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10T21:11:07Z</t>
+          <t>2026-08-11T21:14:59Z</t>
         </is>
       </c>
     </row>
@@ -3966,7 +3966,7 @@
       </c>
       <c r="S45" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10T21:11:07Z</t>
+          <t>2026-08-11T21:14:59Z</t>
         </is>
       </c>
     </row>
@@ -4051,7 +4051,7 @@
       </c>
       <c r="S46" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10T21:11:07Z</t>
+          <t>2026-08-11T21:14:59Z</t>
         </is>
       </c>
     </row>
@@ -4136,7 +4136,7 @@
       </c>
       <c r="S47" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10T21:11:07Z</t>
+          <t>2026-08-11T21:14:59Z</t>
         </is>
       </c>
     </row>
@@ -4221,7 +4221,7 @@
       </c>
       <c r="S48" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10T21:11:07Z</t>
+          <t>2026-08-11T21:14:59Z</t>
         </is>
       </c>
     </row>
@@ -4306,7 +4306,7 @@
       </c>
       <c r="S49" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10T21:11:07Z</t>
+          <t>2026-08-11T21:14:59Z</t>
         </is>
       </c>
     </row>
@@ -4391,7 +4391,7 @@
       </c>
       <c r="S50" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10T21:11:07Z</t>
+          <t>2026-08-11T21:14:59Z</t>
         </is>
       </c>
     </row>
@@ -4476,7 +4476,7 @@
       </c>
       <c r="S51" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10T21:11:07Z</t>
+          <t>2026-08-11T21:14:59Z</t>
         </is>
       </c>
     </row>
@@ -4561,7 +4561,7 @@
       </c>
       <c r="S52" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10T21:11:07Z</t>
+          <t>2026-08-11T21:14:59Z</t>
         </is>
       </c>
     </row>
@@ -4646,7 +4646,7 @@
       </c>
       <c r="S53" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10T21:11:07Z</t>
+          <t>2026-08-11T21:14:59Z</t>
         </is>
       </c>
     </row>
@@ -4731,7 +4731,7 @@
       </c>
       <c r="S54" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10T21:11:07Z</t>
+          <t>2026-08-11T21:14:59Z</t>
         </is>
       </c>
     </row>
@@ -4816,7 +4816,7 @@
       </c>
       <c r="S55" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10T21:11:07Z</t>
+          <t>2026-08-11T21:14:59Z</t>
         </is>
       </c>
     </row>
@@ -4901,7 +4901,7 @@
       </c>
       <c r="S56" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10T21:11:07Z</t>
+          <t>2026-08-11T21:14:59Z</t>
         </is>
       </c>
     </row>
@@ -4986,7 +4986,7 @@
       </c>
       <c r="S57" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10T21:11:07Z</t>
+          <t>2026-08-11T21:14:59Z</t>
         </is>
       </c>
     </row>
@@ -5071,7 +5071,7 @@
       </c>
       <c r="S58" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10T21:11:07Z</t>
+          <t>2026-08-11T21:14:59Z</t>
         </is>
       </c>
     </row>
@@ -5156,7 +5156,7 @@
       </c>
       <c r="S59" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10T21:11:07Z</t>
+          <t>2026-08-11T21:14:59Z</t>
         </is>
       </c>
     </row>
@@ -5241,7 +5241,7 @@
       </c>
       <c r="S60" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10T21:11:07Z</t>
+          <t>2026-08-11T21:14:59Z</t>
         </is>
       </c>
     </row>
@@ -5326,7 +5326,7 @@
       </c>
       <c r="S61" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10T21:11:07Z</t>
+          <t>2026-08-11T21:14:59Z</t>
         </is>
       </c>
     </row>
@@ -5411,7 +5411,7 @@
       </c>
       <c r="S62" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10T21:11:07Z</t>
+          <t>2026-08-11T21:14:59Z</t>
         </is>
       </c>
     </row>
@@ -5496,7 +5496,7 @@
       </c>
       <c r="S63" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10T21:11:07Z</t>
+          <t>2026-08-11T21:14:59Z</t>
         </is>
       </c>
     </row>
@@ -5581,7 +5581,7 @@
       </c>
       <c r="S64" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10T21:11:07Z</t>
+          <t>2026-08-11T21:14:59Z</t>
         </is>
       </c>
     </row>
@@ -5666,7 +5666,7 @@
       </c>
       <c r="S65" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10T21:11:07Z</t>
+          <t>2026-08-11T21:14:59Z</t>
         </is>
       </c>
     </row>
@@ -5751,7 +5751,7 @@
       </c>
       <c r="S66" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10T21:11:07Z</t>
+          <t>2026-08-11T21:14:59Z</t>
         </is>
       </c>
     </row>
@@ -5836,7 +5836,7 @@
       </c>
       <c r="S67" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10T21:11:07Z</t>
+          <t>2026-08-11T21:14:59Z</t>
         </is>
       </c>
     </row>
@@ -5921,7 +5921,7 @@
       </c>
       <c r="S68" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10T21:11:07Z</t>
+          <t>2026-08-11T21:14:59Z</t>
         </is>
       </c>
     </row>
@@ -6006,7 +6006,7 @@
       </c>
       <c r="S69" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10T21:11:07Z</t>
+          <t>2026-08-11T21:14:59Z</t>
         </is>
       </c>
     </row>
@@ -6091,7 +6091,7 @@
       </c>
       <c r="S70" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10T21:11:07Z</t>
+          <t>2026-08-11T21:14:59Z</t>
         </is>
       </c>
     </row>
@@ -6176,7 +6176,7 @@
       </c>
       <c r="S71" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10T21:11:07Z</t>
+          <t>2026-08-11T21:14:59Z</t>
         </is>
       </c>
     </row>
@@ -6261,7 +6261,7 @@
       </c>
       <c r="S72" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10T21:11:07Z</t>
+          <t>2026-08-11T21:14:59Z</t>
         </is>
       </c>
     </row>
@@ -6346,7 +6346,7 @@
       </c>
       <c r="S73" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10T21:11:07Z</t>
+          <t>2026-08-11T21:14:59Z</t>
         </is>
       </c>
     </row>
@@ -6431,7 +6431,7 @@
       </c>
       <c r="S74" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10T21:11:07Z</t>
+          <t>2026-08-11T21:14:59Z</t>
         </is>
       </c>
     </row>
@@ -6516,7 +6516,7 @@
       </c>
       <c r="S75" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10T21:11:07Z</t>
+          <t>2026-08-11T21:14:59Z</t>
         </is>
       </c>
     </row>
@@ -6601,7 +6601,7 @@
       </c>
       <c r="S76" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10T21:11:07Z</t>
+          <t>2026-08-11T21:14:59Z</t>
         </is>
       </c>
     </row>
@@ -6686,7 +6686,7 @@
       </c>
       <c r="S77" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10T21:11:07Z</t>
+          <t>2026-08-11T21:14:59Z</t>
         </is>
       </c>
     </row>
@@ -6771,7 +6771,7 @@
       </c>
       <c r="S78" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10T21:11:07Z</t>
+          <t>2026-08-11T21:14:59Z</t>
         </is>
       </c>
     </row>
@@ -6856,7 +6856,7 @@
       </c>
       <c r="S79" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10T21:11:07Z</t>
+          <t>2026-08-11T21:14:59Z</t>
         </is>
       </c>
     </row>
@@ -6941,7 +6941,7 @@
       </c>
       <c r="S80" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10T21:11:07Z</t>
+          <t>2026-08-11T21:14:59Z</t>
         </is>
       </c>
     </row>
@@ -7026,7 +7026,7 @@
       </c>
       <c r="S81" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10T21:11:07Z</t>
+          <t>2026-08-11T21:14:59Z</t>
         </is>
       </c>
     </row>
@@ -7111,7 +7111,7 @@
       </c>
       <c r="S82" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10T21:11:07Z</t>
+          <t>2026-08-11T21:14:59Z</t>
         </is>
       </c>
     </row>
@@ -7196,7 +7196,7 @@
       </c>
       <c r="S83" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10T21:11:07Z</t>
+          <t>2026-08-11T21:14:59Z</t>
         </is>
       </c>
     </row>
@@ -7281,7 +7281,7 @@
       </c>
       <c r="S84" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10T21:11:07Z</t>
+          <t>2026-08-11T21:14:59Z</t>
         </is>
       </c>
     </row>
@@ -7366,7 +7366,7 @@
       </c>
       <c r="S85" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10T21:11:07Z</t>
+          <t>2026-08-11T21:14:59Z</t>
         </is>
       </c>
     </row>
@@ -7451,7 +7451,7 @@
       </c>
       <c r="S86" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10T21:11:07Z</t>
+          <t>2026-08-11T21:14:59Z</t>
         </is>
       </c>
     </row>
@@ -7536,7 +7536,7 @@
       </c>
       <c r="S87" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10T21:11:07Z</t>
+          <t>2026-08-11T21:14:59Z</t>
         </is>
       </c>
     </row>
@@ -7621,7 +7621,7 @@
       </c>
       <c r="S88" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10T21:11:07Z</t>
+          <t>2026-08-11T21:14:59Z</t>
         </is>
       </c>
     </row>
@@ -7706,7 +7706,7 @@
       </c>
       <c r="S89" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10T21:11:07Z</t>
+          <t>2026-08-11T21:14:59Z</t>
         </is>
       </c>
     </row>
@@ -7791,7 +7791,7 @@
       </c>
       <c r="S90" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10T21:11:07Z</t>
+          <t>2026-08-11T21:14:59Z</t>
         </is>
       </c>
     </row>
@@ -7876,7 +7876,7 @@
       </c>
       <c r="S91" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10T21:11:07Z</t>
+          <t>2026-08-11T21:14:59Z</t>
         </is>
       </c>
     </row>
@@ -7961,7 +7961,7 @@
       </c>
       <c r="S92" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10T21:11:07Z</t>
+          <t>2026-08-11T21:14:59Z</t>
         </is>
       </c>
     </row>
@@ -8046,7 +8046,7 @@
       </c>
       <c r="S93" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10T21:11:07Z</t>
+          <t>2026-08-11T21:14:59Z</t>
         </is>
       </c>
     </row>
@@ -8131,7 +8131,7 @@
       </c>
       <c r="S94" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10T21:11:07Z</t>
+          <t>2026-08-11T21:14:59Z</t>
         </is>
       </c>
     </row>
@@ -8216,7 +8216,7 @@
       </c>
       <c r="S95" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10T21:11:07Z</t>
+          <t>2026-08-11T21:14:59Z</t>
         </is>
       </c>
     </row>
@@ -8301,7 +8301,7 @@
       </c>
       <c r="S96" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10T21:11:07Z</t>
+          <t>2026-08-11T21:14:59Z</t>
         </is>
       </c>
     </row>
@@ -8386,7 +8386,7 @@
       </c>
       <c r="S97" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10T21:11:07Z</t>
+          <t>2026-08-11T21:14:59Z</t>
         </is>
       </c>
     </row>
@@ -8471,7 +8471,7 @@
       </c>
       <c r="S98" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10T21:11:07Z</t>
+          <t>2026-08-11T21:14:59Z</t>
         </is>
       </c>
     </row>
@@ -8556,7 +8556,7 @@
       </c>
       <c r="S99" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10T21:11:07Z</t>
+          <t>2026-08-11T21:14:59Z</t>
         </is>
       </c>
     </row>
@@ -8641,7 +8641,7 @@
       </c>
       <c r="S100" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10T21:11:07Z</t>
+          <t>2026-08-11T21:14:59Z</t>
         </is>
       </c>
     </row>
@@ -8726,7 +8726,7 @@
       </c>
       <c r="S101" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10T21:11:07Z</t>
+          <t>2026-08-11T21:14:59Z</t>
         </is>
       </c>
     </row>
@@ -8811,7 +8811,7 @@
       </c>
       <c r="S102" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10T21:11:07Z</t>
+          <t>2026-08-11T21:14:59Z</t>
         </is>
       </c>
     </row>
@@ -8896,7 +8896,7 @@
       </c>
       <c r="S103" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10T21:11:07Z</t>
+          <t>2026-08-11T21:14:59Z</t>
         </is>
       </c>
     </row>
@@ -8981,7 +8981,7 @@
       </c>
       <c r="S104" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10T21:11:07Z</t>
+          <t>2026-08-11T21:14:59Z</t>
         </is>
       </c>
     </row>
@@ -9066,7 +9066,7 @@
       </c>
       <c r="S105" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10T21:11:07Z</t>
+          <t>2026-08-11T21:14:59Z</t>
         </is>
       </c>
     </row>
@@ -9151,7 +9151,7 @@
       </c>
       <c r="S106" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10T21:11:07Z</t>
+          <t>2026-08-11T21:14:59Z</t>
         </is>
       </c>
     </row>
@@ -9236,7 +9236,7 @@
       </c>
       <c r="S107" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10T21:11:07Z</t>
+          <t>2026-08-11T21:14:59Z</t>
         </is>
       </c>
     </row>
@@ -9321,7 +9321,7 @@
       </c>
       <c r="S108" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10T21:11:07Z</t>
+          <t>2026-08-11T21:14:59Z</t>
         </is>
       </c>
     </row>
@@ -9406,7 +9406,7 @@
       </c>
       <c r="S109" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10T21:11:07Z</t>
+          <t>2026-08-11T21:14:59Z</t>
         </is>
       </c>
     </row>
@@ -9491,7 +9491,7 @@
       </c>
       <c r="S110" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10T21:11:07Z</t>
+          <t>2026-08-11T21:14:59Z</t>
         </is>
       </c>
     </row>
@@ -9576,7 +9576,7 @@
       </c>
       <c r="S111" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10T21:11:07Z</t>
+          <t>2026-08-11T21:14:59Z</t>
         </is>
       </c>
     </row>
@@ -9661,7 +9661,7 @@
       </c>
       <c r="S112" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10T21:11:07Z</t>
+          <t>2026-08-11T21:14:59Z</t>
         </is>
       </c>
     </row>
@@ -9746,7 +9746,7 @@
       </c>
       <c r="S113" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10T21:11:07Z</t>
+          <t>2026-08-11T21:14:59Z</t>
         </is>
       </c>
     </row>
@@ -9831,7 +9831,7 @@
       </c>
       <c r="S114" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10T21:11:07Z</t>
+          <t>2026-08-11T21:14:59Z</t>
         </is>
       </c>
     </row>
@@ -9916,7 +9916,7 @@
       </c>
       <c r="S115" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10T21:11:07Z</t>
+          <t>2026-08-11T21:14:59Z</t>
         </is>
       </c>
     </row>
@@ -10001,7 +10001,7 @@
       </c>
       <c r="S116" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10T21:11:07Z</t>
+          <t>2026-08-11T21:14:59Z</t>
         </is>
       </c>
     </row>
@@ -10086,7 +10086,7 @@
       </c>
       <c r="S117" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10T21:11:07Z</t>
+          <t>2026-08-11T21:14:59Z</t>
         </is>
       </c>
     </row>
@@ -10171,7 +10171,7 @@
       </c>
       <c r="S118" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10T21:11:07Z</t>
+          <t>2026-08-11T21:14:59Z</t>
         </is>
       </c>
     </row>
@@ -10256,7 +10256,7 @@
       </c>
       <c r="S119" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10T21:11:07Z</t>
+          <t>2026-08-11T21:14:59Z</t>
         </is>
       </c>
     </row>
@@ -10341,7 +10341,7 @@
       </c>
       <c r="S120" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10T21:11:07Z</t>
+          <t>2026-08-11T21:14:59Z</t>
         </is>
       </c>
     </row>
@@ -10426,7 +10426,7 @@
       </c>
       <c r="S121" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10T21:11:07Z</t>
+          <t>2026-08-11T21:14:59Z</t>
         </is>
       </c>
     </row>
@@ -10511,7 +10511,7 @@
       </c>
       <c r="S122" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10T21:11:07Z</t>
+          <t>2026-08-11T21:14:59Z</t>
         </is>
       </c>
     </row>
@@ -10596,7 +10596,7 @@
       </c>
       <c r="S123" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10T21:11:07Z</t>
+          <t>2026-08-11T21:14:59Z</t>
         </is>
       </c>
     </row>
@@ -10681,7 +10681,7 @@
       </c>
       <c r="S124" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10T21:11:07Z</t>
+          <t>2026-08-11T21:14:59Z</t>
         </is>
       </c>
     </row>
@@ -10766,7 +10766,7 @@
       </c>
       <c r="S125" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10T21:11:07Z</t>
+          <t>2026-08-11T21:14:59Z</t>
         </is>
       </c>
     </row>
@@ -10851,7 +10851,7 @@
       </c>
       <c r="S126" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10T21:11:07Z</t>
+          <t>2026-08-11T21:14:59Z</t>
         </is>
       </c>
     </row>
@@ -10936,7 +10936,7 @@
       </c>
       <c r="S127" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10T21:11:07Z</t>
+          <t>2026-08-11T21:14:59Z</t>
         </is>
       </c>
     </row>
@@ -11021,7 +11021,7 @@
       </c>
       <c r="S128" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10T21:11:07Z</t>
+          <t>2026-08-11T21:14:59Z</t>
         </is>
       </c>
     </row>
@@ -11106,7 +11106,7 @@
       </c>
       <c r="S129" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10T21:11:07Z</t>
+          <t>2026-08-11T21:14:59Z</t>
         </is>
       </c>
     </row>
@@ -11191,7 +11191,7 @@
       </c>
       <c r="S130" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10T21:11:07Z</t>
+          <t>2026-08-11T21:14:59Z</t>
         </is>
       </c>
     </row>
@@ -11276,7 +11276,7 @@
       </c>
       <c r="S131" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10T21:11:07Z</t>
+          <t>2026-08-11T21:14:59Z</t>
         </is>
       </c>
     </row>
@@ -11361,7 +11361,7 @@
       </c>
       <c r="S132" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10T21:11:07Z</t>
+          <t>2026-08-11T21:14:59Z</t>
         </is>
       </c>
     </row>
@@ -11446,7 +11446,7 @@
       </c>
       <c r="S133" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10T21:11:07Z</t>
+          <t>2026-08-11T21:14:59Z</t>
         </is>
       </c>
     </row>
@@ -11531,7 +11531,7 @@
       </c>
       <c r="S134" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10T21:11:07Z</t>
+          <t>2026-08-11T21:14:59Z</t>
         </is>
       </c>
     </row>
@@ -11616,7 +11616,7 @@
       </c>
       <c r="S135" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10T21:11:07Z</t>
+          <t>2026-08-11T21:14:59Z</t>
         </is>
       </c>
     </row>
@@ -11701,7 +11701,7 @@
       </c>
       <c r="S136" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10T21:11:07Z</t>
+          <t>2026-08-11T21:14:59Z</t>
         </is>
       </c>
     </row>
@@ -11786,7 +11786,7 @@
       </c>
       <c r="S137" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10T21:11:07Z</t>
+          <t>2026-08-11T21:14:59Z</t>
         </is>
       </c>
     </row>
@@ -11871,7 +11871,7 @@
       </c>
       <c r="S138" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10T21:11:07Z</t>
+          <t>2026-08-11T21:14:59Z</t>
         </is>
       </c>
     </row>
@@ -11956,7 +11956,7 @@
       </c>
       <c r="S139" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10T21:11:07Z</t>
+          <t>2026-08-11T21:14:59Z</t>
         </is>
       </c>
     </row>
@@ -12041,7 +12041,7 @@
       </c>
       <c r="S140" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10T21:11:07Z</t>
+          <t>2026-08-11T21:14:59Z</t>
         </is>
       </c>
     </row>
@@ -12126,7 +12126,7 @@
       </c>
       <c r="S141" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10T21:11:07Z</t>
+          <t>2026-08-11T21:14:59Z</t>
         </is>
       </c>
     </row>
@@ -12258,7 +12258,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10T21:11:07Z</t>
+          <t>2026-08-11T21:14:59Z</t>
         </is>
       </c>
     </row>
@@ -12338,7 +12338,7 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>{"dataset_id": "bcv_pib_historico_anual", "title": "Producto interno bruto histórico anual", "table": "PIB histórico anual", "source_file": "7_1_14_anual.xls", "base": "1957/1968/1984/1997", "price_type": "Precios constantes", "measure": "Nivel", "frequency": "Anual", "period": "2017", "year": 2017, "quarter": null, "classification": "Total economía", "component": "Producto interno bruto", "value": 392393.12, "unit": "Millones de bolívares a precios constantes", "status": "", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/7_1_14_anual.xls", "fetched_at": "2026-08-10T21:11:07Z"}</t>
+          <t>{"dataset_id": "bcv_pib_historico_anual", "title": "Producto interno bruto histórico anual", "table": "PIB histórico anual", "source_file": "7_1_14_anual.xls", "base": "1957/1968/1984/1997", "price_type": "Precios constantes", "measure": "Nivel", "frequency": "Anual", "period": "2017", "year": 2017, "quarter": null, "classification": "Total economía", "component": "Producto interno bruto", "value": 392393.12, "unit": "Millones de bolívares a precios constantes", "status": "", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/7_1_14_anual.xls", "fetched_at": "2026-08-11T21:14:59Z"}</t>
         </is>
       </c>
     </row>

--- a/assets/data/bcv/excel/ove_bcv_pib_historico_anual.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_pib_historico_anual.xlsx
@@ -736,7 +736,7 @@
       </c>
       <c r="S7" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11T21:14:59Z</t>
+          <t>2026-08-12T14:32:12Z</t>
         </is>
       </c>
     </row>
@@ -821,7 +821,7 @@
       </c>
       <c r="S8" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11T21:14:59Z</t>
+          <t>2026-08-12T14:32:12Z</t>
         </is>
       </c>
     </row>
@@ -906,7 +906,7 @@
       </c>
       <c r="S9" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11T21:14:59Z</t>
+          <t>2026-08-12T14:32:12Z</t>
         </is>
       </c>
     </row>
@@ -991,7 +991,7 @@
       </c>
       <c r="S10" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11T21:14:59Z</t>
+          <t>2026-08-12T14:32:12Z</t>
         </is>
       </c>
     </row>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="S11" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11T21:14:59Z</t>
+          <t>2026-08-12T14:32:12Z</t>
         </is>
       </c>
     </row>
@@ -1161,7 +1161,7 @@
       </c>
       <c r="S12" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11T21:14:59Z</t>
+          <t>2026-08-12T14:32:12Z</t>
         </is>
       </c>
     </row>
@@ -1246,7 +1246,7 @@
       </c>
       <c r="S13" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11T21:14:59Z</t>
+          <t>2026-08-12T14:32:12Z</t>
         </is>
       </c>
     </row>
@@ -1331,7 +1331,7 @@
       </c>
       <c r="S14" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11T21:14:59Z</t>
+          <t>2026-08-12T14:32:12Z</t>
         </is>
       </c>
     </row>
@@ -1416,7 +1416,7 @@
       </c>
       <c r="S15" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11T21:14:59Z</t>
+          <t>2026-08-12T14:32:12Z</t>
         </is>
       </c>
     </row>
@@ -1501,7 +1501,7 @@
       </c>
       <c r="S16" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11T21:14:59Z</t>
+          <t>2026-08-12T14:32:12Z</t>
         </is>
       </c>
     </row>
@@ -1586,7 +1586,7 @@
       </c>
       <c r="S17" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11T21:14:59Z</t>
+          <t>2026-08-12T14:32:12Z</t>
         </is>
       </c>
     </row>
@@ -1671,7 +1671,7 @@
       </c>
       <c r="S18" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11T21:14:59Z</t>
+          <t>2026-08-12T14:32:12Z</t>
         </is>
       </c>
     </row>
@@ -1756,7 +1756,7 @@
       </c>
       <c r="S19" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11T21:14:59Z</t>
+          <t>2026-08-12T14:32:12Z</t>
         </is>
       </c>
     </row>
@@ -1841,7 +1841,7 @@
       </c>
       <c r="S20" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11T21:14:59Z</t>
+          <t>2026-08-12T14:32:12Z</t>
         </is>
       </c>
     </row>
@@ -1926,7 +1926,7 @@
       </c>
       <c r="S21" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11T21:14:59Z</t>
+          <t>2026-08-12T14:32:12Z</t>
         </is>
       </c>
     </row>
@@ -2011,7 +2011,7 @@
       </c>
       <c r="S22" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11T21:14:59Z</t>
+          <t>2026-08-12T14:32:12Z</t>
         </is>
       </c>
     </row>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="S23" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11T21:14:59Z</t>
+          <t>2026-08-12T14:32:12Z</t>
         </is>
       </c>
     </row>
@@ -2181,7 +2181,7 @@
       </c>
       <c r="S24" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11T21:14:59Z</t>
+          <t>2026-08-12T14:32:12Z</t>
         </is>
       </c>
     </row>
@@ -2266,7 +2266,7 @@
       </c>
       <c r="S25" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11T21:14:59Z</t>
+          <t>2026-08-12T14:32:12Z</t>
         </is>
       </c>
     </row>
@@ -2351,7 +2351,7 @@
       </c>
       <c r="S26" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11T21:14:59Z</t>
+          <t>2026-08-12T14:32:12Z</t>
         </is>
       </c>
     </row>
@@ -2436,7 +2436,7 @@
       </c>
       <c r="S27" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11T21:14:59Z</t>
+          <t>2026-08-12T14:32:12Z</t>
         </is>
       </c>
     </row>
@@ -2521,7 +2521,7 @@
       </c>
       <c r="S28" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11T21:14:59Z</t>
+          <t>2026-08-12T14:32:12Z</t>
         </is>
       </c>
     </row>
@@ -2606,7 +2606,7 @@
       </c>
       <c r="S29" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11T21:14:59Z</t>
+          <t>2026-08-12T14:32:12Z</t>
         </is>
       </c>
     </row>
@@ -2691,7 +2691,7 @@
       </c>
       <c r="S30" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11T21:14:59Z</t>
+          <t>2026-08-12T14:32:12Z</t>
         </is>
       </c>
     </row>
@@ -2776,7 +2776,7 @@
       </c>
       <c r="S31" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11T21:14:59Z</t>
+          <t>2026-08-12T14:32:12Z</t>
         </is>
       </c>
     </row>
@@ -2861,7 +2861,7 @@
       </c>
       <c r="S32" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11T21:14:59Z</t>
+          <t>2026-08-12T14:32:12Z</t>
         </is>
       </c>
     </row>
@@ -2946,7 +2946,7 @@
       </c>
       <c r="S33" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11T21:14:59Z</t>
+          <t>2026-08-12T14:32:12Z</t>
         </is>
       </c>
     </row>
@@ -3031,7 +3031,7 @@
       </c>
       <c r="S34" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11T21:14:59Z</t>
+          <t>2026-08-12T14:32:12Z</t>
         </is>
       </c>
     </row>
@@ -3116,7 +3116,7 @@
       </c>
       <c r="S35" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11T21:14:59Z</t>
+          <t>2026-08-12T14:32:12Z</t>
         </is>
       </c>
     </row>
@@ -3201,7 +3201,7 @@
       </c>
       <c r="S36" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11T21:14:59Z</t>
+          <t>2026-08-12T14:32:12Z</t>
         </is>
       </c>
     </row>
@@ -3286,7 +3286,7 @@
       </c>
       <c r="S37" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11T21:14:59Z</t>
+          <t>2026-08-12T14:32:12Z</t>
         </is>
       </c>
     </row>
@@ -3371,7 +3371,7 @@
       </c>
       <c r="S38" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11T21:14:59Z</t>
+          <t>2026-08-12T14:32:12Z</t>
         </is>
       </c>
     </row>
@@ -3456,7 +3456,7 @@
       </c>
       <c r="S39" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11T21:14:59Z</t>
+          <t>2026-08-12T14:32:12Z</t>
         </is>
       </c>
     </row>
@@ -3541,7 +3541,7 @@
       </c>
       <c r="S40" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11T21:14:59Z</t>
+          <t>2026-08-12T14:32:12Z</t>
         </is>
       </c>
     </row>
@@ -3626,7 +3626,7 @@
       </c>
       <c r="S41" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11T21:14:59Z</t>
+          <t>2026-08-12T14:32:12Z</t>
         </is>
       </c>
     </row>
@@ -3711,7 +3711,7 @@
       </c>
       <c r="S42" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11T21:14:59Z</t>
+          <t>2026-08-12T14:32:12Z</t>
         </is>
       </c>
     </row>
@@ -3796,7 +3796,7 @@
       </c>
       <c r="S43" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11T21:14:59Z</t>
+          <t>2026-08-12T14:32:12Z</t>
         </is>
       </c>
     </row>
@@ -3881,7 +3881,7 @@
       </c>
       <c r="S44" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11T21:14:59Z</t>
+          <t>2026-08-12T14:32:12Z</t>
         </is>
       </c>
     </row>
@@ -3966,7 +3966,7 @@
       </c>
       <c r="S45" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11T21:14:59Z</t>
+          <t>2026-08-12T14:32:12Z</t>
         </is>
       </c>
     </row>
@@ -4051,7 +4051,7 @@
       </c>
       <c r="S46" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11T21:14:59Z</t>
+          <t>2026-08-12T14:32:12Z</t>
         </is>
       </c>
     </row>
@@ -4136,7 +4136,7 @@
       </c>
       <c r="S47" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11T21:14:59Z</t>
+          <t>2026-08-12T14:32:12Z</t>
         </is>
       </c>
     </row>
@@ -4221,7 +4221,7 @@
       </c>
       <c r="S48" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11T21:14:59Z</t>
+          <t>2026-08-12T14:32:12Z</t>
         </is>
       </c>
     </row>
@@ -4306,7 +4306,7 @@
       </c>
       <c r="S49" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11T21:14:59Z</t>
+          <t>2026-08-12T14:32:12Z</t>
         </is>
       </c>
     </row>
@@ -4391,7 +4391,7 @@
       </c>
       <c r="S50" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11T21:14:59Z</t>
+          <t>2026-08-12T14:32:12Z</t>
         </is>
       </c>
     </row>
@@ -4476,7 +4476,7 @@
       </c>
       <c r="S51" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11T21:14:59Z</t>
+          <t>2026-08-12T14:32:12Z</t>
         </is>
       </c>
     </row>
@@ -4561,7 +4561,7 @@
       </c>
       <c r="S52" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11T21:14:59Z</t>
+          <t>2026-08-12T14:32:12Z</t>
         </is>
       </c>
     </row>
@@ -4646,7 +4646,7 @@
       </c>
       <c r="S53" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11T21:14:59Z</t>
+          <t>2026-08-12T14:32:12Z</t>
         </is>
       </c>
     </row>
@@ -4731,7 +4731,7 @@
       </c>
       <c r="S54" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11T21:14:59Z</t>
+          <t>2026-08-12T14:32:12Z</t>
         </is>
       </c>
     </row>
@@ -4816,7 +4816,7 @@
       </c>
       <c r="S55" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11T21:14:59Z</t>
+          <t>2026-08-12T14:32:12Z</t>
         </is>
       </c>
     </row>
@@ -4901,7 +4901,7 @@
       </c>
       <c r="S56" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11T21:14:59Z</t>
+          <t>2026-08-12T14:32:12Z</t>
         </is>
       </c>
     </row>
@@ -4986,7 +4986,7 @@
       </c>
       <c r="S57" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11T21:14:59Z</t>
+          <t>2026-08-12T14:32:12Z</t>
         </is>
       </c>
     </row>
@@ -5071,7 +5071,7 @@
       </c>
       <c r="S58" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11T21:14:59Z</t>
+          <t>2026-08-12T14:32:12Z</t>
         </is>
       </c>
     </row>
@@ -5156,7 +5156,7 @@
       </c>
       <c r="S59" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11T21:14:59Z</t>
+          <t>2026-08-12T14:32:12Z</t>
         </is>
       </c>
     </row>
@@ -5241,7 +5241,7 @@
       </c>
       <c r="S60" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11T21:14:59Z</t>
+          <t>2026-08-12T14:32:12Z</t>
         </is>
       </c>
     </row>
@@ -5326,7 +5326,7 @@
       </c>
       <c r="S61" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11T21:14:59Z</t>
+          <t>2026-08-12T14:32:12Z</t>
         </is>
       </c>
     </row>
@@ -5411,7 +5411,7 @@
       </c>
       <c r="S62" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11T21:14:59Z</t>
+          <t>2026-08-12T14:32:12Z</t>
         </is>
       </c>
     </row>
@@ -5496,7 +5496,7 @@
       </c>
       <c r="S63" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11T21:14:59Z</t>
+          <t>2026-08-12T14:32:12Z</t>
         </is>
       </c>
     </row>
@@ -5581,7 +5581,7 @@
       </c>
       <c r="S64" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11T21:14:59Z</t>
+          <t>2026-08-12T14:32:12Z</t>
         </is>
       </c>
     </row>
@@ -5666,7 +5666,7 @@
       </c>
       <c r="S65" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11T21:14:59Z</t>
+          <t>2026-08-12T14:32:12Z</t>
         </is>
       </c>
     </row>
@@ -5751,7 +5751,7 @@
       </c>
       <c r="S66" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11T21:14:59Z</t>
+          <t>2026-08-12T14:32:12Z</t>
         </is>
       </c>
     </row>
@@ -5836,7 +5836,7 @@
       </c>
       <c r="S67" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11T21:14:59Z</t>
+          <t>2026-08-12T14:32:12Z</t>
         </is>
       </c>
     </row>
@@ -5921,7 +5921,7 @@
       </c>
       <c r="S68" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11T21:14:59Z</t>
+          <t>2026-08-12T14:32:12Z</t>
         </is>
       </c>
     </row>
@@ -6006,7 +6006,7 @@
       </c>
       <c r="S69" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11T21:14:59Z</t>
+          <t>2026-08-12T14:32:12Z</t>
         </is>
       </c>
     </row>
@@ -6091,7 +6091,7 @@
       </c>
       <c r="S70" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11T21:14:59Z</t>
+          <t>2026-08-12T14:32:12Z</t>
         </is>
       </c>
     </row>
@@ -6176,7 +6176,7 @@
       </c>
       <c r="S71" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11T21:14:59Z</t>
+          <t>2026-08-12T14:32:12Z</t>
         </is>
       </c>
     </row>
@@ -6261,7 +6261,7 @@
       </c>
       <c r="S72" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11T21:14:59Z</t>
+          <t>2026-08-12T14:32:12Z</t>
         </is>
       </c>
     </row>
@@ -6346,7 +6346,7 @@
       </c>
       <c r="S73" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11T21:14:59Z</t>
+          <t>2026-08-12T14:32:12Z</t>
         </is>
       </c>
     </row>
@@ -6431,7 +6431,7 @@
       </c>
       <c r="S74" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11T21:14:59Z</t>
+          <t>2026-08-12T14:32:12Z</t>
         </is>
       </c>
     </row>
@@ -6516,7 +6516,7 @@
       </c>
       <c r="S75" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11T21:14:59Z</t>
+          <t>2026-08-12T14:32:12Z</t>
         </is>
       </c>
     </row>
@@ -6601,7 +6601,7 @@
       </c>
       <c r="S76" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11T21:14:59Z</t>
+          <t>2026-08-12T14:32:12Z</t>
         </is>
       </c>
     </row>
@@ -6686,7 +6686,7 @@
       </c>
       <c r="S77" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11T21:14:59Z</t>
+          <t>2026-08-12T14:32:12Z</t>
         </is>
       </c>
     </row>
@@ -6771,7 +6771,7 @@
       </c>
       <c r="S78" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11T21:14:59Z</t>
+          <t>2026-08-12T14:32:12Z</t>
         </is>
       </c>
     </row>
@@ -6856,7 +6856,7 @@
       </c>
       <c r="S79" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11T21:14:59Z</t>
+          <t>2026-08-12T14:32:12Z</t>
         </is>
       </c>
     </row>
@@ -6941,7 +6941,7 @@
       </c>
       <c r="S80" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11T21:14:59Z</t>
+          <t>2026-08-12T14:32:12Z</t>
         </is>
       </c>
     </row>
@@ -7026,7 +7026,7 @@
       </c>
       <c r="S81" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11T21:14:59Z</t>
+          <t>2026-08-12T14:32:12Z</t>
         </is>
       </c>
     </row>
@@ -7111,7 +7111,7 @@
       </c>
       <c r="S82" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11T21:14:59Z</t>
+          <t>2026-08-12T14:32:12Z</t>
         </is>
       </c>
     </row>
@@ -7196,7 +7196,7 @@
       </c>
       <c r="S83" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11T21:14:59Z</t>
+          <t>2026-08-12T14:32:12Z</t>
         </is>
       </c>
     </row>
@@ -7281,7 +7281,7 @@
       </c>
       <c r="S84" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11T21:14:59Z</t>
+          <t>2026-08-12T14:32:12Z</t>
         </is>
       </c>
     </row>
@@ -7366,7 +7366,7 @@
       </c>
       <c r="S85" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11T21:14:59Z</t>
+          <t>2026-08-12T14:32:12Z</t>
         </is>
       </c>
     </row>
@@ -7451,7 +7451,7 @@
       </c>
       <c r="S86" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11T21:14:59Z</t>
+          <t>2026-08-12T14:32:12Z</t>
         </is>
       </c>
     </row>
@@ -7536,7 +7536,7 @@
       </c>
       <c r="S87" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11T21:14:59Z</t>
+          <t>2026-08-12T14:32:12Z</t>
         </is>
       </c>
     </row>
@@ -7621,7 +7621,7 @@
       </c>
       <c r="S88" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11T21:14:59Z</t>
+          <t>2026-08-12T14:32:12Z</t>
         </is>
       </c>
     </row>
@@ -7706,7 +7706,7 @@
       </c>
       <c r="S89" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11T21:14:59Z</t>
+          <t>2026-08-12T14:32:12Z</t>
         </is>
       </c>
     </row>
@@ -7791,7 +7791,7 @@
       </c>
       <c r="S90" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11T21:14:59Z</t>
+          <t>2026-08-12T14:32:12Z</t>
         </is>
       </c>
     </row>
@@ -7876,7 +7876,7 @@
       </c>
       <c r="S91" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11T21:14:59Z</t>
+          <t>2026-08-12T14:32:12Z</t>
         </is>
       </c>
     </row>
@@ -7961,7 +7961,7 @@
       </c>
       <c r="S92" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11T21:14:59Z</t>
+          <t>2026-08-12T14:32:12Z</t>
         </is>
       </c>
     </row>
@@ -8046,7 +8046,7 @@
       </c>
       <c r="S93" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11T21:14:59Z</t>
+          <t>2026-08-12T14:32:12Z</t>
         </is>
       </c>
     </row>
@@ -8131,7 +8131,7 @@
       </c>
       <c r="S94" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11T21:14:59Z</t>
+          <t>2026-08-12T14:32:12Z</t>
         </is>
       </c>
     </row>
@@ -8216,7 +8216,7 @@
       </c>
       <c r="S95" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11T21:14:59Z</t>
+          <t>2026-08-12T14:32:12Z</t>
         </is>
       </c>
     </row>
@@ -8301,7 +8301,7 @@
       </c>
       <c r="S96" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11T21:14:59Z</t>
+          <t>2026-08-12T14:32:12Z</t>
         </is>
       </c>
     </row>
@@ -8386,7 +8386,7 @@
       </c>
       <c r="S97" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11T21:14:59Z</t>
+          <t>2026-08-12T14:32:12Z</t>
         </is>
       </c>
     </row>
@@ -8471,7 +8471,7 @@
       </c>
       <c r="S98" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11T21:14:59Z</t>
+          <t>2026-08-12T14:32:12Z</t>
         </is>
       </c>
     </row>
@@ -8556,7 +8556,7 @@
       </c>
       <c r="S99" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11T21:14:59Z</t>
+          <t>2026-08-12T14:32:12Z</t>
         </is>
       </c>
     </row>
@@ -8641,7 +8641,7 @@
       </c>
       <c r="S100" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11T21:14:59Z</t>
+          <t>2026-08-12T14:32:12Z</t>
         </is>
       </c>
     </row>
@@ -8726,7 +8726,7 @@
       </c>
       <c r="S101" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11T21:14:59Z</t>
+          <t>2026-08-12T14:32:12Z</t>
         </is>
       </c>
     </row>
@@ -8811,7 +8811,7 @@
       </c>
       <c r="S102" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11T21:14:59Z</t>
+          <t>2026-08-12T14:32:12Z</t>
         </is>
       </c>
     </row>
@@ -8896,7 +8896,7 @@
       </c>
       <c r="S103" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11T21:14:59Z</t>
+          <t>2026-08-12T14:32:12Z</t>
         </is>
       </c>
     </row>
@@ -8981,7 +8981,7 @@
       </c>
       <c r="S104" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11T21:14:59Z</t>
+          <t>2026-08-12T14:32:12Z</t>
         </is>
       </c>
     </row>
@@ -9066,7 +9066,7 @@
       </c>
       <c r="S105" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11T21:14:59Z</t>
+          <t>2026-08-12T14:32:12Z</t>
         </is>
       </c>
     </row>
@@ -9151,7 +9151,7 @@
       </c>
       <c r="S106" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11T21:14:59Z</t>
+          <t>2026-08-12T14:32:12Z</t>
         </is>
       </c>
     </row>
@@ -9236,7 +9236,7 @@
       </c>
       <c r="S107" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11T21:14:59Z</t>
+          <t>2026-08-12T14:32:12Z</t>
         </is>
       </c>
     </row>
@@ -9321,7 +9321,7 @@
       </c>
       <c r="S108" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11T21:14:59Z</t>
+          <t>2026-08-12T14:32:12Z</t>
         </is>
       </c>
     </row>
@@ -9406,7 +9406,7 @@
       </c>
       <c r="S109" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11T21:14:59Z</t>
+          <t>2026-08-12T14:32:12Z</t>
         </is>
       </c>
     </row>
@@ -9491,7 +9491,7 @@
       </c>
       <c r="S110" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11T21:14:59Z</t>
+          <t>2026-08-12T14:32:12Z</t>
         </is>
       </c>
     </row>
@@ -9576,7 +9576,7 @@
       </c>
       <c r="S111" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11T21:14:59Z</t>
+          <t>2026-08-12T14:32:12Z</t>
         </is>
       </c>
     </row>
@@ -9661,7 +9661,7 @@
       </c>
       <c r="S112" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11T21:14:59Z</t>
+          <t>2026-08-12T14:32:12Z</t>
         </is>
       </c>
     </row>
@@ -9746,7 +9746,7 @@
       </c>
       <c r="S113" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11T21:14:59Z</t>
+          <t>2026-08-12T14:32:12Z</t>
         </is>
       </c>
     </row>
@@ -9831,7 +9831,7 @@
       </c>
       <c r="S114" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11T21:14:59Z</t>
+          <t>2026-08-12T14:32:12Z</t>
         </is>
       </c>
     </row>
@@ -9916,7 +9916,7 @@
       </c>
       <c r="S115" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11T21:14:59Z</t>
+          <t>2026-08-12T14:32:12Z</t>
         </is>
       </c>
     </row>
@@ -10001,7 +10001,7 @@
       </c>
       <c r="S116" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11T21:14:59Z</t>
+          <t>2026-08-12T14:32:12Z</t>
         </is>
       </c>
     </row>
@@ -10086,7 +10086,7 @@
       </c>
       <c r="S117" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11T21:14:59Z</t>
+          <t>2026-08-12T14:32:12Z</t>
         </is>
       </c>
     </row>
@@ -10171,7 +10171,7 @@
       </c>
       <c r="S118" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11T21:14:59Z</t>
+          <t>2026-08-12T14:32:12Z</t>
         </is>
       </c>
     </row>
@@ -10256,7 +10256,7 @@
       </c>
       <c r="S119" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11T21:14:59Z</t>
+          <t>2026-08-12T14:32:12Z</t>
         </is>
       </c>
     </row>
@@ -10341,7 +10341,7 @@
       </c>
       <c r="S120" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11T21:14:59Z</t>
+          <t>2026-08-12T14:32:12Z</t>
         </is>
       </c>
     </row>
@@ -10426,7 +10426,7 @@
       </c>
       <c r="S121" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11T21:14:59Z</t>
+          <t>2026-08-12T14:32:12Z</t>
         </is>
       </c>
     </row>
@@ -10511,7 +10511,7 @@
       </c>
       <c r="S122" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11T21:14:59Z</t>
+          <t>2026-08-12T14:32:12Z</t>
         </is>
       </c>
     </row>
@@ -10596,7 +10596,7 @@
       </c>
       <c r="S123" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11T21:14:59Z</t>
+          <t>2026-08-12T14:32:12Z</t>
         </is>
       </c>
     </row>
@@ -10681,7 +10681,7 @@
       </c>
       <c r="S124" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11T21:14:59Z</t>
+          <t>2026-08-12T14:32:12Z</t>
         </is>
       </c>
     </row>
@@ -10766,7 +10766,7 @@
       </c>
       <c r="S125" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11T21:14:59Z</t>
+          <t>2026-08-12T14:32:12Z</t>
         </is>
       </c>
     </row>
@@ -10851,7 +10851,7 @@
       </c>
       <c r="S126" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11T21:14:59Z</t>
+          <t>2026-08-12T14:32:12Z</t>
         </is>
       </c>
     </row>
@@ -10936,7 +10936,7 @@
       </c>
       <c r="S127" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11T21:14:59Z</t>
+          <t>2026-08-12T14:32:12Z</t>
         </is>
       </c>
     </row>
@@ -11021,7 +11021,7 @@
       </c>
       <c r="S128" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11T21:14:59Z</t>
+          <t>2026-08-12T14:32:12Z</t>
         </is>
       </c>
     </row>
@@ -11106,7 +11106,7 @@
       </c>
       <c r="S129" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11T21:14:59Z</t>
+          <t>2026-08-12T14:32:12Z</t>
         </is>
       </c>
     </row>
@@ -11191,7 +11191,7 @@
       </c>
       <c r="S130" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11T21:14:59Z</t>
+          <t>2026-08-12T14:32:12Z</t>
         </is>
       </c>
     </row>
@@ -11276,7 +11276,7 @@
       </c>
       <c r="S131" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11T21:14:59Z</t>
+          <t>2026-08-12T14:32:12Z</t>
         </is>
       </c>
     </row>
@@ -11361,7 +11361,7 @@
       </c>
       <c r="S132" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11T21:14:59Z</t>
+          <t>2026-08-12T14:32:12Z</t>
         </is>
       </c>
     </row>
@@ -11446,7 +11446,7 @@
       </c>
       <c r="S133" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11T21:14:59Z</t>
+          <t>2026-08-12T14:32:12Z</t>
         </is>
       </c>
     </row>
@@ -11531,7 +11531,7 @@
       </c>
       <c r="S134" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11T21:14:59Z</t>
+          <t>2026-08-12T14:32:12Z</t>
         </is>
       </c>
     </row>
@@ -11616,7 +11616,7 @@
       </c>
       <c r="S135" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11T21:14:59Z</t>
+          <t>2026-08-12T14:32:12Z</t>
         </is>
       </c>
     </row>
@@ -11701,7 +11701,7 @@
       </c>
       <c r="S136" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11T21:14:59Z</t>
+          <t>2026-08-12T14:32:12Z</t>
         </is>
       </c>
     </row>
@@ -11786,7 +11786,7 @@
       </c>
       <c r="S137" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11T21:14:59Z</t>
+          <t>2026-08-12T14:32:12Z</t>
         </is>
       </c>
     </row>
@@ -11871,7 +11871,7 @@
       </c>
       <c r="S138" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11T21:14:59Z</t>
+          <t>2026-08-12T14:32:12Z</t>
         </is>
       </c>
     </row>
@@ -11956,7 +11956,7 @@
       </c>
       <c r="S139" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11T21:14:59Z</t>
+          <t>2026-08-12T14:32:12Z</t>
         </is>
       </c>
     </row>
@@ -12041,7 +12041,7 @@
       </c>
       <c r="S140" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11T21:14:59Z</t>
+          <t>2026-08-12T14:32:12Z</t>
         </is>
       </c>
     </row>
@@ -12126,7 +12126,7 @@
       </c>
       <c r="S141" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11T21:14:59Z</t>
+          <t>2026-08-12T14:32:12Z</t>
         </is>
       </c>
     </row>
@@ -12258,7 +12258,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11T21:14:59Z</t>
+          <t>2026-08-12T14:32:12Z</t>
         </is>
       </c>
     </row>
@@ -12338,7 +12338,7 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>{"dataset_id": "bcv_pib_historico_anual", "title": "Producto interno bruto histórico anual", "table": "PIB histórico anual", "source_file": "7_1_14_anual.xls", "base": "1957/1968/1984/1997", "price_type": "Precios constantes", "measure": "Nivel", "frequency": "Anual", "period": "2017", "year": 2017, "quarter": null, "classification": "Total economía", "component": "Producto interno bruto", "value": 392393.12, "unit": "Millones de bolívares a precios constantes", "status": "", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/7_1_14_anual.xls", "fetched_at": "2026-08-11T21:14:59Z"}</t>
+          <t>{"dataset_id": "bcv_pib_historico_anual", "title": "Producto interno bruto histórico anual", "table": "PIB histórico anual", "source_file": "7_1_14_anual.xls", "base": "1957/1968/1984/1997", "price_type": "Precios constantes", "measure": "Nivel", "frequency": "Anual", "period": "2017", "year": 2017, "quarter": null, "classification": "Total economía", "component": "Producto interno bruto", "value": 392393.12, "unit": "Millones de bolívares a precios constantes", "status": "", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/7_1_14_anual.xls", "fetched_at": "2026-08-12T14:32:12Z"}</t>
         </is>
       </c>
     </row>

--- a/assets/data/bcv/excel/ove_bcv_pib_historico_anual.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_pib_historico_anual.xlsx
@@ -736,7 +736,7 @@
       </c>
       <c r="S7" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T14:32:12Z</t>
+          <t>2026-08-12T21:12:48Z</t>
         </is>
       </c>
     </row>
@@ -821,7 +821,7 @@
       </c>
       <c r="S8" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T14:32:12Z</t>
+          <t>2026-08-12T21:12:48Z</t>
         </is>
       </c>
     </row>
@@ -906,7 +906,7 @@
       </c>
       <c r="S9" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T14:32:12Z</t>
+          <t>2026-08-12T21:12:48Z</t>
         </is>
       </c>
     </row>
@@ -991,7 +991,7 @@
       </c>
       <c r="S10" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T14:32:12Z</t>
+          <t>2026-08-12T21:12:48Z</t>
         </is>
       </c>
     </row>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="S11" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T14:32:12Z</t>
+          <t>2026-08-12T21:12:48Z</t>
         </is>
       </c>
     </row>
@@ -1161,7 +1161,7 @@
       </c>
       <c r="S12" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T14:32:12Z</t>
+          <t>2026-08-12T21:12:48Z</t>
         </is>
       </c>
     </row>
@@ -1246,7 +1246,7 @@
       </c>
       <c r="S13" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T14:32:12Z</t>
+          <t>2026-08-12T21:12:48Z</t>
         </is>
       </c>
     </row>
@@ -1331,7 +1331,7 @@
       </c>
       <c r="S14" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T14:32:12Z</t>
+          <t>2026-08-12T21:12:48Z</t>
         </is>
       </c>
     </row>
@@ -1416,7 +1416,7 @@
       </c>
       <c r="S15" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T14:32:12Z</t>
+          <t>2026-08-12T21:12:48Z</t>
         </is>
       </c>
     </row>
@@ -1501,7 +1501,7 @@
       </c>
       <c r="S16" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T14:32:12Z</t>
+          <t>2026-08-12T21:12:48Z</t>
         </is>
       </c>
     </row>
@@ -1586,7 +1586,7 @@
       </c>
       <c r="S17" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T14:32:12Z</t>
+          <t>2026-08-12T21:12:48Z</t>
         </is>
       </c>
     </row>
@@ -1671,7 +1671,7 @@
       </c>
       <c r="S18" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T14:32:12Z</t>
+          <t>2026-08-12T21:12:48Z</t>
         </is>
       </c>
     </row>
@@ -1756,7 +1756,7 @@
       </c>
       <c r="S19" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T14:32:12Z</t>
+          <t>2026-08-12T21:12:48Z</t>
         </is>
       </c>
     </row>
@@ -1841,7 +1841,7 @@
       </c>
       <c r="S20" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T14:32:12Z</t>
+          <t>2026-08-12T21:12:48Z</t>
         </is>
       </c>
     </row>
@@ -1926,7 +1926,7 @@
       </c>
       <c r="S21" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T14:32:12Z</t>
+          <t>2026-08-12T21:12:48Z</t>
         </is>
       </c>
     </row>
@@ -2011,7 +2011,7 @@
       </c>
       <c r="S22" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T14:32:12Z</t>
+          <t>2026-08-12T21:12:48Z</t>
         </is>
       </c>
     </row>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="S23" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T14:32:12Z</t>
+          <t>2026-08-12T21:12:48Z</t>
         </is>
       </c>
     </row>
@@ -2181,7 +2181,7 @@
       </c>
       <c r="S24" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T14:32:12Z</t>
+          <t>2026-08-12T21:12:48Z</t>
         </is>
       </c>
     </row>
@@ -2266,7 +2266,7 @@
       </c>
       <c r="S25" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T14:32:12Z</t>
+          <t>2026-08-12T21:12:48Z</t>
         </is>
       </c>
     </row>
@@ -2351,7 +2351,7 @@
       </c>
       <c r="S26" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T14:32:12Z</t>
+          <t>2026-08-12T21:12:48Z</t>
         </is>
       </c>
     </row>
@@ -2436,7 +2436,7 @@
       </c>
       <c r="S27" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T14:32:12Z</t>
+          <t>2026-08-12T21:12:48Z</t>
         </is>
       </c>
     </row>
@@ -2521,7 +2521,7 @@
       </c>
       <c r="S28" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T14:32:12Z</t>
+          <t>2026-08-12T21:12:48Z</t>
         </is>
       </c>
     </row>
@@ -2606,7 +2606,7 @@
       </c>
       <c r="S29" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T14:32:12Z</t>
+          <t>2026-08-12T21:12:48Z</t>
         </is>
       </c>
     </row>
@@ -2691,7 +2691,7 @@
       </c>
       <c r="S30" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T14:32:12Z</t>
+          <t>2026-08-12T21:12:48Z</t>
         </is>
       </c>
     </row>
@@ -2776,7 +2776,7 @@
       </c>
       <c r="S31" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T14:32:12Z</t>
+          <t>2026-08-12T21:12:48Z</t>
         </is>
       </c>
     </row>
@@ -2861,7 +2861,7 @@
       </c>
       <c r="S32" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T14:32:12Z</t>
+          <t>2026-08-12T21:12:48Z</t>
         </is>
       </c>
     </row>
@@ -2946,7 +2946,7 @@
       </c>
       <c r="S33" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T14:32:12Z</t>
+          <t>2026-08-12T21:12:48Z</t>
         </is>
       </c>
     </row>
@@ -3031,7 +3031,7 @@
       </c>
       <c r="S34" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T14:32:12Z</t>
+          <t>2026-08-12T21:12:48Z</t>
         </is>
       </c>
     </row>
@@ -3116,7 +3116,7 @@
       </c>
       <c r="S35" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T14:32:12Z</t>
+          <t>2026-08-12T21:12:48Z</t>
         </is>
       </c>
     </row>
@@ -3201,7 +3201,7 @@
       </c>
       <c r="S36" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T14:32:12Z</t>
+          <t>2026-08-12T21:12:48Z</t>
         </is>
       </c>
     </row>
@@ -3286,7 +3286,7 @@
       </c>
       <c r="S37" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T14:32:12Z</t>
+          <t>2026-08-12T21:12:48Z</t>
         </is>
       </c>
     </row>
@@ -3371,7 +3371,7 @@
       </c>
       <c r="S38" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T14:32:12Z</t>
+          <t>2026-08-12T21:12:48Z</t>
         </is>
       </c>
     </row>
@@ -3456,7 +3456,7 @@
       </c>
       <c r="S39" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T14:32:12Z</t>
+          <t>2026-08-12T21:12:48Z</t>
         </is>
       </c>
     </row>
@@ -3541,7 +3541,7 @@
       </c>
       <c r="S40" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T14:32:12Z</t>
+          <t>2026-08-12T21:12:48Z</t>
         </is>
       </c>
     </row>
@@ -3626,7 +3626,7 @@
       </c>
       <c r="S41" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T14:32:12Z</t>
+          <t>2026-08-12T21:12:48Z</t>
         </is>
       </c>
     </row>
@@ -3711,7 +3711,7 @@
       </c>
       <c r="S42" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T14:32:12Z</t>
+          <t>2026-08-12T21:12:48Z</t>
         </is>
       </c>
     </row>
@@ -3796,7 +3796,7 @@
       </c>
       <c r="S43" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T14:32:12Z</t>
+          <t>2026-08-12T21:12:48Z</t>
         </is>
       </c>
     </row>
@@ -3881,7 +3881,7 @@
       </c>
       <c r="S44" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T14:32:12Z</t>
+          <t>2026-08-12T21:12:48Z</t>
         </is>
       </c>
     </row>
@@ -3966,7 +3966,7 @@
       </c>
       <c r="S45" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T14:32:12Z</t>
+          <t>2026-08-12T21:12:48Z</t>
         </is>
       </c>
     </row>
@@ -4051,7 +4051,7 @@
       </c>
       <c r="S46" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T14:32:12Z</t>
+          <t>2026-08-12T21:12:48Z</t>
         </is>
       </c>
     </row>
@@ -4136,7 +4136,7 @@
       </c>
       <c r="S47" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T14:32:12Z</t>
+          <t>2026-08-12T21:12:48Z</t>
         </is>
       </c>
     </row>
@@ -4221,7 +4221,7 @@
       </c>
       <c r="S48" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T14:32:12Z</t>
+          <t>2026-08-12T21:12:48Z</t>
         </is>
       </c>
     </row>
@@ -4306,7 +4306,7 @@
       </c>
       <c r="S49" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T14:32:12Z</t>
+          <t>2026-08-12T21:12:48Z</t>
         </is>
       </c>
     </row>
@@ -4391,7 +4391,7 @@
       </c>
       <c r="S50" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T14:32:12Z</t>
+          <t>2026-08-12T21:12:48Z</t>
         </is>
       </c>
     </row>
@@ -4476,7 +4476,7 @@
       </c>
       <c r="S51" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T14:32:12Z</t>
+          <t>2026-08-12T21:12:48Z</t>
         </is>
       </c>
     </row>
@@ -4561,7 +4561,7 @@
       </c>
       <c r="S52" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T14:32:12Z</t>
+          <t>2026-08-12T21:12:48Z</t>
         </is>
       </c>
     </row>
@@ -4646,7 +4646,7 @@
       </c>
       <c r="S53" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T14:32:12Z</t>
+          <t>2026-08-12T21:12:48Z</t>
         </is>
       </c>
     </row>
@@ -4731,7 +4731,7 @@
       </c>
       <c r="S54" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T14:32:12Z</t>
+          <t>2026-08-12T21:12:48Z</t>
         </is>
       </c>
     </row>
@@ -4816,7 +4816,7 @@
       </c>
       <c r="S55" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T14:32:12Z</t>
+          <t>2026-08-12T21:12:48Z</t>
         </is>
       </c>
     </row>
@@ -4901,7 +4901,7 @@
       </c>
       <c r="S56" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T14:32:12Z</t>
+          <t>2026-08-12T21:12:48Z</t>
         </is>
       </c>
     </row>
@@ -4986,7 +4986,7 @@
       </c>
       <c r="S57" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T14:32:12Z</t>
+          <t>2026-08-12T21:12:48Z</t>
         </is>
       </c>
     </row>
@@ -5071,7 +5071,7 @@
       </c>
       <c r="S58" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T14:32:12Z</t>
+          <t>2026-08-12T21:12:48Z</t>
         </is>
       </c>
     </row>
@@ -5156,7 +5156,7 @@
       </c>
       <c r="S59" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T14:32:12Z</t>
+          <t>2026-08-12T21:12:48Z</t>
         </is>
       </c>
     </row>
@@ -5241,7 +5241,7 @@
       </c>
       <c r="S60" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T14:32:12Z</t>
+          <t>2026-08-12T21:12:48Z</t>
         </is>
       </c>
     </row>
@@ -5326,7 +5326,7 @@
       </c>
       <c r="S61" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T14:32:12Z</t>
+          <t>2026-08-12T21:12:48Z</t>
         </is>
       </c>
     </row>
@@ -5411,7 +5411,7 @@
       </c>
       <c r="S62" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T14:32:12Z</t>
+          <t>2026-08-12T21:12:48Z</t>
         </is>
       </c>
     </row>
@@ -5496,7 +5496,7 @@
       </c>
       <c r="S63" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T14:32:12Z</t>
+          <t>2026-08-12T21:12:48Z</t>
         </is>
       </c>
     </row>
@@ -5581,7 +5581,7 @@
       </c>
       <c r="S64" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T14:32:12Z</t>
+          <t>2026-08-12T21:12:48Z</t>
         </is>
       </c>
     </row>
@@ -5666,7 +5666,7 @@
       </c>
       <c r="S65" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T14:32:12Z</t>
+          <t>2026-08-12T21:12:48Z</t>
         </is>
       </c>
     </row>
@@ -5751,7 +5751,7 @@
       </c>
       <c r="S66" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T14:32:12Z</t>
+          <t>2026-08-12T21:12:48Z</t>
         </is>
       </c>
     </row>
@@ -5836,7 +5836,7 @@
       </c>
       <c r="S67" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T14:32:12Z</t>
+          <t>2026-08-12T21:12:48Z</t>
         </is>
       </c>
     </row>
@@ -5921,7 +5921,7 @@
       </c>
       <c r="S68" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T14:32:12Z</t>
+          <t>2026-08-12T21:12:48Z</t>
         </is>
       </c>
     </row>
@@ -6006,7 +6006,7 @@
       </c>
       <c r="S69" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T14:32:12Z</t>
+          <t>2026-08-12T21:12:48Z</t>
         </is>
       </c>
     </row>
@@ -6091,7 +6091,7 @@
       </c>
       <c r="S70" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T14:32:12Z</t>
+          <t>2026-08-12T21:12:48Z</t>
         </is>
       </c>
     </row>
@@ -6176,7 +6176,7 @@
       </c>
       <c r="S71" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T14:32:12Z</t>
+          <t>2026-08-12T21:12:48Z</t>
         </is>
       </c>
     </row>
@@ -6261,7 +6261,7 @@
       </c>
       <c r="S72" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T14:32:12Z</t>
+          <t>2026-08-12T21:12:48Z</t>
         </is>
       </c>
     </row>
@@ -6346,7 +6346,7 @@
       </c>
       <c r="S73" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T14:32:12Z</t>
+          <t>2026-08-12T21:12:48Z</t>
         </is>
       </c>
     </row>
@@ -6431,7 +6431,7 @@
       </c>
       <c r="S74" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T14:32:12Z</t>
+          <t>2026-08-12T21:12:48Z</t>
         </is>
       </c>
     </row>
@@ -6516,7 +6516,7 @@
       </c>
       <c r="S75" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T14:32:12Z</t>
+          <t>2026-08-12T21:12:48Z</t>
         </is>
       </c>
     </row>
@@ -6601,7 +6601,7 @@
       </c>
       <c r="S76" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T14:32:12Z</t>
+          <t>2026-08-12T21:12:48Z</t>
         </is>
       </c>
     </row>
@@ -6686,7 +6686,7 @@
       </c>
       <c r="S77" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T14:32:12Z</t>
+          <t>2026-08-12T21:12:48Z</t>
         </is>
       </c>
     </row>
@@ -6771,7 +6771,7 @@
       </c>
       <c r="S78" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T14:32:12Z</t>
+          <t>2026-08-12T21:12:48Z</t>
         </is>
       </c>
     </row>
@@ -6856,7 +6856,7 @@
       </c>
       <c r="S79" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T14:32:12Z</t>
+          <t>2026-08-12T21:12:48Z</t>
         </is>
       </c>
     </row>
@@ -6941,7 +6941,7 @@
       </c>
       <c r="S80" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T14:32:12Z</t>
+          <t>2026-08-12T21:12:48Z</t>
         </is>
       </c>
     </row>
@@ -7026,7 +7026,7 @@
       </c>
       <c r="S81" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T14:32:12Z</t>
+          <t>2026-08-12T21:12:48Z</t>
         </is>
       </c>
     </row>
@@ -7111,7 +7111,7 @@
       </c>
       <c r="S82" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T14:32:12Z</t>
+          <t>2026-08-12T21:12:48Z</t>
         </is>
       </c>
     </row>
@@ -7196,7 +7196,7 @@
       </c>
       <c r="S83" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T14:32:12Z</t>
+          <t>2026-08-12T21:12:48Z</t>
         </is>
       </c>
     </row>
@@ -7281,7 +7281,7 @@
       </c>
       <c r="S84" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T14:32:12Z</t>
+          <t>2026-08-12T21:12:48Z</t>
         </is>
       </c>
     </row>
@@ -7366,7 +7366,7 @@
       </c>
       <c r="S85" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T14:32:12Z</t>
+          <t>2026-08-12T21:12:48Z</t>
         </is>
       </c>
     </row>
@@ -7451,7 +7451,7 @@
       </c>
       <c r="S86" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T14:32:12Z</t>
+          <t>2026-08-12T21:12:48Z</t>
         </is>
       </c>
     </row>
@@ -7536,7 +7536,7 @@
       </c>
       <c r="S87" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T14:32:12Z</t>
+          <t>2026-08-12T21:12:48Z</t>
         </is>
       </c>
     </row>
@@ -7621,7 +7621,7 @@
       </c>
       <c r="S88" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T14:32:12Z</t>
+          <t>2026-08-12T21:12:48Z</t>
         </is>
       </c>
     </row>
@@ -7706,7 +7706,7 @@
       </c>
       <c r="S89" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T14:32:12Z</t>
+          <t>2026-08-12T21:12:48Z</t>
         </is>
       </c>
     </row>
@@ -7791,7 +7791,7 @@
       </c>
       <c r="S90" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T14:32:12Z</t>
+          <t>2026-08-12T21:12:48Z</t>
         </is>
       </c>
     </row>
@@ -7876,7 +7876,7 @@
       </c>
       <c r="S91" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T14:32:12Z</t>
+          <t>2026-08-12T21:12:48Z</t>
         </is>
       </c>
     </row>
@@ -7961,7 +7961,7 @@
       </c>
       <c r="S92" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T14:32:12Z</t>
+          <t>2026-08-12T21:12:48Z</t>
         </is>
       </c>
     </row>
@@ -8046,7 +8046,7 @@
       </c>
       <c r="S93" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T14:32:12Z</t>
+          <t>2026-08-12T21:12:48Z</t>
         </is>
       </c>
     </row>
@@ -8131,7 +8131,7 @@
       </c>
       <c r="S94" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T14:32:12Z</t>
+          <t>2026-08-12T21:12:48Z</t>
         </is>
       </c>
     </row>
@@ -8216,7 +8216,7 @@
       </c>
       <c r="S95" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T14:32:12Z</t>
+          <t>2026-08-12T21:12:48Z</t>
         </is>
       </c>
     </row>
@@ -8301,7 +8301,7 @@
       </c>
       <c r="S96" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T14:32:12Z</t>
+          <t>2026-08-12T21:12:48Z</t>
         </is>
       </c>
     </row>
@@ -8386,7 +8386,7 @@
       </c>
       <c r="S97" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T14:32:12Z</t>
+          <t>2026-08-12T21:12:48Z</t>
         </is>
       </c>
     </row>
@@ -8471,7 +8471,7 @@
       </c>
       <c r="S98" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T14:32:12Z</t>
+          <t>2026-08-12T21:12:48Z</t>
         </is>
       </c>
     </row>
@@ -8556,7 +8556,7 @@
       </c>
       <c r="S99" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T14:32:12Z</t>
+          <t>2026-08-12T21:12:48Z</t>
         </is>
       </c>
     </row>
@@ -8641,7 +8641,7 @@
       </c>
       <c r="S100" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T14:32:12Z</t>
+          <t>2026-08-12T21:12:48Z</t>
         </is>
       </c>
     </row>
@@ -8726,7 +8726,7 @@
       </c>
       <c r="S101" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T14:32:12Z</t>
+          <t>2026-08-12T21:12:48Z</t>
         </is>
       </c>
     </row>
@@ -8811,7 +8811,7 @@
       </c>
       <c r="S102" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T14:32:12Z</t>
+          <t>2026-08-12T21:12:48Z</t>
         </is>
       </c>
     </row>
@@ -8896,7 +8896,7 @@
       </c>
       <c r="S103" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T14:32:12Z</t>
+          <t>2026-08-12T21:12:48Z</t>
         </is>
       </c>
     </row>
@@ -8981,7 +8981,7 @@
       </c>
       <c r="S104" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T14:32:12Z</t>
+          <t>2026-08-12T21:12:48Z</t>
         </is>
       </c>
     </row>
@@ -9066,7 +9066,7 @@
       </c>
       <c r="S105" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T14:32:12Z</t>
+          <t>2026-08-12T21:12:48Z</t>
         </is>
       </c>
     </row>
@@ -9151,7 +9151,7 @@
       </c>
       <c r="S106" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T14:32:12Z</t>
+          <t>2026-08-12T21:12:48Z</t>
         </is>
       </c>
     </row>
@@ -9236,7 +9236,7 @@
       </c>
       <c r="S107" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T14:32:12Z</t>
+          <t>2026-08-12T21:12:48Z</t>
         </is>
       </c>
     </row>
@@ -9321,7 +9321,7 @@
       </c>
       <c r="S108" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T14:32:12Z</t>
+          <t>2026-08-12T21:12:48Z</t>
         </is>
       </c>
     </row>
@@ -9406,7 +9406,7 @@
       </c>
       <c r="S109" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T14:32:12Z</t>
+          <t>2026-08-12T21:12:48Z</t>
         </is>
       </c>
     </row>
@@ -9491,7 +9491,7 @@
       </c>
       <c r="S110" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T14:32:12Z</t>
+          <t>2026-08-12T21:12:48Z</t>
         </is>
       </c>
     </row>
@@ -9576,7 +9576,7 @@
       </c>
       <c r="S111" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T14:32:12Z</t>
+          <t>2026-08-12T21:12:48Z</t>
         </is>
       </c>
     </row>
@@ -9661,7 +9661,7 @@
       </c>
       <c r="S112" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T14:32:12Z</t>
+          <t>2026-08-12T21:12:48Z</t>
         </is>
       </c>
     </row>
@@ -9746,7 +9746,7 @@
       </c>
       <c r="S113" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T14:32:12Z</t>
+          <t>2026-08-12T21:12:48Z</t>
         </is>
       </c>
     </row>
@@ -9831,7 +9831,7 @@
       </c>
       <c r="S114" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T14:32:12Z</t>
+          <t>2026-08-12T21:12:48Z</t>
         </is>
       </c>
     </row>
@@ -9916,7 +9916,7 @@
       </c>
       <c r="S115" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T14:32:12Z</t>
+          <t>2026-08-12T21:12:48Z</t>
         </is>
       </c>
     </row>
@@ -10001,7 +10001,7 @@
       </c>
       <c r="S116" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T14:32:12Z</t>
+          <t>2026-08-12T21:12:48Z</t>
         </is>
       </c>
     </row>
@@ -10086,7 +10086,7 @@
       </c>
       <c r="S117" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T14:32:12Z</t>
+          <t>2026-08-12T21:12:48Z</t>
         </is>
       </c>
     </row>
@@ -10171,7 +10171,7 @@
       </c>
       <c r="S118" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T14:32:12Z</t>
+          <t>2026-08-12T21:12:48Z</t>
         </is>
       </c>
     </row>
@@ -10256,7 +10256,7 @@
       </c>
       <c r="S119" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T14:32:12Z</t>
+          <t>2026-08-12T21:12:48Z</t>
         </is>
       </c>
     </row>
@@ -10341,7 +10341,7 @@
       </c>
       <c r="S120" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T14:32:12Z</t>
+          <t>2026-08-12T21:12:48Z</t>
         </is>
       </c>
     </row>
@@ -10426,7 +10426,7 @@
       </c>
       <c r="S121" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T14:32:12Z</t>
+          <t>2026-08-12T21:12:48Z</t>
         </is>
       </c>
     </row>
@@ -10511,7 +10511,7 @@
       </c>
       <c r="S122" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T14:32:12Z</t>
+          <t>2026-08-12T21:12:48Z</t>
         </is>
       </c>
     </row>
@@ -10596,7 +10596,7 @@
       </c>
       <c r="S123" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T14:32:12Z</t>
+          <t>2026-08-12T21:12:48Z</t>
         </is>
       </c>
     </row>
@@ -10681,7 +10681,7 @@
       </c>
       <c r="S124" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T14:32:12Z</t>
+          <t>2026-08-12T21:12:48Z</t>
         </is>
       </c>
     </row>
@@ -10766,7 +10766,7 @@
       </c>
       <c r="S125" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T14:32:12Z</t>
+          <t>2026-08-12T21:12:48Z</t>
         </is>
       </c>
     </row>
@@ -10851,7 +10851,7 @@
       </c>
       <c r="S126" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T14:32:12Z</t>
+          <t>2026-08-12T21:12:48Z</t>
         </is>
       </c>
     </row>
@@ -10936,7 +10936,7 @@
       </c>
       <c r="S127" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T14:32:12Z</t>
+          <t>2026-08-12T21:12:48Z</t>
         </is>
       </c>
     </row>
@@ -11021,7 +11021,7 @@
       </c>
       <c r="S128" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T14:32:12Z</t>
+          <t>2026-08-12T21:12:48Z</t>
         </is>
       </c>
     </row>
@@ -11106,7 +11106,7 @@
       </c>
       <c r="S129" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T14:32:12Z</t>
+          <t>2026-08-12T21:12:48Z</t>
         </is>
       </c>
     </row>
@@ -11191,7 +11191,7 @@
       </c>
       <c r="S130" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T14:32:12Z</t>
+          <t>2026-08-12T21:12:48Z</t>
         </is>
       </c>
     </row>
@@ -11276,7 +11276,7 @@
       </c>
       <c r="S131" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T14:32:12Z</t>
+          <t>2026-08-12T21:12:48Z</t>
         </is>
       </c>
     </row>
@@ -11361,7 +11361,7 @@
       </c>
       <c r="S132" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T14:32:12Z</t>
+          <t>2026-08-12T21:12:48Z</t>
         </is>
       </c>
     </row>
@@ -11446,7 +11446,7 @@
       </c>
       <c r="S133" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T14:32:12Z</t>
+          <t>2026-08-12T21:12:48Z</t>
         </is>
       </c>
     </row>
@@ -11531,7 +11531,7 @@
       </c>
       <c r="S134" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T14:32:12Z</t>
+          <t>2026-08-12T21:12:48Z</t>
         </is>
       </c>
     </row>
@@ -11616,7 +11616,7 @@
       </c>
       <c r="S135" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T14:32:12Z</t>
+          <t>2026-08-12T21:12:48Z</t>
         </is>
       </c>
     </row>
@@ -11701,7 +11701,7 @@
       </c>
       <c r="S136" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T14:32:12Z</t>
+          <t>2026-08-12T21:12:48Z</t>
         </is>
       </c>
     </row>
@@ -11786,7 +11786,7 @@
       </c>
       <c r="S137" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T14:32:12Z</t>
+          <t>2026-08-12T21:12:48Z</t>
         </is>
       </c>
     </row>
@@ -11871,7 +11871,7 @@
       </c>
       <c r="S138" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T14:32:12Z</t>
+          <t>2026-08-12T21:12:48Z</t>
         </is>
       </c>
     </row>
@@ -11956,7 +11956,7 @@
       </c>
       <c r="S139" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T14:32:12Z</t>
+          <t>2026-08-12T21:12:48Z</t>
         </is>
       </c>
     </row>
@@ -12041,7 +12041,7 @@
       </c>
       <c r="S140" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T14:32:12Z</t>
+          <t>2026-08-12T21:12:48Z</t>
         </is>
       </c>
     </row>
@@ -12126,7 +12126,7 @@
       </c>
       <c r="S141" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T14:32:12Z</t>
+          <t>2026-08-12T21:12:48Z</t>
         </is>
       </c>
     </row>
@@ -12258,7 +12258,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T14:32:12Z</t>
+          <t>2026-08-12T21:12:48Z</t>
         </is>
       </c>
     </row>
@@ -12338,7 +12338,7 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>{"dataset_id": "bcv_pib_historico_anual", "title": "Producto interno bruto histórico anual", "table": "PIB histórico anual", "source_file": "7_1_14_anual.xls", "base": "1957/1968/1984/1997", "price_type": "Precios constantes", "measure": "Nivel", "frequency": "Anual", "period": "2017", "year": 2017, "quarter": null, "classification": "Total economía", "component": "Producto interno bruto", "value": 392393.12, "unit": "Millones de bolívares a precios constantes", "status": "", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/7_1_14_anual.xls", "fetched_at": "2026-08-12T14:32:12Z"}</t>
+          <t>{"dataset_id": "bcv_pib_historico_anual", "title": "Producto interno bruto histórico anual", "table": "PIB histórico anual", "source_file": "7_1_14_anual.xls", "base": "1957/1968/1984/1997", "price_type": "Precios constantes", "measure": "Nivel", "frequency": "Anual", "period": "2017", "year": 2017, "quarter": null, "classification": "Total economía", "component": "Producto interno bruto", "value": 392393.12, "unit": "Millones de bolívares a precios constantes", "status": "", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/7_1_14_anual.xls", "fetched_at": "2026-08-12T21:12:48Z"}</t>
         </is>
       </c>
     </row>

--- a/assets/data/bcv/excel/ove_bcv_pib_historico_anual.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_pib_historico_anual.xlsx
@@ -736,7 +736,7 @@
       </c>
       <c r="S7" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T21:12:48Z</t>
+          <t>2026-08-13T21:12:34Z</t>
         </is>
       </c>
     </row>
@@ -821,7 +821,7 @@
       </c>
       <c r="S8" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T21:12:48Z</t>
+          <t>2026-08-13T21:12:34Z</t>
         </is>
       </c>
     </row>
@@ -906,7 +906,7 @@
       </c>
       <c r="S9" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T21:12:48Z</t>
+          <t>2026-08-13T21:12:34Z</t>
         </is>
       </c>
     </row>
@@ -991,7 +991,7 @@
       </c>
       <c r="S10" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T21:12:48Z</t>
+          <t>2026-08-13T21:12:34Z</t>
         </is>
       </c>
     </row>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="S11" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T21:12:48Z</t>
+          <t>2026-08-13T21:12:34Z</t>
         </is>
       </c>
     </row>
@@ -1161,7 +1161,7 @@
       </c>
       <c r="S12" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T21:12:48Z</t>
+          <t>2026-08-13T21:12:34Z</t>
         </is>
       </c>
     </row>
@@ -1246,7 +1246,7 @@
       </c>
       <c r="S13" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T21:12:48Z</t>
+          <t>2026-08-13T21:12:34Z</t>
         </is>
       </c>
     </row>
@@ -1331,7 +1331,7 @@
       </c>
       <c r="S14" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T21:12:48Z</t>
+          <t>2026-08-13T21:12:34Z</t>
         </is>
       </c>
     </row>
@@ -1416,7 +1416,7 @@
       </c>
       <c r="S15" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T21:12:48Z</t>
+          <t>2026-08-13T21:12:34Z</t>
         </is>
       </c>
     </row>
@@ -1501,7 +1501,7 @@
       </c>
       <c r="S16" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T21:12:48Z</t>
+          <t>2026-08-13T21:12:34Z</t>
         </is>
       </c>
     </row>
@@ -1586,7 +1586,7 @@
       </c>
       <c r="S17" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T21:12:48Z</t>
+          <t>2026-08-13T21:12:34Z</t>
         </is>
       </c>
     </row>
@@ -1671,7 +1671,7 @@
       </c>
       <c r="S18" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T21:12:48Z</t>
+          <t>2026-08-13T21:12:34Z</t>
         </is>
       </c>
     </row>
@@ -1756,7 +1756,7 @@
       </c>
       <c r="S19" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T21:12:48Z</t>
+          <t>2026-08-13T21:12:34Z</t>
         </is>
       </c>
     </row>
@@ -1841,7 +1841,7 @@
       </c>
       <c r="S20" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T21:12:48Z</t>
+          <t>2026-08-13T21:12:34Z</t>
         </is>
       </c>
     </row>
@@ -1926,7 +1926,7 @@
       </c>
       <c r="S21" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T21:12:48Z</t>
+          <t>2026-08-13T21:12:34Z</t>
         </is>
       </c>
     </row>
@@ -2011,7 +2011,7 @@
       </c>
       <c r="S22" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T21:12:48Z</t>
+          <t>2026-08-13T21:12:34Z</t>
         </is>
       </c>
     </row>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="S23" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T21:12:48Z</t>
+          <t>2026-08-13T21:12:34Z</t>
         </is>
       </c>
     </row>
@@ -2181,7 +2181,7 @@
       </c>
       <c r="S24" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T21:12:48Z</t>
+          <t>2026-08-13T21:12:34Z</t>
         </is>
       </c>
     </row>
@@ -2266,7 +2266,7 @@
       </c>
       <c r="S25" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T21:12:48Z</t>
+          <t>2026-08-13T21:12:34Z</t>
         </is>
       </c>
     </row>
@@ -2351,7 +2351,7 @@
       </c>
       <c r="S26" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T21:12:48Z</t>
+          <t>2026-08-13T21:12:34Z</t>
         </is>
       </c>
     </row>
@@ -2436,7 +2436,7 @@
       </c>
       <c r="S27" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T21:12:48Z</t>
+          <t>2026-08-13T21:12:34Z</t>
         </is>
       </c>
     </row>
@@ -2521,7 +2521,7 @@
       </c>
       <c r="S28" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T21:12:48Z</t>
+          <t>2026-08-13T21:12:34Z</t>
         </is>
       </c>
     </row>
@@ -2606,7 +2606,7 @@
       </c>
       <c r="S29" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T21:12:48Z</t>
+          <t>2026-08-13T21:12:34Z</t>
         </is>
       </c>
     </row>
@@ -2691,7 +2691,7 @@
       </c>
       <c r="S30" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T21:12:48Z</t>
+          <t>2026-08-13T21:12:34Z</t>
         </is>
       </c>
     </row>
@@ -2776,7 +2776,7 @@
       </c>
       <c r="S31" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T21:12:48Z</t>
+          <t>2026-08-13T21:12:34Z</t>
         </is>
       </c>
     </row>
@@ -2861,7 +2861,7 @@
       </c>
       <c r="S32" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T21:12:48Z</t>
+          <t>2026-08-13T21:12:34Z</t>
         </is>
       </c>
     </row>
@@ -2946,7 +2946,7 @@
       </c>
       <c r="S33" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T21:12:48Z</t>
+          <t>2026-08-13T21:12:34Z</t>
         </is>
       </c>
     </row>
@@ -3031,7 +3031,7 @@
       </c>
       <c r="S34" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T21:12:48Z</t>
+          <t>2026-08-13T21:12:34Z</t>
         </is>
       </c>
     </row>
@@ -3116,7 +3116,7 @@
       </c>
       <c r="S35" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T21:12:48Z</t>
+          <t>2026-08-13T21:12:34Z</t>
         </is>
       </c>
     </row>
@@ -3201,7 +3201,7 @@
       </c>
       <c r="S36" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T21:12:48Z</t>
+          <t>2026-08-13T21:12:34Z</t>
         </is>
       </c>
     </row>
@@ -3286,7 +3286,7 @@
       </c>
       <c r="S37" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T21:12:48Z</t>
+          <t>2026-08-13T21:12:34Z</t>
         </is>
       </c>
     </row>
@@ -3371,7 +3371,7 @@
       </c>
       <c r="S38" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T21:12:48Z</t>
+          <t>2026-08-13T21:12:34Z</t>
         </is>
       </c>
     </row>
@@ -3456,7 +3456,7 @@
       </c>
       <c r="S39" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T21:12:48Z</t>
+          <t>2026-08-13T21:12:34Z</t>
         </is>
       </c>
     </row>
@@ -3541,7 +3541,7 @@
       </c>
       <c r="S40" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T21:12:48Z</t>
+          <t>2026-08-13T21:12:34Z</t>
         </is>
       </c>
     </row>
@@ -3626,7 +3626,7 @@
       </c>
       <c r="S41" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T21:12:48Z</t>
+          <t>2026-08-13T21:12:34Z</t>
         </is>
       </c>
     </row>
@@ -3711,7 +3711,7 @@
       </c>
       <c r="S42" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T21:12:48Z</t>
+          <t>2026-08-13T21:12:34Z</t>
         </is>
       </c>
     </row>
@@ -3796,7 +3796,7 @@
       </c>
       <c r="S43" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T21:12:48Z</t>
+          <t>2026-08-13T21:12:34Z</t>
         </is>
       </c>
     </row>
@@ -3881,7 +3881,7 @@
       </c>
       <c r="S44" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T21:12:48Z</t>
+          <t>2026-08-13T21:12:34Z</t>
         </is>
       </c>
     </row>
@@ -3966,7 +3966,7 @@
       </c>
       <c r="S45" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T21:12:48Z</t>
+          <t>2026-08-13T21:12:34Z</t>
         </is>
       </c>
     </row>
@@ -4051,7 +4051,7 @@
       </c>
       <c r="S46" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T21:12:48Z</t>
+          <t>2026-08-13T21:12:34Z</t>
         </is>
       </c>
     </row>
@@ -4136,7 +4136,7 @@
       </c>
       <c r="S47" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T21:12:48Z</t>
+          <t>2026-08-13T21:12:34Z</t>
         </is>
       </c>
     </row>
@@ -4221,7 +4221,7 @@
       </c>
       <c r="S48" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T21:12:48Z</t>
+          <t>2026-08-13T21:12:34Z</t>
         </is>
       </c>
     </row>
@@ -4306,7 +4306,7 @@
       </c>
       <c r="S49" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T21:12:48Z</t>
+          <t>2026-08-13T21:12:34Z</t>
         </is>
       </c>
     </row>
@@ -4391,7 +4391,7 @@
       </c>
       <c r="S50" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T21:12:48Z</t>
+          <t>2026-08-13T21:12:34Z</t>
         </is>
       </c>
     </row>
@@ -4476,7 +4476,7 @@
       </c>
       <c r="S51" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T21:12:48Z</t>
+          <t>2026-08-13T21:12:34Z</t>
         </is>
       </c>
     </row>
@@ -4561,7 +4561,7 @@
       </c>
       <c r="S52" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T21:12:48Z</t>
+          <t>2026-08-13T21:12:34Z</t>
         </is>
       </c>
     </row>
@@ -4646,7 +4646,7 @@
       </c>
       <c r="S53" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T21:12:48Z</t>
+          <t>2026-08-13T21:12:34Z</t>
         </is>
       </c>
     </row>
@@ -4731,7 +4731,7 @@
       </c>
       <c r="S54" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T21:12:48Z</t>
+          <t>2026-08-13T21:12:34Z</t>
         </is>
       </c>
     </row>
@@ -4816,7 +4816,7 @@
       </c>
       <c r="S55" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T21:12:48Z</t>
+          <t>2026-08-13T21:12:34Z</t>
         </is>
       </c>
     </row>
@@ -4901,7 +4901,7 @@
       </c>
       <c r="S56" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T21:12:48Z</t>
+          <t>2026-08-13T21:12:34Z</t>
         </is>
       </c>
     </row>
@@ -4986,7 +4986,7 @@
       </c>
       <c r="S57" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T21:12:48Z</t>
+          <t>2026-08-13T21:12:34Z</t>
         </is>
       </c>
     </row>
@@ -5071,7 +5071,7 @@
       </c>
       <c r="S58" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T21:12:48Z</t>
+          <t>2026-08-13T21:12:34Z</t>
         </is>
       </c>
     </row>
@@ -5156,7 +5156,7 @@
       </c>
       <c r="S59" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T21:12:48Z</t>
+          <t>2026-08-13T21:12:34Z</t>
         </is>
       </c>
     </row>
@@ -5241,7 +5241,7 @@
       </c>
       <c r="S60" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T21:12:48Z</t>
+          <t>2026-08-13T21:12:34Z</t>
         </is>
       </c>
     </row>
@@ -5326,7 +5326,7 @@
       </c>
       <c r="S61" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T21:12:48Z</t>
+          <t>2026-08-13T21:12:34Z</t>
         </is>
       </c>
     </row>
@@ -5411,7 +5411,7 @@
       </c>
       <c r="S62" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T21:12:48Z</t>
+          <t>2026-08-13T21:12:34Z</t>
         </is>
       </c>
     </row>
@@ -5496,7 +5496,7 @@
       </c>
       <c r="S63" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T21:12:48Z</t>
+          <t>2026-08-13T21:12:34Z</t>
         </is>
       </c>
     </row>
@@ -5581,7 +5581,7 @@
       </c>
       <c r="S64" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T21:12:48Z</t>
+          <t>2026-08-13T21:12:34Z</t>
         </is>
       </c>
     </row>
@@ -5666,7 +5666,7 @@
       </c>
       <c r="S65" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T21:12:48Z</t>
+          <t>2026-08-13T21:12:34Z</t>
         </is>
       </c>
     </row>
@@ -5751,7 +5751,7 @@
       </c>
       <c r="S66" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T21:12:48Z</t>
+          <t>2026-08-13T21:12:34Z</t>
         </is>
       </c>
     </row>
@@ -5836,7 +5836,7 @@
       </c>
       <c r="S67" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T21:12:48Z</t>
+          <t>2026-08-13T21:12:34Z</t>
         </is>
       </c>
     </row>
@@ -5921,7 +5921,7 @@
       </c>
       <c r="S68" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T21:12:48Z</t>
+          <t>2026-08-13T21:12:34Z</t>
         </is>
       </c>
     </row>
@@ -6006,7 +6006,7 @@
       </c>
       <c r="S69" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T21:12:48Z</t>
+          <t>2026-08-13T21:12:34Z</t>
         </is>
       </c>
     </row>
@@ -6091,7 +6091,7 @@
       </c>
       <c r="S70" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T21:12:48Z</t>
+          <t>2026-08-13T21:12:34Z</t>
         </is>
       </c>
     </row>
@@ -6176,7 +6176,7 @@
       </c>
       <c r="S71" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T21:12:48Z</t>
+          <t>2026-08-13T21:12:34Z</t>
         </is>
       </c>
     </row>
@@ -6261,7 +6261,7 @@
       </c>
       <c r="S72" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T21:12:48Z</t>
+          <t>2026-08-13T21:12:34Z</t>
         </is>
       </c>
     </row>
@@ -6346,7 +6346,7 @@
       </c>
       <c r="S73" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T21:12:48Z</t>
+          <t>2026-08-13T21:12:34Z</t>
         </is>
       </c>
     </row>
@@ -6431,7 +6431,7 @@
       </c>
       <c r="S74" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T21:12:48Z</t>
+          <t>2026-08-13T21:12:34Z</t>
         </is>
       </c>
     </row>
@@ -6516,7 +6516,7 @@
       </c>
       <c r="S75" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T21:12:48Z</t>
+          <t>2026-08-13T21:12:34Z</t>
         </is>
       </c>
     </row>
@@ -6601,7 +6601,7 @@
       </c>
       <c r="S76" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T21:12:48Z</t>
+          <t>2026-08-13T21:12:34Z</t>
         </is>
       </c>
     </row>
@@ -6686,7 +6686,7 @@
       </c>
       <c r="S77" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T21:12:48Z</t>
+          <t>2026-08-13T21:12:34Z</t>
         </is>
       </c>
     </row>
@@ -6771,7 +6771,7 @@
       </c>
       <c r="S78" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T21:12:48Z</t>
+          <t>2026-08-13T21:12:34Z</t>
         </is>
       </c>
     </row>
@@ -6856,7 +6856,7 @@
       </c>
       <c r="S79" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T21:12:48Z</t>
+          <t>2026-08-13T21:12:34Z</t>
         </is>
       </c>
     </row>
@@ -6941,7 +6941,7 @@
       </c>
       <c r="S80" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T21:12:48Z</t>
+          <t>2026-08-13T21:12:34Z</t>
         </is>
       </c>
     </row>
@@ -7026,7 +7026,7 @@
       </c>
       <c r="S81" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T21:12:48Z</t>
+          <t>2026-08-13T21:12:34Z</t>
         </is>
       </c>
     </row>
@@ -7111,7 +7111,7 @@
       </c>
       <c r="S82" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T21:12:48Z</t>
+          <t>2026-08-13T21:12:34Z</t>
         </is>
       </c>
     </row>
@@ -7196,7 +7196,7 @@
       </c>
       <c r="S83" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T21:12:48Z</t>
+          <t>2026-08-13T21:12:34Z</t>
         </is>
       </c>
     </row>
@@ -7281,7 +7281,7 @@
       </c>
       <c r="S84" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T21:12:48Z</t>
+          <t>2026-08-13T21:12:34Z</t>
         </is>
       </c>
     </row>
@@ -7366,7 +7366,7 @@
       </c>
       <c r="S85" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T21:12:48Z</t>
+          <t>2026-08-13T21:12:34Z</t>
         </is>
       </c>
     </row>
@@ -7451,7 +7451,7 @@
       </c>
       <c r="S86" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T21:12:48Z</t>
+          <t>2026-08-13T21:12:34Z</t>
         </is>
       </c>
     </row>
@@ -7536,7 +7536,7 @@
       </c>
       <c r="S87" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T21:12:48Z</t>
+          <t>2026-08-13T21:12:34Z</t>
         </is>
       </c>
     </row>
@@ -7621,7 +7621,7 @@
       </c>
       <c r="S88" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T21:12:48Z</t>
+          <t>2026-08-13T21:12:34Z</t>
         </is>
       </c>
     </row>
@@ -7706,7 +7706,7 @@
       </c>
       <c r="S89" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T21:12:48Z</t>
+          <t>2026-08-13T21:12:34Z</t>
         </is>
       </c>
     </row>
@@ -7791,7 +7791,7 @@
       </c>
       <c r="S90" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T21:12:48Z</t>
+          <t>2026-08-13T21:12:34Z</t>
         </is>
       </c>
     </row>
@@ -7876,7 +7876,7 @@
       </c>
       <c r="S91" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T21:12:48Z</t>
+          <t>2026-08-13T21:12:34Z</t>
         </is>
       </c>
     </row>
@@ -7961,7 +7961,7 @@
       </c>
       <c r="S92" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T21:12:48Z</t>
+          <t>2026-08-13T21:12:34Z</t>
         </is>
       </c>
     </row>
@@ -8046,7 +8046,7 @@
       </c>
       <c r="S93" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T21:12:48Z</t>
+          <t>2026-08-13T21:12:34Z</t>
         </is>
       </c>
     </row>
@@ -8131,7 +8131,7 @@
       </c>
       <c r="S94" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T21:12:48Z</t>
+          <t>2026-08-13T21:12:34Z</t>
         </is>
       </c>
     </row>
@@ -8216,7 +8216,7 @@
       </c>
       <c r="S95" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T21:12:48Z</t>
+          <t>2026-08-13T21:12:34Z</t>
         </is>
       </c>
     </row>
@@ -8301,7 +8301,7 @@
       </c>
       <c r="S96" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T21:12:48Z</t>
+          <t>2026-08-13T21:12:34Z</t>
         </is>
       </c>
     </row>
@@ -8386,7 +8386,7 @@
       </c>
       <c r="S97" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T21:12:48Z</t>
+          <t>2026-08-13T21:12:34Z</t>
         </is>
       </c>
     </row>
@@ -8471,7 +8471,7 @@
       </c>
       <c r="S98" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T21:12:48Z</t>
+          <t>2026-08-13T21:12:34Z</t>
         </is>
       </c>
     </row>
@@ -8556,7 +8556,7 @@
       </c>
       <c r="S99" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T21:12:48Z</t>
+          <t>2026-08-13T21:12:34Z</t>
         </is>
       </c>
     </row>
@@ -8641,7 +8641,7 @@
       </c>
       <c r="S100" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T21:12:48Z</t>
+          <t>2026-08-13T21:12:34Z</t>
         </is>
       </c>
     </row>
@@ -8726,7 +8726,7 @@
       </c>
       <c r="S101" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T21:12:48Z</t>
+          <t>2026-08-13T21:12:34Z</t>
         </is>
       </c>
     </row>
@@ -8811,7 +8811,7 @@
       </c>
       <c r="S102" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T21:12:48Z</t>
+          <t>2026-08-13T21:12:34Z</t>
         </is>
       </c>
     </row>
@@ -8896,7 +8896,7 @@
       </c>
       <c r="S103" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T21:12:48Z</t>
+          <t>2026-08-13T21:12:34Z</t>
         </is>
       </c>
     </row>
@@ -8981,7 +8981,7 @@
       </c>
       <c r="S104" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T21:12:48Z</t>
+          <t>2026-08-13T21:12:34Z</t>
         </is>
       </c>
     </row>
@@ -9066,7 +9066,7 @@
       </c>
       <c r="S105" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T21:12:48Z</t>
+          <t>2026-08-13T21:12:34Z</t>
         </is>
       </c>
     </row>
@@ -9151,7 +9151,7 @@
       </c>
       <c r="S106" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T21:12:48Z</t>
+          <t>2026-08-13T21:12:34Z</t>
         </is>
       </c>
     </row>
@@ -9236,7 +9236,7 @@
       </c>
       <c r="S107" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T21:12:48Z</t>
+          <t>2026-08-13T21:12:34Z</t>
         </is>
       </c>
     </row>
@@ -9321,7 +9321,7 @@
       </c>
       <c r="S108" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T21:12:48Z</t>
+          <t>2026-08-13T21:12:34Z</t>
         </is>
       </c>
     </row>
@@ -9406,7 +9406,7 @@
       </c>
       <c r="S109" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T21:12:48Z</t>
+          <t>2026-08-13T21:12:34Z</t>
         </is>
       </c>
     </row>
@@ -9491,7 +9491,7 @@
       </c>
       <c r="S110" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T21:12:48Z</t>
+          <t>2026-08-13T21:12:34Z</t>
         </is>
       </c>
     </row>
@@ -9576,7 +9576,7 @@
       </c>
       <c r="S111" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T21:12:48Z</t>
+          <t>2026-08-13T21:12:34Z</t>
         </is>
       </c>
     </row>
@@ -9661,7 +9661,7 @@
       </c>
       <c r="S112" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T21:12:48Z</t>
+          <t>2026-08-13T21:12:34Z</t>
         </is>
       </c>
     </row>
@@ -9746,7 +9746,7 @@
       </c>
       <c r="S113" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T21:12:48Z</t>
+          <t>2026-08-13T21:12:34Z</t>
         </is>
       </c>
     </row>
@@ -9831,7 +9831,7 @@
       </c>
       <c r="S114" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T21:12:48Z</t>
+          <t>2026-08-13T21:12:34Z</t>
         </is>
       </c>
     </row>
@@ -9916,7 +9916,7 @@
       </c>
       <c r="S115" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T21:12:48Z</t>
+          <t>2026-08-13T21:12:34Z</t>
         </is>
       </c>
     </row>
@@ -10001,7 +10001,7 @@
       </c>
       <c r="S116" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T21:12:48Z</t>
+          <t>2026-08-13T21:12:34Z</t>
         </is>
       </c>
     </row>
@@ -10086,7 +10086,7 @@
       </c>
       <c r="S117" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T21:12:48Z</t>
+          <t>2026-08-13T21:12:34Z</t>
         </is>
       </c>
     </row>
@@ -10171,7 +10171,7 @@
       </c>
       <c r="S118" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T21:12:48Z</t>
+          <t>2026-08-13T21:12:34Z</t>
         </is>
       </c>
     </row>
@@ -10256,7 +10256,7 @@
       </c>
       <c r="S119" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T21:12:48Z</t>
+          <t>2026-08-13T21:12:34Z</t>
         </is>
       </c>
     </row>
@@ -10341,7 +10341,7 @@
       </c>
       <c r="S120" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T21:12:48Z</t>
+          <t>2026-08-13T21:12:34Z</t>
         </is>
       </c>
     </row>
@@ -10426,7 +10426,7 @@
       </c>
       <c r="S121" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T21:12:48Z</t>
+          <t>2026-08-13T21:12:34Z</t>
         </is>
       </c>
     </row>
@@ -10511,7 +10511,7 @@
       </c>
       <c r="S122" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T21:12:48Z</t>
+          <t>2026-08-13T21:12:34Z</t>
         </is>
       </c>
     </row>
@@ -10596,7 +10596,7 @@
       </c>
       <c r="S123" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T21:12:48Z</t>
+          <t>2026-08-13T21:12:34Z</t>
         </is>
       </c>
     </row>
@@ -10681,7 +10681,7 @@
       </c>
       <c r="S124" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T21:12:48Z</t>
+          <t>2026-08-13T21:12:34Z</t>
         </is>
       </c>
     </row>
@@ -10766,7 +10766,7 @@
       </c>
       <c r="S125" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T21:12:48Z</t>
+          <t>2026-08-13T21:12:34Z</t>
         </is>
       </c>
     </row>
@@ -10851,7 +10851,7 @@
       </c>
       <c r="S126" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T21:12:48Z</t>
+          <t>2026-08-13T21:12:34Z</t>
         </is>
       </c>
     </row>
@@ -10936,7 +10936,7 @@
       </c>
       <c r="S127" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T21:12:48Z</t>
+          <t>2026-08-13T21:12:34Z</t>
         </is>
       </c>
     </row>
@@ -11021,7 +11021,7 @@
       </c>
       <c r="S128" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T21:12:48Z</t>
+          <t>2026-08-13T21:12:34Z</t>
         </is>
       </c>
     </row>
@@ -11106,7 +11106,7 @@
       </c>
       <c r="S129" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T21:12:48Z</t>
+          <t>2026-08-13T21:12:34Z</t>
         </is>
       </c>
     </row>
@@ -11191,7 +11191,7 @@
       </c>
       <c r="S130" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T21:12:48Z</t>
+          <t>2026-08-13T21:12:34Z</t>
         </is>
       </c>
     </row>
@@ -11276,7 +11276,7 @@
       </c>
       <c r="S131" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T21:12:48Z</t>
+          <t>2026-08-13T21:12:34Z</t>
         </is>
       </c>
     </row>
@@ -11361,7 +11361,7 @@
       </c>
       <c r="S132" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T21:12:48Z</t>
+          <t>2026-08-13T21:12:34Z</t>
         </is>
       </c>
     </row>
@@ -11446,7 +11446,7 @@
       </c>
       <c r="S133" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T21:12:48Z</t>
+          <t>2026-08-13T21:12:34Z</t>
         </is>
       </c>
     </row>
@@ -11531,7 +11531,7 @@
       </c>
       <c r="S134" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T21:12:48Z</t>
+          <t>2026-08-13T21:12:34Z</t>
         </is>
       </c>
     </row>
@@ -11616,7 +11616,7 @@
       </c>
       <c r="S135" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T21:12:48Z</t>
+          <t>2026-08-13T21:12:34Z</t>
         </is>
       </c>
     </row>
@@ -11701,7 +11701,7 @@
       </c>
       <c r="S136" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T21:12:48Z</t>
+          <t>2026-08-13T21:12:34Z</t>
         </is>
       </c>
     </row>
@@ -11786,7 +11786,7 @@
       </c>
       <c r="S137" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T21:12:48Z</t>
+          <t>2026-08-13T21:12:34Z</t>
         </is>
       </c>
     </row>
@@ -11871,7 +11871,7 @@
       </c>
       <c r="S138" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T21:12:48Z</t>
+          <t>2026-08-13T21:12:34Z</t>
         </is>
       </c>
     </row>
@@ -11956,7 +11956,7 @@
       </c>
       <c r="S139" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T21:12:48Z</t>
+          <t>2026-08-13T21:12:34Z</t>
         </is>
       </c>
     </row>
@@ -12041,7 +12041,7 @@
       </c>
       <c r="S140" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T21:12:48Z</t>
+          <t>2026-08-13T21:12:34Z</t>
         </is>
       </c>
     </row>
@@ -12126,7 +12126,7 @@
       </c>
       <c r="S141" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T21:12:48Z</t>
+          <t>2026-08-13T21:12:34Z</t>
         </is>
       </c>
     </row>
@@ -12258,7 +12258,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T21:12:48Z</t>
+          <t>2026-08-13T21:12:34Z</t>
         </is>
       </c>
     </row>
@@ -12338,7 +12338,7 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>{"dataset_id": "bcv_pib_historico_anual", "title": "Producto interno bruto histórico anual", "table": "PIB histórico anual", "source_file": "7_1_14_anual.xls", "base": "1957/1968/1984/1997", "price_type": "Precios constantes", "measure": "Nivel", "frequency": "Anual", "period": "2017", "year": 2017, "quarter": null, "classification": "Total economía", "component": "Producto interno bruto", "value": 392393.12, "unit": "Millones de bolívares a precios constantes", "status": "", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/7_1_14_anual.xls", "fetched_at": "2026-08-12T21:12:48Z"}</t>
+          <t>{"dataset_id": "bcv_pib_historico_anual", "title": "Producto interno bruto histórico anual", "table": "PIB histórico anual", "source_file": "7_1_14_anual.xls", "base": "1957/1968/1984/1997", "price_type": "Precios constantes", "measure": "Nivel", "frequency": "Anual", "period": "2017", "year": 2017, "quarter": null, "classification": "Total economía", "component": "Producto interno bruto", "value": 392393.12, "unit": "Millones de bolívares a precios constantes", "status": "", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/7_1_14_anual.xls", "fetched_at": "2026-08-13T21:12:34Z"}</t>
         </is>
       </c>
     </row>

--- a/assets/data/bcv/excel/ove_bcv_pib_historico_anual.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_pib_historico_anual.xlsx
@@ -736,7 +736,7 @@
       </c>
       <c r="S7" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -821,7 +821,7 @@
       </c>
       <c r="S8" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -906,7 +906,7 @@
       </c>
       <c r="S9" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -991,7 +991,7 @@
       </c>
       <c r="S10" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="S11" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -1161,7 +1161,7 @@
       </c>
       <c r="S12" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -1246,7 +1246,7 @@
       </c>
       <c r="S13" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -1331,7 +1331,7 @@
       </c>
       <c r="S14" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -1416,7 +1416,7 @@
       </c>
       <c r="S15" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -1501,7 +1501,7 @@
       </c>
       <c r="S16" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -1586,7 +1586,7 @@
       </c>
       <c r="S17" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -1671,7 +1671,7 @@
       </c>
       <c r="S18" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -1756,7 +1756,7 @@
       </c>
       <c r="S19" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -1841,7 +1841,7 @@
       </c>
       <c r="S20" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -1926,7 +1926,7 @@
       </c>
       <c r="S21" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -2011,7 +2011,7 @@
       </c>
       <c r="S22" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="S23" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -2181,7 +2181,7 @@
       </c>
       <c r="S24" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -2266,7 +2266,7 @@
       </c>
       <c r="S25" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -2351,7 +2351,7 @@
       </c>
       <c r="S26" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -2436,7 +2436,7 @@
       </c>
       <c r="S27" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -2521,7 +2521,7 @@
       </c>
       <c r="S28" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -2606,7 +2606,7 @@
       </c>
       <c r="S29" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -2691,7 +2691,7 @@
       </c>
       <c r="S30" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -2776,7 +2776,7 @@
       </c>
       <c r="S31" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -2861,7 +2861,7 @@
       </c>
       <c r="S32" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -2946,7 +2946,7 @@
       </c>
       <c r="S33" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -3031,7 +3031,7 @@
       </c>
       <c r="S34" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -3116,7 +3116,7 @@
       </c>
       <c r="S35" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -3201,7 +3201,7 @@
       </c>
       <c r="S36" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -3286,7 +3286,7 @@
       </c>
       <c r="S37" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -3371,7 +3371,7 @@
       </c>
       <c r="S38" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -3456,7 +3456,7 @@
       </c>
       <c r="S39" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -3541,7 +3541,7 @@
       </c>
       <c r="S40" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -3626,7 +3626,7 @@
       </c>
       <c r="S41" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -3711,7 +3711,7 @@
       </c>
       <c r="S42" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -3796,7 +3796,7 @@
       </c>
       <c r="S43" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -3881,7 +3881,7 @@
       </c>
       <c r="S44" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -3966,7 +3966,7 @@
       </c>
       <c r="S45" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -4051,7 +4051,7 @@
       </c>
       <c r="S46" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -4136,7 +4136,7 @@
       </c>
       <c r="S47" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -4221,7 +4221,7 @@
       </c>
       <c r="S48" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -4306,7 +4306,7 @@
       </c>
       <c r="S49" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -4391,7 +4391,7 @@
       </c>
       <c r="S50" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -4476,7 +4476,7 @@
       </c>
       <c r="S51" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -4561,7 +4561,7 @@
       </c>
       <c r="S52" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -4646,7 +4646,7 @@
       </c>
       <c r="S53" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -4731,7 +4731,7 @@
       </c>
       <c r="S54" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -4816,7 +4816,7 @@
       </c>
       <c r="S55" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -4901,7 +4901,7 @@
       </c>
       <c r="S56" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -4986,7 +4986,7 @@
       </c>
       <c r="S57" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -5071,7 +5071,7 @@
       </c>
       <c r="S58" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -5156,7 +5156,7 @@
       </c>
       <c r="S59" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -5241,7 +5241,7 @@
       </c>
       <c r="S60" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -5326,7 +5326,7 @@
       </c>
       <c r="S61" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -5411,7 +5411,7 @@
       </c>
       <c r="S62" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -5496,7 +5496,7 @@
       </c>
       <c r="S63" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -5581,7 +5581,7 @@
       </c>
       <c r="S64" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -5666,7 +5666,7 @@
       </c>
       <c r="S65" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -5751,7 +5751,7 @@
       </c>
       <c r="S66" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -5836,7 +5836,7 @@
       </c>
       <c r="S67" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -5921,7 +5921,7 @@
       </c>
       <c r="S68" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -6006,7 +6006,7 @@
       </c>
       <c r="S69" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -6091,7 +6091,7 @@
       </c>
       <c r="S70" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -6176,7 +6176,7 @@
       </c>
       <c r="S71" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -6261,7 +6261,7 @@
       </c>
       <c r="S72" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -6346,7 +6346,7 @@
       </c>
       <c r="S73" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -6431,7 +6431,7 @@
       </c>
       <c r="S74" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -6516,7 +6516,7 @@
       </c>
       <c r="S75" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -6601,7 +6601,7 @@
       </c>
       <c r="S76" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -6686,7 +6686,7 @@
       </c>
       <c r="S77" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -6771,7 +6771,7 @@
       </c>
       <c r="S78" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -6856,7 +6856,7 @@
       </c>
       <c r="S79" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -6941,7 +6941,7 @@
       </c>
       <c r="S80" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -7026,7 +7026,7 @@
       </c>
       <c r="S81" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -7111,7 +7111,7 @@
       </c>
       <c r="S82" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -7196,7 +7196,7 @@
       </c>
       <c r="S83" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -7281,7 +7281,7 @@
       </c>
       <c r="S84" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -7366,7 +7366,7 @@
       </c>
       <c r="S85" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -7451,7 +7451,7 @@
       </c>
       <c r="S86" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -7536,7 +7536,7 @@
       </c>
       <c r="S87" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -7621,7 +7621,7 @@
       </c>
       <c r="S88" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -7706,7 +7706,7 @@
       </c>
       <c r="S89" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -7791,7 +7791,7 @@
       </c>
       <c r="S90" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -7876,7 +7876,7 @@
       </c>
       <c r="S91" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -7961,7 +7961,7 @@
       </c>
       <c r="S92" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -8046,7 +8046,7 @@
       </c>
       <c r="S93" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -8131,7 +8131,7 @@
       </c>
       <c r="S94" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -8216,7 +8216,7 @@
       </c>
       <c r="S95" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -8301,7 +8301,7 @@
       </c>
       <c r="S96" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -8386,7 +8386,7 @@
       </c>
       <c r="S97" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -8471,7 +8471,7 @@
       </c>
       <c r="S98" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -8556,7 +8556,7 @@
       </c>
       <c r="S99" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -8641,7 +8641,7 @@
       </c>
       <c r="S100" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -8726,7 +8726,7 @@
       </c>
       <c r="S101" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -8811,7 +8811,7 @@
       </c>
       <c r="S102" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -8896,7 +8896,7 @@
       </c>
       <c r="S103" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -8981,7 +8981,7 @@
       </c>
       <c r="S104" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -9066,7 +9066,7 @@
       </c>
       <c r="S105" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -9151,7 +9151,7 @@
       </c>
       <c r="S106" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -9236,7 +9236,7 @@
       </c>
       <c r="S107" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -9321,7 +9321,7 @@
       </c>
       <c r="S108" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -9406,7 +9406,7 @@
       </c>
       <c r="S109" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -9491,7 +9491,7 @@
       </c>
       <c r="S110" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -9576,7 +9576,7 @@
       </c>
       <c r="S111" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -9661,7 +9661,7 @@
       </c>
       <c r="S112" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -9746,7 +9746,7 @@
       </c>
       <c r="S113" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -9831,7 +9831,7 @@
       </c>
       <c r="S114" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -9916,7 +9916,7 @@
       </c>
       <c r="S115" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -10001,7 +10001,7 @@
       </c>
       <c r="S116" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -10086,7 +10086,7 @@
       </c>
       <c r="S117" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -10171,7 +10171,7 @@
       </c>
       <c r="S118" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -10256,7 +10256,7 @@
       </c>
       <c r="S119" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -10341,7 +10341,7 @@
       </c>
       <c r="S120" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -10426,7 +10426,7 @@
       </c>
       <c r="S121" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -10511,7 +10511,7 @@
       </c>
       <c r="S122" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -10596,7 +10596,7 @@
       </c>
       <c r="S123" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -10681,7 +10681,7 @@
       </c>
       <c r="S124" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -10766,7 +10766,7 @@
       </c>
       <c r="S125" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -10851,7 +10851,7 @@
       </c>
       <c r="S126" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -10936,7 +10936,7 @@
       </c>
       <c r="S127" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -11021,7 +11021,7 @@
       </c>
       <c r="S128" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -11106,7 +11106,7 @@
       </c>
       <c r="S129" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -11191,7 +11191,7 @@
       </c>
       <c r="S130" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -11276,7 +11276,7 @@
       </c>
       <c r="S131" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -11361,7 +11361,7 @@
       </c>
       <c r="S132" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -11446,7 +11446,7 @@
       </c>
       <c r="S133" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -11531,7 +11531,7 @@
       </c>
       <c r="S134" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -11616,7 +11616,7 @@
       </c>
       <c r="S135" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -11701,7 +11701,7 @@
       </c>
       <c r="S136" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -11786,7 +11786,7 @@
       </c>
       <c r="S137" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -11871,7 +11871,7 @@
       </c>
       <c r="S138" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -11956,7 +11956,7 @@
       </c>
       <c r="S139" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -12041,7 +12041,7 @@
       </c>
       <c r="S140" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -12126,7 +12126,7 @@
       </c>
       <c r="S141" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -12258,7 +12258,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -12338,7 +12338,7 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>{"dataset_id": "bcv_pib_historico_anual", "title": "Producto interno bruto histórico anual", "table": "PIB histórico anual", "source_file": "7_1_14_anual.xls", "base": "1957/1968/1984/1997", "price_type": "Precios constantes", "measure": "Nivel", "frequency": "Anual", "period": "2017", "year": 2017, "quarter": null, "classification": "Total economía", "component": "Producto interno bruto", "value": 392393.12, "unit": "Millones de bolívares a precios constantes", "status": "", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/7_1_14_anual.xls", "fetched_at": "2026-08-13T21:12:34Z"}</t>
+          <t>{"dataset_id": "bcv_pib_historico_anual", "title": "Producto interno bruto histórico anual", "table": "PIB histórico anual", "source_file": "7_1_14_anual.xls", "base": "1957/1968/1984/1997", "price_type": "Precios constantes", "measure": "Nivel", "frequency": "Anual", "period": "2017", "year": 2017, "quarter": null, "classification": "Total economía", "component": "Producto interno bruto", "value": 392393.12, "unit": "Millones de bolívares a precios constantes", "status": "", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/7_1_14_anual.xls", "fetched_at": "2026-08-14T20:55:16Z"}</t>
         </is>
       </c>
     </row>

--- a/assets/data/bcv/excel/ove_bcv_pib_historico_anual.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_pib_historico_anual.xlsx
@@ -736,7 +736,7 @@
       </c>
       <c r="S7" s="4" t="inlineStr">
         <is>
-          <t>2026-08-14T20:55:16Z</t>
+          <t>2026-08-15T20:47:08Z</t>
         </is>
       </c>
     </row>
@@ -821,7 +821,7 @@
       </c>
       <c r="S8" s="4" t="inlineStr">
         <is>
-          <t>2026-08-14T20:55:16Z</t>
+          <t>2026-08-15T20:47:08Z</t>
         </is>
       </c>
     </row>
@@ -906,7 +906,7 @@
       </c>
       <c r="S9" s="4" t="inlineStr">
         <is>
-          <t>2026-08-14T20:55:16Z</t>
+          <t>2026-08-15T20:47:08Z</t>
         </is>
       </c>
     </row>
@@ -991,7 +991,7 @@
       </c>
       <c r="S10" s="4" t="inlineStr">
         <is>
-          <t>2026-08-14T20:55:16Z</t>
+          <t>2026-08-15T20:47:08Z</t>
         </is>
       </c>
     </row>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="S11" s="4" t="inlineStr">
         <is>
-          <t>2026-08-14T20:55:16Z</t>
+          <t>2026-08-15T20:47:08Z</t>
         </is>
       </c>
     </row>
@@ -1161,7 +1161,7 @@
       </c>
       <c r="S12" s="4" t="inlineStr">
         <is>
-          <t>2026-08-14T20:55:16Z</t>
+          <t>2026-08-15T20:47:08Z</t>
         </is>
       </c>
     </row>
@@ -1246,7 +1246,7 @@
       </c>
       <c r="S13" s="4" t="inlineStr">
         <is>
-          <t>2026-08-14T20:55:16Z</t>
+          <t>2026-08-15T20:47:08Z</t>
         </is>
       </c>
     </row>
@@ -1331,7 +1331,7 @@
       </c>
       <c r="S14" s="4" t="inlineStr">
         <is>
-          <t>2026-08-14T20:55:16Z</t>
+          <t>2026-08-15T20:47:08Z</t>
         </is>
       </c>
     </row>
@@ -1416,7 +1416,7 @@
       </c>
       <c r="S15" s="4" t="inlineStr">
         <is>
-          <t>2026-08-14T20:55:16Z</t>
+          <t>2026-08-15T20:47:08Z</t>
         </is>
       </c>
     </row>
@@ -1501,7 +1501,7 @@
       </c>
       <c r="S16" s="4" t="inlineStr">
         <is>
-          <t>2026-08-14T20:55:16Z</t>
+          <t>2026-08-15T20:47:08Z</t>
         </is>
       </c>
     </row>
@@ -1586,7 +1586,7 @@
       </c>
       <c r="S17" s="4" t="inlineStr">
         <is>
-          <t>2026-08-14T20:55:16Z</t>
+          <t>2026-08-15T20:47:08Z</t>
         </is>
       </c>
     </row>
@@ -1671,7 +1671,7 @@
       </c>
       <c r="S18" s="4" t="inlineStr">
         <is>
-          <t>2026-08-14T20:55:16Z</t>
+          <t>2026-08-15T20:47:08Z</t>
         </is>
       </c>
     </row>
@@ -1756,7 +1756,7 @@
       </c>
       <c r="S19" s="4" t="inlineStr">
         <is>
-          <t>2026-08-14T20:55:16Z</t>
+          <t>2026-08-15T20:47:08Z</t>
         </is>
       </c>
     </row>
@@ -1841,7 +1841,7 @@
       </c>
       <c r="S20" s="4" t="inlineStr">
         <is>
-          <t>2026-08-14T20:55:16Z</t>
+          <t>2026-08-15T20:47:08Z</t>
         </is>
       </c>
     </row>
@@ -1926,7 +1926,7 @@
       </c>
       <c r="S21" s="4" t="inlineStr">
         <is>
-          <t>2026-08-14T20:55:16Z</t>
+          <t>2026-08-15T20:47:08Z</t>
         </is>
       </c>
     </row>
@@ -2011,7 +2011,7 @@
       </c>
       <c r="S22" s="4" t="inlineStr">
         <is>
-          <t>2026-08-14T20:55:16Z</t>
+          <t>2026-08-15T20:47:08Z</t>
         </is>
       </c>
     </row>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="S23" s="4" t="inlineStr">
         <is>
-          <t>2026-08-14T20:55:16Z</t>
+          <t>2026-08-15T20:47:08Z</t>
         </is>
       </c>
     </row>
@@ -2181,7 +2181,7 @@
       </c>
       <c r="S24" s="4" t="inlineStr">
         <is>
-          <t>2026-08-14T20:55:16Z</t>
+          <t>2026-08-15T20:47:08Z</t>
         </is>
       </c>
     </row>
@@ -2266,7 +2266,7 @@
       </c>
       <c r="S25" s="4" t="inlineStr">
         <is>
-          <t>2026-08-14T20:55:16Z</t>
+          <t>2026-08-15T20:47:08Z</t>
         </is>
       </c>
     </row>
@@ -2351,7 +2351,7 @@
       </c>
       <c r="S26" s="4" t="inlineStr">
         <is>
-          <t>2026-08-14T20:55:16Z</t>
+          <t>2026-08-15T20:47:08Z</t>
         </is>
       </c>
     </row>
@@ -2436,7 +2436,7 @@
       </c>
       <c r="S27" s="4" t="inlineStr">
         <is>
-          <t>2026-08-14T20:55:16Z</t>
+          <t>2026-08-15T20:47:08Z</t>
         </is>
       </c>
     </row>
@@ -2521,7 +2521,7 @@
       </c>
       <c r="S28" s="4" t="inlineStr">
         <is>
-          <t>2026-08-14T20:55:16Z</t>
+          <t>2026-08-15T20:47:08Z</t>
         </is>
       </c>
     </row>
@@ -2606,7 +2606,7 @@
       </c>
       <c r="S29" s="4" t="inlineStr">
         <is>
-          <t>2026-08-14T20:55:16Z</t>
+          <t>2026-08-15T20:47:08Z</t>
         </is>
       </c>
     </row>
@@ -2691,7 +2691,7 @@
       </c>
       <c r="S30" s="4" t="inlineStr">
         <is>
-          <t>2026-08-14T20:55:16Z</t>
+          <t>2026-08-15T20:47:08Z</t>
         </is>
       </c>
     </row>
@@ -2776,7 +2776,7 @@
       </c>
       <c r="S31" s="4" t="inlineStr">
         <is>
-          <t>2026-08-14T20:55:16Z</t>
+          <t>2026-08-15T20:47:08Z</t>
         </is>
       </c>
     </row>
@@ -2861,7 +2861,7 @@
       </c>
       <c r="S32" s="4" t="inlineStr">
         <is>
-          <t>2026-08-14T20:55:16Z</t>
+          <t>2026-08-15T20:47:08Z</t>
         </is>
       </c>
     </row>
@@ -2946,7 +2946,7 @@
       </c>
       <c r="S33" s="4" t="inlineStr">
         <is>
-          <t>2026-08-14T20:55:16Z</t>
+          <t>2026-08-15T20:47:08Z</t>
         </is>
       </c>
     </row>
@@ -3031,7 +3031,7 @@
       </c>
       <c r="S34" s="4" t="inlineStr">
         <is>
-          <t>2026-08-14T20:55:16Z</t>
+          <t>2026-08-15T20:47:08Z</t>
         </is>
       </c>
     </row>
@@ -3116,7 +3116,7 @@
       </c>
       <c r="S35" s="4" t="inlineStr">
         <is>
-          <t>2026-08-14T20:55:16Z</t>
+          <t>2026-08-15T20:47:08Z</t>
         </is>
       </c>
     </row>
@@ -3201,7 +3201,7 @@
       </c>
       <c r="S36" s="4" t="inlineStr">
         <is>
-          <t>2026-08-14T20:55:16Z</t>
+          <t>2026-08-15T20:47:08Z</t>
         </is>
       </c>
     </row>
@@ -3286,7 +3286,7 @@
       </c>
       <c r="S37" s="4" t="inlineStr">
         <is>
-          <t>2026-08-14T20:55:16Z</t>
+          <t>2026-08-15T20:47:08Z</t>
         </is>
       </c>
     </row>
@@ -3371,7 +3371,7 @@
       </c>
       <c r="S38" s="4" t="inlineStr">
         <is>
-          <t>2026-08-14T20:55:16Z</t>
+          <t>2026-08-15T20:47:08Z</t>
         </is>
       </c>
     </row>
@@ -3456,7 +3456,7 @@
       </c>
       <c r="S39" s="4" t="inlineStr">
         <is>
-          <t>2026-08-14T20:55:16Z</t>
+          <t>2026-08-15T20:47:08Z</t>
         </is>
       </c>
     </row>
@@ -3541,7 +3541,7 @@
       </c>
       <c r="S40" s="4" t="inlineStr">
         <is>
-          <t>2026-08-14T20:55:16Z</t>
+          <t>2026-08-15T20:47:08Z</t>
         </is>
       </c>
     </row>
@@ -3626,7 +3626,7 @@
       </c>
       <c r="S41" s="4" t="inlineStr">
         <is>
-          <t>2026-08-14T20:55:16Z</t>
+          <t>2026-08-15T20:47:08Z</t>
         </is>
       </c>
     </row>
@@ -3711,7 +3711,7 @@
       </c>
       <c r="S42" s="4" t="inlineStr">
         <is>
-          <t>2026-08-14T20:55:16Z</t>
+          <t>2026-08-15T20:47:08Z</t>
         </is>
       </c>
     </row>
@@ -3796,7 +3796,7 @@
       </c>
       <c r="S43" s="4" t="inlineStr">
         <is>
-          <t>2026-08-14T20:55:16Z</t>
+          <t>2026-08-15T20:47:08Z</t>
         </is>
       </c>
     </row>
@@ -3881,7 +3881,7 @@
       </c>
       <c r="S44" s="4" t="inlineStr">
         <is>
-          <t>2026-08-14T20:55:16Z</t>
+          <t>2026-08-15T20:47:08Z</t>
         </is>
       </c>
     </row>
@@ -3966,7 +3966,7 @@
       </c>
       <c r="S45" s="4" t="inlineStr">
         <is>
-          <t>2026-08-14T20:55:16Z</t>
+          <t>2026-08-15T20:47:08Z</t>
         </is>
       </c>
     </row>
@@ -4051,7 +4051,7 @@
       </c>
       <c r="S46" s="4" t="inlineStr">
         <is>
-          <t>2026-08-14T20:55:16Z</t>
+          <t>2026-08-15T20:47:08Z</t>
         </is>
       </c>
     </row>
@@ -4136,7 +4136,7 @@
       </c>
       <c r="S47" s="4" t="inlineStr">
         <is>
-          <t>2026-08-14T20:55:16Z</t>
+          <t>2026-08-15T20:47:08Z</t>
         </is>
       </c>
     </row>
@@ -4221,7 +4221,7 @@
       </c>
       <c r="S48" s="4" t="inlineStr">
         <is>
-          <t>2026-08-14T20:55:16Z</t>
+          <t>2026-08-15T20:47:08Z</t>
         </is>
       </c>
     </row>
@@ -4306,7 +4306,7 @@
       </c>
       <c r="S49" s="4" t="inlineStr">
         <is>
-          <t>2026-08-14T20:55:16Z</t>
+          <t>2026-08-15T20:47:08Z</t>
         </is>
       </c>
     </row>
@@ -4391,7 +4391,7 @@
       </c>
       <c r="S50" s="4" t="inlineStr">
         <is>
-          <t>2026-08-14T20:55:16Z</t>
+          <t>2026-08-15T20:47:08Z</t>
         </is>
       </c>
     </row>
@@ -4476,7 +4476,7 @@
       </c>
       <c r="S51" s="4" t="inlineStr">
         <is>
-          <t>2026-08-14T20:55:16Z</t>
+          <t>2026-08-15T20:47:08Z</t>
         </is>
       </c>
     </row>
@@ -4561,7 +4561,7 @@
       </c>
       <c r="S52" s="4" t="inlineStr">
         <is>
-          <t>2026-08-14T20:55:16Z</t>
+          <t>2026-08-15T20:47:08Z</t>
         </is>
       </c>
     </row>
@@ -4646,7 +4646,7 @@
       </c>
       <c r="S53" s="4" t="inlineStr">
         <is>
-          <t>2026-08-14T20:55:16Z</t>
+          <t>2026-08-15T20:47:08Z</t>
         </is>
       </c>
     </row>
@@ -4731,7 +4731,7 @@
       </c>
       <c r="S54" s="4" t="inlineStr">
         <is>
-          <t>2026-08-14T20:55:16Z</t>
+          <t>2026-08-15T20:47:08Z</t>
         </is>
       </c>
     </row>
@@ -4816,7 +4816,7 @@
       </c>
       <c r="S55" s="4" t="inlineStr">
         <is>
-          <t>2026-08-14T20:55:16Z</t>
+          <t>2026-08-15T20:47:08Z</t>
         </is>
       </c>
     </row>
@@ -4901,7 +4901,7 @@
       </c>
       <c r="S56" s="4" t="inlineStr">
         <is>
-          <t>2026-08-14T20:55:16Z</t>
+          <t>2026-08-15T20:47:08Z</t>
         </is>
       </c>
     </row>
@@ -4986,7 +4986,7 @@
       </c>
       <c r="S57" s="4" t="inlineStr">
         <is>
-          <t>2026-08-14T20:55:16Z</t>
+          <t>2026-08-15T20:47:08Z</t>
         </is>
       </c>
     </row>
@@ -5071,7 +5071,7 @@
       </c>
       <c r="S58" s="4" t="inlineStr">
         <is>
-          <t>2026-08-14T20:55:16Z</t>
+          <t>2026-08-15T20:47:08Z</t>
         </is>
       </c>
     </row>
@@ -5156,7 +5156,7 @@
       </c>
       <c r="S59" s="4" t="inlineStr">
         <is>
-          <t>2026-08-14T20:55:16Z</t>
+          <t>2026-08-15T20:47:08Z</t>
         </is>
       </c>
     </row>
@@ -5241,7 +5241,7 @@
       </c>
       <c r="S60" s="4" t="inlineStr">
         <is>
-          <t>2026-08-14T20:55:16Z</t>
+          <t>2026-08-15T20:47:08Z</t>
         </is>
       </c>
     </row>
@@ -5326,7 +5326,7 @@
       </c>
       <c r="S61" s="4" t="inlineStr">
         <is>
-          <t>2026-08-14T20:55:16Z</t>
+          <t>2026-08-15T20:47:08Z</t>
         </is>
       </c>
     </row>
@@ -5411,7 +5411,7 @@
       </c>
       <c r="S62" s="4" t="inlineStr">
         <is>
-          <t>2026-08-14T20:55:16Z</t>
+          <t>2026-08-15T20:47:08Z</t>
         </is>
       </c>
     </row>
@@ -5496,7 +5496,7 @@
       </c>
       <c r="S63" s="4" t="inlineStr">
         <is>
-          <t>2026-08-14T20:55:16Z</t>
+          <t>2026-08-15T20:47:08Z</t>
         </is>
       </c>
     </row>
@@ -5581,7 +5581,7 @@
       </c>
       <c r="S64" s="4" t="inlineStr">
         <is>
-          <t>2026-08-14T20:55:16Z</t>
+          <t>2026-08-15T20:47:08Z</t>
         </is>
       </c>
     </row>
@@ -5666,7 +5666,7 @@
       </c>
       <c r="S65" s="4" t="inlineStr">
         <is>
-          <t>2026-08-14T20:55:16Z</t>
+          <t>2026-08-15T20:47:08Z</t>
         </is>
       </c>
     </row>
@@ -5751,7 +5751,7 @@
       </c>
       <c r="S66" s="4" t="inlineStr">
         <is>
-          <t>2026-08-14T20:55:16Z</t>
+          <t>2026-08-15T20:47:08Z</t>
         </is>
       </c>
     </row>
@@ -5836,7 +5836,7 @@
       </c>
       <c r="S67" s="4" t="inlineStr">
         <is>
-          <t>2026-08-14T20:55:16Z</t>
+          <t>2026-08-15T20:47:08Z</t>
         </is>
       </c>
     </row>
@@ -5921,7 +5921,7 @@
       </c>
       <c r="S68" s="4" t="inlineStr">
         <is>
-          <t>2026-08-14T20:55:16Z</t>
+          <t>2026-08-15T20:47:08Z</t>
         </is>
       </c>
     </row>
@@ -6006,7 +6006,7 @@
       </c>
       <c r="S69" s="4" t="inlineStr">
         <is>
-          <t>2026-08-14T20:55:16Z</t>
+          <t>2026-08-15T20:47:08Z</t>
         </is>
       </c>
     </row>
@@ -6091,7 +6091,7 @@
       </c>
       <c r="S70" s="4" t="inlineStr">
         <is>
-          <t>2026-08-14T20:55:16Z</t>
+          <t>2026-08-15T20:47:08Z</t>
         </is>
       </c>
     </row>
@@ -6176,7 +6176,7 @@
       </c>
       <c r="S71" s="4" t="inlineStr">
         <is>
-          <t>2026-08-14T20:55:16Z</t>
+          <t>2026-08-15T20:47:08Z</t>
         </is>
       </c>
     </row>
@@ -6261,7 +6261,7 @@
       </c>
       <c r="S72" s="4" t="inlineStr">
         <is>
-          <t>2026-08-14T20:55:16Z</t>
+          <t>2026-08-15T20:47:08Z</t>
         </is>
       </c>
     </row>
@@ -6346,7 +6346,7 @@
       </c>
       <c r="S73" s="4" t="inlineStr">
         <is>
-          <t>2026-08-14T20:55:16Z</t>
+          <t>2026-08-15T20:47:08Z</t>
         </is>
       </c>
     </row>
@@ -6431,7 +6431,7 @@
       </c>
       <c r="S74" s="4" t="inlineStr">
         <is>
-          <t>2026-08-14T20:55:16Z</t>
+          <t>2026-08-15T20:47:08Z</t>
         </is>
       </c>
     </row>
@@ -6516,7 +6516,7 @@
       </c>
       <c r="S75" s="4" t="inlineStr">
         <is>
-          <t>2026-08-14T20:55:16Z</t>
+          <t>2026-08-15T20:47:08Z</t>
         </is>
       </c>
     </row>
@@ -6601,7 +6601,7 @@
       </c>
       <c r="S76" s="4" t="inlineStr">
         <is>
-          <t>2026-08-14T20:55:16Z</t>
+          <t>2026-08-15T20:47:08Z</t>
         </is>
       </c>
     </row>
@@ -6686,7 +6686,7 @@
       </c>
       <c r="S77" s="4" t="inlineStr">
         <is>
-          <t>2026-08-14T20:55:16Z</t>
+          <t>2026-08-15T20:47:08Z</t>
         </is>
       </c>
     </row>
@@ -6771,7 +6771,7 @@
       </c>
       <c r="S78" s="4" t="inlineStr">
         <is>
-          <t>2026-08-14T20:55:16Z</t>
+          <t>2026-08-15T20:47:08Z</t>
         </is>
       </c>
     </row>
@@ -6856,7 +6856,7 @@
       </c>
       <c r="S79" s="4" t="inlineStr">
         <is>
-          <t>2026-08-14T20:55:16Z</t>
+          <t>2026-08-15T20:47:08Z</t>
         </is>
       </c>
     </row>
@@ -6941,7 +6941,7 @@
       </c>
       <c r="S80" s="4" t="inlineStr">
         <is>
-          <t>2026-08-14T20:55:16Z</t>
+          <t>2026-08-15T20:47:08Z</t>
         </is>
       </c>
     </row>
@@ -7026,7 +7026,7 @@
       </c>
       <c r="S81" s="4" t="inlineStr">
         <is>
-          <t>2026-08-14T20:55:16Z</t>
+          <t>2026-08-15T20:47:08Z</t>
         </is>
       </c>
     </row>
@@ -7111,7 +7111,7 @@
       </c>
       <c r="S82" s="4" t="inlineStr">
         <is>
-          <t>2026-08-14T20:55:16Z</t>
+          <t>2026-08-15T20:47:08Z</t>
         </is>
       </c>
     </row>
@@ -7196,7 +7196,7 @@
       </c>
       <c r="S83" s="4" t="inlineStr">
         <is>
-          <t>2026-08-14T20:55:16Z</t>
+          <t>2026-08-15T20:47:08Z</t>
         </is>
       </c>
     </row>
@@ -7281,7 +7281,7 @@
       </c>
       <c r="S84" s="4" t="inlineStr">
         <is>
-          <t>2026-08-14T20:55:16Z</t>
+          <t>2026-08-15T20:47:08Z</t>
         </is>
       </c>
     </row>
@@ -7366,7 +7366,7 @@
       </c>
       <c r="S85" s="4" t="inlineStr">
         <is>
-          <t>2026-08-14T20:55:16Z</t>
+          <t>2026-08-15T20:47:08Z</t>
         </is>
       </c>
     </row>
@@ -7451,7 +7451,7 @@
       </c>
       <c r="S86" s="4" t="inlineStr">
         <is>
-          <t>2026-08-14T20:55:16Z</t>
+          <t>2026-08-15T20:47:08Z</t>
         </is>
       </c>
     </row>
@@ -7536,7 +7536,7 @@
       </c>
       <c r="S87" s="4" t="inlineStr">
         <is>
-          <t>2026-08-14T20:55:16Z</t>
+          <t>2026-08-15T20:47:08Z</t>
         </is>
       </c>
     </row>
@@ -7621,7 +7621,7 @@
       </c>
       <c r="S88" s="4" t="inlineStr">
         <is>
-          <t>2026-08-14T20:55:16Z</t>
+          <t>2026-08-15T20:47:08Z</t>
         </is>
       </c>
     </row>
@@ -7706,7 +7706,7 @@
       </c>
       <c r="S89" s="4" t="inlineStr">
         <is>
-          <t>2026-08-14T20:55:16Z</t>
+          <t>2026-08-15T20:47:08Z</t>
         </is>
       </c>
     </row>
@@ -7791,7 +7791,7 @@
       </c>
       <c r="S90" s="4" t="inlineStr">
         <is>
-          <t>2026-08-14T20:55:16Z</t>
+          <t>2026-08-15T20:47:08Z</t>
         </is>
       </c>
     </row>
@@ -7876,7 +7876,7 @@
       </c>
       <c r="S91" s="4" t="inlineStr">
         <is>
-          <t>2026-08-14T20:55:16Z</t>
+          <t>2026-08-15T20:47:08Z</t>
         </is>
       </c>
     </row>
@@ -7961,7 +7961,7 @@
       </c>
       <c r="S92" s="4" t="inlineStr">
         <is>
-          <t>2026-08-14T20:55:16Z</t>
+          <t>2026-08-15T20:47:08Z</t>
         </is>
       </c>
     </row>
@@ -8046,7 +8046,7 @@
       </c>
       <c r="S93" s="4" t="inlineStr">
         <is>
-          <t>2026-08-14T20:55:16Z</t>
+          <t>2026-08-15T20:47:08Z</t>
         </is>
       </c>
     </row>
@@ -8131,7 +8131,7 @@
       </c>
       <c r="S94" s="4" t="inlineStr">
         <is>
-          <t>2026-08-14T20:55:16Z</t>
+          <t>2026-08-15T20:47:08Z</t>
         </is>
       </c>
     </row>
@@ -8216,7 +8216,7 @@
       </c>
       <c r="S95" s="4" t="inlineStr">
         <is>
-          <t>2026-08-14T20:55:16Z</t>
+          <t>2026-08-15T20:47:08Z</t>
         </is>
       </c>
     </row>
@@ -8301,7 +8301,7 @@
       </c>
       <c r="S96" s="4" t="inlineStr">
         <is>
-          <t>2026-08-14T20:55:16Z</t>
+          <t>2026-08-15T20:47:08Z</t>
         </is>
       </c>
     </row>
@@ -8386,7 +8386,7 @@
       </c>
       <c r="S97" s="4" t="inlineStr">
         <is>
-          <t>2026-08-14T20:55:16Z</t>
+          <t>2026-08-15T20:47:08Z</t>
         </is>
       </c>
     </row>
@@ -8471,7 +8471,7 @@
       </c>
       <c r="S98" s="4" t="inlineStr">
         <is>
-          <t>2026-08-14T20:55:16Z</t>
+          <t>2026-08-15T20:47:08Z</t>
         </is>
       </c>
     </row>
@@ -8556,7 +8556,7 @@
       </c>
       <c r="S99" s="4" t="inlineStr">
         <is>
-          <t>2026-08-14T20:55:16Z</t>
+          <t>2026-08-15T20:47:08Z</t>
         </is>
       </c>
     </row>
@@ -8641,7 +8641,7 @@
       </c>
       <c r="S100" s="4" t="inlineStr">
         <is>
-          <t>2026-08-14T20:55:16Z</t>
+          <t>2026-08-15T20:47:08Z</t>
         </is>
       </c>
     </row>
@@ -8726,7 +8726,7 @@
       </c>
       <c r="S101" s="4" t="inlineStr">
         <is>
-          <t>2026-08-14T20:55:16Z</t>
+          <t>2026-08-15T20:47:08Z</t>
         </is>
       </c>
     </row>
@@ -8811,7 +8811,7 @@
       </c>
       <c r="S102" s="4" t="inlineStr">
         <is>
-          <t>2026-08-14T20:55:16Z</t>
+          <t>2026-08-15T20:47:08Z</t>
         </is>
       </c>
     </row>
@@ -8896,7 +8896,7 @@
       </c>
       <c r="S103" s="4" t="inlineStr">
         <is>
-          <t>2026-08-14T20:55:16Z</t>
+          <t>2026-08-15T20:47:08Z</t>
         </is>
       </c>
     </row>
@@ -8981,7 +8981,7 @@
       </c>
       <c r="S104" s="4" t="inlineStr">
         <is>
-          <t>2026-08-14T20:55:16Z</t>
+          <t>2026-08-15T20:47:08Z</t>
         </is>
       </c>
     </row>
@@ -9066,7 +9066,7 @@
       </c>
       <c r="S105" s="4" t="inlineStr">
         <is>
-          <t>2026-08-14T20:55:16Z</t>
+          <t>2026-08-15T20:47:08Z</t>
         </is>
       </c>
     </row>
@@ -9151,7 +9151,7 @@
       </c>
       <c r="S106" s="4" t="inlineStr">
         <is>
-          <t>2026-08-14T20:55:16Z</t>
+          <t>2026-08-15T20:47:08Z</t>
         </is>
       </c>
     </row>
@@ -9236,7 +9236,7 @@
       </c>
       <c r="S107" s="4" t="inlineStr">
         <is>
-          <t>2026-08-14T20:55:16Z</t>
+          <t>2026-08-15T20:47:08Z</t>
         </is>
       </c>
     </row>
@@ -9321,7 +9321,7 @@
       </c>
       <c r="S108" s="4" t="inlineStr">
         <is>
-          <t>2026-08-14T20:55:16Z</t>
+          <t>2026-08-15T20:47:08Z</t>
         </is>
       </c>
     </row>
@@ -9406,7 +9406,7 @@
       </c>
       <c r="S109" s="4" t="inlineStr">
         <is>
-          <t>2026-08-14T20:55:16Z</t>
+          <t>2026-08-15T20:47:08Z</t>
         </is>
       </c>
     </row>
@@ -9491,7 +9491,7 @@
       </c>
       <c r="S110" s="4" t="inlineStr">
         <is>
-          <t>2026-08-14T20:55:16Z</t>
+          <t>2026-08-15T20:47:08Z</t>
         </is>
       </c>
     </row>
@@ -9576,7 +9576,7 @@
       </c>
       <c r="S111" s="4" t="inlineStr">
         <is>
-          <t>2026-08-14T20:55:16Z</t>
+          <t>2026-08-15T20:47:08Z</t>
         </is>
       </c>
     </row>
@@ -9661,7 +9661,7 @@
       </c>
       <c r="S112" s="4" t="inlineStr">
         <is>
-          <t>2026-08-14T20:55:16Z</t>
+          <t>2026-08-15T20:47:08Z</t>
         </is>
       </c>
     </row>
@@ -9746,7 +9746,7 @@
       </c>
       <c r="S113" s="4" t="inlineStr">
         <is>
-          <t>2026-08-14T20:55:16Z</t>
+          <t>2026-08-15T20:47:08Z</t>
         </is>
       </c>
     </row>
@@ -9831,7 +9831,7 @@
       </c>
       <c r="S114" s="4" t="inlineStr">
         <is>
-          <t>2026-08-14T20:55:16Z</t>
+          <t>2026-08-15T20:47:08Z</t>
         </is>
       </c>
     </row>
@@ -9916,7 +9916,7 @@
       </c>
       <c r="S115" s="4" t="inlineStr">
         <is>
-          <t>2026-08-14T20:55:16Z</t>
+          <t>2026-08-15T20:47:08Z</t>
         </is>
       </c>
     </row>
@@ -10001,7 +10001,7 @@
       </c>
       <c r="S116" s="4" t="inlineStr">
         <is>
-          <t>2026-08-14T20:55:16Z</t>
+          <t>2026-08-15T20:47:08Z</t>
         </is>
       </c>
     </row>
@@ -10086,7 +10086,7 @@
       </c>
       <c r="S117" s="4" t="inlineStr">
         <is>
-          <t>2026-08-14T20:55:16Z</t>
+          <t>2026-08-15T20:47:08Z</t>
         </is>
       </c>
     </row>
@@ -10171,7 +10171,7 @@
       </c>
       <c r="S118" s="4" t="inlineStr">
         <is>
-          <t>2026-08-14T20:55:16Z</t>
+          <t>2026-08-15T20:47:08Z</t>
         </is>
       </c>
     </row>
@@ -10256,7 +10256,7 @@
       </c>
       <c r="S119" s="4" t="inlineStr">
         <is>
-          <t>2026-08-14T20:55:16Z</t>
+          <t>2026-08-15T20:47:08Z</t>
         </is>
       </c>
     </row>
@@ -10341,7 +10341,7 @@
       </c>
       <c r="S120" s="4" t="inlineStr">
         <is>
-          <t>2026-08-14T20:55:16Z</t>
+          <t>2026-08-15T20:47:08Z</t>
         </is>
       </c>
     </row>
@@ -10426,7 +10426,7 @@
       </c>
       <c r="S121" s="4" t="inlineStr">
         <is>
-          <t>2026-08-14T20:55:16Z</t>
+          <t>2026-08-15T20:47:08Z</t>
         </is>
       </c>
     </row>
@@ -10511,7 +10511,7 @@
       </c>
       <c r="S122" s="4" t="inlineStr">
         <is>
-          <t>2026-08-14T20:55:16Z</t>
+          <t>2026-08-15T20:47:08Z</t>
         </is>
       </c>
     </row>
@@ -10596,7 +10596,7 @@
       </c>
       <c r="S123" s="4" t="inlineStr">
         <is>
-          <t>2026-08-14T20:55:16Z</t>
+          <t>2026-08-15T20:47:08Z</t>
         </is>
       </c>
     </row>
@@ -10681,7 +10681,7 @@
       </c>
       <c r="S124" s="4" t="inlineStr">
         <is>
-          <t>2026-08-14T20:55:16Z</t>
+          <t>2026-08-15T20:47:08Z</t>
         </is>
       </c>
     </row>
@@ -10766,7 +10766,7 @@
       </c>
       <c r="S125" s="4" t="inlineStr">
         <is>
-          <t>2026-08-14T20:55:16Z</t>
+          <t>2026-08-15T20:47:08Z</t>
         </is>
       </c>
     </row>
@@ -10851,7 +10851,7 @@
       </c>
       <c r="S126" s="4" t="inlineStr">
         <is>
-          <t>2026-08-14T20:55:16Z</t>
+          <t>2026-08-15T20:47:08Z</t>
         </is>
       </c>
     </row>
@@ -10936,7 +10936,7 @@
       </c>
       <c r="S127" s="4" t="inlineStr">
         <is>
-          <t>2026-08-14T20:55:16Z</t>
+          <t>2026-08-15T20:47:08Z</t>
         </is>
       </c>
     </row>
@@ -11021,7 +11021,7 @@
       </c>
       <c r="S128" s="4" t="inlineStr">
         <is>
-          <t>2026-08-14T20:55:16Z</t>
+          <t>2026-08-15T20:47:08Z</t>
         </is>
       </c>
     </row>
@@ -11106,7 +11106,7 @@
       </c>
       <c r="S129" s="4" t="inlineStr">
         <is>
-          <t>2026-08-14T20:55:16Z</t>
+          <t>2026-08-15T20:47:08Z</t>
         </is>
       </c>
     </row>
@@ -11191,7 +11191,7 @@
       </c>
       <c r="S130" s="4" t="inlineStr">
         <is>
-          <t>2026-08-14T20:55:16Z</t>
+          <t>2026-08-15T20:47:08Z</t>
         </is>
       </c>
     </row>
@@ -11276,7 +11276,7 @@
       </c>
       <c r="S131" s="4" t="inlineStr">
         <is>
-          <t>2026-08-14T20:55:16Z</t>
+          <t>2026-08-15T20:47:08Z</t>
         </is>
       </c>
     </row>
@@ -11361,7 +11361,7 @@
       </c>
       <c r="S132" s="4" t="inlineStr">
         <is>
-          <t>2026-08-14T20:55:16Z</t>
+          <t>2026-08-15T20:47:08Z</t>
         </is>
       </c>
     </row>
@@ -11446,7 +11446,7 @@
       </c>
       <c r="S133" s="4" t="inlineStr">
         <is>
-          <t>2026-08-14T20:55:16Z</t>
+          <t>2026-08-15T20:47:08Z</t>
         </is>
       </c>
     </row>
@@ -11531,7 +11531,7 @@
       </c>
       <c r="S134" s="4" t="inlineStr">
         <is>
-          <t>2026-08-14T20:55:16Z</t>
+          <t>2026-08-15T20:47:08Z</t>
         </is>
       </c>
     </row>
@@ -11616,7 +11616,7 @@
       </c>
       <c r="S135" s="4" t="inlineStr">
         <is>
-          <t>2026-08-14T20:55:16Z</t>
+          <t>2026-08-15T20:47:08Z</t>
         </is>
       </c>
     </row>
@@ -11701,7 +11701,7 @@
       </c>
       <c r="S136" s="4" t="inlineStr">
         <is>
-          <t>2026-08-14T20:55:16Z</t>
+          <t>2026-08-15T20:47:08Z</t>
         </is>
       </c>
     </row>
@@ -11786,7 +11786,7 @@
       </c>
       <c r="S137" s="4" t="inlineStr">
         <is>
-          <t>2026-08-14T20:55:16Z</t>
+          <t>2026-08-15T20:47:08Z</t>
         </is>
       </c>
     </row>
@@ -11871,7 +11871,7 @@
       </c>
       <c r="S138" s="4" t="inlineStr">
         <is>
-          <t>2026-08-14T20:55:16Z</t>
+          <t>2026-08-15T20:47:08Z</t>
         </is>
       </c>
     </row>
@@ -11956,7 +11956,7 @@
       </c>
       <c r="S139" s="4" t="inlineStr">
         <is>
-          <t>2026-08-14T20:55:16Z</t>
+          <t>2026-08-15T20:47:08Z</t>
         </is>
       </c>
     </row>
@@ -12041,7 +12041,7 @@
       </c>
       <c r="S140" s="4" t="inlineStr">
         <is>
-          <t>2026-08-14T20:55:16Z</t>
+          <t>2026-08-15T20:47:08Z</t>
         </is>
       </c>
     </row>
@@ -12126,7 +12126,7 @@
       </c>
       <c r="S141" s="4" t="inlineStr">
         <is>
-          <t>2026-08-14T20:55:16Z</t>
+          <t>2026-08-15T20:47:08Z</t>
         </is>
       </c>
     </row>
@@ -12258,7 +12258,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>2026-08-14T20:55:16Z</t>
+          <t>2026-08-15T20:47:08Z</t>
         </is>
       </c>
     </row>
@@ -12338,7 +12338,7 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>{"dataset_id": "bcv_pib_historico_anual", "title": "Producto interno bruto histórico anual", "table": "PIB histórico anual", "source_file": "7_1_14_anual.xls", "base": "1957/1968/1984/1997", "price_type": "Precios constantes", "measure": "Nivel", "frequency": "Anual", "period": "2017", "year": 2017, "quarter": null, "classification": "Total economía", "component": "Producto interno bruto", "value": 392393.12, "unit": "Millones de bolívares a precios constantes", "status": "", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/7_1_14_anual.xls", "fetched_at": "2026-08-14T20:55:16Z"}</t>
+          <t>{"dataset_id": "bcv_pib_historico_anual", "title": "Producto interno bruto histórico anual", "table": "PIB histórico anual", "source_file": "7_1_14_anual.xls", "base": "1957/1968/1984/1997", "price_type": "Precios constantes", "measure": "Nivel", "frequency": "Anual", "period": "2017", "year": 2017, "quarter": null, "classification": "Total economía", "component": "Producto interno bruto", "value": 392393.12, "unit": "Millones de bolívares a precios constantes", "status": "", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/7_1_14_anual.xls", "fetched_at": "2026-08-15T20:47:08Z"}</t>
         </is>
       </c>
     </row>

--- a/assets/data/bcv/excel/ove_bcv_pib_historico_anual.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_pib_historico_anual.xlsx
@@ -736,7 +736,7 @@
       </c>
       <c r="S7" s="4" t="inlineStr">
         <is>
-          <t>2026-08-15T20:47:08Z</t>
+          <t>2026-08-16T20:46:08Z</t>
         </is>
       </c>
     </row>
@@ -821,7 +821,7 @@
       </c>
       <c r="S8" s="4" t="inlineStr">
         <is>
-          <t>2026-08-15T20:47:08Z</t>
+          <t>2026-08-16T20:46:08Z</t>
         </is>
       </c>
     </row>
@@ -906,7 +906,7 @@
       </c>
       <c r="S9" s="4" t="inlineStr">
         <is>
-          <t>2026-08-15T20:47:08Z</t>
+          <t>2026-08-16T20:46:08Z</t>
         </is>
       </c>
     </row>
@@ -991,7 +991,7 @@
       </c>
       <c r="S10" s="4" t="inlineStr">
         <is>
-          <t>2026-08-15T20:47:08Z</t>
+          <t>2026-08-16T20:46:08Z</t>
         </is>
       </c>
     </row>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="S11" s="4" t="inlineStr">
         <is>
-          <t>2026-08-15T20:47:08Z</t>
+          <t>2026-08-16T20:46:08Z</t>
         </is>
       </c>
     </row>
@@ -1161,7 +1161,7 @@
       </c>
       <c r="S12" s="4" t="inlineStr">
         <is>
-          <t>2026-08-15T20:47:08Z</t>
+          <t>2026-08-16T20:46:08Z</t>
         </is>
       </c>
     </row>
@@ -1246,7 +1246,7 @@
       </c>
       <c r="S13" s="4" t="inlineStr">
         <is>
-          <t>2026-08-15T20:47:08Z</t>
+          <t>2026-08-16T20:46:08Z</t>
         </is>
       </c>
     </row>
@@ -1331,7 +1331,7 @@
       </c>
       <c r="S14" s="4" t="inlineStr">
         <is>
-          <t>2026-08-15T20:47:08Z</t>
+          <t>2026-08-16T20:46:08Z</t>
         </is>
       </c>
     </row>
@@ -1416,7 +1416,7 @@
       </c>
       <c r="S15" s="4" t="inlineStr">
         <is>
-          <t>2026-08-15T20:47:08Z</t>
+          <t>2026-08-16T20:46:08Z</t>
         </is>
       </c>
     </row>
@@ -1501,7 +1501,7 @@
       </c>
       <c r="S16" s="4" t="inlineStr">
         <is>
-          <t>2026-08-15T20:47:08Z</t>
+          <t>2026-08-16T20:46:08Z</t>
         </is>
       </c>
     </row>
@@ -1586,7 +1586,7 @@
       </c>
       <c r="S17" s="4" t="inlineStr">
         <is>
-          <t>2026-08-15T20:47:08Z</t>
+          <t>2026-08-16T20:46:08Z</t>
         </is>
       </c>
     </row>
@@ -1671,7 +1671,7 @@
       </c>
       <c r="S18" s="4" t="inlineStr">
         <is>
-          <t>2026-08-15T20:47:08Z</t>
+          <t>2026-08-16T20:46:08Z</t>
         </is>
       </c>
     </row>
@@ -1756,7 +1756,7 @@
       </c>
       <c r="S19" s="4" t="inlineStr">
         <is>
-          <t>2026-08-15T20:47:08Z</t>
+          <t>2026-08-16T20:46:08Z</t>
         </is>
       </c>
     </row>
@@ -1841,7 +1841,7 @@
       </c>
       <c r="S20" s="4" t="inlineStr">
         <is>
-          <t>2026-08-15T20:47:08Z</t>
+          <t>2026-08-16T20:46:08Z</t>
         </is>
       </c>
     </row>
@@ -1926,7 +1926,7 @@
       </c>
       <c r="S21" s="4" t="inlineStr">
         <is>
-          <t>2026-08-15T20:47:08Z</t>
+          <t>2026-08-16T20:46:08Z</t>
         </is>
       </c>
     </row>
@@ -2011,7 +2011,7 @@
       </c>
       <c r="S22" s="4" t="inlineStr">
         <is>
-          <t>2026-08-15T20:47:08Z</t>
+          <t>2026-08-16T20:46:08Z</t>
         </is>
       </c>
     </row>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="S23" s="4" t="inlineStr">
         <is>
-          <t>2026-08-15T20:47:08Z</t>
+          <t>2026-08-16T20:46:08Z</t>
         </is>
       </c>
     </row>
@@ -2181,7 +2181,7 @@
       </c>
       <c r="S24" s="4" t="inlineStr">
         <is>
-          <t>2026-08-15T20:47:08Z</t>
+          <t>2026-08-16T20:46:08Z</t>
         </is>
       </c>
     </row>
@@ -2266,7 +2266,7 @@
       </c>
       <c r="S25" s="4" t="inlineStr">
         <is>
-          <t>2026-08-15T20:47:08Z</t>
+          <t>2026-08-16T20:46:08Z</t>
         </is>
       </c>
     </row>
@@ -2351,7 +2351,7 @@
       </c>
       <c r="S26" s="4" t="inlineStr">
         <is>
-          <t>2026-08-15T20:47:08Z</t>
+          <t>2026-08-16T20:46:08Z</t>
         </is>
       </c>
     </row>
@@ -2436,7 +2436,7 @@
       </c>
       <c r="S27" s="4" t="inlineStr">
         <is>
-          <t>2026-08-15T20:47:08Z</t>
+          <t>2026-08-16T20:46:08Z</t>
         </is>
       </c>
     </row>
@@ -2521,7 +2521,7 @@
       </c>
       <c r="S28" s="4" t="inlineStr">
         <is>
-          <t>2026-08-15T20:47:08Z</t>
+          <t>2026-08-16T20:46:08Z</t>
         </is>
       </c>
     </row>
@@ -2606,7 +2606,7 @@
       </c>
       <c r="S29" s="4" t="inlineStr">
         <is>
-          <t>2026-08-15T20:47:08Z</t>
+          <t>2026-08-16T20:46:08Z</t>
         </is>
       </c>
     </row>
@@ -2691,7 +2691,7 @@
       </c>
       <c r="S30" s="4" t="inlineStr">
         <is>
-          <t>2026-08-15T20:47:08Z</t>
+          <t>2026-08-16T20:46:08Z</t>
         </is>
       </c>
     </row>
@@ -2776,7 +2776,7 @@
       </c>
       <c r="S31" s="4" t="inlineStr">
         <is>
-          <t>2026-08-15T20:47:08Z</t>
+          <t>2026-08-16T20:46:08Z</t>
         </is>
       </c>
     </row>
@@ -2861,7 +2861,7 @@
       </c>
       <c r="S32" s="4" t="inlineStr">
         <is>
-          <t>2026-08-15T20:47:08Z</t>
+          <t>2026-08-16T20:46:08Z</t>
         </is>
       </c>
     </row>
@@ -2946,7 +2946,7 @@
       </c>
       <c r="S33" s="4" t="inlineStr">
         <is>
-          <t>2026-08-15T20:47:08Z</t>
+          <t>2026-08-16T20:46:08Z</t>
         </is>
       </c>
     </row>
@@ -3031,7 +3031,7 @@
       </c>
       <c r="S34" s="4" t="inlineStr">
         <is>
-          <t>2026-08-15T20:47:08Z</t>
+          <t>2026-08-16T20:46:08Z</t>
         </is>
       </c>
     </row>
@@ -3116,7 +3116,7 @@
       </c>
       <c r="S35" s="4" t="inlineStr">
         <is>
-          <t>2026-08-15T20:47:08Z</t>
+          <t>2026-08-16T20:46:08Z</t>
         </is>
       </c>
     </row>
@@ -3201,7 +3201,7 @@
       </c>
       <c r="S36" s="4" t="inlineStr">
         <is>
-          <t>2026-08-15T20:47:08Z</t>
+          <t>2026-08-16T20:46:08Z</t>
         </is>
       </c>
     </row>
@@ -3286,7 +3286,7 @@
       </c>
       <c r="S37" s="4" t="inlineStr">
         <is>
-          <t>2026-08-15T20:47:08Z</t>
+          <t>2026-08-16T20:46:08Z</t>
         </is>
       </c>
     </row>
@@ -3371,7 +3371,7 @@
       </c>
       <c r="S38" s="4" t="inlineStr">
         <is>
-          <t>2026-08-15T20:47:08Z</t>
+          <t>2026-08-16T20:46:08Z</t>
         </is>
       </c>
     </row>
@@ -3456,7 +3456,7 @@
       </c>
       <c r="S39" s="4" t="inlineStr">
         <is>
-          <t>2026-08-15T20:47:08Z</t>
+          <t>2026-08-16T20:46:08Z</t>
         </is>
       </c>
     </row>
@@ -3541,7 +3541,7 @@
       </c>
       <c r="S40" s="4" t="inlineStr">
         <is>
-          <t>2026-08-15T20:47:08Z</t>
+          <t>2026-08-16T20:46:08Z</t>
         </is>
       </c>
     </row>
@@ -3626,7 +3626,7 @@
       </c>
       <c r="S41" s="4" t="inlineStr">
         <is>
-          <t>2026-08-15T20:47:08Z</t>
+          <t>2026-08-16T20:46:08Z</t>
         </is>
       </c>
     </row>
@@ -3711,7 +3711,7 @@
       </c>
       <c r="S42" s="4" t="inlineStr">
         <is>
-          <t>2026-08-15T20:47:08Z</t>
+          <t>2026-08-16T20:46:08Z</t>
         </is>
       </c>
     </row>
@@ -3796,7 +3796,7 @@
       </c>
       <c r="S43" s="4" t="inlineStr">
         <is>
-          <t>2026-08-15T20:47:08Z</t>
+          <t>2026-08-16T20:46:08Z</t>
         </is>
       </c>
     </row>
@@ -3881,7 +3881,7 @@
       </c>
       <c r="S44" s="4" t="inlineStr">
         <is>
-          <t>2026-08-15T20:47:08Z</t>
+          <t>2026-08-16T20:46:08Z</t>
         </is>
       </c>
     </row>
@@ -3966,7 +3966,7 @@
       </c>
       <c r="S45" s="4" t="inlineStr">
         <is>
-          <t>2026-08-15T20:47:08Z</t>
+          <t>2026-08-16T20:46:08Z</t>
         </is>
       </c>
     </row>
@@ -4051,7 +4051,7 @@
       </c>
       <c r="S46" s="4" t="inlineStr">
         <is>
-          <t>2026-08-15T20:47:08Z</t>
+          <t>2026-08-16T20:46:08Z</t>
         </is>
       </c>
     </row>
@@ -4136,7 +4136,7 @@
       </c>
       <c r="S47" s="4" t="inlineStr">
         <is>
-          <t>2026-08-15T20:47:08Z</t>
+          <t>2026-08-16T20:46:08Z</t>
         </is>
       </c>
     </row>
@@ -4221,7 +4221,7 @@
       </c>
       <c r="S48" s="4" t="inlineStr">
         <is>
-          <t>2026-08-15T20:47:08Z</t>
+          <t>2026-08-16T20:46:08Z</t>
         </is>
       </c>
     </row>
@@ -4306,7 +4306,7 @@
       </c>
       <c r="S49" s="4" t="inlineStr">
         <is>
-          <t>2026-08-15T20:47:08Z</t>
+          <t>2026-08-16T20:46:08Z</t>
         </is>
       </c>
     </row>
@@ -4391,7 +4391,7 @@
       </c>
       <c r="S50" s="4" t="inlineStr">
         <is>
-          <t>2026-08-15T20:47:08Z</t>
+          <t>2026-08-16T20:46:08Z</t>
         </is>
       </c>
     </row>
@@ -4476,7 +4476,7 @@
       </c>
       <c r="S51" s="4" t="inlineStr">
         <is>
-          <t>2026-08-15T20:47:08Z</t>
+          <t>2026-08-16T20:46:08Z</t>
         </is>
       </c>
     </row>
@@ -4561,7 +4561,7 @@
       </c>
       <c r="S52" s="4" t="inlineStr">
         <is>
-          <t>2026-08-15T20:47:08Z</t>
+          <t>2026-08-16T20:46:08Z</t>
         </is>
       </c>
     </row>
@@ -4646,7 +4646,7 @@
       </c>
       <c r="S53" s="4" t="inlineStr">
         <is>
-          <t>2026-08-15T20:47:08Z</t>
+          <t>2026-08-16T20:46:08Z</t>
         </is>
       </c>
     </row>
@@ -4731,7 +4731,7 @@
       </c>
       <c r="S54" s="4" t="inlineStr">
         <is>
-          <t>2026-08-15T20:47:08Z</t>
+          <t>2026-08-16T20:46:08Z</t>
         </is>
       </c>
     </row>
@@ -4816,7 +4816,7 @@
       </c>
       <c r="S55" s="4" t="inlineStr">
         <is>
-          <t>2026-08-15T20:47:08Z</t>
+          <t>2026-08-16T20:46:08Z</t>
         </is>
       </c>
     </row>
@@ -4901,7 +4901,7 @@
       </c>
       <c r="S56" s="4" t="inlineStr">
         <is>
-          <t>2026-08-15T20:47:08Z</t>
+          <t>2026-08-16T20:46:08Z</t>
         </is>
       </c>
     </row>
@@ -4986,7 +4986,7 @@
       </c>
       <c r="S57" s="4" t="inlineStr">
         <is>
-          <t>2026-08-15T20:47:08Z</t>
+          <t>2026-08-16T20:46:08Z</t>
         </is>
       </c>
     </row>
@@ -5071,7 +5071,7 @@
       </c>
       <c r="S58" s="4" t="inlineStr">
         <is>
-          <t>2026-08-15T20:47:08Z</t>
+          <t>2026-08-16T20:46:08Z</t>
         </is>
       </c>
     </row>
@@ -5156,7 +5156,7 @@
       </c>
       <c r="S59" s="4" t="inlineStr">
         <is>
-          <t>2026-08-15T20:47:08Z</t>
+          <t>2026-08-16T20:46:08Z</t>
         </is>
       </c>
     </row>
@@ -5241,7 +5241,7 @@
       </c>
       <c r="S60" s="4" t="inlineStr">
         <is>
-          <t>2026-08-15T20:47:08Z</t>
+          <t>2026-08-16T20:46:08Z</t>
         </is>
       </c>
     </row>
@@ -5326,7 +5326,7 @@
       </c>
       <c r="S61" s="4" t="inlineStr">
         <is>
-          <t>2026-08-15T20:47:08Z</t>
+          <t>2026-08-16T20:46:08Z</t>
         </is>
       </c>
     </row>
@@ -5411,7 +5411,7 @@
       </c>
       <c r="S62" s="4" t="inlineStr">
         <is>
-          <t>2026-08-15T20:47:08Z</t>
+          <t>2026-08-16T20:46:08Z</t>
         </is>
       </c>
     </row>
@@ -5496,7 +5496,7 @@
       </c>
       <c r="S63" s="4" t="inlineStr">
         <is>
-          <t>2026-08-15T20:47:08Z</t>
+          <t>2026-08-16T20:46:08Z</t>
         </is>
       </c>
     </row>
@@ -5581,7 +5581,7 @@
       </c>
       <c r="S64" s="4" t="inlineStr">
         <is>
-          <t>2026-08-15T20:47:08Z</t>
+          <t>2026-08-16T20:46:08Z</t>
         </is>
       </c>
     </row>
@@ -5666,7 +5666,7 @@
       </c>
       <c r="S65" s="4" t="inlineStr">
         <is>
-          <t>2026-08-15T20:47:08Z</t>
+          <t>2026-08-16T20:46:08Z</t>
         </is>
       </c>
     </row>
@@ -5751,7 +5751,7 @@
       </c>
       <c r="S66" s="4" t="inlineStr">
         <is>
-          <t>2026-08-15T20:47:08Z</t>
+          <t>2026-08-16T20:46:08Z</t>
         </is>
       </c>
     </row>
@@ -5836,7 +5836,7 @@
       </c>
       <c r="S67" s="4" t="inlineStr">
         <is>
-          <t>2026-08-15T20:47:08Z</t>
+          <t>2026-08-16T20:46:08Z</t>
         </is>
       </c>
     </row>
@@ -5921,7 +5921,7 @@
       </c>
       <c r="S68" s="4" t="inlineStr">
         <is>
-          <t>2026-08-15T20:47:08Z</t>
+          <t>2026-08-16T20:46:08Z</t>
         </is>
       </c>
     </row>
@@ -6006,7 +6006,7 @@
       </c>
       <c r="S69" s="4" t="inlineStr">
         <is>
-          <t>2026-08-15T20:47:08Z</t>
+          <t>2026-08-16T20:46:08Z</t>
         </is>
       </c>
     </row>
@@ -6091,7 +6091,7 @@
       </c>
       <c r="S70" s="4" t="inlineStr">
         <is>
-          <t>2026-08-15T20:47:08Z</t>
+          <t>2026-08-16T20:46:08Z</t>
         </is>
       </c>
     </row>
@@ -6176,7 +6176,7 @@
       </c>
       <c r="S71" s="4" t="inlineStr">
         <is>
-          <t>2026-08-15T20:47:08Z</t>
+          <t>2026-08-16T20:46:08Z</t>
         </is>
       </c>
     </row>
@@ -6261,7 +6261,7 @@
       </c>
       <c r="S72" s="4" t="inlineStr">
         <is>
-          <t>2026-08-15T20:47:08Z</t>
+          <t>2026-08-16T20:46:08Z</t>
         </is>
       </c>
     </row>
@@ -6346,7 +6346,7 @@
       </c>
       <c r="S73" s="4" t="inlineStr">
         <is>
-          <t>2026-08-15T20:47:08Z</t>
+          <t>2026-08-16T20:46:08Z</t>
         </is>
       </c>
     </row>
@@ -6431,7 +6431,7 @@
       </c>
       <c r="S74" s="4" t="inlineStr">
         <is>
-          <t>2026-08-15T20:47:08Z</t>
+          <t>2026-08-16T20:46:08Z</t>
         </is>
       </c>
     </row>
@@ -6516,7 +6516,7 @@
       </c>
       <c r="S75" s="4" t="inlineStr">
         <is>
-          <t>2026-08-15T20:47:08Z</t>
+          <t>2026-08-16T20:46:08Z</t>
         </is>
       </c>
     </row>
@@ -6601,7 +6601,7 @@
       </c>
       <c r="S76" s="4" t="inlineStr">
         <is>
-          <t>2026-08-15T20:47:08Z</t>
+          <t>2026-08-16T20:46:08Z</t>
         </is>
       </c>
     </row>
@@ -6686,7 +6686,7 @@
       </c>
       <c r="S77" s="4" t="inlineStr">
         <is>
-          <t>2026-08-15T20:47:08Z</t>
+          <t>2026-08-16T20:46:08Z</t>
         </is>
       </c>
     </row>
@@ -6771,7 +6771,7 @@
       </c>
       <c r="S78" s="4" t="inlineStr">
         <is>
-          <t>2026-08-15T20:47:08Z</t>
+          <t>2026-08-16T20:46:08Z</t>
         </is>
       </c>
     </row>
@@ -6856,7 +6856,7 @@
       </c>
       <c r="S79" s="4" t="inlineStr">
         <is>
-          <t>2026-08-15T20:47:08Z</t>
+          <t>2026-08-16T20:46:08Z</t>
         </is>
       </c>
     </row>
@@ -6941,7 +6941,7 @@
       </c>
       <c r="S80" s="4" t="inlineStr">
         <is>
-          <t>2026-08-15T20:47:08Z</t>
+          <t>2026-08-16T20:46:08Z</t>
         </is>
       </c>
     </row>
@@ -7026,7 +7026,7 @@
       </c>
       <c r="S81" s="4" t="inlineStr">
         <is>
-          <t>2026-08-15T20:47:08Z</t>
+          <t>2026-08-16T20:46:08Z</t>
         </is>
       </c>
     </row>
@@ -7111,7 +7111,7 @@
       </c>
       <c r="S82" s="4" t="inlineStr">
         <is>
-          <t>2026-08-15T20:47:08Z</t>
+          <t>2026-08-16T20:46:08Z</t>
         </is>
       </c>
     </row>
@@ -7196,7 +7196,7 @@
       </c>
       <c r="S83" s="4" t="inlineStr">
         <is>
-          <t>2026-08-15T20:47:08Z</t>
+          <t>2026-08-16T20:46:08Z</t>
         </is>
       </c>
     </row>
@@ -7281,7 +7281,7 @@
       </c>
       <c r="S84" s="4" t="inlineStr">
         <is>
-          <t>2026-08-15T20:47:08Z</t>
+          <t>2026-08-16T20:46:08Z</t>
         </is>
       </c>
     </row>
@@ -7366,7 +7366,7 @@
       </c>
       <c r="S85" s="4" t="inlineStr">
         <is>
-          <t>2026-08-15T20:47:08Z</t>
+          <t>2026-08-16T20:46:08Z</t>
         </is>
       </c>
     </row>
@@ -7451,7 +7451,7 @@
       </c>
       <c r="S86" s="4" t="inlineStr">
         <is>
-          <t>2026-08-15T20:47:08Z</t>
+          <t>2026-08-16T20:46:08Z</t>
         </is>
       </c>
     </row>
@@ -7536,7 +7536,7 @@
       </c>
       <c r="S87" s="4" t="inlineStr">
         <is>
-          <t>2026-08-15T20:47:08Z</t>
+          <t>2026-08-16T20:46:08Z</t>
         </is>
       </c>
     </row>
@@ -7621,7 +7621,7 @@
       </c>
       <c r="S88" s="4" t="inlineStr">
         <is>
-          <t>2026-08-15T20:47:08Z</t>
+          <t>2026-08-16T20:46:08Z</t>
         </is>
       </c>
     </row>
@@ -7706,7 +7706,7 @@
       </c>
       <c r="S89" s="4" t="inlineStr">
         <is>
-          <t>2026-08-15T20:47:08Z</t>
+          <t>2026-08-16T20:46:08Z</t>
         </is>
       </c>
     </row>
@@ -7791,7 +7791,7 @@
       </c>
       <c r="S90" s="4" t="inlineStr">
         <is>
-          <t>2026-08-15T20:47:08Z</t>
+          <t>2026-08-16T20:46:08Z</t>
         </is>
       </c>
     </row>
@@ -7876,7 +7876,7 @@
       </c>
       <c r="S91" s="4" t="inlineStr">
         <is>
-          <t>2026-08-15T20:47:08Z</t>
+          <t>2026-08-16T20:46:08Z</t>
         </is>
       </c>
     </row>
@@ -7961,7 +7961,7 @@
       </c>
       <c r="S92" s="4" t="inlineStr">
         <is>
-          <t>2026-08-15T20:47:08Z</t>
+          <t>2026-08-16T20:46:08Z</t>
         </is>
       </c>
     </row>
@@ -8046,7 +8046,7 @@
       </c>
       <c r="S93" s="4" t="inlineStr">
         <is>
-          <t>2026-08-15T20:47:08Z</t>
+          <t>2026-08-16T20:46:08Z</t>
         </is>
       </c>
     </row>
@@ -8131,7 +8131,7 @@
       </c>
       <c r="S94" s="4" t="inlineStr">
         <is>
-          <t>2026-08-15T20:47:08Z</t>
+          <t>2026-08-16T20:46:08Z</t>
         </is>
       </c>
     </row>
@@ -8216,7 +8216,7 @@
       </c>
       <c r="S95" s="4" t="inlineStr">
         <is>
-          <t>2026-08-15T20:47:08Z</t>
+          <t>2026-08-16T20:46:08Z</t>
         </is>
       </c>
     </row>
@@ -8301,7 +8301,7 @@
       </c>
       <c r="S96" s="4" t="inlineStr">
         <is>
-          <t>2026-08-15T20:47:08Z</t>
+          <t>2026-08-16T20:46:08Z</t>
         </is>
       </c>
     </row>
@@ -8386,7 +8386,7 @@
       </c>
       <c r="S97" s="4" t="inlineStr">
         <is>
-          <t>2026-08-15T20:47:08Z</t>
+          <t>2026-08-16T20:46:08Z</t>
         </is>
       </c>
     </row>
@@ -8471,7 +8471,7 @@
       </c>
       <c r="S98" s="4" t="inlineStr">
         <is>
-          <t>2026-08-15T20:47:08Z</t>
+          <t>2026-08-16T20:46:08Z</t>
         </is>
       </c>
     </row>
@@ -8556,7 +8556,7 @@
       </c>
       <c r="S99" s="4" t="inlineStr">
         <is>
-          <t>2026-08-15T20:47:08Z</t>
+          <t>2026-08-16T20:46:08Z</t>
         </is>
       </c>
     </row>
@@ -8641,7 +8641,7 @@
       </c>
       <c r="S100" s="4" t="inlineStr">
         <is>
-          <t>2026-08-15T20:47:08Z</t>
+          <t>2026-08-16T20:46:08Z</t>
         </is>
       </c>
     </row>
@@ -8726,7 +8726,7 @@
       </c>
       <c r="S101" s="4" t="inlineStr">
         <is>
-          <t>2026-08-15T20:47:08Z</t>
+          <t>2026-08-16T20:46:08Z</t>
         </is>
       </c>
     </row>
@@ -8811,7 +8811,7 @@
       </c>
       <c r="S102" s="4" t="inlineStr">
         <is>
-          <t>2026-08-15T20:47:08Z</t>
+          <t>2026-08-16T20:46:08Z</t>
         </is>
       </c>
     </row>
@@ -8896,7 +8896,7 @@
       </c>
       <c r="S103" s="4" t="inlineStr">
         <is>
-          <t>2026-08-15T20:47:08Z</t>
+          <t>2026-08-16T20:46:08Z</t>
         </is>
       </c>
     </row>
@@ -8981,7 +8981,7 @@
       </c>
       <c r="S104" s="4" t="inlineStr">
         <is>
-          <t>2026-08-15T20:47:08Z</t>
+          <t>2026-08-16T20:46:08Z</t>
         </is>
       </c>
     </row>
@@ -9066,7 +9066,7 @@
       </c>
       <c r="S105" s="4" t="inlineStr">
         <is>
-          <t>2026-08-15T20:47:08Z</t>
+          <t>2026-08-16T20:46:08Z</t>
         </is>
       </c>
     </row>
@@ -9151,7 +9151,7 @@
       </c>
       <c r="S106" s="4" t="inlineStr">
         <is>
-          <t>2026-08-15T20:47:08Z</t>
+          <t>2026-08-16T20:46:08Z</t>
         </is>
       </c>
     </row>
@@ -9236,7 +9236,7 @@
       </c>
       <c r="S107" s="4" t="inlineStr">
         <is>
-          <t>2026-08-15T20:47:08Z</t>
+          <t>2026-08-16T20:46:08Z</t>
         </is>
       </c>
     </row>
@@ -9321,7 +9321,7 @@
       </c>
       <c r="S108" s="4" t="inlineStr">
         <is>
-          <t>2026-08-15T20:47:08Z</t>
+          <t>2026-08-16T20:46:08Z</t>
         </is>
       </c>
     </row>
@@ -9406,7 +9406,7 @@
       </c>
       <c r="S109" s="4" t="inlineStr">
         <is>
-          <t>2026-08-15T20:47:08Z</t>
+          <t>2026-08-16T20:46:08Z</t>
         </is>
       </c>
     </row>
@@ -9491,7 +9491,7 @@
       </c>
       <c r="S110" s="4" t="inlineStr">
         <is>
-          <t>2026-08-15T20:47:08Z</t>
+          <t>2026-08-16T20:46:08Z</t>
         </is>
       </c>
     </row>
@@ -9576,7 +9576,7 @@
       </c>
       <c r="S111" s="4" t="inlineStr">
         <is>
-          <t>2026-08-15T20:47:08Z</t>
+          <t>2026-08-16T20:46:08Z</t>
         </is>
       </c>
     </row>
@@ -9661,7 +9661,7 @@
       </c>
       <c r="S112" s="4" t="inlineStr">
         <is>
-          <t>2026-08-15T20:47:08Z</t>
+          <t>2026-08-16T20:46:08Z</t>
         </is>
       </c>
     </row>
@@ -9746,7 +9746,7 @@
       </c>
       <c r="S113" s="4" t="inlineStr">
         <is>
-          <t>2026-08-15T20:47:08Z</t>
+          <t>2026-08-16T20:46:08Z</t>
         </is>
       </c>
     </row>
@@ -9831,7 +9831,7 @@
       </c>
       <c r="S114" s="4" t="inlineStr">
         <is>
-          <t>2026-08-15T20:47:08Z</t>
+          <t>2026-08-16T20:46:08Z</t>
         </is>
       </c>
     </row>
@@ -9916,7 +9916,7 @@
       </c>
       <c r="S115" s="4" t="inlineStr">
         <is>
-          <t>2026-08-15T20:47:08Z</t>
+          <t>2026-08-16T20:46:08Z</t>
         </is>
       </c>
     </row>
@@ -10001,7 +10001,7 @@
       </c>
       <c r="S116" s="4" t="inlineStr">
         <is>
-          <t>2026-08-15T20:47:08Z</t>
+          <t>2026-08-16T20:46:08Z</t>
         </is>
       </c>
     </row>
@@ -10086,7 +10086,7 @@
       </c>
       <c r="S117" s="4" t="inlineStr">
         <is>
-          <t>2026-08-15T20:47:08Z</t>
+          <t>2026-08-16T20:46:08Z</t>
         </is>
       </c>
     </row>
@@ -10171,7 +10171,7 @@
       </c>
       <c r="S118" s="4" t="inlineStr">
         <is>
-          <t>2026-08-15T20:47:08Z</t>
+          <t>2026-08-16T20:46:08Z</t>
         </is>
       </c>
     </row>
@@ -10256,7 +10256,7 @@
       </c>
       <c r="S119" s="4" t="inlineStr">
         <is>
-          <t>2026-08-15T20:47:08Z</t>
+          <t>2026-08-16T20:46:08Z</t>
         </is>
       </c>
     </row>
@@ -10341,7 +10341,7 @@
       </c>
       <c r="S120" s="4" t="inlineStr">
         <is>
-          <t>2026-08-15T20:47:08Z</t>
+          <t>2026-08-16T20:46:08Z</t>
         </is>
       </c>
     </row>
@@ -10426,7 +10426,7 @@
       </c>
       <c r="S121" s="4" t="inlineStr">
         <is>
-          <t>2026-08-15T20:47:08Z</t>
+          <t>2026-08-16T20:46:08Z</t>
         </is>
       </c>
     </row>
@@ -10511,7 +10511,7 @@
       </c>
       <c r="S122" s="4" t="inlineStr">
         <is>
-          <t>2026-08-15T20:47:08Z</t>
+          <t>2026-08-16T20:46:08Z</t>
         </is>
       </c>
     </row>
@@ -10596,7 +10596,7 @@
       </c>
       <c r="S123" s="4" t="inlineStr">
         <is>
-          <t>2026-08-15T20:47:08Z</t>
+          <t>2026-08-16T20:46:08Z</t>
         </is>
       </c>
     </row>
@@ -10681,7 +10681,7 @@
       </c>
       <c r="S124" s="4" t="inlineStr">
         <is>
-          <t>2026-08-15T20:47:08Z</t>
+          <t>2026-08-16T20:46:08Z</t>
         </is>
       </c>
     </row>
@@ -10766,7 +10766,7 @@
       </c>
       <c r="S125" s="4" t="inlineStr">
         <is>
-          <t>2026-08-15T20:47:08Z</t>
+          <t>2026-08-16T20:46:08Z</t>
         </is>
       </c>
     </row>
@@ -10851,7 +10851,7 @@
       </c>
       <c r="S126" s="4" t="inlineStr">
         <is>
-          <t>2026-08-15T20:47:08Z</t>
+          <t>2026-08-16T20:46:08Z</t>
         </is>
       </c>
     </row>
@@ -10936,7 +10936,7 @@
       </c>
       <c r="S127" s="4" t="inlineStr">
         <is>
-          <t>2026-08-15T20:47:08Z</t>
+          <t>2026-08-16T20:46:08Z</t>
         </is>
       </c>
     </row>
@@ -11021,7 +11021,7 @@
       </c>
       <c r="S128" s="4" t="inlineStr">
         <is>
-          <t>2026-08-15T20:47:08Z</t>
+          <t>2026-08-16T20:46:08Z</t>
         </is>
       </c>
     </row>
@@ -11106,7 +11106,7 @@
       </c>
       <c r="S129" s="4" t="inlineStr">
         <is>
-          <t>2026-08-15T20:47:08Z</t>
+          <t>2026-08-16T20:46:08Z</t>
         </is>
       </c>
     </row>
@@ -11191,7 +11191,7 @@
       </c>
       <c r="S130" s="4" t="inlineStr">
         <is>
-          <t>2026-08-15T20:47:08Z</t>
+          <t>2026-08-16T20:46:08Z</t>
         </is>
       </c>
     </row>
@@ -11276,7 +11276,7 @@
       </c>
       <c r="S131" s="4" t="inlineStr">
         <is>
-          <t>2026-08-15T20:47:08Z</t>
+          <t>2026-08-16T20:46:08Z</t>
         </is>
       </c>
     </row>
@@ -11361,7 +11361,7 @@
       </c>
       <c r="S132" s="4" t="inlineStr">
         <is>
-          <t>2026-08-15T20:47:08Z</t>
+          <t>2026-08-16T20:46:08Z</t>
         </is>
       </c>
     </row>
@@ -11446,7 +11446,7 @@
       </c>
       <c r="S133" s="4" t="inlineStr">
         <is>
-          <t>2026-08-15T20:47:08Z</t>
+          <t>2026-08-16T20:46:08Z</t>
         </is>
       </c>
     </row>
@@ -11531,7 +11531,7 @@
       </c>
       <c r="S134" s="4" t="inlineStr">
         <is>
-          <t>2026-08-15T20:47:08Z</t>
+          <t>2026-08-16T20:46:08Z</t>
         </is>
       </c>
     </row>
@@ -11616,7 +11616,7 @@
       </c>
       <c r="S135" s="4" t="inlineStr">
         <is>
-          <t>2026-08-15T20:47:08Z</t>
+          <t>2026-08-16T20:46:08Z</t>
         </is>
       </c>
     </row>
@@ -11701,7 +11701,7 @@
       </c>
       <c r="S136" s="4" t="inlineStr">
         <is>
-          <t>2026-08-15T20:47:08Z</t>
+          <t>2026-08-16T20:46:08Z</t>
         </is>
       </c>
     </row>
@@ -11786,7 +11786,7 @@
       </c>
       <c r="S137" s="4" t="inlineStr">
         <is>
-          <t>2026-08-15T20:47:08Z</t>
+          <t>2026-08-16T20:46:08Z</t>
         </is>
       </c>
     </row>
@@ -11871,7 +11871,7 @@
       </c>
       <c r="S138" s="4" t="inlineStr">
         <is>
-          <t>2026-08-15T20:47:08Z</t>
+          <t>2026-08-16T20:46:08Z</t>
         </is>
       </c>
     </row>
@@ -11956,7 +11956,7 @@
       </c>
       <c r="S139" s="4" t="inlineStr">
         <is>
-          <t>2026-08-15T20:47:08Z</t>
+          <t>2026-08-16T20:46:08Z</t>
         </is>
       </c>
     </row>
@@ -12041,7 +12041,7 @@
       </c>
       <c r="S140" s="4" t="inlineStr">
         <is>
-          <t>2026-08-15T20:47:08Z</t>
+          <t>2026-08-16T20:46:08Z</t>
         </is>
       </c>
     </row>
@@ -12126,7 +12126,7 @@
       </c>
       <c r="S141" s="4" t="inlineStr">
         <is>
-          <t>2026-08-15T20:47:08Z</t>
+          <t>2026-08-16T20:46:08Z</t>
         </is>
       </c>
     </row>
@@ -12258,7 +12258,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>2026-08-15T20:47:08Z</t>
+          <t>2026-08-16T20:46:08Z</t>
         </is>
       </c>
     </row>
@@ -12338,7 +12338,7 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>{"dataset_id": "bcv_pib_historico_anual", "title": "Producto interno bruto histórico anual", "table": "PIB histórico anual", "source_file": "7_1_14_anual.xls", "base": "1957/1968/1984/1997", "price_type": "Precios constantes", "measure": "Nivel", "frequency": "Anual", "period": "2017", "year": 2017, "quarter": null, "classification": "Total economía", "component": "Producto interno bruto", "value": 392393.12, "unit": "Millones de bolívares a precios constantes", "status": "", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/7_1_14_anual.xls", "fetched_at": "2026-08-15T20:47:08Z"}</t>
+          <t>{"dataset_id": "bcv_pib_historico_anual", "title": "Producto interno bruto histórico anual", "table": "PIB histórico anual", "source_file": "7_1_14_anual.xls", "base": "1957/1968/1984/1997", "price_type": "Precios constantes", "measure": "Nivel", "frequency": "Anual", "period": "2017", "year": 2017, "quarter": null, "classification": "Total economía", "component": "Producto interno bruto", "value": 392393.12, "unit": "Millones de bolívares a precios constantes", "status": "", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/7_1_14_anual.xls", "fetched_at": "2026-08-16T20:46:08Z"}</t>
         </is>
       </c>
     </row>

--- a/assets/data/bcv/excel/ove_bcv_pib_historico_anual.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_pib_historico_anual.xlsx
@@ -736,7 +736,7 @@
       </c>
       <c r="S7" s="4" t="inlineStr">
         <is>
-          <t>2026-08-16T20:46:08Z</t>
+          <t>2026-08-17T13:52:16Z</t>
         </is>
       </c>
     </row>
@@ -821,7 +821,7 @@
       </c>
       <c r="S8" s="4" t="inlineStr">
         <is>
-          <t>2026-08-16T20:46:08Z</t>
+          <t>2026-08-17T13:52:16Z</t>
         </is>
       </c>
     </row>
@@ -906,7 +906,7 @@
       </c>
       <c r="S9" s="4" t="inlineStr">
         <is>
-          <t>2026-08-16T20:46:08Z</t>
+          <t>2026-08-17T13:52:16Z</t>
         </is>
       </c>
     </row>
@@ -991,7 +991,7 @@
       </c>
       <c r="S10" s="4" t="inlineStr">
         <is>
-          <t>2026-08-16T20:46:08Z</t>
+          <t>2026-08-17T13:52:16Z</t>
         </is>
       </c>
     </row>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="S11" s="4" t="inlineStr">
         <is>
-          <t>2026-08-16T20:46:08Z</t>
+          <t>2026-08-17T13:52:16Z</t>
         </is>
       </c>
     </row>
@@ -1161,7 +1161,7 @@
       </c>
       <c r="S12" s="4" t="inlineStr">
         <is>
-          <t>2026-08-16T20:46:08Z</t>
+          <t>2026-08-17T13:52:16Z</t>
         </is>
       </c>
     </row>
@@ -1246,7 +1246,7 @@
       </c>
       <c r="S13" s="4" t="inlineStr">
         <is>
-          <t>2026-08-16T20:46:08Z</t>
+          <t>2026-08-17T13:52:16Z</t>
         </is>
       </c>
     </row>
@@ -1331,7 +1331,7 @@
       </c>
       <c r="S14" s="4" t="inlineStr">
         <is>
-          <t>2026-08-16T20:46:08Z</t>
+          <t>2026-08-17T13:52:16Z</t>
         </is>
       </c>
     </row>
@@ -1416,7 +1416,7 @@
       </c>
       <c r="S15" s="4" t="inlineStr">
         <is>
-          <t>2026-08-16T20:46:08Z</t>
+          <t>2026-08-17T13:52:16Z</t>
         </is>
       </c>
     </row>
@@ -1501,7 +1501,7 @@
       </c>
       <c r="S16" s="4" t="inlineStr">
         <is>
-          <t>2026-08-16T20:46:08Z</t>
+          <t>2026-08-17T13:52:16Z</t>
         </is>
       </c>
     </row>
@@ -1586,7 +1586,7 @@
       </c>
       <c r="S17" s="4" t="inlineStr">
         <is>
-          <t>2026-08-16T20:46:08Z</t>
+          <t>2026-08-17T13:52:16Z</t>
         </is>
       </c>
     </row>
@@ -1671,7 +1671,7 @@
       </c>
       <c r="S18" s="4" t="inlineStr">
         <is>
-          <t>2026-08-16T20:46:08Z</t>
+          <t>2026-08-17T13:52:16Z</t>
         </is>
       </c>
     </row>
@@ -1756,7 +1756,7 @@
       </c>
       <c r="S19" s="4" t="inlineStr">
         <is>
-          <t>2026-08-16T20:46:08Z</t>
+          <t>2026-08-17T13:52:16Z</t>
         </is>
       </c>
     </row>
@@ -1841,7 +1841,7 @@
       </c>
       <c r="S20" s="4" t="inlineStr">
         <is>
-          <t>2026-08-16T20:46:08Z</t>
+          <t>2026-08-17T13:52:16Z</t>
         </is>
       </c>
     </row>
@@ -1926,7 +1926,7 @@
       </c>
       <c r="S21" s="4" t="inlineStr">
         <is>
-          <t>2026-08-16T20:46:08Z</t>
+          <t>2026-08-17T13:52:16Z</t>
         </is>
       </c>
     </row>
@@ -2011,7 +2011,7 @@
       </c>
       <c r="S22" s="4" t="inlineStr">
         <is>
-          <t>2026-08-16T20:46:08Z</t>
+          <t>2026-08-17T13:52:16Z</t>
         </is>
       </c>
     </row>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="S23" s="4" t="inlineStr">
         <is>
-          <t>2026-08-16T20:46:08Z</t>
+          <t>2026-08-17T13:52:16Z</t>
         </is>
       </c>
     </row>
@@ -2181,7 +2181,7 @@
       </c>
       <c r="S24" s="4" t="inlineStr">
         <is>
-          <t>2026-08-16T20:46:08Z</t>
+          <t>2026-08-17T13:52:16Z</t>
         </is>
       </c>
     </row>
@@ -2266,7 +2266,7 @@
       </c>
       <c r="S25" s="4" t="inlineStr">
         <is>
-          <t>2026-08-16T20:46:08Z</t>
+          <t>2026-08-17T13:52:16Z</t>
         </is>
       </c>
     </row>
@@ -2351,7 +2351,7 @@
       </c>
       <c r="S26" s="4" t="inlineStr">
         <is>
-          <t>2026-08-16T20:46:08Z</t>
+          <t>2026-08-17T13:52:16Z</t>
         </is>
       </c>
     </row>
@@ -2436,7 +2436,7 @@
       </c>
       <c r="S27" s="4" t="inlineStr">
         <is>
-          <t>2026-08-16T20:46:08Z</t>
+          <t>2026-08-17T13:52:16Z</t>
         </is>
       </c>
     </row>
@@ -2521,7 +2521,7 @@
       </c>
       <c r="S28" s="4" t="inlineStr">
         <is>
-          <t>2026-08-16T20:46:08Z</t>
+          <t>2026-08-17T13:52:16Z</t>
         </is>
       </c>
     </row>
@@ -2606,7 +2606,7 @@
       </c>
       <c r="S29" s="4" t="inlineStr">
         <is>
-          <t>2026-08-16T20:46:08Z</t>
+          <t>2026-08-17T13:52:16Z</t>
         </is>
       </c>
     </row>
@@ -2691,7 +2691,7 @@
       </c>
       <c r="S30" s="4" t="inlineStr">
         <is>
-          <t>2026-08-16T20:46:08Z</t>
+          <t>2026-08-17T13:52:16Z</t>
         </is>
       </c>
     </row>
@@ -2776,7 +2776,7 @@
       </c>
       <c r="S31" s="4" t="inlineStr">
         <is>
-          <t>2026-08-16T20:46:08Z</t>
+          <t>2026-08-17T13:52:16Z</t>
         </is>
       </c>
     </row>
@@ -2861,7 +2861,7 @@
       </c>
       <c r="S32" s="4" t="inlineStr">
         <is>
-          <t>2026-08-16T20:46:08Z</t>
+          <t>2026-08-17T13:52:16Z</t>
         </is>
       </c>
     </row>
@@ -2946,7 +2946,7 @@
       </c>
       <c r="S33" s="4" t="inlineStr">
         <is>
-          <t>2026-08-16T20:46:08Z</t>
+          <t>2026-08-17T13:52:16Z</t>
         </is>
       </c>
     </row>
@@ -3031,7 +3031,7 @@
       </c>
       <c r="S34" s="4" t="inlineStr">
         <is>
-          <t>2026-08-16T20:46:08Z</t>
+          <t>2026-08-17T13:52:16Z</t>
         </is>
       </c>
     </row>
@@ -3116,7 +3116,7 @@
       </c>
       <c r="S35" s="4" t="inlineStr">
         <is>
-          <t>2026-08-16T20:46:08Z</t>
+          <t>2026-08-17T13:52:16Z</t>
         </is>
       </c>
     </row>
@@ -3201,7 +3201,7 @@
       </c>
       <c r="S36" s="4" t="inlineStr">
         <is>
-          <t>2026-08-16T20:46:08Z</t>
+          <t>2026-08-17T13:52:16Z</t>
         </is>
       </c>
     </row>
@@ -3286,7 +3286,7 @@
       </c>
       <c r="S37" s="4" t="inlineStr">
         <is>
-          <t>2026-08-16T20:46:08Z</t>
+          <t>2026-08-17T13:52:16Z</t>
         </is>
       </c>
     </row>
@@ -3371,7 +3371,7 @@
       </c>
       <c r="S38" s="4" t="inlineStr">
         <is>
-          <t>2026-08-16T20:46:08Z</t>
+          <t>2026-08-17T13:52:16Z</t>
         </is>
       </c>
     </row>
@@ -3456,7 +3456,7 @@
       </c>
       <c r="S39" s="4" t="inlineStr">
         <is>
-          <t>2026-08-16T20:46:08Z</t>
+          <t>2026-08-17T13:52:16Z</t>
         </is>
       </c>
     </row>
@@ -3541,7 +3541,7 @@
       </c>
       <c r="S40" s="4" t="inlineStr">
         <is>
-          <t>2026-08-16T20:46:08Z</t>
+          <t>2026-08-17T13:52:16Z</t>
         </is>
       </c>
     </row>
@@ -3626,7 +3626,7 @@
       </c>
       <c r="S41" s="4" t="inlineStr">
         <is>
-          <t>2026-08-16T20:46:08Z</t>
+          <t>2026-08-17T13:52:16Z</t>
         </is>
       </c>
     </row>
@@ -3711,7 +3711,7 @@
       </c>
       <c r="S42" s="4" t="inlineStr">
         <is>
-          <t>2026-08-16T20:46:08Z</t>
+          <t>2026-08-17T13:52:16Z</t>
         </is>
       </c>
     </row>
@@ -3796,7 +3796,7 @@
       </c>
       <c r="S43" s="4" t="inlineStr">
         <is>
-          <t>2026-08-16T20:46:08Z</t>
+          <t>2026-08-17T13:52:16Z</t>
         </is>
       </c>
     </row>
@@ -3881,7 +3881,7 @@
       </c>
       <c r="S44" s="4" t="inlineStr">
         <is>
-          <t>2026-08-16T20:46:08Z</t>
+          <t>2026-08-17T13:52:16Z</t>
         </is>
       </c>
     </row>
@@ -3966,7 +3966,7 @@
       </c>
       <c r="S45" s="4" t="inlineStr">
         <is>
-          <t>2026-08-16T20:46:08Z</t>
+          <t>2026-08-17T13:52:16Z</t>
         </is>
       </c>
     </row>
@@ -4051,7 +4051,7 @@
       </c>
       <c r="S46" s="4" t="inlineStr">
         <is>
-          <t>2026-08-16T20:46:08Z</t>
+          <t>2026-08-17T13:52:16Z</t>
         </is>
       </c>
     </row>
@@ -4136,7 +4136,7 @@
       </c>
       <c r="S47" s="4" t="inlineStr">
         <is>
-          <t>2026-08-16T20:46:08Z</t>
+          <t>2026-08-17T13:52:16Z</t>
         </is>
       </c>
     </row>
@@ -4221,7 +4221,7 @@
       </c>
       <c r="S48" s="4" t="inlineStr">
         <is>
-          <t>2026-08-16T20:46:08Z</t>
+          <t>2026-08-17T13:52:16Z</t>
         </is>
       </c>
     </row>
@@ -4306,7 +4306,7 @@
       </c>
       <c r="S49" s="4" t="inlineStr">
         <is>
-          <t>2026-08-16T20:46:08Z</t>
+          <t>2026-08-17T13:52:16Z</t>
         </is>
       </c>
     </row>
@@ -4391,7 +4391,7 @@
       </c>
       <c r="S50" s="4" t="inlineStr">
         <is>
-          <t>2026-08-16T20:46:08Z</t>
+          <t>2026-08-17T13:52:16Z</t>
         </is>
       </c>
     </row>
@@ -4476,7 +4476,7 @@
       </c>
       <c r="S51" s="4" t="inlineStr">
         <is>
-          <t>2026-08-16T20:46:08Z</t>
+          <t>2026-08-17T13:52:16Z</t>
         </is>
       </c>
     </row>
@@ -4561,7 +4561,7 @@
       </c>
       <c r="S52" s="4" t="inlineStr">
         <is>
-          <t>2026-08-16T20:46:08Z</t>
+          <t>2026-08-17T13:52:16Z</t>
         </is>
       </c>
     </row>
@@ -4646,7 +4646,7 @@
       </c>
       <c r="S53" s="4" t="inlineStr">
         <is>
-          <t>2026-08-16T20:46:08Z</t>
+          <t>2026-08-17T13:52:16Z</t>
         </is>
       </c>
     </row>
@@ -4731,7 +4731,7 @@
       </c>
       <c r="S54" s="4" t="inlineStr">
         <is>
-          <t>2026-08-16T20:46:08Z</t>
+          <t>2026-08-17T13:52:16Z</t>
         </is>
       </c>
     </row>
@@ -4816,7 +4816,7 @@
       </c>
       <c r="S55" s="4" t="inlineStr">
         <is>
-          <t>2026-08-16T20:46:08Z</t>
+          <t>2026-08-17T13:52:16Z</t>
         </is>
       </c>
     </row>
@@ -4901,7 +4901,7 @@
       </c>
       <c r="S56" s="4" t="inlineStr">
         <is>
-          <t>2026-08-16T20:46:08Z</t>
+          <t>2026-08-17T13:52:16Z</t>
         </is>
       </c>
     </row>
@@ -4986,7 +4986,7 @@
       </c>
       <c r="S57" s="4" t="inlineStr">
         <is>
-          <t>2026-08-16T20:46:08Z</t>
+          <t>2026-08-17T13:52:16Z</t>
         </is>
       </c>
     </row>
@@ -5071,7 +5071,7 @@
       </c>
       <c r="S58" s="4" t="inlineStr">
         <is>
-          <t>2026-08-16T20:46:08Z</t>
+          <t>2026-08-17T13:52:16Z</t>
         </is>
       </c>
     </row>
@@ -5156,7 +5156,7 @@
       </c>
       <c r="S59" s="4" t="inlineStr">
         <is>
-          <t>2026-08-16T20:46:08Z</t>
+          <t>2026-08-17T13:52:16Z</t>
         </is>
       </c>
     </row>
@@ -5241,7 +5241,7 @@
       </c>
       <c r="S60" s="4" t="inlineStr">
         <is>
-          <t>2026-08-16T20:46:08Z</t>
+          <t>2026-08-17T13:52:16Z</t>
         </is>
       </c>
     </row>
@@ -5326,7 +5326,7 @@
       </c>
       <c r="S61" s="4" t="inlineStr">
         <is>
-          <t>2026-08-16T20:46:08Z</t>
+          <t>2026-08-17T13:52:16Z</t>
         </is>
       </c>
     </row>
@@ -5411,7 +5411,7 @@
       </c>
       <c r="S62" s="4" t="inlineStr">
         <is>
-          <t>2026-08-16T20:46:08Z</t>
+          <t>2026-08-17T13:52:16Z</t>
         </is>
       </c>
     </row>
@@ -5496,7 +5496,7 @@
       </c>
       <c r="S63" s="4" t="inlineStr">
         <is>
-          <t>2026-08-16T20:46:08Z</t>
+          <t>2026-08-17T13:52:16Z</t>
         </is>
       </c>
     </row>
@@ -5581,7 +5581,7 @@
       </c>
       <c r="S64" s="4" t="inlineStr">
         <is>
-          <t>2026-08-16T20:46:08Z</t>
+          <t>2026-08-17T13:52:16Z</t>
         </is>
       </c>
     </row>
@@ -5666,7 +5666,7 @@
       </c>
       <c r="S65" s="4" t="inlineStr">
         <is>
-          <t>2026-08-16T20:46:08Z</t>
+          <t>2026-08-17T13:52:16Z</t>
         </is>
       </c>
     </row>
@@ -5751,7 +5751,7 @@
       </c>
       <c r="S66" s="4" t="inlineStr">
         <is>
-          <t>2026-08-16T20:46:08Z</t>
+          <t>2026-08-17T13:52:16Z</t>
         </is>
       </c>
     </row>
@@ -5836,7 +5836,7 @@
       </c>
       <c r="S67" s="4" t="inlineStr">
         <is>
-          <t>2026-08-16T20:46:08Z</t>
+          <t>2026-08-17T13:52:16Z</t>
         </is>
       </c>
     </row>
@@ -5921,7 +5921,7 @@
       </c>
       <c r="S68" s="4" t="inlineStr">
         <is>
-          <t>2026-08-16T20:46:08Z</t>
+          <t>2026-08-17T13:52:16Z</t>
         </is>
       </c>
     </row>
@@ -6006,7 +6006,7 @@
       </c>
       <c r="S69" s="4" t="inlineStr">
         <is>
-          <t>2026-08-16T20:46:08Z</t>
+          <t>2026-08-17T13:52:16Z</t>
         </is>
       </c>
     </row>
@@ -6091,7 +6091,7 @@
       </c>
       <c r="S70" s="4" t="inlineStr">
         <is>
-          <t>2026-08-16T20:46:08Z</t>
+          <t>2026-08-17T13:52:16Z</t>
         </is>
       </c>
     </row>
@@ -6176,7 +6176,7 @@
       </c>
       <c r="S71" s="4" t="inlineStr">
         <is>
-          <t>2026-08-16T20:46:08Z</t>
+          <t>2026-08-17T13:52:16Z</t>
         </is>
       </c>
     </row>
@@ -6261,7 +6261,7 @@
       </c>
       <c r="S72" s="4" t="inlineStr">
         <is>
-          <t>2026-08-16T20:46:08Z</t>
+          <t>2026-08-17T13:52:16Z</t>
         </is>
       </c>
     </row>
@@ -6346,7 +6346,7 @@
       </c>
       <c r="S73" s="4" t="inlineStr">
         <is>
-          <t>2026-08-16T20:46:08Z</t>
+          <t>2026-08-17T13:52:16Z</t>
         </is>
       </c>
     </row>
@@ -6431,7 +6431,7 @@
       </c>
       <c r="S74" s="4" t="inlineStr">
         <is>
-          <t>2026-08-16T20:46:08Z</t>
+          <t>2026-08-17T13:52:16Z</t>
         </is>
       </c>
     </row>
@@ -6516,7 +6516,7 @@
       </c>
       <c r="S75" s="4" t="inlineStr">
         <is>
-          <t>2026-08-16T20:46:08Z</t>
+          <t>2026-08-17T13:52:16Z</t>
         </is>
       </c>
     </row>
@@ -6601,7 +6601,7 @@
       </c>
       <c r="S76" s="4" t="inlineStr">
         <is>
-          <t>2026-08-16T20:46:08Z</t>
+          <t>2026-08-17T13:52:16Z</t>
         </is>
       </c>
     </row>
@@ -6686,7 +6686,7 @@
       </c>
       <c r="S77" s="4" t="inlineStr">
         <is>
-          <t>2026-08-16T20:46:08Z</t>
+          <t>2026-08-17T13:52:16Z</t>
         </is>
       </c>
     </row>
@@ -6771,7 +6771,7 @@
       </c>
       <c r="S78" s="4" t="inlineStr">
         <is>
-          <t>2026-08-16T20:46:08Z</t>
+          <t>2026-08-17T13:52:16Z</t>
         </is>
       </c>
     </row>
@@ -6856,7 +6856,7 @@
       </c>
       <c r="S79" s="4" t="inlineStr">
         <is>
-          <t>2026-08-16T20:46:08Z</t>
+          <t>2026-08-17T13:52:16Z</t>
         </is>
       </c>
     </row>
@@ -6941,7 +6941,7 @@
       </c>
       <c r="S80" s="4" t="inlineStr">
         <is>
-          <t>2026-08-16T20:46:08Z</t>
+          <t>2026-08-17T13:52:16Z</t>
         </is>
       </c>
     </row>
@@ -7026,7 +7026,7 @@
       </c>
       <c r="S81" s="4" t="inlineStr">
         <is>
-          <t>2026-08-16T20:46:08Z</t>
+          <t>2026-08-17T13:52:16Z</t>
         </is>
       </c>
     </row>
@@ -7111,7 +7111,7 @@
       </c>
       <c r="S82" s="4" t="inlineStr">
         <is>
-          <t>2026-08-16T20:46:08Z</t>
+          <t>2026-08-17T13:52:16Z</t>
         </is>
       </c>
     </row>
@@ -7196,7 +7196,7 @@
       </c>
       <c r="S83" s="4" t="inlineStr">
         <is>
-          <t>2026-08-16T20:46:08Z</t>
+          <t>2026-08-17T13:52:16Z</t>
         </is>
       </c>
     </row>
@@ -7281,7 +7281,7 @@
       </c>
       <c r="S84" s="4" t="inlineStr">
         <is>
-          <t>2026-08-16T20:46:08Z</t>
+          <t>2026-08-17T13:52:16Z</t>
         </is>
       </c>
     </row>
@@ -7366,7 +7366,7 @@
       </c>
       <c r="S85" s="4" t="inlineStr">
         <is>
-          <t>2026-08-16T20:46:08Z</t>
+          <t>2026-08-17T13:52:16Z</t>
         </is>
       </c>
     </row>
@@ -7451,7 +7451,7 @@
       </c>
       <c r="S86" s="4" t="inlineStr">
         <is>
-          <t>2026-08-16T20:46:08Z</t>
+          <t>2026-08-17T13:52:16Z</t>
         </is>
       </c>
     </row>
@@ -7536,7 +7536,7 @@
       </c>
       <c r="S87" s="4" t="inlineStr">
         <is>
-          <t>2026-08-16T20:46:08Z</t>
+          <t>2026-08-17T13:52:16Z</t>
         </is>
       </c>
     </row>
@@ -7621,7 +7621,7 @@
       </c>
       <c r="S88" s="4" t="inlineStr">
         <is>
-          <t>2026-08-16T20:46:08Z</t>
+          <t>2026-08-17T13:52:16Z</t>
         </is>
       </c>
     </row>
@@ -7706,7 +7706,7 @@
       </c>
       <c r="S89" s="4" t="inlineStr">
         <is>
-          <t>2026-08-16T20:46:08Z</t>
+          <t>2026-08-17T13:52:16Z</t>
         </is>
       </c>
     </row>
@@ -7791,7 +7791,7 @@
       </c>
       <c r="S90" s="4" t="inlineStr">
         <is>
-          <t>2026-08-16T20:46:08Z</t>
+          <t>2026-08-17T13:52:16Z</t>
         </is>
       </c>
     </row>
@@ -7876,7 +7876,7 @@
       </c>
       <c r="S91" s="4" t="inlineStr">
         <is>
-          <t>2026-08-16T20:46:08Z</t>
+          <t>2026-08-17T13:52:16Z</t>
         </is>
       </c>
     </row>
@@ -7961,7 +7961,7 @@
       </c>
       <c r="S92" s="4" t="inlineStr">
         <is>
-          <t>2026-08-16T20:46:08Z</t>
+          <t>2026-08-17T13:52:16Z</t>
         </is>
       </c>
     </row>
@@ -8046,7 +8046,7 @@
       </c>
       <c r="S93" s="4" t="inlineStr">
         <is>
-          <t>2026-08-16T20:46:08Z</t>
+          <t>2026-08-17T13:52:16Z</t>
         </is>
       </c>
     </row>
@@ -8131,7 +8131,7 @@
       </c>
       <c r="S94" s="4" t="inlineStr">
         <is>
-          <t>2026-08-16T20:46:08Z</t>
+          <t>2026-08-17T13:52:16Z</t>
         </is>
       </c>
     </row>
@@ -8216,7 +8216,7 @@
       </c>
       <c r="S95" s="4" t="inlineStr">
         <is>
-          <t>2026-08-16T20:46:08Z</t>
+          <t>2026-08-17T13:52:16Z</t>
         </is>
       </c>
     </row>
@@ -8301,7 +8301,7 @@
       </c>
       <c r="S96" s="4" t="inlineStr">
         <is>
-          <t>2026-08-16T20:46:08Z</t>
+          <t>2026-08-17T13:52:16Z</t>
         </is>
       </c>
     </row>
@@ -8386,7 +8386,7 @@
       </c>
       <c r="S97" s="4" t="inlineStr">
         <is>
-          <t>2026-08-16T20:46:08Z</t>
+          <t>2026-08-17T13:52:16Z</t>
         </is>
       </c>
     </row>
@@ -8471,7 +8471,7 @@
       </c>
       <c r="S98" s="4" t="inlineStr">
         <is>
-          <t>2026-08-16T20:46:08Z</t>
+          <t>2026-08-17T13:52:16Z</t>
         </is>
       </c>
     </row>
@@ -8556,7 +8556,7 @@
       </c>
       <c r="S99" s="4" t="inlineStr">
         <is>
-          <t>2026-08-16T20:46:08Z</t>
+          <t>2026-08-17T13:52:16Z</t>
         </is>
       </c>
     </row>
@@ -8641,7 +8641,7 @@
       </c>
       <c r="S100" s="4" t="inlineStr">
         <is>
-          <t>2026-08-16T20:46:08Z</t>
+          <t>2026-08-17T13:52:16Z</t>
         </is>
       </c>
     </row>
@@ -8726,7 +8726,7 @@
       </c>
       <c r="S101" s="4" t="inlineStr">
         <is>
-          <t>2026-08-16T20:46:08Z</t>
+          <t>2026-08-17T13:52:16Z</t>
         </is>
       </c>
     </row>
@@ -8811,7 +8811,7 @@
       </c>
       <c r="S102" s="4" t="inlineStr">
         <is>
-          <t>2026-08-16T20:46:08Z</t>
+          <t>2026-08-17T13:52:16Z</t>
         </is>
       </c>
     </row>
@@ -8896,7 +8896,7 @@
       </c>
       <c r="S103" s="4" t="inlineStr">
         <is>
-          <t>2026-08-16T20:46:08Z</t>
+          <t>2026-08-17T13:52:16Z</t>
         </is>
       </c>
     </row>
@@ -8981,7 +8981,7 @@
       </c>
       <c r="S104" s="4" t="inlineStr">
         <is>
-          <t>2026-08-16T20:46:08Z</t>
+          <t>2026-08-17T13:52:16Z</t>
         </is>
       </c>
     </row>
@@ -9066,7 +9066,7 @@
       </c>
       <c r="S105" s="4" t="inlineStr">
         <is>
-          <t>2026-08-16T20:46:08Z</t>
+          <t>2026-08-17T13:52:16Z</t>
         </is>
       </c>
     </row>
@@ -9151,7 +9151,7 @@
       </c>
       <c r="S106" s="4" t="inlineStr">
         <is>
-          <t>2026-08-16T20:46:08Z</t>
+          <t>2026-08-17T13:52:16Z</t>
         </is>
       </c>
     </row>
@@ -9236,7 +9236,7 @@
       </c>
       <c r="S107" s="4" t="inlineStr">
         <is>
-          <t>2026-08-16T20:46:08Z</t>
+          <t>2026-08-17T13:52:16Z</t>
         </is>
       </c>
     </row>
@@ -9321,7 +9321,7 @@
       </c>
       <c r="S108" s="4" t="inlineStr">
         <is>
-          <t>2026-08-16T20:46:08Z</t>
+          <t>2026-08-17T13:52:16Z</t>
         </is>
       </c>
     </row>
@@ -9406,7 +9406,7 @@
       </c>
       <c r="S109" s="4" t="inlineStr">
         <is>
-          <t>2026-08-16T20:46:08Z</t>
+          <t>2026-08-17T13:52:16Z</t>
         </is>
       </c>
     </row>
@@ -9491,7 +9491,7 @@
       </c>
       <c r="S110" s="4" t="inlineStr">
         <is>
-          <t>2026-08-16T20:46:08Z</t>
+          <t>2026-08-17T13:52:16Z</t>
         </is>
       </c>
     </row>
@@ -9576,7 +9576,7 @@
       </c>
       <c r="S111" s="4" t="inlineStr">
         <is>
-          <t>2026-08-16T20:46:08Z</t>
+          <t>2026-08-17T13:52:16Z</t>
         </is>
       </c>
     </row>
@@ -9661,7 +9661,7 @@
       </c>
       <c r="S112" s="4" t="inlineStr">
         <is>
-          <t>2026-08-16T20:46:08Z</t>
+          <t>2026-08-17T13:52:16Z</t>
         </is>
       </c>
     </row>
@@ -9746,7 +9746,7 @@
       </c>
       <c r="S113" s="4" t="inlineStr">
         <is>
-          <t>2026-08-16T20:46:08Z</t>
+          <t>2026-08-17T13:52:16Z</t>
         </is>
       </c>
     </row>
@@ -9831,7 +9831,7 @@
       </c>
       <c r="S114" s="4" t="inlineStr">
         <is>
-          <t>2026-08-16T20:46:08Z</t>
+          <t>2026-08-17T13:52:16Z</t>
         </is>
       </c>
     </row>
@@ -9916,7 +9916,7 @@
       </c>
       <c r="S115" s="4" t="inlineStr">
         <is>
-          <t>2026-08-16T20:46:08Z</t>
+          <t>2026-08-17T13:52:16Z</t>
         </is>
       </c>
     </row>
@@ -10001,7 +10001,7 @@
       </c>
       <c r="S116" s="4" t="inlineStr">
         <is>
-          <t>2026-08-16T20:46:08Z</t>
+          <t>2026-08-17T13:52:16Z</t>
         </is>
       </c>
     </row>
@@ -10086,7 +10086,7 @@
       </c>
       <c r="S117" s="4" t="inlineStr">
         <is>
-          <t>2026-08-16T20:46:08Z</t>
+          <t>2026-08-17T13:52:16Z</t>
         </is>
       </c>
     </row>
@@ -10171,7 +10171,7 @@
       </c>
       <c r="S118" s="4" t="inlineStr">
         <is>
-          <t>2026-08-16T20:46:08Z</t>
+          <t>2026-08-17T13:52:16Z</t>
         </is>
       </c>
     </row>
@@ -10256,7 +10256,7 @@
       </c>
       <c r="S119" s="4" t="inlineStr">
         <is>
-          <t>2026-08-16T20:46:08Z</t>
+          <t>2026-08-17T13:52:16Z</t>
         </is>
       </c>
     </row>
@@ -10341,7 +10341,7 @@
       </c>
       <c r="S120" s="4" t="inlineStr">
         <is>
-          <t>2026-08-16T20:46:08Z</t>
+          <t>2026-08-17T13:52:16Z</t>
         </is>
       </c>
     </row>
@@ -10426,7 +10426,7 @@
       </c>
       <c r="S121" s="4" t="inlineStr">
         <is>
-          <t>2026-08-16T20:46:08Z</t>
+          <t>2026-08-17T13:52:16Z</t>
         </is>
       </c>
     </row>
@@ -10511,7 +10511,7 @@
       </c>
       <c r="S122" s="4" t="inlineStr">
         <is>
-          <t>2026-08-16T20:46:08Z</t>
+          <t>2026-08-17T13:52:16Z</t>
         </is>
       </c>
     </row>
@@ -10596,7 +10596,7 @@
       </c>
       <c r="S123" s="4" t="inlineStr">
         <is>
-          <t>2026-08-16T20:46:08Z</t>
+          <t>2026-08-17T13:52:16Z</t>
         </is>
       </c>
     </row>
@@ -10681,7 +10681,7 @@
       </c>
       <c r="S124" s="4" t="inlineStr">
         <is>
-          <t>2026-08-16T20:46:08Z</t>
+          <t>2026-08-17T13:52:16Z</t>
         </is>
       </c>
     </row>
@@ -10766,7 +10766,7 @@
       </c>
       <c r="S125" s="4" t="inlineStr">
         <is>
-          <t>2026-08-16T20:46:08Z</t>
+          <t>2026-08-17T13:52:16Z</t>
         </is>
       </c>
     </row>
@@ -10851,7 +10851,7 @@
       </c>
       <c r="S126" s="4" t="inlineStr">
         <is>
-          <t>2026-08-16T20:46:08Z</t>
+          <t>2026-08-17T13:52:16Z</t>
         </is>
       </c>
     </row>
@@ -10936,7 +10936,7 @@
       </c>
       <c r="S127" s="4" t="inlineStr">
         <is>
-          <t>2026-08-16T20:46:08Z</t>
+          <t>2026-08-17T13:52:16Z</t>
         </is>
       </c>
     </row>
@@ -11021,7 +11021,7 @@
       </c>
       <c r="S128" s="4" t="inlineStr">
         <is>
-          <t>2026-08-16T20:46:08Z</t>
+          <t>2026-08-17T13:52:16Z</t>
         </is>
       </c>
     </row>
@@ -11106,7 +11106,7 @@
       </c>
       <c r="S129" s="4" t="inlineStr">
         <is>
-          <t>2026-08-16T20:46:08Z</t>
+          <t>2026-08-17T13:52:16Z</t>
         </is>
       </c>
     </row>
@@ -11191,7 +11191,7 @@
       </c>
       <c r="S130" s="4" t="inlineStr">
         <is>
-          <t>2026-08-16T20:46:08Z</t>
+          <t>2026-08-17T13:52:16Z</t>
         </is>
       </c>
     </row>
@@ -11276,7 +11276,7 @@
       </c>
       <c r="S131" s="4" t="inlineStr">
         <is>
-          <t>2026-08-16T20:46:08Z</t>
+          <t>2026-08-17T13:52:16Z</t>
         </is>
       </c>
     </row>
@@ -11361,7 +11361,7 @@
       </c>
       <c r="S132" s="4" t="inlineStr">
         <is>
-          <t>2026-08-16T20:46:08Z</t>
+          <t>2026-08-17T13:52:16Z</t>
         </is>
       </c>
     </row>
@@ -11446,7 +11446,7 @@
       </c>
       <c r="S133" s="4" t="inlineStr">
         <is>
-          <t>2026-08-16T20:46:08Z</t>
+          <t>2026-08-17T13:52:16Z</t>
         </is>
       </c>
     </row>
@@ -11531,7 +11531,7 @@
       </c>
       <c r="S134" s="4" t="inlineStr">
         <is>
-          <t>2026-08-16T20:46:08Z</t>
+          <t>2026-08-17T13:52:16Z</t>
         </is>
       </c>
     </row>
@@ -11616,7 +11616,7 @@
       </c>
       <c r="S135" s="4" t="inlineStr">
         <is>
-          <t>2026-08-16T20:46:08Z</t>
+          <t>2026-08-17T13:52:16Z</t>
         </is>
       </c>
     </row>
@@ -11701,7 +11701,7 @@
       </c>
       <c r="S136" s="4" t="inlineStr">
         <is>
-          <t>2026-08-16T20:46:08Z</t>
+          <t>2026-08-17T13:52:16Z</t>
         </is>
       </c>
     </row>
@@ -11786,7 +11786,7 @@
       </c>
       <c r="S137" s="4" t="inlineStr">
         <is>
-          <t>2026-08-16T20:46:08Z</t>
+          <t>2026-08-17T13:52:16Z</t>
         </is>
       </c>
     </row>
@@ -11871,7 +11871,7 @@
       </c>
       <c r="S138" s="4" t="inlineStr">
         <is>
-          <t>2026-08-16T20:46:08Z</t>
+          <t>2026-08-17T13:52:16Z</t>
         </is>
       </c>
     </row>
@@ -11956,7 +11956,7 @@
       </c>
       <c r="S139" s="4" t="inlineStr">
         <is>
-          <t>2026-08-16T20:46:08Z</t>
+          <t>2026-08-17T13:52:16Z</t>
         </is>
       </c>
     </row>
@@ -12041,7 +12041,7 @@
       </c>
       <c r="S140" s="4" t="inlineStr">
         <is>
-          <t>2026-08-16T20:46:08Z</t>
+          <t>2026-08-17T13:52:16Z</t>
         </is>
       </c>
     </row>
@@ -12126,7 +12126,7 @@
       </c>
       <c r="S141" s="4" t="inlineStr">
         <is>
-          <t>2026-08-16T20:46:08Z</t>
+          <t>2026-08-17T13:52:16Z</t>
         </is>
       </c>
     </row>
@@ -12258,7 +12258,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>2026-08-16T20:46:08Z</t>
+          <t>2026-08-17T13:52:16Z</t>
         </is>
       </c>
     </row>
@@ -12338,7 +12338,7 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>{"dataset_id": "bcv_pib_historico_anual", "title": "Producto interno bruto histórico anual", "table": "PIB histórico anual", "source_file": "7_1_14_anual.xls", "base": "1957/1968/1984/1997", "price_type": "Precios constantes", "measure": "Nivel", "frequency": "Anual", "period": "2017", "year": 2017, "quarter": null, "classification": "Total economía", "component": "Producto interno bruto", "value": 392393.12, "unit": "Millones de bolívares a precios constantes", "status": "", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/7_1_14_anual.xls", "fetched_at": "2026-08-16T20:46:08Z"}</t>
+          <t>{"dataset_id": "bcv_pib_historico_anual", "title": "Producto interno bruto histórico anual", "table": "PIB histórico anual", "source_file": "7_1_14_anual.xls", "base": "1957/1968/1984/1997", "price_type": "Precios constantes", "measure": "Nivel", "frequency": "Anual", "period": "2017", "year": 2017, "quarter": null, "classification": "Total economía", "component": "Producto interno bruto", "value": 392393.12, "unit": "Millones de bolívares a precios constantes", "status": "", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/7_1_14_anual.xls", "fetched_at": "2026-08-17T13:52:16Z"}</t>
         </is>
       </c>
     </row>

--- a/assets/data/bcv/excel/ove_bcv_pib_historico_anual.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_pib_historico_anual.xlsx
@@ -736,7 +736,7 @@
       </c>
       <c r="S7" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T13:52:16Z</t>
+          <t>2026-08-17T20:52:47Z</t>
         </is>
       </c>
     </row>
@@ -821,7 +821,7 @@
       </c>
       <c r="S8" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T13:52:16Z</t>
+          <t>2026-08-17T20:52:47Z</t>
         </is>
       </c>
     </row>
@@ -906,7 +906,7 @@
       </c>
       <c r="S9" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T13:52:16Z</t>
+          <t>2026-08-17T20:52:47Z</t>
         </is>
       </c>
     </row>
@@ -991,7 +991,7 @@
       </c>
       <c r="S10" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T13:52:16Z</t>
+          <t>2026-08-17T20:52:47Z</t>
         </is>
       </c>
     </row>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="S11" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T13:52:16Z</t>
+          <t>2026-08-17T20:52:47Z</t>
         </is>
       </c>
     </row>
@@ -1161,7 +1161,7 @@
       </c>
       <c r="S12" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T13:52:16Z</t>
+          <t>2026-08-17T20:52:47Z</t>
         </is>
       </c>
     </row>
@@ -1246,7 +1246,7 @@
       </c>
       <c r="S13" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T13:52:16Z</t>
+          <t>2026-08-17T20:52:47Z</t>
         </is>
       </c>
     </row>
@@ -1331,7 +1331,7 @@
       </c>
       <c r="S14" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T13:52:16Z</t>
+          <t>2026-08-17T20:52:47Z</t>
         </is>
       </c>
     </row>
@@ -1416,7 +1416,7 @@
       </c>
       <c r="S15" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T13:52:16Z</t>
+          <t>2026-08-17T20:52:47Z</t>
         </is>
       </c>
     </row>
@@ -1501,7 +1501,7 @@
       </c>
       <c r="S16" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T13:52:16Z</t>
+          <t>2026-08-17T20:52:47Z</t>
         </is>
       </c>
     </row>
@@ -1586,7 +1586,7 @@
       </c>
       <c r="S17" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T13:52:16Z</t>
+          <t>2026-08-17T20:52:47Z</t>
         </is>
       </c>
     </row>
@@ -1671,7 +1671,7 @@
       </c>
       <c r="S18" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T13:52:16Z</t>
+          <t>2026-08-17T20:52:47Z</t>
         </is>
       </c>
     </row>
@@ -1756,7 +1756,7 @@
       </c>
       <c r="S19" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T13:52:16Z</t>
+          <t>2026-08-17T20:52:47Z</t>
         </is>
       </c>
     </row>
@@ -1841,7 +1841,7 @@
       </c>
       <c r="S20" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T13:52:16Z</t>
+          <t>2026-08-17T20:52:47Z</t>
         </is>
       </c>
     </row>
@@ -1926,7 +1926,7 @@
       </c>
       <c r="S21" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T13:52:16Z</t>
+          <t>2026-08-17T20:52:47Z</t>
         </is>
       </c>
     </row>
@@ -2011,7 +2011,7 @@
       </c>
       <c r="S22" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T13:52:16Z</t>
+          <t>2026-08-17T20:52:47Z</t>
         </is>
       </c>
     </row>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="S23" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T13:52:16Z</t>
+          <t>2026-08-17T20:52:47Z</t>
         </is>
       </c>
     </row>
@@ -2181,7 +2181,7 @@
       </c>
       <c r="S24" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T13:52:16Z</t>
+          <t>2026-08-17T20:52:47Z</t>
         </is>
       </c>
     </row>
@@ -2266,7 +2266,7 @@
       </c>
       <c r="S25" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T13:52:16Z</t>
+          <t>2026-08-17T20:52:47Z</t>
         </is>
       </c>
     </row>
@@ -2351,7 +2351,7 @@
       </c>
       <c r="S26" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T13:52:16Z</t>
+          <t>2026-08-17T20:52:47Z</t>
         </is>
       </c>
     </row>
@@ -2436,7 +2436,7 @@
       </c>
       <c r="S27" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T13:52:16Z</t>
+          <t>2026-08-17T20:52:47Z</t>
         </is>
       </c>
     </row>
@@ -2521,7 +2521,7 @@
       </c>
       <c r="S28" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T13:52:16Z</t>
+          <t>2026-08-17T20:52:47Z</t>
         </is>
       </c>
     </row>
@@ -2606,7 +2606,7 @@
       </c>
       <c r="S29" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T13:52:16Z</t>
+          <t>2026-08-17T20:52:47Z</t>
         </is>
       </c>
     </row>
@@ -2691,7 +2691,7 @@
       </c>
       <c r="S30" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T13:52:16Z</t>
+          <t>2026-08-17T20:52:47Z</t>
         </is>
       </c>
     </row>
@@ -2776,7 +2776,7 @@
       </c>
       <c r="S31" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T13:52:16Z</t>
+          <t>2026-08-17T20:52:47Z</t>
         </is>
       </c>
     </row>
@@ -2861,7 +2861,7 @@
       </c>
       <c r="S32" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T13:52:16Z</t>
+          <t>2026-08-17T20:52:47Z</t>
         </is>
       </c>
     </row>
@@ -2946,7 +2946,7 @@
       </c>
       <c r="S33" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T13:52:16Z</t>
+          <t>2026-08-17T20:52:47Z</t>
         </is>
       </c>
     </row>
@@ -3031,7 +3031,7 @@
       </c>
       <c r="S34" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T13:52:16Z</t>
+          <t>2026-08-17T20:52:47Z</t>
         </is>
       </c>
     </row>
@@ -3116,7 +3116,7 @@
       </c>
       <c r="S35" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T13:52:16Z</t>
+          <t>2026-08-17T20:52:47Z</t>
         </is>
       </c>
     </row>
@@ -3201,7 +3201,7 @@
       </c>
       <c r="S36" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T13:52:16Z</t>
+          <t>2026-08-17T20:52:47Z</t>
         </is>
       </c>
     </row>
@@ -3286,7 +3286,7 @@
       </c>
       <c r="S37" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T13:52:16Z</t>
+          <t>2026-08-17T20:52:47Z</t>
         </is>
       </c>
     </row>
@@ -3371,7 +3371,7 @@
       </c>
       <c r="S38" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T13:52:16Z</t>
+          <t>2026-08-17T20:52:47Z</t>
         </is>
       </c>
     </row>
@@ -3456,7 +3456,7 @@
       </c>
       <c r="S39" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T13:52:16Z</t>
+          <t>2026-08-17T20:52:47Z</t>
         </is>
       </c>
     </row>
@@ -3541,7 +3541,7 @@
       </c>
       <c r="S40" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T13:52:16Z</t>
+          <t>2026-08-17T20:52:47Z</t>
         </is>
       </c>
     </row>
@@ -3626,7 +3626,7 @@
       </c>
       <c r="S41" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T13:52:16Z</t>
+          <t>2026-08-17T20:52:47Z</t>
         </is>
       </c>
     </row>
@@ -3711,7 +3711,7 @@
       </c>
       <c r="S42" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T13:52:16Z</t>
+          <t>2026-08-17T20:52:47Z</t>
         </is>
       </c>
     </row>
@@ -3796,7 +3796,7 @@
       </c>
       <c r="S43" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T13:52:16Z</t>
+          <t>2026-08-17T20:52:47Z</t>
         </is>
       </c>
     </row>
@@ -3881,7 +3881,7 @@
       </c>
       <c r="S44" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T13:52:16Z</t>
+          <t>2026-08-17T20:52:47Z</t>
         </is>
       </c>
     </row>
@@ -3966,7 +3966,7 @@
       </c>
       <c r="S45" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T13:52:16Z</t>
+          <t>2026-08-17T20:52:47Z</t>
         </is>
       </c>
     </row>
@@ -4051,7 +4051,7 @@
       </c>
       <c r="S46" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T13:52:16Z</t>
+          <t>2026-08-17T20:52:47Z</t>
         </is>
       </c>
     </row>
@@ -4136,7 +4136,7 @@
       </c>
       <c r="S47" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T13:52:16Z</t>
+          <t>2026-08-17T20:52:47Z</t>
         </is>
       </c>
     </row>
@@ -4221,7 +4221,7 @@
       </c>
       <c r="S48" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T13:52:16Z</t>
+          <t>2026-08-17T20:52:47Z</t>
         </is>
       </c>
     </row>
@@ -4306,7 +4306,7 @@
       </c>
       <c r="S49" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T13:52:16Z</t>
+          <t>2026-08-17T20:52:47Z</t>
         </is>
       </c>
     </row>
@@ -4391,7 +4391,7 @@
       </c>
       <c r="S50" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T13:52:16Z</t>
+          <t>2026-08-17T20:52:47Z</t>
         </is>
       </c>
     </row>
@@ -4476,7 +4476,7 @@
       </c>
       <c r="S51" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T13:52:16Z</t>
+          <t>2026-08-17T20:52:47Z</t>
         </is>
       </c>
     </row>
@@ -4561,7 +4561,7 @@
       </c>
       <c r="S52" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T13:52:16Z</t>
+          <t>2026-08-17T20:52:47Z</t>
         </is>
       </c>
     </row>
@@ -4646,7 +4646,7 @@
       </c>
       <c r="S53" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T13:52:16Z</t>
+          <t>2026-08-17T20:52:47Z</t>
         </is>
       </c>
     </row>
@@ -4731,7 +4731,7 @@
       </c>
       <c r="S54" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T13:52:16Z</t>
+          <t>2026-08-17T20:52:47Z</t>
         </is>
       </c>
     </row>
@@ -4816,7 +4816,7 @@
       </c>
       <c r="S55" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T13:52:16Z</t>
+          <t>2026-08-17T20:52:47Z</t>
         </is>
       </c>
     </row>
@@ -4901,7 +4901,7 @@
       </c>
       <c r="S56" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T13:52:16Z</t>
+          <t>2026-08-17T20:52:47Z</t>
         </is>
       </c>
     </row>
@@ -4986,7 +4986,7 @@
       </c>
       <c r="S57" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T13:52:16Z</t>
+          <t>2026-08-17T20:52:47Z</t>
         </is>
       </c>
     </row>
@@ -5071,7 +5071,7 @@
       </c>
       <c r="S58" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T13:52:16Z</t>
+          <t>2026-08-17T20:52:47Z</t>
         </is>
       </c>
     </row>
@@ -5156,7 +5156,7 @@
       </c>
       <c r="S59" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T13:52:16Z</t>
+          <t>2026-08-17T20:52:47Z</t>
         </is>
       </c>
     </row>
@@ -5241,7 +5241,7 @@
       </c>
       <c r="S60" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T13:52:16Z</t>
+          <t>2026-08-17T20:52:47Z</t>
         </is>
       </c>
     </row>
@@ -5326,7 +5326,7 @@
       </c>
       <c r="S61" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T13:52:16Z</t>
+          <t>2026-08-17T20:52:47Z</t>
         </is>
       </c>
     </row>
@@ -5411,7 +5411,7 @@
       </c>
       <c r="S62" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T13:52:16Z</t>
+          <t>2026-08-17T20:52:47Z</t>
         </is>
       </c>
     </row>
@@ -5496,7 +5496,7 @@
       </c>
       <c r="S63" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T13:52:16Z</t>
+          <t>2026-08-17T20:52:47Z</t>
         </is>
       </c>
     </row>
@@ -5581,7 +5581,7 @@
       </c>
       <c r="S64" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T13:52:16Z</t>
+          <t>2026-08-17T20:52:47Z</t>
         </is>
       </c>
     </row>
@@ -5666,7 +5666,7 @@
       </c>
       <c r="S65" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T13:52:16Z</t>
+          <t>2026-08-17T20:52:47Z</t>
         </is>
       </c>
     </row>
@@ -5751,7 +5751,7 @@
       </c>
       <c r="S66" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T13:52:16Z</t>
+          <t>2026-08-17T20:52:47Z</t>
         </is>
       </c>
     </row>
@@ -5836,7 +5836,7 @@
       </c>
       <c r="S67" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T13:52:16Z</t>
+          <t>2026-08-17T20:52:47Z</t>
         </is>
       </c>
     </row>
@@ -5921,7 +5921,7 @@
       </c>
       <c r="S68" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T13:52:16Z</t>
+          <t>2026-08-17T20:52:47Z</t>
         </is>
       </c>
     </row>
@@ -6006,7 +6006,7 @@
       </c>
       <c r="S69" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T13:52:16Z</t>
+          <t>2026-08-17T20:52:47Z</t>
         </is>
       </c>
     </row>
@@ -6091,7 +6091,7 @@
       </c>
       <c r="S70" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T13:52:16Z</t>
+          <t>2026-08-17T20:52:47Z</t>
         </is>
       </c>
     </row>
@@ -6176,7 +6176,7 @@
       </c>
       <c r="S71" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T13:52:16Z</t>
+          <t>2026-08-17T20:52:47Z</t>
         </is>
       </c>
     </row>
@@ -6261,7 +6261,7 @@
       </c>
       <c r="S72" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T13:52:16Z</t>
+          <t>2026-08-17T20:52:47Z</t>
         </is>
       </c>
     </row>
@@ -6346,7 +6346,7 @@
       </c>
       <c r="S73" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T13:52:16Z</t>
+          <t>2026-08-17T20:52:47Z</t>
         </is>
       </c>
     </row>
@@ -6431,7 +6431,7 @@
       </c>
       <c r="S74" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T13:52:16Z</t>
+          <t>2026-08-17T20:52:47Z</t>
         </is>
       </c>
     </row>
@@ -6516,7 +6516,7 @@
       </c>
       <c r="S75" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T13:52:16Z</t>
+          <t>2026-08-17T20:52:47Z</t>
         </is>
       </c>
     </row>
@@ -6601,7 +6601,7 @@
       </c>
       <c r="S76" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T13:52:16Z</t>
+          <t>2026-08-17T20:52:47Z</t>
         </is>
       </c>
     </row>
@@ -6686,7 +6686,7 @@
       </c>
       <c r="S77" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T13:52:16Z</t>
+          <t>2026-08-17T20:52:47Z</t>
         </is>
       </c>
     </row>
@@ -6771,7 +6771,7 @@
       </c>
       <c r="S78" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T13:52:16Z</t>
+          <t>2026-08-17T20:52:47Z</t>
         </is>
       </c>
     </row>
@@ -6856,7 +6856,7 @@
       </c>
       <c r="S79" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T13:52:16Z</t>
+          <t>2026-08-17T20:52:47Z</t>
         </is>
       </c>
     </row>
@@ -6941,7 +6941,7 @@
       </c>
       <c r="S80" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T13:52:16Z</t>
+          <t>2026-08-17T20:52:47Z</t>
         </is>
       </c>
     </row>
@@ -7026,7 +7026,7 @@
       </c>
       <c r="S81" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T13:52:16Z</t>
+          <t>2026-08-17T20:52:47Z</t>
         </is>
       </c>
     </row>
@@ -7111,7 +7111,7 @@
       </c>
       <c r="S82" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T13:52:16Z</t>
+          <t>2026-08-17T20:52:47Z</t>
         </is>
       </c>
     </row>
@@ -7196,7 +7196,7 @@
       </c>
       <c r="S83" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T13:52:16Z</t>
+          <t>2026-08-17T20:52:47Z</t>
         </is>
       </c>
     </row>
@@ -7281,7 +7281,7 @@
       </c>
       <c r="S84" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T13:52:16Z</t>
+          <t>2026-08-17T20:52:47Z</t>
         </is>
       </c>
     </row>
@@ -7366,7 +7366,7 @@
       </c>
       <c r="S85" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T13:52:16Z</t>
+          <t>2026-08-17T20:52:47Z</t>
         </is>
       </c>
     </row>
@@ -7451,7 +7451,7 @@
       </c>
       <c r="S86" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T13:52:16Z</t>
+          <t>2026-08-17T20:52:47Z</t>
         </is>
       </c>
     </row>
@@ -7536,7 +7536,7 @@
       </c>
       <c r="S87" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T13:52:16Z</t>
+          <t>2026-08-17T20:52:47Z</t>
         </is>
       </c>
     </row>
@@ -7621,7 +7621,7 @@
       </c>
       <c r="S88" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T13:52:16Z</t>
+          <t>2026-08-17T20:52:47Z</t>
         </is>
       </c>
     </row>
@@ -7706,7 +7706,7 @@
       </c>
       <c r="S89" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T13:52:16Z</t>
+          <t>2026-08-17T20:52:47Z</t>
         </is>
       </c>
     </row>
@@ -7791,7 +7791,7 @@
       </c>
       <c r="S90" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T13:52:16Z</t>
+          <t>2026-08-17T20:52:47Z</t>
         </is>
       </c>
     </row>
@@ -7876,7 +7876,7 @@
       </c>
       <c r="S91" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T13:52:16Z</t>
+          <t>2026-08-17T20:52:47Z</t>
         </is>
       </c>
     </row>
@@ -7961,7 +7961,7 @@
       </c>
       <c r="S92" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T13:52:16Z</t>
+          <t>2026-08-17T20:52:47Z</t>
         </is>
       </c>
     </row>
@@ -8046,7 +8046,7 @@
       </c>
       <c r="S93" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T13:52:16Z</t>
+          <t>2026-08-17T20:52:47Z</t>
         </is>
       </c>
     </row>
@@ -8131,7 +8131,7 @@
       </c>
       <c r="S94" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T13:52:16Z</t>
+          <t>2026-08-17T20:52:47Z</t>
         </is>
       </c>
     </row>
@@ -8216,7 +8216,7 @@
       </c>
       <c r="S95" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T13:52:16Z</t>
+          <t>2026-08-17T20:52:47Z</t>
         </is>
       </c>
     </row>
@@ -8301,7 +8301,7 @@
       </c>
       <c r="S96" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T13:52:16Z</t>
+          <t>2026-08-17T20:52:47Z</t>
         </is>
       </c>
     </row>
@@ -8386,7 +8386,7 @@
       </c>
       <c r="S97" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T13:52:16Z</t>
+          <t>2026-08-17T20:52:47Z</t>
         </is>
       </c>
     </row>
@@ -8471,7 +8471,7 @@
       </c>
       <c r="S98" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T13:52:16Z</t>
+          <t>2026-08-17T20:52:47Z</t>
         </is>
       </c>
     </row>
@@ -8556,7 +8556,7 @@
       </c>
       <c r="S99" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T13:52:16Z</t>
+          <t>2026-08-17T20:52:47Z</t>
         </is>
       </c>
     </row>
@@ -8641,7 +8641,7 @@
       </c>
       <c r="S100" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T13:52:16Z</t>
+          <t>2026-08-17T20:52:47Z</t>
         </is>
       </c>
     </row>
@@ -8726,7 +8726,7 @@
       </c>
       <c r="S101" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T13:52:16Z</t>
+          <t>2026-08-17T20:52:47Z</t>
         </is>
       </c>
     </row>
@@ -8811,7 +8811,7 @@
       </c>
       <c r="S102" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T13:52:16Z</t>
+          <t>2026-08-17T20:52:47Z</t>
         </is>
       </c>
     </row>
@@ -8896,7 +8896,7 @@
       </c>
       <c r="S103" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T13:52:16Z</t>
+          <t>2026-08-17T20:52:47Z</t>
         </is>
       </c>
     </row>
@@ -8981,7 +8981,7 @@
       </c>
       <c r="S104" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T13:52:16Z</t>
+          <t>2026-08-17T20:52:47Z</t>
         </is>
       </c>
     </row>
@@ -9066,7 +9066,7 @@
       </c>
       <c r="S105" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T13:52:16Z</t>
+          <t>2026-08-17T20:52:47Z</t>
         </is>
       </c>
     </row>
@@ -9151,7 +9151,7 @@
       </c>
       <c r="S106" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T13:52:16Z</t>
+          <t>2026-08-17T20:52:47Z</t>
         </is>
       </c>
     </row>
@@ -9236,7 +9236,7 @@
       </c>
       <c r="S107" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T13:52:16Z</t>
+          <t>2026-08-17T20:52:47Z</t>
         </is>
       </c>
     </row>
@@ -9321,7 +9321,7 @@
       </c>
       <c r="S108" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T13:52:16Z</t>
+          <t>2026-08-17T20:52:47Z</t>
         </is>
       </c>
     </row>
@@ -9406,7 +9406,7 @@
       </c>
       <c r="S109" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T13:52:16Z</t>
+          <t>2026-08-17T20:52:47Z</t>
         </is>
       </c>
     </row>
@@ -9491,7 +9491,7 @@
       </c>
       <c r="S110" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T13:52:16Z</t>
+          <t>2026-08-17T20:52:47Z</t>
         </is>
       </c>
     </row>
@@ -9576,7 +9576,7 @@
       </c>
       <c r="S111" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T13:52:16Z</t>
+          <t>2026-08-17T20:52:47Z</t>
         </is>
       </c>
     </row>
@@ -9661,7 +9661,7 @@
       </c>
       <c r="S112" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T13:52:16Z</t>
+          <t>2026-08-17T20:52:47Z</t>
         </is>
       </c>
     </row>
@@ -9746,7 +9746,7 @@
       </c>
       <c r="S113" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T13:52:16Z</t>
+          <t>2026-08-17T20:52:47Z</t>
         </is>
       </c>
     </row>
@@ -9831,7 +9831,7 @@
       </c>
       <c r="S114" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T13:52:16Z</t>
+          <t>2026-08-17T20:52:47Z</t>
         </is>
       </c>
     </row>
@@ -9916,7 +9916,7 @@
       </c>
       <c r="S115" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T13:52:16Z</t>
+          <t>2026-08-17T20:52:47Z</t>
         </is>
       </c>
     </row>
@@ -10001,7 +10001,7 @@
       </c>
       <c r="S116" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T13:52:16Z</t>
+          <t>2026-08-17T20:52:47Z</t>
         </is>
       </c>
     </row>
@@ -10086,7 +10086,7 @@
       </c>
       <c r="S117" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T13:52:16Z</t>
+          <t>2026-08-17T20:52:47Z</t>
         </is>
       </c>
     </row>
@@ -10171,7 +10171,7 @@
       </c>
       <c r="S118" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T13:52:16Z</t>
+          <t>2026-08-17T20:52:47Z</t>
         </is>
       </c>
     </row>
@@ -10256,7 +10256,7 @@
       </c>
       <c r="S119" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T13:52:16Z</t>
+          <t>2026-08-17T20:52:47Z</t>
         </is>
       </c>
     </row>
@@ -10341,7 +10341,7 @@
       </c>
       <c r="S120" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T13:52:16Z</t>
+          <t>2026-08-17T20:52:47Z</t>
         </is>
       </c>
     </row>
@@ -10426,7 +10426,7 @@
       </c>
       <c r="S121" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T13:52:16Z</t>
+          <t>2026-08-17T20:52:47Z</t>
         </is>
       </c>
     </row>
@@ -10511,7 +10511,7 @@
       </c>
       <c r="S122" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T13:52:16Z</t>
+          <t>2026-08-17T20:52:47Z</t>
         </is>
       </c>
     </row>
@@ -10596,7 +10596,7 @@
       </c>
       <c r="S123" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T13:52:16Z</t>
+          <t>2026-08-17T20:52:47Z</t>
         </is>
       </c>
     </row>
@@ -10681,7 +10681,7 @@
       </c>
       <c r="S124" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T13:52:16Z</t>
+          <t>2026-08-17T20:52:47Z</t>
         </is>
       </c>
     </row>
@@ -10766,7 +10766,7 @@
       </c>
       <c r="S125" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T13:52:16Z</t>
+          <t>2026-08-17T20:52:47Z</t>
         </is>
       </c>
     </row>
@@ -10851,7 +10851,7 @@
       </c>
       <c r="S126" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T13:52:16Z</t>
+          <t>2026-08-17T20:52:47Z</t>
         </is>
       </c>
     </row>
@@ -10936,7 +10936,7 @@
       </c>
       <c r="S127" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T13:52:16Z</t>
+          <t>2026-08-17T20:52:47Z</t>
         </is>
       </c>
     </row>
@@ -11021,7 +11021,7 @@
       </c>
       <c r="S128" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T13:52:16Z</t>
+          <t>2026-08-17T20:52:47Z</t>
         </is>
       </c>
     </row>
@@ -11106,7 +11106,7 @@
       </c>
       <c r="S129" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T13:52:16Z</t>
+          <t>2026-08-17T20:52:47Z</t>
         </is>
       </c>
     </row>
@@ -11191,7 +11191,7 @@
       </c>
       <c r="S130" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T13:52:16Z</t>
+          <t>2026-08-17T20:52:47Z</t>
         </is>
       </c>
     </row>
@@ -11276,7 +11276,7 @@
       </c>
       <c r="S131" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T13:52:16Z</t>
+          <t>2026-08-17T20:52:47Z</t>
         </is>
       </c>
     </row>
@@ -11361,7 +11361,7 @@
       </c>
       <c r="S132" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T13:52:16Z</t>
+          <t>2026-08-17T20:52:47Z</t>
         </is>
       </c>
     </row>
@@ -11446,7 +11446,7 @@
       </c>
       <c r="S133" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T13:52:16Z</t>
+          <t>2026-08-17T20:52:47Z</t>
         </is>
       </c>
     </row>
@@ -11531,7 +11531,7 @@
       </c>
       <c r="S134" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T13:52:16Z</t>
+          <t>2026-08-17T20:52:47Z</t>
         </is>
       </c>
     </row>
@@ -11616,7 +11616,7 @@
       </c>
       <c r="S135" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T13:52:16Z</t>
+          <t>2026-08-17T20:52:47Z</t>
         </is>
       </c>
     </row>
@@ -11701,7 +11701,7 @@
       </c>
       <c r="S136" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T13:52:16Z</t>
+          <t>2026-08-17T20:52:47Z</t>
         </is>
       </c>
     </row>
@@ -11786,7 +11786,7 @@
       </c>
       <c r="S137" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T13:52:16Z</t>
+          <t>2026-08-17T20:52:47Z</t>
         </is>
       </c>
     </row>
@@ -11871,7 +11871,7 @@
       </c>
       <c r="S138" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T13:52:16Z</t>
+          <t>2026-08-17T20:52:47Z</t>
         </is>
       </c>
     </row>
@@ -11956,7 +11956,7 @@
       </c>
       <c r="S139" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T13:52:16Z</t>
+          <t>2026-08-17T20:52:47Z</t>
         </is>
       </c>
     </row>
@@ -12041,7 +12041,7 @@
       </c>
       <c r="S140" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T13:52:16Z</t>
+          <t>2026-08-17T20:52:47Z</t>
         </is>
       </c>
     </row>
@@ -12126,7 +12126,7 @@
       </c>
       <c r="S141" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T13:52:16Z</t>
+          <t>2026-08-17T20:52:47Z</t>
         </is>
       </c>
     </row>
@@ -12258,7 +12258,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T13:52:16Z</t>
+          <t>2026-08-17T20:52:47Z</t>
         </is>
       </c>
     </row>
@@ -12338,7 +12338,7 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>{"dataset_id": "bcv_pib_historico_anual", "title": "Producto interno bruto histórico anual", "table": "PIB histórico anual", "source_file": "7_1_14_anual.xls", "base": "1957/1968/1984/1997", "price_type": "Precios constantes", "measure": "Nivel", "frequency": "Anual", "period": "2017", "year": 2017, "quarter": null, "classification": "Total economía", "component": "Producto interno bruto", "value": 392393.12, "unit": "Millones de bolívares a precios constantes", "status": "", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/7_1_14_anual.xls", "fetched_at": "2026-08-17T13:52:16Z"}</t>
+          <t>{"dataset_id": "bcv_pib_historico_anual", "title": "Producto interno bruto histórico anual", "table": "PIB histórico anual", "source_file": "7_1_14_anual.xls", "base": "1957/1968/1984/1997", "price_type": "Precios constantes", "measure": "Nivel", "frequency": "Anual", "period": "2017", "year": 2017, "quarter": null, "classification": "Total economía", "component": "Producto interno bruto", "value": 392393.12, "unit": "Millones de bolívares a precios constantes", "status": "", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/7_1_14_anual.xls", "fetched_at": "2026-08-17T20:52:47Z"}</t>
         </is>
       </c>
     </row>

--- a/assets/data/bcv/excel/ove_bcv_pib_historico_anual.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_pib_historico_anual.xlsx
@@ -736,7 +736,7 @@
       </c>
       <c r="S7" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T20:52:47Z</t>
+          <t>2026-08-21T16:34:24Z</t>
         </is>
       </c>
     </row>
@@ -821,7 +821,7 @@
       </c>
       <c r="S8" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T20:52:47Z</t>
+          <t>2026-08-21T16:34:24Z</t>
         </is>
       </c>
     </row>
@@ -906,7 +906,7 @@
       </c>
       <c r="S9" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T20:52:47Z</t>
+          <t>2026-08-21T16:34:24Z</t>
         </is>
       </c>
     </row>
@@ -991,7 +991,7 @@
       </c>
       <c r="S10" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T20:52:47Z</t>
+          <t>2026-08-21T16:34:24Z</t>
         </is>
       </c>
     </row>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="S11" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T20:52:47Z</t>
+          <t>2026-08-21T16:34:24Z</t>
         </is>
       </c>
     </row>
@@ -1161,7 +1161,7 @@
       </c>
       <c r="S12" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T20:52:47Z</t>
+          <t>2026-08-21T16:34:24Z</t>
         </is>
       </c>
     </row>
@@ -1246,7 +1246,7 @@
       </c>
       <c r="S13" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T20:52:47Z</t>
+          <t>2026-08-21T16:34:24Z</t>
         </is>
       </c>
     </row>
@@ -1331,7 +1331,7 @@
       </c>
       <c r="S14" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T20:52:47Z</t>
+          <t>2026-08-21T16:34:24Z</t>
         </is>
       </c>
     </row>
@@ -1416,7 +1416,7 @@
       </c>
       <c r="S15" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T20:52:47Z</t>
+          <t>2026-08-21T16:34:24Z</t>
         </is>
       </c>
     </row>
@@ -1501,7 +1501,7 @@
       </c>
       <c r="S16" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T20:52:47Z</t>
+          <t>2026-08-21T16:34:24Z</t>
         </is>
       </c>
     </row>
@@ -1586,7 +1586,7 @@
       </c>
       <c r="S17" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T20:52:47Z</t>
+          <t>2026-08-21T16:34:24Z</t>
         </is>
       </c>
     </row>
@@ -1671,7 +1671,7 @@
       </c>
       <c r="S18" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T20:52:47Z</t>
+          <t>2026-08-21T16:34:24Z</t>
         </is>
       </c>
     </row>
@@ -1756,7 +1756,7 @@
       </c>
       <c r="S19" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T20:52:47Z</t>
+          <t>2026-08-21T16:34:24Z</t>
         </is>
       </c>
     </row>
@@ -1841,7 +1841,7 @@
       </c>
       <c r="S20" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T20:52:47Z</t>
+          <t>2026-08-21T16:34:24Z</t>
         </is>
       </c>
     </row>
@@ -1926,7 +1926,7 @@
       </c>
       <c r="S21" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T20:52:47Z</t>
+          <t>2026-08-21T16:34:24Z</t>
         </is>
       </c>
     </row>
@@ -2011,7 +2011,7 @@
       </c>
       <c r="S22" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T20:52:47Z</t>
+          <t>2026-08-21T16:34:24Z</t>
         </is>
       </c>
     </row>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="S23" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T20:52:47Z</t>
+          <t>2026-08-21T16:34:24Z</t>
         </is>
       </c>
     </row>
@@ -2181,7 +2181,7 @@
       </c>
       <c r="S24" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T20:52:47Z</t>
+          <t>2026-08-21T16:34:24Z</t>
         </is>
       </c>
     </row>
@@ -2266,7 +2266,7 @@
       </c>
       <c r="S25" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T20:52:47Z</t>
+          <t>2026-08-21T16:34:24Z</t>
         </is>
       </c>
     </row>
@@ -2351,7 +2351,7 @@
       </c>
       <c r="S26" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T20:52:47Z</t>
+          <t>2026-08-21T16:34:24Z</t>
         </is>
       </c>
     </row>
@@ -2436,7 +2436,7 @@
       </c>
       <c r="S27" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T20:52:47Z</t>
+          <t>2026-08-21T16:34:24Z</t>
         </is>
       </c>
     </row>
@@ -2521,7 +2521,7 @@
       </c>
       <c r="S28" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T20:52:47Z</t>
+          <t>2026-08-21T16:34:24Z</t>
         </is>
       </c>
     </row>
@@ -2606,7 +2606,7 @@
       </c>
       <c r="S29" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T20:52:47Z</t>
+          <t>2026-08-21T16:34:24Z</t>
         </is>
       </c>
     </row>
@@ -2691,7 +2691,7 @@
       </c>
       <c r="S30" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T20:52:47Z</t>
+          <t>2026-08-21T16:34:24Z</t>
         </is>
       </c>
     </row>
@@ -2776,7 +2776,7 @@
       </c>
       <c r="S31" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T20:52:47Z</t>
+          <t>2026-08-21T16:34:24Z</t>
         </is>
       </c>
     </row>
@@ -2861,7 +2861,7 @@
       </c>
       <c r="S32" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T20:52:47Z</t>
+          <t>2026-08-21T16:34:24Z</t>
         </is>
       </c>
     </row>
@@ -2946,7 +2946,7 @@
       </c>
       <c r="S33" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T20:52:47Z</t>
+          <t>2026-08-21T16:34:24Z</t>
         </is>
       </c>
     </row>
@@ -3031,7 +3031,7 @@
       </c>
       <c r="S34" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T20:52:47Z</t>
+          <t>2026-08-21T16:34:24Z</t>
         </is>
       </c>
     </row>
@@ -3116,7 +3116,7 @@
       </c>
       <c r="S35" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T20:52:47Z</t>
+          <t>2026-08-21T16:34:24Z</t>
         </is>
       </c>
     </row>
@@ -3201,7 +3201,7 @@
       </c>
       <c r="S36" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T20:52:47Z</t>
+          <t>2026-08-21T16:34:24Z</t>
         </is>
       </c>
     </row>
@@ -3286,7 +3286,7 @@
       </c>
       <c r="S37" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T20:52:47Z</t>
+          <t>2026-08-21T16:34:24Z</t>
         </is>
       </c>
     </row>
@@ -3371,7 +3371,7 @@
       </c>
       <c r="S38" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T20:52:47Z</t>
+          <t>2026-08-21T16:34:24Z</t>
         </is>
       </c>
     </row>
@@ -3456,7 +3456,7 @@
       </c>
       <c r="S39" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T20:52:47Z</t>
+          <t>2026-08-21T16:34:24Z</t>
         </is>
       </c>
     </row>
@@ -3541,7 +3541,7 @@
       </c>
       <c r="S40" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T20:52:47Z</t>
+          <t>2026-08-21T16:34:24Z</t>
         </is>
       </c>
     </row>
@@ -3626,7 +3626,7 @@
       </c>
       <c r="S41" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T20:52:47Z</t>
+          <t>2026-08-21T16:34:24Z</t>
         </is>
       </c>
     </row>
@@ -3711,7 +3711,7 @@
       </c>
       <c r="S42" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T20:52:47Z</t>
+          <t>2026-08-21T16:34:24Z</t>
         </is>
       </c>
     </row>
@@ -3796,7 +3796,7 @@
       </c>
       <c r="S43" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T20:52:47Z</t>
+          <t>2026-08-21T16:34:24Z</t>
         </is>
       </c>
     </row>
@@ -3881,7 +3881,7 @@
       </c>
       <c r="S44" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T20:52:47Z</t>
+          <t>2026-08-21T16:34:24Z</t>
         </is>
       </c>
     </row>
@@ -3966,7 +3966,7 @@
       </c>
       <c r="S45" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T20:52:47Z</t>
+          <t>2026-08-21T16:34:24Z</t>
         </is>
       </c>
     </row>
@@ -4051,7 +4051,7 @@
       </c>
       <c r="S46" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T20:52:47Z</t>
+          <t>2026-08-21T16:34:24Z</t>
         </is>
       </c>
     </row>
@@ -4136,7 +4136,7 @@
       </c>
       <c r="S47" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T20:52:47Z</t>
+          <t>2026-08-21T16:34:24Z</t>
         </is>
       </c>
     </row>
@@ -4221,7 +4221,7 @@
       </c>
       <c r="S48" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T20:52:47Z</t>
+          <t>2026-08-21T16:34:24Z</t>
         </is>
       </c>
     </row>
@@ -4306,7 +4306,7 @@
       </c>
       <c r="S49" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T20:52:47Z</t>
+          <t>2026-08-21T16:34:24Z</t>
         </is>
       </c>
     </row>
@@ -4391,7 +4391,7 @@
       </c>
       <c r="S50" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T20:52:47Z</t>
+          <t>2026-08-21T16:34:24Z</t>
         </is>
       </c>
     </row>
@@ -4476,7 +4476,7 @@
       </c>
       <c r="S51" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T20:52:47Z</t>
+          <t>2026-08-21T16:34:24Z</t>
         </is>
       </c>
     </row>
@@ -4561,7 +4561,7 @@
       </c>
       <c r="S52" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T20:52:47Z</t>
+          <t>2026-08-21T16:34:24Z</t>
         </is>
       </c>
     </row>
@@ -4646,7 +4646,7 @@
       </c>
       <c r="S53" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T20:52:47Z</t>
+          <t>2026-08-21T16:34:24Z</t>
         </is>
       </c>
     </row>
@@ -4731,7 +4731,7 @@
       </c>
       <c r="S54" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T20:52:47Z</t>
+          <t>2026-08-21T16:34:24Z</t>
         </is>
       </c>
     </row>
@@ -4816,7 +4816,7 @@
       </c>
       <c r="S55" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T20:52:47Z</t>
+          <t>2026-08-21T16:34:24Z</t>
         </is>
       </c>
     </row>
@@ -4901,7 +4901,7 @@
       </c>
       <c r="S56" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T20:52:47Z</t>
+          <t>2026-08-21T16:34:24Z</t>
         </is>
       </c>
     </row>
@@ -4986,7 +4986,7 @@
       </c>
       <c r="S57" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T20:52:47Z</t>
+          <t>2026-08-21T16:34:24Z</t>
         </is>
       </c>
     </row>
@@ -5071,7 +5071,7 @@
       </c>
       <c r="S58" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T20:52:47Z</t>
+          <t>2026-08-21T16:34:24Z</t>
         </is>
       </c>
     </row>
@@ -5156,7 +5156,7 @@
       </c>
       <c r="S59" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T20:52:47Z</t>
+          <t>2026-08-21T16:34:24Z</t>
         </is>
       </c>
     </row>
@@ -5241,7 +5241,7 @@
       </c>
       <c r="S60" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T20:52:47Z</t>
+          <t>2026-08-21T16:34:24Z</t>
         </is>
       </c>
     </row>
@@ -5326,7 +5326,7 @@
       </c>
       <c r="S61" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T20:52:47Z</t>
+          <t>2026-08-21T16:34:24Z</t>
         </is>
       </c>
     </row>
@@ -5411,7 +5411,7 @@
       </c>
       <c r="S62" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T20:52:47Z</t>
+          <t>2026-08-21T16:34:24Z</t>
         </is>
       </c>
     </row>
@@ -5496,7 +5496,7 @@
       </c>
       <c r="S63" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T20:52:47Z</t>
+          <t>2026-08-21T16:34:24Z</t>
         </is>
       </c>
     </row>
@@ -5581,7 +5581,7 @@
       </c>
       <c r="S64" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T20:52:47Z</t>
+          <t>2026-08-21T16:34:24Z</t>
         </is>
       </c>
     </row>
@@ -5666,7 +5666,7 @@
       </c>
       <c r="S65" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T20:52:47Z</t>
+          <t>2026-08-21T16:34:24Z</t>
         </is>
       </c>
     </row>
@@ -5751,7 +5751,7 @@
       </c>
       <c r="S66" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T20:52:47Z</t>
+          <t>2026-08-21T16:34:24Z</t>
         </is>
       </c>
     </row>
@@ -5836,7 +5836,7 @@
       </c>
       <c r="S67" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T20:52:47Z</t>
+          <t>2026-08-21T16:34:24Z</t>
         </is>
       </c>
     </row>
@@ -5921,7 +5921,7 @@
       </c>
       <c r="S68" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T20:52:47Z</t>
+          <t>2026-08-21T16:34:24Z</t>
         </is>
       </c>
     </row>
@@ -6006,7 +6006,7 @@
       </c>
       <c r="S69" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T20:52:47Z</t>
+          <t>2026-08-21T16:34:24Z</t>
         </is>
       </c>
     </row>
@@ -6091,7 +6091,7 @@
       </c>
       <c r="S70" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T20:52:47Z</t>
+          <t>2026-08-21T16:34:24Z</t>
         </is>
       </c>
     </row>
@@ -6176,7 +6176,7 @@
       </c>
       <c r="S71" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T20:52:47Z</t>
+          <t>2026-08-21T16:34:24Z</t>
         </is>
       </c>
     </row>
@@ -6261,7 +6261,7 @@
       </c>
       <c r="S72" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T20:52:47Z</t>
+          <t>2026-08-21T16:34:24Z</t>
         </is>
       </c>
     </row>
@@ -6346,7 +6346,7 @@
       </c>
       <c r="S73" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T20:52:47Z</t>
+          <t>2026-08-21T16:34:24Z</t>
         </is>
       </c>
     </row>
@@ -6431,7 +6431,7 @@
       </c>
       <c r="S74" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T20:52:47Z</t>
+          <t>2026-08-21T16:34:24Z</t>
         </is>
       </c>
     </row>
@@ -6516,7 +6516,7 @@
       </c>
       <c r="S75" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T20:52:47Z</t>
+          <t>2026-08-21T16:34:24Z</t>
         </is>
       </c>
     </row>
@@ -6601,7 +6601,7 @@
       </c>
       <c r="S76" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T20:52:47Z</t>
+          <t>2026-08-21T16:34:24Z</t>
         </is>
       </c>
     </row>
@@ -6686,7 +6686,7 @@
       </c>
       <c r="S77" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T20:52:47Z</t>
+          <t>2026-08-21T16:34:24Z</t>
         </is>
       </c>
     </row>
@@ -6771,7 +6771,7 @@
       </c>
       <c r="S78" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T20:52:47Z</t>
+          <t>2026-08-21T16:34:24Z</t>
         </is>
       </c>
     </row>
@@ -6856,7 +6856,7 @@
       </c>
       <c r="S79" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T20:52:47Z</t>
+          <t>2026-08-21T16:34:24Z</t>
         </is>
       </c>
     </row>
@@ -6941,7 +6941,7 @@
       </c>
       <c r="S80" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T20:52:47Z</t>
+          <t>2026-08-21T16:34:24Z</t>
         </is>
       </c>
     </row>
@@ -7026,7 +7026,7 @@
       </c>
       <c r="S81" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T20:52:47Z</t>
+          <t>2026-08-21T16:34:24Z</t>
         </is>
       </c>
     </row>
@@ -7111,7 +7111,7 @@
       </c>
       <c r="S82" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T20:52:47Z</t>
+          <t>2026-08-21T16:34:24Z</t>
         </is>
       </c>
     </row>
@@ -7196,7 +7196,7 @@
       </c>
       <c r="S83" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T20:52:47Z</t>
+          <t>2026-08-21T16:34:24Z</t>
         </is>
       </c>
     </row>
@@ -7281,7 +7281,7 @@
       </c>
       <c r="S84" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T20:52:47Z</t>
+          <t>2026-08-21T16:34:24Z</t>
         </is>
       </c>
     </row>
@@ -7366,7 +7366,7 @@
       </c>
       <c r="S85" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T20:52:47Z</t>
+          <t>2026-08-21T16:34:24Z</t>
         </is>
       </c>
     </row>
@@ -7451,7 +7451,7 @@
       </c>
       <c r="S86" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T20:52:47Z</t>
+          <t>2026-08-21T16:34:24Z</t>
         </is>
       </c>
     </row>
@@ -7536,7 +7536,7 @@
       </c>
       <c r="S87" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T20:52:47Z</t>
+          <t>2026-08-21T16:34:24Z</t>
         </is>
       </c>
     </row>
@@ -7621,7 +7621,7 @@
       </c>
       <c r="S88" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T20:52:47Z</t>
+          <t>2026-08-21T16:34:24Z</t>
         </is>
       </c>
     </row>
@@ -7706,7 +7706,7 @@
       </c>
       <c r="S89" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T20:52:47Z</t>
+          <t>2026-08-21T16:34:24Z</t>
         </is>
       </c>
     </row>
@@ -7791,7 +7791,7 @@
       </c>
       <c r="S90" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T20:52:47Z</t>
+          <t>2026-08-21T16:34:24Z</t>
         </is>
       </c>
     </row>
@@ -7876,7 +7876,7 @@
       </c>
       <c r="S91" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T20:52:47Z</t>
+          <t>2026-08-21T16:34:24Z</t>
         </is>
       </c>
     </row>
@@ -7961,7 +7961,7 @@
       </c>
       <c r="S92" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T20:52:47Z</t>
+          <t>2026-08-21T16:34:24Z</t>
         </is>
       </c>
     </row>
@@ -8046,7 +8046,7 @@
       </c>
       <c r="S93" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T20:52:47Z</t>
+          <t>2026-08-21T16:34:24Z</t>
         </is>
       </c>
     </row>
@@ -8131,7 +8131,7 @@
       </c>
       <c r="S94" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T20:52:47Z</t>
+          <t>2026-08-21T16:34:24Z</t>
         </is>
       </c>
     </row>
@@ -8216,7 +8216,7 @@
       </c>
       <c r="S95" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T20:52:47Z</t>
+          <t>2026-08-21T16:34:24Z</t>
         </is>
       </c>
     </row>
@@ -8301,7 +8301,7 @@
       </c>
       <c r="S96" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T20:52:47Z</t>
+          <t>2026-08-21T16:34:24Z</t>
         </is>
       </c>
     </row>
@@ -8386,7 +8386,7 @@
       </c>
       <c r="S97" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T20:52:47Z</t>
+          <t>2026-08-21T16:34:24Z</t>
         </is>
       </c>
     </row>
@@ -8471,7 +8471,7 @@
       </c>
       <c r="S98" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T20:52:47Z</t>
+          <t>2026-08-21T16:34:24Z</t>
         </is>
       </c>
     </row>
@@ -8556,7 +8556,7 @@
       </c>
       <c r="S99" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T20:52:47Z</t>
+          <t>2026-08-21T16:34:24Z</t>
         </is>
       </c>
     </row>
@@ -8641,7 +8641,7 @@
       </c>
       <c r="S100" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T20:52:47Z</t>
+          <t>2026-08-21T16:34:24Z</t>
         </is>
       </c>
     </row>
@@ -8726,7 +8726,7 @@
       </c>
       <c r="S101" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T20:52:47Z</t>
+          <t>2026-08-21T16:34:24Z</t>
         </is>
       </c>
     </row>
@@ -8811,7 +8811,7 @@
       </c>
       <c r="S102" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T20:52:47Z</t>
+          <t>2026-08-21T16:34:24Z</t>
         </is>
       </c>
     </row>
@@ -8896,7 +8896,7 @@
       </c>
       <c r="S103" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T20:52:47Z</t>
+          <t>2026-08-21T16:34:24Z</t>
         </is>
       </c>
     </row>
@@ -8981,7 +8981,7 @@
       </c>
       <c r="S104" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T20:52:47Z</t>
+          <t>2026-08-21T16:34:24Z</t>
         </is>
       </c>
     </row>
@@ -9066,7 +9066,7 @@
       </c>
       <c r="S105" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T20:52:47Z</t>
+          <t>2026-08-21T16:34:24Z</t>
         </is>
       </c>
     </row>
@@ -9151,7 +9151,7 @@
       </c>
       <c r="S106" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T20:52:47Z</t>
+          <t>2026-08-21T16:34:24Z</t>
         </is>
       </c>
     </row>
@@ -9236,7 +9236,7 @@
       </c>
       <c r="S107" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T20:52:47Z</t>
+          <t>2026-08-21T16:34:24Z</t>
         </is>
       </c>
     </row>
@@ -9321,7 +9321,7 @@
       </c>
       <c r="S108" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T20:52:47Z</t>
+          <t>2026-08-21T16:34:24Z</t>
         </is>
       </c>
     </row>
@@ -9406,7 +9406,7 @@
       </c>
       <c r="S109" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T20:52:47Z</t>
+          <t>2026-08-21T16:34:24Z</t>
         </is>
       </c>
     </row>
@@ -9491,7 +9491,7 @@
       </c>
       <c r="S110" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T20:52:47Z</t>
+          <t>2026-08-21T16:34:24Z</t>
         </is>
       </c>
     </row>
@@ -9576,7 +9576,7 @@
       </c>
       <c r="S111" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T20:52:47Z</t>
+          <t>2026-08-21T16:34:24Z</t>
         </is>
       </c>
     </row>
@@ -9661,7 +9661,7 @@
       </c>
       <c r="S112" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T20:52:47Z</t>
+          <t>2026-08-21T16:34:24Z</t>
         </is>
       </c>
     </row>
@@ -9746,7 +9746,7 @@
       </c>
       <c r="S113" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T20:52:47Z</t>
+          <t>2026-08-21T16:34:24Z</t>
         </is>
       </c>
     </row>
@@ -9831,7 +9831,7 @@
       </c>
       <c r="S114" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T20:52:47Z</t>
+          <t>2026-08-21T16:34:24Z</t>
         </is>
       </c>
     </row>
@@ -9916,7 +9916,7 @@
       </c>
       <c r="S115" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T20:52:47Z</t>
+          <t>2026-08-21T16:34:24Z</t>
         </is>
       </c>
     </row>
@@ -10001,7 +10001,7 @@
       </c>
       <c r="S116" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T20:52:47Z</t>
+          <t>2026-08-21T16:34:24Z</t>
         </is>
       </c>
     </row>
@@ -10086,7 +10086,7 @@
       </c>
       <c r="S117" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T20:52:47Z</t>
+          <t>2026-08-21T16:34:24Z</t>
         </is>
       </c>
     </row>
@@ -10171,7 +10171,7 @@
       </c>
       <c r="S118" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T20:52:47Z</t>
+          <t>2026-08-21T16:34:24Z</t>
         </is>
       </c>
     </row>
@@ -10256,7 +10256,7 @@
       </c>
       <c r="S119" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T20:52:47Z</t>
+          <t>2026-08-21T16:34:24Z</t>
         </is>
       </c>
     </row>
@@ -10341,7 +10341,7 @@
       </c>
       <c r="S120" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T20:52:47Z</t>
+          <t>2026-08-21T16:34:24Z</t>
         </is>
       </c>
     </row>
@@ -10426,7 +10426,7 @@
       </c>
       <c r="S121" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T20:52:47Z</t>
+          <t>2026-08-21T16:34:24Z</t>
         </is>
       </c>
     </row>
@@ -10511,7 +10511,7 @@
       </c>
       <c r="S122" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T20:52:47Z</t>
+          <t>2026-08-21T16:34:24Z</t>
         </is>
       </c>
     </row>
@@ -10596,7 +10596,7 @@
       </c>
       <c r="S123" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T20:52:47Z</t>
+          <t>2026-08-21T16:34:24Z</t>
         </is>
       </c>
     </row>
@@ -10681,7 +10681,7 @@
       </c>
       <c r="S124" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T20:52:47Z</t>
+          <t>2026-08-21T16:34:24Z</t>
         </is>
       </c>
     </row>
@@ -10766,7 +10766,7 @@
       </c>
       <c r="S125" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T20:52:47Z</t>
+          <t>2026-08-21T16:34:24Z</t>
         </is>
       </c>
     </row>
@@ -10851,7 +10851,7 @@
       </c>
       <c r="S126" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T20:52:47Z</t>
+          <t>2026-08-21T16:34:24Z</t>
         </is>
       </c>
     </row>
@@ -10936,7 +10936,7 @@
       </c>
       <c r="S127" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T20:52:47Z</t>
+          <t>2026-08-21T16:34:24Z</t>
         </is>
       </c>
     </row>
@@ -11021,7 +11021,7 @@
       </c>
       <c r="S128" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T20:52:47Z</t>
+          <t>2026-08-21T16:34:24Z</t>
         </is>
       </c>
     </row>
@@ -11106,7 +11106,7 @@
       </c>
       <c r="S129" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T20:52:47Z</t>
+          <t>2026-08-21T16:34:24Z</t>
         </is>
       </c>
     </row>
@@ -11191,7 +11191,7 @@
       </c>
       <c r="S130" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T20:52:47Z</t>
+          <t>2026-08-21T16:34:24Z</t>
         </is>
       </c>
     </row>
@@ -11276,7 +11276,7 @@
       </c>
       <c r="S131" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T20:52:47Z</t>
+          <t>2026-08-21T16:34:24Z</t>
         </is>
       </c>
     </row>
@@ -11361,7 +11361,7 @@
       </c>
       <c r="S132" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T20:52:47Z</t>
+          <t>2026-08-21T16:34:24Z</t>
         </is>
       </c>
     </row>
@@ -11446,7 +11446,7 @@
       </c>
       <c r="S133" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T20:52:47Z</t>
+          <t>2026-08-21T16:34:24Z</t>
         </is>
       </c>
     </row>
@@ -11531,7 +11531,7 @@
       </c>
       <c r="S134" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T20:52:47Z</t>
+          <t>2026-08-21T16:34:24Z</t>
         </is>
       </c>
     </row>
@@ -11616,7 +11616,7 @@
       </c>
       <c r="S135" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T20:52:47Z</t>
+          <t>2026-08-21T16:34:24Z</t>
         </is>
       </c>
     </row>
@@ -11701,7 +11701,7 @@
       </c>
       <c r="S136" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T20:52:47Z</t>
+          <t>2026-08-21T16:34:24Z</t>
         </is>
       </c>
     </row>
@@ -11786,7 +11786,7 @@
       </c>
       <c r="S137" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T20:52:47Z</t>
+          <t>2026-08-21T16:34:24Z</t>
         </is>
       </c>
     </row>
@@ -11871,7 +11871,7 @@
       </c>
       <c r="S138" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T20:52:47Z</t>
+          <t>2026-08-21T16:34:24Z</t>
         </is>
       </c>
     </row>
@@ -11956,7 +11956,7 @@
       </c>
       <c r="S139" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T20:52:47Z</t>
+          <t>2026-08-21T16:34:24Z</t>
         </is>
       </c>
     </row>
@@ -12041,7 +12041,7 @@
       </c>
       <c r="S140" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T20:52:47Z</t>
+          <t>2026-08-21T16:34:24Z</t>
         </is>
       </c>
     </row>
@@ -12126,7 +12126,7 @@
       </c>
       <c r="S141" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T20:52:47Z</t>
+          <t>2026-08-21T16:34:24Z</t>
         </is>
       </c>
     </row>
@@ -12258,7 +12258,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T20:52:47Z</t>
+          <t>2026-08-21T16:34:24Z</t>
         </is>
       </c>
     </row>
@@ -12338,7 +12338,7 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>{"dataset_id": "bcv_pib_historico_anual", "title": "Producto interno bruto histórico anual", "table": "PIB histórico anual", "source_file": "7_1_14_anual.xls", "base": "1957/1968/1984/1997", "price_type": "Precios constantes", "measure": "Nivel", "frequency": "Anual", "period": "2017", "year": 2017, "quarter": null, "classification": "Total economía", "component": "Producto interno bruto", "value": 392393.12, "unit": "Millones de bolívares a precios constantes", "status": "", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/7_1_14_anual.xls", "fetched_at": "2026-08-17T20:52:47Z"}</t>
+          <t>{"dataset_id": "bcv_pib_historico_anual", "title": "Producto interno bruto histórico anual", "table": "PIB histórico anual", "source_file": "7_1_14_anual.xls", "base": "1957/1968/1984/1997", "price_type": "Precios constantes", "measure": "Nivel", "frequency": "Anual", "period": "2017", "year": 2017, "quarter": null, "classification": "Total economía", "component": "Producto interno bruto", "value": 392393.12, "unit": "Millones de bolívares a precios constantes", "status": "", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/7_1_14_anual.xls", "fetched_at": "2026-08-21T16:34:24Z"}</t>
         </is>
       </c>
     </row>

--- a/assets/data/bcv/excel/ove_bcv_pib_historico_anual.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_pib_historico_anual.xlsx
@@ -736,7 +736,7 @@
       </c>
       <c r="S7" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21T16:34:24Z</t>
+          <t>2026-08-21T20:49:33Z</t>
         </is>
       </c>
     </row>
@@ -821,7 +821,7 @@
       </c>
       <c r="S8" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21T16:34:24Z</t>
+          <t>2026-08-21T20:49:33Z</t>
         </is>
       </c>
     </row>
@@ -906,7 +906,7 @@
       </c>
       <c r="S9" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21T16:34:24Z</t>
+          <t>2026-08-21T20:49:33Z</t>
         </is>
       </c>
     </row>
@@ -991,7 +991,7 @@
       </c>
       <c r="S10" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21T16:34:24Z</t>
+          <t>2026-08-21T20:49:33Z</t>
         </is>
       </c>
     </row>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="S11" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21T16:34:24Z</t>
+          <t>2026-08-21T20:49:33Z</t>
         </is>
       </c>
     </row>
@@ -1161,7 +1161,7 @@
       </c>
       <c r="S12" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21T16:34:24Z</t>
+          <t>2026-08-21T20:49:33Z</t>
         </is>
       </c>
     </row>
@@ -1246,7 +1246,7 @@
       </c>
       <c r="S13" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21T16:34:24Z</t>
+          <t>2026-08-21T20:49:33Z</t>
         </is>
       </c>
     </row>
@@ -1331,7 +1331,7 @@
       </c>
       <c r="S14" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21T16:34:24Z</t>
+          <t>2026-08-21T20:49:33Z</t>
         </is>
       </c>
     </row>
@@ -1416,7 +1416,7 @@
       </c>
       <c r="S15" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21T16:34:24Z</t>
+          <t>2026-08-21T20:49:33Z</t>
         </is>
       </c>
     </row>
@@ -1501,7 +1501,7 @@
       </c>
       <c r="S16" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21T16:34:24Z</t>
+          <t>2026-08-21T20:49:33Z</t>
         </is>
       </c>
     </row>
@@ -1586,7 +1586,7 @@
       </c>
       <c r="S17" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21T16:34:24Z</t>
+          <t>2026-08-21T20:49:33Z</t>
         </is>
       </c>
     </row>
@@ -1671,7 +1671,7 @@
       </c>
       <c r="S18" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21T16:34:24Z</t>
+          <t>2026-08-21T20:49:33Z</t>
         </is>
       </c>
     </row>
@@ -1756,7 +1756,7 @@
       </c>
       <c r="S19" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21T16:34:24Z</t>
+          <t>2026-08-21T20:49:33Z</t>
         </is>
       </c>
     </row>
@@ -1841,7 +1841,7 @@
       </c>
       <c r="S20" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21T16:34:24Z</t>
+          <t>2026-08-21T20:49:33Z</t>
         </is>
       </c>
     </row>
@@ -1926,7 +1926,7 @@
       </c>
       <c r="S21" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21T16:34:24Z</t>
+          <t>2026-08-21T20:49:33Z</t>
         </is>
       </c>
     </row>
@@ -2011,7 +2011,7 @@
       </c>
       <c r="S22" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21T16:34:24Z</t>
+          <t>2026-08-21T20:49:33Z</t>
         </is>
       </c>
     </row>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="S23" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21T16:34:24Z</t>
+          <t>2026-08-21T20:49:33Z</t>
         </is>
       </c>
     </row>
@@ -2181,7 +2181,7 @@
       </c>
       <c r="S24" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21T16:34:24Z</t>
+          <t>2026-08-21T20:49:33Z</t>
         </is>
       </c>
     </row>
@@ -2266,7 +2266,7 @@
       </c>
       <c r="S25" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21T16:34:24Z</t>
+          <t>2026-08-21T20:49:33Z</t>
         </is>
       </c>
     </row>
@@ -2351,7 +2351,7 @@
       </c>
       <c r="S26" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21T16:34:24Z</t>
+          <t>2026-08-21T20:49:33Z</t>
         </is>
       </c>
     </row>
@@ -2436,7 +2436,7 @@
       </c>
       <c r="S27" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21T16:34:24Z</t>
+          <t>2026-08-21T20:49:33Z</t>
         </is>
       </c>
     </row>
@@ -2521,7 +2521,7 @@
       </c>
       <c r="S28" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21T16:34:24Z</t>
+          <t>2026-08-21T20:49:33Z</t>
         </is>
       </c>
     </row>
@@ -2606,7 +2606,7 @@
       </c>
       <c r="S29" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21T16:34:24Z</t>
+          <t>2026-08-21T20:49:33Z</t>
         </is>
       </c>
     </row>
@@ -2691,7 +2691,7 @@
       </c>
       <c r="S30" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21T16:34:24Z</t>
+          <t>2026-08-21T20:49:33Z</t>
         </is>
       </c>
     </row>
@@ -2776,7 +2776,7 @@
       </c>
       <c r="S31" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21T16:34:24Z</t>
+          <t>2026-08-21T20:49:33Z</t>
         </is>
       </c>
     </row>
@@ -2861,7 +2861,7 @@
       </c>
       <c r="S32" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21T16:34:24Z</t>
+          <t>2026-08-21T20:49:33Z</t>
         </is>
       </c>
     </row>
@@ -2946,7 +2946,7 @@
       </c>
       <c r="S33" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21T16:34:24Z</t>
+          <t>2026-08-21T20:49:33Z</t>
         </is>
       </c>
     </row>
@@ -3031,7 +3031,7 @@
       </c>
       <c r="S34" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21T16:34:24Z</t>
+          <t>2026-08-21T20:49:33Z</t>
         </is>
       </c>
     </row>
@@ -3116,7 +3116,7 @@
       </c>
       <c r="S35" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21T16:34:24Z</t>
+          <t>2026-08-21T20:49:33Z</t>
         </is>
       </c>
     </row>
@@ -3201,7 +3201,7 @@
       </c>
       <c r="S36" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21T16:34:24Z</t>
+          <t>2026-08-21T20:49:33Z</t>
         </is>
       </c>
     </row>
@@ -3286,7 +3286,7 @@
       </c>
       <c r="S37" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21T16:34:24Z</t>
+          <t>2026-08-21T20:49:33Z</t>
         </is>
       </c>
     </row>
@@ -3371,7 +3371,7 @@
       </c>
       <c r="S38" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21T16:34:24Z</t>
+          <t>2026-08-21T20:49:33Z</t>
         </is>
       </c>
     </row>
@@ -3456,7 +3456,7 @@
       </c>
       <c r="S39" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21T16:34:24Z</t>
+          <t>2026-08-21T20:49:33Z</t>
         </is>
       </c>
     </row>
@@ -3541,7 +3541,7 @@
       </c>
       <c r="S40" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21T16:34:24Z</t>
+          <t>2026-08-21T20:49:33Z</t>
         </is>
       </c>
     </row>
@@ -3626,7 +3626,7 @@
       </c>
       <c r="S41" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21T16:34:24Z</t>
+          <t>2026-08-21T20:49:33Z</t>
         </is>
       </c>
     </row>
@@ -3711,7 +3711,7 @@
       </c>
       <c r="S42" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21T16:34:24Z</t>
+          <t>2026-08-21T20:49:33Z</t>
         </is>
       </c>
     </row>
@@ -3796,7 +3796,7 @@
       </c>
       <c r="S43" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21T16:34:24Z</t>
+          <t>2026-08-21T20:49:33Z</t>
         </is>
       </c>
     </row>
@@ -3881,7 +3881,7 @@
       </c>
       <c r="S44" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21T16:34:24Z</t>
+          <t>2026-08-21T20:49:33Z</t>
         </is>
       </c>
     </row>
@@ -3966,7 +3966,7 @@
       </c>
       <c r="S45" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21T16:34:24Z</t>
+          <t>2026-08-21T20:49:33Z</t>
         </is>
       </c>
     </row>
@@ -4051,7 +4051,7 @@
       </c>
       <c r="S46" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21T16:34:24Z</t>
+          <t>2026-08-21T20:49:33Z</t>
         </is>
       </c>
     </row>
@@ -4136,7 +4136,7 @@
       </c>
       <c r="S47" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21T16:34:24Z</t>
+          <t>2026-08-21T20:49:33Z</t>
         </is>
       </c>
     </row>
@@ -4221,7 +4221,7 @@
       </c>
       <c r="S48" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21T16:34:24Z</t>
+          <t>2026-08-21T20:49:33Z</t>
         </is>
       </c>
     </row>
@@ -4306,7 +4306,7 @@
       </c>
       <c r="S49" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21T16:34:24Z</t>
+          <t>2026-08-21T20:49:33Z</t>
         </is>
       </c>
     </row>
@@ -4391,7 +4391,7 @@
       </c>
       <c r="S50" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21T16:34:24Z</t>
+          <t>2026-08-21T20:49:33Z</t>
         </is>
       </c>
     </row>
@@ -4476,7 +4476,7 @@
       </c>
       <c r="S51" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21T16:34:24Z</t>
+          <t>2026-08-21T20:49:33Z</t>
         </is>
       </c>
     </row>
@@ -4561,7 +4561,7 @@
       </c>
       <c r="S52" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21T16:34:24Z</t>
+          <t>2026-08-21T20:49:33Z</t>
         </is>
       </c>
     </row>
@@ -4646,7 +4646,7 @@
       </c>
       <c r="S53" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21T16:34:24Z</t>
+          <t>2026-08-21T20:49:33Z</t>
         </is>
       </c>
     </row>
@@ -4731,7 +4731,7 @@
       </c>
       <c r="S54" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21T16:34:24Z</t>
+          <t>2026-08-21T20:49:33Z</t>
         </is>
       </c>
     </row>
@@ -4816,7 +4816,7 @@
       </c>
       <c r="S55" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21T16:34:24Z</t>
+          <t>2026-08-21T20:49:33Z</t>
         </is>
       </c>
     </row>
@@ -4901,7 +4901,7 @@
       </c>
       <c r="S56" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21T16:34:24Z</t>
+          <t>2026-08-21T20:49:33Z</t>
         </is>
       </c>
     </row>
@@ -4986,7 +4986,7 @@
       </c>
       <c r="S57" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21T16:34:24Z</t>
+          <t>2026-08-21T20:49:33Z</t>
         </is>
       </c>
     </row>
@@ -5071,7 +5071,7 @@
       </c>
       <c r="S58" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21T16:34:24Z</t>
+          <t>2026-08-21T20:49:33Z</t>
         </is>
       </c>
     </row>
@@ -5156,7 +5156,7 @@
       </c>
       <c r="S59" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21T16:34:24Z</t>
+          <t>2026-08-21T20:49:33Z</t>
         </is>
       </c>
     </row>
@@ -5241,7 +5241,7 @@
       </c>
       <c r="S60" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21T16:34:24Z</t>
+          <t>2026-08-21T20:49:33Z</t>
         </is>
       </c>
     </row>
@@ -5326,7 +5326,7 @@
       </c>
       <c r="S61" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21T16:34:24Z</t>
+          <t>2026-08-21T20:49:33Z</t>
         </is>
       </c>
     </row>
@@ -5411,7 +5411,7 @@
       </c>
       <c r="S62" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21T16:34:24Z</t>
+          <t>2026-08-21T20:49:33Z</t>
         </is>
       </c>
     </row>
@@ -5496,7 +5496,7 @@
       </c>
       <c r="S63" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21T16:34:24Z</t>
+          <t>2026-08-21T20:49:33Z</t>
         </is>
       </c>
     </row>
@@ -5581,7 +5581,7 @@
       </c>
       <c r="S64" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21T16:34:24Z</t>
+          <t>2026-08-21T20:49:33Z</t>
         </is>
       </c>
     </row>
@@ -5666,7 +5666,7 @@
       </c>
       <c r="S65" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21T16:34:24Z</t>
+          <t>2026-08-21T20:49:33Z</t>
         </is>
       </c>
     </row>
@@ -5751,7 +5751,7 @@
       </c>
       <c r="S66" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21T16:34:24Z</t>
+          <t>2026-08-21T20:49:33Z</t>
         </is>
       </c>
     </row>
@@ -5836,7 +5836,7 @@
       </c>
       <c r="S67" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21T16:34:24Z</t>
+          <t>2026-08-21T20:49:33Z</t>
         </is>
       </c>
     </row>
@@ -5921,7 +5921,7 @@
       </c>
       <c r="S68" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21T16:34:24Z</t>
+          <t>2026-08-21T20:49:33Z</t>
         </is>
       </c>
     </row>
@@ -6006,7 +6006,7 @@
       </c>
       <c r="S69" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21T16:34:24Z</t>
+          <t>2026-08-21T20:49:33Z</t>
         </is>
       </c>
     </row>
@@ -6091,7 +6091,7 @@
       </c>
       <c r="S70" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21T16:34:24Z</t>
+          <t>2026-08-21T20:49:33Z</t>
         </is>
       </c>
     </row>
@@ -6176,7 +6176,7 @@
       </c>
       <c r="S71" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21T16:34:24Z</t>
+          <t>2026-08-21T20:49:33Z</t>
         </is>
       </c>
     </row>
@@ -6261,7 +6261,7 @@
       </c>
       <c r="S72" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21T16:34:24Z</t>
+          <t>2026-08-21T20:49:33Z</t>
         </is>
       </c>
     </row>
@@ -6346,7 +6346,7 @@
       </c>
       <c r="S73" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21T16:34:24Z</t>
+          <t>2026-08-21T20:49:33Z</t>
         </is>
       </c>
     </row>
@@ -6431,7 +6431,7 @@
       </c>
       <c r="S74" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21T16:34:24Z</t>
+          <t>2026-08-21T20:49:33Z</t>
         </is>
       </c>
     </row>
@@ -6516,7 +6516,7 @@
       </c>
       <c r="S75" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21T16:34:24Z</t>
+          <t>2026-08-21T20:49:33Z</t>
         </is>
       </c>
     </row>
@@ -6601,7 +6601,7 @@
       </c>
       <c r="S76" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21T16:34:24Z</t>
+          <t>2026-08-21T20:49:33Z</t>
         </is>
       </c>
     </row>
@@ -6686,7 +6686,7 @@
       </c>
       <c r="S77" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21T16:34:24Z</t>
+          <t>2026-08-21T20:49:33Z</t>
         </is>
       </c>
     </row>
@@ -6771,7 +6771,7 @@
       </c>
       <c r="S78" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21T16:34:24Z</t>
+          <t>2026-08-21T20:49:33Z</t>
         </is>
       </c>
     </row>
@@ -6856,7 +6856,7 @@
       </c>
       <c r="S79" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21T16:34:24Z</t>
+          <t>2026-08-21T20:49:33Z</t>
         </is>
       </c>
     </row>
@@ -6941,7 +6941,7 @@
       </c>
       <c r="S80" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21T16:34:24Z</t>
+          <t>2026-08-21T20:49:33Z</t>
         </is>
       </c>
     </row>
@@ -7026,7 +7026,7 @@
       </c>
       <c r="S81" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21T16:34:24Z</t>
+          <t>2026-08-21T20:49:33Z</t>
         </is>
       </c>
     </row>
@@ -7111,7 +7111,7 @@
       </c>
       <c r="S82" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21T16:34:24Z</t>
+          <t>2026-08-21T20:49:33Z</t>
         </is>
       </c>
     </row>
@@ -7196,7 +7196,7 @@
       </c>
       <c r="S83" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21T16:34:24Z</t>
+          <t>2026-08-21T20:49:33Z</t>
         </is>
       </c>
     </row>
@@ -7281,7 +7281,7 @@
       </c>
       <c r="S84" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21T16:34:24Z</t>
+          <t>2026-08-21T20:49:33Z</t>
         </is>
       </c>
     </row>
@@ -7366,7 +7366,7 @@
       </c>
       <c r="S85" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21T16:34:24Z</t>
+          <t>2026-08-21T20:49:33Z</t>
         </is>
       </c>
     </row>
@@ -7451,7 +7451,7 @@
       </c>
       <c r="S86" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21T16:34:24Z</t>
+          <t>2026-08-21T20:49:33Z</t>
         </is>
       </c>
     </row>
@@ -7536,7 +7536,7 @@
       </c>
       <c r="S87" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21T16:34:24Z</t>
+          <t>2026-08-21T20:49:33Z</t>
         </is>
       </c>
     </row>
@@ -7621,7 +7621,7 @@
       </c>
       <c r="S88" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21T16:34:24Z</t>
+          <t>2026-08-21T20:49:33Z</t>
         </is>
       </c>
     </row>
@@ -7706,7 +7706,7 @@
       </c>
       <c r="S89" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21T16:34:24Z</t>
+          <t>2026-08-21T20:49:33Z</t>
         </is>
       </c>
     </row>
@@ -7791,7 +7791,7 @@
       </c>
       <c r="S90" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21T16:34:24Z</t>
+          <t>2026-08-21T20:49:33Z</t>
         </is>
       </c>
     </row>
@@ -7876,7 +7876,7 @@
       </c>
       <c r="S91" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21T16:34:24Z</t>
+          <t>2026-08-21T20:49:33Z</t>
         </is>
       </c>
     </row>
@@ -7961,7 +7961,7 @@
       </c>
       <c r="S92" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21T16:34:24Z</t>
+          <t>2026-08-21T20:49:33Z</t>
         </is>
       </c>
     </row>
@@ -8046,7 +8046,7 @@
       </c>
       <c r="S93" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21T16:34:24Z</t>
+          <t>2026-08-21T20:49:33Z</t>
         </is>
       </c>
     </row>
@@ -8131,7 +8131,7 @@
       </c>
       <c r="S94" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21T16:34:24Z</t>
+          <t>2026-08-21T20:49:33Z</t>
         </is>
       </c>
     </row>
@@ -8216,7 +8216,7 @@
       </c>
       <c r="S95" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21T16:34:24Z</t>
+          <t>2026-08-21T20:49:33Z</t>
         </is>
       </c>
     </row>
@@ -8301,7 +8301,7 @@
       </c>
       <c r="S96" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21T16:34:24Z</t>
+          <t>2026-08-21T20:49:33Z</t>
         </is>
       </c>
     </row>
@@ -8386,7 +8386,7 @@
       </c>
       <c r="S97" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21T16:34:24Z</t>
+          <t>2026-08-21T20:49:33Z</t>
         </is>
       </c>
     </row>
@@ -8471,7 +8471,7 @@
       </c>
       <c r="S98" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21T16:34:24Z</t>
+          <t>2026-08-21T20:49:33Z</t>
         </is>
       </c>
     </row>
@@ -8556,7 +8556,7 @@
       </c>
       <c r="S99" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21T16:34:24Z</t>
+          <t>2026-08-21T20:49:33Z</t>
         </is>
       </c>
     </row>
@@ -8641,7 +8641,7 @@
       </c>
       <c r="S100" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21T16:34:24Z</t>
+          <t>2026-08-21T20:49:33Z</t>
         </is>
       </c>
     </row>
@@ -8726,7 +8726,7 @@
       </c>
       <c r="S101" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21T16:34:24Z</t>
+          <t>2026-08-21T20:49:33Z</t>
         </is>
       </c>
     </row>
@@ -8811,7 +8811,7 @@
       </c>
       <c r="S102" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21T16:34:24Z</t>
+          <t>2026-08-21T20:49:33Z</t>
         </is>
       </c>
     </row>
@@ -8896,7 +8896,7 @@
       </c>
       <c r="S103" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21T16:34:24Z</t>
+          <t>2026-08-21T20:49:33Z</t>
         </is>
       </c>
     </row>
@@ -8981,7 +8981,7 @@
       </c>
       <c r="S104" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21T16:34:24Z</t>
+          <t>2026-08-21T20:49:33Z</t>
         </is>
       </c>
     </row>
@@ -9066,7 +9066,7 @@
       </c>
       <c r="S105" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21T16:34:24Z</t>
+          <t>2026-08-21T20:49:33Z</t>
         </is>
       </c>
     </row>
@@ -9151,7 +9151,7 @@
       </c>
       <c r="S106" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21T16:34:24Z</t>
+          <t>2026-08-21T20:49:33Z</t>
         </is>
       </c>
     </row>
@@ -9236,7 +9236,7 @@
       </c>
       <c r="S107" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21T16:34:24Z</t>
+          <t>2026-08-21T20:49:33Z</t>
         </is>
       </c>
     </row>
@@ -9321,7 +9321,7 @@
       </c>
       <c r="S108" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21T16:34:24Z</t>
+          <t>2026-08-21T20:49:33Z</t>
         </is>
       </c>
     </row>
@@ -9406,7 +9406,7 @@
       </c>
       <c r="S109" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21T16:34:24Z</t>
+          <t>2026-08-21T20:49:33Z</t>
         </is>
       </c>
     </row>
@@ -9491,7 +9491,7 @@
       </c>
       <c r="S110" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21T16:34:24Z</t>
+          <t>2026-08-21T20:49:33Z</t>
         </is>
       </c>
     </row>
@@ -9576,7 +9576,7 @@
       </c>
       <c r="S111" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21T16:34:24Z</t>
+          <t>2026-08-21T20:49:33Z</t>
         </is>
       </c>
     </row>
@@ -9661,7 +9661,7 @@
       </c>
       <c r="S112" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21T16:34:24Z</t>
+          <t>2026-08-21T20:49:33Z</t>
         </is>
       </c>
     </row>
@@ -9746,7 +9746,7 @@
       </c>
       <c r="S113" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21T16:34:24Z</t>
+          <t>2026-08-21T20:49:33Z</t>
         </is>
       </c>
     </row>
@@ -9831,7 +9831,7 @@
       </c>
       <c r="S114" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21T16:34:24Z</t>
+          <t>2026-08-21T20:49:33Z</t>
         </is>
       </c>
     </row>
@@ -9916,7 +9916,7 @@
       </c>
       <c r="S115" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21T16:34:24Z</t>
+          <t>2026-08-21T20:49:33Z</t>
         </is>
       </c>
     </row>
@@ -10001,7 +10001,7 @@
       </c>
       <c r="S116" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21T16:34:24Z</t>
+          <t>2026-08-21T20:49:33Z</t>
         </is>
       </c>
     </row>
@@ -10086,7 +10086,7 @@
       </c>
       <c r="S117" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21T16:34:24Z</t>
+          <t>2026-08-21T20:49:33Z</t>
         </is>
       </c>
     </row>
@@ -10171,7 +10171,7 @@
       </c>
       <c r="S118" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21T16:34:24Z</t>
+          <t>2026-08-21T20:49:33Z</t>
         </is>
       </c>
     </row>
@@ -10256,7 +10256,7 @@
       </c>
       <c r="S119" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21T16:34:24Z</t>
+          <t>2026-08-21T20:49:33Z</t>
         </is>
       </c>
     </row>
@@ -10341,7 +10341,7 @@
       </c>
       <c r="S120" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21T16:34:24Z</t>
+          <t>2026-08-21T20:49:33Z</t>
         </is>
       </c>
     </row>
@@ -10426,7 +10426,7 @@
       </c>
       <c r="S121" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21T16:34:24Z</t>
+          <t>2026-08-21T20:49:33Z</t>
         </is>
       </c>
     </row>
@@ -10511,7 +10511,7 @@
       </c>
       <c r="S122" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21T16:34:24Z</t>
+          <t>2026-08-21T20:49:33Z</t>
         </is>
       </c>
     </row>
@@ -10596,7 +10596,7 @@
       </c>
       <c r="S123" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21T16:34:24Z</t>
+          <t>2026-08-21T20:49:33Z</t>
         </is>
       </c>
     </row>
@@ -10681,7 +10681,7 @@
       </c>
       <c r="S124" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21T16:34:24Z</t>
+          <t>2026-08-21T20:49:33Z</t>
         </is>
       </c>
     </row>
@@ -10766,7 +10766,7 @@
       </c>
       <c r="S125" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21T16:34:24Z</t>
+          <t>2026-08-21T20:49:33Z</t>
         </is>
       </c>
     </row>
@@ -10851,7 +10851,7 @@
       </c>
       <c r="S126" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21T16:34:24Z</t>
+          <t>2026-08-21T20:49:33Z</t>
         </is>
       </c>
     </row>
@@ -10936,7 +10936,7 @@
       </c>
       <c r="S127" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21T16:34:24Z</t>
+          <t>2026-08-21T20:49:33Z</t>
         </is>
       </c>
     </row>
@@ -11021,7 +11021,7 @@
       </c>
       <c r="S128" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21T16:34:24Z</t>
+          <t>2026-08-21T20:49:33Z</t>
         </is>
       </c>
     </row>
@@ -11106,7 +11106,7 @@
       </c>
       <c r="S129" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21T16:34:24Z</t>
+          <t>2026-08-21T20:49:33Z</t>
         </is>
       </c>
     </row>
@@ -11191,7 +11191,7 @@
       </c>
       <c r="S130" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21T16:34:24Z</t>
+          <t>2026-08-21T20:49:33Z</t>
         </is>
       </c>
     </row>
@@ -11276,7 +11276,7 @@
       </c>
       <c r="S131" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21T16:34:24Z</t>
+          <t>2026-08-21T20:49:33Z</t>
         </is>
       </c>
     </row>
@@ -11361,7 +11361,7 @@
       </c>
       <c r="S132" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21T16:34:24Z</t>
+          <t>2026-08-21T20:49:33Z</t>
         </is>
       </c>
     </row>
@@ -11446,7 +11446,7 @@
       </c>
       <c r="S133" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21T16:34:24Z</t>
+          <t>2026-08-21T20:49:33Z</t>
         </is>
       </c>
     </row>
@@ -11531,7 +11531,7 @@
       </c>
       <c r="S134" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21T16:34:24Z</t>
+          <t>2026-08-21T20:49:33Z</t>
         </is>
       </c>
     </row>
@@ -11616,7 +11616,7 @@
       </c>
       <c r="S135" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21T16:34:24Z</t>
+          <t>2026-08-21T20:49:33Z</t>
         </is>
       </c>
     </row>
@@ -11701,7 +11701,7 @@
       </c>
       <c r="S136" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21T16:34:24Z</t>
+          <t>2026-08-21T20:49:33Z</t>
         </is>
       </c>
     </row>
@@ -11786,7 +11786,7 @@
       </c>
       <c r="S137" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21T16:34:24Z</t>
+          <t>2026-08-21T20:49:33Z</t>
         </is>
       </c>
     </row>
@@ -11871,7 +11871,7 @@
       </c>
       <c r="S138" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21T16:34:24Z</t>
+          <t>2026-08-21T20:49:33Z</t>
         </is>
       </c>
     </row>
@@ -11956,7 +11956,7 @@
       </c>
       <c r="S139" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21T16:34:24Z</t>
+          <t>2026-08-21T20:49:33Z</t>
         </is>
       </c>
     </row>
@@ -12041,7 +12041,7 @@
       </c>
       <c r="S140" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21T16:34:24Z</t>
+          <t>2026-08-21T20:49:33Z</t>
         </is>
       </c>
     </row>
@@ -12126,7 +12126,7 @@
       </c>
       <c r="S141" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21T16:34:24Z</t>
+          <t>2026-08-21T20:49:33Z</t>
         </is>
       </c>
     </row>
@@ -12258,7 +12258,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21T16:34:24Z</t>
+          <t>2026-08-21T20:49:33Z</t>
         </is>
       </c>
     </row>
@@ -12338,7 +12338,7 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>{"dataset_id": "bcv_pib_historico_anual", "title": "Producto interno bruto histórico anual", "table": "PIB histórico anual", "source_file": "7_1_14_anual.xls", "base": "1957/1968/1984/1997", "price_type": "Precios constantes", "measure": "Nivel", "frequency": "Anual", "period": "2017", "year": 2017, "quarter": null, "classification": "Total economía", "component": "Producto interno bruto", "value": 392393.12, "unit": "Millones de bolívares a precios constantes", "status": "", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/7_1_14_anual.xls", "fetched_at": "2026-08-21T16:34:24Z"}</t>
+          <t>{"dataset_id": "bcv_pib_historico_anual", "title": "Producto interno bruto histórico anual", "table": "PIB histórico anual", "source_file": "7_1_14_anual.xls", "base": "1957/1968/1984/1997", "price_type": "Precios constantes", "measure": "Nivel", "frequency": "Anual", "period": "2017", "year": 2017, "quarter": null, "classification": "Total economía", "component": "Producto interno bruto", "value": 392393.12, "unit": "Millones de bolívares a precios constantes", "status": "", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/7_1_14_anual.xls", "fetched_at": "2026-08-21T20:49:33Z"}</t>
         </is>
       </c>
     </row>

--- a/assets/data/bcv/excel/ove_bcv_pib_historico_anual.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_pib_historico_anual.xlsx
@@ -736,7 +736,7 @@
       </c>
       <c r="S7" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21T20:49:33Z</t>
+          <t>2026-08-22T13:43:43Z</t>
         </is>
       </c>
     </row>
@@ -821,7 +821,7 @@
       </c>
       <c r="S8" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21T20:49:33Z</t>
+          <t>2026-08-22T13:43:43Z</t>
         </is>
       </c>
     </row>
@@ -906,7 +906,7 @@
       </c>
       <c r="S9" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21T20:49:33Z</t>
+          <t>2026-08-22T13:43:43Z</t>
         </is>
       </c>
     </row>
@@ -991,7 +991,7 @@
       </c>
       <c r="S10" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21T20:49:33Z</t>
+          <t>2026-08-22T13:43:43Z</t>
         </is>
       </c>
     </row>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="S11" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21T20:49:33Z</t>
+          <t>2026-08-22T13:43:43Z</t>
         </is>
       </c>
     </row>
@@ -1161,7 +1161,7 @@
       </c>
       <c r="S12" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21T20:49:33Z</t>
+          <t>2026-08-22T13:43:43Z</t>
         </is>
       </c>
     </row>
@@ -1246,7 +1246,7 @@
       </c>
       <c r="S13" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21T20:49:33Z</t>
+          <t>2026-08-22T13:43:43Z</t>
         </is>
       </c>
     </row>
@@ -1331,7 +1331,7 @@
       </c>
       <c r="S14" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21T20:49:33Z</t>
+          <t>2026-08-22T13:43:43Z</t>
         </is>
       </c>
     </row>
@@ -1416,7 +1416,7 @@
       </c>
       <c r="S15" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21T20:49:33Z</t>
+          <t>2026-08-22T13:43:43Z</t>
         </is>
       </c>
     </row>
@@ -1501,7 +1501,7 @@
       </c>
       <c r="S16" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21T20:49:33Z</t>
+          <t>2026-08-22T13:43:43Z</t>
         </is>
       </c>
     </row>
@@ -1586,7 +1586,7 @@
       </c>
       <c r="S17" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21T20:49:33Z</t>
+          <t>2026-08-22T13:43:43Z</t>
         </is>
       </c>
     </row>
@@ -1671,7 +1671,7 @@
       </c>
       <c r="S18" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21T20:49:33Z</t>
+          <t>2026-08-22T13:43:43Z</t>
         </is>
       </c>
     </row>
@@ -1756,7 +1756,7 @@
       </c>
       <c r="S19" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21T20:49:33Z</t>
+          <t>2026-08-22T13:43:43Z</t>
         </is>
       </c>
     </row>
@@ -1841,7 +1841,7 @@
       </c>
       <c r="S20" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21T20:49:33Z</t>
+          <t>2026-08-22T13:43:43Z</t>
         </is>
       </c>
     </row>
@@ -1926,7 +1926,7 @@
       </c>
       <c r="S21" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21T20:49:33Z</t>
+          <t>2026-08-22T13:43:43Z</t>
         </is>
       </c>
     </row>
@@ -2011,7 +2011,7 @@
       </c>
       <c r="S22" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21T20:49:33Z</t>
+          <t>2026-08-22T13:43:43Z</t>
         </is>
       </c>
     </row>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="S23" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21T20:49:33Z</t>
+          <t>2026-08-22T13:43:43Z</t>
         </is>
       </c>
     </row>
@@ -2181,7 +2181,7 @@
       </c>
       <c r="S24" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21T20:49:33Z</t>
+          <t>2026-08-22T13:43:43Z</t>
         </is>
       </c>
     </row>
@@ -2266,7 +2266,7 @@
       </c>
       <c r="S25" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21T20:49:33Z</t>
+          <t>2026-08-22T13:43:43Z</t>
         </is>
       </c>
     </row>
@@ -2351,7 +2351,7 @@
       </c>
       <c r="S26" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21T20:49:33Z</t>
+          <t>2026-08-22T13:43:43Z</t>
         </is>
       </c>
     </row>
@@ -2436,7 +2436,7 @@
       </c>
       <c r="S27" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21T20:49:33Z</t>
+          <t>2026-08-22T13:43:43Z</t>
         </is>
       </c>
     </row>
@@ -2521,7 +2521,7 @@
       </c>
       <c r="S28" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21T20:49:33Z</t>
+          <t>2026-08-22T13:43:43Z</t>
         </is>
       </c>
     </row>
@@ -2606,7 +2606,7 @@
       </c>
       <c r="S29" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21T20:49:33Z</t>
+          <t>2026-08-22T13:43:43Z</t>
         </is>
       </c>
     </row>
@@ -2691,7 +2691,7 @@
       </c>
       <c r="S30" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21T20:49:33Z</t>
+          <t>2026-08-22T13:43:43Z</t>
         </is>
       </c>
     </row>
@@ -2776,7 +2776,7 @@
       </c>
       <c r="S31" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21T20:49:33Z</t>
+          <t>2026-08-22T13:43:43Z</t>
         </is>
       </c>
     </row>
@@ -2861,7 +2861,7 @@
       </c>
       <c r="S32" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21T20:49:33Z</t>
+          <t>2026-08-22T13:43:43Z</t>
         </is>
       </c>
     </row>
@@ -2946,7 +2946,7 @@
       </c>
       <c r="S33" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21T20:49:33Z</t>
+          <t>2026-08-22T13:43:43Z</t>
         </is>
       </c>
     </row>
@@ -3031,7 +3031,7 @@
       </c>
       <c r="S34" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21T20:49:33Z</t>
+          <t>2026-08-22T13:43:43Z</t>
         </is>
       </c>
     </row>
@@ -3116,7 +3116,7 @@
       </c>
       <c r="S35" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21T20:49:33Z</t>
+          <t>2026-08-22T13:43:43Z</t>
         </is>
       </c>
     </row>
@@ -3201,7 +3201,7 @@
       </c>
       <c r="S36" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21T20:49:33Z</t>
+          <t>2026-08-22T13:43:43Z</t>
         </is>
       </c>
     </row>
@@ -3286,7 +3286,7 @@
       </c>
       <c r="S37" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21T20:49:33Z</t>
+          <t>2026-08-22T13:43:43Z</t>
         </is>
       </c>
     </row>
@@ -3371,7 +3371,7 @@
       </c>
       <c r="S38" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21T20:49:33Z</t>
+          <t>2026-08-22T13:43:43Z</t>
         </is>
       </c>
     </row>
@@ -3456,7 +3456,7 @@
       </c>
       <c r="S39" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21T20:49:33Z</t>
+          <t>2026-08-22T13:43:43Z</t>
         </is>
       </c>
     </row>
@@ -3541,7 +3541,7 @@
       </c>
       <c r="S40" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21T20:49:33Z</t>
+          <t>2026-08-22T13:43:43Z</t>
         </is>
       </c>
     </row>
@@ -3626,7 +3626,7 @@
       </c>
       <c r="S41" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21T20:49:33Z</t>
+          <t>2026-08-22T13:43:43Z</t>
         </is>
       </c>
     </row>
@@ -3711,7 +3711,7 @@
       </c>
       <c r="S42" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21T20:49:33Z</t>
+          <t>2026-08-22T13:43:43Z</t>
         </is>
       </c>
     </row>
@@ -3796,7 +3796,7 @@
       </c>
       <c r="S43" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21T20:49:33Z</t>
+          <t>2026-08-22T13:43:43Z</t>
         </is>
       </c>
     </row>
@@ -3881,7 +3881,7 @@
       </c>
       <c r="S44" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21T20:49:33Z</t>
+          <t>2026-08-22T13:43:43Z</t>
         </is>
       </c>
     </row>
@@ -3966,7 +3966,7 @@
       </c>
       <c r="S45" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21T20:49:33Z</t>
+          <t>2026-08-22T13:43:43Z</t>
         </is>
       </c>
     </row>
@@ -4051,7 +4051,7 @@
       </c>
       <c r="S46" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21T20:49:33Z</t>
+          <t>2026-08-22T13:43:43Z</t>
         </is>
       </c>
     </row>
@@ -4136,7 +4136,7 @@
       </c>
       <c r="S47" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21T20:49:33Z</t>
+          <t>2026-08-22T13:43:43Z</t>
         </is>
       </c>
     </row>
@@ -4221,7 +4221,7 @@
       </c>
       <c r="S48" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21T20:49:33Z</t>
+          <t>2026-08-22T13:43:43Z</t>
         </is>
       </c>
     </row>
@@ -4306,7 +4306,7 @@
       </c>
       <c r="S49" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21T20:49:33Z</t>
+          <t>2026-08-22T13:43:43Z</t>
         </is>
       </c>
     </row>
@@ -4391,7 +4391,7 @@
       </c>
       <c r="S50" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21T20:49:33Z</t>
+          <t>2026-08-22T13:43:43Z</t>
         </is>
       </c>
     </row>
@@ -4476,7 +4476,7 @@
       </c>
       <c r="S51" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21T20:49:33Z</t>
+          <t>2026-08-22T13:43:43Z</t>
         </is>
       </c>
     </row>
@@ -4561,7 +4561,7 @@
       </c>
       <c r="S52" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21T20:49:33Z</t>
+          <t>2026-08-22T13:43:43Z</t>
         </is>
       </c>
     </row>
@@ -4646,7 +4646,7 @@
       </c>
       <c r="S53" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21T20:49:33Z</t>
+          <t>2026-08-22T13:43:43Z</t>
         </is>
       </c>
     </row>
@@ -4731,7 +4731,7 @@
       </c>
       <c r="S54" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21T20:49:33Z</t>
+          <t>2026-08-22T13:43:43Z</t>
         </is>
       </c>
     </row>
@@ -4816,7 +4816,7 @@
       </c>
       <c r="S55" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21T20:49:33Z</t>
+          <t>2026-08-22T13:43:43Z</t>
         </is>
       </c>
     </row>
@@ -4901,7 +4901,7 @@
       </c>
       <c r="S56" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21T20:49:33Z</t>
+          <t>2026-08-22T13:43:43Z</t>
         </is>
       </c>
     </row>
@@ -4986,7 +4986,7 @@
       </c>
       <c r="S57" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21T20:49:33Z</t>
+          <t>2026-08-22T13:43:43Z</t>
         </is>
       </c>
     </row>
@@ -5071,7 +5071,7 @@
       </c>
       <c r="S58" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21T20:49:33Z</t>
+          <t>2026-08-22T13:43:43Z</t>
         </is>
       </c>
     </row>
@@ -5156,7 +5156,7 @@
       </c>
       <c r="S59" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21T20:49:33Z</t>
+          <t>2026-08-22T13:43:43Z</t>
         </is>
       </c>
     </row>
@@ -5241,7 +5241,7 @@
       </c>
       <c r="S60" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21T20:49:33Z</t>
+          <t>2026-08-22T13:43:43Z</t>
         </is>
       </c>
     </row>
@@ -5326,7 +5326,7 @@
       </c>
       <c r="S61" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21T20:49:33Z</t>
+          <t>2026-08-22T13:43:43Z</t>
         </is>
       </c>
     </row>
@@ -5411,7 +5411,7 @@
       </c>
       <c r="S62" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21T20:49:33Z</t>
+          <t>2026-08-22T13:43:43Z</t>
         </is>
       </c>
     </row>
@@ -5496,7 +5496,7 @@
       </c>
       <c r="S63" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21T20:49:33Z</t>
+          <t>2026-08-22T13:43:43Z</t>
         </is>
       </c>
     </row>
@@ -5581,7 +5581,7 @@
       </c>
       <c r="S64" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21T20:49:33Z</t>
+          <t>2026-08-22T13:43:43Z</t>
         </is>
       </c>
     </row>
@@ -5666,7 +5666,7 @@
       </c>
       <c r="S65" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21T20:49:33Z</t>
+          <t>2026-08-22T13:43:43Z</t>
         </is>
       </c>
     </row>
@@ -5751,7 +5751,7 @@
       </c>
       <c r="S66" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21T20:49:33Z</t>
+          <t>2026-08-22T13:43:43Z</t>
         </is>
       </c>
     </row>
@@ -5836,7 +5836,7 @@
       </c>
       <c r="S67" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21T20:49:33Z</t>
+          <t>2026-08-22T13:43:43Z</t>
         </is>
       </c>
     </row>
@@ -5921,7 +5921,7 @@
       </c>
       <c r="S68" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21T20:49:33Z</t>
+          <t>2026-08-22T13:43:43Z</t>
         </is>
       </c>
     </row>
@@ -6006,7 +6006,7 @@
       </c>
       <c r="S69" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21T20:49:33Z</t>
+          <t>2026-08-22T13:43:43Z</t>
         </is>
       </c>
     </row>
@@ -6091,7 +6091,7 @@
       </c>
       <c r="S70" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21T20:49:33Z</t>
+          <t>2026-08-22T13:43:43Z</t>
         </is>
       </c>
     </row>
@@ -6176,7 +6176,7 @@
       </c>
       <c r="S71" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21T20:49:33Z</t>
+          <t>2026-08-22T13:43:43Z</t>
         </is>
       </c>
     </row>
@@ -6261,7 +6261,7 @@
       </c>
       <c r="S72" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21T20:49:33Z</t>
+          <t>2026-08-22T13:43:43Z</t>
         </is>
       </c>
     </row>
@@ -6346,7 +6346,7 @@
       </c>
       <c r="S73" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21T20:49:33Z</t>
+          <t>2026-08-22T13:43:43Z</t>
         </is>
       </c>
     </row>
@@ -6431,7 +6431,7 @@
       </c>
       <c r="S74" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21T20:49:33Z</t>
+          <t>2026-08-22T13:43:43Z</t>
         </is>
       </c>
     </row>
@@ -6516,7 +6516,7 @@
       </c>
       <c r="S75" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21T20:49:33Z</t>
+          <t>2026-08-22T13:43:43Z</t>
         </is>
       </c>
     </row>
@@ -6601,7 +6601,7 @@
       </c>
       <c r="S76" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21T20:49:33Z</t>
+          <t>2026-08-22T13:43:43Z</t>
         </is>
       </c>
     </row>
@@ -6686,7 +6686,7 @@
       </c>
       <c r="S77" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21T20:49:33Z</t>
+          <t>2026-08-22T13:43:43Z</t>
         </is>
       </c>
     </row>
@@ -6771,7 +6771,7 @@
       </c>
       <c r="S78" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21T20:49:33Z</t>
+          <t>2026-08-22T13:43:43Z</t>
         </is>
       </c>
     </row>
@@ -6856,7 +6856,7 @@
       </c>
       <c r="S79" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21T20:49:33Z</t>
+          <t>2026-08-22T13:43:43Z</t>
         </is>
       </c>
     </row>
@@ -6941,7 +6941,7 @@
       </c>
       <c r="S80" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21T20:49:33Z</t>
+          <t>2026-08-22T13:43:43Z</t>
         </is>
       </c>
     </row>
@@ -7026,7 +7026,7 @@
       </c>
       <c r="S81" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21T20:49:33Z</t>
+          <t>2026-08-22T13:43:43Z</t>
         </is>
       </c>
     </row>
@@ -7111,7 +7111,7 @@
       </c>
       <c r="S82" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21T20:49:33Z</t>
+          <t>2026-08-22T13:43:43Z</t>
         </is>
       </c>
     </row>
@@ -7196,7 +7196,7 @@
       </c>
       <c r="S83" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21T20:49:33Z</t>
+          <t>2026-08-22T13:43:43Z</t>
         </is>
       </c>
     </row>
@@ -7281,7 +7281,7 @@
       </c>
       <c r="S84" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21T20:49:33Z</t>
+          <t>2026-08-22T13:43:43Z</t>
         </is>
       </c>
     </row>
@@ -7366,7 +7366,7 @@
       </c>
       <c r="S85" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21T20:49:33Z</t>
+          <t>2026-08-22T13:43:43Z</t>
         </is>
       </c>
     </row>
@@ -7451,7 +7451,7 @@
       </c>
       <c r="S86" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21T20:49:33Z</t>
+          <t>2026-08-22T13:43:43Z</t>
         </is>
       </c>
     </row>
@@ -7536,7 +7536,7 @@
       </c>
       <c r="S87" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21T20:49:33Z</t>
+          <t>2026-08-22T13:43:43Z</t>
         </is>
       </c>
     </row>
@@ -7621,7 +7621,7 @@
       </c>
       <c r="S88" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21T20:49:33Z</t>
+          <t>2026-08-22T13:43:43Z</t>
         </is>
       </c>
     </row>
@@ -7706,7 +7706,7 @@
       </c>
       <c r="S89" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21T20:49:33Z</t>
+          <t>2026-08-22T13:43:43Z</t>
         </is>
       </c>
     </row>
@@ -7791,7 +7791,7 @@
       </c>
       <c r="S90" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21T20:49:33Z</t>
+          <t>2026-08-22T13:43:43Z</t>
         </is>
       </c>
     </row>
@@ -7876,7 +7876,7 @@
       </c>
       <c r="S91" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21T20:49:33Z</t>
+          <t>2026-08-22T13:43:43Z</t>
         </is>
       </c>
     </row>
@@ -7961,7 +7961,7 @@
       </c>
       <c r="S92" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21T20:49:33Z</t>
+          <t>2026-08-22T13:43:43Z</t>
         </is>
       </c>
     </row>
@@ -8046,7 +8046,7 @@
       </c>
       <c r="S93" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21T20:49:33Z</t>
+          <t>2026-08-22T13:43:43Z</t>
         </is>
       </c>
     </row>
@@ -8131,7 +8131,7 @@
       </c>
       <c r="S94" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21T20:49:33Z</t>
+          <t>2026-08-22T13:43:43Z</t>
         </is>
       </c>
     </row>
@@ -8216,7 +8216,7 @@
       </c>
       <c r="S95" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21T20:49:33Z</t>
+          <t>2026-08-22T13:43:43Z</t>
         </is>
       </c>
     </row>
@@ -8301,7 +8301,7 @@
       </c>
       <c r="S96" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21T20:49:33Z</t>
+          <t>2026-08-22T13:43:43Z</t>
         </is>
       </c>
     </row>
@@ -8386,7 +8386,7 @@
       </c>
       <c r="S97" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21T20:49:33Z</t>
+          <t>2026-08-22T13:43:43Z</t>
         </is>
       </c>
     </row>
@@ -8471,7 +8471,7 @@
       </c>
       <c r="S98" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21T20:49:33Z</t>
+          <t>2026-08-22T13:43:43Z</t>
         </is>
       </c>
     </row>
@@ -8556,7 +8556,7 @@
       </c>
       <c r="S99" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21T20:49:33Z</t>
+          <t>2026-08-22T13:43:43Z</t>
         </is>
       </c>
     </row>
@@ -8641,7 +8641,7 @@
       </c>
       <c r="S100" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21T20:49:33Z</t>
+          <t>2026-08-22T13:43:43Z</t>
         </is>
       </c>
     </row>
@@ -8726,7 +8726,7 @@
       </c>
       <c r="S101" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21T20:49:33Z</t>
+          <t>2026-08-22T13:43:43Z</t>
         </is>
       </c>
     </row>
@@ -8811,7 +8811,7 @@
       </c>
       <c r="S102" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21T20:49:33Z</t>
+          <t>2026-08-22T13:43:43Z</t>
         </is>
       </c>
     </row>
@@ -8896,7 +8896,7 @@
       </c>
       <c r="S103" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21T20:49:33Z</t>
+          <t>2026-08-22T13:43:43Z</t>
         </is>
       </c>
     </row>
@@ -8981,7 +8981,7 @@
       </c>
       <c r="S104" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21T20:49:33Z</t>
+          <t>2026-08-22T13:43:43Z</t>
         </is>
       </c>
     </row>
@@ -9066,7 +9066,7 @@
       </c>
       <c r="S105" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21T20:49:33Z</t>
+          <t>2026-08-22T13:43:43Z</t>
         </is>
       </c>
     </row>
@@ -9151,7 +9151,7 @@
       </c>
       <c r="S106" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21T20:49:33Z</t>
+          <t>2026-08-22T13:43:43Z</t>
         </is>
       </c>
     </row>
@@ -9236,7 +9236,7 @@
       </c>
       <c r="S107" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21T20:49:33Z</t>
+          <t>2026-08-22T13:43:43Z</t>
         </is>
       </c>
     </row>
@@ -9321,7 +9321,7 @@
       </c>
       <c r="S108" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21T20:49:33Z</t>
+          <t>2026-08-22T13:43:43Z</t>
         </is>
       </c>
     </row>
@@ -9406,7 +9406,7 @@
       </c>
       <c r="S109" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21T20:49:33Z</t>
+          <t>2026-08-22T13:43:43Z</t>
         </is>
       </c>
     </row>
@@ -9491,7 +9491,7 @@
       </c>
       <c r="S110" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21T20:49:33Z</t>
+          <t>2026-08-22T13:43:43Z</t>
         </is>
       </c>
     </row>
@@ -9576,7 +9576,7 @@
       </c>
       <c r="S111" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21T20:49:33Z</t>
+          <t>2026-08-22T13:43:43Z</t>
         </is>
       </c>
     </row>
@@ -9661,7 +9661,7 @@
       </c>
       <c r="S112" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21T20:49:33Z</t>
+          <t>2026-08-22T13:43:43Z</t>
         </is>
       </c>
     </row>
@@ -9746,7 +9746,7 @@
       </c>
       <c r="S113" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21T20:49:33Z</t>
+          <t>2026-08-22T13:43:43Z</t>
         </is>
       </c>
     </row>
@@ -9831,7 +9831,7 @@
       </c>
       <c r="S114" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21T20:49:33Z</t>
+          <t>2026-08-22T13:43:43Z</t>
         </is>
       </c>
     </row>
@@ -9916,7 +9916,7 @@
       </c>
       <c r="S115" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21T20:49:33Z</t>
+          <t>2026-08-22T13:43:43Z</t>
         </is>
       </c>
     </row>
@@ -10001,7 +10001,7 @@
       </c>
       <c r="S116" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21T20:49:33Z</t>
+          <t>2026-08-22T13:43:43Z</t>
         </is>
       </c>
     </row>
@@ -10086,7 +10086,7 @@
       </c>
       <c r="S117" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21T20:49:33Z</t>
+          <t>2026-08-22T13:43:43Z</t>
         </is>
       </c>
     </row>
@@ -10171,7 +10171,7 @@
       </c>
       <c r="S118" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21T20:49:33Z</t>
+          <t>2026-08-22T13:43:43Z</t>
         </is>
       </c>
     </row>
@@ -10256,7 +10256,7 @@
       </c>
       <c r="S119" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21T20:49:33Z</t>
+          <t>2026-08-22T13:43:43Z</t>
         </is>
       </c>
     </row>
@@ -10341,7 +10341,7 @@
       </c>
       <c r="S120" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21T20:49:33Z</t>
+          <t>2026-08-22T13:43:43Z</t>
         </is>
       </c>
     </row>
@@ -10426,7 +10426,7 @@
       </c>
       <c r="S121" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21T20:49:33Z</t>
+          <t>2026-08-22T13:43:43Z</t>
         </is>
       </c>
     </row>
@@ -10511,7 +10511,7 @@
       </c>
       <c r="S122" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21T20:49:33Z</t>
+          <t>2026-08-22T13:43:43Z</t>
         </is>
       </c>
     </row>
@@ -10596,7 +10596,7 @@
       </c>
       <c r="S123" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21T20:49:33Z</t>
+          <t>2026-08-22T13:43:43Z</t>
         </is>
       </c>
     </row>
@@ -10681,7 +10681,7 @@
       </c>
       <c r="S124" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21T20:49:33Z</t>
+          <t>2026-08-22T13:43:43Z</t>
         </is>
       </c>
     </row>
@@ -10766,7 +10766,7 @@
       </c>
       <c r="S125" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21T20:49:33Z</t>
+          <t>2026-08-22T13:43:43Z</t>
         </is>
       </c>
     </row>
@@ -10851,7 +10851,7 @@
       </c>
       <c r="S126" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21T20:49:33Z</t>
+          <t>2026-08-22T13:43:43Z</t>
         </is>
       </c>
     </row>
@@ -10936,7 +10936,7 @@
       </c>
       <c r="S127" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21T20:49:33Z</t>
+          <t>2026-08-22T13:43:43Z</t>
         </is>
       </c>
     </row>
@@ -11021,7 +11021,7 @@
       </c>
       <c r="S128" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21T20:49:33Z</t>
+          <t>2026-08-22T13:43:43Z</t>
         </is>
       </c>
     </row>
@@ -11106,7 +11106,7 @@
       </c>
       <c r="S129" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21T20:49:33Z</t>
+          <t>2026-08-22T13:43:43Z</t>
         </is>
       </c>
     </row>
@@ -11191,7 +11191,7 @@
       </c>
       <c r="S130" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21T20:49:33Z</t>
+          <t>2026-08-22T13:43:43Z</t>
         </is>
       </c>
     </row>
@@ -11276,7 +11276,7 @@
       </c>
       <c r="S131" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21T20:49:33Z</t>
+          <t>2026-08-22T13:43:43Z</t>
         </is>
       </c>
     </row>
@@ -11361,7 +11361,7 @@
       </c>
       <c r="S132" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21T20:49:33Z</t>
+          <t>2026-08-22T13:43:43Z</t>
         </is>
       </c>
     </row>
@@ -11446,7 +11446,7 @@
       </c>
       <c r="S133" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21T20:49:33Z</t>
+          <t>2026-08-22T13:43:43Z</t>
         </is>
       </c>
     </row>
@@ -11531,7 +11531,7 @@
       </c>
       <c r="S134" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21T20:49:33Z</t>
+          <t>2026-08-22T13:43:43Z</t>
         </is>
       </c>
     </row>
@@ -11616,7 +11616,7 @@
       </c>
       <c r="S135" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21T20:49:33Z</t>
+          <t>2026-08-22T13:43:43Z</t>
         </is>
       </c>
     </row>
@@ -11701,7 +11701,7 @@
       </c>
       <c r="S136" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21T20:49:33Z</t>
+          <t>2026-08-22T13:43:43Z</t>
         </is>
       </c>
     </row>
@@ -11786,7 +11786,7 @@
       </c>
       <c r="S137" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21T20:49:33Z</t>
+          <t>2026-08-22T13:43:43Z</t>
         </is>
       </c>
     </row>
@@ -11871,7 +11871,7 @@
       </c>
       <c r="S138" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21T20:49:33Z</t>
+          <t>2026-08-22T13:43:43Z</t>
         </is>
       </c>
     </row>
@@ -11956,7 +11956,7 @@
       </c>
       <c r="S139" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21T20:49:33Z</t>
+          <t>2026-08-22T13:43:43Z</t>
         </is>
       </c>
     </row>
@@ -12041,7 +12041,7 @@
       </c>
       <c r="S140" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21T20:49:33Z</t>
+          <t>2026-08-22T13:43:43Z</t>
         </is>
       </c>
     </row>
@@ -12126,7 +12126,7 @@
       </c>
       <c r="S141" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21T20:49:33Z</t>
+          <t>2026-08-22T13:43:43Z</t>
         </is>
       </c>
     </row>
@@ -12258,7 +12258,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21T20:49:33Z</t>
+          <t>2026-08-22T13:43:43Z</t>
         </is>
       </c>
     </row>
@@ -12338,7 +12338,7 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>{"dataset_id": "bcv_pib_historico_anual", "title": "Producto interno bruto histórico anual", "table": "PIB histórico anual", "source_file": "7_1_14_anual.xls", "base": "1957/1968/1984/1997", "price_type": "Precios constantes", "measure": "Nivel", "frequency": "Anual", "period": "2017", "year": 2017, "quarter": null, "classification": "Total economía", "component": "Producto interno bruto", "value": 392393.12, "unit": "Millones de bolívares a precios constantes", "status": "", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/7_1_14_anual.xls", "fetched_at": "2026-08-21T20:49:33Z"}</t>
+          <t>{"dataset_id": "bcv_pib_historico_anual", "title": "Producto interno bruto histórico anual", "table": "PIB histórico anual", "source_file": "7_1_14_anual.xls", "base": "1957/1968/1984/1997", "price_type": "Precios constantes", "measure": "Nivel", "frequency": "Anual", "period": "2017", "year": 2017, "quarter": null, "classification": "Total economía", "component": "Producto interno bruto", "value": 392393.12, "unit": "Millones de bolívares a precios constantes", "status": "", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/7_1_14_anual.xls", "fetched_at": "2026-08-22T13:43:43Z"}</t>
         </is>
       </c>
     </row>

--- a/assets/data/bcv/excel/ove_bcv_pib_historico_anual.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_pib_historico_anual.xlsx
@@ -736,7 +736,7 @@
       </c>
       <c r="S7" s="4" t="inlineStr">
         <is>
-          <t>2026-08-22T13:43:43Z</t>
+          <t>2026-08-22T20:47:45Z</t>
         </is>
       </c>
     </row>
@@ -821,7 +821,7 @@
       </c>
       <c r="S8" s="4" t="inlineStr">
         <is>
-          <t>2026-08-22T13:43:43Z</t>
+          <t>2026-08-22T20:47:45Z</t>
         </is>
       </c>
     </row>
@@ -906,7 +906,7 @@
       </c>
       <c r="S9" s="4" t="inlineStr">
         <is>
-          <t>2026-08-22T13:43:43Z</t>
+          <t>2026-08-22T20:47:45Z</t>
         </is>
       </c>
     </row>
@@ -991,7 +991,7 @@
       </c>
       <c r="S10" s="4" t="inlineStr">
         <is>
-          <t>2026-08-22T13:43:43Z</t>
+          <t>2026-08-22T20:47:45Z</t>
         </is>
       </c>
     </row>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="S11" s="4" t="inlineStr">
         <is>
-          <t>2026-08-22T13:43:43Z</t>
+          <t>2026-08-22T20:47:45Z</t>
         </is>
       </c>
     </row>
@@ -1161,7 +1161,7 @@
       </c>
       <c r="S12" s="4" t="inlineStr">
         <is>
-          <t>2026-08-22T13:43:43Z</t>
+          <t>2026-08-22T20:47:45Z</t>
         </is>
       </c>
     </row>
@@ -1246,7 +1246,7 @@
       </c>
       <c r="S13" s="4" t="inlineStr">
         <is>
-          <t>2026-08-22T13:43:43Z</t>
+          <t>2026-08-22T20:47:45Z</t>
         </is>
       </c>
     </row>
@@ -1331,7 +1331,7 @@
       </c>
       <c r="S14" s="4" t="inlineStr">
         <is>
-          <t>2026-08-22T13:43:43Z</t>
+          <t>2026-08-22T20:47:45Z</t>
         </is>
       </c>
     </row>
@@ -1416,7 +1416,7 @@
       </c>
       <c r="S15" s="4" t="inlineStr">
         <is>
-          <t>2026-08-22T13:43:43Z</t>
+          <t>2026-08-22T20:47:45Z</t>
         </is>
       </c>
     </row>
@@ -1501,7 +1501,7 @@
       </c>
       <c r="S16" s="4" t="inlineStr">
         <is>
-          <t>2026-08-22T13:43:43Z</t>
+          <t>2026-08-22T20:47:45Z</t>
         </is>
       </c>
     </row>
@@ -1586,7 +1586,7 @@
       </c>
       <c r="S17" s="4" t="inlineStr">
         <is>
-          <t>2026-08-22T13:43:43Z</t>
+          <t>2026-08-22T20:47:45Z</t>
         </is>
       </c>
     </row>
@@ -1671,7 +1671,7 @@
       </c>
       <c r="S18" s="4" t="inlineStr">
         <is>
-          <t>2026-08-22T13:43:43Z</t>
+          <t>2026-08-22T20:47:45Z</t>
         </is>
       </c>
     </row>
@@ -1756,7 +1756,7 @@
       </c>
       <c r="S19" s="4" t="inlineStr">
         <is>
-          <t>2026-08-22T13:43:43Z</t>
+          <t>2026-08-22T20:47:45Z</t>
         </is>
       </c>
     </row>
@@ -1841,7 +1841,7 @@
       </c>
       <c r="S20" s="4" t="inlineStr">
         <is>
-          <t>2026-08-22T13:43:43Z</t>
+          <t>2026-08-22T20:47:45Z</t>
         </is>
       </c>
     </row>
@@ -1926,7 +1926,7 @@
       </c>
       <c r="S21" s="4" t="inlineStr">
         <is>
-          <t>2026-08-22T13:43:43Z</t>
+          <t>2026-08-22T20:47:45Z</t>
         </is>
       </c>
     </row>
@@ -2011,7 +2011,7 @@
       </c>
       <c r="S22" s="4" t="inlineStr">
         <is>
-          <t>2026-08-22T13:43:43Z</t>
+          <t>2026-08-22T20:47:45Z</t>
         </is>
       </c>
     </row>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="S23" s="4" t="inlineStr">
         <is>
-          <t>2026-08-22T13:43:43Z</t>
+          <t>2026-08-22T20:47:45Z</t>
         </is>
       </c>
     </row>
@@ -2181,7 +2181,7 @@
       </c>
       <c r="S24" s="4" t="inlineStr">
         <is>
-          <t>2026-08-22T13:43:43Z</t>
+          <t>2026-08-22T20:47:45Z</t>
         </is>
       </c>
     </row>
@@ -2266,7 +2266,7 @@
       </c>
       <c r="S25" s="4" t="inlineStr">
         <is>
-          <t>2026-08-22T13:43:43Z</t>
+          <t>2026-08-22T20:47:45Z</t>
         </is>
       </c>
     </row>
@@ -2351,7 +2351,7 @@
       </c>
       <c r="S26" s="4" t="inlineStr">
         <is>
-          <t>2026-08-22T13:43:43Z</t>
+          <t>2026-08-22T20:47:45Z</t>
         </is>
       </c>
     </row>
@@ -2436,7 +2436,7 @@
       </c>
       <c r="S27" s="4" t="inlineStr">
         <is>
-          <t>2026-08-22T13:43:43Z</t>
+          <t>2026-08-22T20:47:45Z</t>
         </is>
       </c>
     </row>
@@ -2521,7 +2521,7 @@
       </c>
       <c r="S28" s="4" t="inlineStr">
         <is>
-          <t>2026-08-22T13:43:43Z</t>
+          <t>2026-08-22T20:47:45Z</t>
         </is>
       </c>
     </row>
@@ -2606,7 +2606,7 @@
       </c>
       <c r="S29" s="4" t="inlineStr">
         <is>
-          <t>2026-08-22T13:43:43Z</t>
+          <t>2026-08-22T20:47:45Z</t>
         </is>
       </c>
     </row>
@@ -2691,7 +2691,7 @@
       </c>
       <c r="S30" s="4" t="inlineStr">
         <is>
-          <t>2026-08-22T13:43:43Z</t>
+          <t>2026-08-22T20:47:45Z</t>
         </is>
       </c>
     </row>
@@ -2776,7 +2776,7 @@
       </c>
       <c r="S31" s="4" t="inlineStr">
         <is>
-          <t>2026-08-22T13:43:43Z</t>
+          <t>2026-08-22T20:47:45Z</t>
         </is>
       </c>
     </row>
@@ -2861,7 +2861,7 @@
       </c>
       <c r="S32" s="4" t="inlineStr">
         <is>
-          <t>2026-08-22T13:43:43Z</t>
+          <t>2026-08-22T20:47:45Z</t>
         </is>
       </c>
     </row>
@@ -2946,7 +2946,7 @@
       </c>
       <c r="S33" s="4" t="inlineStr">
         <is>
-          <t>2026-08-22T13:43:43Z</t>
+          <t>2026-08-22T20:47:45Z</t>
         </is>
       </c>
     </row>
@@ -3031,7 +3031,7 @@
       </c>
       <c r="S34" s="4" t="inlineStr">
         <is>
-          <t>2026-08-22T13:43:43Z</t>
+          <t>2026-08-22T20:47:45Z</t>
         </is>
       </c>
     </row>
@@ -3116,7 +3116,7 @@
       </c>
       <c r="S35" s="4" t="inlineStr">
         <is>
-          <t>2026-08-22T13:43:43Z</t>
+          <t>2026-08-22T20:47:45Z</t>
         </is>
       </c>
     </row>
@@ -3201,7 +3201,7 @@
       </c>
       <c r="S36" s="4" t="inlineStr">
         <is>
-          <t>2026-08-22T13:43:43Z</t>
+          <t>2026-08-22T20:47:45Z</t>
         </is>
       </c>
     </row>
@@ -3286,7 +3286,7 @@
       </c>
       <c r="S37" s="4" t="inlineStr">
         <is>
-          <t>2026-08-22T13:43:43Z</t>
+          <t>2026-08-22T20:47:45Z</t>
         </is>
       </c>
     </row>
@@ -3371,7 +3371,7 @@
       </c>
       <c r="S38" s="4" t="inlineStr">
         <is>
-          <t>2026-08-22T13:43:43Z</t>
+          <t>2026-08-22T20:47:45Z</t>
         </is>
       </c>
     </row>
@@ -3456,7 +3456,7 @@
       </c>
       <c r="S39" s="4" t="inlineStr">
         <is>
-          <t>2026-08-22T13:43:43Z</t>
+          <t>2026-08-22T20:47:45Z</t>
         </is>
       </c>
     </row>
@@ -3541,7 +3541,7 @@
       </c>
       <c r="S40" s="4" t="inlineStr">
         <is>
-          <t>2026-08-22T13:43:43Z</t>
+          <t>2026-08-22T20:47:45Z</t>
         </is>
       </c>
     </row>
@@ -3626,7 +3626,7 @@
       </c>
       <c r="S41" s="4" t="inlineStr">
         <is>
-          <t>2026-08-22T13:43:43Z</t>
+          <t>2026-08-22T20:47:45Z</t>
         </is>
       </c>
     </row>
@@ -3711,7 +3711,7 @@
       </c>
       <c r="S42" s="4" t="inlineStr">
         <is>
-          <t>2026-08-22T13:43:43Z</t>
+          <t>2026-08-22T20:47:45Z</t>
         </is>
       </c>
     </row>
@@ -3796,7 +3796,7 @@
       </c>
       <c r="S43" s="4" t="inlineStr">
         <is>
-          <t>2026-08-22T13:43:43Z</t>
+          <t>2026-08-22T20:47:45Z</t>
         </is>
       </c>
     </row>
@@ -3881,7 +3881,7 @@
       </c>
       <c r="S44" s="4" t="inlineStr">
         <is>
-          <t>2026-08-22T13:43:43Z</t>
+          <t>2026-08-22T20:47:45Z</t>
         </is>
       </c>
     </row>
@@ -3966,7 +3966,7 @@
       </c>
       <c r="S45" s="4" t="inlineStr">
         <is>
-          <t>2026-08-22T13:43:43Z</t>
+          <t>2026-08-22T20:47:45Z</t>
         </is>
       </c>
     </row>
@@ -4051,7 +4051,7 @@
       </c>
       <c r="S46" s="4" t="inlineStr">
         <is>
-          <t>2026-08-22T13:43:43Z</t>
+          <t>2026-08-22T20:47:45Z</t>
         </is>
       </c>
     </row>
@@ -4136,7 +4136,7 @@
       </c>
       <c r="S47" s="4" t="inlineStr">
         <is>
-          <t>2026-08-22T13:43:43Z</t>
+          <t>2026-08-22T20:47:45Z</t>
         </is>
       </c>
     </row>
@@ -4221,7 +4221,7 @@
       </c>
       <c r="S48" s="4" t="inlineStr">
         <is>
-          <t>2026-08-22T13:43:43Z</t>
+          <t>2026-08-22T20:47:45Z</t>
         </is>
       </c>
     </row>
@@ -4306,7 +4306,7 @@
       </c>
       <c r="S49" s="4" t="inlineStr">
         <is>
-          <t>2026-08-22T13:43:43Z</t>
+          <t>2026-08-22T20:47:45Z</t>
         </is>
       </c>
     </row>
@@ -4391,7 +4391,7 @@
       </c>
       <c r="S50" s="4" t="inlineStr">
         <is>
-          <t>2026-08-22T13:43:43Z</t>
+          <t>2026-08-22T20:47:45Z</t>
         </is>
       </c>
     </row>
@@ -4476,7 +4476,7 @@
       </c>
       <c r="S51" s="4" t="inlineStr">
         <is>
-          <t>2026-08-22T13:43:43Z</t>
+          <t>2026-08-22T20:47:45Z</t>
         </is>
       </c>
     </row>
@@ -4561,7 +4561,7 @@
       </c>
       <c r="S52" s="4" t="inlineStr">
         <is>
-          <t>2026-08-22T13:43:43Z</t>
+          <t>2026-08-22T20:47:45Z</t>
         </is>
       </c>
     </row>
@@ -4646,7 +4646,7 @@
       </c>
       <c r="S53" s="4" t="inlineStr">
         <is>
-          <t>2026-08-22T13:43:43Z</t>
+          <t>2026-08-22T20:47:45Z</t>
         </is>
       </c>
     </row>
@@ -4731,7 +4731,7 @@
       </c>
       <c r="S54" s="4" t="inlineStr">
         <is>
-          <t>2026-08-22T13:43:43Z</t>
+          <t>2026-08-22T20:47:45Z</t>
         </is>
       </c>
     </row>
@@ -4816,7 +4816,7 @@
       </c>
       <c r="S55" s="4" t="inlineStr">
         <is>
-          <t>2026-08-22T13:43:43Z</t>
+          <t>2026-08-22T20:47:45Z</t>
         </is>
       </c>
     </row>
@@ -4901,7 +4901,7 @@
       </c>
       <c r="S56" s="4" t="inlineStr">
         <is>
-          <t>2026-08-22T13:43:43Z</t>
+          <t>2026-08-22T20:47:45Z</t>
         </is>
       </c>
     </row>
@@ -4986,7 +4986,7 @@
       </c>
       <c r="S57" s="4" t="inlineStr">
         <is>
-          <t>2026-08-22T13:43:43Z</t>
+          <t>2026-08-22T20:47:45Z</t>
         </is>
       </c>
     </row>
@@ -5071,7 +5071,7 @@
       </c>
       <c r="S58" s="4" t="inlineStr">
         <is>
-          <t>2026-08-22T13:43:43Z</t>
+          <t>2026-08-22T20:47:45Z</t>
         </is>
       </c>
     </row>
@@ -5156,7 +5156,7 @@
       </c>
       <c r="S59" s="4" t="inlineStr">
         <is>
-          <t>2026-08-22T13:43:43Z</t>
+          <t>2026-08-22T20:47:45Z</t>
         </is>
       </c>
     </row>
@@ -5241,7 +5241,7 @@
       </c>
       <c r="S60" s="4" t="inlineStr">
         <is>
-          <t>2026-08-22T13:43:43Z</t>
+          <t>2026-08-22T20:47:45Z</t>
         </is>
       </c>
     </row>
@@ -5326,7 +5326,7 @@
       </c>
       <c r="S61" s="4" t="inlineStr">
         <is>
-          <t>2026-08-22T13:43:43Z</t>
+          <t>2026-08-22T20:47:45Z</t>
         </is>
       </c>
     </row>
@@ -5411,7 +5411,7 @@
       </c>
       <c r="S62" s="4" t="inlineStr">
         <is>
-          <t>2026-08-22T13:43:43Z</t>
+          <t>2026-08-22T20:47:45Z</t>
         </is>
       </c>
     </row>
@@ -5496,7 +5496,7 @@
       </c>
       <c r="S63" s="4" t="inlineStr">
         <is>
-          <t>2026-08-22T13:43:43Z</t>
+          <t>2026-08-22T20:47:45Z</t>
         </is>
       </c>
     </row>
@@ -5581,7 +5581,7 @@
       </c>
       <c r="S64" s="4" t="inlineStr">
         <is>
-          <t>2026-08-22T13:43:43Z</t>
+          <t>2026-08-22T20:47:45Z</t>
         </is>
       </c>
     </row>
@@ -5666,7 +5666,7 @@
       </c>
       <c r="S65" s="4" t="inlineStr">
         <is>
-          <t>2026-08-22T13:43:43Z</t>
+          <t>2026-08-22T20:47:45Z</t>
         </is>
       </c>
     </row>
@@ -5751,7 +5751,7 @@
       </c>
       <c r="S66" s="4" t="inlineStr">
         <is>
-          <t>2026-08-22T13:43:43Z</t>
+          <t>2026-08-22T20:47:45Z</t>
         </is>
       </c>
     </row>
@@ -5836,7 +5836,7 @@
       </c>
       <c r="S67" s="4" t="inlineStr">
         <is>
-          <t>2026-08-22T13:43:43Z</t>
+          <t>2026-08-22T20:47:45Z</t>
         </is>
       </c>
     </row>
@@ -5921,7 +5921,7 @@
       </c>
       <c r="S68" s="4" t="inlineStr">
         <is>
-          <t>2026-08-22T13:43:43Z</t>
+          <t>2026-08-22T20:47:45Z</t>
         </is>
       </c>
     </row>
@@ -6006,7 +6006,7 @@
       </c>
       <c r="S69" s="4" t="inlineStr">
         <is>
-          <t>2026-08-22T13:43:43Z</t>
+          <t>2026-08-22T20:47:45Z</t>
         </is>
       </c>
     </row>
@@ -6091,7 +6091,7 @@
       </c>
       <c r="S70" s="4" t="inlineStr">
         <is>
-          <t>2026-08-22T13:43:43Z</t>
+          <t>2026-08-22T20:47:45Z</t>
         </is>
       </c>
     </row>
@@ -6176,7 +6176,7 @@
       </c>
       <c r="S71" s="4" t="inlineStr">
         <is>
-          <t>2026-08-22T13:43:43Z</t>
+          <t>2026-08-22T20:47:45Z</t>
         </is>
       </c>
     </row>
@@ -6261,7 +6261,7 @@
       </c>
       <c r="S72" s="4" t="inlineStr">
         <is>
-          <t>2026-08-22T13:43:43Z</t>
+          <t>2026-08-22T20:47:45Z</t>
         </is>
       </c>
     </row>
@@ -6346,7 +6346,7 @@
       </c>
       <c r="S73" s="4" t="inlineStr">
         <is>
-          <t>2026-08-22T13:43:43Z</t>
+          <t>2026-08-22T20:47:45Z</t>
         </is>
       </c>
     </row>
@@ -6431,7 +6431,7 @@
       </c>
       <c r="S74" s="4" t="inlineStr">
         <is>
-          <t>2026-08-22T13:43:43Z</t>
+          <t>2026-08-22T20:47:45Z</t>
         </is>
       </c>
     </row>
@@ -6516,7 +6516,7 @@
       </c>
       <c r="S75" s="4" t="inlineStr">
         <is>
-          <t>2026-08-22T13:43:43Z</t>
+          <t>2026-08-22T20:47:45Z</t>
         </is>
       </c>
     </row>
@@ -6601,7 +6601,7 @@
       </c>
       <c r="S76" s="4" t="inlineStr">
         <is>
-          <t>2026-08-22T13:43:43Z</t>
+          <t>2026-08-22T20:47:45Z</t>
         </is>
       </c>
     </row>
@@ -6686,7 +6686,7 @@
       </c>
       <c r="S77" s="4" t="inlineStr">
         <is>
-          <t>2026-08-22T13:43:43Z</t>
+          <t>2026-08-22T20:47:45Z</t>
         </is>
       </c>
     </row>
@@ -6771,7 +6771,7 @@
       </c>
       <c r="S78" s="4" t="inlineStr">
         <is>
-          <t>2026-08-22T13:43:43Z</t>
+          <t>2026-08-22T20:47:45Z</t>
         </is>
       </c>
     </row>
@@ -6856,7 +6856,7 @@
       </c>
       <c r="S79" s="4" t="inlineStr">
         <is>
-          <t>2026-08-22T13:43:43Z</t>
+          <t>2026-08-22T20:47:45Z</t>
         </is>
       </c>
     </row>
@@ -6941,7 +6941,7 @@
       </c>
       <c r="S80" s="4" t="inlineStr">
         <is>
-          <t>2026-08-22T13:43:43Z</t>
+          <t>2026-08-22T20:47:45Z</t>
         </is>
       </c>
     </row>
@@ -7026,7 +7026,7 @@
       </c>
       <c r="S81" s="4" t="inlineStr">
         <is>
-          <t>2026-08-22T13:43:43Z</t>
+          <t>2026-08-22T20:47:45Z</t>
         </is>
       </c>
     </row>
@@ -7111,7 +7111,7 @@
       </c>
       <c r="S82" s="4" t="inlineStr">
         <is>
-          <t>2026-08-22T13:43:43Z</t>
+          <t>2026-08-22T20:47:45Z</t>
         </is>
       </c>
     </row>
@@ -7196,7 +7196,7 @@
       </c>
       <c r="S83" s="4" t="inlineStr">
         <is>
-          <t>2026-08-22T13:43:43Z</t>
+          <t>2026-08-22T20:47:45Z</t>
         </is>
       </c>
     </row>
@@ -7281,7 +7281,7 @@
       </c>
       <c r="S84" s="4" t="inlineStr">
         <is>
-          <t>2026-08-22T13:43:43Z</t>
+          <t>2026-08-22T20:47:45Z</t>
         </is>
       </c>
     </row>
@@ -7366,7 +7366,7 @@
       </c>
       <c r="S85" s="4" t="inlineStr">
         <is>
-          <t>2026-08-22T13:43:43Z</t>
+          <t>2026-08-22T20:47:45Z</t>
         </is>
       </c>
     </row>
@@ -7451,7 +7451,7 @@
       </c>
       <c r="S86" s="4" t="inlineStr">
         <is>
-          <t>2026-08-22T13:43:43Z</t>
+          <t>2026-08-22T20:47:45Z</t>
         </is>
       </c>
     </row>
@@ -7536,7 +7536,7 @@
       </c>
       <c r="S87" s="4" t="inlineStr">
         <is>
-          <t>2026-08-22T13:43:43Z</t>
+          <t>2026-08-22T20:47:45Z</t>
         </is>
       </c>
     </row>
@@ -7621,7 +7621,7 @@
       </c>
       <c r="S88" s="4" t="inlineStr">
         <is>
-          <t>2026-08-22T13:43:43Z</t>
+          <t>2026-08-22T20:47:45Z</t>
         </is>
       </c>
     </row>
@@ -7706,7 +7706,7 @@
       </c>
       <c r="S89" s="4" t="inlineStr">
         <is>
-          <t>2026-08-22T13:43:43Z</t>
+          <t>2026-08-22T20:47:45Z</t>
         </is>
       </c>
     </row>
@@ -7791,7 +7791,7 @@
       </c>
       <c r="S90" s="4" t="inlineStr">
         <is>
-          <t>2026-08-22T13:43:43Z</t>
+          <t>2026-08-22T20:47:45Z</t>
         </is>
       </c>
     </row>
@@ -7876,7 +7876,7 @@
       </c>
       <c r="S91" s="4" t="inlineStr">
         <is>
-          <t>2026-08-22T13:43:43Z</t>
+          <t>2026-08-22T20:47:45Z</t>
         </is>
       </c>
     </row>
@@ -7961,7 +7961,7 @@
       </c>
       <c r="S92" s="4" t="inlineStr">
         <is>
-          <t>2026-08-22T13:43:43Z</t>
+          <t>2026-08-22T20:47:45Z</t>
         </is>
       </c>
     </row>
@@ -8046,7 +8046,7 @@
       </c>
       <c r="S93" s="4" t="inlineStr">
         <is>
-          <t>2026-08-22T13:43:43Z</t>
+          <t>2026-08-22T20:47:45Z</t>
         </is>
       </c>
     </row>
@@ -8131,7 +8131,7 @@
       </c>
       <c r="S94" s="4" t="inlineStr">
         <is>
-          <t>2026-08-22T13:43:43Z</t>
+          <t>2026-08-22T20:47:45Z</t>
         </is>
       </c>
     </row>
@@ -8216,7 +8216,7 @@
       </c>
       <c r="S95" s="4" t="inlineStr">
         <is>
-          <t>2026-08-22T13:43:43Z</t>
+          <t>2026-08-22T20:47:45Z</t>
         </is>
       </c>
     </row>
@@ -8301,7 +8301,7 @@
       </c>
       <c r="S96" s="4" t="inlineStr">
         <is>
-          <t>2026-08-22T13:43:43Z</t>
+          <t>2026-08-22T20:47:45Z</t>
         </is>
       </c>
     </row>
@@ -8386,7 +8386,7 @@
       </c>
       <c r="S97" s="4" t="inlineStr">
         <is>
-          <t>2026-08-22T13:43:43Z</t>
+          <t>2026-08-22T20:47:45Z</t>
         </is>
       </c>
     </row>
@@ -8471,7 +8471,7 @@
       </c>
       <c r="S98" s="4" t="inlineStr">
         <is>
-          <t>2026-08-22T13:43:43Z</t>
+          <t>2026-08-22T20:47:45Z</t>
         </is>
       </c>
     </row>
@@ -8556,7 +8556,7 @@
       </c>
       <c r="S99" s="4" t="inlineStr">
         <is>
-          <t>2026-08-22T13:43:43Z</t>
+          <t>2026-08-22T20:47:45Z</t>
         </is>
       </c>
     </row>
@@ -8641,7 +8641,7 @@
       </c>
       <c r="S100" s="4" t="inlineStr">
         <is>
-          <t>2026-08-22T13:43:43Z</t>
+          <t>2026-08-22T20:47:45Z</t>
         </is>
       </c>
     </row>
@@ -8726,7 +8726,7 @@
       </c>
       <c r="S101" s="4" t="inlineStr">
         <is>
-          <t>2026-08-22T13:43:43Z</t>
+          <t>2026-08-22T20:47:45Z</t>
         </is>
       </c>
     </row>
@@ -8811,7 +8811,7 @@
       </c>
       <c r="S102" s="4" t="inlineStr">
         <is>
-          <t>2026-08-22T13:43:43Z</t>
+          <t>2026-08-22T20:47:45Z</t>
         </is>
       </c>
     </row>
@@ -8896,7 +8896,7 @@
       </c>
       <c r="S103" s="4" t="inlineStr">
         <is>
-          <t>2026-08-22T13:43:43Z</t>
+          <t>2026-08-22T20:47:45Z</t>
         </is>
       </c>
     </row>
@@ -8981,7 +8981,7 @@
       </c>
       <c r="S104" s="4" t="inlineStr">
         <is>
-          <t>2026-08-22T13:43:43Z</t>
+          <t>2026-08-22T20:47:45Z</t>
         </is>
       </c>
     </row>
@@ -9066,7 +9066,7 @@
       </c>
       <c r="S105" s="4" t="inlineStr">
         <is>
-          <t>2026-08-22T13:43:43Z</t>
+          <t>2026-08-22T20:47:45Z</t>
         </is>
       </c>
     </row>
@@ -9151,7 +9151,7 @@
       </c>
       <c r="S106" s="4" t="inlineStr">
         <is>
-          <t>2026-08-22T13:43:43Z</t>
+          <t>2026-08-22T20:47:45Z</t>
         </is>
       </c>
     </row>
@@ -9236,7 +9236,7 @@
       </c>
       <c r="S107" s="4" t="inlineStr">
         <is>
-          <t>2026-08-22T13:43:43Z</t>
+          <t>2026-08-22T20:47:45Z</t>
         </is>
       </c>
     </row>
@@ -9321,7 +9321,7 @@
       </c>
       <c r="S108" s="4" t="inlineStr">
         <is>
-          <t>2026-08-22T13:43:43Z</t>
+          <t>2026-08-22T20:47:45Z</t>
         </is>
       </c>
     </row>
@@ -9406,7 +9406,7 @@
       </c>
       <c r="S109" s="4" t="inlineStr">
         <is>
-          <t>2026-08-22T13:43:43Z</t>
+          <t>2026-08-22T20:47:45Z</t>
         </is>
       </c>
     </row>
@@ -9491,7 +9491,7 @@
       </c>
       <c r="S110" s="4" t="inlineStr">
         <is>
-          <t>2026-08-22T13:43:43Z</t>
+          <t>2026-08-22T20:47:45Z</t>
         </is>
       </c>
     </row>
@@ -9576,7 +9576,7 @@
       </c>
       <c r="S111" s="4" t="inlineStr">
         <is>
-          <t>2026-08-22T13:43:43Z</t>
+          <t>2026-08-22T20:47:45Z</t>
         </is>
       </c>
     </row>
@@ -9661,7 +9661,7 @@
       </c>
       <c r="S112" s="4" t="inlineStr">
         <is>
-          <t>2026-08-22T13:43:43Z</t>
+          <t>2026-08-22T20:47:45Z</t>
         </is>
       </c>
     </row>
@@ -9746,7 +9746,7 @@
       </c>
       <c r="S113" s="4" t="inlineStr">
         <is>
-          <t>2026-08-22T13:43:43Z</t>
+          <t>2026-08-22T20:47:45Z</t>
         </is>
       </c>
     </row>
@@ -9831,7 +9831,7 @@
       </c>
       <c r="S114" s="4" t="inlineStr">
         <is>
-          <t>2026-08-22T13:43:43Z</t>
+          <t>2026-08-22T20:47:45Z</t>
         </is>
       </c>
     </row>
@@ -9916,7 +9916,7 @@
       </c>
       <c r="S115" s="4" t="inlineStr">
         <is>
-          <t>2026-08-22T13:43:43Z</t>
+          <t>2026-08-22T20:47:45Z</t>
         </is>
       </c>
     </row>
@@ -10001,7 +10001,7 @@
       </c>
       <c r="S116" s="4" t="inlineStr">
         <is>
-          <t>2026-08-22T13:43:43Z</t>
+          <t>2026-08-22T20:47:45Z</t>
         </is>
       </c>
     </row>
@@ -10086,7 +10086,7 @@
       </c>
       <c r="S117" s="4" t="inlineStr">
         <is>
-          <t>2026-08-22T13:43:43Z</t>
+          <t>2026-08-22T20:47:45Z</t>
         </is>
       </c>
     </row>
@@ -10171,7 +10171,7 @@
       </c>
       <c r="S118" s="4" t="inlineStr">
         <is>
-          <t>2026-08-22T13:43:43Z</t>
+          <t>2026-08-22T20:47:45Z</t>
         </is>
       </c>
     </row>
@@ -10256,7 +10256,7 @@
       </c>
       <c r="S119" s="4" t="inlineStr">
         <is>
-          <t>2026-08-22T13:43:43Z</t>
+          <t>2026-08-22T20:47:45Z</t>
         </is>
       </c>
     </row>
@@ -10341,7 +10341,7 @@
       </c>
       <c r="S120" s="4" t="inlineStr">
         <is>
-          <t>2026-08-22T13:43:43Z</t>
+          <t>2026-08-22T20:47:45Z</t>
         </is>
       </c>
     </row>
@@ -10426,7 +10426,7 @@
       </c>
       <c r="S121" s="4" t="inlineStr">
         <is>
-          <t>2026-08-22T13:43:43Z</t>
+          <t>2026-08-22T20:47:45Z</t>
         </is>
       </c>
     </row>
@@ -10511,7 +10511,7 @@
       </c>
       <c r="S122" s="4" t="inlineStr">
         <is>
-          <t>2026-08-22T13:43:43Z</t>
+          <t>2026-08-22T20:47:45Z</t>
         </is>
       </c>
     </row>
@@ -10596,7 +10596,7 @@
       </c>
       <c r="S123" s="4" t="inlineStr">
         <is>
-          <t>2026-08-22T13:43:43Z</t>
+          <t>2026-08-22T20:47:45Z</t>
         </is>
       </c>
     </row>
@@ -10681,7 +10681,7 @@
       </c>
       <c r="S124" s="4" t="inlineStr">
         <is>
-          <t>2026-08-22T13:43:43Z</t>
+          <t>2026-08-22T20:47:45Z</t>
         </is>
       </c>
     </row>
@@ -10766,7 +10766,7 @@
       </c>
       <c r="S125" s="4" t="inlineStr">
         <is>
-          <t>2026-08-22T13:43:43Z</t>
+          <t>2026-08-22T20:47:45Z</t>
         </is>
       </c>
     </row>
@@ -10851,7 +10851,7 @@
       </c>
       <c r="S126" s="4" t="inlineStr">
         <is>
-          <t>2026-08-22T13:43:43Z</t>
+          <t>2026-08-22T20:47:45Z</t>
         </is>
       </c>
     </row>
@@ -10936,7 +10936,7 @@
       </c>
       <c r="S127" s="4" t="inlineStr">
         <is>
-          <t>2026-08-22T13:43:43Z</t>
+          <t>2026-08-22T20:47:45Z</t>
         </is>
       </c>
     </row>
@@ -11021,7 +11021,7 @@
       </c>
       <c r="S128" s="4" t="inlineStr">
         <is>
-          <t>2026-08-22T13:43:43Z</t>
+          <t>2026-08-22T20:47:45Z</t>
         </is>
       </c>
     </row>
@@ -11106,7 +11106,7 @@
       </c>
       <c r="S129" s="4" t="inlineStr">
         <is>
-          <t>2026-08-22T13:43:43Z</t>
+          <t>2026-08-22T20:47:45Z</t>
         </is>
       </c>
     </row>
@@ -11191,7 +11191,7 @@
       </c>
       <c r="S130" s="4" t="inlineStr">
         <is>
-          <t>2026-08-22T13:43:43Z</t>
+          <t>2026-08-22T20:47:45Z</t>
         </is>
       </c>
     </row>
@@ -11276,7 +11276,7 @@
       </c>
       <c r="S131" s="4" t="inlineStr">
         <is>
-          <t>2026-08-22T13:43:43Z</t>
+          <t>2026-08-22T20:47:45Z</t>
         </is>
       </c>
     </row>
@@ -11361,7 +11361,7 @@
       </c>
       <c r="S132" s="4" t="inlineStr">
         <is>
-          <t>2026-08-22T13:43:43Z</t>
+          <t>2026-08-22T20:47:45Z</t>
         </is>
       </c>
     </row>
@@ -11446,7 +11446,7 @@
       </c>
       <c r="S133" s="4" t="inlineStr">
         <is>
-          <t>2026-08-22T13:43:43Z</t>
+          <t>2026-08-22T20:47:45Z</t>
         </is>
       </c>
     </row>
@@ -11531,7 +11531,7 @@
       </c>
       <c r="S134" s="4" t="inlineStr">
         <is>
-          <t>2026-08-22T13:43:43Z</t>
+          <t>2026-08-22T20:47:45Z</t>
         </is>
       </c>
     </row>
@@ -11616,7 +11616,7 @@
       </c>
       <c r="S135" s="4" t="inlineStr">
         <is>
-          <t>2026-08-22T13:43:43Z</t>
+          <t>2026-08-22T20:47:45Z</t>
         </is>
       </c>
     </row>
@@ -11701,7 +11701,7 @@
       </c>
       <c r="S136" s="4" t="inlineStr">
         <is>
-          <t>2026-08-22T13:43:43Z</t>
+          <t>2026-08-22T20:47:45Z</t>
         </is>
       </c>
     </row>
@@ -11786,7 +11786,7 @@
       </c>
       <c r="S137" s="4" t="inlineStr">
         <is>
-          <t>2026-08-22T13:43:43Z</t>
+          <t>2026-08-22T20:47:45Z</t>
         </is>
       </c>
     </row>
@@ -11871,7 +11871,7 @@
       </c>
       <c r="S138" s="4" t="inlineStr">
         <is>
-          <t>2026-08-22T13:43:43Z</t>
+          <t>2026-08-22T20:47:45Z</t>
         </is>
       </c>
     </row>
@@ -11956,7 +11956,7 @@
       </c>
       <c r="S139" s="4" t="inlineStr">
         <is>
-          <t>2026-08-22T13:43:43Z</t>
+          <t>2026-08-22T20:47:45Z</t>
         </is>
       </c>
     </row>
@@ -12041,7 +12041,7 @@
       </c>
       <c r="S140" s="4" t="inlineStr">
         <is>
-          <t>2026-08-22T13:43:43Z</t>
+          <t>2026-08-22T20:47:45Z</t>
         </is>
       </c>
     </row>
@@ -12126,7 +12126,7 @@
       </c>
       <c r="S141" s="4" t="inlineStr">
         <is>
-          <t>2026-08-22T13:43:43Z</t>
+          <t>2026-08-22T20:47:45Z</t>
         </is>
       </c>
     </row>
@@ -12258,7 +12258,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>2026-08-22T13:43:43Z</t>
+          <t>2026-08-22T20:47:45Z</t>
         </is>
       </c>
     </row>
@@ -12338,7 +12338,7 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>{"dataset_id": "bcv_pib_historico_anual", "title": "Producto interno bruto histórico anual", "table": "PIB histórico anual", "source_file": "7_1_14_anual.xls", "base": "1957/1968/1984/1997", "price_type": "Precios constantes", "measure": "Nivel", "frequency": "Anual", "period": "2017", "year": 2017, "quarter": null, "classification": "Total economía", "component": "Producto interno bruto", "value": 392393.12, "unit": "Millones de bolívares a precios constantes", "status": "", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/7_1_14_anual.xls", "fetched_at": "2026-08-22T13:43:43Z"}</t>
+          <t>{"dataset_id": "bcv_pib_historico_anual", "title": "Producto interno bruto histórico anual", "table": "PIB histórico anual", "source_file": "7_1_14_anual.xls", "base": "1957/1968/1984/1997", "price_type": "Precios constantes", "measure": "Nivel", "frequency": "Anual", "period": "2017", "year": 2017, "quarter": null, "classification": "Total economía", "component": "Producto interno bruto", "value": 392393.12, "unit": "Millones de bolívares a precios constantes", "status": "", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/7_1_14_anual.xls", "fetched_at": "2026-08-22T20:47:45Z"}</t>
         </is>
       </c>
     </row>

--- a/assets/data/bcv/excel/ove_bcv_pib_historico_anual.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_pib_historico_anual.xlsx
@@ -736,7 +736,7 @@
       </c>
       <c r="S7" s="4" t="inlineStr">
         <is>
-          <t>2026-08-22T20:47:45Z</t>
+          <t>2026-08-23T20:47:28Z</t>
         </is>
       </c>
     </row>
@@ -821,7 +821,7 @@
       </c>
       <c r="S8" s="4" t="inlineStr">
         <is>
-          <t>2026-08-22T20:47:45Z</t>
+          <t>2026-08-23T20:47:28Z</t>
         </is>
       </c>
     </row>
@@ -906,7 +906,7 @@
       </c>
       <c r="S9" s="4" t="inlineStr">
         <is>
-          <t>2026-08-22T20:47:45Z</t>
+          <t>2026-08-23T20:47:28Z</t>
         </is>
       </c>
     </row>
@@ -991,7 +991,7 @@
       </c>
       <c r="S10" s="4" t="inlineStr">
         <is>
-          <t>2026-08-22T20:47:45Z</t>
+          <t>2026-08-23T20:47:28Z</t>
         </is>
       </c>
     </row>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="S11" s="4" t="inlineStr">
         <is>
-          <t>2026-08-22T20:47:45Z</t>
+          <t>2026-08-23T20:47:28Z</t>
         </is>
       </c>
     </row>
@@ -1161,7 +1161,7 @@
       </c>
       <c r="S12" s="4" t="inlineStr">
         <is>
-          <t>2026-08-22T20:47:45Z</t>
+          <t>2026-08-23T20:47:28Z</t>
         </is>
       </c>
     </row>
@@ -1246,7 +1246,7 @@
       </c>
       <c r="S13" s="4" t="inlineStr">
         <is>
-          <t>2026-08-22T20:47:45Z</t>
+          <t>2026-08-23T20:47:28Z</t>
         </is>
       </c>
     </row>
@@ -1331,7 +1331,7 @@
       </c>
       <c r="S14" s="4" t="inlineStr">
         <is>
-          <t>2026-08-22T20:47:45Z</t>
+          <t>2026-08-23T20:47:28Z</t>
         </is>
       </c>
     </row>
@@ -1416,7 +1416,7 @@
       </c>
       <c r="S15" s="4" t="inlineStr">
         <is>
-          <t>2026-08-22T20:47:45Z</t>
+          <t>2026-08-23T20:47:28Z</t>
         </is>
       </c>
     </row>
@@ -1501,7 +1501,7 @@
       </c>
       <c r="S16" s="4" t="inlineStr">
         <is>
-          <t>2026-08-22T20:47:45Z</t>
+          <t>2026-08-23T20:47:28Z</t>
         </is>
       </c>
     </row>
@@ -1586,7 +1586,7 @@
       </c>
       <c r="S17" s="4" t="inlineStr">
         <is>
-          <t>2026-08-22T20:47:45Z</t>
+          <t>2026-08-23T20:47:28Z</t>
         </is>
       </c>
     </row>
@@ -1671,7 +1671,7 @@
       </c>
       <c r="S18" s="4" t="inlineStr">
         <is>
-          <t>2026-08-22T20:47:45Z</t>
+          <t>2026-08-23T20:47:28Z</t>
         </is>
       </c>
     </row>
@@ -1756,7 +1756,7 @@
       </c>
       <c r="S19" s="4" t="inlineStr">
         <is>
-          <t>2026-08-22T20:47:45Z</t>
+          <t>2026-08-23T20:47:28Z</t>
         </is>
       </c>
     </row>
@@ -1841,7 +1841,7 @@
       </c>
       <c r="S20" s="4" t="inlineStr">
         <is>
-          <t>2026-08-22T20:47:45Z</t>
+          <t>2026-08-23T20:47:28Z</t>
         </is>
       </c>
     </row>
@@ -1926,7 +1926,7 @@
       </c>
       <c r="S21" s="4" t="inlineStr">
         <is>
-          <t>2026-08-22T20:47:45Z</t>
+          <t>2026-08-23T20:47:28Z</t>
         </is>
       </c>
     </row>
@@ -2011,7 +2011,7 @@
       </c>
       <c r="S22" s="4" t="inlineStr">
         <is>
-          <t>2026-08-22T20:47:45Z</t>
+          <t>2026-08-23T20:47:28Z</t>
         </is>
       </c>
     </row>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="S23" s="4" t="inlineStr">
         <is>
-          <t>2026-08-22T20:47:45Z</t>
+          <t>2026-08-23T20:47:28Z</t>
         </is>
       </c>
     </row>
@@ -2181,7 +2181,7 @@
       </c>
       <c r="S24" s="4" t="inlineStr">
         <is>
-          <t>2026-08-22T20:47:45Z</t>
+          <t>2026-08-23T20:47:28Z</t>
         </is>
       </c>
     </row>
@@ -2266,7 +2266,7 @@
       </c>
       <c r="S25" s="4" t="inlineStr">
         <is>
-          <t>2026-08-22T20:47:45Z</t>
+          <t>2026-08-23T20:47:28Z</t>
         </is>
       </c>
     </row>
@@ -2351,7 +2351,7 @@
       </c>
       <c r="S26" s="4" t="inlineStr">
         <is>
-          <t>2026-08-22T20:47:45Z</t>
+          <t>2026-08-23T20:47:28Z</t>
         </is>
       </c>
     </row>
@@ -2436,7 +2436,7 @@
       </c>
       <c r="S27" s="4" t="inlineStr">
         <is>
-          <t>2026-08-22T20:47:45Z</t>
+          <t>2026-08-23T20:47:28Z</t>
         </is>
       </c>
     </row>
@@ -2521,7 +2521,7 @@
       </c>
       <c r="S28" s="4" t="inlineStr">
         <is>
-          <t>2026-08-22T20:47:45Z</t>
+          <t>2026-08-23T20:47:28Z</t>
         </is>
       </c>
     </row>
@@ -2606,7 +2606,7 @@
       </c>
       <c r="S29" s="4" t="inlineStr">
         <is>
-          <t>2026-08-22T20:47:45Z</t>
+          <t>2026-08-23T20:47:28Z</t>
         </is>
       </c>
     </row>
@@ -2691,7 +2691,7 @@
       </c>
       <c r="S30" s="4" t="inlineStr">
         <is>
-          <t>2026-08-22T20:47:45Z</t>
+          <t>2026-08-23T20:47:28Z</t>
         </is>
       </c>
     </row>
@@ -2776,7 +2776,7 @@
       </c>
       <c r="S31" s="4" t="inlineStr">
         <is>
-          <t>2026-08-22T20:47:45Z</t>
+          <t>2026-08-23T20:47:28Z</t>
         </is>
       </c>
     </row>
@@ -2861,7 +2861,7 @@
       </c>
       <c r="S32" s="4" t="inlineStr">
         <is>
-          <t>2026-08-22T20:47:45Z</t>
+          <t>2026-08-23T20:47:28Z</t>
         </is>
       </c>
     </row>
@@ -2946,7 +2946,7 @@
       </c>
       <c r="S33" s="4" t="inlineStr">
         <is>
-          <t>2026-08-22T20:47:45Z</t>
+          <t>2026-08-23T20:47:28Z</t>
         </is>
       </c>
     </row>
@@ -3031,7 +3031,7 @@
       </c>
       <c r="S34" s="4" t="inlineStr">
         <is>
-          <t>2026-08-22T20:47:45Z</t>
+          <t>2026-08-23T20:47:28Z</t>
         </is>
       </c>
     </row>
@@ -3116,7 +3116,7 @@
       </c>
       <c r="S35" s="4" t="inlineStr">
         <is>
-          <t>2026-08-22T20:47:45Z</t>
+          <t>2026-08-23T20:47:28Z</t>
         </is>
       </c>
     </row>
@@ -3201,7 +3201,7 @@
       </c>
       <c r="S36" s="4" t="inlineStr">
         <is>
-          <t>2026-08-22T20:47:45Z</t>
+          <t>2026-08-23T20:47:28Z</t>
         </is>
       </c>
     </row>
@@ -3286,7 +3286,7 @@
       </c>
       <c r="S37" s="4" t="inlineStr">
         <is>
-          <t>2026-08-22T20:47:45Z</t>
+          <t>2026-08-23T20:47:28Z</t>
         </is>
       </c>
     </row>
@@ -3371,7 +3371,7 @@
       </c>
       <c r="S38" s="4" t="inlineStr">
         <is>
-          <t>2026-08-22T20:47:45Z</t>
+          <t>2026-08-23T20:47:28Z</t>
         </is>
       </c>
     </row>
@@ -3456,7 +3456,7 @@
       </c>
       <c r="S39" s="4" t="inlineStr">
         <is>
-          <t>2026-08-22T20:47:45Z</t>
+          <t>2026-08-23T20:47:28Z</t>
         </is>
       </c>
     </row>
@@ -3541,7 +3541,7 @@
       </c>
       <c r="S40" s="4" t="inlineStr">
         <is>
-          <t>2026-08-22T20:47:45Z</t>
+          <t>2026-08-23T20:47:28Z</t>
         </is>
       </c>
     </row>
@@ -3626,7 +3626,7 @@
       </c>
       <c r="S41" s="4" t="inlineStr">
         <is>
-          <t>2026-08-22T20:47:45Z</t>
+          <t>2026-08-23T20:47:28Z</t>
         </is>
       </c>
     </row>
@@ -3711,7 +3711,7 @@
       </c>
       <c r="S42" s="4" t="inlineStr">
         <is>
-          <t>2026-08-22T20:47:45Z</t>
+          <t>2026-08-23T20:47:28Z</t>
         </is>
       </c>
     </row>
@@ -3796,7 +3796,7 @@
       </c>
       <c r="S43" s="4" t="inlineStr">
         <is>
-          <t>2026-08-22T20:47:45Z</t>
+          <t>2026-08-23T20:47:28Z</t>
         </is>
       </c>
     </row>
@@ -3881,7 +3881,7 @@
       </c>
       <c r="S44" s="4" t="inlineStr">
         <is>
-          <t>2026-08-22T20:47:45Z</t>
+          <t>2026-08-23T20:47:28Z</t>
         </is>
       </c>
     </row>
@@ -3966,7 +3966,7 @@
       </c>
       <c r="S45" s="4" t="inlineStr">
         <is>
-          <t>2026-08-22T20:47:45Z</t>
+          <t>2026-08-23T20:47:28Z</t>
         </is>
       </c>
     </row>
@@ -4051,7 +4051,7 @@
       </c>
       <c r="S46" s="4" t="inlineStr">
         <is>
-          <t>2026-08-22T20:47:45Z</t>
+          <t>2026-08-23T20:47:28Z</t>
         </is>
       </c>
     </row>
@@ -4136,7 +4136,7 @@
       </c>
       <c r="S47" s="4" t="inlineStr">
         <is>
-          <t>2026-08-22T20:47:45Z</t>
+          <t>2026-08-23T20:47:28Z</t>
         </is>
       </c>
     </row>
@@ -4221,7 +4221,7 @@
       </c>
       <c r="S48" s="4" t="inlineStr">
         <is>
-          <t>2026-08-22T20:47:45Z</t>
+          <t>2026-08-23T20:47:28Z</t>
         </is>
       </c>
     </row>
@@ -4306,7 +4306,7 @@
       </c>
       <c r="S49" s="4" t="inlineStr">
         <is>
-          <t>2026-08-22T20:47:45Z</t>
+          <t>2026-08-23T20:47:28Z</t>
         </is>
       </c>
     </row>
@@ -4391,7 +4391,7 @@
       </c>
       <c r="S50" s="4" t="inlineStr">
         <is>
-          <t>2026-08-22T20:47:45Z</t>
+          <t>2026-08-23T20:47:28Z</t>
         </is>
       </c>
     </row>
@@ -4476,7 +4476,7 @@
       </c>
       <c r="S51" s="4" t="inlineStr">
         <is>
-          <t>2026-08-22T20:47:45Z</t>
+          <t>2026-08-23T20:47:28Z</t>
         </is>
       </c>
     </row>
@@ -4561,7 +4561,7 @@
       </c>
       <c r="S52" s="4" t="inlineStr">
         <is>
-          <t>2026-08-22T20:47:45Z</t>
+          <t>2026-08-23T20:47:28Z</t>
         </is>
       </c>
     </row>
@@ -4646,7 +4646,7 @@
       </c>
       <c r="S53" s="4" t="inlineStr">
         <is>
-          <t>2026-08-22T20:47:45Z</t>
+          <t>2026-08-23T20:47:28Z</t>
         </is>
       </c>
     </row>
@@ -4731,7 +4731,7 @@
       </c>
       <c r="S54" s="4" t="inlineStr">
         <is>
-          <t>2026-08-22T20:47:45Z</t>
+          <t>2026-08-23T20:47:28Z</t>
         </is>
       </c>
     </row>
@@ -4816,7 +4816,7 @@
       </c>
       <c r="S55" s="4" t="inlineStr">
         <is>
-          <t>2026-08-22T20:47:45Z</t>
+          <t>2026-08-23T20:47:28Z</t>
         </is>
       </c>
     </row>
@@ -4901,7 +4901,7 @@
       </c>
       <c r="S56" s="4" t="inlineStr">
         <is>
-          <t>2026-08-22T20:47:45Z</t>
+          <t>2026-08-23T20:47:28Z</t>
         </is>
       </c>
     </row>
@@ -4986,7 +4986,7 @@
       </c>
       <c r="S57" s="4" t="inlineStr">
         <is>
-          <t>2026-08-22T20:47:45Z</t>
+          <t>2026-08-23T20:47:28Z</t>
         </is>
       </c>
     </row>
@@ -5071,7 +5071,7 @@
       </c>
       <c r="S58" s="4" t="inlineStr">
         <is>
-          <t>2026-08-22T20:47:45Z</t>
+          <t>2026-08-23T20:47:28Z</t>
         </is>
       </c>
     </row>
@@ -5156,7 +5156,7 @@
       </c>
       <c r="S59" s="4" t="inlineStr">
         <is>
-          <t>2026-08-22T20:47:45Z</t>
+          <t>2026-08-23T20:47:28Z</t>
         </is>
       </c>
     </row>
@@ -5241,7 +5241,7 @@
       </c>
       <c r="S60" s="4" t="inlineStr">
         <is>
-          <t>2026-08-22T20:47:45Z</t>
+          <t>2026-08-23T20:47:28Z</t>
         </is>
       </c>
     </row>
@@ -5326,7 +5326,7 @@
       </c>
       <c r="S61" s="4" t="inlineStr">
         <is>
-          <t>2026-08-22T20:47:45Z</t>
+          <t>2026-08-23T20:47:28Z</t>
         </is>
       </c>
     </row>
@@ -5411,7 +5411,7 @@
       </c>
       <c r="S62" s="4" t="inlineStr">
         <is>
-          <t>2026-08-22T20:47:45Z</t>
+          <t>2026-08-23T20:47:28Z</t>
         </is>
       </c>
     </row>
@@ -5496,7 +5496,7 @@
       </c>
       <c r="S63" s="4" t="inlineStr">
         <is>
-          <t>2026-08-22T20:47:45Z</t>
+          <t>2026-08-23T20:47:28Z</t>
         </is>
       </c>
     </row>
@@ -5581,7 +5581,7 @@
       </c>
       <c r="S64" s="4" t="inlineStr">
         <is>
-          <t>2026-08-22T20:47:45Z</t>
+          <t>2026-08-23T20:47:28Z</t>
         </is>
       </c>
     </row>
@@ -5666,7 +5666,7 @@
       </c>
       <c r="S65" s="4" t="inlineStr">
         <is>
-          <t>2026-08-22T20:47:45Z</t>
+          <t>2026-08-23T20:47:28Z</t>
         </is>
       </c>
     </row>
@@ -5751,7 +5751,7 @@
       </c>
       <c r="S66" s="4" t="inlineStr">
         <is>
-          <t>2026-08-22T20:47:45Z</t>
+          <t>2026-08-23T20:47:28Z</t>
         </is>
       </c>
     </row>
@@ -5836,7 +5836,7 @@
       </c>
       <c r="S67" s="4" t="inlineStr">
         <is>
-          <t>2026-08-22T20:47:45Z</t>
+          <t>2026-08-23T20:47:28Z</t>
         </is>
       </c>
     </row>
@@ -5921,7 +5921,7 @@
       </c>
       <c r="S68" s="4" t="inlineStr">
         <is>
-          <t>2026-08-22T20:47:45Z</t>
+          <t>2026-08-23T20:47:28Z</t>
         </is>
       </c>
     </row>
@@ -6006,7 +6006,7 @@
       </c>
       <c r="S69" s="4" t="inlineStr">
         <is>
-          <t>2026-08-22T20:47:45Z</t>
+          <t>2026-08-23T20:47:28Z</t>
         </is>
       </c>
     </row>
@@ -6091,7 +6091,7 @@
       </c>
       <c r="S70" s="4" t="inlineStr">
         <is>
-          <t>2026-08-22T20:47:45Z</t>
+          <t>2026-08-23T20:47:28Z</t>
         </is>
       </c>
     </row>
@@ -6176,7 +6176,7 @@
       </c>
       <c r="S71" s="4" t="inlineStr">
         <is>
-          <t>2026-08-22T20:47:45Z</t>
+          <t>2026-08-23T20:47:28Z</t>
         </is>
       </c>
     </row>
@@ -6261,7 +6261,7 @@
       </c>
       <c r="S72" s="4" t="inlineStr">
         <is>
-          <t>2026-08-22T20:47:45Z</t>
+          <t>2026-08-23T20:47:28Z</t>
         </is>
       </c>
     </row>
@@ -6346,7 +6346,7 @@
       </c>
       <c r="S73" s="4" t="inlineStr">
         <is>
-          <t>2026-08-22T20:47:45Z</t>
+          <t>2026-08-23T20:47:28Z</t>
         </is>
       </c>
     </row>
@@ -6431,7 +6431,7 @@
       </c>
       <c r="S74" s="4" t="inlineStr">
         <is>
-          <t>2026-08-22T20:47:45Z</t>
+          <t>2026-08-23T20:47:28Z</t>
         </is>
       </c>
     </row>
@@ -6516,7 +6516,7 @@
       </c>
       <c r="S75" s="4" t="inlineStr">
         <is>
-          <t>2026-08-22T20:47:45Z</t>
+          <t>2026-08-23T20:47:28Z</t>
         </is>
       </c>
     </row>
@@ -6601,7 +6601,7 @@
       </c>
       <c r="S76" s="4" t="inlineStr">
         <is>
-          <t>2026-08-22T20:47:45Z</t>
+          <t>2026-08-23T20:47:28Z</t>
         </is>
       </c>
     </row>
@@ -6686,7 +6686,7 @@
       </c>
       <c r="S77" s="4" t="inlineStr">
         <is>
-          <t>2026-08-22T20:47:45Z</t>
+          <t>2026-08-23T20:47:28Z</t>
         </is>
       </c>
     </row>
@@ -6771,7 +6771,7 @@
       </c>
       <c r="S78" s="4" t="inlineStr">
         <is>
-          <t>2026-08-22T20:47:45Z</t>
+          <t>2026-08-23T20:47:28Z</t>
         </is>
       </c>
     </row>
@@ -6856,7 +6856,7 @@
       </c>
       <c r="S79" s="4" t="inlineStr">
         <is>
-          <t>2026-08-22T20:47:45Z</t>
+          <t>2026-08-23T20:47:28Z</t>
         </is>
       </c>
     </row>
@@ -6941,7 +6941,7 @@
       </c>
       <c r="S80" s="4" t="inlineStr">
         <is>
-          <t>2026-08-22T20:47:45Z</t>
+          <t>2026-08-23T20:47:28Z</t>
         </is>
       </c>
     </row>
@@ -7026,7 +7026,7 @@
       </c>
       <c r="S81" s="4" t="inlineStr">
         <is>
-          <t>2026-08-22T20:47:45Z</t>
+          <t>2026-08-23T20:47:28Z</t>
         </is>
       </c>
     </row>
@@ -7111,7 +7111,7 @@
       </c>
       <c r="S82" s="4" t="inlineStr">
         <is>
-          <t>2026-08-22T20:47:45Z</t>
+          <t>2026-08-23T20:47:28Z</t>
         </is>
       </c>
     </row>
@@ -7196,7 +7196,7 @@
       </c>
       <c r="S83" s="4" t="inlineStr">
         <is>
-          <t>2026-08-22T20:47:45Z</t>
+          <t>2026-08-23T20:47:28Z</t>
         </is>
       </c>
     </row>
@@ -7281,7 +7281,7 @@
       </c>
       <c r="S84" s="4" t="inlineStr">
         <is>
-          <t>2026-08-22T20:47:45Z</t>
+          <t>2026-08-23T20:47:28Z</t>
         </is>
       </c>
     </row>
@@ -7366,7 +7366,7 @@
       </c>
       <c r="S85" s="4" t="inlineStr">
         <is>
-          <t>2026-08-22T20:47:45Z</t>
+          <t>2026-08-23T20:47:28Z</t>
         </is>
       </c>
     </row>
@@ -7451,7 +7451,7 @@
       </c>
       <c r="S86" s="4" t="inlineStr">
         <is>
-          <t>2026-08-22T20:47:45Z</t>
+          <t>2026-08-23T20:47:28Z</t>
         </is>
       </c>
     </row>
@@ -7536,7 +7536,7 @@
       </c>
       <c r="S87" s="4" t="inlineStr">
         <is>
-          <t>2026-08-22T20:47:45Z</t>
+          <t>2026-08-23T20:47:28Z</t>
         </is>
       </c>
     </row>
@@ -7621,7 +7621,7 @@
       </c>
       <c r="S88" s="4" t="inlineStr">
         <is>
-          <t>2026-08-22T20:47:45Z</t>
+          <t>2026-08-23T20:47:28Z</t>
         </is>
       </c>
     </row>
@@ -7706,7 +7706,7 @@
       </c>
       <c r="S89" s="4" t="inlineStr">
         <is>
-          <t>2026-08-22T20:47:45Z</t>
+          <t>2026-08-23T20:47:28Z</t>
         </is>
       </c>
     </row>
@@ -7791,7 +7791,7 @@
       </c>
       <c r="S90" s="4" t="inlineStr">
         <is>
-          <t>2026-08-22T20:47:45Z</t>
+          <t>2026-08-23T20:47:28Z</t>
         </is>
       </c>
     </row>
@@ -7876,7 +7876,7 @@
       </c>
       <c r="S91" s="4" t="inlineStr">
         <is>
-          <t>2026-08-22T20:47:45Z</t>
+          <t>2026-08-23T20:47:28Z</t>
         </is>
       </c>
     </row>
@@ -7961,7 +7961,7 @@
       </c>
       <c r="S92" s="4" t="inlineStr">
         <is>
-          <t>2026-08-22T20:47:45Z</t>
+          <t>2026-08-23T20:47:28Z</t>
         </is>
       </c>
     </row>
@@ -8046,7 +8046,7 @@
       </c>
       <c r="S93" s="4" t="inlineStr">
         <is>
-          <t>2026-08-22T20:47:45Z</t>
+          <t>2026-08-23T20:47:28Z</t>
         </is>
       </c>
     </row>
@@ -8131,7 +8131,7 @@
       </c>
       <c r="S94" s="4" t="inlineStr">
         <is>
-          <t>2026-08-22T20:47:45Z</t>
+          <t>2026-08-23T20:47:28Z</t>
         </is>
       </c>
     </row>
@@ -8216,7 +8216,7 @@
       </c>
       <c r="S95" s="4" t="inlineStr">
         <is>
-          <t>2026-08-22T20:47:45Z</t>
+          <t>2026-08-23T20:47:28Z</t>
         </is>
       </c>
     </row>
@@ -8301,7 +8301,7 @@
       </c>
       <c r="S96" s="4" t="inlineStr">
         <is>
-          <t>2026-08-22T20:47:45Z</t>
+          <t>2026-08-23T20:47:28Z</t>
         </is>
       </c>
     </row>
@@ -8386,7 +8386,7 @@
       </c>
       <c r="S97" s="4" t="inlineStr">
         <is>
-          <t>2026-08-22T20:47:45Z</t>
+          <t>2026-08-23T20:47:28Z</t>
         </is>
       </c>
     </row>
@@ -8471,7 +8471,7 @@
       </c>
       <c r="S98" s="4" t="inlineStr">
         <is>
-          <t>2026-08-22T20:47:45Z</t>
+          <t>2026-08-23T20:47:28Z</t>
         </is>
       </c>
     </row>
@@ -8556,7 +8556,7 @@
       </c>
       <c r="S99" s="4" t="inlineStr">
         <is>
-          <t>2026-08-22T20:47:45Z</t>
+          <t>2026-08-23T20:47:28Z</t>
         </is>
       </c>
     </row>
@@ -8641,7 +8641,7 @@
       </c>
       <c r="S100" s="4" t="inlineStr">
         <is>
-          <t>2026-08-22T20:47:45Z</t>
+          <t>2026-08-23T20:47:28Z</t>
         </is>
       </c>
     </row>
@@ -8726,7 +8726,7 @@
       </c>
       <c r="S101" s="4" t="inlineStr">
         <is>
-          <t>2026-08-22T20:47:45Z</t>
+          <t>2026-08-23T20:47:28Z</t>
         </is>
       </c>
     </row>
@@ -8811,7 +8811,7 @@
       </c>
       <c r="S102" s="4" t="inlineStr">
         <is>
-          <t>2026-08-22T20:47:45Z</t>
+          <t>2026-08-23T20:47:28Z</t>
         </is>
       </c>
     </row>
@@ -8896,7 +8896,7 @@
       </c>
       <c r="S103" s="4" t="inlineStr">
         <is>
-          <t>2026-08-22T20:47:45Z</t>
+          <t>2026-08-23T20:47:28Z</t>
         </is>
       </c>
     </row>
@@ -8981,7 +8981,7 @@
       </c>
       <c r="S104" s="4" t="inlineStr">
         <is>
-          <t>2026-08-22T20:47:45Z</t>
+          <t>2026-08-23T20:47:28Z</t>
         </is>
       </c>
     </row>
@@ -9066,7 +9066,7 @@
       </c>
       <c r="S105" s="4" t="inlineStr">
         <is>
-          <t>2026-08-22T20:47:45Z</t>
+          <t>2026-08-23T20:47:28Z</t>
         </is>
       </c>
     </row>
@@ -9151,7 +9151,7 @@
       </c>
       <c r="S106" s="4" t="inlineStr">
         <is>
-          <t>2026-08-22T20:47:45Z</t>
+          <t>2026-08-23T20:47:28Z</t>
         </is>
       </c>
     </row>
@@ -9236,7 +9236,7 @@
       </c>
       <c r="S107" s="4" t="inlineStr">
         <is>
-          <t>2026-08-22T20:47:45Z</t>
+          <t>2026-08-23T20:47:28Z</t>
         </is>
       </c>
     </row>
@@ -9321,7 +9321,7 @@
       </c>
       <c r="S108" s="4" t="inlineStr">
         <is>
-          <t>2026-08-22T20:47:45Z</t>
+          <t>2026-08-23T20:47:28Z</t>
         </is>
       </c>
     </row>
@@ -9406,7 +9406,7 @@
       </c>
       <c r="S109" s="4" t="inlineStr">
         <is>
-          <t>2026-08-22T20:47:45Z</t>
+          <t>2026-08-23T20:47:28Z</t>
         </is>
       </c>
     </row>
@@ -9491,7 +9491,7 @@
       </c>
       <c r="S110" s="4" t="inlineStr">
         <is>
-          <t>2026-08-22T20:47:45Z</t>
+          <t>2026-08-23T20:47:28Z</t>
         </is>
       </c>
     </row>
@@ -9576,7 +9576,7 @@
       </c>
       <c r="S111" s="4" t="inlineStr">
         <is>
-          <t>2026-08-22T20:47:45Z</t>
+          <t>2026-08-23T20:47:28Z</t>
         </is>
       </c>
     </row>
@@ -9661,7 +9661,7 @@
       </c>
       <c r="S112" s="4" t="inlineStr">
         <is>
-          <t>2026-08-22T20:47:45Z</t>
+          <t>2026-08-23T20:47:28Z</t>
         </is>
       </c>
     </row>
@@ -9746,7 +9746,7 @@
       </c>
       <c r="S113" s="4" t="inlineStr">
         <is>
-          <t>2026-08-22T20:47:45Z</t>
+          <t>2026-08-23T20:47:28Z</t>
         </is>
       </c>
     </row>
@@ -9831,7 +9831,7 @@
       </c>
       <c r="S114" s="4" t="inlineStr">
         <is>
-          <t>2026-08-22T20:47:45Z</t>
+          <t>2026-08-23T20:47:28Z</t>
         </is>
       </c>
     </row>
@@ -9916,7 +9916,7 @@
       </c>
       <c r="S115" s="4" t="inlineStr">
         <is>
-          <t>2026-08-22T20:47:45Z</t>
+          <t>2026-08-23T20:47:28Z</t>
         </is>
       </c>
     </row>
@@ -10001,7 +10001,7 @@
       </c>
       <c r="S116" s="4" t="inlineStr">
         <is>
-          <t>2026-08-22T20:47:45Z</t>
+          <t>2026-08-23T20:47:28Z</t>
         </is>
       </c>
     </row>
@@ -10086,7 +10086,7 @@
       </c>
       <c r="S117" s="4" t="inlineStr">
         <is>
-          <t>2026-08-22T20:47:45Z</t>
+          <t>2026-08-23T20:47:28Z</t>
         </is>
       </c>
     </row>
@@ -10171,7 +10171,7 @@
       </c>
       <c r="S118" s="4" t="inlineStr">
         <is>
-          <t>2026-08-22T20:47:45Z</t>
+          <t>2026-08-23T20:47:28Z</t>
         </is>
       </c>
     </row>
@@ -10256,7 +10256,7 @@
       </c>
       <c r="S119" s="4" t="inlineStr">
         <is>
-          <t>2026-08-22T20:47:45Z</t>
+          <t>2026-08-23T20:47:28Z</t>
         </is>
       </c>
     </row>
@@ -10341,7 +10341,7 @@
       </c>
       <c r="S120" s="4" t="inlineStr">
         <is>
-          <t>2026-08-22T20:47:45Z</t>
+          <t>2026-08-23T20:47:28Z</t>
         </is>
       </c>
     </row>
@@ -10426,7 +10426,7 @@
       </c>
       <c r="S121" s="4" t="inlineStr">
         <is>
-          <t>2026-08-22T20:47:45Z</t>
+          <t>2026-08-23T20:47:28Z</t>
         </is>
       </c>
     </row>
@@ -10511,7 +10511,7 @@
       </c>
       <c r="S122" s="4" t="inlineStr">
         <is>
-          <t>2026-08-22T20:47:45Z</t>
+          <t>2026-08-23T20:47:28Z</t>
         </is>
       </c>
     </row>
@@ -10596,7 +10596,7 @@
       </c>
       <c r="S123" s="4" t="inlineStr">
         <is>
-          <t>2026-08-22T20:47:45Z</t>
+          <t>2026-08-23T20:47:28Z</t>
         </is>
       </c>
     </row>
@@ -10681,7 +10681,7 @@
       </c>
       <c r="S124" s="4" t="inlineStr">
         <is>
-          <t>2026-08-22T20:47:45Z</t>
+          <t>2026-08-23T20:47:28Z</t>
         </is>
       </c>
     </row>
@@ -10766,7 +10766,7 @@
       </c>
       <c r="S125" s="4" t="inlineStr">
         <is>
-          <t>2026-08-22T20:47:45Z</t>
+          <t>2026-08-23T20:47:28Z</t>
         </is>
       </c>
     </row>
@@ -10851,7 +10851,7 @@
       </c>
       <c r="S126" s="4" t="inlineStr">
         <is>
-          <t>2026-08-22T20:47:45Z</t>
+          <t>2026-08-23T20:47:28Z</t>
         </is>
       </c>
     </row>
@@ -10936,7 +10936,7 @@
       </c>
       <c r="S127" s="4" t="inlineStr">
         <is>
-          <t>2026-08-22T20:47:45Z</t>
+          <t>2026-08-23T20:47:28Z</t>
         </is>
       </c>
     </row>
@@ -11021,7 +11021,7 @@
       </c>
       <c r="S128" s="4" t="inlineStr">
         <is>
-          <t>2026-08-22T20:47:45Z</t>
+          <t>2026-08-23T20:47:28Z</t>
         </is>
       </c>
     </row>
@@ -11106,7 +11106,7 @@
       </c>
       <c r="S129" s="4" t="inlineStr">
         <is>
-          <t>2026-08-22T20:47:45Z</t>
+          <t>2026-08-23T20:47:28Z</t>
         </is>
       </c>
     </row>
@@ -11191,7 +11191,7 @@
       </c>
       <c r="S130" s="4" t="inlineStr">
         <is>
-          <t>2026-08-22T20:47:45Z</t>
+          <t>2026-08-23T20:47:28Z</t>
         </is>
       </c>
     </row>
@@ -11276,7 +11276,7 @@
       </c>
       <c r="S131" s="4" t="inlineStr">
         <is>
-          <t>2026-08-22T20:47:45Z</t>
+          <t>2026-08-23T20:47:28Z</t>
         </is>
       </c>
     </row>
@@ -11361,7 +11361,7 @@
       </c>
       <c r="S132" s="4" t="inlineStr">
         <is>
-          <t>2026-08-22T20:47:45Z</t>
+          <t>2026-08-23T20:47:28Z</t>
         </is>
       </c>
     </row>
@@ -11446,7 +11446,7 @@
       </c>
       <c r="S133" s="4" t="inlineStr">
         <is>
-          <t>2026-08-22T20:47:45Z</t>
+          <t>2026-08-23T20:47:28Z</t>
         </is>
       </c>
     </row>
@@ -11531,7 +11531,7 @@
       </c>
       <c r="S134" s="4" t="inlineStr">
         <is>
-          <t>2026-08-22T20:47:45Z</t>
+          <t>2026-08-23T20:47:28Z</t>
         </is>
       </c>
     </row>
@@ -11616,7 +11616,7 @@
       </c>
       <c r="S135" s="4" t="inlineStr">
         <is>
-          <t>2026-08-22T20:47:45Z</t>
+          <t>2026-08-23T20:47:28Z</t>
         </is>
       </c>
     </row>
@@ -11701,7 +11701,7 @@
       </c>
       <c r="S136" s="4" t="inlineStr">
         <is>
-          <t>2026-08-22T20:47:45Z</t>
+          <t>2026-08-23T20:47:28Z</t>
         </is>
       </c>
     </row>
@@ -11786,7 +11786,7 @@
       </c>
       <c r="S137" s="4" t="inlineStr">
         <is>
-          <t>2026-08-22T20:47:45Z</t>
+          <t>2026-08-23T20:47:28Z</t>
         </is>
       </c>
     </row>
@@ -11871,7 +11871,7 @@
       </c>
       <c r="S138" s="4" t="inlineStr">
         <is>
-          <t>2026-08-22T20:47:45Z</t>
+          <t>2026-08-23T20:47:28Z</t>
         </is>
       </c>
     </row>
@@ -11956,7 +11956,7 @@
       </c>
       <c r="S139" s="4" t="inlineStr">
         <is>
-          <t>2026-08-22T20:47:45Z</t>
+          <t>2026-08-23T20:47:28Z</t>
         </is>
       </c>
     </row>
@@ -12041,7 +12041,7 @@
       </c>
       <c r="S140" s="4" t="inlineStr">
         <is>
-          <t>2026-08-22T20:47:45Z</t>
+          <t>2026-08-23T20:47:28Z</t>
         </is>
       </c>
     </row>
@@ -12126,7 +12126,7 @@
       </c>
       <c r="S141" s="4" t="inlineStr">
         <is>
-          <t>2026-08-22T20:47:45Z</t>
+          <t>2026-08-23T20:47:28Z</t>
         </is>
       </c>
     </row>
@@ -12258,7 +12258,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>2026-08-22T20:47:45Z</t>
+          <t>2026-08-23T20:47:28Z</t>
         </is>
       </c>
     </row>
@@ -12338,7 +12338,7 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>{"dataset_id": "bcv_pib_historico_anual", "title": "Producto interno bruto histórico anual", "table": "PIB histórico anual", "source_file": "7_1_14_anual.xls", "base": "1957/1968/1984/1997", "price_type": "Precios constantes", "measure": "Nivel", "frequency": "Anual", "period": "2017", "year": 2017, "quarter": null, "classification": "Total economía", "component": "Producto interno bruto", "value": 392393.12, "unit": "Millones de bolívares a precios constantes", "status": "", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/7_1_14_anual.xls", "fetched_at": "2026-08-22T20:47:45Z"}</t>
+          <t>{"dataset_id": "bcv_pib_historico_anual", "title": "Producto interno bruto histórico anual", "table": "PIB histórico anual", "source_file": "7_1_14_anual.xls", "base": "1957/1968/1984/1997", "price_type": "Precios constantes", "measure": "Nivel", "frequency": "Anual", "period": "2017", "year": 2017, "quarter": null, "classification": "Total economía", "component": "Producto interno bruto", "value": 392393.12, "unit": "Millones de bolívares a precios constantes", "status": "", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/7_1_14_anual.xls", "fetched_at": "2026-08-23T20:47:28Z"}</t>
         </is>
       </c>
     </row>

--- a/assets/data/bcv/excel/ove_bcv_pib_historico_anual.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_pib_historico_anual.xlsx
@@ -736,7 +736,7 @@
       </c>
       <c r="S7" s="4" t="inlineStr">
         <is>
-          <t>2026-08-23T20:47:28Z</t>
+          <t>2026-08-24T20:57:43Z</t>
         </is>
       </c>
     </row>
@@ -821,7 +821,7 @@
       </c>
       <c r="S8" s="4" t="inlineStr">
         <is>
-          <t>2026-08-23T20:47:28Z</t>
+          <t>2026-08-24T20:57:43Z</t>
         </is>
       </c>
     </row>
@@ -906,7 +906,7 @@
       </c>
       <c r="S9" s="4" t="inlineStr">
         <is>
-          <t>2026-08-23T20:47:28Z</t>
+          <t>2026-08-24T20:57:43Z</t>
         </is>
       </c>
     </row>
@@ -991,7 +991,7 @@
       </c>
       <c r="S10" s="4" t="inlineStr">
         <is>
-          <t>2026-08-23T20:47:28Z</t>
+          <t>2026-08-24T20:57:43Z</t>
         </is>
       </c>
     </row>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="S11" s="4" t="inlineStr">
         <is>
-          <t>2026-08-23T20:47:28Z</t>
+          <t>2026-08-24T20:57:43Z</t>
         </is>
       </c>
     </row>
@@ -1161,7 +1161,7 @@
       </c>
       <c r="S12" s="4" t="inlineStr">
         <is>
-          <t>2026-08-23T20:47:28Z</t>
+          <t>2026-08-24T20:57:43Z</t>
         </is>
       </c>
     </row>
@@ -1246,7 +1246,7 @@
       </c>
       <c r="S13" s="4" t="inlineStr">
         <is>
-          <t>2026-08-23T20:47:28Z</t>
+          <t>2026-08-24T20:57:43Z</t>
         </is>
       </c>
     </row>
@@ -1331,7 +1331,7 @@
       </c>
       <c r="S14" s="4" t="inlineStr">
         <is>
-          <t>2026-08-23T20:47:28Z</t>
+          <t>2026-08-24T20:57:43Z</t>
         </is>
       </c>
     </row>
@@ -1416,7 +1416,7 @@
       </c>
       <c r="S15" s="4" t="inlineStr">
         <is>
-          <t>2026-08-23T20:47:28Z</t>
+          <t>2026-08-24T20:57:43Z</t>
         </is>
       </c>
     </row>
@@ -1501,7 +1501,7 @@
       </c>
       <c r="S16" s="4" t="inlineStr">
         <is>
-          <t>2026-08-23T20:47:28Z</t>
+          <t>2026-08-24T20:57:43Z</t>
         </is>
       </c>
     </row>
@@ -1586,7 +1586,7 @@
       </c>
       <c r="S17" s="4" t="inlineStr">
         <is>
-          <t>2026-08-23T20:47:28Z</t>
+          <t>2026-08-24T20:57:43Z</t>
         </is>
       </c>
     </row>
@@ -1671,7 +1671,7 @@
       </c>
       <c r="S18" s="4" t="inlineStr">
         <is>
-          <t>2026-08-23T20:47:28Z</t>
+          <t>2026-08-24T20:57:43Z</t>
         </is>
       </c>
     </row>
@@ -1756,7 +1756,7 @@
       </c>
       <c r="S19" s="4" t="inlineStr">
         <is>
-          <t>2026-08-23T20:47:28Z</t>
+          <t>2026-08-24T20:57:43Z</t>
         </is>
       </c>
     </row>
@@ -1841,7 +1841,7 @@
       </c>
       <c r="S20" s="4" t="inlineStr">
         <is>
-          <t>2026-08-23T20:47:28Z</t>
+          <t>2026-08-24T20:57:43Z</t>
         </is>
       </c>
     </row>
@@ -1926,7 +1926,7 @@
       </c>
       <c r="S21" s="4" t="inlineStr">
         <is>
-          <t>2026-08-23T20:47:28Z</t>
+          <t>2026-08-24T20:57:43Z</t>
         </is>
       </c>
     </row>
@@ -2011,7 +2011,7 @@
       </c>
       <c r="S22" s="4" t="inlineStr">
         <is>
-          <t>2026-08-23T20:47:28Z</t>
+          <t>2026-08-24T20:57:43Z</t>
         </is>
       </c>
     </row>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="S23" s="4" t="inlineStr">
         <is>
-          <t>2026-08-23T20:47:28Z</t>
+          <t>2026-08-24T20:57:43Z</t>
         </is>
       </c>
     </row>
@@ -2181,7 +2181,7 @@
       </c>
       <c r="S24" s="4" t="inlineStr">
         <is>
-          <t>2026-08-23T20:47:28Z</t>
+          <t>2026-08-24T20:57:43Z</t>
         </is>
       </c>
     </row>
@@ -2266,7 +2266,7 @@
       </c>
       <c r="S25" s="4" t="inlineStr">
         <is>
-          <t>2026-08-23T20:47:28Z</t>
+          <t>2026-08-24T20:57:43Z</t>
         </is>
       </c>
     </row>
@@ -2351,7 +2351,7 @@
       </c>
       <c r="S26" s="4" t="inlineStr">
         <is>
-          <t>2026-08-23T20:47:28Z</t>
+          <t>2026-08-24T20:57:43Z</t>
         </is>
       </c>
     </row>
@@ -2436,7 +2436,7 @@
       </c>
       <c r="S27" s="4" t="inlineStr">
         <is>
-          <t>2026-08-23T20:47:28Z</t>
+          <t>2026-08-24T20:57:43Z</t>
         </is>
       </c>
     </row>
@@ -2521,7 +2521,7 @@
       </c>
       <c r="S28" s="4" t="inlineStr">
         <is>
-          <t>2026-08-23T20:47:28Z</t>
+          <t>2026-08-24T20:57:43Z</t>
         </is>
       </c>
     </row>
@@ -2606,7 +2606,7 @@
       </c>
       <c r="S29" s="4" t="inlineStr">
         <is>
-          <t>2026-08-23T20:47:28Z</t>
+          <t>2026-08-24T20:57:43Z</t>
         </is>
       </c>
     </row>
@@ -2691,7 +2691,7 @@
       </c>
       <c r="S30" s="4" t="inlineStr">
         <is>
-          <t>2026-08-23T20:47:28Z</t>
+          <t>2026-08-24T20:57:43Z</t>
         </is>
       </c>
     </row>
@@ -2776,7 +2776,7 @@
       </c>
       <c r="S31" s="4" t="inlineStr">
         <is>
-          <t>2026-08-23T20:47:28Z</t>
+          <t>2026-08-24T20:57:43Z</t>
         </is>
       </c>
     </row>
@@ -2861,7 +2861,7 @@
       </c>
       <c r="S32" s="4" t="inlineStr">
         <is>
-          <t>2026-08-23T20:47:28Z</t>
+          <t>2026-08-24T20:57:43Z</t>
         </is>
       </c>
     </row>
@@ -2946,7 +2946,7 @@
       </c>
       <c r="S33" s="4" t="inlineStr">
         <is>
-          <t>2026-08-23T20:47:28Z</t>
+          <t>2026-08-24T20:57:43Z</t>
         </is>
       </c>
     </row>
@@ -3031,7 +3031,7 @@
       </c>
       <c r="S34" s="4" t="inlineStr">
         <is>
-          <t>2026-08-23T20:47:28Z</t>
+          <t>2026-08-24T20:57:43Z</t>
         </is>
       </c>
     </row>
@@ -3116,7 +3116,7 @@
       </c>
       <c r="S35" s="4" t="inlineStr">
         <is>
-          <t>2026-08-23T20:47:28Z</t>
+          <t>2026-08-24T20:57:43Z</t>
         </is>
       </c>
     </row>
@@ -3201,7 +3201,7 @@
       </c>
       <c r="S36" s="4" t="inlineStr">
         <is>
-          <t>2026-08-23T20:47:28Z</t>
+          <t>2026-08-24T20:57:43Z</t>
         </is>
       </c>
     </row>
@@ -3286,7 +3286,7 @@
       </c>
       <c r="S37" s="4" t="inlineStr">
         <is>
-          <t>2026-08-23T20:47:28Z</t>
+          <t>2026-08-24T20:57:43Z</t>
         </is>
       </c>
     </row>
@@ -3371,7 +3371,7 @@
       </c>
       <c r="S38" s="4" t="inlineStr">
         <is>
-          <t>2026-08-23T20:47:28Z</t>
+          <t>2026-08-24T20:57:43Z</t>
         </is>
       </c>
     </row>
@@ -3456,7 +3456,7 @@
       </c>
       <c r="S39" s="4" t="inlineStr">
         <is>
-          <t>2026-08-23T20:47:28Z</t>
+          <t>2026-08-24T20:57:43Z</t>
         </is>
       </c>
     </row>
@@ -3541,7 +3541,7 @@
       </c>
       <c r="S40" s="4" t="inlineStr">
         <is>
-          <t>2026-08-23T20:47:28Z</t>
+          <t>2026-08-24T20:57:43Z</t>
         </is>
       </c>
     </row>
@@ -3626,7 +3626,7 @@
       </c>
       <c r="S41" s="4" t="inlineStr">
         <is>
-          <t>2026-08-23T20:47:28Z</t>
+          <t>2026-08-24T20:57:43Z</t>
         </is>
       </c>
     </row>
@@ -3711,7 +3711,7 @@
       </c>
       <c r="S42" s="4" t="inlineStr">
         <is>
-          <t>2026-08-23T20:47:28Z</t>
+          <t>2026-08-24T20:57:43Z</t>
         </is>
       </c>
     </row>
@@ -3796,7 +3796,7 @@
       </c>
       <c r="S43" s="4" t="inlineStr">
         <is>
-          <t>2026-08-23T20:47:28Z</t>
+          <t>2026-08-24T20:57:43Z</t>
         </is>
       </c>
     </row>
@@ -3881,7 +3881,7 @@
       </c>
       <c r="S44" s="4" t="inlineStr">
         <is>
-          <t>2026-08-23T20:47:28Z</t>
+          <t>2026-08-24T20:57:43Z</t>
         </is>
       </c>
     </row>
@@ -3966,7 +3966,7 @@
       </c>
       <c r="S45" s="4" t="inlineStr">
         <is>
-          <t>2026-08-23T20:47:28Z</t>
+          <t>2026-08-24T20:57:43Z</t>
         </is>
       </c>
     </row>
@@ -4051,7 +4051,7 @@
       </c>
       <c r="S46" s="4" t="inlineStr">
         <is>
-          <t>2026-08-23T20:47:28Z</t>
+          <t>2026-08-24T20:57:43Z</t>
         </is>
       </c>
     </row>
@@ -4136,7 +4136,7 @@
       </c>
       <c r="S47" s="4" t="inlineStr">
         <is>
-          <t>2026-08-23T20:47:28Z</t>
+          <t>2026-08-24T20:57:43Z</t>
         </is>
       </c>
     </row>
@@ -4221,7 +4221,7 @@
       </c>
       <c r="S48" s="4" t="inlineStr">
         <is>
-          <t>2026-08-23T20:47:28Z</t>
+          <t>2026-08-24T20:57:43Z</t>
         </is>
       </c>
     </row>
@@ -4306,7 +4306,7 @@
       </c>
       <c r="S49" s="4" t="inlineStr">
         <is>
-          <t>2026-08-23T20:47:28Z</t>
+          <t>2026-08-24T20:57:43Z</t>
         </is>
       </c>
     </row>
@@ -4391,7 +4391,7 @@
       </c>
       <c r="S50" s="4" t="inlineStr">
         <is>
-          <t>2026-08-23T20:47:28Z</t>
+          <t>2026-08-24T20:57:43Z</t>
         </is>
       </c>
     </row>
@@ -4476,7 +4476,7 @@
       </c>
       <c r="S51" s="4" t="inlineStr">
         <is>
-          <t>2026-08-23T20:47:28Z</t>
+          <t>2026-08-24T20:57:43Z</t>
         </is>
       </c>
     </row>
@@ -4561,7 +4561,7 @@
       </c>
       <c r="S52" s="4" t="inlineStr">
         <is>
-          <t>2026-08-23T20:47:28Z</t>
+          <t>2026-08-24T20:57:43Z</t>
         </is>
       </c>
     </row>
@@ -4646,7 +4646,7 @@
       </c>
       <c r="S53" s="4" t="inlineStr">
         <is>
-          <t>2026-08-23T20:47:28Z</t>
+          <t>2026-08-24T20:57:43Z</t>
         </is>
       </c>
     </row>
@@ -4731,7 +4731,7 @@
       </c>
       <c r="S54" s="4" t="inlineStr">
         <is>
-          <t>2026-08-23T20:47:28Z</t>
+          <t>2026-08-24T20:57:43Z</t>
         </is>
       </c>
     </row>
@@ -4816,7 +4816,7 @@
       </c>
       <c r="S55" s="4" t="inlineStr">
         <is>
-          <t>2026-08-23T20:47:28Z</t>
+          <t>2026-08-24T20:57:43Z</t>
         </is>
       </c>
     </row>
@@ -4901,7 +4901,7 @@
       </c>
       <c r="S56" s="4" t="inlineStr">
         <is>
-          <t>2026-08-23T20:47:28Z</t>
+          <t>2026-08-24T20:57:43Z</t>
         </is>
       </c>
     </row>
@@ -4986,7 +4986,7 @@
       </c>
       <c r="S57" s="4" t="inlineStr">
         <is>
-          <t>2026-08-23T20:47:28Z</t>
+          <t>2026-08-24T20:57:43Z</t>
         </is>
       </c>
     </row>
@@ -5071,7 +5071,7 @@
       </c>
       <c r="S58" s="4" t="inlineStr">
         <is>
-          <t>2026-08-23T20:47:28Z</t>
+          <t>2026-08-24T20:57:43Z</t>
         </is>
       </c>
     </row>
@@ -5156,7 +5156,7 @@
       </c>
       <c r="S59" s="4" t="inlineStr">
         <is>
-          <t>2026-08-23T20:47:28Z</t>
+          <t>2026-08-24T20:57:43Z</t>
         </is>
       </c>
     </row>
@@ -5241,7 +5241,7 @@
       </c>
       <c r="S60" s="4" t="inlineStr">
         <is>
-          <t>2026-08-23T20:47:28Z</t>
+          <t>2026-08-24T20:57:43Z</t>
         </is>
       </c>
     </row>
@@ -5326,7 +5326,7 @@
       </c>
       <c r="S61" s="4" t="inlineStr">
         <is>
-          <t>2026-08-23T20:47:28Z</t>
+          <t>2026-08-24T20:57:43Z</t>
         </is>
       </c>
     </row>
@@ -5411,7 +5411,7 @@
       </c>
       <c r="S62" s="4" t="inlineStr">
         <is>
-          <t>2026-08-23T20:47:28Z</t>
+          <t>2026-08-24T20:57:43Z</t>
         </is>
       </c>
     </row>
@@ -5496,7 +5496,7 @@
       </c>
       <c r="S63" s="4" t="inlineStr">
         <is>
-          <t>2026-08-23T20:47:28Z</t>
+          <t>2026-08-24T20:57:43Z</t>
         </is>
       </c>
     </row>
@@ -5581,7 +5581,7 @@
       </c>
       <c r="S64" s="4" t="inlineStr">
         <is>
-          <t>2026-08-23T20:47:28Z</t>
+          <t>2026-08-24T20:57:43Z</t>
         </is>
       </c>
     </row>
@@ -5666,7 +5666,7 @@
       </c>
       <c r="S65" s="4" t="inlineStr">
         <is>
-          <t>2026-08-23T20:47:28Z</t>
+          <t>2026-08-24T20:57:43Z</t>
         </is>
       </c>
     </row>
@@ -5751,7 +5751,7 @@
       </c>
       <c r="S66" s="4" t="inlineStr">
         <is>
-          <t>2026-08-23T20:47:28Z</t>
+          <t>2026-08-24T20:57:43Z</t>
         </is>
       </c>
     </row>
@@ -5836,7 +5836,7 @@
       </c>
       <c r="S67" s="4" t="inlineStr">
         <is>
-          <t>2026-08-23T20:47:28Z</t>
+          <t>2026-08-24T20:57:43Z</t>
         </is>
       </c>
     </row>
@@ -5921,7 +5921,7 @@
       </c>
       <c r="S68" s="4" t="inlineStr">
         <is>
-          <t>2026-08-23T20:47:28Z</t>
+          <t>2026-08-24T20:57:43Z</t>
         </is>
       </c>
     </row>
@@ -6006,7 +6006,7 @@
       </c>
       <c r="S69" s="4" t="inlineStr">
         <is>
-          <t>2026-08-23T20:47:28Z</t>
+          <t>2026-08-24T20:57:43Z</t>
         </is>
       </c>
     </row>
@@ -6091,7 +6091,7 @@
       </c>
       <c r="S70" s="4" t="inlineStr">
         <is>
-          <t>2026-08-23T20:47:28Z</t>
+          <t>2026-08-24T20:57:43Z</t>
         </is>
       </c>
     </row>
@@ -6176,7 +6176,7 @@
       </c>
       <c r="S71" s="4" t="inlineStr">
         <is>
-          <t>2026-08-23T20:47:28Z</t>
+          <t>2026-08-24T20:57:43Z</t>
         </is>
       </c>
     </row>
@@ -6261,7 +6261,7 @@
       </c>
       <c r="S72" s="4" t="inlineStr">
         <is>
-          <t>2026-08-23T20:47:28Z</t>
+          <t>2026-08-24T20:57:43Z</t>
         </is>
       </c>
     </row>
@@ -6346,7 +6346,7 @@
       </c>
       <c r="S73" s="4" t="inlineStr">
         <is>
-          <t>2026-08-23T20:47:28Z</t>
+          <t>2026-08-24T20:57:43Z</t>
         </is>
       </c>
     </row>
@@ -6431,7 +6431,7 @@
       </c>
       <c r="S74" s="4" t="inlineStr">
         <is>
-          <t>2026-08-23T20:47:28Z</t>
+          <t>2026-08-24T20:57:43Z</t>
         </is>
       </c>
     </row>
@@ -6516,7 +6516,7 @@
       </c>
       <c r="S75" s="4" t="inlineStr">
         <is>
-          <t>2026-08-23T20:47:28Z</t>
+          <t>2026-08-24T20:57:43Z</t>
         </is>
       </c>
     </row>
@@ -6601,7 +6601,7 @@
       </c>
       <c r="S76" s="4" t="inlineStr">
         <is>
-          <t>2026-08-23T20:47:28Z</t>
+          <t>2026-08-24T20:57:43Z</t>
         </is>
       </c>
     </row>
@@ -6686,7 +6686,7 @@
       </c>
       <c r="S77" s="4" t="inlineStr">
         <is>
-          <t>2026-08-23T20:47:28Z</t>
+          <t>2026-08-24T20:57:43Z</t>
         </is>
       </c>
     </row>
@@ -6771,7 +6771,7 @@
       </c>
       <c r="S78" s="4" t="inlineStr">
         <is>
-          <t>2026-08-23T20:47:28Z</t>
+          <t>2026-08-24T20:57:43Z</t>
         </is>
       </c>
     </row>
@@ -6856,7 +6856,7 @@
       </c>
       <c r="S79" s="4" t="inlineStr">
         <is>
-          <t>2026-08-23T20:47:28Z</t>
+          <t>2026-08-24T20:57:43Z</t>
         </is>
       </c>
     </row>
@@ -6941,7 +6941,7 @@
       </c>
       <c r="S80" s="4" t="inlineStr">
         <is>
-          <t>2026-08-23T20:47:28Z</t>
+          <t>2026-08-24T20:57:43Z</t>
         </is>
       </c>
     </row>
@@ -7026,7 +7026,7 @@
       </c>
       <c r="S81" s="4" t="inlineStr">
         <is>
-          <t>2026-08-23T20:47:28Z</t>
+          <t>2026-08-24T20:57:43Z</t>
         </is>
       </c>
     </row>
@@ -7111,7 +7111,7 @@
       </c>
       <c r="S82" s="4" t="inlineStr">
         <is>
-          <t>2026-08-23T20:47:28Z</t>
+          <t>2026-08-24T20:57:43Z</t>
         </is>
       </c>
     </row>
@@ -7196,7 +7196,7 @@
       </c>
       <c r="S83" s="4" t="inlineStr">
         <is>
-          <t>2026-08-23T20:47:28Z</t>
+          <t>2026-08-24T20:57:43Z</t>
         </is>
       </c>
     </row>
@@ -7281,7 +7281,7 @@
       </c>
       <c r="S84" s="4" t="inlineStr">
         <is>
-          <t>2026-08-23T20:47:28Z</t>
+          <t>2026-08-24T20:57:43Z</t>
         </is>
       </c>
     </row>
@@ -7366,7 +7366,7 @@
       </c>
       <c r="S85" s="4" t="inlineStr">
         <is>
-          <t>2026-08-23T20:47:28Z</t>
+          <t>2026-08-24T20:57:43Z</t>
         </is>
       </c>
     </row>
@@ -7451,7 +7451,7 @@
       </c>
       <c r="S86" s="4" t="inlineStr">
         <is>
-          <t>2026-08-23T20:47:28Z</t>
+          <t>2026-08-24T20:57:43Z</t>
         </is>
       </c>
     </row>
@@ -7536,7 +7536,7 @@
       </c>
       <c r="S87" s="4" t="inlineStr">
         <is>
-          <t>2026-08-23T20:47:28Z</t>
+          <t>2026-08-24T20:57:43Z</t>
         </is>
       </c>
     </row>
@@ -7621,7 +7621,7 @@
       </c>
       <c r="S88" s="4" t="inlineStr">
         <is>
-          <t>2026-08-23T20:47:28Z</t>
+          <t>2026-08-24T20:57:43Z</t>
         </is>
       </c>
     </row>
@@ -7706,7 +7706,7 @@
       </c>
       <c r="S89" s="4" t="inlineStr">
         <is>
-          <t>2026-08-23T20:47:28Z</t>
+          <t>2026-08-24T20:57:43Z</t>
         </is>
       </c>
     </row>
@@ -7791,7 +7791,7 @@
       </c>
       <c r="S90" s="4" t="inlineStr">
         <is>
-          <t>2026-08-23T20:47:28Z</t>
+          <t>2026-08-24T20:57:43Z</t>
         </is>
       </c>
     </row>
@@ -7876,7 +7876,7 @@
       </c>
       <c r="S91" s="4" t="inlineStr">
         <is>
-          <t>2026-08-23T20:47:28Z</t>
+          <t>2026-08-24T20:57:43Z</t>
         </is>
       </c>
     </row>
@@ -7961,7 +7961,7 @@
       </c>
       <c r="S92" s="4" t="inlineStr">
         <is>
-          <t>2026-08-23T20:47:28Z</t>
+          <t>2026-08-24T20:57:43Z</t>
         </is>
       </c>
     </row>
@@ -8046,7 +8046,7 @@
       </c>
       <c r="S93" s="4" t="inlineStr">
         <is>
-          <t>2026-08-23T20:47:28Z</t>
+          <t>2026-08-24T20:57:43Z</t>
         </is>
       </c>
     </row>
@@ -8131,7 +8131,7 @@
       </c>
       <c r="S94" s="4" t="inlineStr">
         <is>
-          <t>2026-08-23T20:47:28Z</t>
+          <t>2026-08-24T20:57:43Z</t>
         </is>
       </c>
     </row>
@@ -8216,7 +8216,7 @@
       </c>
       <c r="S95" s="4" t="inlineStr">
         <is>
-          <t>2026-08-23T20:47:28Z</t>
+          <t>2026-08-24T20:57:43Z</t>
         </is>
       </c>
     </row>
@@ -8301,7 +8301,7 @@
       </c>
       <c r="S96" s="4" t="inlineStr">
         <is>
-          <t>2026-08-23T20:47:28Z</t>
+          <t>2026-08-24T20:57:43Z</t>
         </is>
       </c>
     </row>
@@ -8386,7 +8386,7 @@
       </c>
       <c r="S97" s="4" t="inlineStr">
         <is>
-          <t>2026-08-23T20:47:28Z</t>
+          <t>2026-08-24T20:57:43Z</t>
         </is>
       </c>
     </row>
@@ -8471,7 +8471,7 @@
       </c>
       <c r="S98" s="4" t="inlineStr">
         <is>
-          <t>2026-08-23T20:47:28Z</t>
+          <t>2026-08-24T20:57:43Z</t>
         </is>
       </c>
     </row>
@@ -8556,7 +8556,7 @@
       </c>
       <c r="S99" s="4" t="inlineStr">
         <is>
-          <t>2026-08-23T20:47:28Z</t>
+          <t>2026-08-24T20:57:43Z</t>
         </is>
       </c>
     </row>
@@ -8641,7 +8641,7 @@
       </c>
       <c r="S100" s="4" t="inlineStr">
         <is>
-          <t>2026-08-23T20:47:28Z</t>
+          <t>2026-08-24T20:57:43Z</t>
         </is>
       </c>
     </row>
@@ -8726,7 +8726,7 @@
       </c>
       <c r="S101" s="4" t="inlineStr">
         <is>
-          <t>2026-08-23T20:47:28Z</t>
+          <t>2026-08-24T20:57:43Z</t>
         </is>
       </c>
     </row>
@@ -8811,7 +8811,7 @@
       </c>
       <c r="S102" s="4" t="inlineStr">
         <is>
-          <t>2026-08-23T20:47:28Z</t>
+          <t>2026-08-24T20:57:43Z</t>
         </is>
       </c>
     </row>
@@ -8896,7 +8896,7 @@
       </c>
       <c r="S103" s="4" t="inlineStr">
         <is>
-          <t>2026-08-23T20:47:28Z</t>
+          <t>2026-08-24T20:57:43Z</t>
         </is>
       </c>
     </row>
@@ -8981,7 +8981,7 @@
       </c>
       <c r="S104" s="4" t="inlineStr">
         <is>
-          <t>2026-08-23T20:47:28Z</t>
+          <t>2026-08-24T20:57:43Z</t>
         </is>
       </c>
     </row>
@@ -9066,7 +9066,7 @@
       </c>
       <c r="S105" s="4" t="inlineStr">
         <is>
-          <t>2026-08-23T20:47:28Z</t>
+          <t>2026-08-24T20:57:43Z</t>
         </is>
       </c>
     </row>
@@ -9151,7 +9151,7 @@
       </c>
       <c r="S106" s="4" t="inlineStr">
         <is>
-          <t>2026-08-23T20:47:28Z</t>
+          <t>2026-08-24T20:57:43Z</t>
         </is>
       </c>
     </row>
@@ -9236,7 +9236,7 @@
       </c>
       <c r="S107" s="4" t="inlineStr">
         <is>
-          <t>2026-08-23T20:47:28Z</t>
+          <t>2026-08-24T20:57:43Z</t>
         </is>
       </c>
     </row>
@@ -9321,7 +9321,7 @@
       </c>
       <c r="S108" s="4" t="inlineStr">
         <is>
-          <t>2026-08-23T20:47:28Z</t>
+          <t>2026-08-24T20:57:43Z</t>
         </is>
       </c>
     </row>
@@ -9406,7 +9406,7 @@
       </c>
       <c r="S109" s="4" t="inlineStr">
         <is>
-          <t>2026-08-23T20:47:28Z</t>
+          <t>2026-08-24T20:57:43Z</t>
         </is>
       </c>
     </row>
@@ -9491,7 +9491,7 @@
       </c>
       <c r="S110" s="4" t="inlineStr">
         <is>
-          <t>2026-08-23T20:47:28Z</t>
+          <t>2026-08-24T20:57:43Z</t>
         </is>
       </c>
     </row>
@@ -9576,7 +9576,7 @@
       </c>
       <c r="S111" s="4" t="inlineStr">
         <is>
-          <t>2026-08-23T20:47:28Z</t>
+          <t>2026-08-24T20:57:43Z</t>
         </is>
       </c>
     </row>
@@ -9661,7 +9661,7 @@
       </c>
       <c r="S112" s="4" t="inlineStr">
         <is>
-          <t>2026-08-23T20:47:28Z</t>
+          <t>2026-08-24T20:57:43Z</t>
         </is>
       </c>
     </row>
@@ -9746,7 +9746,7 @@
       </c>
       <c r="S113" s="4" t="inlineStr">
         <is>
-          <t>2026-08-23T20:47:28Z</t>
+          <t>2026-08-24T20:57:43Z</t>
         </is>
       </c>
     </row>
@@ -9831,7 +9831,7 @@
       </c>
       <c r="S114" s="4" t="inlineStr">
         <is>
-          <t>2026-08-23T20:47:28Z</t>
+          <t>2026-08-24T20:57:43Z</t>
         </is>
       </c>
     </row>
@@ -9916,7 +9916,7 @@
       </c>
       <c r="S115" s="4" t="inlineStr">
         <is>
-          <t>2026-08-23T20:47:28Z</t>
+          <t>2026-08-24T20:57:43Z</t>
         </is>
       </c>
     </row>
@@ -10001,7 +10001,7 @@
       </c>
       <c r="S116" s="4" t="inlineStr">
         <is>
-          <t>2026-08-23T20:47:28Z</t>
+          <t>2026-08-24T20:57:43Z</t>
         </is>
       </c>
     </row>
@@ -10086,7 +10086,7 @@
       </c>
       <c r="S117" s="4" t="inlineStr">
         <is>
-          <t>2026-08-23T20:47:28Z</t>
+          <t>2026-08-24T20:57:43Z</t>
         </is>
       </c>
     </row>
@@ -10171,7 +10171,7 @@
       </c>
       <c r="S118" s="4" t="inlineStr">
         <is>
-          <t>2026-08-23T20:47:28Z</t>
+          <t>2026-08-24T20:57:43Z</t>
         </is>
       </c>
     </row>
@@ -10256,7 +10256,7 @@
       </c>
       <c r="S119" s="4" t="inlineStr">
         <is>
-          <t>2026-08-23T20:47:28Z</t>
+          <t>2026-08-24T20:57:43Z</t>
         </is>
       </c>
     </row>
@@ -10341,7 +10341,7 @@
       </c>
       <c r="S120" s="4" t="inlineStr">
         <is>
-          <t>2026-08-23T20:47:28Z</t>
+          <t>2026-08-24T20:57:43Z</t>
         </is>
       </c>
     </row>
@@ -10426,7 +10426,7 @@
       </c>
       <c r="S121" s="4" t="inlineStr">
         <is>
-          <t>2026-08-23T20:47:28Z</t>
+          <t>2026-08-24T20:57:43Z</t>
         </is>
       </c>
     </row>
@@ -10511,7 +10511,7 @@
       </c>
       <c r="S122" s="4" t="inlineStr">
         <is>
-          <t>2026-08-23T20:47:28Z</t>
+          <t>2026-08-24T20:57:43Z</t>
         </is>
       </c>
     </row>
@@ -10596,7 +10596,7 @@
       </c>
       <c r="S123" s="4" t="inlineStr">
         <is>
-          <t>2026-08-23T20:47:28Z</t>
+          <t>2026-08-24T20:57:43Z</t>
         </is>
       </c>
     </row>
@@ -10681,7 +10681,7 @@
       </c>
       <c r="S124" s="4" t="inlineStr">
         <is>
-          <t>2026-08-23T20:47:28Z</t>
+          <t>2026-08-24T20:57:43Z</t>
         </is>
       </c>
     </row>
@@ -10766,7 +10766,7 @@
       </c>
       <c r="S125" s="4" t="inlineStr">
         <is>
-          <t>2026-08-23T20:47:28Z</t>
+          <t>2026-08-24T20:57:43Z</t>
         </is>
       </c>
     </row>
@@ -10851,7 +10851,7 @@
       </c>
       <c r="S126" s="4" t="inlineStr">
         <is>
-          <t>2026-08-23T20:47:28Z</t>
+          <t>2026-08-24T20:57:43Z</t>
         </is>
       </c>
     </row>
@@ -10936,7 +10936,7 @@
       </c>
       <c r="S127" s="4" t="inlineStr">
         <is>
-          <t>2026-08-23T20:47:28Z</t>
+          <t>2026-08-24T20:57:43Z</t>
         </is>
       </c>
     </row>
@@ -11021,7 +11021,7 @@
       </c>
       <c r="S128" s="4" t="inlineStr">
         <is>
-          <t>2026-08-23T20:47:28Z</t>
+          <t>2026-08-24T20:57:43Z</t>
         </is>
       </c>
     </row>
@@ -11106,7 +11106,7 @@
       </c>
       <c r="S129" s="4" t="inlineStr">
         <is>
-          <t>2026-08-23T20:47:28Z</t>
+          <t>2026-08-24T20:57:43Z</t>
         </is>
       </c>
     </row>
@@ -11191,7 +11191,7 @@
       </c>
       <c r="S130" s="4" t="inlineStr">
         <is>
-          <t>2026-08-23T20:47:28Z</t>
+          <t>2026-08-24T20:57:43Z</t>
         </is>
       </c>
     </row>
@@ -11276,7 +11276,7 @@
       </c>
       <c r="S131" s="4" t="inlineStr">
         <is>
-          <t>2026-08-23T20:47:28Z</t>
+          <t>2026-08-24T20:57:43Z</t>
         </is>
       </c>
     </row>
@@ -11361,7 +11361,7 @@
       </c>
       <c r="S132" s="4" t="inlineStr">
         <is>
-          <t>2026-08-23T20:47:28Z</t>
+          <t>2026-08-24T20:57:43Z</t>
         </is>
       </c>
     </row>
@@ -11446,7 +11446,7 @@
       </c>
       <c r="S133" s="4" t="inlineStr">
         <is>
-          <t>2026-08-23T20:47:28Z</t>
+          <t>2026-08-24T20:57:43Z</t>
         </is>
       </c>
     </row>
@@ -11531,7 +11531,7 @@
       </c>
       <c r="S134" s="4" t="inlineStr">
         <is>
-          <t>2026-08-23T20:47:28Z</t>
+          <t>2026-08-24T20:57:43Z</t>
         </is>
       </c>
     </row>
@@ -11616,7 +11616,7 @@
       </c>
       <c r="S135" s="4" t="inlineStr">
         <is>
-          <t>2026-08-23T20:47:28Z</t>
+          <t>2026-08-24T20:57:43Z</t>
         </is>
       </c>
     </row>
@@ -11701,7 +11701,7 @@
       </c>
       <c r="S136" s="4" t="inlineStr">
         <is>
-          <t>2026-08-23T20:47:28Z</t>
+          <t>2026-08-24T20:57:43Z</t>
         </is>
       </c>
     </row>
@@ -11786,7 +11786,7 @@
       </c>
       <c r="S137" s="4" t="inlineStr">
         <is>
-          <t>2026-08-23T20:47:28Z</t>
+          <t>2026-08-24T20:57:43Z</t>
         </is>
       </c>
     </row>
@@ -11871,7 +11871,7 @@
       </c>
       <c r="S138" s="4" t="inlineStr">
         <is>
-          <t>2026-08-23T20:47:28Z</t>
+          <t>2026-08-24T20:57:43Z</t>
         </is>
       </c>
     </row>
@@ -11956,7 +11956,7 @@
       </c>
       <c r="S139" s="4" t="inlineStr">
         <is>
-          <t>2026-08-23T20:47:28Z</t>
+          <t>2026-08-24T20:57:43Z</t>
         </is>
       </c>
     </row>
@@ -12041,7 +12041,7 @@
       </c>
       <c r="S140" s="4" t="inlineStr">
         <is>
-          <t>2026-08-23T20:47:28Z</t>
+          <t>2026-08-24T20:57:43Z</t>
         </is>
       </c>
     </row>
@@ -12126,7 +12126,7 @@
       </c>
       <c r="S141" s="4" t="inlineStr">
         <is>
-          <t>2026-08-23T20:47:28Z</t>
+          <t>2026-08-24T20:57:43Z</t>
         </is>
       </c>
     </row>
@@ -12258,7 +12258,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>2026-08-23T20:47:28Z</t>
+          <t>2026-08-24T20:57:43Z</t>
         </is>
       </c>
     </row>
@@ -12338,7 +12338,7 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>{"dataset_id": "bcv_pib_historico_anual", "title": "Producto interno bruto histórico anual", "table": "PIB histórico anual", "source_file": "7_1_14_anual.xls", "base": "1957/1968/1984/1997", "price_type": "Precios constantes", "measure": "Nivel", "frequency": "Anual", "period": "2017", "year": 2017, "quarter": null, "classification": "Total economía", "component": "Producto interno bruto", "value": 392393.12, "unit": "Millones de bolívares a precios constantes", "status": "", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/7_1_14_anual.xls", "fetched_at": "2026-08-23T20:47:28Z"}</t>
+          <t>{"dataset_id": "bcv_pib_historico_anual", "title": "Producto interno bruto histórico anual", "table": "PIB histórico anual", "source_file": "7_1_14_anual.xls", "base": "1957/1968/1984/1997", "price_type": "Precios constantes", "measure": "Nivel", "frequency": "Anual", "period": "2017", "year": 2017, "quarter": null, "classification": "Total economía", "component": "Producto interno bruto", "value": 392393.12, "unit": "Millones de bolívares a precios constantes", "status": "", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/7_1_14_anual.xls", "fetched_at": "2026-08-24T20:57:43Z"}</t>
         </is>
       </c>
     </row>

--- a/assets/data/bcv/excel/ove_bcv_pib_historico_anual.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_pib_historico_anual.xlsx
@@ -736,7 +736,7 @@
       </c>
       <c r="S7" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24T20:57:43Z</t>
+          <t>2026-08-25T20:55:02Z</t>
         </is>
       </c>
     </row>
@@ -821,7 +821,7 @@
       </c>
       <c r="S8" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24T20:57:43Z</t>
+          <t>2026-08-25T20:55:02Z</t>
         </is>
       </c>
     </row>
@@ -906,7 +906,7 @@
       </c>
       <c r="S9" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24T20:57:43Z</t>
+          <t>2026-08-25T20:55:02Z</t>
         </is>
       </c>
     </row>
@@ -991,7 +991,7 @@
       </c>
       <c r="S10" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24T20:57:43Z</t>
+          <t>2026-08-25T20:55:02Z</t>
         </is>
       </c>
     </row>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="S11" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24T20:57:43Z</t>
+          <t>2026-08-25T20:55:02Z</t>
         </is>
       </c>
     </row>
@@ -1161,7 +1161,7 @@
       </c>
       <c r="S12" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24T20:57:43Z</t>
+          <t>2026-08-25T20:55:02Z</t>
         </is>
       </c>
     </row>
@@ -1246,7 +1246,7 @@
       </c>
       <c r="S13" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24T20:57:43Z</t>
+          <t>2026-08-25T20:55:02Z</t>
         </is>
       </c>
     </row>
@@ -1331,7 +1331,7 @@
       </c>
       <c r="S14" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24T20:57:43Z</t>
+          <t>2026-08-25T20:55:02Z</t>
         </is>
       </c>
     </row>
@@ -1416,7 +1416,7 @@
       </c>
       <c r="S15" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24T20:57:43Z</t>
+          <t>2026-08-25T20:55:02Z</t>
         </is>
       </c>
     </row>
@@ -1501,7 +1501,7 @@
       </c>
       <c r="S16" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24T20:57:43Z</t>
+          <t>2026-08-25T20:55:02Z</t>
         </is>
       </c>
     </row>
@@ -1586,7 +1586,7 @@
       </c>
       <c r="S17" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24T20:57:43Z</t>
+          <t>2026-08-25T20:55:02Z</t>
         </is>
       </c>
     </row>
@@ -1671,7 +1671,7 @@
       </c>
       <c r="S18" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24T20:57:43Z</t>
+          <t>2026-08-25T20:55:02Z</t>
         </is>
       </c>
     </row>
@@ -1756,7 +1756,7 @@
       </c>
       <c r="S19" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24T20:57:43Z</t>
+          <t>2026-08-25T20:55:02Z</t>
         </is>
       </c>
     </row>
@@ -1841,7 +1841,7 @@
       </c>
       <c r="S20" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24T20:57:43Z</t>
+          <t>2026-08-25T20:55:02Z</t>
         </is>
       </c>
     </row>
@@ -1926,7 +1926,7 @@
       </c>
       <c r="S21" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24T20:57:43Z</t>
+          <t>2026-08-25T20:55:02Z</t>
         </is>
       </c>
     </row>
@@ -2011,7 +2011,7 @@
       </c>
       <c r="S22" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24T20:57:43Z</t>
+          <t>2026-08-25T20:55:02Z</t>
         </is>
       </c>
     </row>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="S23" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24T20:57:43Z</t>
+          <t>2026-08-25T20:55:02Z</t>
         </is>
       </c>
     </row>
@@ -2181,7 +2181,7 @@
       </c>
       <c r="S24" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24T20:57:43Z</t>
+          <t>2026-08-25T20:55:02Z</t>
         </is>
       </c>
     </row>
@@ -2266,7 +2266,7 @@
       </c>
       <c r="S25" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24T20:57:43Z</t>
+          <t>2026-08-25T20:55:02Z</t>
         </is>
       </c>
     </row>
@@ -2351,7 +2351,7 @@
       </c>
       <c r="S26" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24T20:57:43Z</t>
+          <t>2026-08-25T20:55:02Z</t>
         </is>
       </c>
     </row>
@@ -2436,7 +2436,7 @@
       </c>
       <c r="S27" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24T20:57:43Z</t>
+          <t>2026-08-25T20:55:02Z</t>
         </is>
       </c>
     </row>
@@ -2521,7 +2521,7 @@
       </c>
       <c r="S28" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24T20:57:43Z</t>
+          <t>2026-08-25T20:55:02Z</t>
         </is>
       </c>
     </row>
@@ -2606,7 +2606,7 @@
       </c>
       <c r="S29" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24T20:57:43Z</t>
+          <t>2026-08-25T20:55:02Z</t>
         </is>
       </c>
     </row>
@@ -2691,7 +2691,7 @@
       </c>
       <c r="S30" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24T20:57:43Z</t>
+          <t>2026-08-25T20:55:02Z</t>
         </is>
       </c>
     </row>
@@ -2776,7 +2776,7 @@
       </c>
       <c r="S31" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24T20:57:43Z</t>
+          <t>2026-08-25T20:55:02Z</t>
         </is>
       </c>
     </row>
@@ -2861,7 +2861,7 @@
       </c>
       <c r="S32" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24T20:57:43Z</t>
+          <t>2026-08-25T20:55:02Z</t>
         </is>
       </c>
     </row>
@@ -2946,7 +2946,7 @@
       </c>
       <c r="S33" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24T20:57:43Z</t>
+          <t>2026-08-25T20:55:02Z</t>
         </is>
       </c>
     </row>
@@ -3031,7 +3031,7 @@
       </c>
       <c r="S34" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24T20:57:43Z</t>
+          <t>2026-08-25T20:55:02Z</t>
         </is>
       </c>
     </row>
@@ -3116,7 +3116,7 @@
       </c>
       <c r="S35" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24T20:57:43Z</t>
+          <t>2026-08-25T20:55:02Z</t>
         </is>
       </c>
     </row>
@@ -3201,7 +3201,7 @@
       </c>
       <c r="S36" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24T20:57:43Z</t>
+          <t>2026-08-25T20:55:02Z</t>
         </is>
       </c>
     </row>
@@ -3286,7 +3286,7 @@
       </c>
       <c r="S37" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24T20:57:43Z</t>
+          <t>2026-08-25T20:55:02Z</t>
         </is>
       </c>
     </row>
@@ -3371,7 +3371,7 @@
       </c>
       <c r="S38" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24T20:57:43Z</t>
+          <t>2026-08-25T20:55:02Z</t>
         </is>
       </c>
     </row>
@@ -3456,7 +3456,7 @@
       </c>
       <c r="S39" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24T20:57:43Z</t>
+          <t>2026-08-25T20:55:02Z</t>
         </is>
       </c>
     </row>
@@ -3541,7 +3541,7 @@
       </c>
       <c r="S40" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24T20:57:43Z</t>
+          <t>2026-08-25T20:55:02Z</t>
         </is>
       </c>
     </row>
@@ -3626,7 +3626,7 @@
       </c>
       <c r="S41" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24T20:57:43Z</t>
+          <t>2026-08-25T20:55:02Z</t>
         </is>
       </c>
     </row>
@@ -3711,7 +3711,7 @@
       </c>
       <c r="S42" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24T20:57:43Z</t>
+          <t>2026-08-25T20:55:02Z</t>
         </is>
       </c>
     </row>
@@ -3796,7 +3796,7 @@
       </c>
       <c r="S43" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24T20:57:43Z</t>
+          <t>2026-08-25T20:55:02Z</t>
         </is>
       </c>
     </row>
@@ -3881,7 +3881,7 @@
       </c>
       <c r="S44" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24T20:57:43Z</t>
+          <t>2026-08-25T20:55:02Z</t>
         </is>
       </c>
     </row>
@@ -3966,7 +3966,7 @@
       </c>
       <c r="S45" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24T20:57:43Z</t>
+          <t>2026-08-25T20:55:02Z</t>
         </is>
       </c>
     </row>
@@ -4051,7 +4051,7 @@
       </c>
       <c r="S46" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24T20:57:43Z</t>
+          <t>2026-08-25T20:55:02Z</t>
         </is>
       </c>
     </row>
@@ -4136,7 +4136,7 @@
       </c>
       <c r="S47" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24T20:57:43Z</t>
+          <t>2026-08-25T20:55:02Z</t>
         </is>
       </c>
     </row>
@@ -4221,7 +4221,7 @@
       </c>
       <c r="S48" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24T20:57:43Z</t>
+          <t>2026-08-25T20:55:02Z</t>
         </is>
       </c>
     </row>
@@ -4306,7 +4306,7 @@
       </c>
       <c r="S49" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24T20:57:43Z</t>
+          <t>2026-08-25T20:55:02Z</t>
         </is>
       </c>
     </row>
@@ -4391,7 +4391,7 @@
       </c>
       <c r="S50" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24T20:57:43Z</t>
+          <t>2026-08-25T20:55:02Z</t>
         </is>
       </c>
     </row>
@@ -4476,7 +4476,7 @@
       </c>
       <c r="S51" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24T20:57:43Z</t>
+          <t>2026-08-25T20:55:02Z</t>
         </is>
       </c>
     </row>
@@ -4561,7 +4561,7 @@
       </c>
       <c r="S52" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24T20:57:43Z</t>
+          <t>2026-08-25T20:55:02Z</t>
         </is>
       </c>
     </row>
@@ -4646,7 +4646,7 @@
       </c>
       <c r="S53" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24T20:57:43Z</t>
+          <t>2026-08-25T20:55:02Z</t>
         </is>
       </c>
     </row>
@@ -4731,7 +4731,7 @@
       </c>
       <c r="S54" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24T20:57:43Z</t>
+          <t>2026-08-25T20:55:02Z</t>
         </is>
       </c>
     </row>
@@ -4816,7 +4816,7 @@
       </c>
       <c r="S55" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24T20:57:43Z</t>
+          <t>2026-08-25T20:55:02Z</t>
         </is>
       </c>
     </row>
@@ -4901,7 +4901,7 @@
       </c>
       <c r="S56" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24T20:57:43Z</t>
+          <t>2026-08-25T20:55:02Z</t>
         </is>
       </c>
     </row>
@@ -4986,7 +4986,7 @@
       </c>
       <c r="S57" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24T20:57:43Z</t>
+          <t>2026-08-25T20:55:02Z</t>
         </is>
       </c>
     </row>
@@ -5071,7 +5071,7 @@
       </c>
       <c r="S58" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24T20:57:43Z</t>
+          <t>2026-08-25T20:55:02Z</t>
         </is>
       </c>
     </row>
@@ -5156,7 +5156,7 @@
       </c>
       <c r="S59" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24T20:57:43Z</t>
+          <t>2026-08-25T20:55:02Z</t>
         </is>
       </c>
     </row>
@@ -5241,7 +5241,7 @@
       </c>
       <c r="S60" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24T20:57:43Z</t>
+          <t>2026-08-25T20:55:02Z</t>
         </is>
       </c>
     </row>
@@ -5326,7 +5326,7 @@
       </c>
       <c r="S61" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24T20:57:43Z</t>
+          <t>2026-08-25T20:55:02Z</t>
         </is>
       </c>
     </row>
@@ -5411,7 +5411,7 @@
       </c>
       <c r="S62" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24T20:57:43Z</t>
+          <t>2026-08-25T20:55:02Z</t>
         </is>
       </c>
     </row>
@@ -5496,7 +5496,7 @@
       </c>
       <c r="S63" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24T20:57:43Z</t>
+          <t>2026-08-25T20:55:02Z</t>
         </is>
       </c>
     </row>
@@ -5581,7 +5581,7 @@
       </c>
       <c r="S64" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24T20:57:43Z</t>
+          <t>2026-08-25T20:55:02Z</t>
         </is>
       </c>
     </row>
@@ -5666,7 +5666,7 @@
       </c>
       <c r="S65" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24T20:57:43Z</t>
+          <t>2026-08-25T20:55:02Z</t>
         </is>
       </c>
     </row>
@@ -5751,7 +5751,7 @@
       </c>
       <c r="S66" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24T20:57:43Z</t>
+          <t>2026-08-25T20:55:02Z</t>
         </is>
       </c>
     </row>
@@ -5836,7 +5836,7 @@
       </c>
       <c r="S67" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24T20:57:43Z</t>
+          <t>2026-08-25T20:55:02Z</t>
         </is>
       </c>
     </row>
@@ -5921,7 +5921,7 @@
       </c>
       <c r="S68" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24T20:57:43Z</t>
+          <t>2026-08-25T20:55:02Z</t>
         </is>
       </c>
     </row>
@@ -6006,7 +6006,7 @@
       </c>
       <c r="S69" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24T20:57:43Z</t>
+          <t>2026-08-25T20:55:02Z</t>
         </is>
       </c>
     </row>
@@ -6091,7 +6091,7 @@
       </c>
       <c r="S70" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24T20:57:43Z</t>
+          <t>2026-08-25T20:55:02Z</t>
         </is>
       </c>
     </row>
@@ -6176,7 +6176,7 @@
       </c>
       <c r="S71" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24T20:57:43Z</t>
+          <t>2026-08-25T20:55:02Z</t>
         </is>
       </c>
     </row>
@@ -6261,7 +6261,7 @@
       </c>
       <c r="S72" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24T20:57:43Z</t>
+          <t>2026-08-25T20:55:02Z</t>
         </is>
       </c>
     </row>
@@ -6346,7 +6346,7 @@
       </c>
       <c r="S73" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24T20:57:43Z</t>
+          <t>2026-08-25T20:55:02Z</t>
         </is>
       </c>
     </row>
@@ -6431,7 +6431,7 @@
       </c>
       <c r="S74" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24T20:57:43Z</t>
+          <t>2026-08-25T20:55:02Z</t>
         </is>
       </c>
     </row>
@@ -6516,7 +6516,7 @@
       </c>
       <c r="S75" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24T20:57:43Z</t>
+          <t>2026-08-25T20:55:02Z</t>
         </is>
       </c>
     </row>
@@ -6601,7 +6601,7 @@
       </c>
       <c r="S76" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24T20:57:43Z</t>
+          <t>2026-08-25T20:55:02Z</t>
         </is>
       </c>
     </row>
@@ -6686,7 +6686,7 @@
       </c>
       <c r="S77" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24T20:57:43Z</t>
+          <t>2026-08-25T20:55:02Z</t>
         </is>
       </c>
     </row>
@@ -6771,7 +6771,7 @@
       </c>
       <c r="S78" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24T20:57:43Z</t>
+          <t>2026-08-25T20:55:02Z</t>
         </is>
       </c>
     </row>
@@ -6856,7 +6856,7 @@
       </c>
       <c r="S79" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24T20:57:43Z</t>
+          <t>2026-08-25T20:55:02Z</t>
         </is>
       </c>
     </row>
@@ -6941,7 +6941,7 @@
       </c>
       <c r="S80" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24T20:57:43Z</t>
+          <t>2026-08-25T20:55:02Z</t>
         </is>
       </c>
     </row>
@@ -7026,7 +7026,7 @@
       </c>
       <c r="S81" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24T20:57:43Z</t>
+          <t>2026-08-25T20:55:02Z</t>
         </is>
       </c>
     </row>
@@ -7111,7 +7111,7 @@
       </c>
       <c r="S82" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24T20:57:43Z</t>
+          <t>2026-08-25T20:55:02Z</t>
         </is>
       </c>
     </row>
@@ -7196,7 +7196,7 @@
       </c>
       <c r="S83" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24T20:57:43Z</t>
+          <t>2026-08-25T20:55:02Z</t>
         </is>
       </c>
     </row>
@@ -7281,7 +7281,7 @@
       </c>
       <c r="S84" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24T20:57:43Z</t>
+          <t>2026-08-25T20:55:02Z</t>
         </is>
       </c>
     </row>
@@ -7366,7 +7366,7 @@
       </c>
       <c r="S85" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24T20:57:43Z</t>
+          <t>2026-08-25T20:55:02Z</t>
         </is>
       </c>
     </row>
@@ -7451,7 +7451,7 @@
       </c>
       <c r="S86" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24T20:57:43Z</t>
+          <t>2026-08-25T20:55:02Z</t>
         </is>
       </c>
     </row>
@@ -7536,7 +7536,7 @@
       </c>
       <c r="S87" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24T20:57:43Z</t>
+          <t>2026-08-25T20:55:02Z</t>
         </is>
       </c>
     </row>
@@ -7621,7 +7621,7 @@
       </c>
       <c r="S88" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24T20:57:43Z</t>
+          <t>2026-08-25T20:55:02Z</t>
         </is>
       </c>
     </row>
@@ -7706,7 +7706,7 @@
       </c>
       <c r="S89" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24T20:57:43Z</t>
+          <t>2026-08-25T20:55:02Z</t>
         </is>
       </c>
     </row>
@@ -7791,7 +7791,7 @@
       </c>
       <c r="S90" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24T20:57:43Z</t>
+          <t>2026-08-25T20:55:02Z</t>
         </is>
       </c>
     </row>
@@ -7876,7 +7876,7 @@
       </c>
       <c r="S91" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24T20:57:43Z</t>
+          <t>2026-08-25T20:55:02Z</t>
         </is>
       </c>
     </row>
@@ -7961,7 +7961,7 @@
       </c>
       <c r="S92" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24T20:57:43Z</t>
+          <t>2026-08-25T20:55:02Z</t>
         </is>
       </c>
     </row>
@@ -8046,7 +8046,7 @@
       </c>
       <c r="S93" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24T20:57:43Z</t>
+          <t>2026-08-25T20:55:02Z</t>
         </is>
       </c>
     </row>
@@ -8131,7 +8131,7 @@
       </c>
       <c r="S94" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24T20:57:43Z</t>
+          <t>2026-08-25T20:55:02Z</t>
         </is>
       </c>
     </row>
@@ -8216,7 +8216,7 @@
       </c>
       <c r="S95" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24T20:57:43Z</t>
+          <t>2026-08-25T20:55:02Z</t>
         </is>
       </c>
     </row>
@@ -8301,7 +8301,7 @@
       </c>
       <c r="S96" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24T20:57:43Z</t>
+          <t>2026-08-25T20:55:02Z</t>
         </is>
       </c>
     </row>
@@ -8386,7 +8386,7 @@
       </c>
       <c r="S97" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24T20:57:43Z</t>
+          <t>2026-08-25T20:55:02Z</t>
         </is>
       </c>
     </row>
@@ -8471,7 +8471,7 @@
       </c>
       <c r="S98" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24T20:57:43Z</t>
+          <t>2026-08-25T20:55:02Z</t>
         </is>
       </c>
     </row>
@@ -8556,7 +8556,7 @@
       </c>
       <c r="S99" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24T20:57:43Z</t>
+          <t>2026-08-25T20:55:02Z</t>
         </is>
       </c>
     </row>
@@ -8641,7 +8641,7 @@
       </c>
       <c r="S100" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24T20:57:43Z</t>
+          <t>2026-08-25T20:55:02Z</t>
         </is>
       </c>
     </row>
@@ -8726,7 +8726,7 @@
       </c>
       <c r="S101" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24T20:57:43Z</t>
+          <t>2026-08-25T20:55:02Z</t>
         </is>
       </c>
     </row>
@@ -8811,7 +8811,7 @@
       </c>
       <c r="S102" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24T20:57:43Z</t>
+          <t>2026-08-25T20:55:02Z</t>
         </is>
       </c>
     </row>
@@ -8896,7 +8896,7 @@
       </c>
       <c r="S103" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24T20:57:43Z</t>
+          <t>2026-08-25T20:55:02Z</t>
         </is>
       </c>
     </row>
@@ -8981,7 +8981,7 @@
       </c>
       <c r="S104" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24T20:57:43Z</t>
+          <t>2026-08-25T20:55:02Z</t>
         </is>
       </c>
     </row>
@@ -9066,7 +9066,7 @@
       </c>
       <c r="S105" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24T20:57:43Z</t>
+          <t>2026-08-25T20:55:02Z</t>
         </is>
       </c>
     </row>
@@ -9151,7 +9151,7 @@
       </c>
       <c r="S106" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24T20:57:43Z</t>
+          <t>2026-08-25T20:55:02Z</t>
         </is>
       </c>
     </row>
@@ -9236,7 +9236,7 @@
       </c>
       <c r="S107" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24T20:57:43Z</t>
+          <t>2026-08-25T20:55:02Z</t>
         </is>
       </c>
     </row>
@@ -9321,7 +9321,7 @@
       </c>
       <c r="S108" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24T20:57:43Z</t>
+          <t>2026-08-25T20:55:02Z</t>
         </is>
       </c>
     </row>
@@ -9406,7 +9406,7 @@
       </c>
       <c r="S109" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24T20:57:43Z</t>
+          <t>2026-08-25T20:55:02Z</t>
         </is>
       </c>
     </row>
@@ -9491,7 +9491,7 @@
       </c>
       <c r="S110" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24T20:57:43Z</t>
+          <t>2026-08-25T20:55:02Z</t>
         </is>
       </c>
     </row>
@@ -9576,7 +9576,7 @@
       </c>
       <c r="S111" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24T20:57:43Z</t>
+          <t>2026-08-25T20:55:02Z</t>
         </is>
       </c>
     </row>
@@ -9661,7 +9661,7 @@
       </c>
       <c r="S112" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24T20:57:43Z</t>
+          <t>2026-08-25T20:55:02Z</t>
         </is>
       </c>
     </row>
@@ -9746,7 +9746,7 @@
       </c>
       <c r="S113" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24T20:57:43Z</t>
+          <t>2026-08-25T20:55:02Z</t>
         </is>
       </c>
     </row>
@@ -9831,7 +9831,7 @@
       </c>
       <c r="S114" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24T20:57:43Z</t>
+          <t>2026-08-25T20:55:02Z</t>
         </is>
       </c>
     </row>
@@ -9916,7 +9916,7 @@
       </c>
       <c r="S115" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24T20:57:43Z</t>
+          <t>2026-08-25T20:55:02Z</t>
         </is>
       </c>
     </row>
@@ -10001,7 +10001,7 @@
       </c>
       <c r="S116" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24T20:57:43Z</t>
+          <t>2026-08-25T20:55:02Z</t>
         </is>
       </c>
     </row>
@@ -10086,7 +10086,7 @@
       </c>
       <c r="S117" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24T20:57:43Z</t>
+          <t>2026-08-25T20:55:02Z</t>
         </is>
       </c>
     </row>
@@ -10171,7 +10171,7 @@
       </c>
       <c r="S118" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24T20:57:43Z</t>
+          <t>2026-08-25T20:55:02Z</t>
         </is>
       </c>
     </row>
@@ -10256,7 +10256,7 @@
       </c>
       <c r="S119" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24T20:57:43Z</t>
+          <t>2026-08-25T20:55:02Z</t>
         </is>
       </c>
     </row>
@@ -10341,7 +10341,7 @@
       </c>
       <c r="S120" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24T20:57:43Z</t>
+          <t>2026-08-25T20:55:02Z</t>
         </is>
       </c>
     </row>
@@ -10426,7 +10426,7 @@
       </c>
       <c r="S121" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24T20:57:43Z</t>
+          <t>2026-08-25T20:55:02Z</t>
         </is>
       </c>
     </row>
@@ -10511,7 +10511,7 @@
       </c>
       <c r="S122" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24T20:57:43Z</t>
+          <t>2026-08-25T20:55:02Z</t>
         </is>
       </c>
     </row>
@@ -10596,7 +10596,7 @@
       </c>
       <c r="S123" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24T20:57:43Z</t>
+          <t>2026-08-25T20:55:02Z</t>
         </is>
       </c>
     </row>
@@ -10681,7 +10681,7 @@
       </c>
       <c r="S124" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24T20:57:43Z</t>
+          <t>2026-08-25T20:55:02Z</t>
         </is>
       </c>
     </row>
@@ -10766,7 +10766,7 @@
       </c>
       <c r="S125" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24T20:57:43Z</t>
+          <t>2026-08-25T20:55:02Z</t>
         </is>
       </c>
     </row>
@@ -10851,7 +10851,7 @@
       </c>
       <c r="S126" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24T20:57:43Z</t>
+          <t>2026-08-25T20:55:02Z</t>
         </is>
       </c>
     </row>
@@ -10936,7 +10936,7 @@
       </c>
       <c r="S127" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24T20:57:43Z</t>
+          <t>2026-08-25T20:55:02Z</t>
         </is>
       </c>
     </row>
@@ -11021,7 +11021,7 @@
       </c>
       <c r="S128" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24T20:57:43Z</t>
+          <t>2026-08-25T20:55:02Z</t>
         </is>
       </c>
     </row>
@@ -11106,7 +11106,7 @@
       </c>
       <c r="S129" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24T20:57:43Z</t>
+          <t>2026-08-25T20:55:02Z</t>
         </is>
       </c>
     </row>
@@ -11191,7 +11191,7 @@
       </c>
       <c r="S130" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24T20:57:43Z</t>
+          <t>2026-08-25T20:55:02Z</t>
         </is>
       </c>
     </row>
@@ -11276,7 +11276,7 @@
       </c>
       <c r="S131" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24T20:57:43Z</t>
+          <t>2026-08-25T20:55:02Z</t>
         </is>
       </c>
     </row>
@@ -11361,7 +11361,7 @@
       </c>
       <c r="S132" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24T20:57:43Z</t>
+          <t>2026-08-25T20:55:02Z</t>
         </is>
       </c>
     </row>
@@ -11446,7 +11446,7 @@
       </c>
       <c r="S133" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24T20:57:43Z</t>
+          <t>2026-08-25T20:55:02Z</t>
         </is>
       </c>
     </row>
@@ -11531,7 +11531,7 @@
       </c>
       <c r="S134" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24T20:57:43Z</t>
+          <t>2026-08-25T20:55:02Z</t>
         </is>
       </c>
     </row>
@@ -11616,7 +11616,7 @@
       </c>
       <c r="S135" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24T20:57:43Z</t>
+          <t>2026-08-25T20:55:02Z</t>
         </is>
       </c>
     </row>
@@ -11701,7 +11701,7 @@
       </c>
       <c r="S136" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24T20:57:43Z</t>
+          <t>2026-08-25T20:55:02Z</t>
         </is>
       </c>
     </row>
@@ -11786,7 +11786,7 @@
       </c>
       <c r="S137" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24T20:57:43Z</t>
+          <t>2026-08-25T20:55:02Z</t>
         </is>
       </c>
     </row>
@@ -11871,7 +11871,7 @@
       </c>
       <c r="S138" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24T20:57:43Z</t>
+          <t>2026-08-25T20:55:02Z</t>
         </is>
       </c>
     </row>
@@ -11956,7 +11956,7 @@
       </c>
       <c r="S139" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24T20:57:43Z</t>
+          <t>2026-08-25T20:55:02Z</t>
         </is>
       </c>
     </row>
@@ -12041,7 +12041,7 @@
       </c>
       <c r="S140" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24T20:57:43Z</t>
+          <t>2026-08-25T20:55:02Z</t>
         </is>
       </c>
     </row>
@@ -12126,7 +12126,7 @@
       </c>
       <c r="S141" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24T20:57:43Z</t>
+          <t>2026-08-25T20:55:02Z</t>
         </is>
       </c>
     </row>
@@ -12258,7 +12258,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24T20:57:43Z</t>
+          <t>2026-08-25T20:55:02Z</t>
         </is>
       </c>
     </row>
@@ -12338,7 +12338,7 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>{"dataset_id": "bcv_pib_historico_anual", "title": "Producto interno bruto histórico anual", "table": "PIB histórico anual", "source_file": "7_1_14_anual.xls", "base": "1957/1968/1984/1997", "price_type": "Precios constantes", "measure": "Nivel", "frequency": "Anual", "period": "2017", "year": 2017, "quarter": null, "classification": "Total economía", "component": "Producto interno bruto", "value": 392393.12, "unit": "Millones de bolívares a precios constantes", "status": "", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/7_1_14_anual.xls", "fetched_at": "2026-08-24T20:57:43Z"}</t>
+          <t>{"dataset_id": "bcv_pib_historico_anual", "title": "Producto interno bruto histórico anual", "table": "PIB histórico anual", "source_file": "7_1_14_anual.xls", "base": "1957/1968/1984/1997", "price_type": "Precios constantes", "measure": "Nivel", "frequency": "Anual", "period": "2017", "year": 2017, "quarter": null, "classification": "Total economía", "component": "Producto interno bruto", "value": 392393.12, "unit": "Millones de bolívares a precios constantes", "status": "", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/7_1_14_anual.xls", "fetched_at": "2026-08-25T20:55:02Z"}</t>
         </is>
       </c>
     </row>

--- a/assets/data/bcv/excel/ove_bcv_pib_historico_anual.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_pib_historico_anual.xlsx
@@ -736,7 +736,7 @@
       </c>
       <c r="S7" s="4" t="inlineStr">
         <is>
-          <t>2026-08-25T20:55:02Z</t>
+          <t>2026-08-26T23:55:48Z</t>
         </is>
       </c>
     </row>
@@ -821,7 +821,7 @@
       </c>
       <c r="S8" s="4" t="inlineStr">
         <is>
-          <t>2026-08-25T20:55:02Z</t>
+          <t>2026-08-26T23:55:48Z</t>
         </is>
       </c>
     </row>
@@ -906,7 +906,7 @@
       </c>
       <c r="S9" s="4" t="inlineStr">
         <is>
-          <t>2026-08-25T20:55:02Z</t>
+          <t>2026-08-26T23:55:48Z</t>
         </is>
       </c>
     </row>
@@ -991,7 +991,7 @@
       </c>
       <c r="S10" s="4" t="inlineStr">
         <is>
-          <t>2026-08-25T20:55:02Z</t>
+          <t>2026-08-26T23:55:48Z</t>
         </is>
       </c>
     </row>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="S11" s="4" t="inlineStr">
         <is>
-          <t>2026-08-25T20:55:02Z</t>
+          <t>2026-08-26T23:55:48Z</t>
         </is>
       </c>
     </row>
@@ -1161,7 +1161,7 @@
       </c>
       <c r="S12" s="4" t="inlineStr">
         <is>
-          <t>2026-08-25T20:55:02Z</t>
+          <t>2026-08-26T23:55:48Z</t>
         </is>
       </c>
     </row>
@@ -1246,7 +1246,7 @@
       </c>
       <c r="S13" s="4" t="inlineStr">
         <is>
-          <t>2026-08-25T20:55:02Z</t>
+          <t>2026-08-26T23:55:48Z</t>
         </is>
       </c>
     </row>
@@ -1331,7 +1331,7 @@
       </c>
       <c r="S14" s="4" t="inlineStr">
         <is>
-          <t>2026-08-25T20:55:02Z</t>
+          <t>2026-08-26T23:55:48Z</t>
         </is>
       </c>
     </row>
@@ -1416,7 +1416,7 @@
       </c>
       <c r="S15" s="4" t="inlineStr">
         <is>
-          <t>2026-08-25T20:55:02Z</t>
+          <t>2026-08-26T23:55:48Z</t>
         </is>
       </c>
     </row>
@@ -1501,7 +1501,7 @@
       </c>
       <c r="S16" s="4" t="inlineStr">
         <is>
-          <t>2026-08-25T20:55:02Z</t>
+          <t>2026-08-26T23:55:48Z</t>
         </is>
       </c>
     </row>
@@ -1586,7 +1586,7 @@
       </c>
       <c r="S17" s="4" t="inlineStr">
         <is>
-          <t>2026-08-25T20:55:02Z</t>
+          <t>2026-08-26T23:55:48Z</t>
         </is>
       </c>
     </row>
@@ -1671,7 +1671,7 @@
       </c>
       <c r="S18" s="4" t="inlineStr">
         <is>
-          <t>2026-08-25T20:55:02Z</t>
+          <t>2026-08-26T23:55:48Z</t>
         </is>
       </c>
     </row>
@@ -1756,7 +1756,7 @@
       </c>
       <c r="S19" s="4" t="inlineStr">
         <is>
-          <t>2026-08-25T20:55:02Z</t>
+          <t>2026-08-26T23:55:48Z</t>
         </is>
       </c>
     </row>
@@ -1841,7 +1841,7 @@
       </c>
       <c r="S20" s="4" t="inlineStr">
         <is>
-          <t>2026-08-25T20:55:02Z</t>
+          <t>2026-08-26T23:55:48Z</t>
         </is>
       </c>
     </row>
@@ -1926,7 +1926,7 @@
       </c>
       <c r="S21" s="4" t="inlineStr">
         <is>
-          <t>2026-08-25T20:55:02Z</t>
+          <t>2026-08-26T23:55:48Z</t>
         </is>
       </c>
     </row>
@@ -2011,7 +2011,7 @@
       </c>
       <c r="S22" s="4" t="inlineStr">
         <is>
-          <t>2026-08-25T20:55:02Z</t>
+          <t>2026-08-26T23:55:48Z</t>
         </is>
       </c>
     </row>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="S23" s="4" t="inlineStr">
         <is>
-          <t>2026-08-25T20:55:02Z</t>
+          <t>2026-08-26T23:55:48Z</t>
         </is>
       </c>
     </row>
@@ -2181,7 +2181,7 @@
       </c>
       <c r="S24" s="4" t="inlineStr">
         <is>
-          <t>2026-08-25T20:55:02Z</t>
+          <t>2026-08-26T23:55:48Z</t>
         </is>
       </c>
     </row>
@@ -2266,7 +2266,7 @@
       </c>
       <c r="S25" s="4" t="inlineStr">
         <is>
-          <t>2026-08-25T20:55:02Z</t>
+          <t>2026-08-26T23:55:48Z</t>
         </is>
       </c>
     </row>
@@ -2351,7 +2351,7 @@
       </c>
       <c r="S26" s="4" t="inlineStr">
         <is>
-          <t>2026-08-25T20:55:02Z</t>
+          <t>2026-08-26T23:55:48Z</t>
         </is>
       </c>
     </row>
@@ -2436,7 +2436,7 @@
       </c>
       <c r="S27" s="4" t="inlineStr">
         <is>
-          <t>2026-08-25T20:55:02Z</t>
+          <t>2026-08-26T23:55:48Z</t>
         </is>
       </c>
     </row>
@@ -2521,7 +2521,7 @@
       </c>
       <c r="S28" s="4" t="inlineStr">
         <is>
-          <t>2026-08-25T20:55:02Z</t>
+          <t>2026-08-26T23:55:48Z</t>
         </is>
       </c>
     </row>
@@ -2606,7 +2606,7 @@
       </c>
       <c r="S29" s="4" t="inlineStr">
         <is>
-          <t>2026-08-25T20:55:02Z</t>
+          <t>2026-08-26T23:55:48Z</t>
         </is>
       </c>
     </row>
@@ -2691,7 +2691,7 @@
       </c>
       <c r="S30" s="4" t="inlineStr">
         <is>
-          <t>2026-08-25T20:55:02Z</t>
+          <t>2026-08-26T23:55:48Z</t>
         </is>
       </c>
     </row>
@@ -2776,7 +2776,7 @@
       </c>
       <c r="S31" s="4" t="inlineStr">
         <is>
-          <t>2026-08-25T20:55:02Z</t>
+          <t>2026-08-26T23:55:48Z</t>
         </is>
       </c>
     </row>
@@ -2861,7 +2861,7 @@
       </c>
       <c r="S32" s="4" t="inlineStr">
         <is>
-          <t>2026-08-25T20:55:02Z</t>
+          <t>2026-08-26T23:55:48Z</t>
         </is>
       </c>
     </row>
@@ -2946,7 +2946,7 @@
       </c>
       <c r="S33" s="4" t="inlineStr">
         <is>
-          <t>2026-08-25T20:55:02Z</t>
+          <t>2026-08-26T23:55:48Z</t>
         </is>
       </c>
     </row>
@@ -3031,7 +3031,7 @@
       </c>
       <c r="S34" s="4" t="inlineStr">
         <is>
-          <t>2026-08-25T20:55:02Z</t>
+          <t>2026-08-26T23:55:48Z</t>
         </is>
       </c>
     </row>
@@ -3116,7 +3116,7 @@
       </c>
       <c r="S35" s="4" t="inlineStr">
         <is>
-          <t>2026-08-25T20:55:02Z</t>
+          <t>2026-08-26T23:55:48Z</t>
         </is>
       </c>
     </row>
@@ -3201,7 +3201,7 @@
       </c>
       <c r="S36" s="4" t="inlineStr">
         <is>
-          <t>2026-08-25T20:55:02Z</t>
+          <t>2026-08-26T23:55:48Z</t>
         </is>
       </c>
     </row>
@@ -3286,7 +3286,7 @@
       </c>
       <c r="S37" s="4" t="inlineStr">
         <is>
-          <t>2026-08-25T20:55:02Z</t>
+          <t>2026-08-26T23:55:48Z</t>
         </is>
       </c>
     </row>
@@ -3371,7 +3371,7 @@
       </c>
       <c r="S38" s="4" t="inlineStr">
         <is>
-          <t>2026-08-25T20:55:02Z</t>
+          <t>2026-08-26T23:55:48Z</t>
         </is>
       </c>
     </row>
@@ -3456,7 +3456,7 @@
       </c>
       <c r="S39" s="4" t="inlineStr">
         <is>
-          <t>2026-08-25T20:55:02Z</t>
+          <t>2026-08-26T23:55:48Z</t>
         </is>
       </c>
     </row>
@@ -3541,7 +3541,7 @@
       </c>
       <c r="S40" s="4" t="inlineStr">
         <is>
-          <t>2026-08-25T20:55:02Z</t>
+          <t>2026-08-26T23:55:48Z</t>
         </is>
       </c>
     </row>
@@ -3626,7 +3626,7 @@
       </c>
       <c r="S41" s="4" t="inlineStr">
         <is>
-          <t>2026-08-25T20:55:02Z</t>
+          <t>2026-08-26T23:55:48Z</t>
         </is>
       </c>
     </row>
@@ -3711,7 +3711,7 @@
       </c>
       <c r="S42" s="4" t="inlineStr">
         <is>
-          <t>2026-08-25T20:55:02Z</t>
+          <t>2026-08-26T23:55:48Z</t>
         </is>
       </c>
     </row>
@@ -3796,7 +3796,7 @@
       </c>
       <c r="S43" s="4" t="inlineStr">
         <is>
-          <t>2026-08-25T20:55:02Z</t>
+          <t>2026-08-26T23:55:48Z</t>
         </is>
       </c>
     </row>
@@ -3881,7 +3881,7 @@
       </c>
       <c r="S44" s="4" t="inlineStr">
         <is>
-          <t>2026-08-25T20:55:02Z</t>
+          <t>2026-08-26T23:55:48Z</t>
         </is>
       </c>
     </row>
@@ -3966,7 +3966,7 @@
       </c>
       <c r="S45" s="4" t="inlineStr">
         <is>
-          <t>2026-08-25T20:55:02Z</t>
+          <t>2026-08-26T23:55:48Z</t>
         </is>
       </c>
     </row>
@@ -4051,7 +4051,7 @@
       </c>
       <c r="S46" s="4" t="inlineStr">
         <is>
-          <t>2026-08-25T20:55:02Z</t>
+          <t>2026-08-26T23:55:48Z</t>
         </is>
       </c>
     </row>
@@ -4136,7 +4136,7 @@
       </c>
       <c r="S47" s="4" t="inlineStr">
         <is>
-          <t>2026-08-25T20:55:02Z</t>
+          <t>2026-08-26T23:55:48Z</t>
         </is>
       </c>
     </row>
@@ -4221,7 +4221,7 @@
       </c>
       <c r="S48" s="4" t="inlineStr">
         <is>
-          <t>2026-08-25T20:55:02Z</t>
+          <t>2026-08-26T23:55:48Z</t>
         </is>
       </c>
     </row>
@@ -4306,7 +4306,7 @@
       </c>
       <c r="S49" s="4" t="inlineStr">
         <is>
-          <t>2026-08-25T20:55:02Z</t>
+          <t>2026-08-26T23:55:48Z</t>
         </is>
       </c>
     </row>
@@ -4391,7 +4391,7 @@
       </c>
       <c r="S50" s="4" t="inlineStr">
         <is>
-          <t>2026-08-25T20:55:02Z</t>
+          <t>2026-08-26T23:55:48Z</t>
         </is>
       </c>
     </row>
@@ -4476,7 +4476,7 @@
       </c>
       <c r="S51" s="4" t="inlineStr">
         <is>
-          <t>2026-08-25T20:55:02Z</t>
+          <t>2026-08-26T23:55:48Z</t>
         </is>
       </c>
     </row>
@@ -4561,7 +4561,7 @@
       </c>
       <c r="S52" s="4" t="inlineStr">
         <is>
-          <t>2026-08-25T20:55:02Z</t>
+          <t>2026-08-26T23:55:48Z</t>
         </is>
       </c>
     </row>
@@ -4646,7 +4646,7 @@
       </c>
       <c r="S53" s="4" t="inlineStr">
         <is>
-          <t>2026-08-25T20:55:02Z</t>
+          <t>2026-08-26T23:55:48Z</t>
         </is>
       </c>
     </row>
@@ -4731,7 +4731,7 @@
       </c>
       <c r="S54" s="4" t="inlineStr">
         <is>
-          <t>2026-08-25T20:55:02Z</t>
+          <t>2026-08-26T23:55:48Z</t>
         </is>
       </c>
     </row>
@@ -4816,7 +4816,7 @@
       </c>
       <c r="S55" s="4" t="inlineStr">
         <is>
-          <t>2026-08-25T20:55:02Z</t>
+          <t>2026-08-26T23:55:48Z</t>
         </is>
       </c>
     </row>
@@ -4901,7 +4901,7 @@
       </c>
       <c r="S56" s="4" t="inlineStr">
         <is>
-          <t>2026-08-25T20:55:02Z</t>
+          <t>2026-08-26T23:55:48Z</t>
         </is>
       </c>
     </row>
@@ -4986,7 +4986,7 @@
       </c>
       <c r="S57" s="4" t="inlineStr">
         <is>
-          <t>2026-08-25T20:55:02Z</t>
+          <t>2026-08-26T23:55:48Z</t>
         </is>
       </c>
     </row>
@@ -5071,7 +5071,7 @@
       </c>
       <c r="S58" s="4" t="inlineStr">
         <is>
-          <t>2026-08-25T20:55:02Z</t>
+          <t>2026-08-26T23:55:48Z</t>
         </is>
       </c>
     </row>
@@ -5156,7 +5156,7 @@
       </c>
       <c r="S59" s="4" t="inlineStr">
         <is>
-          <t>2026-08-25T20:55:02Z</t>
+          <t>2026-08-26T23:55:48Z</t>
         </is>
       </c>
     </row>
@@ -5241,7 +5241,7 @@
       </c>
       <c r="S60" s="4" t="inlineStr">
         <is>
-          <t>2026-08-25T20:55:02Z</t>
+          <t>2026-08-26T23:55:48Z</t>
         </is>
       </c>
     </row>
@@ -5326,7 +5326,7 @@
       </c>
       <c r="S61" s="4" t="inlineStr">
         <is>
-          <t>2026-08-25T20:55:02Z</t>
+          <t>2026-08-26T23:55:48Z</t>
         </is>
       </c>
     </row>
@@ -5411,7 +5411,7 @@
       </c>
       <c r="S62" s="4" t="inlineStr">
         <is>
-          <t>2026-08-25T20:55:02Z</t>
+          <t>2026-08-26T23:55:48Z</t>
         </is>
       </c>
     </row>
@@ -5496,7 +5496,7 @@
       </c>
       <c r="S63" s="4" t="inlineStr">
         <is>
-          <t>2026-08-25T20:55:02Z</t>
+          <t>2026-08-26T23:55:48Z</t>
         </is>
       </c>
     </row>
@@ -5581,7 +5581,7 @@
       </c>
       <c r="S64" s="4" t="inlineStr">
         <is>
-          <t>2026-08-25T20:55:02Z</t>
+          <t>2026-08-26T23:55:48Z</t>
         </is>
       </c>
     </row>
@@ -5666,7 +5666,7 @@
       </c>
       <c r="S65" s="4" t="inlineStr">
         <is>
-          <t>2026-08-25T20:55:02Z</t>
+          <t>2026-08-26T23:55:48Z</t>
         </is>
       </c>
     </row>
@@ -5751,7 +5751,7 @@
       </c>
       <c r="S66" s="4" t="inlineStr">
         <is>
-          <t>2026-08-25T20:55:02Z</t>
+          <t>2026-08-26T23:55:48Z</t>
         </is>
       </c>
     </row>
@@ -5836,7 +5836,7 @@
       </c>
       <c r="S67" s="4" t="inlineStr">
         <is>
-          <t>2026-08-25T20:55:02Z</t>
+          <t>2026-08-26T23:55:48Z</t>
         </is>
       </c>
     </row>
@@ -5921,7 +5921,7 @@
       </c>
       <c r="S68" s="4" t="inlineStr">
         <is>
-          <t>2026-08-25T20:55:02Z</t>
+          <t>2026-08-26T23:55:48Z</t>
         </is>
       </c>
     </row>
@@ -6006,7 +6006,7 @@
       </c>
       <c r="S69" s="4" t="inlineStr">
         <is>
-          <t>2026-08-25T20:55:02Z</t>
+          <t>2026-08-26T23:55:48Z</t>
         </is>
       </c>
     </row>
@@ -6091,7 +6091,7 @@
       </c>
       <c r="S70" s="4" t="inlineStr">
         <is>
-          <t>2026-08-25T20:55:02Z</t>
+          <t>2026-08-26T23:55:48Z</t>
         </is>
       </c>
     </row>
@@ -6176,7 +6176,7 @@
       </c>
       <c r="S71" s="4" t="inlineStr">
         <is>
-          <t>2026-08-25T20:55:02Z</t>
+          <t>2026-08-26T23:55:48Z</t>
         </is>
       </c>
     </row>
@@ -6261,7 +6261,7 @@
       </c>
       <c r="S72" s="4" t="inlineStr">
         <is>
-          <t>2026-08-25T20:55:02Z</t>
+          <t>2026-08-26T23:55:48Z</t>
         </is>
       </c>
     </row>
@@ -6346,7 +6346,7 @@
       </c>
       <c r="S73" s="4" t="inlineStr">
         <is>
-          <t>2026-08-25T20:55:02Z</t>
+          <t>2026-08-26T23:55:48Z</t>
         </is>
       </c>
     </row>
@@ -6431,7 +6431,7 @@
       </c>
       <c r="S74" s="4" t="inlineStr">
         <is>
-          <t>2026-08-25T20:55:02Z</t>
+          <t>2026-08-26T23:55:48Z</t>
         </is>
       </c>
     </row>
@@ -6516,7 +6516,7 @@
       </c>
       <c r="S75" s="4" t="inlineStr">
         <is>
-          <t>2026-08-25T20:55:02Z</t>
+          <t>2026-08-26T23:55:48Z</t>
         </is>
       </c>
     </row>
@@ -6601,7 +6601,7 @@
       </c>
       <c r="S76" s="4" t="inlineStr">
         <is>
-          <t>2026-08-25T20:55:02Z</t>
+          <t>2026-08-26T23:55:48Z</t>
         </is>
       </c>
     </row>
@@ -6686,7 +6686,7 @@
       </c>
       <c r="S77" s="4" t="inlineStr">
         <is>
-          <t>2026-08-25T20:55:02Z</t>
+          <t>2026-08-26T23:55:48Z</t>
         </is>
       </c>
     </row>
@@ -6771,7 +6771,7 @@
       </c>
       <c r="S78" s="4" t="inlineStr">
         <is>
-          <t>2026-08-25T20:55:02Z</t>
+          <t>2026-08-26T23:55:48Z</t>
         </is>
       </c>
     </row>
@@ -6856,7 +6856,7 @@
       </c>
       <c r="S79" s="4" t="inlineStr">
         <is>
-          <t>2026-08-25T20:55:02Z</t>
+          <t>2026-08-26T23:55:48Z</t>
         </is>
       </c>
     </row>
@@ -6941,7 +6941,7 @@
       </c>
       <c r="S80" s="4" t="inlineStr">
         <is>
-          <t>2026-08-25T20:55:02Z</t>
+          <t>2026-08-26T23:55:48Z</t>
         </is>
       </c>
     </row>
@@ -7026,7 +7026,7 @@
       </c>
       <c r="S81" s="4" t="inlineStr">
         <is>
-          <t>2026-08-25T20:55:02Z</t>
+          <t>2026-08-26T23:55:48Z</t>
         </is>
       </c>
     </row>
@@ -7111,7 +7111,7 @@
       </c>
       <c r="S82" s="4" t="inlineStr">
         <is>
-          <t>2026-08-25T20:55:02Z</t>
+          <t>2026-08-26T23:55:48Z</t>
         </is>
       </c>
     </row>
@@ -7196,7 +7196,7 @@
       </c>
       <c r="S83" s="4" t="inlineStr">
         <is>
-          <t>2026-08-25T20:55:02Z</t>
+          <t>2026-08-26T23:55:48Z</t>
         </is>
       </c>
     </row>
@@ -7281,7 +7281,7 @@
       </c>
       <c r="S84" s="4" t="inlineStr">
         <is>
-          <t>2026-08-25T20:55:02Z</t>
+          <t>2026-08-26T23:55:48Z</t>
         </is>
       </c>
     </row>
@@ -7366,7 +7366,7 @@
       </c>
       <c r="S85" s="4" t="inlineStr">
         <is>
-          <t>2026-08-25T20:55:02Z</t>
+          <t>2026-08-26T23:55:48Z</t>
         </is>
       </c>
     </row>
@@ -7451,7 +7451,7 @@
       </c>
       <c r="S86" s="4" t="inlineStr">
         <is>
-          <t>2026-08-25T20:55:02Z</t>
+          <t>2026-08-26T23:55:48Z</t>
         </is>
       </c>
     </row>
@@ -7536,7 +7536,7 @@
       </c>
       <c r="S87" s="4" t="inlineStr">
         <is>
-          <t>2026-08-25T20:55:02Z</t>
+          <t>2026-08-26T23:55:48Z</t>
         </is>
       </c>
     </row>
@@ -7621,7 +7621,7 @@
       </c>
       <c r="S88" s="4" t="inlineStr">
         <is>
-          <t>2026-08-25T20:55:02Z</t>
+          <t>2026-08-26T23:55:48Z</t>
         </is>
       </c>
     </row>
@@ -7706,7 +7706,7 @@
       </c>
       <c r="S89" s="4" t="inlineStr">
         <is>
-          <t>2026-08-25T20:55:02Z</t>
+          <t>2026-08-26T23:55:48Z</t>
         </is>
       </c>
     </row>
@@ -7791,7 +7791,7 @@
       </c>
       <c r="S90" s="4" t="inlineStr">
         <is>
-          <t>2026-08-25T20:55:02Z</t>
+          <t>2026-08-26T23:55:48Z</t>
         </is>
       </c>
     </row>
@@ -7876,7 +7876,7 @@
       </c>
       <c r="S91" s="4" t="inlineStr">
         <is>
-          <t>2026-08-25T20:55:02Z</t>
+          <t>2026-08-26T23:55:48Z</t>
         </is>
       </c>
     </row>
@@ -7961,7 +7961,7 @@
       </c>
       <c r="S92" s="4" t="inlineStr">
         <is>
-          <t>2026-08-25T20:55:02Z</t>
+          <t>2026-08-26T23:55:48Z</t>
         </is>
       </c>
     </row>
@@ -8046,7 +8046,7 @@
       </c>
       <c r="S93" s="4" t="inlineStr">
         <is>
-          <t>2026-08-25T20:55:02Z</t>
+          <t>2026-08-26T23:55:48Z</t>
         </is>
       </c>
     </row>
@@ -8131,7 +8131,7 @@
       </c>
       <c r="S94" s="4" t="inlineStr">
         <is>
-          <t>2026-08-25T20:55:02Z</t>
+          <t>2026-08-26T23:55:48Z</t>
         </is>
       </c>
     </row>
@@ -8216,7 +8216,7 @@
       </c>
       <c r="S95" s="4" t="inlineStr">
         <is>
-          <t>2026-08-25T20:55:02Z</t>
+          <t>2026-08-26T23:55:48Z</t>
         </is>
       </c>
     </row>
@@ -8301,7 +8301,7 @@
       </c>
       <c r="S96" s="4" t="inlineStr">
         <is>
-          <t>2026-08-25T20:55:02Z</t>
+          <t>2026-08-26T23:55:48Z</t>
         </is>
       </c>
     </row>
@@ -8386,7 +8386,7 @@
       </c>
       <c r="S97" s="4" t="inlineStr">
         <is>
-          <t>2026-08-25T20:55:02Z</t>
+          <t>2026-08-26T23:55:48Z</t>
         </is>
       </c>
     </row>
@@ -8471,7 +8471,7 @@
       </c>
       <c r="S98" s="4" t="inlineStr">
         <is>
-          <t>2026-08-25T20:55:02Z</t>
+          <t>2026-08-26T23:55:48Z</t>
         </is>
       </c>
     </row>
@@ -8556,7 +8556,7 @@
       </c>
       <c r="S99" s="4" t="inlineStr">
         <is>
-          <t>2026-08-25T20:55:02Z</t>
+          <t>2026-08-26T23:55:48Z</t>
         </is>
       </c>
     </row>
@@ -8641,7 +8641,7 @@
       </c>
       <c r="S100" s="4" t="inlineStr">
         <is>
-          <t>2026-08-25T20:55:02Z</t>
+          <t>2026-08-26T23:55:48Z</t>
         </is>
       </c>
     </row>
@@ -8726,7 +8726,7 @@
       </c>
       <c r="S101" s="4" t="inlineStr">
         <is>
-          <t>2026-08-25T20:55:02Z</t>
+          <t>2026-08-26T23:55:48Z</t>
         </is>
       </c>
     </row>
@@ -8811,7 +8811,7 @@
       </c>
       <c r="S102" s="4" t="inlineStr">
         <is>
-          <t>2026-08-25T20:55:02Z</t>
+          <t>2026-08-26T23:55:48Z</t>
         </is>
       </c>
     </row>
@@ -8896,7 +8896,7 @@
       </c>
       <c r="S103" s="4" t="inlineStr">
         <is>
-          <t>2026-08-25T20:55:02Z</t>
+          <t>2026-08-26T23:55:48Z</t>
         </is>
       </c>
     </row>
@@ -8981,7 +8981,7 @@
       </c>
       <c r="S104" s="4" t="inlineStr">
         <is>
-          <t>2026-08-25T20:55:02Z</t>
+          <t>2026-08-26T23:55:48Z</t>
         </is>
       </c>
     </row>
@@ -9066,7 +9066,7 @@
       </c>
       <c r="S105" s="4" t="inlineStr">
         <is>
-          <t>2026-08-25T20:55:02Z</t>
+          <t>2026-08-26T23:55:48Z</t>
         </is>
       </c>
     </row>
@@ -9151,7 +9151,7 @@
       </c>
       <c r="S106" s="4" t="inlineStr">
         <is>
-          <t>2026-08-25T20:55:02Z</t>
+          <t>2026-08-26T23:55:48Z</t>
         </is>
       </c>
     </row>
@@ -9236,7 +9236,7 @@
       </c>
       <c r="S107" s="4" t="inlineStr">
         <is>
-          <t>2026-08-25T20:55:02Z</t>
+          <t>2026-08-26T23:55:48Z</t>
         </is>
       </c>
     </row>
@@ -9321,7 +9321,7 @@
       </c>
       <c r="S108" s="4" t="inlineStr">
         <is>
-          <t>2026-08-25T20:55:02Z</t>
+          <t>2026-08-26T23:55:48Z</t>
         </is>
       </c>
     </row>
@@ -9406,7 +9406,7 @@
       </c>
       <c r="S109" s="4" t="inlineStr">
         <is>
-          <t>2026-08-25T20:55:02Z</t>
+          <t>2026-08-26T23:55:48Z</t>
         </is>
       </c>
     </row>
@@ -9491,7 +9491,7 @@
       </c>
       <c r="S110" s="4" t="inlineStr">
         <is>
-          <t>2026-08-25T20:55:02Z</t>
+          <t>2026-08-26T23:55:48Z</t>
         </is>
       </c>
     </row>
@@ -9576,7 +9576,7 @@
       </c>
       <c r="S111" s="4" t="inlineStr">
         <is>
-          <t>2026-08-25T20:55:02Z</t>
+          <t>2026-08-26T23:55:48Z</t>
         </is>
       </c>
     </row>
@@ -9661,7 +9661,7 @@
       </c>
       <c r="S112" s="4" t="inlineStr">
         <is>
-          <t>2026-08-25T20:55:02Z</t>
+          <t>2026-08-26T23:55:48Z</t>
         </is>
       </c>
     </row>
@@ -9746,7 +9746,7 @@
       </c>
       <c r="S113" s="4" t="inlineStr">
         <is>
-          <t>2026-08-25T20:55:02Z</t>
+          <t>2026-08-26T23:55:48Z</t>
         </is>
       </c>
     </row>
@@ -9831,7 +9831,7 @@
       </c>
       <c r="S114" s="4" t="inlineStr">
         <is>
-          <t>2026-08-25T20:55:02Z</t>
+          <t>2026-08-26T23:55:48Z</t>
         </is>
       </c>
     </row>
@@ -9916,7 +9916,7 @@
       </c>
       <c r="S115" s="4" t="inlineStr">
         <is>
-          <t>2026-08-25T20:55:02Z</t>
+          <t>2026-08-26T23:55:48Z</t>
         </is>
       </c>
     </row>
@@ -10001,7 +10001,7 @@
       </c>
       <c r="S116" s="4" t="inlineStr">
         <is>
-          <t>2026-08-25T20:55:02Z</t>
+          <t>2026-08-26T23:55:48Z</t>
         </is>
       </c>
     </row>
@@ -10086,7 +10086,7 @@
       </c>
       <c r="S117" s="4" t="inlineStr">
         <is>
-          <t>2026-08-25T20:55:02Z</t>
+          <t>2026-08-26T23:55:48Z</t>
         </is>
       </c>
     </row>
@@ -10171,7 +10171,7 @@
       </c>
       <c r="S118" s="4" t="inlineStr">
         <is>
-          <t>2026-08-25T20:55:02Z</t>
+          <t>2026-08-26T23:55:48Z</t>
         </is>
       </c>
     </row>
@@ -10256,7 +10256,7 @@
       </c>
       <c r="S119" s="4" t="inlineStr">
         <is>
-          <t>2026-08-25T20:55:02Z</t>
+          <t>2026-08-26T23:55:48Z</t>
         </is>
       </c>
     </row>
@@ -10341,7 +10341,7 @@
       </c>
       <c r="S120" s="4" t="inlineStr">
         <is>
-          <t>2026-08-25T20:55:02Z</t>
+          <t>2026-08-26T23:55:48Z</t>
         </is>
       </c>
     </row>
@@ -10426,7 +10426,7 @@
       </c>
       <c r="S121" s="4" t="inlineStr">
         <is>
-          <t>2026-08-25T20:55:02Z</t>
+          <t>2026-08-26T23:55:48Z</t>
         </is>
       </c>
     </row>
@@ -10511,7 +10511,7 @@
       </c>
       <c r="S122" s="4" t="inlineStr">
         <is>
-          <t>2026-08-25T20:55:02Z</t>
+          <t>2026-08-26T23:55:48Z</t>
         </is>
       </c>
     </row>
@@ -10596,7 +10596,7 @@
       </c>
       <c r="S123" s="4" t="inlineStr">
         <is>
-          <t>2026-08-25T20:55:02Z</t>
+          <t>2026-08-26T23:55:48Z</t>
         </is>
       </c>
     </row>
@@ -10681,7 +10681,7 @@
       </c>
       <c r="S124" s="4" t="inlineStr">
         <is>
-          <t>2026-08-25T20:55:02Z</t>
+          <t>2026-08-26T23:55:48Z</t>
         </is>
       </c>
     </row>
@@ -10766,7 +10766,7 @@
       </c>
       <c r="S125" s="4" t="inlineStr">
         <is>
-          <t>2026-08-25T20:55:02Z</t>
+          <t>2026-08-26T23:55:48Z</t>
         </is>
       </c>
     </row>
@@ -10851,7 +10851,7 @@
       </c>
       <c r="S126" s="4" t="inlineStr">
         <is>
-          <t>2026-08-25T20:55:02Z</t>
+          <t>2026-08-26T23:55:48Z</t>
         </is>
       </c>
     </row>
@@ -10936,7 +10936,7 @@
       </c>
       <c r="S127" s="4" t="inlineStr">
         <is>
-          <t>2026-08-25T20:55:02Z</t>
+          <t>2026-08-26T23:55:48Z</t>
         </is>
       </c>
     </row>
@@ -11021,7 +11021,7 @@
       </c>
       <c r="S128" s="4" t="inlineStr">
         <is>
-          <t>2026-08-25T20:55:02Z</t>
+          <t>2026-08-26T23:55:48Z</t>
         </is>
       </c>
     </row>
@@ -11106,7 +11106,7 @@
       </c>
       <c r="S129" s="4" t="inlineStr">
         <is>
-          <t>2026-08-25T20:55:02Z</t>
+          <t>2026-08-26T23:55:48Z</t>
         </is>
       </c>
     </row>
@@ -11191,7 +11191,7 @@
       </c>
       <c r="S130" s="4" t="inlineStr">
         <is>
-          <t>2026-08-25T20:55:02Z</t>
+          <t>2026-08-26T23:55:48Z</t>
         </is>
       </c>
     </row>
@@ -11276,7 +11276,7 @@
       </c>
       <c r="S131" s="4" t="inlineStr">
         <is>
-          <t>2026-08-25T20:55:02Z</t>
+          <t>2026-08-26T23:55:48Z</t>
         </is>
       </c>
     </row>
@@ -11361,7 +11361,7 @@
       </c>
       <c r="S132" s="4" t="inlineStr">
         <is>
-          <t>2026-08-25T20:55:02Z</t>
+          <t>2026-08-26T23:55:48Z</t>
         </is>
       </c>
     </row>
@@ -11446,7 +11446,7 @@
       </c>
       <c r="S133" s="4" t="inlineStr">
         <is>
-          <t>2026-08-25T20:55:02Z</t>
+          <t>2026-08-26T23:55:48Z</t>
         </is>
       </c>
     </row>
@@ -11531,7 +11531,7 @@
       </c>
       <c r="S134" s="4" t="inlineStr">
         <is>
-          <t>2026-08-25T20:55:02Z</t>
+          <t>2026-08-26T23:55:48Z</t>
         </is>
       </c>
     </row>
@@ -11616,7 +11616,7 @@
       </c>
       <c r="S135" s="4" t="inlineStr">
         <is>
-          <t>2026-08-25T20:55:02Z</t>
+          <t>2026-08-26T23:55:48Z</t>
         </is>
       </c>
     </row>
@@ -11701,7 +11701,7 @@
       </c>
       <c r="S136" s="4" t="inlineStr">
         <is>
-          <t>2026-08-25T20:55:02Z</t>
+          <t>2026-08-26T23:55:48Z</t>
         </is>
       </c>
     </row>
@@ -11786,7 +11786,7 @@
       </c>
       <c r="S137" s="4" t="inlineStr">
         <is>
-          <t>2026-08-25T20:55:02Z</t>
+          <t>2026-08-26T23:55:48Z</t>
         </is>
       </c>
     </row>
@@ -11871,7 +11871,7 @@
       </c>
       <c r="S138" s="4" t="inlineStr">
         <is>
-          <t>2026-08-25T20:55:02Z</t>
+          <t>2026-08-26T23:55:48Z</t>
         </is>
       </c>
     </row>
@@ -11956,7 +11956,7 @@
       </c>
       <c r="S139" s="4" t="inlineStr">
         <is>
-          <t>2026-08-25T20:55:02Z</t>
+          <t>2026-08-26T23:55:48Z</t>
         </is>
       </c>
     </row>
@@ -12041,7 +12041,7 @@
       </c>
       <c r="S140" s="4" t="inlineStr">
         <is>
-          <t>2026-08-25T20:55:02Z</t>
+          <t>2026-08-26T23:55:48Z</t>
         </is>
       </c>
     </row>
@@ -12126,7 +12126,7 @@
       </c>
       <c r="S141" s="4" t="inlineStr">
         <is>
-          <t>2026-08-25T20:55:02Z</t>
+          <t>2026-08-26T23:55:48Z</t>
         </is>
       </c>
     </row>
@@ -12258,7 +12258,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>2026-08-25T20:55:02Z</t>
+          <t>2026-08-26T23:55:48Z</t>
         </is>
       </c>
     </row>
@@ -12338,7 +12338,7 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>{"dataset_id": "bcv_pib_historico_anual", "title": "Producto interno bruto histórico anual", "table": "PIB histórico anual", "source_file": "7_1_14_anual.xls", "base": "1957/1968/1984/1997", "price_type": "Precios constantes", "measure": "Nivel", "frequency": "Anual", "period": "2017", "year": 2017, "quarter": null, "classification": "Total economía", "component": "Producto interno bruto", "value": 392393.12, "unit": "Millones de bolívares a precios constantes", "status": "", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/7_1_14_anual.xls", "fetched_at": "2026-08-25T20:55:02Z"}</t>
+          <t>{"dataset_id": "bcv_pib_historico_anual", "title": "Producto interno bruto histórico anual", "table": "PIB histórico anual", "source_file": "7_1_14_anual.xls", "base": "1957/1968/1984/1997", "price_type": "Precios constantes", "measure": "Nivel", "frequency": "Anual", "period": "2017", "year": 2017, "quarter": null, "classification": "Total economía", "component": "Producto interno bruto", "value": 392393.12, "unit": "Millones de bolívares a precios constantes", "status": "", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/7_1_14_anual.xls", "fetched_at": "2026-08-26T23:55:48Z"}</t>
         </is>
       </c>
     </row>

--- a/assets/data/bcv/excel/ove_bcv_pib_historico_anual.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_pib_historico_anual.xlsx
@@ -736,7 +736,7 @@
       </c>
       <c r="S7" s="4" t="inlineStr">
         <is>
-          <t>2026-08-26T23:55:48Z</t>
+          <t>2026-08-28T04:25:04Z</t>
         </is>
       </c>
     </row>
@@ -821,7 +821,7 @@
       </c>
       <c r="S8" s="4" t="inlineStr">
         <is>
-          <t>2026-08-26T23:55:48Z</t>
+          <t>2026-08-28T04:25:04Z</t>
         </is>
       </c>
     </row>
@@ -906,7 +906,7 @@
       </c>
       <c r="S9" s="4" t="inlineStr">
         <is>
-          <t>2026-08-26T23:55:48Z</t>
+          <t>2026-08-28T04:25:04Z</t>
         </is>
       </c>
     </row>
@@ -991,7 +991,7 @@
       </c>
       <c r="S10" s="4" t="inlineStr">
         <is>
-          <t>2026-08-26T23:55:48Z</t>
+          <t>2026-08-28T04:25:04Z</t>
         </is>
       </c>
     </row>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="S11" s="4" t="inlineStr">
         <is>
-          <t>2026-08-26T23:55:48Z</t>
+          <t>2026-08-28T04:25:04Z</t>
         </is>
       </c>
     </row>
@@ -1161,7 +1161,7 @@
       </c>
       <c r="S12" s="4" t="inlineStr">
         <is>
-          <t>2026-08-26T23:55:48Z</t>
+          <t>2026-08-28T04:25:04Z</t>
         </is>
       </c>
     </row>
@@ -1246,7 +1246,7 @@
       </c>
       <c r="S13" s="4" t="inlineStr">
         <is>
-          <t>2026-08-26T23:55:48Z</t>
+          <t>2026-08-28T04:25:04Z</t>
         </is>
       </c>
     </row>
@@ -1331,7 +1331,7 @@
       </c>
       <c r="S14" s="4" t="inlineStr">
         <is>
-          <t>2026-08-26T23:55:48Z</t>
+          <t>2026-08-28T04:25:04Z</t>
         </is>
       </c>
     </row>
@@ -1416,7 +1416,7 @@
       </c>
       <c r="S15" s="4" t="inlineStr">
         <is>
-          <t>2026-08-26T23:55:48Z</t>
+          <t>2026-08-28T04:25:04Z</t>
         </is>
       </c>
     </row>
@@ -1501,7 +1501,7 @@
       </c>
       <c r="S16" s="4" t="inlineStr">
         <is>
-          <t>2026-08-26T23:55:48Z</t>
+          <t>2026-08-28T04:25:04Z</t>
         </is>
       </c>
     </row>
@@ -1586,7 +1586,7 @@
       </c>
       <c r="S17" s="4" t="inlineStr">
         <is>
-          <t>2026-08-26T23:55:48Z</t>
+          <t>2026-08-28T04:25:04Z</t>
         </is>
       </c>
     </row>
@@ -1671,7 +1671,7 @@
       </c>
       <c r="S18" s="4" t="inlineStr">
         <is>
-          <t>2026-08-26T23:55:48Z</t>
+          <t>2026-08-28T04:25:04Z</t>
         </is>
       </c>
     </row>
@@ -1756,7 +1756,7 @@
       </c>
       <c r="S19" s="4" t="inlineStr">
         <is>
-          <t>2026-08-26T23:55:48Z</t>
+          <t>2026-08-28T04:25:04Z</t>
         </is>
       </c>
     </row>
@@ -1841,7 +1841,7 @@
       </c>
       <c r="S20" s="4" t="inlineStr">
         <is>
-          <t>2026-08-26T23:55:48Z</t>
+          <t>2026-08-28T04:25:04Z</t>
         </is>
       </c>
     </row>
@@ -1926,7 +1926,7 @@
       </c>
       <c r="S21" s="4" t="inlineStr">
         <is>
-          <t>2026-08-26T23:55:48Z</t>
+          <t>2026-08-28T04:25:04Z</t>
         </is>
       </c>
     </row>
@@ -2011,7 +2011,7 @@
       </c>
       <c r="S22" s="4" t="inlineStr">
         <is>
-          <t>2026-08-26T23:55:48Z</t>
+          <t>2026-08-28T04:25:04Z</t>
         </is>
       </c>
     </row>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="S23" s="4" t="inlineStr">
         <is>
-          <t>2026-08-26T23:55:48Z</t>
+          <t>2026-08-28T04:25:04Z</t>
         </is>
       </c>
     </row>
@@ -2181,7 +2181,7 @@
       </c>
       <c r="S24" s="4" t="inlineStr">
         <is>
-          <t>2026-08-26T23:55:48Z</t>
+          <t>2026-08-28T04:25:04Z</t>
         </is>
       </c>
     </row>
@@ -2266,7 +2266,7 @@
       </c>
       <c r="S25" s="4" t="inlineStr">
         <is>
-          <t>2026-08-26T23:55:48Z</t>
+          <t>2026-08-28T04:25:04Z</t>
         </is>
       </c>
     </row>
@@ -2351,7 +2351,7 @@
       </c>
       <c r="S26" s="4" t="inlineStr">
         <is>
-          <t>2026-08-26T23:55:48Z</t>
+          <t>2026-08-28T04:25:04Z</t>
         </is>
       </c>
     </row>
@@ -2436,7 +2436,7 @@
       </c>
       <c r="S27" s="4" t="inlineStr">
         <is>
-          <t>2026-08-26T23:55:48Z</t>
+          <t>2026-08-28T04:25:04Z</t>
         </is>
       </c>
     </row>
@@ -2521,7 +2521,7 @@
       </c>
       <c r="S28" s="4" t="inlineStr">
         <is>
-          <t>2026-08-26T23:55:48Z</t>
+          <t>2026-08-28T04:25:04Z</t>
         </is>
       </c>
     </row>
@@ -2606,7 +2606,7 @@
       </c>
       <c r="S29" s="4" t="inlineStr">
         <is>
-          <t>2026-08-26T23:55:48Z</t>
+          <t>2026-08-28T04:25:04Z</t>
         </is>
       </c>
     </row>
@@ -2691,7 +2691,7 @@
       </c>
       <c r="S30" s="4" t="inlineStr">
         <is>
-          <t>2026-08-26T23:55:48Z</t>
+          <t>2026-08-28T04:25:04Z</t>
         </is>
       </c>
     </row>
@@ -2776,7 +2776,7 @@
       </c>
       <c r="S31" s="4" t="inlineStr">
         <is>
-          <t>2026-08-26T23:55:48Z</t>
+          <t>2026-08-28T04:25:04Z</t>
         </is>
       </c>
     </row>
@@ -2861,7 +2861,7 @@
       </c>
       <c r="S32" s="4" t="inlineStr">
         <is>
-          <t>2026-08-26T23:55:48Z</t>
+          <t>2026-08-28T04:25:04Z</t>
         </is>
       </c>
     </row>
@@ -2946,7 +2946,7 @@
       </c>
       <c r="S33" s="4" t="inlineStr">
         <is>
-          <t>2026-08-26T23:55:48Z</t>
+          <t>2026-08-28T04:25:04Z</t>
         </is>
       </c>
     </row>
@@ -3031,7 +3031,7 @@
       </c>
       <c r="S34" s="4" t="inlineStr">
         <is>
-          <t>2026-08-26T23:55:48Z</t>
+          <t>2026-08-28T04:25:04Z</t>
         </is>
       </c>
     </row>
@@ -3116,7 +3116,7 @@
       </c>
       <c r="S35" s="4" t="inlineStr">
         <is>
-          <t>2026-08-26T23:55:48Z</t>
+          <t>2026-08-28T04:25:04Z</t>
         </is>
       </c>
     </row>
@@ -3201,7 +3201,7 @@
       </c>
       <c r="S36" s="4" t="inlineStr">
         <is>
-          <t>2026-08-26T23:55:48Z</t>
+          <t>2026-08-28T04:25:04Z</t>
         </is>
       </c>
     </row>
@@ -3286,7 +3286,7 @@
       </c>
       <c r="S37" s="4" t="inlineStr">
         <is>
-          <t>2026-08-26T23:55:48Z</t>
+          <t>2026-08-28T04:25:04Z</t>
         </is>
       </c>
     </row>
@@ -3371,7 +3371,7 @@
       </c>
       <c r="S38" s="4" t="inlineStr">
         <is>
-          <t>2026-08-26T23:55:48Z</t>
+          <t>2026-08-28T04:25:04Z</t>
         </is>
       </c>
     </row>
@@ -3456,7 +3456,7 @@
       </c>
       <c r="S39" s="4" t="inlineStr">
         <is>
-          <t>2026-08-26T23:55:48Z</t>
+          <t>2026-08-28T04:25:04Z</t>
         </is>
       </c>
     </row>
@@ -3541,7 +3541,7 @@
       </c>
       <c r="S40" s="4" t="inlineStr">
         <is>
-          <t>2026-08-26T23:55:48Z</t>
+          <t>2026-08-28T04:25:04Z</t>
         </is>
       </c>
     </row>
@@ -3626,7 +3626,7 @@
       </c>
       <c r="S41" s="4" t="inlineStr">
         <is>
-          <t>2026-08-26T23:55:48Z</t>
+          <t>2026-08-28T04:25:04Z</t>
         </is>
       </c>
     </row>
@@ -3711,7 +3711,7 @@
       </c>
       <c r="S42" s="4" t="inlineStr">
         <is>
-          <t>2026-08-26T23:55:48Z</t>
+          <t>2026-08-28T04:25:04Z</t>
         </is>
       </c>
     </row>
@@ -3796,7 +3796,7 @@
       </c>
       <c r="S43" s="4" t="inlineStr">
         <is>
-          <t>2026-08-26T23:55:48Z</t>
+          <t>2026-08-28T04:25:04Z</t>
         </is>
       </c>
     </row>
@@ -3881,7 +3881,7 @@
       </c>
       <c r="S44" s="4" t="inlineStr">
         <is>
-          <t>2026-08-26T23:55:48Z</t>
+          <t>2026-08-28T04:25:04Z</t>
         </is>
       </c>
     </row>
@@ -3966,7 +3966,7 @@
       </c>
       <c r="S45" s="4" t="inlineStr">
         <is>
-          <t>2026-08-26T23:55:48Z</t>
+          <t>2026-08-28T04:25:04Z</t>
         </is>
       </c>
     </row>
@@ -4051,7 +4051,7 @@
       </c>
       <c r="S46" s="4" t="inlineStr">
         <is>
-          <t>2026-08-26T23:55:48Z</t>
+          <t>2026-08-28T04:25:04Z</t>
         </is>
       </c>
     </row>
@@ -4136,7 +4136,7 @@
       </c>
       <c r="S47" s="4" t="inlineStr">
         <is>
-          <t>2026-08-26T23:55:48Z</t>
+          <t>2026-08-28T04:25:04Z</t>
         </is>
       </c>
     </row>
@@ -4221,7 +4221,7 @@
       </c>
       <c r="S48" s="4" t="inlineStr">
         <is>
-          <t>2026-08-26T23:55:48Z</t>
+          <t>2026-08-28T04:25:04Z</t>
         </is>
       </c>
     </row>
@@ -4306,7 +4306,7 @@
       </c>
       <c r="S49" s="4" t="inlineStr">
         <is>
-          <t>2026-08-26T23:55:48Z</t>
+          <t>2026-08-28T04:25:04Z</t>
         </is>
       </c>
     </row>
@@ -4391,7 +4391,7 @@
       </c>
       <c r="S50" s="4" t="inlineStr">
         <is>
-          <t>2026-08-26T23:55:48Z</t>
+          <t>2026-08-28T04:25:04Z</t>
         </is>
       </c>
     </row>
@@ -4476,7 +4476,7 @@
       </c>
       <c r="S51" s="4" t="inlineStr">
         <is>
-          <t>2026-08-26T23:55:48Z</t>
+          <t>2026-08-28T04:25:04Z</t>
         </is>
       </c>
     </row>
@@ -4561,7 +4561,7 @@
       </c>
       <c r="S52" s="4" t="inlineStr">
         <is>
-          <t>2026-08-26T23:55:48Z</t>
+          <t>2026-08-28T04:25:04Z</t>
         </is>
       </c>
     </row>
@@ -4646,7 +4646,7 @@
       </c>
       <c r="S53" s="4" t="inlineStr">
         <is>
-          <t>2026-08-26T23:55:48Z</t>
+          <t>2026-08-28T04:25:04Z</t>
         </is>
       </c>
     </row>
@@ -4731,7 +4731,7 @@
       </c>
       <c r="S54" s="4" t="inlineStr">
         <is>
-          <t>2026-08-26T23:55:48Z</t>
+          <t>2026-08-28T04:25:04Z</t>
         </is>
       </c>
     </row>
@@ -4816,7 +4816,7 @@
       </c>
       <c r="S55" s="4" t="inlineStr">
         <is>
-          <t>2026-08-26T23:55:48Z</t>
+          <t>2026-08-28T04:25:04Z</t>
         </is>
       </c>
     </row>
@@ -4901,7 +4901,7 @@
       </c>
       <c r="S56" s="4" t="inlineStr">
         <is>
-          <t>2026-08-26T23:55:48Z</t>
+          <t>2026-08-28T04:25:04Z</t>
         </is>
       </c>
     </row>
@@ -4986,7 +4986,7 @@
       </c>
       <c r="S57" s="4" t="inlineStr">
         <is>
-          <t>2026-08-26T23:55:48Z</t>
+          <t>2026-08-28T04:25:04Z</t>
         </is>
       </c>
     </row>
@@ -5071,7 +5071,7 @@
       </c>
       <c r="S58" s="4" t="inlineStr">
         <is>
-          <t>2026-08-26T23:55:48Z</t>
+          <t>2026-08-28T04:25:04Z</t>
         </is>
       </c>
     </row>
@@ -5156,7 +5156,7 @@
       </c>
       <c r="S59" s="4" t="inlineStr">
         <is>
-          <t>2026-08-26T23:55:48Z</t>
+          <t>2026-08-28T04:25:04Z</t>
         </is>
       </c>
     </row>
@@ -5241,7 +5241,7 @@
       </c>
       <c r="S60" s="4" t="inlineStr">
         <is>
-          <t>2026-08-26T23:55:48Z</t>
+          <t>2026-08-28T04:25:04Z</t>
         </is>
       </c>
     </row>
@@ -5326,7 +5326,7 @@
       </c>
       <c r="S61" s="4" t="inlineStr">
         <is>
-          <t>2026-08-26T23:55:48Z</t>
+          <t>2026-08-28T04:25:04Z</t>
         </is>
       </c>
     </row>
@@ -5411,7 +5411,7 @@
       </c>
       <c r="S62" s="4" t="inlineStr">
         <is>
-          <t>2026-08-26T23:55:48Z</t>
+          <t>2026-08-28T04:25:04Z</t>
         </is>
       </c>
     </row>
@@ -5496,7 +5496,7 @@
       </c>
       <c r="S63" s="4" t="inlineStr">
         <is>
-          <t>2026-08-26T23:55:48Z</t>
+          <t>2026-08-28T04:25:04Z</t>
         </is>
       </c>
     </row>
@@ -5581,7 +5581,7 @@
       </c>
       <c r="S64" s="4" t="inlineStr">
         <is>
-          <t>2026-08-26T23:55:48Z</t>
+          <t>2026-08-28T04:25:04Z</t>
         </is>
       </c>
     </row>
@@ -5666,7 +5666,7 @@
       </c>
       <c r="S65" s="4" t="inlineStr">
         <is>
-          <t>2026-08-26T23:55:48Z</t>
+          <t>2026-08-28T04:25:04Z</t>
         </is>
       </c>
     </row>
@@ -5751,7 +5751,7 @@
       </c>
       <c r="S66" s="4" t="inlineStr">
         <is>
-          <t>2026-08-26T23:55:48Z</t>
+          <t>2026-08-28T04:25:04Z</t>
         </is>
       </c>
     </row>
@@ -5836,7 +5836,7 @@
       </c>
       <c r="S67" s="4" t="inlineStr">
         <is>
-          <t>2026-08-26T23:55:48Z</t>
+          <t>2026-08-28T04:25:04Z</t>
         </is>
       </c>
     </row>
@@ -5921,7 +5921,7 @@
       </c>
       <c r="S68" s="4" t="inlineStr">
         <is>
-          <t>2026-08-26T23:55:48Z</t>
+          <t>2026-08-28T04:25:04Z</t>
         </is>
       </c>
     </row>
@@ -6006,7 +6006,7 @@
       </c>
       <c r="S69" s="4" t="inlineStr">
         <is>
-          <t>2026-08-26T23:55:48Z</t>
+          <t>2026-08-28T04:25:04Z</t>
         </is>
       </c>
     </row>
@@ -6091,7 +6091,7 @@
       </c>
       <c r="S70" s="4" t="inlineStr">
         <is>
-          <t>2026-08-26T23:55:48Z</t>
+          <t>2026-08-28T04:25:04Z</t>
         </is>
       </c>
     </row>
@@ -6176,7 +6176,7 @@
       </c>
       <c r="S71" s="4" t="inlineStr">
         <is>
-          <t>2026-08-26T23:55:48Z</t>
+          <t>2026-08-28T04:25:04Z</t>
         </is>
       </c>
     </row>
@@ -6261,7 +6261,7 @@
       </c>
       <c r="S72" s="4" t="inlineStr">
         <is>
-          <t>2026-08-26T23:55:48Z</t>
+          <t>2026-08-28T04:25:04Z</t>
         </is>
       </c>
     </row>
@@ -6346,7 +6346,7 @@
       </c>
       <c r="S73" s="4" t="inlineStr">
         <is>
-          <t>2026-08-26T23:55:48Z</t>
+          <t>2026-08-28T04:25:04Z</t>
         </is>
       </c>
     </row>
@@ -6431,7 +6431,7 @@
       </c>
       <c r="S74" s="4" t="inlineStr">
         <is>
-          <t>2026-08-26T23:55:48Z</t>
+          <t>2026-08-28T04:25:04Z</t>
         </is>
       </c>
     </row>
@@ -6516,7 +6516,7 @@
       </c>
       <c r="S75" s="4" t="inlineStr">
         <is>
-          <t>2026-08-26T23:55:48Z</t>
+          <t>2026-08-28T04:25:04Z</t>
         </is>
       </c>
     </row>
@@ -6601,7 +6601,7 @@
       </c>
       <c r="S76" s="4" t="inlineStr">
         <is>
-          <t>2026-08-26T23:55:48Z</t>
+          <t>2026-08-28T04:25:04Z</t>
         </is>
       </c>
     </row>
@@ -6686,7 +6686,7 @@
       </c>
       <c r="S77" s="4" t="inlineStr">
         <is>
-          <t>2026-08-26T23:55:48Z</t>
+          <t>2026-08-28T04:25:04Z</t>
         </is>
       </c>
     </row>
@@ -6771,7 +6771,7 @@
       </c>
       <c r="S78" s="4" t="inlineStr">
         <is>
-          <t>2026-08-26T23:55:48Z</t>
+          <t>2026-08-28T04:25:04Z</t>
         </is>
       </c>
     </row>
@@ -6856,7 +6856,7 @@
       </c>
       <c r="S79" s="4" t="inlineStr">
         <is>
-          <t>2026-08-26T23:55:48Z</t>
+          <t>2026-08-28T04:25:04Z</t>
         </is>
       </c>
     </row>
@@ -6941,7 +6941,7 @@
       </c>
       <c r="S80" s="4" t="inlineStr">
         <is>
-          <t>2026-08-26T23:55:48Z</t>
+          <t>2026-08-28T04:25:04Z</t>
         </is>
       </c>
     </row>
@@ -7026,7 +7026,7 @@
       </c>
       <c r="S81" s="4" t="inlineStr">
         <is>
-          <t>2026-08-26T23:55:48Z</t>
+          <t>2026-08-28T04:25:04Z</t>
         </is>
       </c>
     </row>
@@ -7111,7 +7111,7 @@
       </c>
       <c r="S82" s="4" t="inlineStr">
         <is>
-          <t>2026-08-26T23:55:48Z</t>
+          <t>2026-08-28T04:25:04Z</t>
         </is>
       </c>
     </row>
@@ -7196,7 +7196,7 @@
       </c>
       <c r="S83" s="4" t="inlineStr">
         <is>
-          <t>2026-08-26T23:55:48Z</t>
+          <t>2026-08-28T04:25:04Z</t>
         </is>
       </c>
     </row>
@@ -7281,7 +7281,7 @@
       </c>
       <c r="S84" s="4" t="inlineStr">
         <is>
-          <t>2026-08-26T23:55:48Z</t>
+          <t>2026-08-28T04:25:04Z</t>
         </is>
       </c>
     </row>
@@ -7366,7 +7366,7 @@
       </c>
       <c r="S85" s="4" t="inlineStr">
         <is>
-          <t>2026-08-26T23:55:48Z</t>
+          <t>2026-08-28T04:25:04Z</t>
         </is>
       </c>
     </row>
@@ -7451,7 +7451,7 @@
       </c>
       <c r="S86" s="4" t="inlineStr">
         <is>
-          <t>2026-08-26T23:55:48Z</t>
+          <t>2026-08-28T04:25:04Z</t>
         </is>
       </c>
     </row>
@@ -7536,7 +7536,7 @@
       </c>
       <c r="S87" s="4" t="inlineStr">
         <is>
-          <t>2026-08-26T23:55:48Z</t>
+          <t>2026-08-28T04:25:04Z</t>
         </is>
       </c>
     </row>
@@ -7621,7 +7621,7 @@
       </c>
       <c r="S88" s="4" t="inlineStr">
         <is>
-          <t>2026-08-26T23:55:48Z</t>
+          <t>2026-08-28T04:25:04Z</t>
         </is>
       </c>
     </row>
@@ -7706,7 +7706,7 @@
       </c>
       <c r="S89" s="4" t="inlineStr">
         <is>
-          <t>2026-08-26T23:55:48Z</t>
+          <t>2026-08-28T04:25:04Z</t>
         </is>
       </c>
     </row>
@@ -7791,7 +7791,7 @@
       </c>
       <c r="S90" s="4" t="inlineStr">
         <is>
-          <t>2026-08-26T23:55:48Z</t>
+          <t>2026-08-28T04:25:04Z</t>
         </is>
       </c>
     </row>
@@ -7876,7 +7876,7 @@
       </c>
       <c r="S91" s="4" t="inlineStr">
         <is>
-          <t>2026-08-26T23:55:48Z</t>
+          <t>2026-08-28T04:25:04Z</t>
         </is>
       </c>
     </row>
@@ -7961,7 +7961,7 @@
       </c>
       <c r="S92" s="4" t="inlineStr">
         <is>
-          <t>2026-08-26T23:55:48Z</t>
+          <t>2026-08-28T04:25:04Z</t>
         </is>
       </c>
     </row>
@@ -8046,7 +8046,7 @@
       </c>
       <c r="S93" s="4" t="inlineStr">
         <is>
-          <t>2026-08-26T23:55:48Z</t>
+          <t>2026-08-28T04:25:04Z</t>
         </is>
       </c>
     </row>
@@ -8131,7 +8131,7 @@
       </c>
       <c r="S94" s="4" t="inlineStr">
         <is>
-          <t>2026-08-26T23:55:48Z</t>
+          <t>2026-08-28T04:25:04Z</t>
         </is>
       </c>
     </row>
@@ -8216,7 +8216,7 @@
       </c>
       <c r="S95" s="4" t="inlineStr">
         <is>
-          <t>2026-08-26T23:55:48Z</t>
+          <t>2026-08-28T04:25:04Z</t>
         </is>
       </c>
     </row>
@@ -8301,7 +8301,7 @@
       </c>
       <c r="S96" s="4" t="inlineStr">
         <is>
-          <t>2026-08-26T23:55:48Z</t>
+          <t>2026-08-28T04:25:04Z</t>
         </is>
       </c>
     </row>
@@ -8386,7 +8386,7 @@
       </c>
       <c r="S97" s="4" t="inlineStr">
         <is>
-          <t>2026-08-26T23:55:48Z</t>
+          <t>2026-08-28T04:25:04Z</t>
         </is>
       </c>
     </row>
@@ -8471,7 +8471,7 @@
       </c>
       <c r="S98" s="4" t="inlineStr">
         <is>
-          <t>2026-08-26T23:55:48Z</t>
+          <t>2026-08-28T04:25:04Z</t>
         </is>
       </c>
     </row>
@@ -8556,7 +8556,7 @@
       </c>
       <c r="S99" s="4" t="inlineStr">
         <is>
-          <t>2026-08-26T23:55:48Z</t>
+          <t>2026-08-28T04:25:04Z</t>
         </is>
       </c>
     </row>
@@ -8641,7 +8641,7 @@
       </c>
       <c r="S100" s="4" t="inlineStr">
         <is>
-          <t>2026-08-26T23:55:48Z</t>
+          <t>2026-08-28T04:25:04Z</t>
         </is>
       </c>
     </row>
@@ -8726,7 +8726,7 @@
       </c>
       <c r="S101" s="4" t="inlineStr">
         <is>
-          <t>2026-08-26T23:55:48Z</t>
+          <t>2026-08-28T04:25:04Z</t>
         </is>
       </c>
     </row>
@@ -8811,7 +8811,7 @@
       </c>
       <c r="S102" s="4" t="inlineStr">
         <is>
-          <t>2026-08-26T23:55:48Z</t>
+          <t>2026-08-28T04:25:04Z</t>
         </is>
       </c>
     </row>
@@ -8896,7 +8896,7 @@
       </c>
       <c r="S103" s="4" t="inlineStr">
         <is>
-          <t>2026-08-26T23:55:48Z</t>
+          <t>2026-08-28T04:25:04Z</t>
         </is>
       </c>
     </row>
@@ -8981,7 +8981,7 @@
       </c>
       <c r="S104" s="4" t="inlineStr">
         <is>
-          <t>2026-08-26T23:55:48Z</t>
+          <t>2026-08-28T04:25:04Z</t>
         </is>
       </c>
     </row>
@@ -9066,7 +9066,7 @@
       </c>
       <c r="S105" s="4" t="inlineStr">
         <is>
-          <t>2026-08-26T23:55:48Z</t>
+          <t>2026-08-28T04:25:04Z</t>
         </is>
       </c>
     </row>
@@ -9151,7 +9151,7 @@
       </c>
       <c r="S106" s="4" t="inlineStr">
         <is>
-          <t>2026-08-26T23:55:48Z</t>
+          <t>2026-08-28T04:25:04Z</t>
         </is>
       </c>
     </row>
@@ -9236,7 +9236,7 @@
       </c>
       <c r="S107" s="4" t="inlineStr">
         <is>
-          <t>2026-08-26T23:55:48Z</t>
+          <t>2026-08-28T04:25:04Z</t>
         </is>
       </c>
     </row>
@@ -9321,7 +9321,7 @@
       </c>
       <c r="S108" s="4" t="inlineStr">
         <is>
-          <t>2026-08-26T23:55:48Z</t>
+          <t>2026-08-28T04:25:04Z</t>
         </is>
       </c>
     </row>
@@ -9406,7 +9406,7 @@
       </c>
       <c r="S109" s="4" t="inlineStr">
         <is>
-          <t>2026-08-26T23:55:48Z</t>
+          <t>2026-08-28T04:25:04Z</t>
         </is>
       </c>
     </row>
@@ -9491,7 +9491,7 @@
       </c>
       <c r="S110" s="4" t="inlineStr">
         <is>
-          <t>2026-08-26T23:55:48Z</t>
+          <t>2026-08-28T04:25:04Z</t>
         </is>
       </c>
     </row>
@@ -9576,7 +9576,7 @@
       </c>
       <c r="S111" s="4" t="inlineStr">
         <is>
-          <t>2026-08-26T23:55:48Z</t>
+          <t>2026-08-28T04:25:04Z</t>
         </is>
       </c>
     </row>
@@ -9661,7 +9661,7 @@
       </c>
       <c r="S112" s="4" t="inlineStr">
         <is>
-          <t>2026-08-26T23:55:48Z</t>
+          <t>2026-08-28T04:25:04Z</t>
         </is>
       </c>
     </row>
@@ -9746,7 +9746,7 @@
       </c>
       <c r="S113" s="4" t="inlineStr">
         <is>
-          <t>2026-08-26T23:55:48Z</t>
+          <t>2026-08-28T04:25:04Z</t>
         </is>
       </c>
     </row>
@@ -9831,7 +9831,7 @@
       </c>
       <c r="S114" s="4" t="inlineStr">
         <is>
-          <t>2026-08-26T23:55:48Z</t>
+          <t>2026-08-28T04:25:04Z</t>
         </is>
       </c>
     </row>
@@ -9916,7 +9916,7 @@
       </c>
       <c r="S115" s="4" t="inlineStr">
         <is>
-          <t>2026-08-26T23:55:48Z</t>
+          <t>2026-08-28T04:25:04Z</t>
         </is>
       </c>
     </row>
@@ -10001,7 +10001,7 @@
       </c>
       <c r="S116" s="4" t="inlineStr">
         <is>
-          <t>2026-08-26T23:55:48Z</t>
+          <t>2026-08-28T04:25:04Z</t>
         </is>
       </c>
     </row>
@@ -10086,7 +10086,7 @@
       </c>
       <c r="S117" s="4" t="inlineStr">
         <is>
-          <t>2026-08-26T23:55:48Z</t>
+          <t>2026-08-28T04:25:04Z</t>
         </is>
       </c>
     </row>
@@ -10171,7 +10171,7 @@
       </c>
       <c r="S118" s="4" t="inlineStr">
         <is>
-          <t>2026-08-26T23:55:48Z</t>
+          <t>2026-08-28T04:25:04Z</t>
         </is>
       </c>
     </row>
@@ -10256,7 +10256,7 @@
       </c>
       <c r="S119" s="4" t="inlineStr">
         <is>
-          <t>2026-08-26T23:55:48Z</t>
+          <t>2026-08-28T04:25:04Z</t>
         </is>
       </c>
     </row>
@@ -10341,7 +10341,7 @@
       </c>
       <c r="S120" s="4" t="inlineStr">
         <is>
-          <t>2026-08-26T23:55:48Z</t>
+          <t>2026-08-28T04:25:04Z</t>
         </is>
       </c>
     </row>
@@ -10426,7 +10426,7 @@
       </c>
       <c r="S121" s="4" t="inlineStr">
         <is>
-          <t>2026-08-26T23:55:48Z</t>
+          <t>2026-08-28T04:25:04Z</t>
         </is>
       </c>
     </row>
@@ -10511,7 +10511,7 @@
       </c>
       <c r="S122" s="4" t="inlineStr">
         <is>
-          <t>2026-08-26T23:55:48Z</t>
+          <t>2026-08-28T04:25:04Z</t>
         </is>
       </c>
     </row>
@@ -10596,7 +10596,7 @@
       </c>
       <c r="S123" s="4" t="inlineStr">
         <is>
-          <t>2026-08-26T23:55:48Z</t>
+          <t>2026-08-28T04:25:04Z</t>
         </is>
       </c>
     </row>
@@ -10681,7 +10681,7 @@
       </c>
       <c r="S124" s="4" t="inlineStr">
         <is>
-          <t>2026-08-26T23:55:48Z</t>
+          <t>2026-08-28T04:25:04Z</t>
         </is>
       </c>
     </row>
@@ -10766,7 +10766,7 @@
       </c>
       <c r="S125" s="4" t="inlineStr">
         <is>
-          <t>2026-08-26T23:55:48Z</t>
+          <t>2026-08-28T04:25:04Z</t>
         </is>
       </c>
     </row>
@@ -10851,7 +10851,7 @@
       </c>
       <c r="S126" s="4" t="inlineStr">
         <is>
-          <t>2026-08-26T23:55:48Z</t>
+          <t>2026-08-28T04:25:04Z</t>
         </is>
       </c>
     </row>
@@ -10936,7 +10936,7 @@
       </c>
       <c r="S127" s="4" t="inlineStr">
         <is>
-          <t>2026-08-26T23:55:48Z</t>
+          <t>2026-08-28T04:25:04Z</t>
         </is>
       </c>
     </row>
@@ -11021,7 +11021,7 @@
       </c>
       <c r="S128" s="4" t="inlineStr">
         <is>
-          <t>2026-08-26T23:55:48Z</t>
+          <t>2026-08-28T04:25:04Z</t>
         </is>
       </c>
     </row>
@@ -11106,7 +11106,7 @@
       </c>
       <c r="S129" s="4" t="inlineStr">
         <is>
-          <t>2026-08-26T23:55:48Z</t>
+          <t>2026-08-28T04:25:04Z</t>
         </is>
       </c>
     </row>
@@ -11191,7 +11191,7 @@
       </c>
       <c r="S130" s="4" t="inlineStr">
         <is>
-          <t>2026-08-26T23:55:48Z</t>
+          <t>2026-08-28T04:25:04Z</t>
         </is>
       </c>
     </row>
@@ -11276,7 +11276,7 @@
       </c>
       <c r="S131" s="4" t="inlineStr">
         <is>
-          <t>2026-08-26T23:55:48Z</t>
+          <t>2026-08-28T04:25:04Z</t>
         </is>
       </c>
     </row>
@@ -11361,7 +11361,7 @@
       </c>
       <c r="S132" s="4" t="inlineStr">
         <is>
-          <t>2026-08-26T23:55:48Z</t>
+          <t>2026-08-28T04:25:04Z</t>
         </is>
       </c>
     </row>
@@ -11446,7 +11446,7 @@
       </c>
       <c r="S133" s="4" t="inlineStr">
         <is>
-          <t>2026-08-26T23:55:48Z</t>
+          <t>2026-08-28T04:25:04Z</t>
         </is>
       </c>
     </row>
@@ -11531,7 +11531,7 @@
       </c>
       <c r="S134" s="4" t="inlineStr">
         <is>
-          <t>2026-08-26T23:55:48Z</t>
+          <t>2026-08-28T04:25:04Z</t>
         </is>
       </c>
     </row>
@@ -11616,7 +11616,7 @@
       </c>
       <c r="S135" s="4" t="inlineStr">
         <is>
-          <t>2026-08-26T23:55:48Z</t>
+          <t>2026-08-28T04:25:04Z</t>
         </is>
       </c>
     </row>
@@ -11701,7 +11701,7 @@
       </c>
       <c r="S136" s="4" t="inlineStr">
         <is>
-          <t>2026-08-26T23:55:48Z</t>
+          <t>2026-08-28T04:25:04Z</t>
         </is>
       </c>
     </row>
@@ -11786,7 +11786,7 @@
       </c>
       <c r="S137" s="4" t="inlineStr">
         <is>
-          <t>2026-08-26T23:55:48Z</t>
+          <t>2026-08-28T04:25:04Z</t>
         </is>
       </c>
     </row>
@@ -11871,7 +11871,7 @@
       </c>
       <c r="S138" s="4" t="inlineStr">
         <is>
-          <t>2026-08-26T23:55:48Z</t>
+          <t>2026-08-28T04:25:04Z</t>
         </is>
       </c>
     </row>
@@ -11956,7 +11956,7 @@
       </c>
       <c r="S139" s="4" t="inlineStr">
         <is>
-          <t>2026-08-26T23:55:48Z</t>
+          <t>2026-08-28T04:25:04Z</t>
         </is>
       </c>
     </row>
@@ -12041,7 +12041,7 @@
       </c>
       <c r="S140" s="4" t="inlineStr">
         <is>
-          <t>2026-08-26T23:55:48Z</t>
+          <t>2026-08-28T04:25:04Z</t>
         </is>
       </c>
     </row>
@@ -12126,7 +12126,7 @@
       </c>
       <c r="S141" s="4" t="inlineStr">
         <is>
-          <t>2026-08-26T23:55:48Z</t>
+          <t>2026-08-28T04:25:04Z</t>
         </is>
       </c>
     </row>
@@ -12258,7 +12258,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>2026-08-26T23:55:48Z</t>
+          <t>2026-08-28T04:25:04Z</t>
         </is>
       </c>
     </row>
@@ -12338,7 +12338,7 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>{"dataset_id": "bcv_pib_historico_anual", "title": "Producto interno bruto histórico anual", "table": "PIB histórico anual", "source_file": "7_1_14_anual.xls", "base": "1957/1968/1984/1997", "price_type": "Precios constantes", "measure": "Nivel", "frequency": "Anual", "period": "2017", "year": 2017, "quarter": null, "classification": "Total economía", "component": "Producto interno bruto", "value": 392393.12, "unit": "Millones de bolívares a precios constantes", "status": "", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/7_1_14_anual.xls", "fetched_at": "2026-08-26T23:55:48Z"}</t>
+          <t>{"dataset_id": "bcv_pib_historico_anual", "title": "Producto interno bruto histórico anual", "table": "PIB histórico anual", "source_file": "7_1_14_anual.xls", "base": "1957/1968/1984/1997", "price_type": "Precios constantes", "measure": "Nivel", "frequency": "Anual", "period": "2017", "year": 2017, "quarter": null, "classification": "Total economía", "component": "Producto interno bruto", "value": 392393.12, "unit": "Millones de bolívares a precios constantes", "status": "", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/7_1_14_anual.xls", "fetched_at": "2026-08-28T04:25:04Z"}</t>
         </is>
       </c>
     </row>

--- a/assets/data/bcv/excel/ove_bcv_pib_historico_anual.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_pib_historico_anual.xlsx
@@ -736,7 +736,7 @@
       </c>
       <c r="S7" s="4" t="inlineStr">
         <is>
-          <t>2026-08-28T04:25:04Z</t>
+          <t>2026-08-29T02:52:52Z</t>
         </is>
       </c>
     </row>
@@ -821,7 +821,7 @@
       </c>
       <c r="S8" s="4" t="inlineStr">
         <is>
-          <t>2026-08-28T04:25:04Z</t>
+          <t>2026-08-29T02:52:52Z</t>
         </is>
       </c>
     </row>
@@ -906,7 +906,7 @@
       </c>
       <c r="S9" s="4" t="inlineStr">
         <is>
-          <t>2026-08-28T04:25:04Z</t>
+          <t>2026-08-29T02:52:52Z</t>
         </is>
       </c>
     </row>
@@ -991,7 +991,7 @@
       </c>
       <c r="S10" s="4" t="inlineStr">
         <is>
-          <t>2026-08-28T04:25:04Z</t>
+          <t>2026-08-29T02:52:52Z</t>
         </is>
       </c>
     </row>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="S11" s="4" t="inlineStr">
         <is>
-          <t>2026-08-28T04:25:04Z</t>
+          <t>2026-08-29T02:52:52Z</t>
         </is>
       </c>
     </row>
@@ -1161,7 +1161,7 @@
       </c>
       <c r="S12" s="4" t="inlineStr">
         <is>
-          <t>2026-08-28T04:25:04Z</t>
+          <t>2026-08-29T02:52:52Z</t>
         </is>
       </c>
     </row>
@@ -1246,7 +1246,7 @@
       </c>
       <c r="S13" s="4" t="inlineStr">
         <is>
-          <t>2026-08-28T04:25:04Z</t>
+          <t>2026-08-29T02:52:52Z</t>
         </is>
       </c>
     </row>
@@ -1331,7 +1331,7 @@
       </c>
       <c r="S14" s="4" t="inlineStr">
         <is>
-          <t>2026-08-28T04:25:04Z</t>
+          <t>2026-08-29T02:52:52Z</t>
         </is>
       </c>
     </row>
@@ -1416,7 +1416,7 @@
       </c>
       <c r="S15" s="4" t="inlineStr">
         <is>
-          <t>2026-08-28T04:25:04Z</t>
+          <t>2026-08-29T02:52:52Z</t>
         </is>
       </c>
     </row>
@@ -1501,7 +1501,7 @@
       </c>
       <c r="S16" s="4" t="inlineStr">
         <is>
-          <t>2026-08-28T04:25:04Z</t>
+          <t>2026-08-29T02:52:52Z</t>
         </is>
       </c>
     </row>
@@ -1586,7 +1586,7 @@
       </c>
       <c r="S17" s="4" t="inlineStr">
         <is>
-          <t>2026-08-28T04:25:04Z</t>
+          <t>2026-08-29T02:52:52Z</t>
         </is>
       </c>
     </row>
@@ -1671,7 +1671,7 @@
       </c>
       <c r="S18" s="4" t="inlineStr">
         <is>
-          <t>2026-08-28T04:25:04Z</t>
+          <t>2026-08-29T02:52:52Z</t>
         </is>
       </c>
     </row>
@@ -1756,7 +1756,7 @@
       </c>
       <c r="S19" s="4" t="inlineStr">
         <is>
-          <t>2026-08-28T04:25:04Z</t>
+          <t>2026-08-29T02:52:52Z</t>
         </is>
       </c>
     </row>
@@ -1841,7 +1841,7 @@
       </c>
       <c r="S20" s="4" t="inlineStr">
         <is>
-          <t>2026-08-28T04:25:04Z</t>
+          <t>2026-08-29T02:52:52Z</t>
         </is>
       </c>
     </row>
@@ -1926,7 +1926,7 @@
       </c>
       <c r="S21" s="4" t="inlineStr">
         <is>
-          <t>2026-08-28T04:25:04Z</t>
+          <t>2026-08-29T02:52:52Z</t>
         </is>
       </c>
     </row>
@@ -2011,7 +2011,7 @@
       </c>
       <c r="S22" s="4" t="inlineStr">
         <is>
-          <t>2026-08-28T04:25:04Z</t>
+          <t>2026-08-29T02:52:52Z</t>
         </is>
       </c>
     </row>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="S23" s="4" t="inlineStr">
         <is>
-          <t>2026-08-28T04:25:04Z</t>
+          <t>2026-08-29T02:52:52Z</t>
         </is>
       </c>
     </row>
@@ -2181,7 +2181,7 @@
       </c>
       <c r="S24" s="4" t="inlineStr">
         <is>
-          <t>2026-08-28T04:25:04Z</t>
+          <t>2026-08-29T02:52:52Z</t>
         </is>
       </c>
     </row>
@@ -2266,7 +2266,7 @@
       </c>
       <c r="S25" s="4" t="inlineStr">
         <is>
-          <t>2026-08-28T04:25:04Z</t>
+          <t>2026-08-29T02:52:52Z</t>
         </is>
       </c>
     </row>
@@ -2351,7 +2351,7 @@
       </c>
       <c r="S26" s="4" t="inlineStr">
         <is>
-          <t>2026-08-28T04:25:04Z</t>
+          <t>2026-08-29T02:52:52Z</t>
         </is>
       </c>
     </row>
@@ -2436,7 +2436,7 @@
       </c>
       <c r="S27" s="4" t="inlineStr">
         <is>
-          <t>2026-08-28T04:25:04Z</t>
+          <t>2026-08-29T02:52:52Z</t>
         </is>
       </c>
     </row>
@@ -2521,7 +2521,7 @@
       </c>
       <c r="S28" s="4" t="inlineStr">
         <is>
-          <t>2026-08-28T04:25:04Z</t>
+          <t>2026-08-29T02:52:52Z</t>
         </is>
       </c>
     </row>
@@ -2606,7 +2606,7 @@
       </c>
       <c r="S29" s="4" t="inlineStr">
         <is>
-          <t>2026-08-28T04:25:04Z</t>
+          <t>2026-08-29T02:52:52Z</t>
         </is>
       </c>
     </row>
@@ -2691,7 +2691,7 @@
       </c>
       <c r="S30" s="4" t="inlineStr">
         <is>
-          <t>2026-08-28T04:25:04Z</t>
+          <t>2026-08-29T02:52:52Z</t>
         </is>
       </c>
     </row>
@@ -2776,7 +2776,7 @@
       </c>
       <c r="S31" s="4" t="inlineStr">
         <is>
-          <t>2026-08-28T04:25:04Z</t>
+          <t>2026-08-29T02:52:52Z</t>
         </is>
       </c>
     </row>
@@ -2861,7 +2861,7 @@
       </c>
       <c r="S32" s="4" t="inlineStr">
         <is>
-          <t>2026-08-28T04:25:04Z</t>
+          <t>2026-08-29T02:52:52Z</t>
         </is>
       </c>
     </row>
@@ -2946,7 +2946,7 @@
       </c>
       <c r="S33" s="4" t="inlineStr">
         <is>
-          <t>2026-08-28T04:25:04Z</t>
+          <t>2026-08-29T02:52:52Z</t>
         </is>
       </c>
     </row>
@@ -3031,7 +3031,7 @@
       </c>
       <c r="S34" s="4" t="inlineStr">
         <is>
-          <t>2026-08-28T04:25:04Z</t>
+          <t>2026-08-29T02:52:52Z</t>
         </is>
       </c>
     </row>
@@ -3116,7 +3116,7 @@
       </c>
       <c r="S35" s="4" t="inlineStr">
         <is>
-          <t>2026-08-28T04:25:04Z</t>
+          <t>2026-08-29T02:52:52Z</t>
         </is>
       </c>
     </row>
@@ -3201,7 +3201,7 @@
       </c>
       <c r="S36" s="4" t="inlineStr">
         <is>
-          <t>2026-08-28T04:25:04Z</t>
+          <t>2026-08-29T02:52:52Z</t>
         </is>
       </c>
     </row>
@@ -3286,7 +3286,7 @@
       </c>
       <c r="S37" s="4" t="inlineStr">
         <is>
-          <t>2026-08-28T04:25:04Z</t>
+          <t>2026-08-29T02:52:52Z</t>
         </is>
       </c>
     </row>
@@ -3371,7 +3371,7 @@
       </c>
       <c r="S38" s="4" t="inlineStr">
         <is>
-          <t>2026-08-28T04:25:04Z</t>
+          <t>2026-08-29T02:52:52Z</t>
         </is>
       </c>
     </row>
@@ -3456,7 +3456,7 @@
       </c>
       <c r="S39" s="4" t="inlineStr">
         <is>
-          <t>2026-08-28T04:25:04Z</t>
+          <t>2026-08-29T02:52:52Z</t>
         </is>
       </c>
     </row>
@@ -3541,7 +3541,7 @@
       </c>
       <c r="S40" s="4" t="inlineStr">
         <is>
-          <t>2026-08-28T04:25:04Z</t>
+          <t>2026-08-29T02:52:52Z</t>
         </is>
       </c>
     </row>
@@ -3626,7 +3626,7 @@
       </c>
       <c r="S41" s="4" t="inlineStr">
         <is>
-          <t>2026-08-28T04:25:04Z</t>
+          <t>2026-08-29T02:52:52Z</t>
         </is>
       </c>
     </row>
@@ -3711,7 +3711,7 @@
       </c>
       <c r="S42" s="4" t="inlineStr">
         <is>
-          <t>2026-08-28T04:25:04Z</t>
+          <t>2026-08-29T02:52:52Z</t>
         </is>
       </c>
     </row>
@@ -3796,7 +3796,7 @@
       </c>
       <c r="S43" s="4" t="inlineStr">
         <is>
-          <t>2026-08-28T04:25:04Z</t>
+          <t>2026-08-29T02:52:52Z</t>
         </is>
       </c>
     </row>
@@ -3881,7 +3881,7 @@
       </c>
       <c r="S44" s="4" t="inlineStr">
         <is>
-          <t>2026-08-28T04:25:04Z</t>
+          <t>2026-08-29T02:52:52Z</t>
         </is>
       </c>
     </row>
@@ -3966,7 +3966,7 @@
       </c>
       <c r="S45" s="4" t="inlineStr">
         <is>
-          <t>2026-08-28T04:25:04Z</t>
+          <t>2026-08-29T02:52:52Z</t>
         </is>
       </c>
     </row>
@@ -4051,7 +4051,7 @@
       </c>
       <c r="S46" s="4" t="inlineStr">
         <is>
-          <t>2026-08-28T04:25:04Z</t>
+          <t>2026-08-29T02:52:52Z</t>
         </is>
       </c>
     </row>
@@ -4136,7 +4136,7 @@
       </c>
       <c r="S47" s="4" t="inlineStr">
         <is>
-          <t>2026-08-28T04:25:04Z</t>
+          <t>2026-08-29T02:52:52Z</t>
         </is>
       </c>
     </row>
@@ -4221,7 +4221,7 @@
       </c>
       <c r="S48" s="4" t="inlineStr">
         <is>
-          <t>2026-08-28T04:25:04Z</t>
+          <t>2026-08-29T02:52:52Z</t>
         </is>
       </c>
     </row>
@@ -4306,7 +4306,7 @@
       </c>
       <c r="S49" s="4" t="inlineStr">
         <is>
-          <t>2026-08-28T04:25:04Z</t>
+          <t>2026-08-29T02:52:52Z</t>
         </is>
       </c>
     </row>
@@ -4391,7 +4391,7 @@
       </c>
       <c r="S50" s="4" t="inlineStr">
         <is>
-          <t>2026-08-28T04:25:04Z</t>
+          <t>2026-08-29T02:52:52Z</t>
         </is>
       </c>
     </row>
@@ -4476,7 +4476,7 @@
       </c>
       <c r="S51" s="4" t="inlineStr">
         <is>
-          <t>2026-08-28T04:25:04Z</t>
+          <t>2026-08-29T02:52:52Z</t>
         </is>
       </c>
     </row>
@@ -4561,7 +4561,7 @@
       </c>
       <c r="S52" s="4" t="inlineStr">
         <is>
-          <t>2026-08-28T04:25:04Z</t>
+          <t>2026-08-29T02:52:52Z</t>
         </is>
       </c>
     </row>
@@ -4646,7 +4646,7 @@
       </c>
       <c r="S53" s="4" t="inlineStr">
         <is>
-          <t>2026-08-28T04:25:04Z</t>
+          <t>2026-08-29T02:52:52Z</t>
         </is>
       </c>
     </row>
@@ -4731,7 +4731,7 @@
       </c>
       <c r="S54" s="4" t="inlineStr">
         <is>
-          <t>2026-08-28T04:25:04Z</t>
+          <t>2026-08-29T02:52:52Z</t>
         </is>
       </c>
     </row>
@@ -4816,7 +4816,7 @@
       </c>
       <c r="S55" s="4" t="inlineStr">
         <is>
-          <t>2026-08-28T04:25:04Z</t>
+          <t>2026-08-29T02:52:52Z</t>
         </is>
       </c>
     </row>
@@ -4901,7 +4901,7 @@
       </c>
       <c r="S56" s="4" t="inlineStr">
         <is>
-          <t>2026-08-28T04:25:04Z</t>
+          <t>2026-08-29T02:52:52Z</t>
         </is>
       </c>
     </row>
@@ -4986,7 +4986,7 @@
       </c>
       <c r="S57" s="4" t="inlineStr">
         <is>
-          <t>2026-08-28T04:25:04Z</t>
+          <t>2026-08-29T02:52:52Z</t>
         </is>
       </c>
     </row>
@@ -5071,7 +5071,7 @@
       </c>
       <c r="S58" s="4" t="inlineStr">
         <is>
-          <t>2026-08-28T04:25:04Z</t>
+          <t>2026-08-29T02:52:52Z</t>
         </is>
       </c>
     </row>
@@ -5156,7 +5156,7 @@
       </c>
       <c r="S59" s="4" t="inlineStr">
         <is>
-          <t>2026-08-28T04:25:04Z</t>
+          <t>2026-08-29T02:52:52Z</t>
         </is>
       </c>
     </row>
@@ -5241,7 +5241,7 @@
       </c>
       <c r="S60" s="4" t="inlineStr">
         <is>
-          <t>2026-08-28T04:25:04Z</t>
+          <t>2026-08-29T02:52:52Z</t>
         </is>
       </c>
     </row>
@@ -5326,7 +5326,7 @@
       </c>
       <c r="S61" s="4" t="inlineStr">
         <is>
-          <t>2026-08-28T04:25:04Z</t>
+          <t>2026-08-29T02:52:52Z</t>
         </is>
       </c>
     </row>
@@ -5411,7 +5411,7 @@
       </c>
       <c r="S62" s="4" t="inlineStr">
         <is>
-          <t>2026-08-28T04:25:04Z</t>
+          <t>2026-08-29T02:52:52Z</t>
         </is>
       </c>
     </row>
@@ -5496,7 +5496,7 @@
       </c>
       <c r="S63" s="4" t="inlineStr">
         <is>
-          <t>2026-08-28T04:25:04Z</t>
+          <t>2026-08-29T02:52:52Z</t>
         </is>
       </c>
     </row>
@@ -5581,7 +5581,7 @@
       </c>
       <c r="S64" s="4" t="inlineStr">
         <is>
-          <t>2026-08-28T04:25:04Z</t>
+          <t>2026-08-29T02:52:52Z</t>
         </is>
       </c>
     </row>
@@ -5666,7 +5666,7 @@
       </c>
       <c r="S65" s="4" t="inlineStr">
         <is>
-          <t>2026-08-28T04:25:04Z</t>
+          <t>2026-08-29T02:52:52Z</t>
         </is>
       </c>
     </row>
@@ -5751,7 +5751,7 @@
       </c>
       <c r="S66" s="4" t="inlineStr">
         <is>
-          <t>2026-08-28T04:25:04Z</t>
+          <t>2026-08-29T02:52:52Z</t>
         </is>
       </c>
     </row>
@@ -5836,7 +5836,7 @@
       </c>
       <c r="S67" s="4" t="inlineStr">
         <is>
-          <t>2026-08-28T04:25:04Z</t>
+          <t>2026-08-29T02:52:52Z</t>
         </is>
       </c>
     </row>
@@ -5921,7 +5921,7 @@
       </c>
       <c r="S68" s="4" t="inlineStr">
         <is>
-          <t>2026-08-28T04:25:04Z</t>
+          <t>2026-08-29T02:52:52Z</t>
         </is>
       </c>
     </row>
@@ -6006,7 +6006,7 @@
       </c>
       <c r="S69" s="4" t="inlineStr">
         <is>
-          <t>2026-08-28T04:25:04Z</t>
+          <t>2026-08-29T02:52:52Z</t>
         </is>
       </c>
     </row>
@@ -6091,7 +6091,7 @@
       </c>
       <c r="S70" s="4" t="inlineStr">
         <is>
-          <t>2026-08-28T04:25:04Z</t>
+          <t>2026-08-29T02:52:52Z</t>
         </is>
       </c>
     </row>
@@ -6176,7 +6176,7 @@
       </c>
       <c r="S71" s="4" t="inlineStr">
         <is>
-          <t>2026-08-28T04:25:04Z</t>
+          <t>2026-08-29T02:52:52Z</t>
         </is>
       </c>
     </row>
@@ -6261,7 +6261,7 @@
       </c>
       <c r="S72" s="4" t="inlineStr">
         <is>
-          <t>2026-08-28T04:25:04Z</t>
+          <t>2026-08-29T02:52:52Z</t>
         </is>
       </c>
     </row>
@@ -6346,7 +6346,7 @@
       </c>
       <c r="S73" s="4" t="inlineStr">
         <is>
-          <t>2026-08-28T04:25:04Z</t>
+          <t>2026-08-29T02:52:52Z</t>
         </is>
       </c>
     </row>
@@ -6431,7 +6431,7 @@
       </c>
       <c r="S74" s="4" t="inlineStr">
         <is>
-          <t>2026-08-28T04:25:04Z</t>
+          <t>2026-08-29T02:52:52Z</t>
         </is>
       </c>
     </row>
@@ -6516,7 +6516,7 @@
       </c>
       <c r="S75" s="4" t="inlineStr">
         <is>
-          <t>2026-08-28T04:25:04Z</t>
+          <t>2026-08-29T02:52:52Z</t>
         </is>
       </c>
     </row>
@@ -6601,7 +6601,7 @@
       </c>
       <c r="S76" s="4" t="inlineStr">
         <is>
-          <t>2026-08-28T04:25:04Z</t>
+          <t>2026-08-29T02:52:52Z</t>
         </is>
       </c>
     </row>
@@ -6686,7 +6686,7 @@
       </c>
       <c r="S77" s="4" t="inlineStr">
         <is>
-          <t>2026-08-28T04:25:04Z</t>
+          <t>2026-08-29T02:52:52Z</t>
         </is>
       </c>
     </row>
@@ -6771,7 +6771,7 @@
       </c>
       <c r="S78" s="4" t="inlineStr">
         <is>
-          <t>2026-08-28T04:25:04Z</t>
+          <t>2026-08-29T02:52:52Z</t>
         </is>
       </c>
     </row>
@@ -6856,7 +6856,7 @@
       </c>
       <c r="S79" s="4" t="inlineStr">
         <is>
-          <t>2026-08-28T04:25:04Z</t>
+          <t>2026-08-29T02:52:52Z</t>
         </is>
       </c>
     </row>
@@ -6941,7 +6941,7 @@
       </c>
       <c r="S80" s="4" t="inlineStr">
         <is>
-          <t>2026-08-28T04:25:04Z</t>
+          <t>2026-08-29T02:52:52Z</t>
         </is>
       </c>
     </row>
@@ -7026,7 +7026,7 @@
       </c>
       <c r="S81" s="4" t="inlineStr">
         <is>
-          <t>2026-08-28T04:25:04Z</t>
+          <t>2026-08-29T02:52:52Z</t>
         </is>
       </c>
     </row>
@@ -7111,7 +7111,7 @@
       </c>
       <c r="S82" s="4" t="inlineStr">
         <is>
-          <t>2026-08-28T04:25:04Z</t>
+          <t>2026-08-29T02:52:52Z</t>
         </is>
       </c>
     </row>
@@ -7196,7 +7196,7 @@
       </c>
       <c r="S83" s="4" t="inlineStr">
         <is>
-          <t>2026-08-28T04:25:04Z</t>
+          <t>2026-08-29T02:52:52Z</t>
         </is>
       </c>
     </row>
@@ -7281,7 +7281,7 @@
       </c>
       <c r="S84" s="4" t="inlineStr">
         <is>
-          <t>2026-08-28T04:25:04Z</t>
+          <t>2026-08-29T02:52:52Z</t>
         </is>
       </c>
     </row>
@@ -7366,7 +7366,7 @@
       </c>
       <c r="S85" s="4" t="inlineStr">
         <is>
-          <t>2026-08-28T04:25:04Z</t>
+          <t>2026-08-29T02:52:52Z</t>
         </is>
       </c>
     </row>
@@ -7451,7 +7451,7 @@
       </c>
       <c r="S86" s="4" t="inlineStr">
         <is>
-          <t>2026-08-28T04:25:04Z</t>
+          <t>2026-08-29T02:52:52Z</t>
         </is>
       </c>
     </row>
@@ -7536,7 +7536,7 @@
       </c>
       <c r="S87" s="4" t="inlineStr">
         <is>
-          <t>2026-08-28T04:25:04Z</t>
+          <t>2026-08-29T02:52:52Z</t>
         </is>
       </c>
     </row>
@@ -7621,7 +7621,7 @@
       </c>
       <c r="S88" s="4" t="inlineStr">
         <is>
-          <t>2026-08-28T04:25:04Z</t>
+          <t>2026-08-29T02:52:52Z</t>
         </is>
       </c>
     </row>
@@ -7706,7 +7706,7 @@
       </c>
       <c r="S89" s="4" t="inlineStr">
         <is>
-          <t>2026-08-28T04:25:04Z</t>
+          <t>2026-08-29T02:52:52Z</t>
         </is>
       </c>
     </row>
@@ -7791,7 +7791,7 @@
       </c>
       <c r="S90" s="4" t="inlineStr">
         <is>
-          <t>2026-08-28T04:25:04Z</t>
+          <t>2026-08-29T02:52:52Z</t>
         </is>
       </c>
     </row>
@@ -7876,7 +7876,7 @@
       </c>
       <c r="S91" s="4" t="inlineStr">
         <is>
-          <t>2026-08-28T04:25:04Z</t>
+          <t>2026-08-29T02:52:52Z</t>
         </is>
       </c>
     </row>
@@ -7961,7 +7961,7 @@
       </c>
       <c r="S92" s="4" t="inlineStr">
         <is>
-          <t>2026-08-28T04:25:04Z</t>
+          <t>2026-08-29T02:52:52Z</t>
         </is>
       </c>
     </row>
@@ -8046,7 +8046,7 @@
       </c>
       <c r="S93" s="4" t="inlineStr">
         <is>
-          <t>2026-08-28T04:25:04Z</t>
+          <t>2026-08-29T02:52:52Z</t>
         </is>
       </c>
     </row>
@@ -8131,7 +8131,7 @@
       </c>
       <c r="S94" s="4" t="inlineStr">
         <is>
-          <t>2026-08-28T04:25:04Z</t>
+          <t>2026-08-29T02:52:52Z</t>
         </is>
       </c>
     </row>
@@ -8216,7 +8216,7 @@
       </c>
       <c r="S95" s="4" t="inlineStr">
         <is>
-          <t>2026-08-28T04:25:04Z</t>
+          <t>2026-08-29T02:52:52Z</t>
         </is>
       </c>
     </row>
@@ -8301,7 +8301,7 @@
       </c>
       <c r="S96" s="4" t="inlineStr">
         <is>
-          <t>2026-08-28T04:25:04Z</t>
+          <t>2026-08-29T02:52:52Z</t>
         </is>
       </c>
     </row>
@@ -8386,7 +8386,7 @@
       </c>
       <c r="S97" s="4" t="inlineStr">
         <is>
-          <t>2026-08-28T04:25:04Z</t>
+          <t>2026-08-29T02:52:52Z</t>
         </is>
       </c>
     </row>
@@ -8471,7 +8471,7 @@
       </c>
       <c r="S98" s="4" t="inlineStr">
         <is>
-          <t>2026-08-28T04:25:04Z</t>
+          <t>2026-08-29T02:52:52Z</t>
         </is>
       </c>
     </row>
@@ -8556,7 +8556,7 @@
       </c>
       <c r="S99" s="4" t="inlineStr">
         <is>
-          <t>2026-08-28T04:25:04Z</t>
+          <t>2026-08-29T02:52:52Z</t>
         </is>
       </c>
     </row>
@@ -8641,7 +8641,7 @@
       </c>
       <c r="S100" s="4" t="inlineStr">
         <is>
-          <t>2026-08-28T04:25:04Z</t>
+          <t>2026-08-29T02:52:52Z</t>
         </is>
       </c>
     </row>
@@ -8726,7 +8726,7 @@
       </c>
       <c r="S101" s="4" t="inlineStr">
         <is>
-          <t>2026-08-28T04:25:04Z</t>
+          <t>2026-08-29T02:52:52Z</t>
         </is>
       </c>
     </row>
@@ -8811,7 +8811,7 @@
       </c>
       <c r="S102" s="4" t="inlineStr">
         <is>
-          <t>2026-08-28T04:25:04Z</t>
+          <t>2026-08-29T02:52:52Z</t>
         </is>
       </c>
     </row>
@@ -8896,7 +8896,7 @@
       </c>
       <c r="S103" s="4" t="inlineStr">
         <is>
-          <t>2026-08-28T04:25:04Z</t>
+          <t>2026-08-29T02:52:52Z</t>
         </is>
       </c>
     </row>
@@ -8981,7 +8981,7 @@
       </c>
       <c r="S104" s="4" t="inlineStr">
         <is>
-          <t>2026-08-28T04:25:04Z</t>
+          <t>2026-08-29T02:52:52Z</t>
         </is>
       </c>
     </row>
@@ -9066,7 +9066,7 @@
       </c>
       <c r="S105" s="4" t="inlineStr">
         <is>
-          <t>2026-08-28T04:25:04Z</t>
+          <t>2026-08-29T02:52:52Z</t>
         </is>
       </c>
     </row>
@@ -9151,7 +9151,7 @@
       </c>
       <c r="S106" s="4" t="inlineStr">
         <is>
-          <t>2026-08-28T04:25:04Z</t>
+          <t>2026-08-29T02:52:52Z</t>
         </is>
       </c>
     </row>
@@ -9236,7 +9236,7 @@
       </c>
       <c r="S107" s="4" t="inlineStr">
         <is>
-          <t>2026-08-28T04:25:04Z</t>
+          <t>2026-08-29T02:52:52Z</t>
         </is>
       </c>
     </row>
@@ -9321,7 +9321,7 @@
       </c>
       <c r="S108" s="4" t="inlineStr">
         <is>
-          <t>2026-08-28T04:25:04Z</t>
+          <t>2026-08-29T02:52:52Z</t>
         </is>
       </c>
     </row>
@@ -9406,7 +9406,7 @@
       </c>
       <c r="S109" s="4" t="inlineStr">
         <is>
-          <t>2026-08-28T04:25:04Z</t>
+          <t>2026-08-29T02:52:52Z</t>
         </is>
       </c>
     </row>
@@ -9491,7 +9491,7 @@
       </c>
       <c r="S110" s="4" t="inlineStr">
         <is>
-          <t>2026-08-28T04:25:04Z</t>
+          <t>2026-08-29T02:52:52Z</t>
         </is>
       </c>
     </row>
@@ -9576,7 +9576,7 @@
       </c>
       <c r="S111" s="4" t="inlineStr">
         <is>
-          <t>2026-08-28T04:25:04Z</t>
+          <t>2026-08-29T02:52:52Z</t>
         </is>
       </c>
     </row>
@@ -9661,7 +9661,7 @@
       </c>
       <c r="S112" s="4" t="inlineStr">
         <is>
-          <t>2026-08-28T04:25:04Z</t>
+          <t>2026-08-29T02:52:52Z</t>
         </is>
       </c>
     </row>
@@ -9746,7 +9746,7 @@
       </c>
       <c r="S113" s="4" t="inlineStr">
         <is>
-          <t>2026-08-28T04:25:04Z</t>
+          <t>2026-08-29T02:52:52Z</t>
         </is>
       </c>
     </row>
@@ -9831,7 +9831,7 @@
       </c>
       <c r="S114" s="4" t="inlineStr">
         <is>
-          <t>2026-08-28T04:25:04Z</t>
+          <t>2026-08-29T02:52:52Z</t>
         </is>
       </c>
     </row>
@@ -9916,7 +9916,7 @@
       </c>
       <c r="S115" s="4" t="inlineStr">
         <is>
-          <t>2026-08-28T04:25:04Z</t>
+          <t>2026-08-29T02:52:52Z</t>
         </is>
       </c>
     </row>
@@ -10001,7 +10001,7 @@
       </c>
       <c r="S116" s="4" t="inlineStr">
         <is>
-          <t>2026-08-28T04:25:04Z</t>
+          <t>2026-08-29T02:52:52Z</t>
         </is>
       </c>
     </row>
@@ -10086,7 +10086,7 @@
       </c>
       <c r="S117" s="4" t="inlineStr">
         <is>
-          <t>2026-08-28T04:25:04Z</t>
+          <t>2026-08-29T02:52:52Z</t>
         </is>
       </c>
     </row>
@@ -10171,7 +10171,7 @@
       </c>
       <c r="S118" s="4" t="inlineStr">
         <is>
-          <t>2026-08-28T04:25:04Z</t>
+          <t>2026-08-29T02:52:52Z</t>
         </is>
       </c>
     </row>
@@ -10256,7 +10256,7 @@
       </c>
       <c r="S119" s="4" t="inlineStr">
         <is>
-          <t>2026-08-28T04:25:04Z</t>
+          <t>2026-08-29T02:52:52Z</t>
         </is>
       </c>
     </row>
@@ -10341,7 +10341,7 @@
       </c>
       <c r="S120" s="4" t="inlineStr">
         <is>
-          <t>2026-08-28T04:25:04Z</t>
+          <t>2026-08-29T02:52:52Z</t>
         </is>
       </c>
     </row>
@@ -10426,7 +10426,7 @@
       </c>
       <c r="S121" s="4" t="inlineStr">
         <is>
-          <t>2026-08-28T04:25:04Z</t>
+          <t>2026-08-29T02:52:52Z</t>
         </is>
       </c>
     </row>
@@ -10511,7 +10511,7 @@
       </c>
       <c r="S122" s="4" t="inlineStr">
         <is>
-          <t>2026-08-28T04:25:04Z</t>
+          <t>2026-08-29T02:52:52Z</t>
         </is>
       </c>
     </row>
@@ -10596,7 +10596,7 @@
       </c>
       <c r="S123" s="4" t="inlineStr">
         <is>
-          <t>2026-08-28T04:25:04Z</t>
+          <t>2026-08-29T02:52:52Z</t>
         </is>
       </c>
     </row>
@@ -10681,7 +10681,7 @@
       </c>
       <c r="S124" s="4" t="inlineStr">
         <is>
-          <t>2026-08-28T04:25:04Z</t>
+          <t>2026-08-29T02:52:52Z</t>
         </is>
       </c>
     </row>
@@ -10766,7 +10766,7 @@
       </c>
       <c r="S125" s="4" t="inlineStr">
         <is>
-          <t>2026-08-28T04:25:04Z</t>
+          <t>2026-08-29T02:52:52Z</t>
         </is>
       </c>
     </row>
@@ -10851,7 +10851,7 @@
       </c>
       <c r="S126" s="4" t="inlineStr">
         <is>
-          <t>2026-08-28T04:25:04Z</t>
+          <t>2026-08-29T02:52:52Z</t>
         </is>
       </c>
     </row>
@@ -10936,7 +10936,7 @@
       </c>
       <c r="S127" s="4" t="inlineStr">
         <is>
-          <t>2026-08-28T04:25:04Z</t>
+          <t>2026-08-29T02:52:52Z</t>
         </is>
       </c>
     </row>
@@ -11021,7 +11021,7 @@
       </c>
       <c r="S128" s="4" t="inlineStr">
         <is>
-          <t>2026-08-28T04:25:04Z</t>
+          <t>2026-08-29T02:52:52Z</t>
         </is>
       </c>
     </row>
@@ -11106,7 +11106,7 @@
       </c>
       <c r="S129" s="4" t="inlineStr">
         <is>
-          <t>2026-08-28T04:25:04Z</t>
+          <t>2026-08-29T02:52:52Z</t>
         </is>
       </c>
     </row>
@@ -11191,7 +11191,7 @@
       </c>
       <c r="S130" s="4" t="inlineStr">
         <is>
-          <t>2026-08-28T04:25:04Z</t>
+          <t>2026-08-29T02:52:52Z</t>
         </is>
       </c>
     </row>
@@ -11276,7 +11276,7 @@
       </c>
       <c r="S131" s="4" t="inlineStr">
         <is>
-          <t>2026-08-28T04:25:04Z</t>
+          <t>2026-08-29T02:52:52Z</t>
         </is>
       </c>
     </row>
@@ -11361,7 +11361,7 @@
       </c>
       <c r="S132" s="4" t="inlineStr">
         <is>
-          <t>2026-08-28T04:25:04Z</t>
+          <t>2026-08-29T02:52:52Z</t>
         </is>
       </c>
     </row>
@@ -11446,7 +11446,7 @@
       </c>
       <c r="S133" s="4" t="inlineStr">
         <is>
-          <t>2026-08-28T04:25:04Z</t>
+          <t>2026-08-29T02:52:52Z</t>
         </is>
       </c>
     </row>
@@ -11531,7 +11531,7 @@
       </c>
       <c r="S134" s="4" t="inlineStr">
         <is>
-          <t>2026-08-28T04:25:04Z</t>
+          <t>2026-08-29T02:52:52Z</t>
         </is>
       </c>
     </row>
@@ -11616,7 +11616,7 @@
       </c>
       <c r="S135" s="4" t="inlineStr">
         <is>
-          <t>2026-08-28T04:25:04Z</t>
+          <t>2026-08-29T02:52:52Z</t>
         </is>
       </c>
     </row>
@@ -11701,7 +11701,7 @@
       </c>
       <c r="S136" s="4" t="inlineStr">
         <is>
-          <t>2026-08-28T04:25:04Z</t>
+          <t>2026-08-29T02:52:52Z</t>
         </is>
       </c>
     </row>
@@ -11786,7 +11786,7 @@
       </c>
       <c r="S137" s="4" t="inlineStr">
         <is>
-          <t>2026-08-28T04:25:04Z</t>
+          <t>2026-08-29T02:52:52Z</t>
         </is>
       </c>
     </row>
@@ -11871,7 +11871,7 @@
       </c>
       <c r="S138" s="4" t="inlineStr">
         <is>
-          <t>2026-08-28T04:25:04Z</t>
+          <t>2026-08-29T02:52:52Z</t>
         </is>
       </c>
     </row>
@@ -11956,7 +11956,7 @@
       </c>
       <c r="S139" s="4" t="inlineStr">
         <is>
-          <t>2026-08-28T04:25:04Z</t>
+          <t>2026-08-29T02:52:52Z</t>
         </is>
       </c>
     </row>
@@ -12041,7 +12041,7 @@
       </c>
       <c r="S140" s="4" t="inlineStr">
         <is>
-          <t>2026-08-28T04:25:04Z</t>
+          <t>2026-08-29T02:52:52Z</t>
         </is>
       </c>
     </row>
@@ -12126,7 +12126,7 @@
       </c>
       <c r="S141" s="4" t="inlineStr">
         <is>
-          <t>2026-08-28T04:25:04Z</t>
+          <t>2026-08-29T02:52:52Z</t>
         </is>
       </c>
     </row>
@@ -12258,7 +12258,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>2026-08-28T04:25:04Z</t>
+          <t>2026-08-29T02:52:52Z</t>
         </is>
       </c>
     </row>
@@ -12338,7 +12338,7 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>{"dataset_id": "bcv_pib_historico_anual", "title": "Producto interno bruto histórico anual", "table": "PIB histórico anual", "source_file": "7_1_14_anual.xls", "base": "1957/1968/1984/1997", "price_type": "Precios constantes", "measure": "Nivel", "frequency": "Anual", "period": "2017", "year": 2017, "quarter": null, "classification": "Total economía", "component": "Producto interno bruto", "value": 392393.12, "unit": "Millones de bolívares a precios constantes", "status": "", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/7_1_14_anual.xls", "fetched_at": "2026-08-28T04:25:04Z"}</t>
+          <t>{"dataset_id": "bcv_pib_historico_anual", "title": "Producto interno bruto histórico anual", "table": "PIB histórico anual", "source_file": "7_1_14_anual.xls", "base": "1957/1968/1984/1997", "price_type": "Precios constantes", "measure": "Nivel", "frequency": "Anual", "period": "2017", "year": 2017, "quarter": null, "classification": "Total economía", "component": "Producto interno bruto", "value": 392393.12, "unit": "Millones de bolívares a precios constantes", "status": "", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/7_1_14_anual.xls", "fetched_at": "2026-08-29T02:52:52Z"}</t>
         </is>
       </c>
     </row>

--- a/assets/data/bcv/excel/ove_bcv_pib_historico_anual.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_pib_historico_anual.xlsx
@@ -736,7 +736,7 @@
       </c>
       <c r="S7" s="4" t="inlineStr">
         <is>
-          <t>2026-08-29T02:52:52Z</t>
+          <t>2026-08-29T22:43:12Z</t>
         </is>
       </c>
     </row>
@@ -821,7 +821,7 @@
       </c>
       <c r="S8" s="4" t="inlineStr">
         <is>
-          <t>2026-08-29T02:52:52Z</t>
+          <t>2026-08-29T22:43:12Z</t>
         </is>
       </c>
     </row>
@@ -906,7 +906,7 @@
       </c>
       <c r="S9" s="4" t="inlineStr">
         <is>
-          <t>2026-08-29T02:52:52Z</t>
+          <t>2026-08-29T22:43:12Z</t>
         </is>
       </c>
     </row>
@@ -991,7 +991,7 @@
       </c>
       <c r="S10" s="4" t="inlineStr">
         <is>
-          <t>2026-08-29T02:52:52Z</t>
+          <t>2026-08-29T22:43:12Z</t>
         </is>
       </c>
     </row>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="S11" s="4" t="inlineStr">
         <is>
-          <t>2026-08-29T02:52:52Z</t>
+          <t>2026-08-29T22:43:12Z</t>
         </is>
       </c>
     </row>
@@ -1161,7 +1161,7 @@
       </c>
       <c r="S12" s="4" t="inlineStr">
         <is>
-          <t>2026-08-29T02:52:52Z</t>
+          <t>2026-08-29T22:43:12Z</t>
         </is>
       </c>
     </row>
@@ -1246,7 +1246,7 @@
       </c>
       <c r="S13" s="4" t="inlineStr">
         <is>
-          <t>2026-08-29T02:52:52Z</t>
+          <t>2026-08-29T22:43:12Z</t>
         </is>
       </c>
     </row>
@@ -1331,7 +1331,7 @@
       </c>
       <c r="S14" s="4" t="inlineStr">
         <is>
-          <t>2026-08-29T02:52:52Z</t>
+          <t>2026-08-29T22:43:12Z</t>
         </is>
       </c>
     </row>
@@ -1416,7 +1416,7 @@
       </c>
       <c r="S15" s="4" t="inlineStr">
         <is>
-          <t>2026-08-29T02:52:52Z</t>
+          <t>2026-08-29T22:43:12Z</t>
         </is>
       </c>
     </row>
@@ -1501,7 +1501,7 @@
       </c>
       <c r="S16" s="4" t="inlineStr">
         <is>
-          <t>2026-08-29T02:52:52Z</t>
+          <t>2026-08-29T22:43:12Z</t>
         </is>
       </c>
     </row>
@@ -1586,7 +1586,7 @@
       </c>
       <c r="S17" s="4" t="inlineStr">
         <is>
-          <t>2026-08-29T02:52:52Z</t>
+          <t>2026-08-29T22:43:12Z</t>
         </is>
       </c>
     </row>
@@ -1671,7 +1671,7 @@
       </c>
       <c r="S18" s="4" t="inlineStr">
         <is>
-          <t>2026-08-29T02:52:52Z</t>
+          <t>2026-08-29T22:43:12Z</t>
         </is>
       </c>
     </row>
@@ -1756,7 +1756,7 @@
       </c>
       <c r="S19" s="4" t="inlineStr">
         <is>
-          <t>2026-08-29T02:52:52Z</t>
+          <t>2026-08-29T22:43:12Z</t>
         </is>
       </c>
     </row>
@@ -1841,7 +1841,7 @@
       </c>
       <c r="S20" s="4" t="inlineStr">
         <is>
-          <t>2026-08-29T02:52:52Z</t>
+          <t>2026-08-29T22:43:12Z</t>
         </is>
       </c>
     </row>
@@ -1926,7 +1926,7 @@
       </c>
       <c r="S21" s="4" t="inlineStr">
         <is>
-          <t>2026-08-29T02:52:52Z</t>
+          <t>2026-08-29T22:43:12Z</t>
         </is>
       </c>
     </row>
@@ -2011,7 +2011,7 @@
       </c>
       <c r="S22" s="4" t="inlineStr">
         <is>
-          <t>2026-08-29T02:52:52Z</t>
+          <t>2026-08-29T22:43:12Z</t>
         </is>
       </c>
     </row>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="S23" s="4" t="inlineStr">
         <is>
-          <t>2026-08-29T02:52:52Z</t>
+          <t>2026-08-29T22:43:12Z</t>
         </is>
       </c>
     </row>
@@ -2181,7 +2181,7 @@
       </c>
       <c r="S24" s="4" t="inlineStr">
         <is>
-          <t>2026-08-29T02:52:52Z</t>
+          <t>2026-08-29T22:43:12Z</t>
         </is>
       </c>
     </row>
@@ -2266,7 +2266,7 @@
       </c>
       <c r="S25" s="4" t="inlineStr">
         <is>
-          <t>2026-08-29T02:52:52Z</t>
+          <t>2026-08-29T22:43:12Z</t>
         </is>
       </c>
     </row>
@@ -2351,7 +2351,7 @@
       </c>
       <c r="S26" s="4" t="inlineStr">
         <is>
-          <t>2026-08-29T02:52:52Z</t>
+          <t>2026-08-29T22:43:12Z</t>
         </is>
       </c>
     </row>
@@ -2436,7 +2436,7 @@
       </c>
       <c r="S27" s="4" t="inlineStr">
         <is>
-          <t>2026-08-29T02:52:52Z</t>
+          <t>2026-08-29T22:43:12Z</t>
         </is>
       </c>
     </row>
@@ -2521,7 +2521,7 @@
       </c>
       <c r="S28" s="4" t="inlineStr">
         <is>
-          <t>2026-08-29T02:52:52Z</t>
+          <t>2026-08-29T22:43:12Z</t>
         </is>
       </c>
     </row>
@@ -2606,7 +2606,7 @@
       </c>
       <c r="S29" s="4" t="inlineStr">
         <is>
-          <t>2026-08-29T02:52:52Z</t>
+          <t>2026-08-29T22:43:12Z</t>
         </is>
       </c>
     </row>
@@ -2691,7 +2691,7 @@
       </c>
       <c r="S30" s="4" t="inlineStr">
         <is>
-          <t>2026-08-29T02:52:52Z</t>
+          <t>2026-08-29T22:43:12Z</t>
         </is>
       </c>
     </row>
@@ -2776,7 +2776,7 @@
       </c>
       <c r="S31" s="4" t="inlineStr">
         <is>
-          <t>2026-08-29T02:52:52Z</t>
+          <t>2026-08-29T22:43:12Z</t>
         </is>
       </c>
     </row>
@@ -2861,7 +2861,7 @@
       </c>
       <c r="S32" s="4" t="inlineStr">
         <is>
-          <t>2026-08-29T02:52:52Z</t>
+          <t>2026-08-29T22:43:12Z</t>
         </is>
       </c>
     </row>
@@ -2946,7 +2946,7 @@
       </c>
       <c r="S33" s="4" t="inlineStr">
         <is>
-          <t>2026-08-29T02:52:52Z</t>
+          <t>2026-08-29T22:43:12Z</t>
         </is>
       </c>
     </row>
@@ -3031,7 +3031,7 @@
       </c>
       <c r="S34" s="4" t="inlineStr">
         <is>
-          <t>2026-08-29T02:52:52Z</t>
+          <t>2026-08-29T22:43:12Z</t>
         </is>
       </c>
     </row>
@@ -3116,7 +3116,7 @@
       </c>
       <c r="S35" s="4" t="inlineStr">
         <is>
-          <t>2026-08-29T02:52:52Z</t>
+          <t>2026-08-29T22:43:12Z</t>
         </is>
       </c>
     </row>
@@ -3201,7 +3201,7 @@
       </c>
       <c r="S36" s="4" t="inlineStr">
         <is>
-          <t>2026-08-29T02:52:52Z</t>
+          <t>2026-08-29T22:43:12Z</t>
         </is>
       </c>
     </row>
@@ -3286,7 +3286,7 @@
       </c>
       <c r="S37" s="4" t="inlineStr">
         <is>
-          <t>2026-08-29T02:52:52Z</t>
+          <t>2026-08-29T22:43:12Z</t>
         </is>
       </c>
     </row>
@@ -3371,7 +3371,7 @@
       </c>
       <c r="S38" s="4" t="inlineStr">
         <is>
-          <t>2026-08-29T02:52:52Z</t>
+          <t>2026-08-29T22:43:12Z</t>
         </is>
       </c>
     </row>
@@ -3456,7 +3456,7 @@
       </c>
       <c r="S39" s="4" t="inlineStr">
         <is>
-          <t>2026-08-29T02:52:52Z</t>
+          <t>2026-08-29T22:43:12Z</t>
         </is>
       </c>
     </row>
@@ -3541,7 +3541,7 @@
       </c>
       <c r="S40" s="4" t="inlineStr">
         <is>
-          <t>2026-08-29T02:52:52Z</t>
+          <t>2026-08-29T22:43:12Z</t>
         </is>
       </c>
     </row>
@@ -3626,7 +3626,7 @@
       </c>
       <c r="S41" s="4" t="inlineStr">
         <is>
-          <t>2026-08-29T02:52:52Z</t>
+          <t>2026-08-29T22:43:12Z</t>
         </is>
       </c>
     </row>
@@ -3711,7 +3711,7 @@
       </c>
       <c r="S42" s="4" t="inlineStr">
         <is>
-          <t>2026-08-29T02:52:52Z</t>
+          <t>2026-08-29T22:43:12Z</t>
         </is>
       </c>
     </row>
@@ -3796,7 +3796,7 @@
       </c>
       <c r="S43" s="4" t="inlineStr">
         <is>
-          <t>2026-08-29T02:52:52Z</t>
+          <t>2026-08-29T22:43:12Z</t>
         </is>
       </c>
     </row>
@@ -3881,7 +3881,7 @@
       </c>
       <c r="S44" s="4" t="inlineStr">
         <is>
-          <t>2026-08-29T02:52:52Z</t>
+          <t>2026-08-29T22:43:12Z</t>
         </is>
       </c>
     </row>
@@ -3966,7 +3966,7 @@
       </c>
       <c r="S45" s="4" t="inlineStr">
         <is>
-          <t>2026-08-29T02:52:52Z</t>
+          <t>2026-08-29T22:43:12Z</t>
         </is>
       </c>
     </row>
@@ -4051,7 +4051,7 @@
       </c>
       <c r="S46" s="4" t="inlineStr">
         <is>
-          <t>2026-08-29T02:52:52Z</t>
+          <t>2026-08-29T22:43:12Z</t>
         </is>
       </c>
     </row>
@@ -4136,7 +4136,7 @@
       </c>
       <c r="S47" s="4" t="inlineStr">
         <is>
-          <t>2026-08-29T02:52:52Z</t>
+          <t>2026-08-29T22:43:12Z</t>
         </is>
       </c>
     </row>
@@ -4221,7 +4221,7 @@
       </c>
       <c r="S48" s="4" t="inlineStr">
         <is>
-          <t>2026-08-29T02:52:52Z</t>
+          <t>2026-08-29T22:43:12Z</t>
         </is>
       </c>
     </row>
@@ -4306,7 +4306,7 @@
       </c>
       <c r="S49" s="4" t="inlineStr">
         <is>
-          <t>2026-08-29T02:52:52Z</t>
+          <t>2026-08-29T22:43:12Z</t>
         </is>
       </c>
     </row>
@@ -4391,7 +4391,7 @@
       </c>
       <c r="S50" s="4" t="inlineStr">
         <is>
-          <t>2026-08-29T02:52:52Z</t>
+          <t>2026-08-29T22:43:12Z</t>
         </is>
       </c>
     </row>
@@ -4476,7 +4476,7 @@
       </c>
       <c r="S51" s="4" t="inlineStr">
         <is>
-          <t>2026-08-29T02:52:52Z</t>
+          <t>2026-08-29T22:43:12Z</t>
         </is>
       </c>
     </row>
@@ -4561,7 +4561,7 @@
       </c>
       <c r="S52" s="4" t="inlineStr">
         <is>
-          <t>2026-08-29T02:52:52Z</t>
+          <t>2026-08-29T22:43:12Z</t>
         </is>
       </c>
     </row>
@@ -4646,7 +4646,7 @@
       </c>
       <c r="S53" s="4" t="inlineStr">
         <is>
-          <t>2026-08-29T02:52:52Z</t>
+          <t>2026-08-29T22:43:12Z</t>
         </is>
       </c>
     </row>
@@ -4731,7 +4731,7 @@
       </c>
       <c r="S54" s="4" t="inlineStr">
         <is>
-          <t>2026-08-29T02:52:52Z</t>
+          <t>2026-08-29T22:43:12Z</t>
         </is>
       </c>
     </row>
@@ -4816,7 +4816,7 @@
       </c>
       <c r="S55" s="4" t="inlineStr">
         <is>
-          <t>2026-08-29T02:52:52Z</t>
+          <t>2026-08-29T22:43:12Z</t>
         </is>
       </c>
     </row>
@@ -4901,7 +4901,7 @@
       </c>
       <c r="S56" s="4" t="inlineStr">
         <is>
-          <t>2026-08-29T02:52:52Z</t>
+          <t>2026-08-29T22:43:12Z</t>
         </is>
       </c>
     </row>
@@ -4986,7 +4986,7 @@
       </c>
       <c r="S57" s="4" t="inlineStr">
         <is>
-          <t>2026-08-29T02:52:52Z</t>
+          <t>2026-08-29T22:43:12Z</t>
         </is>
       </c>
     </row>
@@ -5071,7 +5071,7 @@
       </c>
       <c r="S58" s="4" t="inlineStr">
         <is>
-          <t>2026-08-29T02:52:52Z</t>
+          <t>2026-08-29T22:43:12Z</t>
         </is>
       </c>
     </row>
@@ -5156,7 +5156,7 @@
       </c>
       <c r="S59" s="4" t="inlineStr">
         <is>
-          <t>2026-08-29T02:52:52Z</t>
+          <t>2026-08-29T22:43:12Z</t>
         </is>
       </c>
     </row>
@@ -5241,7 +5241,7 @@
       </c>
       <c r="S60" s="4" t="inlineStr">
         <is>
-          <t>2026-08-29T02:52:52Z</t>
+          <t>2026-08-29T22:43:12Z</t>
         </is>
       </c>
     </row>
@@ -5326,7 +5326,7 @@
       </c>
       <c r="S61" s="4" t="inlineStr">
         <is>
-          <t>2026-08-29T02:52:52Z</t>
+          <t>2026-08-29T22:43:12Z</t>
         </is>
       </c>
     </row>
@@ -5411,7 +5411,7 @@
       </c>
       <c r="S62" s="4" t="inlineStr">
         <is>
-          <t>2026-08-29T02:52:52Z</t>
+          <t>2026-08-29T22:43:12Z</t>
         </is>
       </c>
     </row>
@@ -5496,7 +5496,7 @@
       </c>
       <c r="S63" s="4" t="inlineStr">
         <is>
-          <t>2026-08-29T02:52:52Z</t>
+          <t>2026-08-29T22:43:12Z</t>
         </is>
       </c>
     </row>
@@ -5581,7 +5581,7 @@
       </c>
       <c r="S64" s="4" t="inlineStr">
         <is>
-          <t>2026-08-29T02:52:52Z</t>
+          <t>2026-08-29T22:43:12Z</t>
         </is>
       </c>
     </row>
@@ -5666,7 +5666,7 @@
       </c>
       <c r="S65" s="4" t="inlineStr">
         <is>
-          <t>2026-08-29T02:52:52Z</t>
+          <t>2026-08-29T22:43:12Z</t>
         </is>
       </c>
     </row>
@@ -5751,7 +5751,7 @@
       </c>
       <c r="S66" s="4" t="inlineStr">
         <is>
-          <t>2026-08-29T02:52:52Z</t>
+          <t>2026-08-29T22:43:12Z</t>
         </is>
       </c>
     </row>
@@ -5836,7 +5836,7 @@
       </c>
       <c r="S67" s="4" t="inlineStr">
         <is>
-          <t>2026-08-29T02:52:52Z</t>
+          <t>2026-08-29T22:43:12Z</t>
         </is>
       </c>
     </row>
@@ -5921,7 +5921,7 @@
       </c>
       <c r="S68" s="4" t="inlineStr">
         <is>
-          <t>2026-08-29T02:52:52Z</t>
+          <t>2026-08-29T22:43:12Z</t>
         </is>
       </c>
     </row>
@@ -6006,7 +6006,7 @@
       </c>
       <c r="S69" s="4" t="inlineStr">
         <is>
-          <t>2026-08-29T02:52:52Z</t>
+          <t>2026-08-29T22:43:12Z</t>
         </is>
       </c>
     </row>
@@ -6091,7 +6091,7 @@
       </c>
       <c r="S70" s="4" t="inlineStr">
         <is>
-          <t>2026-08-29T02:52:52Z</t>
+          <t>2026-08-29T22:43:12Z</t>
         </is>
       </c>
     </row>
@@ -6176,7 +6176,7 @@
       </c>
       <c r="S71" s="4" t="inlineStr">
         <is>
-          <t>2026-08-29T02:52:52Z</t>
+          <t>2026-08-29T22:43:12Z</t>
         </is>
       </c>
     </row>
@@ -6261,7 +6261,7 @@
       </c>
       <c r="S72" s="4" t="inlineStr">
         <is>
-          <t>2026-08-29T02:52:52Z</t>
+          <t>2026-08-29T22:43:12Z</t>
         </is>
       </c>
     </row>
@@ -6346,7 +6346,7 @@
       </c>
       <c r="S73" s="4" t="inlineStr">
         <is>
-          <t>2026-08-29T02:52:52Z</t>
+          <t>2026-08-29T22:43:12Z</t>
         </is>
       </c>
     </row>
@@ -6431,7 +6431,7 @@
       </c>
       <c r="S74" s="4" t="inlineStr">
         <is>
-          <t>2026-08-29T02:52:52Z</t>
+          <t>2026-08-29T22:43:12Z</t>
         </is>
       </c>
     </row>
@@ -6516,7 +6516,7 @@
       </c>
       <c r="S75" s="4" t="inlineStr">
         <is>
-          <t>2026-08-29T02:52:52Z</t>
+          <t>2026-08-29T22:43:12Z</t>
         </is>
       </c>
     </row>
@@ -6601,7 +6601,7 @@
       </c>
       <c r="S76" s="4" t="inlineStr">
         <is>
-          <t>2026-08-29T02:52:52Z</t>
+          <t>2026-08-29T22:43:12Z</t>
         </is>
       </c>
     </row>
@@ -6686,7 +6686,7 @@
       </c>
       <c r="S77" s="4" t="inlineStr">
         <is>
-          <t>2026-08-29T02:52:52Z</t>
+          <t>2026-08-29T22:43:12Z</t>
         </is>
       </c>
     </row>
@@ -6771,7 +6771,7 @@
       </c>
       <c r="S78" s="4" t="inlineStr">
         <is>
-          <t>2026-08-29T02:52:52Z</t>
+          <t>2026-08-29T22:43:12Z</t>
         </is>
       </c>
     </row>
@@ -6856,7 +6856,7 @@
       </c>
       <c r="S79" s="4" t="inlineStr">
         <is>
-          <t>2026-08-29T02:52:52Z</t>
+          <t>2026-08-29T22:43:12Z</t>
         </is>
       </c>
     </row>
@@ -6941,7 +6941,7 @@
       </c>
       <c r="S80" s="4" t="inlineStr">
         <is>
-          <t>2026-08-29T02:52:52Z</t>
+          <t>2026-08-29T22:43:12Z</t>
         </is>
       </c>
     </row>
@@ -7026,7 +7026,7 @@
       </c>
       <c r="S81" s="4" t="inlineStr">
         <is>
-          <t>2026-08-29T02:52:52Z</t>
+          <t>2026-08-29T22:43:12Z</t>
         </is>
       </c>
     </row>
@@ -7111,7 +7111,7 @@
       </c>
       <c r="S82" s="4" t="inlineStr">
         <is>
-          <t>2026-08-29T02:52:52Z</t>
+          <t>2026-08-29T22:43:12Z</t>
         </is>
       </c>
     </row>
@@ -7196,7 +7196,7 @@
       </c>
       <c r="S83" s="4" t="inlineStr">
         <is>
-          <t>2026-08-29T02:52:52Z</t>
+          <t>2026-08-29T22:43:12Z</t>
         </is>
       </c>
     </row>
@@ -7281,7 +7281,7 @@
       </c>
       <c r="S84" s="4" t="inlineStr">
         <is>
-          <t>2026-08-29T02:52:52Z</t>
+          <t>2026-08-29T22:43:12Z</t>
         </is>
       </c>
     </row>
@@ -7366,7 +7366,7 @@
       </c>
       <c r="S85" s="4" t="inlineStr">
         <is>
-          <t>2026-08-29T02:52:52Z</t>
+          <t>2026-08-29T22:43:12Z</t>
         </is>
       </c>
     </row>
@@ -7451,7 +7451,7 @@
       </c>
       <c r="S86" s="4" t="inlineStr">
         <is>
-          <t>2026-08-29T02:52:52Z</t>
+          <t>2026-08-29T22:43:12Z</t>
         </is>
       </c>
     </row>
@@ -7536,7 +7536,7 @@
       </c>
       <c r="S87" s="4" t="inlineStr">
         <is>
-          <t>2026-08-29T02:52:52Z</t>
+          <t>2026-08-29T22:43:12Z</t>
         </is>
       </c>
     </row>
@@ -7621,7 +7621,7 @@
       </c>
       <c r="S88" s="4" t="inlineStr">
         <is>
-          <t>2026-08-29T02:52:52Z</t>
+          <t>2026-08-29T22:43:12Z</t>
         </is>
       </c>
     </row>
@@ -7706,7 +7706,7 @@
       </c>
       <c r="S89" s="4" t="inlineStr">
         <is>
-          <t>2026-08-29T02:52:52Z</t>
+          <t>2026-08-29T22:43:12Z</t>
         </is>
       </c>
     </row>
@@ -7791,7 +7791,7 @@
       </c>
       <c r="S90" s="4" t="inlineStr">
         <is>
-          <t>2026-08-29T02:52:52Z</t>
+          <t>2026-08-29T22:43:12Z</t>
         </is>
       </c>
     </row>
@@ -7876,7 +7876,7 @@
       </c>
       <c r="S91" s="4" t="inlineStr">
         <is>
-          <t>2026-08-29T02:52:52Z</t>
+          <t>2026-08-29T22:43:12Z</t>
         </is>
       </c>
     </row>
@@ -7961,7 +7961,7 @@
       </c>
       <c r="S92" s="4" t="inlineStr">
         <is>
-          <t>2026-08-29T02:52:52Z</t>
+          <t>2026-08-29T22:43:12Z</t>
         </is>
       </c>
     </row>
@@ -8046,7 +8046,7 @@
       </c>
       <c r="S93" s="4" t="inlineStr">
         <is>
-          <t>2026-08-29T02:52:52Z</t>
+          <t>2026-08-29T22:43:12Z</t>
         </is>
       </c>
     </row>
@@ -8131,7 +8131,7 @@
       </c>
       <c r="S94" s="4" t="inlineStr">
         <is>
-          <t>2026-08-29T02:52:52Z</t>
+          <t>2026-08-29T22:43:12Z</t>
         </is>
       </c>
     </row>
@@ -8216,7 +8216,7 @@
       </c>
       <c r="S95" s="4" t="inlineStr">
         <is>
-          <t>2026-08-29T02:52:52Z</t>
+          <t>2026-08-29T22:43:12Z</t>
         </is>
       </c>
     </row>
@@ -8301,7 +8301,7 @@
       </c>
       <c r="S96" s="4" t="inlineStr">
         <is>
-          <t>2026-08-29T02:52:52Z</t>
+          <t>2026-08-29T22:43:12Z</t>
         </is>
       </c>
     </row>
@@ -8386,7 +8386,7 @@
       </c>
       <c r="S97" s="4" t="inlineStr">
         <is>
-          <t>2026-08-29T02:52:52Z</t>
+          <t>2026-08-29T22:43:12Z</t>
         </is>
       </c>
     </row>
@@ -8471,7 +8471,7 @@
       </c>
       <c r="S98" s="4" t="inlineStr">
         <is>
-          <t>2026-08-29T02:52:52Z</t>
+          <t>2026-08-29T22:43:12Z</t>
         </is>
       </c>
     </row>
@@ -8556,7 +8556,7 @@
       </c>
       <c r="S99" s="4" t="inlineStr">
         <is>
-          <t>2026-08-29T02:52:52Z</t>
+          <t>2026-08-29T22:43:12Z</t>
         </is>
       </c>
     </row>
@@ -8641,7 +8641,7 @@
       </c>
       <c r="S100" s="4" t="inlineStr">
         <is>
-          <t>2026-08-29T02:52:52Z</t>
+          <t>2026-08-29T22:43:12Z</t>
         </is>
       </c>
     </row>
@@ -8726,7 +8726,7 @@
       </c>
       <c r="S101" s="4" t="inlineStr">
         <is>
-          <t>2026-08-29T02:52:52Z</t>
+          <t>2026-08-29T22:43:12Z</t>
         </is>
       </c>
     </row>
@@ -8811,7 +8811,7 @@
       </c>
       <c r="S102" s="4" t="inlineStr">
         <is>
-          <t>2026-08-29T02:52:52Z</t>
+          <t>2026-08-29T22:43:12Z</t>
         </is>
       </c>
     </row>
@@ -8896,7 +8896,7 @@
       </c>
       <c r="S103" s="4" t="inlineStr">
         <is>
-          <t>2026-08-29T02:52:52Z</t>
+          <t>2026-08-29T22:43:12Z</t>
         </is>
       </c>
     </row>
@@ -8981,7 +8981,7 @@
       </c>
       <c r="S104" s="4" t="inlineStr">
         <is>
-          <t>2026-08-29T02:52:52Z</t>
+          <t>2026-08-29T22:43:12Z</t>
         </is>
       </c>
     </row>
@@ -9066,7 +9066,7 @@
       </c>
       <c r="S105" s="4" t="inlineStr">
         <is>
-          <t>2026-08-29T02:52:52Z</t>
+          <t>2026-08-29T22:43:12Z</t>
         </is>
       </c>
     </row>
@@ -9151,7 +9151,7 @@
       </c>
       <c r="S106" s="4" t="inlineStr">
         <is>
-          <t>2026-08-29T02:52:52Z</t>
+          <t>2026-08-29T22:43:12Z</t>
         </is>
       </c>
     </row>
@@ -9236,7 +9236,7 @@
       </c>
       <c r="S107" s="4" t="inlineStr">
         <is>
-          <t>2026-08-29T02:52:52Z</t>
+          <t>2026-08-29T22:43:12Z</t>
         </is>
       </c>
     </row>
@@ -9321,7 +9321,7 @@
       </c>
       <c r="S108" s="4" t="inlineStr">
         <is>
-          <t>2026-08-29T02:52:52Z</t>
+          <t>2026-08-29T22:43:12Z</t>
         </is>
       </c>
     </row>
@@ -9406,7 +9406,7 @@
       </c>
       <c r="S109" s="4" t="inlineStr">
         <is>
-          <t>2026-08-29T02:52:52Z</t>
+          <t>2026-08-29T22:43:12Z</t>
         </is>
       </c>
     </row>
@@ -9491,7 +9491,7 @@
       </c>
       <c r="S110" s="4" t="inlineStr">
         <is>
-          <t>2026-08-29T02:52:52Z</t>
+          <t>2026-08-29T22:43:12Z</t>
         </is>
       </c>
     </row>
@@ -9576,7 +9576,7 @@
       </c>
       <c r="S111" s="4" t="inlineStr">
         <is>
-          <t>2026-08-29T02:52:52Z</t>
+          <t>2026-08-29T22:43:12Z</t>
         </is>
       </c>
     </row>
@@ -9661,7 +9661,7 @@
       </c>
       <c r="S112" s="4" t="inlineStr">
         <is>
-          <t>2026-08-29T02:52:52Z</t>
+          <t>2026-08-29T22:43:12Z</t>
         </is>
       </c>
     </row>
@@ -9746,7 +9746,7 @@
       </c>
       <c r="S113" s="4" t="inlineStr">
         <is>
-          <t>2026-08-29T02:52:52Z</t>
+          <t>2026-08-29T22:43:12Z</t>
         </is>
       </c>
     </row>
@@ -9831,7 +9831,7 @@
       </c>
       <c r="S114" s="4" t="inlineStr">
         <is>
-          <t>2026-08-29T02:52:52Z</t>
+          <t>2026-08-29T22:43:12Z</t>
         </is>
       </c>
     </row>
@@ -9916,7 +9916,7 @@
       </c>
       <c r="S115" s="4" t="inlineStr">
         <is>
-          <t>2026-08-29T02:52:52Z</t>
+          <t>2026-08-29T22:43:12Z</t>
         </is>
       </c>
     </row>
@@ -10001,7 +10001,7 @@
       </c>
       <c r="S116" s="4" t="inlineStr">
         <is>
-          <t>2026-08-29T02:52:52Z</t>
+          <t>2026-08-29T22:43:12Z</t>
         </is>
       </c>
     </row>
@@ -10086,7 +10086,7 @@
       </c>
       <c r="S117" s="4" t="inlineStr">
         <is>
-          <t>2026-08-29T02:52:52Z</t>
+          <t>2026-08-29T22:43:12Z</t>
         </is>
       </c>
     </row>
@@ -10171,7 +10171,7 @@
       </c>
       <c r="S118" s="4" t="inlineStr">
         <is>
-          <t>2026-08-29T02:52:52Z</t>
+          <t>2026-08-29T22:43:12Z</t>
         </is>
       </c>
     </row>
@@ -10256,7 +10256,7 @@
       </c>
       <c r="S119" s="4" t="inlineStr">
         <is>
-          <t>2026-08-29T02:52:52Z</t>
+          <t>2026-08-29T22:43:12Z</t>
         </is>
       </c>
     </row>
@@ -10341,7 +10341,7 @@
       </c>
       <c r="S120" s="4" t="inlineStr">
         <is>
-          <t>2026-08-29T02:52:52Z</t>
+          <t>2026-08-29T22:43:12Z</t>
         </is>
       </c>
     </row>
@@ -10426,7 +10426,7 @@
       </c>
       <c r="S121" s="4" t="inlineStr">
         <is>
-          <t>2026-08-29T02:52:52Z</t>
+          <t>2026-08-29T22:43:12Z</t>
         </is>
       </c>
     </row>
@@ -10511,7 +10511,7 @@
       </c>
       <c r="S122" s="4" t="inlineStr">
         <is>
-          <t>2026-08-29T02:52:52Z</t>
+          <t>2026-08-29T22:43:12Z</t>
         </is>
       </c>
     </row>
@@ -10596,7 +10596,7 @@
       </c>
       <c r="S123" s="4" t="inlineStr">
         <is>
-          <t>2026-08-29T02:52:52Z</t>
+          <t>2026-08-29T22:43:12Z</t>
         </is>
       </c>
     </row>
@@ -10681,7 +10681,7 @@
       </c>
       <c r="S124" s="4" t="inlineStr">
         <is>
-          <t>2026-08-29T02:52:52Z</t>
+          <t>2026-08-29T22:43:12Z</t>
         </is>
       </c>
     </row>
@@ -10766,7 +10766,7 @@
       </c>
       <c r="S125" s="4" t="inlineStr">
         <is>
-          <t>2026-08-29T02:52:52Z</t>
+          <t>2026-08-29T22:43:12Z</t>
         </is>
       </c>
     </row>
@@ -10851,7 +10851,7 @@
       </c>
       <c r="S126" s="4" t="inlineStr">
         <is>
-          <t>2026-08-29T02:52:52Z</t>
+          <t>2026-08-29T22:43:12Z</t>
         </is>
       </c>
     </row>
@@ -10936,7 +10936,7 @@
       </c>
       <c r="S127" s="4" t="inlineStr">
         <is>
-          <t>2026-08-29T02:52:52Z</t>
+          <t>2026-08-29T22:43:12Z</t>
         </is>
       </c>
     </row>
@@ -11021,7 +11021,7 @@
       </c>
       <c r="S128" s="4" t="inlineStr">
         <is>
-          <t>2026-08-29T02:52:52Z</t>
+          <t>2026-08-29T22:43:12Z</t>
         </is>
       </c>
     </row>
@@ -11106,7 +11106,7 @@
       </c>
       <c r="S129" s="4" t="inlineStr">
         <is>
-          <t>2026-08-29T02:52:52Z</t>
+          <t>2026-08-29T22:43:12Z</t>
         </is>
       </c>
     </row>
@@ -11191,7 +11191,7 @@
       </c>
       <c r="S130" s="4" t="inlineStr">
         <is>
-          <t>2026-08-29T02:52:52Z</t>
+          <t>2026-08-29T22:43:12Z</t>
         </is>
       </c>
     </row>
@@ -11276,7 +11276,7 @@
       </c>
       <c r="S131" s="4" t="inlineStr">
         <is>
-          <t>2026-08-29T02:52:52Z</t>
+          <t>2026-08-29T22:43:12Z</t>
         </is>
       </c>
     </row>
@@ -11361,7 +11361,7 @@
       </c>
       <c r="S132" s="4" t="inlineStr">
         <is>
-          <t>2026-08-29T02:52:52Z</t>
+          <t>2026-08-29T22:43:12Z</t>
         </is>
       </c>
     </row>
@@ -11446,7 +11446,7 @@
       </c>
       <c r="S133" s="4" t="inlineStr">
         <is>
-          <t>2026-08-29T02:52:52Z</t>
+          <t>2026-08-29T22:43:12Z</t>
         </is>
       </c>
     </row>
@@ -11531,7 +11531,7 @@
       </c>
       <c r="S134" s="4" t="inlineStr">
         <is>
-          <t>2026-08-29T02:52:52Z</t>
+          <t>2026-08-29T22:43:12Z</t>
         </is>
       </c>
     </row>
@@ -11616,7 +11616,7 @@
       </c>
       <c r="S135" s="4" t="inlineStr">
         <is>
-          <t>2026-08-29T02:52:52Z</t>
+          <t>2026-08-29T22:43:12Z</t>
         </is>
       </c>
     </row>
@@ -11701,7 +11701,7 @@
       </c>
       <c r="S136" s="4" t="inlineStr">
         <is>
-          <t>2026-08-29T02:52:52Z</t>
+          <t>2026-08-29T22:43:12Z</t>
         </is>
       </c>
     </row>
@@ -11786,7 +11786,7 @@
       </c>
       <c r="S137" s="4" t="inlineStr">
         <is>
-          <t>2026-08-29T02:52:52Z</t>
+          <t>2026-08-29T22:43:12Z</t>
         </is>
       </c>
     </row>
@@ -11871,7 +11871,7 @@
       </c>
       <c r="S138" s="4" t="inlineStr">
         <is>
-          <t>2026-08-29T02:52:52Z</t>
+          <t>2026-08-29T22:43:12Z</t>
         </is>
       </c>
     </row>
@@ -11956,7 +11956,7 @@
       </c>
       <c r="S139" s="4" t="inlineStr">
         <is>
-          <t>2026-08-29T02:52:52Z</t>
+          <t>2026-08-29T22:43:12Z</t>
         </is>
       </c>
     </row>
@@ -12041,7 +12041,7 @@
       </c>
       <c r="S140" s="4" t="inlineStr">
         <is>
-          <t>2026-08-29T02:52:52Z</t>
+          <t>2026-08-29T22:43:12Z</t>
         </is>
       </c>
     </row>
@@ -12126,7 +12126,7 @@
       </c>
       <c r="S141" s="4" t="inlineStr">
         <is>
-          <t>2026-08-29T02:52:52Z</t>
+          <t>2026-08-29T22:43:12Z</t>
         </is>
       </c>
     </row>
@@ -12258,7 +12258,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>2026-08-29T02:52:52Z</t>
+          <t>2026-08-29T22:43:12Z</t>
         </is>
       </c>
     </row>
@@ -12338,7 +12338,7 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>{"dataset_id": "bcv_pib_historico_anual", "title": "Producto interno bruto histórico anual", "table": "PIB histórico anual", "source_file": "7_1_14_anual.xls", "base": "1957/1968/1984/1997", "price_type": "Precios constantes", "measure": "Nivel", "frequency": "Anual", "period": "2017", "year": 2017, "quarter": null, "classification": "Total economía", "component": "Producto interno bruto", "value": 392393.12, "unit": "Millones de bolívares a precios constantes", "status": "", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/7_1_14_anual.xls", "fetched_at": "2026-08-29T02:52:52Z"}</t>
+          <t>{"dataset_id": "bcv_pib_historico_anual", "title": "Producto interno bruto histórico anual", "table": "PIB histórico anual", "source_file": "7_1_14_anual.xls", "base": "1957/1968/1984/1997", "price_type": "Precios constantes", "measure": "Nivel", "frequency": "Anual", "period": "2017", "year": 2017, "quarter": null, "classification": "Total economía", "component": "Producto interno bruto", "value": 392393.12, "unit": "Millones de bolívares a precios constantes", "status": "", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/7_1_14_anual.xls", "fetched_at": "2026-08-29T22:43:12Z"}</t>
         </is>
       </c>
     </row>

--- a/assets/data/bcv/excel/ove_bcv_pib_historico_anual.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_pib_historico_anual.xlsx
@@ -736,7 +736,7 @@
       </c>
       <c r="S7" s="4" t="inlineStr">
         <is>
-          <t>2026-08-29T22:43:12Z</t>
+          <t>2026-08-30T22:52:51Z</t>
         </is>
       </c>
     </row>
@@ -821,7 +821,7 @@
       </c>
       <c r="S8" s="4" t="inlineStr">
         <is>
-          <t>2026-08-29T22:43:12Z</t>
+          <t>2026-08-30T22:52:51Z</t>
         </is>
       </c>
     </row>
@@ -906,7 +906,7 @@
       </c>
       <c r="S9" s="4" t="inlineStr">
         <is>
-          <t>2026-08-29T22:43:12Z</t>
+          <t>2026-08-30T22:52:51Z</t>
         </is>
       </c>
     </row>
@@ -991,7 +991,7 @@
       </c>
       <c r="S10" s="4" t="inlineStr">
         <is>
-          <t>2026-08-29T22:43:12Z</t>
+          <t>2026-08-30T22:52:51Z</t>
         </is>
       </c>
     </row>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="S11" s="4" t="inlineStr">
         <is>
-          <t>2026-08-29T22:43:12Z</t>
+          <t>2026-08-30T22:52:51Z</t>
         </is>
       </c>
     </row>
@@ -1161,7 +1161,7 @@
       </c>
       <c r="S12" s="4" t="inlineStr">
         <is>
-          <t>2026-08-29T22:43:12Z</t>
+          <t>2026-08-30T22:52:51Z</t>
         </is>
       </c>
     </row>
@@ -1246,7 +1246,7 @@
       </c>
       <c r="S13" s="4" t="inlineStr">
         <is>
-          <t>2026-08-29T22:43:12Z</t>
+          <t>2026-08-30T22:52:51Z</t>
         </is>
       </c>
     </row>
@@ -1331,7 +1331,7 @@
       </c>
       <c r="S14" s="4" t="inlineStr">
         <is>
-          <t>2026-08-29T22:43:12Z</t>
+          <t>2026-08-30T22:52:51Z</t>
         </is>
       </c>
     </row>
@@ -1416,7 +1416,7 @@
       </c>
       <c r="S15" s="4" t="inlineStr">
         <is>
-          <t>2026-08-29T22:43:12Z</t>
+          <t>2026-08-30T22:52:51Z</t>
         </is>
       </c>
     </row>
@@ -1501,7 +1501,7 @@
       </c>
       <c r="S16" s="4" t="inlineStr">
         <is>
-          <t>2026-08-29T22:43:12Z</t>
+          <t>2026-08-30T22:52:51Z</t>
         </is>
       </c>
     </row>
@@ -1586,7 +1586,7 @@
       </c>
       <c r="S17" s="4" t="inlineStr">
         <is>
-          <t>2026-08-29T22:43:12Z</t>
+          <t>2026-08-30T22:52:51Z</t>
         </is>
       </c>
     </row>
@@ -1671,7 +1671,7 @@
       </c>
       <c r="S18" s="4" t="inlineStr">
         <is>
-          <t>2026-08-29T22:43:12Z</t>
+          <t>2026-08-30T22:52:51Z</t>
         </is>
       </c>
     </row>
@@ -1756,7 +1756,7 @@
       </c>
       <c r="S19" s="4" t="inlineStr">
         <is>
-          <t>2026-08-29T22:43:12Z</t>
+          <t>2026-08-30T22:52:51Z</t>
         </is>
       </c>
     </row>
@@ -1841,7 +1841,7 @@
       </c>
       <c r="S20" s="4" t="inlineStr">
         <is>
-          <t>2026-08-29T22:43:12Z</t>
+          <t>2026-08-30T22:52:51Z</t>
         </is>
       </c>
     </row>
@@ -1926,7 +1926,7 @@
       </c>
       <c r="S21" s="4" t="inlineStr">
         <is>
-          <t>2026-08-29T22:43:12Z</t>
+          <t>2026-08-30T22:52:51Z</t>
         </is>
       </c>
     </row>
@@ -2011,7 +2011,7 @@
       </c>
       <c r="S22" s="4" t="inlineStr">
         <is>
-          <t>2026-08-29T22:43:12Z</t>
+          <t>2026-08-30T22:52:51Z</t>
         </is>
       </c>
     </row>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="S23" s="4" t="inlineStr">
         <is>
-          <t>2026-08-29T22:43:12Z</t>
+          <t>2026-08-30T22:52:51Z</t>
         </is>
       </c>
     </row>
@@ -2181,7 +2181,7 @@
       </c>
       <c r="S24" s="4" t="inlineStr">
         <is>
-          <t>2026-08-29T22:43:12Z</t>
+          <t>2026-08-30T22:52:51Z</t>
         </is>
       </c>
     </row>
@@ -2266,7 +2266,7 @@
       </c>
       <c r="S25" s="4" t="inlineStr">
         <is>
-          <t>2026-08-29T22:43:12Z</t>
+          <t>2026-08-30T22:52:51Z</t>
         </is>
       </c>
     </row>
@@ -2351,7 +2351,7 @@
       </c>
       <c r="S26" s="4" t="inlineStr">
         <is>
-          <t>2026-08-29T22:43:12Z</t>
+          <t>2026-08-30T22:52:51Z</t>
         </is>
       </c>
     </row>
@@ -2436,7 +2436,7 @@
       </c>
       <c r="S27" s="4" t="inlineStr">
         <is>
-          <t>2026-08-29T22:43:12Z</t>
+          <t>2026-08-30T22:52:51Z</t>
         </is>
       </c>
     </row>
@@ -2521,7 +2521,7 @@
       </c>
       <c r="S28" s="4" t="inlineStr">
         <is>
-          <t>2026-08-29T22:43:12Z</t>
+          <t>2026-08-30T22:52:51Z</t>
         </is>
       </c>
     </row>
@@ -2606,7 +2606,7 @@
       </c>
       <c r="S29" s="4" t="inlineStr">
         <is>
-          <t>2026-08-29T22:43:12Z</t>
+          <t>2026-08-30T22:52:51Z</t>
         </is>
       </c>
     </row>
@@ -2691,7 +2691,7 @@
       </c>
       <c r="S30" s="4" t="inlineStr">
         <is>
-          <t>2026-08-29T22:43:12Z</t>
+          <t>2026-08-30T22:52:51Z</t>
         </is>
       </c>
     </row>
@@ -2776,7 +2776,7 @@
       </c>
       <c r="S31" s="4" t="inlineStr">
         <is>
-          <t>2026-08-29T22:43:12Z</t>
+          <t>2026-08-30T22:52:51Z</t>
         </is>
       </c>
     </row>
@@ -2861,7 +2861,7 @@
       </c>
       <c r="S32" s="4" t="inlineStr">
         <is>
-          <t>2026-08-29T22:43:12Z</t>
+          <t>2026-08-30T22:52:51Z</t>
         </is>
       </c>
     </row>
@@ -2946,7 +2946,7 @@
       </c>
       <c r="S33" s="4" t="inlineStr">
         <is>
-          <t>2026-08-29T22:43:12Z</t>
+          <t>2026-08-30T22:52:51Z</t>
         </is>
       </c>
     </row>
@@ -3031,7 +3031,7 @@
       </c>
       <c r="S34" s="4" t="inlineStr">
         <is>
-          <t>2026-08-29T22:43:12Z</t>
+          <t>2026-08-30T22:52:51Z</t>
         </is>
       </c>
     </row>
@@ -3116,7 +3116,7 @@
       </c>
       <c r="S35" s="4" t="inlineStr">
         <is>
-          <t>2026-08-29T22:43:12Z</t>
+          <t>2026-08-30T22:52:51Z</t>
         </is>
       </c>
     </row>
@@ -3201,7 +3201,7 @@
       </c>
       <c r="S36" s="4" t="inlineStr">
         <is>
-          <t>2026-08-29T22:43:12Z</t>
+          <t>2026-08-30T22:52:51Z</t>
         </is>
       </c>
     </row>
@@ -3286,7 +3286,7 @@
       </c>
       <c r="S37" s="4" t="inlineStr">
         <is>
-          <t>2026-08-29T22:43:12Z</t>
+          <t>2026-08-30T22:52:51Z</t>
         </is>
       </c>
     </row>
@@ -3371,7 +3371,7 @@
       </c>
       <c r="S38" s="4" t="inlineStr">
         <is>
-          <t>2026-08-29T22:43:12Z</t>
+          <t>2026-08-30T22:52:51Z</t>
         </is>
       </c>
     </row>
@@ -3456,7 +3456,7 @@
       </c>
       <c r="S39" s="4" t="inlineStr">
         <is>
-          <t>2026-08-29T22:43:12Z</t>
+          <t>2026-08-30T22:52:51Z</t>
         </is>
       </c>
     </row>
@@ -3541,7 +3541,7 @@
       </c>
       <c r="S40" s="4" t="inlineStr">
         <is>
-          <t>2026-08-29T22:43:12Z</t>
+          <t>2026-08-30T22:52:51Z</t>
         </is>
       </c>
     </row>
@@ -3626,7 +3626,7 @@
       </c>
       <c r="S41" s="4" t="inlineStr">
         <is>
-          <t>2026-08-29T22:43:12Z</t>
+          <t>2026-08-30T22:52:51Z</t>
         </is>
       </c>
     </row>
@@ -3711,7 +3711,7 @@
       </c>
       <c r="S42" s="4" t="inlineStr">
         <is>
-          <t>2026-08-29T22:43:12Z</t>
+          <t>2026-08-30T22:52:51Z</t>
         </is>
       </c>
     </row>
@@ -3796,7 +3796,7 @@
       </c>
       <c r="S43" s="4" t="inlineStr">
         <is>
-          <t>2026-08-29T22:43:12Z</t>
+          <t>2026-08-30T22:52:51Z</t>
         </is>
       </c>
     </row>
@@ -3881,7 +3881,7 @@
       </c>
       <c r="S44" s="4" t="inlineStr">
         <is>
-          <t>2026-08-29T22:43:12Z</t>
+          <t>2026-08-30T22:52:51Z</t>
         </is>
       </c>
     </row>
@@ -3966,7 +3966,7 @@
       </c>
       <c r="S45" s="4" t="inlineStr">
         <is>
-          <t>2026-08-29T22:43:12Z</t>
+          <t>2026-08-30T22:52:51Z</t>
         </is>
       </c>
     </row>
@@ -4051,7 +4051,7 @@
       </c>
       <c r="S46" s="4" t="inlineStr">
         <is>
-          <t>2026-08-29T22:43:12Z</t>
+          <t>2026-08-30T22:52:51Z</t>
         </is>
       </c>
     </row>
@@ -4136,7 +4136,7 @@
       </c>
       <c r="S47" s="4" t="inlineStr">
         <is>
-          <t>2026-08-29T22:43:12Z</t>
+          <t>2026-08-30T22:52:51Z</t>
         </is>
       </c>
     </row>
@@ -4221,7 +4221,7 @@
       </c>
       <c r="S48" s="4" t="inlineStr">
         <is>
-          <t>2026-08-29T22:43:12Z</t>
+          <t>2026-08-30T22:52:51Z</t>
         </is>
       </c>
     </row>
@@ -4306,7 +4306,7 @@
       </c>
       <c r="S49" s="4" t="inlineStr">
         <is>
-          <t>2026-08-29T22:43:12Z</t>
+          <t>2026-08-30T22:52:51Z</t>
         </is>
       </c>
     </row>
@@ -4391,7 +4391,7 @@
       </c>
       <c r="S50" s="4" t="inlineStr">
         <is>
-          <t>2026-08-29T22:43:12Z</t>
+          <t>2026-08-30T22:52:51Z</t>
         </is>
       </c>
     </row>
@@ -4476,7 +4476,7 @@
       </c>
       <c r="S51" s="4" t="inlineStr">
         <is>
-          <t>2026-08-29T22:43:12Z</t>
+          <t>2026-08-30T22:52:51Z</t>
         </is>
       </c>
     </row>
@@ -4561,7 +4561,7 @@
       </c>
       <c r="S52" s="4" t="inlineStr">
         <is>
-          <t>2026-08-29T22:43:12Z</t>
+          <t>2026-08-30T22:52:51Z</t>
         </is>
       </c>
     </row>
@@ -4646,7 +4646,7 @@
       </c>
       <c r="S53" s="4" t="inlineStr">
         <is>
-          <t>2026-08-29T22:43:12Z</t>
+          <t>2026-08-30T22:52:51Z</t>
         </is>
       </c>
     </row>
@@ -4731,7 +4731,7 @@
       </c>
       <c r="S54" s="4" t="inlineStr">
         <is>
-          <t>2026-08-29T22:43:12Z</t>
+          <t>2026-08-30T22:52:51Z</t>
         </is>
       </c>
     </row>
@@ -4816,7 +4816,7 @@
       </c>
       <c r="S55" s="4" t="inlineStr">
         <is>
-          <t>2026-08-29T22:43:12Z</t>
+          <t>2026-08-30T22:52:51Z</t>
         </is>
       </c>
     </row>
@@ -4901,7 +4901,7 @@
       </c>
       <c r="S56" s="4" t="inlineStr">
         <is>
-          <t>2026-08-29T22:43:12Z</t>
+          <t>2026-08-30T22:52:51Z</t>
         </is>
       </c>
     </row>
@@ -4986,7 +4986,7 @@
       </c>
       <c r="S57" s="4" t="inlineStr">
         <is>
-          <t>2026-08-29T22:43:12Z</t>
+          <t>2026-08-30T22:52:51Z</t>
         </is>
       </c>
     </row>
@@ -5071,7 +5071,7 @@
       </c>
       <c r="S58" s="4" t="inlineStr">
         <is>
-          <t>2026-08-29T22:43:12Z</t>
+          <t>2026-08-30T22:52:51Z</t>
         </is>
       </c>
     </row>
@@ -5156,7 +5156,7 @@
       </c>
       <c r="S59" s="4" t="inlineStr">
         <is>
-          <t>2026-08-29T22:43:12Z</t>
+          <t>2026-08-30T22:52:51Z</t>
         </is>
       </c>
     </row>
@@ -5241,7 +5241,7 @@
       </c>
       <c r="S60" s="4" t="inlineStr">
         <is>
-          <t>2026-08-29T22:43:12Z</t>
+          <t>2026-08-30T22:52:51Z</t>
         </is>
       </c>
     </row>
@@ -5326,7 +5326,7 @@
       </c>
       <c r="S61" s="4" t="inlineStr">
         <is>
-          <t>2026-08-29T22:43:12Z</t>
+          <t>2026-08-30T22:52:51Z</t>
         </is>
       </c>
     </row>
@@ -5411,7 +5411,7 @@
       </c>
       <c r="S62" s="4" t="inlineStr">
         <is>
-          <t>2026-08-29T22:43:12Z</t>
+          <t>2026-08-30T22:52:51Z</t>
         </is>
       </c>
     </row>
@@ -5496,7 +5496,7 @@
       </c>
       <c r="S63" s="4" t="inlineStr">
         <is>
-          <t>2026-08-29T22:43:12Z</t>
+          <t>2026-08-30T22:52:51Z</t>
         </is>
       </c>
     </row>
@@ -5581,7 +5581,7 @@
       </c>
       <c r="S64" s="4" t="inlineStr">
         <is>
-          <t>2026-08-29T22:43:12Z</t>
+          <t>2026-08-30T22:52:51Z</t>
         </is>
       </c>
     </row>
@@ -5666,7 +5666,7 @@
       </c>
       <c r="S65" s="4" t="inlineStr">
         <is>
-          <t>2026-08-29T22:43:12Z</t>
+          <t>2026-08-30T22:52:51Z</t>
         </is>
       </c>
     </row>
@@ -5751,7 +5751,7 @@
       </c>
       <c r="S66" s="4" t="inlineStr">
         <is>
-          <t>2026-08-29T22:43:12Z</t>
+          <t>2026-08-30T22:52:51Z</t>
         </is>
       </c>
     </row>
@@ -5836,7 +5836,7 @@
       </c>
       <c r="S67" s="4" t="inlineStr">
         <is>
-          <t>2026-08-29T22:43:12Z</t>
+          <t>2026-08-30T22:52:51Z</t>
         </is>
       </c>
     </row>
@@ -5921,7 +5921,7 @@
       </c>
       <c r="S68" s="4" t="inlineStr">
         <is>
-          <t>2026-08-29T22:43:12Z</t>
+          <t>2026-08-30T22:52:51Z</t>
         </is>
       </c>
     </row>
@@ -6006,7 +6006,7 @@
       </c>
       <c r="S69" s="4" t="inlineStr">
         <is>
-          <t>2026-08-29T22:43:12Z</t>
+          <t>2026-08-30T22:52:51Z</t>
         </is>
       </c>
     </row>
@@ -6091,7 +6091,7 @@
       </c>
       <c r="S70" s="4" t="inlineStr">
         <is>
-          <t>2026-08-29T22:43:12Z</t>
+          <t>2026-08-30T22:52:51Z</t>
         </is>
       </c>
     </row>
@@ -6176,7 +6176,7 @@
       </c>
       <c r="S71" s="4" t="inlineStr">
         <is>
-          <t>2026-08-29T22:43:12Z</t>
+          <t>2026-08-30T22:52:51Z</t>
         </is>
       </c>
     </row>
@@ -6261,7 +6261,7 @@
       </c>
       <c r="S72" s="4" t="inlineStr">
         <is>
-          <t>2026-08-29T22:43:12Z</t>
+          <t>2026-08-30T22:52:51Z</t>
         </is>
       </c>
     </row>
@@ -6346,7 +6346,7 @@
       </c>
       <c r="S73" s="4" t="inlineStr">
         <is>
-          <t>2026-08-29T22:43:12Z</t>
+          <t>2026-08-30T22:52:51Z</t>
         </is>
       </c>
     </row>
@@ -6431,7 +6431,7 @@
       </c>
       <c r="S74" s="4" t="inlineStr">
         <is>
-          <t>2026-08-29T22:43:12Z</t>
+          <t>2026-08-30T22:52:51Z</t>
         </is>
       </c>
     </row>
@@ -6516,7 +6516,7 @@
       </c>
       <c r="S75" s="4" t="inlineStr">
         <is>
-          <t>2026-08-29T22:43:12Z</t>
+          <t>2026-08-30T22:52:51Z</t>
         </is>
       </c>
     </row>
@@ -6601,7 +6601,7 @@
       </c>
       <c r="S76" s="4" t="inlineStr">
         <is>
-          <t>2026-08-29T22:43:12Z</t>
+          <t>2026-08-30T22:52:51Z</t>
         </is>
       </c>
     </row>
@@ -6686,7 +6686,7 @@
       </c>
       <c r="S77" s="4" t="inlineStr">
         <is>
-          <t>2026-08-29T22:43:12Z</t>
+          <t>2026-08-30T22:52:51Z</t>
         </is>
       </c>
     </row>
@@ -6771,7 +6771,7 @@
       </c>
       <c r="S78" s="4" t="inlineStr">
         <is>
-          <t>2026-08-29T22:43:12Z</t>
+          <t>2026-08-30T22:52:51Z</t>
         </is>
       </c>
     </row>
@@ -6856,7 +6856,7 @@
       </c>
       <c r="S79" s="4" t="inlineStr">
         <is>
-          <t>2026-08-29T22:43:12Z</t>
+          <t>2026-08-30T22:52:51Z</t>
         </is>
       </c>
     </row>
@@ -6941,7 +6941,7 @@
       </c>
       <c r="S80" s="4" t="inlineStr">
         <is>
-          <t>2026-08-29T22:43:12Z</t>
+          <t>2026-08-30T22:52:51Z</t>
         </is>
       </c>
     </row>
@@ -7026,7 +7026,7 @@
       </c>
       <c r="S81" s="4" t="inlineStr">
         <is>
-          <t>2026-08-29T22:43:12Z</t>
+          <t>2026-08-30T22:52:51Z</t>
         </is>
       </c>
     </row>
@@ -7111,7 +7111,7 @@
       </c>
       <c r="S82" s="4" t="inlineStr">
         <is>
-          <t>2026-08-29T22:43:12Z</t>
+          <t>2026-08-30T22:52:51Z</t>
         </is>
       </c>
     </row>
@@ -7196,7 +7196,7 @@
       </c>
       <c r="S83" s="4" t="inlineStr">
         <is>
-          <t>2026-08-29T22:43:12Z</t>
+          <t>2026-08-30T22:52:51Z</t>
         </is>
       </c>
     </row>
@@ -7281,7 +7281,7 @@
       </c>
       <c r="S84" s="4" t="inlineStr">
         <is>
-          <t>2026-08-29T22:43:12Z</t>
+          <t>2026-08-30T22:52:51Z</t>
         </is>
       </c>
     </row>
@@ -7366,7 +7366,7 @@
       </c>
       <c r="S85" s="4" t="inlineStr">
         <is>
-          <t>2026-08-29T22:43:12Z</t>
+          <t>2026-08-30T22:52:51Z</t>
         </is>
       </c>
     </row>
@@ -7451,7 +7451,7 @@
       </c>
       <c r="S86" s="4" t="inlineStr">
         <is>
-          <t>2026-08-29T22:43:12Z</t>
+          <t>2026-08-30T22:52:51Z</t>
         </is>
       </c>
     </row>
@@ -7536,7 +7536,7 @@
       </c>
       <c r="S87" s="4" t="inlineStr">
         <is>
-          <t>2026-08-29T22:43:12Z</t>
+          <t>2026-08-30T22:52:51Z</t>
         </is>
       </c>
     </row>
@@ -7621,7 +7621,7 @@
       </c>
       <c r="S88" s="4" t="inlineStr">
         <is>
-          <t>2026-08-29T22:43:12Z</t>
+          <t>2026-08-30T22:52:51Z</t>
         </is>
       </c>
     </row>
@@ -7706,7 +7706,7 @@
       </c>
       <c r="S89" s="4" t="inlineStr">
         <is>
-          <t>2026-08-29T22:43:12Z</t>
+          <t>2026-08-30T22:52:51Z</t>
         </is>
       </c>
     </row>
@@ -7791,7 +7791,7 @@
       </c>
       <c r="S90" s="4" t="inlineStr">
         <is>
-          <t>2026-08-29T22:43:12Z</t>
+          <t>2026-08-30T22:52:51Z</t>
         </is>
       </c>
     </row>
@@ -7876,7 +7876,7 @@
       </c>
       <c r="S91" s="4" t="inlineStr">
         <is>
-          <t>2026-08-29T22:43:12Z</t>
+          <t>2026-08-30T22:52:51Z</t>
         </is>
       </c>
     </row>
@@ -7961,7 +7961,7 @@
       </c>
       <c r="S92" s="4" t="inlineStr">
         <is>
-          <t>2026-08-29T22:43:12Z</t>
+          <t>2026-08-30T22:52:51Z</t>
         </is>
       </c>
     </row>
@@ -8046,7 +8046,7 @@
       </c>
       <c r="S93" s="4" t="inlineStr">
         <is>
-          <t>2026-08-29T22:43:12Z</t>
+          <t>2026-08-30T22:52:51Z</t>
         </is>
       </c>
     </row>
@@ -8131,7 +8131,7 @@
       </c>
       <c r="S94" s="4" t="inlineStr">
         <is>
-          <t>2026-08-29T22:43:12Z</t>
+          <t>2026-08-30T22:52:51Z</t>
         </is>
       </c>
     </row>
@@ -8216,7 +8216,7 @@
       </c>
       <c r="S95" s="4" t="inlineStr">
         <is>
-          <t>2026-08-29T22:43:12Z</t>
+          <t>2026-08-30T22:52:51Z</t>
         </is>
       </c>
     </row>
@@ -8301,7 +8301,7 @@
       </c>
       <c r="S96" s="4" t="inlineStr">
         <is>
-          <t>2026-08-29T22:43:12Z</t>
+          <t>2026-08-30T22:52:51Z</t>
         </is>
       </c>
     </row>
@@ -8386,7 +8386,7 @@
       </c>
       <c r="S97" s="4" t="inlineStr">
         <is>
-          <t>2026-08-29T22:43:12Z</t>
+          <t>2026-08-30T22:52:51Z</t>
         </is>
       </c>
     </row>
@@ -8471,7 +8471,7 @@
       </c>
       <c r="S98" s="4" t="inlineStr">
         <is>
-          <t>2026-08-29T22:43:12Z</t>
+          <t>2026-08-30T22:52:51Z</t>
         </is>
       </c>
     </row>
@@ -8556,7 +8556,7 @@
       </c>
       <c r="S99" s="4" t="inlineStr">
         <is>
-          <t>2026-08-29T22:43:12Z</t>
+          <t>2026-08-30T22:52:51Z</t>
         </is>
       </c>
     </row>
@@ -8641,7 +8641,7 @@
       </c>
       <c r="S100" s="4" t="inlineStr">
         <is>
-          <t>2026-08-29T22:43:12Z</t>
+          <t>2026-08-30T22:52:51Z</t>
         </is>
       </c>
     </row>
@@ -8726,7 +8726,7 @@
       </c>
       <c r="S101" s="4" t="inlineStr">
         <is>
-          <t>2026-08-29T22:43:12Z</t>
+          <t>2026-08-30T22:52:51Z</t>
         </is>
       </c>
     </row>
@@ -8811,7 +8811,7 @@
       </c>
       <c r="S102" s="4" t="inlineStr">
         <is>
-          <t>2026-08-29T22:43:12Z</t>
+          <t>2026-08-30T22:52:51Z</t>
         </is>
       </c>
     </row>
@@ -8896,7 +8896,7 @@
       </c>
       <c r="S103" s="4" t="inlineStr">
         <is>
-          <t>2026-08-29T22:43:12Z</t>
+          <t>2026-08-30T22:52:51Z</t>
         </is>
       </c>
     </row>
@@ -8981,7 +8981,7 @@
       </c>
       <c r="S104" s="4" t="inlineStr">
         <is>
-          <t>2026-08-29T22:43:12Z</t>
+          <t>2026-08-30T22:52:51Z</t>
         </is>
       </c>
     </row>
@@ -9066,7 +9066,7 @@
       </c>
       <c r="S105" s="4" t="inlineStr">
         <is>
-          <t>2026-08-29T22:43:12Z</t>
+          <t>2026-08-30T22:52:51Z</t>
         </is>
       </c>
     </row>
@@ -9151,7 +9151,7 @@
       </c>
       <c r="S106" s="4" t="inlineStr">
         <is>
-          <t>2026-08-29T22:43:12Z</t>
+          <t>2026-08-30T22:52:51Z</t>
         </is>
       </c>
     </row>
@@ -9236,7 +9236,7 @@
       </c>
       <c r="S107" s="4" t="inlineStr">
         <is>
-          <t>2026-08-29T22:43:12Z</t>
+          <t>2026-08-30T22:52:51Z</t>
         </is>
       </c>
     </row>
@@ -9321,7 +9321,7 @@
       </c>
       <c r="S108" s="4" t="inlineStr">
         <is>
-          <t>2026-08-29T22:43:12Z</t>
+          <t>2026-08-30T22:52:51Z</t>
         </is>
       </c>
     </row>
@@ -9406,7 +9406,7 @@
       </c>
       <c r="S109" s="4" t="inlineStr">
         <is>
-          <t>2026-08-29T22:43:12Z</t>
+          <t>2026-08-30T22:52:51Z</t>
         </is>
       </c>
     </row>
@@ -9491,7 +9491,7 @@
       </c>
       <c r="S110" s="4" t="inlineStr">
         <is>
-          <t>2026-08-29T22:43:12Z</t>
+          <t>2026-08-30T22:52:51Z</t>
         </is>
       </c>
     </row>
@@ -9576,7 +9576,7 @@
       </c>
       <c r="S111" s="4" t="inlineStr">
         <is>
-          <t>2026-08-29T22:43:12Z</t>
+          <t>2026-08-30T22:52:51Z</t>
         </is>
       </c>
     </row>
@@ -9661,7 +9661,7 @@
       </c>
       <c r="S112" s="4" t="inlineStr">
         <is>
-          <t>2026-08-29T22:43:12Z</t>
+          <t>2026-08-30T22:52:51Z</t>
         </is>
       </c>
     </row>
@@ -9746,7 +9746,7 @@
       </c>
       <c r="S113" s="4" t="inlineStr">
         <is>
-          <t>2026-08-29T22:43:12Z</t>
+          <t>2026-08-30T22:52:51Z</t>
         </is>
       </c>
     </row>
@@ -9831,7 +9831,7 @@
       </c>
       <c r="S114" s="4" t="inlineStr">
         <is>
-          <t>2026-08-29T22:43:12Z</t>
+          <t>2026-08-30T22:52:51Z</t>
         </is>
       </c>
     </row>
@@ -9916,7 +9916,7 @@
       </c>
       <c r="S115" s="4" t="inlineStr">
         <is>
-          <t>2026-08-29T22:43:12Z</t>
+          <t>2026-08-30T22:52:51Z</t>
         </is>
       </c>
     </row>
@@ -10001,7 +10001,7 @@
       </c>
       <c r="S116" s="4" t="inlineStr">
         <is>
-          <t>2026-08-29T22:43:12Z</t>
+          <t>2026-08-30T22:52:51Z</t>
         </is>
       </c>
     </row>
@@ -10086,7 +10086,7 @@
       </c>
       <c r="S117" s="4" t="inlineStr">
         <is>
-          <t>2026-08-29T22:43:12Z</t>
+          <t>2026-08-30T22:52:51Z</t>
         </is>
       </c>
     </row>
@@ -10171,7 +10171,7 @@
       </c>
       <c r="S118" s="4" t="inlineStr">
         <is>
-          <t>2026-08-29T22:43:12Z</t>
+          <t>2026-08-30T22:52:51Z</t>
         </is>
       </c>
     </row>
@@ -10256,7 +10256,7 @@
       </c>
       <c r="S119" s="4" t="inlineStr">
         <is>
-          <t>2026-08-29T22:43:12Z</t>
+          <t>2026-08-30T22:52:51Z</t>
         </is>
       </c>
     </row>
@@ -10341,7 +10341,7 @@
       </c>
       <c r="S120" s="4" t="inlineStr">
         <is>
-          <t>2026-08-29T22:43:12Z</t>
+          <t>2026-08-30T22:52:51Z</t>
         </is>
       </c>
     </row>
@@ -10426,7 +10426,7 @@
       </c>
       <c r="S121" s="4" t="inlineStr">
         <is>
-          <t>2026-08-29T22:43:12Z</t>
+          <t>2026-08-30T22:52:51Z</t>
         </is>
       </c>
     </row>
@@ -10511,7 +10511,7 @@
       </c>
       <c r="S122" s="4" t="inlineStr">
         <is>
-          <t>2026-08-29T22:43:12Z</t>
+          <t>2026-08-30T22:52:51Z</t>
         </is>
       </c>
     </row>
@@ -10596,7 +10596,7 @@
       </c>
       <c r="S123" s="4" t="inlineStr">
         <is>
-          <t>2026-08-29T22:43:12Z</t>
+          <t>2026-08-30T22:52:51Z</t>
         </is>
       </c>
     </row>
@@ -10681,7 +10681,7 @@
       </c>
       <c r="S124" s="4" t="inlineStr">
         <is>
-          <t>2026-08-29T22:43:12Z</t>
+          <t>2026-08-30T22:52:51Z</t>
         </is>
       </c>
     </row>
@@ -10766,7 +10766,7 @@
       </c>
       <c r="S125" s="4" t="inlineStr">
         <is>
-          <t>2026-08-29T22:43:12Z</t>
+          <t>2026-08-30T22:52:51Z</t>
         </is>
       </c>
     </row>
@@ -10851,7 +10851,7 @@
       </c>
       <c r="S126" s="4" t="inlineStr">
         <is>
-          <t>2026-08-29T22:43:12Z</t>
+          <t>2026-08-30T22:52:51Z</t>
         </is>
       </c>
     </row>
@@ -10936,7 +10936,7 @@
       </c>
       <c r="S127" s="4" t="inlineStr">
         <is>
-          <t>2026-08-29T22:43:12Z</t>
+          <t>2026-08-30T22:52:51Z</t>
         </is>
       </c>
     </row>
@@ -11021,7 +11021,7 @@
       </c>
       <c r="S128" s="4" t="inlineStr">
         <is>
-          <t>2026-08-29T22:43:12Z</t>
+          <t>2026-08-30T22:52:51Z</t>
         </is>
       </c>
     </row>
@@ -11106,7 +11106,7 @@
       </c>
       <c r="S129" s="4" t="inlineStr">
         <is>
-          <t>2026-08-29T22:43:12Z</t>
+          <t>2026-08-30T22:52:51Z</t>
         </is>
       </c>
     </row>
@@ -11191,7 +11191,7 @@
       </c>
       <c r="S130" s="4" t="inlineStr">
         <is>
-          <t>2026-08-29T22:43:12Z</t>
+          <t>2026-08-30T22:52:51Z</t>
         </is>
       </c>
     </row>
@@ -11276,7 +11276,7 @@
       </c>
       <c r="S131" s="4" t="inlineStr">
         <is>
-          <t>2026-08-29T22:43:12Z</t>
+          <t>2026-08-30T22:52:51Z</t>
         </is>
       </c>
     </row>
@@ -11361,7 +11361,7 @@
       </c>
       <c r="S132" s="4" t="inlineStr">
         <is>
-          <t>2026-08-29T22:43:12Z</t>
+          <t>2026-08-30T22:52:51Z</t>
         </is>
       </c>
     </row>
@@ -11446,7 +11446,7 @@
       </c>
       <c r="S133" s="4" t="inlineStr">
         <is>
-          <t>2026-08-29T22:43:12Z</t>
+          <t>2026-08-30T22:52:51Z</t>
         </is>
       </c>
     </row>
@@ -11531,7 +11531,7 @@
       </c>
       <c r="S134" s="4" t="inlineStr">
         <is>
-          <t>2026-08-29T22:43:12Z</t>
+          <t>2026-08-30T22:52:51Z</t>
         </is>
       </c>
     </row>
@@ -11616,7 +11616,7 @@
       </c>
       <c r="S135" s="4" t="inlineStr">
         <is>
-          <t>2026-08-29T22:43:12Z</t>
+          <t>2026-08-30T22:52:51Z</t>
         </is>
       </c>
     </row>
@@ -11701,7 +11701,7 @@
       </c>
       <c r="S136" s="4" t="inlineStr">
         <is>
-          <t>2026-08-29T22:43:12Z</t>
+          <t>2026-08-30T22:52:51Z</t>
         </is>
       </c>
     </row>
@@ -11786,7 +11786,7 @@
       </c>
       <c r="S137" s="4" t="inlineStr">
         <is>
-          <t>2026-08-29T22:43:12Z</t>
+          <t>2026-08-30T22:52:51Z</t>
         </is>
       </c>
     </row>
@@ -11871,7 +11871,7 @@
       </c>
       <c r="S138" s="4" t="inlineStr">
         <is>
-          <t>2026-08-29T22:43:12Z</t>
+          <t>2026-08-30T22:52:51Z</t>
         </is>
       </c>
     </row>
@@ -11956,7 +11956,7 @@
       </c>
       <c r="S139" s="4" t="inlineStr">
         <is>
-          <t>2026-08-29T22:43:12Z</t>
+          <t>2026-08-30T22:52:51Z</t>
         </is>
       </c>
     </row>
@@ -12041,7 +12041,7 @@
       </c>
       <c r="S140" s="4" t="inlineStr">
         <is>
-          <t>2026-08-29T22:43:12Z</t>
+          <t>2026-08-30T22:52:51Z</t>
         </is>
       </c>
     </row>
@@ -12126,7 +12126,7 @@
       </c>
       <c r="S141" s="4" t="inlineStr">
         <is>
-          <t>2026-08-29T22:43:12Z</t>
+          <t>2026-08-30T22:52:51Z</t>
         </is>
       </c>
     </row>
@@ -12258,7 +12258,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>2026-08-29T22:43:12Z</t>
+          <t>2026-08-30T22:52:51Z</t>
         </is>
       </c>
     </row>
@@ -12338,7 +12338,7 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>{"dataset_id": "bcv_pib_historico_anual", "title": "Producto interno bruto histórico anual", "table": "PIB histórico anual", "source_file": "7_1_14_anual.xls", "base": "1957/1968/1984/1997", "price_type": "Precios constantes", "measure": "Nivel", "frequency": "Anual", "period": "2017", "year": 2017, "quarter": null, "classification": "Total economía", "component": "Producto interno bruto", "value": 392393.12, "unit": "Millones de bolívares a precios constantes", "status": "", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/7_1_14_anual.xls", "fetched_at": "2026-08-29T22:43:12Z"}</t>
+          <t>{"dataset_id": "bcv_pib_historico_anual", "title": "Producto interno bruto histórico anual", "table": "PIB histórico anual", "source_file": "7_1_14_anual.xls", "base": "1957/1968/1984/1997", "price_type": "Precios constantes", "measure": "Nivel", "frequency": "Anual", "period": "2017", "year": 2017, "quarter": null, "classification": "Total economía", "component": "Producto interno bruto", "value": 392393.12, "unit": "Millones de bolívares a precios constantes", "status": "", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/7_1_14_anual.xls", "fetched_at": "2026-08-30T22:52:51Z"}</t>
         </is>
       </c>
     </row>

--- a/assets/data/bcv/excel/ove_bcv_pib_historico_anual.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_pib_historico_anual.xlsx
@@ -736,7 +736,7 @@
       </c>
       <c r="S7" s="4" t="inlineStr">
         <is>
-          <t>2026-08-30T22:52:51Z</t>
+          <t>2026-08-31T23:58:41Z</t>
         </is>
       </c>
     </row>
@@ -821,7 +821,7 @@
       </c>
       <c r="S8" s="4" t="inlineStr">
         <is>
-          <t>2026-08-30T22:52:51Z</t>
+          <t>2026-08-31T23:58:41Z</t>
         </is>
       </c>
     </row>
@@ -906,7 +906,7 @@
       </c>
       <c r="S9" s="4" t="inlineStr">
         <is>
-          <t>2026-08-30T22:52:51Z</t>
+          <t>2026-08-31T23:58:41Z</t>
         </is>
       </c>
     </row>
@@ -991,7 +991,7 @@
       </c>
       <c r="S10" s="4" t="inlineStr">
         <is>
-          <t>2026-08-30T22:52:51Z</t>
+          <t>2026-08-31T23:58:41Z</t>
         </is>
       </c>
     </row>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="S11" s="4" t="inlineStr">
         <is>
-          <t>2026-08-30T22:52:51Z</t>
+          <t>2026-08-31T23:58:41Z</t>
         </is>
       </c>
     </row>
@@ -1161,7 +1161,7 @@
       </c>
       <c r="S12" s="4" t="inlineStr">
         <is>
-          <t>2026-08-30T22:52:51Z</t>
+          <t>2026-08-31T23:58:41Z</t>
         </is>
       </c>
     </row>
@@ -1246,7 +1246,7 @@
       </c>
       <c r="S13" s="4" t="inlineStr">
         <is>
-          <t>2026-08-30T22:52:51Z</t>
+          <t>2026-08-31T23:58:41Z</t>
         </is>
       </c>
     </row>
@@ -1331,7 +1331,7 @@
       </c>
       <c r="S14" s="4" t="inlineStr">
         <is>
-          <t>2026-08-30T22:52:51Z</t>
+          <t>2026-08-31T23:58:41Z</t>
         </is>
       </c>
     </row>
@@ -1416,7 +1416,7 @@
       </c>
       <c r="S15" s="4" t="inlineStr">
         <is>
-          <t>2026-08-30T22:52:51Z</t>
+          <t>2026-08-31T23:58:41Z</t>
         </is>
       </c>
     </row>
@@ -1501,7 +1501,7 @@
       </c>
       <c r="S16" s="4" t="inlineStr">
         <is>
-          <t>2026-08-30T22:52:51Z</t>
+          <t>2026-08-31T23:58:41Z</t>
         </is>
       </c>
     </row>
@@ -1586,7 +1586,7 @@
       </c>
       <c r="S17" s="4" t="inlineStr">
         <is>
-          <t>2026-08-30T22:52:51Z</t>
+          <t>2026-08-31T23:58:41Z</t>
         </is>
       </c>
     </row>
@@ -1671,7 +1671,7 @@
       </c>
       <c r="S18" s="4" t="inlineStr">
         <is>
-          <t>2026-08-30T22:52:51Z</t>
+          <t>2026-08-31T23:58:41Z</t>
         </is>
       </c>
     </row>
@@ -1756,7 +1756,7 @@
       </c>
       <c r="S19" s="4" t="inlineStr">
         <is>
-          <t>2026-08-30T22:52:51Z</t>
+          <t>2026-08-31T23:58:41Z</t>
         </is>
       </c>
     </row>
@@ -1841,7 +1841,7 @@
       </c>
       <c r="S20" s="4" t="inlineStr">
         <is>
-          <t>2026-08-30T22:52:51Z</t>
+          <t>2026-08-31T23:58:41Z</t>
         </is>
       </c>
     </row>
@@ -1926,7 +1926,7 @@
       </c>
       <c r="S21" s="4" t="inlineStr">
         <is>
-          <t>2026-08-30T22:52:51Z</t>
+          <t>2026-08-31T23:58:41Z</t>
         </is>
       </c>
     </row>
@@ -2011,7 +2011,7 @@
       </c>
       <c r="S22" s="4" t="inlineStr">
         <is>
-          <t>2026-08-30T22:52:51Z</t>
+          <t>2026-08-31T23:58:41Z</t>
         </is>
       </c>
     </row>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="S23" s="4" t="inlineStr">
         <is>
-          <t>2026-08-30T22:52:51Z</t>
+          <t>2026-08-31T23:58:41Z</t>
         </is>
       </c>
     </row>
@@ -2181,7 +2181,7 @@
       </c>
       <c r="S24" s="4" t="inlineStr">
         <is>
-          <t>2026-08-30T22:52:51Z</t>
+          <t>2026-08-31T23:58:41Z</t>
         </is>
       </c>
     </row>
@@ -2266,7 +2266,7 @@
       </c>
       <c r="S25" s="4" t="inlineStr">
         <is>
-          <t>2026-08-30T22:52:51Z</t>
+          <t>2026-08-31T23:58:41Z</t>
         </is>
       </c>
     </row>
@@ -2351,7 +2351,7 @@
       </c>
       <c r="S26" s="4" t="inlineStr">
         <is>
-          <t>2026-08-30T22:52:51Z</t>
+          <t>2026-08-31T23:58:41Z</t>
         </is>
       </c>
     </row>
@@ -2436,7 +2436,7 @@
       </c>
       <c r="S27" s="4" t="inlineStr">
         <is>
-          <t>2026-08-30T22:52:51Z</t>
+          <t>2026-08-31T23:58:41Z</t>
         </is>
       </c>
     </row>
@@ -2521,7 +2521,7 @@
       </c>
       <c r="S28" s="4" t="inlineStr">
         <is>
-          <t>2026-08-30T22:52:51Z</t>
+          <t>2026-08-31T23:58:41Z</t>
         </is>
       </c>
     </row>
@@ -2606,7 +2606,7 @@
       </c>
       <c r="S29" s="4" t="inlineStr">
         <is>
-          <t>2026-08-30T22:52:51Z</t>
+          <t>2026-08-31T23:58:41Z</t>
         </is>
       </c>
     </row>
@@ -2691,7 +2691,7 @@
       </c>
       <c r="S30" s="4" t="inlineStr">
         <is>
-          <t>2026-08-30T22:52:51Z</t>
+          <t>2026-08-31T23:58:41Z</t>
         </is>
       </c>
     </row>
@@ -2776,7 +2776,7 @@
       </c>
       <c r="S31" s="4" t="inlineStr">
         <is>
-          <t>2026-08-30T22:52:51Z</t>
+          <t>2026-08-31T23:58:41Z</t>
         </is>
       </c>
     </row>
@@ -2861,7 +2861,7 @@
       </c>
       <c r="S32" s="4" t="inlineStr">
         <is>
-          <t>2026-08-30T22:52:51Z</t>
+          <t>2026-08-31T23:58:41Z</t>
         </is>
       </c>
     </row>
@@ -2946,7 +2946,7 @@
       </c>
       <c r="S33" s="4" t="inlineStr">
         <is>
-          <t>2026-08-30T22:52:51Z</t>
+          <t>2026-08-31T23:58:41Z</t>
         </is>
       </c>
     </row>
@@ -3031,7 +3031,7 @@
       </c>
       <c r="S34" s="4" t="inlineStr">
         <is>
-          <t>2026-08-30T22:52:51Z</t>
+          <t>2026-08-31T23:58:41Z</t>
         </is>
       </c>
     </row>
@@ -3116,7 +3116,7 @@
       </c>
       <c r="S35" s="4" t="inlineStr">
         <is>
-          <t>2026-08-30T22:52:51Z</t>
+          <t>2026-08-31T23:58:41Z</t>
         </is>
       </c>
     </row>
@@ -3201,7 +3201,7 @@
       </c>
       <c r="S36" s="4" t="inlineStr">
         <is>
-          <t>2026-08-30T22:52:51Z</t>
+          <t>2026-08-31T23:58:41Z</t>
         </is>
       </c>
     </row>
@@ -3286,7 +3286,7 @@
       </c>
       <c r="S37" s="4" t="inlineStr">
         <is>
-          <t>2026-08-30T22:52:51Z</t>
+          <t>2026-08-31T23:58:41Z</t>
         </is>
       </c>
     </row>
@@ -3371,7 +3371,7 @@
       </c>
       <c r="S38" s="4" t="inlineStr">
         <is>
-          <t>2026-08-30T22:52:51Z</t>
+          <t>2026-08-31T23:58:41Z</t>
         </is>
       </c>
     </row>
@@ -3456,7 +3456,7 @@
       </c>
       <c r="S39" s="4" t="inlineStr">
         <is>
-          <t>2026-08-30T22:52:51Z</t>
+          <t>2026-08-31T23:58:41Z</t>
         </is>
       </c>
     </row>
@@ -3541,7 +3541,7 @@
       </c>
       <c r="S40" s="4" t="inlineStr">
         <is>
-          <t>2026-08-30T22:52:51Z</t>
+          <t>2026-08-31T23:58:41Z</t>
         </is>
       </c>
     </row>
@@ -3626,7 +3626,7 @@
       </c>
       <c r="S41" s="4" t="inlineStr">
         <is>
-          <t>2026-08-30T22:52:51Z</t>
+          <t>2026-08-31T23:58:41Z</t>
         </is>
       </c>
     </row>
@@ -3711,7 +3711,7 @@
       </c>
       <c r="S42" s="4" t="inlineStr">
         <is>
-          <t>2026-08-30T22:52:51Z</t>
+          <t>2026-08-31T23:58:41Z</t>
         </is>
       </c>
     </row>
@@ -3796,7 +3796,7 @@
       </c>
       <c r="S43" s="4" t="inlineStr">
         <is>
-          <t>2026-08-30T22:52:51Z</t>
+          <t>2026-08-31T23:58:41Z</t>
         </is>
       </c>
     </row>
@@ -3881,7 +3881,7 @@
       </c>
       <c r="S44" s="4" t="inlineStr">
         <is>
-          <t>2026-08-30T22:52:51Z</t>
+          <t>2026-08-31T23:58:41Z</t>
         </is>
       </c>
     </row>
@@ -3966,7 +3966,7 @@
       </c>
       <c r="S45" s="4" t="inlineStr">
         <is>
-          <t>2026-08-30T22:52:51Z</t>
+          <t>2026-08-31T23:58:41Z</t>
         </is>
       </c>
     </row>
@@ -4051,7 +4051,7 @@
       </c>
       <c r="S46" s="4" t="inlineStr">
         <is>
-          <t>2026-08-30T22:52:51Z</t>
+          <t>2026-08-31T23:58:41Z</t>
         </is>
       </c>
     </row>
@@ -4136,7 +4136,7 @@
       </c>
       <c r="S47" s="4" t="inlineStr">
         <is>
-          <t>2026-08-30T22:52:51Z</t>
+          <t>2026-08-31T23:58:41Z</t>
         </is>
       </c>
     </row>
@@ -4221,7 +4221,7 @@
       </c>
       <c r="S48" s="4" t="inlineStr">
         <is>
-          <t>2026-08-30T22:52:51Z</t>
+          <t>2026-08-31T23:58:41Z</t>
         </is>
       </c>
     </row>
@@ -4306,7 +4306,7 @@
       </c>
       <c r="S49" s="4" t="inlineStr">
         <is>
-          <t>2026-08-30T22:52:51Z</t>
+          <t>2026-08-31T23:58:41Z</t>
         </is>
       </c>
     </row>
@@ -4391,7 +4391,7 @@
       </c>
       <c r="S50" s="4" t="inlineStr">
         <is>
-          <t>2026-08-30T22:52:51Z</t>
+          <t>2026-08-31T23:58:41Z</t>
         </is>
       </c>
     </row>
@@ -4476,7 +4476,7 @@
       </c>
       <c r="S51" s="4" t="inlineStr">
         <is>
-          <t>2026-08-30T22:52:51Z</t>
+          <t>2026-08-31T23:58:41Z</t>
         </is>
       </c>
     </row>
@@ -4561,7 +4561,7 @@
       </c>
       <c r="S52" s="4" t="inlineStr">
         <is>
-          <t>2026-08-30T22:52:51Z</t>
+          <t>2026-08-31T23:58:41Z</t>
         </is>
       </c>
     </row>
@@ -4646,7 +4646,7 @@
       </c>
       <c r="S53" s="4" t="inlineStr">
         <is>
-          <t>2026-08-30T22:52:51Z</t>
+          <t>2026-08-31T23:58:41Z</t>
         </is>
       </c>
     </row>
@@ -4731,7 +4731,7 @@
       </c>
       <c r="S54" s="4" t="inlineStr">
         <is>
-          <t>2026-08-30T22:52:51Z</t>
+          <t>2026-08-31T23:58:41Z</t>
         </is>
       </c>
     </row>
@@ -4816,7 +4816,7 @@
       </c>
       <c r="S55" s="4" t="inlineStr">
         <is>
-          <t>2026-08-30T22:52:51Z</t>
+          <t>2026-08-31T23:58:41Z</t>
         </is>
       </c>
     </row>
@@ -4901,7 +4901,7 @@
       </c>
       <c r="S56" s="4" t="inlineStr">
         <is>
-          <t>2026-08-30T22:52:51Z</t>
+          <t>2026-08-31T23:58:41Z</t>
         </is>
       </c>
     </row>
@@ -4986,7 +4986,7 @@
       </c>
       <c r="S57" s="4" t="inlineStr">
         <is>
-          <t>2026-08-30T22:52:51Z</t>
+          <t>2026-08-31T23:58:41Z</t>
         </is>
       </c>
     </row>
@@ -5071,7 +5071,7 @@
       </c>
       <c r="S58" s="4" t="inlineStr">
         <is>
-          <t>2026-08-30T22:52:51Z</t>
+          <t>2026-08-31T23:58:41Z</t>
         </is>
       </c>
     </row>
@@ -5156,7 +5156,7 @@
       </c>
       <c r="S59" s="4" t="inlineStr">
         <is>
-          <t>2026-08-30T22:52:51Z</t>
+          <t>2026-08-31T23:58:41Z</t>
         </is>
       </c>
     </row>
@@ -5241,7 +5241,7 @@
       </c>
       <c r="S60" s="4" t="inlineStr">
         <is>
-          <t>2026-08-30T22:52:51Z</t>
+          <t>2026-08-31T23:58:41Z</t>
         </is>
       </c>
     </row>
@@ -5326,7 +5326,7 @@
       </c>
       <c r="S61" s="4" t="inlineStr">
         <is>
-          <t>2026-08-30T22:52:51Z</t>
+          <t>2026-08-31T23:58:41Z</t>
         </is>
       </c>
     </row>
@@ -5411,7 +5411,7 @@
       </c>
       <c r="S62" s="4" t="inlineStr">
         <is>
-          <t>2026-08-30T22:52:51Z</t>
+          <t>2026-08-31T23:58:41Z</t>
         </is>
       </c>
     </row>
@@ -5496,7 +5496,7 @@
       </c>
       <c r="S63" s="4" t="inlineStr">
         <is>
-          <t>2026-08-30T22:52:51Z</t>
+          <t>2026-08-31T23:58:41Z</t>
         </is>
       </c>
     </row>
@@ -5581,7 +5581,7 @@
       </c>
       <c r="S64" s="4" t="inlineStr">
         <is>
-          <t>2026-08-30T22:52:51Z</t>
+          <t>2026-08-31T23:58:41Z</t>
         </is>
       </c>
     </row>
@@ -5666,7 +5666,7 @@
       </c>
       <c r="S65" s="4" t="inlineStr">
         <is>
-          <t>2026-08-30T22:52:51Z</t>
+          <t>2026-08-31T23:58:41Z</t>
         </is>
       </c>
     </row>
@@ -5751,7 +5751,7 @@
       </c>
       <c r="S66" s="4" t="inlineStr">
         <is>
-          <t>2026-08-30T22:52:51Z</t>
+          <t>2026-08-31T23:58:41Z</t>
         </is>
       </c>
     </row>
@@ -5836,7 +5836,7 @@
       </c>
       <c r="S67" s="4" t="inlineStr">
         <is>
-          <t>2026-08-30T22:52:51Z</t>
+          <t>2026-08-31T23:58:41Z</t>
         </is>
       </c>
     </row>
@@ -5921,7 +5921,7 @@
       </c>
       <c r="S68" s="4" t="inlineStr">
         <is>
-          <t>2026-08-30T22:52:51Z</t>
+          <t>2026-08-31T23:58:41Z</t>
         </is>
       </c>
     </row>
@@ -6006,7 +6006,7 @@
       </c>
       <c r="S69" s="4" t="inlineStr">
         <is>
-          <t>2026-08-30T22:52:51Z</t>
+          <t>2026-08-31T23:58:41Z</t>
         </is>
       </c>
     </row>
@@ -6091,7 +6091,7 @@
       </c>
       <c r="S70" s="4" t="inlineStr">
         <is>
-          <t>2026-08-30T22:52:51Z</t>
+          <t>2026-08-31T23:58:41Z</t>
         </is>
       </c>
     </row>
@@ -6176,7 +6176,7 @@
       </c>
       <c r="S71" s="4" t="inlineStr">
         <is>
-          <t>2026-08-30T22:52:51Z</t>
+          <t>2026-08-31T23:58:41Z</t>
         </is>
       </c>
     </row>
@@ -6261,7 +6261,7 @@
       </c>
       <c r="S72" s="4" t="inlineStr">
         <is>
-          <t>2026-08-30T22:52:51Z</t>
+          <t>2026-08-31T23:58:41Z</t>
         </is>
       </c>
     </row>
@@ -6346,7 +6346,7 @@
       </c>
       <c r="S73" s="4" t="inlineStr">
         <is>
-          <t>2026-08-30T22:52:51Z</t>
+          <t>2026-08-31T23:58:41Z</t>
         </is>
       </c>
     </row>
@@ -6431,7 +6431,7 @@
       </c>
       <c r="S74" s="4" t="inlineStr">
         <is>
-          <t>2026-08-30T22:52:51Z</t>
+          <t>2026-08-31T23:58:41Z</t>
         </is>
       </c>
     </row>
@@ -6516,7 +6516,7 @@
       </c>
       <c r="S75" s="4" t="inlineStr">
         <is>
-          <t>2026-08-30T22:52:51Z</t>
+          <t>2026-08-31T23:58:41Z</t>
         </is>
       </c>
     </row>
@@ -6601,7 +6601,7 @@
       </c>
       <c r="S76" s="4" t="inlineStr">
         <is>
-          <t>2026-08-30T22:52:51Z</t>
+          <t>2026-08-31T23:58:41Z</t>
         </is>
       </c>
     </row>
@@ -6686,7 +6686,7 @@
       </c>
       <c r="S77" s="4" t="inlineStr">
         <is>
-          <t>2026-08-30T22:52:51Z</t>
+          <t>2026-08-31T23:58:41Z</t>
         </is>
       </c>
     </row>
@@ -6771,7 +6771,7 @@
       </c>
       <c r="S78" s="4" t="inlineStr">
         <is>
-          <t>2026-08-30T22:52:51Z</t>
+          <t>2026-08-31T23:58:41Z</t>
         </is>
       </c>
     </row>
@@ -6856,7 +6856,7 @@
       </c>
       <c r="S79" s="4" t="inlineStr">
         <is>
-          <t>2026-08-30T22:52:51Z</t>
+          <t>2026-08-31T23:58:41Z</t>
         </is>
       </c>
     </row>
@@ -6941,7 +6941,7 @@
       </c>
       <c r="S80" s="4" t="inlineStr">
         <is>
-          <t>2026-08-30T22:52:51Z</t>
+          <t>2026-08-31T23:58:41Z</t>
         </is>
       </c>
     </row>
@@ -7026,7 +7026,7 @@
       </c>
       <c r="S81" s="4" t="inlineStr">
         <is>
-          <t>2026-08-30T22:52:51Z</t>
+          <t>2026-08-31T23:58:41Z</t>
         </is>
       </c>
     </row>
@@ -7111,7 +7111,7 @@
       </c>
       <c r="S82" s="4" t="inlineStr">
         <is>
-          <t>2026-08-30T22:52:51Z</t>
+          <t>2026-08-31T23:58:41Z</t>
         </is>
       </c>
     </row>
@@ -7196,7 +7196,7 @@
       </c>
       <c r="S83" s="4" t="inlineStr">
         <is>
-          <t>2026-08-30T22:52:51Z</t>
+          <t>2026-08-31T23:58:41Z</t>
         </is>
       </c>
     </row>
@@ -7281,7 +7281,7 @@
       </c>
       <c r="S84" s="4" t="inlineStr">
         <is>
-          <t>2026-08-30T22:52:51Z</t>
+          <t>2026-08-31T23:58:41Z</t>
         </is>
       </c>
     </row>
@@ -7366,7 +7366,7 @@
       </c>
       <c r="S85" s="4" t="inlineStr">
         <is>
-          <t>2026-08-30T22:52:51Z</t>
+          <t>2026-08-31T23:58:41Z</t>
         </is>
       </c>
     </row>
@@ -7451,7 +7451,7 @@
       </c>
       <c r="S86" s="4" t="inlineStr">
         <is>
-          <t>2026-08-30T22:52:51Z</t>
+          <t>2026-08-31T23:58:41Z</t>
         </is>
       </c>
     </row>
@@ -7536,7 +7536,7 @@
       </c>
       <c r="S87" s="4" t="inlineStr">
         <is>
-          <t>2026-08-30T22:52:51Z</t>
+          <t>2026-08-31T23:58:41Z</t>
         </is>
       </c>
     </row>
@@ -7621,7 +7621,7 @@
       </c>
       <c r="S88" s="4" t="inlineStr">
         <is>
-          <t>2026-08-30T22:52:51Z</t>
+          <t>2026-08-31T23:58:41Z</t>
         </is>
       </c>
     </row>
@@ -7706,7 +7706,7 @@
       </c>
       <c r="S89" s="4" t="inlineStr">
         <is>
-          <t>2026-08-30T22:52:51Z</t>
+          <t>2026-08-31T23:58:41Z</t>
         </is>
       </c>
     </row>
@@ -7791,7 +7791,7 @@
       </c>
       <c r="S90" s="4" t="inlineStr">
         <is>
-          <t>2026-08-30T22:52:51Z</t>
+          <t>2026-08-31T23:58:41Z</t>
         </is>
       </c>
     </row>
@@ -7876,7 +7876,7 @@
       </c>
       <c r="S91" s="4" t="inlineStr">
         <is>
-          <t>2026-08-30T22:52:51Z</t>
+          <t>2026-08-31T23:58:41Z</t>
         </is>
       </c>
     </row>
@@ -7961,7 +7961,7 @@
       </c>
       <c r="S92" s="4" t="inlineStr">
         <is>
-          <t>2026-08-30T22:52:51Z</t>
+          <t>2026-08-31T23:58:41Z</t>
         </is>
       </c>
     </row>
@@ -8046,7 +8046,7 @@
       </c>
       <c r="S93" s="4" t="inlineStr">
         <is>
-          <t>2026-08-30T22:52:51Z</t>
+          <t>2026-08-31T23:58:41Z</t>
         </is>
       </c>
     </row>
@@ -8131,7 +8131,7 @@
       </c>
       <c r="S94" s="4" t="inlineStr">
         <is>
-          <t>2026-08-30T22:52:51Z</t>
+          <t>2026-08-31T23:58:41Z</t>
         </is>
       </c>
     </row>
@@ -8216,7 +8216,7 @@
       </c>
       <c r="S95" s="4" t="inlineStr">
         <is>
-          <t>2026-08-30T22:52:51Z</t>
+          <t>2026-08-31T23:58:41Z</t>
         </is>
       </c>
     </row>
@@ -8301,7 +8301,7 @@
       </c>
       <c r="S96" s="4" t="inlineStr">
         <is>
-          <t>2026-08-30T22:52:51Z</t>
+          <t>2026-08-31T23:58:41Z</t>
         </is>
       </c>
     </row>
@@ -8386,7 +8386,7 @@
       </c>
       <c r="S97" s="4" t="inlineStr">
         <is>
-          <t>2026-08-30T22:52:51Z</t>
+          <t>2026-08-31T23:58:41Z</t>
         </is>
       </c>
     </row>
@@ -8471,7 +8471,7 @@
       </c>
       <c r="S98" s="4" t="inlineStr">
         <is>
-          <t>2026-08-30T22:52:51Z</t>
+          <t>2026-08-31T23:58:41Z</t>
         </is>
       </c>
     </row>
@@ -8556,7 +8556,7 @@
       </c>
       <c r="S99" s="4" t="inlineStr">
         <is>
-          <t>2026-08-30T22:52:51Z</t>
+          <t>2026-08-31T23:58:41Z</t>
         </is>
       </c>
     </row>
@@ -8641,7 +8641,7 @@
       </c>
       <c r="S100" s="4" t="inlineStr">
         <is>
-          <t>2026-08-30T22:52:51Z</t>
+          <t>2026-08-31T23:58:41Z</t>
         </is>
       </c>
     </row>
@@ -8726,7 +8726,7 @@
       </c>
       <c r="S101" s="4" t="inlineStr">
         <is>
-          <t>2026-08-30T22:52:51Z</t>
+          <t>2026-08-31T23:58:41Z</t>
         </is>
       </c>
     </row>
@@ -8811,7 +8811,7 @@
       </c>
       <c r="S102" s="4" t="inlineStr">
         <is>
-          <t>2026-08-30T22:52:51Z</t>
+          <t>2026-08-31T23:58:41Z</t>
         </is>
       </c>
     </row>
@@ -8896,7 +8896,7 @@
       </c>
       <c r="S103" s="4" t="inlineStr">
         <is>
-          <t>2026-08-30T22:52:51Z</t>
+          <t>2026-08-31T23:58:41Z</t>
         </is>
       </c>
     </row>
@@ -8981,7 +8981,7 @@
       </c>
       <c r="S104" s="4" t="inlineStr">
         <is>
-          <t>2026-08-30T22:52:51Z</t>
+          <t>2026-08-31T23:58:41Z</t>
         </is>
       </c>
     </row>
@@ -9066,7 +9066,7 @@
       </c>
       <c r="S105" s="4" t="inlineStr">
         <is>
-          <t>2026-08-30T22:52:51Z</t>
+          <t>2026-08-31T23:58:41Z</t>
         </is>
       </c>
     </row>
@@ -9151,7 +9151,7 @@
       </c>
       <c r="S106" s="4" t="inlineStr">
         <is>
-          <t>2026-08-30T22:52:51Z</t>
+          <t>2026-08-31T23:58:41Z</t>
         </is>
       </c>
     </row>
@@ -9236,7 +9236,7 @@
       </c>
       <c r="S107" s="4" t="inlineStr">
         <is>
-          <t>2026-08-30T22:52:51Z</t>
+          <t>2026-08-31T23:58:41Z</t>
         </is>
       </c>
     </row>
@@ -9321,7 +9321,7 @@
       </c>
       <c r="S108" s="4" t="inlineStr">
         <is>
-          <t>2026-08-30T22:52:51Z</t>
+          <t>2026-08-31T23:58:41Z</t>
         </is>
       </c>
     </row>
@@ -9406,7 +9406,7 @@
       </c>
       <c r="S109" s="4" t="inlineStr">
         <is>
-          <t>2026-08-30T22:52:51Z</t>
+          <t>2026-08-31T23:58:41Z</t>
         </is>
       </c>
     </row>
@@ -9491,7 +9491,7 @@
       </c>
       <c r="S110" s="4" t="inlineStr">
         <is>
-          <t>2026-08-30T22:52:51Z</t>
+          <t>2026-08-31T23:58:41Z</t>
         </is>
       </c>
     </row>
@@ -9576,7 +9576,7 @@
       </c>
       <c r="S111" s="4" t="inlineStr">
         <is>
-          <t>2026-08-30T22:52:51Z</t>
+          <t>2026-08-31T23:58:41Z</t>
         </is>
       </c>
     </row>
@@ -9661,7 +9661,7 @@
       </c>
       <c r="S112" s="4" t="inlineStr">
         <is>
-          <t>2026-08-30T22:52:51Z</t>
+          <t>2026-08-31T23:58:41Z</t>
         </is>
       </c>
     </row>
@@ -9746,7 +9746,7 @@
       </c>
       <c r="S113" s="4" t="inlineStr">
         <is>
-          <t>2026-08-30T22:52:51Z</t>
+          <t>2026-08-31T23:58:41Z</t>
         </is>
       </c>
     </row>
@@ -9831,7 +9831,7 @@
       </c>
       <c r="S114" s="4" t="inlineStr">
         <is>
-          <t>2026-08-30T22:52:51Z</t>
+          <t>2026-08-31T23:58:41Z</t>
         </is>
       </c>
     </row>
@@ -9916,7 +9916,7 @@
       </c>
       <c r="S115" s="4" t="inlineStr">
         <is>
-          <t>2026-08-30T22:52:51Z</t>
+          <t>2026-08-31T23:58:41Z</t>
         </is>
       </c>
     </row>
@@ -10001,7 +10001,7 @@
       </c>
       <c r="S116" s="4" t="inlineStr">
         <is>
-          <t>2026-08-30T22:52:51Z</t>
+          <t>2026-08-31T23:58:41Z</t>
         </is>
       </c>
     </row>
@@ -10086,7 +10086,7 @@
       </c>
       <c r="S117" s="4" t="inlineStr">
         <is>
-          <t>2026-08-30T22:52:51Z</t>
+          <t>2026-08-31T23:58:41Z</t>
         </is>
       </c>
     </row>
@@ -10171,7 +10171,7 @@
       </c>
       <c r="S118" s="4" t="inlineStr">
         <is>
-          <t>2026-08-30T22:52:51Z</t>
+          <t>2026-08-31T23:58:41Z</t>
         </is>
       </c>
     </row>
@@ -10256,7 +10256,7 @@
       </c>
       <c r="S119" s="4" t="inlineStr">
         <is>
-          <t>2026-08-30T22:52:51Z</t>
+          <t>2026-08-31T23:58:41Z</t>
         </is>
       </c>
     </row>
@@ -10341,7 +10341,7 @@
       </c>
       <c r="S120" s="4" t="inlineStr">
         <is>
-          <t>2026-08-30T22:52:51Z</t>
+          <t>2026-08-31T23:58:41Z</t>
         </is>
       </c>
     </row>
@@ -10426,7 +10426,7 @@
       </c>
       <c r="S121" s="4" t="inlineStr">
         <is>
-          <t>2026-08-30T22:52:51Z</t>
+          <t>2026-08-31T23:58:41Z</t>
         </is>
       </c>
     </row>
@@ -10511,7 +10511,7 @@
       </c>
       <c r="S122" s="4" t="inlineStr">
         <is>
-          <t>2026-08-30T22:52:51Z</t>
+          <t>2026-08-31T23:58:41Z</t>
         </is>
       </c>
     </row>
@@ -10596,7 +10596,7 @@
       </c>
       <c r="S123" s="4" t="inlineStr">
         <is>
-          <t>2026-08-30T22:52:51Z</t>
+          <t>2026-08-31T23:58:41Z</t>
         </is>
       </c>
     </row>
@@ -10681,7 +10681,7 @@
       </c>
       <c r="S124" s="4" t="inlineStr">
         <is>
-          <t>2026-08-30T22:52:51Z</t>
+          <t>2026-08-31T23:58:41Z</t>
         </is>
       </c>
     </row>
@@ -10766,7 +10766,7 @@
       </c>
       <c r="S125" s="4" t="inlineStr">
         <is>
-          <t>2026-08-30T22:52:51Z</t>
+          <t>2026-08-31T23:58:41Z</t>
         </is>
       </c>
     </row>
@@ -10851,7 +10851,7 @@
       </c>
       <c r="S126" s="4" t="inlineStr">
         <is>
-          <t>2026-08-30T22:52:51Z</t>
+          <t>2026-08-31T23:58:41Z</t>
         </is>
       </c>
     </row>
@@ -10936,7 +10936,7 @@
       </c>
       <c r="S127" s="4" t="inlineStr">
         <is>
-          <t>2026-08-30T22:52:51Z</t>
+          <t>2026-08-31T23:58:41Z</t>
         </is>
       </c>
     </row>
@@ -11021,7 +11021,7 @@
       </c>
       <c r="S128" s="4" t="inlineStr">
         <is>
-          <t>2026-08-30T22:52:51Z</t>
+          <t>2026-08-31T23:58:41Z</t>
         </is>
       </c>
     </row>
@@ -11106,7 +11106,7 @@
       </c>
       <c r="S129" s="4" t="inlineStr">
         <is>
-          <t>2026-08-30T22:52:51Z</t>
+          <t>2026-08-31T23:58:41Z</t>
         </is>
       </c>
     </row>
@@ -11191,7 +11191,7 @@
       </c>
       <c r="S130" s="4" t="inlineStr">
         <is>
-          <t>2026-08-30T22:52:51Z</t>
+          <t>2026-08-31T23:58:41Z</t>
         </is>
       </c>
     </row>
@@ -11276,7 +11276,7 @@
       </c>
       <c r="S131" s="4" t="inlineStr">
         <is>
-          <t>2026-08-30T22:52:51Z</t>
+          <t>2026-08-31T23:58:41Z</t>
         </is>
       </c>
     </row>
@@ -11361,7 +11361,7 @@
       </c>
       <c r="S132" s="4" t="inlineStr">
         <is>
-          <t>2026-08-30T22:52:51Z</t>
+          <t>2026-08-31T23:58:41Z</t>
         </is>
       </c>
     </row>
@@ -11446,7 +11446,7 @@
       </c>
       <c r="S133" s="4" t="inlineStr">
         <is>
-          <t>2026-08-30T22:52:51Z</t>
+          <t>2026-08-31T23:58:41Z</t>
         </is>
       </c>
     </row>
@@ -11531,7 +11531,7 @@
       </c>
       <c r="S134" s="4" t="inlineStr">
         <is>
-          <t>2026-08-30T22:52:51Z</t>
+          <t>2026-08-31T23:58:41Z</t>
         </is>
       </c>
     </row>
@@ -11616,7 +11616,7 @@
       </c>
       <c r="S135" s="4" t="inlineStr">
         <is>
-          <t>2026-08-30T22:52:51Z</t>
+          <t>2026-08-31T23:58:41Z</t>
         </is>
       </c>
     </row>
@@ -11701,7 +11701,7 @@
       </c>
       <c r="S136" s="4" t="inlineStr">
         <is>
-          <t>2026-08-30T22:52:51Z</t>
+          <t>2026-08-31T23:58:41Z</t>
         </is>
       </c>
     </row>
@@ -11786,7 +11786,7 @@
       </c>
       <c r="S137" s="4" t="inlineStr">
         <is>
-          <t>2026-08-30T22:52:51Z</t>
+          <t>2026-08-31T23:58:41Z</t>
         </is>
       </c>
     </row>
@@ -11871,7 +11871,7 @@
       </c>
       <c r="S138" s="4" t="inlineStr">
         <is>
-          <t>2026-08-30T22:52:51Z</t>
+          <t>2026-08-31T23:58:41Z</t>
         </is>
       </c>
     </row>
@@ -11956,7 +11956,7 @@
       </c>
       <c r="S139" s="4" t="inlineStr">
         <is>
-          <t>2026-08-30T22:52:51Z</t>
+          <t>2026-08-31T23:58:41Z</t>
         </is>
       </c>
     </row>
@@ -12041,7 +12041,7 @@
       </c>
       <c r="S140" s="4" t="inlineStr">
         <is>
-          <t>2026-08-30T22:52:51Z</t>
+          <t>2026-08-31T23:58:41Z</t>
         </is>
       </c>
     </row>
@@ -12126,7 +12126,7 @@
       </c>
       <c r="S141" s="4" t="inlineStr">
         <is>
-          <t>2026-08-30T22:52:51Z</t>
+          <t>2026-08-31T23:58:41Z</t>
         </is>
       </c>
     </row>
@@ -12258,7 +12258,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>2026-08-30T22:52:51Z</t>
+          <t>2026-08-31T23:58:41Z</t>
         </is>
       </c>
     </row>
@@ -12338,7 +12338,7 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>{"dataset_id": "bcv_pib_historico_anual", "title": "Producto interno bruto histórico anual", "table": "PIB histórico anual", "source_file": "7_1_14_anual.xls", "base": "1957/1968/1984/1997", "price_type": "Precios constantes", "measure": "Nivel", "frequency": "Anual", "period": "2017", "year": 2017, "quarter": null, "classification": "Total economía", "component": "Producto interno bruto", "value": 392393.12, "unit": "Millones de bolívares a precios constantes", "status": "", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/7_1_14_anual.xls", "fetched_at": "2026-08-30T22:52:51Z"}</t>
+          <t>{"dataset_id": "bcv_pib_historico_anual", "title": "Producto interno bruto histórico anual", "table": "PIB histórico anual", "source_file": "7_1_14_anual.xls", "base": "1957/1968/1984/1997", "price_type": "Precios constantes", "measure": "Nivel", "frequency": "Anual", "period": "2017", "year": 2017, "quarter": null, "classification": "Total economía", "component": "Producto interno bruto", "value": 392393.12, "unit": "Millones de bolívares a precios constantes", "status": "", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/7_1_14_anual.xls", "fetched_at": "2026-08-31T23:58:41Z"}</t>
         </is>
       </c>
     </row>

--- a/assets/data/bcv/excel/ove_bcv_pib_historico_anual.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_pib_historico_anual.xlsx
@@ -736,7 +736,7 @@
       </c>
       <c r="S7" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31T23:58:41Z</t>
+          <t>2026-09-01T22:43:23Z</t>
         </is>
       </c>
     </row>
@@ -821,7 +821,7 @@
       </c>
       <c r="S8" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31T23:58:41Z</t>
+          <t>2026-09-01T22:43:23Z</t>
         </is>
       </c>
     </row>
@@ -906,7 +906,7 @@
       </c>
       <c r="S9" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31T23:58:41Z</t>
+          <t>2026-09-01T22:43:23Z</t>
         </is>
       </c>
     </row>
@@ -991,7 +991,7 @@
       </c>
       <c r="S10" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31T23:58:41Z</t>
+          <t>2026-09-01T22:43:23Z</t>
         </is>
       </c>
     </row>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="S11" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31T23:58:41Z</t>
+          <t>2026-09-01T22:43:23Z</t>
         </is>
       </c>
     </row>
@@ -1161,7 +1161,7 @@
       </c>
       <c r="S12" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31T23:58:41Z</t>
+          <t>2026-09-01T22:43:23Z</t>
         </is>
       </c>
     </row>
@@ -1246,7 +1246,7 @@
       </c>
       <c r="S13" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31T23:58:41Z</t>
+          <t>2026-09-01T22:43:23Z</t>
         </is>
       </c>
     </row>
@@ -1331,7 +1331,7 @@
       </c>
       <c r="S14" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31T23:58:41Z</t>
+          <t>2026-09-01T22:43:23Z</t>
         </is>
       </c>
     </row>
@@ -1416,7 +1416,7 @@
       </c>
       <c r="S15" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31T23:58:41Z</t>
+          <t>2026-09-01T22:43:23Z</t>
         </is>
       </c>
     </row>
@@ -1501,7 +1501,7 @@
       </c>
       <c r="S16" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31T23:58:41Z</t>
+          <t>2026-09-01T22:43:23Z</t>
         </is>
       </c>
     </row>
@@ -1586,7 +1586,7 @@
       </c>
       <c r="S17" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31T23:58:41Z</t>
+          <t>2026-09-01T22:43:23Z</t>
         </is>
       </c>
     </row>
@@ -1671,7 +1671,7 @@
       </c>
       <c r="S18" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31T23:58:41Z</t>
+          <t>2026-09-01T22:43:23Z</t>
         </is>
       </c>
     </row>
@@ -1756,7 +1756,7 @@
       </c>
       <c r="S19" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31T23:58:41Z</t>
+          <t>2026-09-01T22:43:23Z</t>
         </is>
       </c>
     </row>
@@ -1841,7 +1841,7 @@
       </c>
       <c r="S20" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31T23:58:41Z</t>
+          <t>2026-09-01T22:43:23Z</t>
         </is>
       </c>
     </row>
@@ -1926,7 +1926,7 @@
       </c>
       <c r="S21" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31T23:58:41Z</t>
+          <t>2026-09-01T22:43:23Z</t>
         </is>
       </c>
     </row>
@@ -2011,7 +2011,7 @@
       </c>
       <c r="S22" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31T23:58:41Z</t>
+          <t>2026-09-01T22:43:23Z</t>
         </is>
       </c>
     </row>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="S23" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31T23:58:41Z</t>
+          <t>2026-09-01T22:43:23Z</t>
         </is>
       </c>
     </row>
@@ -2181,7 +2181,7 @@
       </c>
       <c r="S24" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31T23:58:41Z</t>
+          <t>2026-09-01T22:43:23Z</t>
         </is>
       </c>
     </row>
@@ -2266,7 +2266,7 @@
       </c>
       <c r="S25" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31T23:58:41Z</t>
+          <t>2026-09-01T22:43:23Z</t>
         </is>
       </c>
     </row>
@@ -2351,7 +2351,7 @@
       </c>
       <c r="S26" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31T23:58:41Z</t>
+          <t>2026-09-01T22:43:23Z</t>
         </is>
       </c>
     </row>
@@ -2436,7 +2436,7 @@
       </c>
       <c r="S27" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31T23:58:41Z</t>
+          <t>2026-09-01T22:43:23Z</t>
         </is>
       </c>
     </row>
@@ -2521,7 +2521,7 @@
       </c>
       <c r="S28" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31T23:58:41Z</t>
+          <t>2026-09-01T22:43:23Z</t>
         </is>
       </c>
     </row>
@@ -2606,7 +2606,7 @@
       </c>
       <c r="S29" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31T23:58:41Z</t>
+          <t>2026-09-01T22:43:23Z</t>
         </is>
       </c>
     </row>
@@ -2691,7 +2691,7 @@
       </c>
       <c r="S30" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31T23:58:41Z</t>
+          <t>2026-09-01T22:43:23Z</t>
         </is>
       </c>
     </row>
@@ -2776,7 +2776,7 @@
       </c>
       <c r="S31" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31T23:58:41Z</t>
+          <t>2026-09-01T22:43:23Z</t>
         </is>
       </c>
     </row>
@@ -2861,7 +2861,7 @@
       </c>
       <c r="S32" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31T23:58:41Z</t>
+          <t>2026-09-01T22:43:23Z</t>
         </is>
       </c>
     </row>
@@ -2946,7 +2946,7 @@
       </c>
       <c r="S33" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31T23:58:41Z</t>
+          <t>2026-09-01T22:43:23Z</t>
         </is>
       </c>
     </row>
@@ -3031,7 +3031,7 @@
       </c>
       <c r="S34" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31T23:58:41Z</t>
+          <t>2026-09-01T22:43:23Z</t>
         </is>
       </c>
     </row>
@@ -3116,7 +3116,7 @@
       </c>
       <c r="S35" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31T23:58:41Z</t>
+          <t>2026-09-01T22:43:23Z</t>
         </is>
       </c>
     </row>
@@ -3201,7 +3201,7 @@
       </c>
       <c r="S36" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31T23:58:41Z</t>
+          <t>2026-09-01T22:43:23Z</t>
         </is>
       </c>
     </row>
@@ -3286,7 +3286,7 @@
       </c>
       <c r="S37" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31T23:58:41Z</t>
+          <t>2026-09-01T22:43:23Z</t>
         </is>
       </c>
     </row>
@@ -3371,7 +3371,7 @@
       </c>
       <c r="S38" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31T23:58:41Z</t>
+          <t>2026-09-01T22:43:23Z</t>
         </is>
       </c>
     </row>
@@ -3456,7 +3456,7 @@
       </c>
       <c r="S39" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31T23:58:41Z</t>
+          <t>2026-09-01T22:43:23Z</t>
         </is>
       </c>
     </row>
@@ -3541,7 +3541,7 @@
       </c>
       <c r="S40" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31T23:58:41Z</t>
+          <t>2026-09-01T22:43:23Z</t>
         </is>
       </c>
     </row>
@@ -3626,7 +3626,7 @@
       </c>
       <c r="S41" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31T23:58:41Z</t>
+          <t>2026-09-01T22:43:23Z</t>
         </is>
       </c>
     </row>
@@ -3711,7 +3711,7 @@
       </c>
       <c r="S42" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31T23:58:41Z</t>
+          <t>2026-09-01T22:43:23Z</t>
         </is>
       </c>
     </row>
@@ -3796,7 +3796,7 @@
       </c>
       <c r="S43" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31T23:58:41Z</t>
+          <t>2026-09-01T22:43:23Z</t>
         </is>
       </c>
     </row>
@@ -3881,7 +3881,7 @@
       </c>
       <c r="S44" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31T23:58:41Z</t>
+          <t>2026-09-01T22:43:23Z</t>
         </is>
       </c>
     </row>
@@ -3966,7 +3966,7 @@
       </c>
       <c r="S45" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31T23:58:41Z</t>
+          <t>2026-09-01T22:43:23Z</t>
         </is>
       </c>
     </row>
@@ -4051,7 +4051,7 @@
       </c>
       <c r="S46" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31T23:58:41Z</t>
+          <t>2026-09-01T22:43:23Z</t>
         </is>
       </c>
     </row>
@@ -4136,7 +4136,7 @@
       </c>
       <c r="S47" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31T23:58:41Z</t>
+          <t>2026-09-01T22:43:23Z</t>
         </is>
       </c>
     </row>
@@ -4221,7 +4221,7 @@
       </c>
       <c r="S48" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31T23:58:41Z</t>
+          <t>2026-09-01T22:43:23Z</t>
         </is>
       </c>
     </row>
@@ -4306,7 +4306,7 @@
       </c>
       <c r="S49" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31T23:58:41Z</t>
+          <t>2026-09-01T22:43:23Z</t>
         </is>
       </c>
     </row>
@@ -4391,7 +4391,7 @@
       </c>
       <c r="S50" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31T23:58:41Z</t>
+          <t>2026-09-01T22:43:23Z</t>
         </is>
       </c>
     </row>
@@ -4476,7 +4476,7 @@
       </c>
       <c r="S51" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31T23:58:41Z</t>
+          <t>2026-09-01T22:43:23Z</t>
         </is>
       </c>
     </row>
@@ -4561,7 +4561,7 @@
       </c>
       <c r="S52" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31T23:58:41Z</t>
+          <t>2026-09-01T22:43:23Z</t>
         </is>
       </c>
     </row>
@@ -4646,7 +4646,7 @@
       </c>
       <c r="S53" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31T23:58:41Z</t>
+          <t>2026-09-01T22:43:23Z</t>
         </is>
       </c>
     </row>
@@ -4731,7 +4731,7 @@
       </c>
       <c r="S54" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31T23:58:41Z</t>
+          <t>2026-09-01T22:43:23Z</t>
         </is>
       </c>
     </row>
@@ -4816,7 +4816,7 @@
       </c>
       <c r="S55" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31T23:58:41Z</t>
+          <t>2026-09-01T22:43:23Z</t>
         </is>
       </c>
     </row>
@@ -4901,7 +4901,7 @@
       </c>
       <c r="S56" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31T23:58:41Z</t>
+          <t>2026-09-01T22:43:23Z</t>
         </is>
       </c>
     </row>
@@ -4986,7 +4986,7 @@
       </c>
       <c r="S57" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31T23:58:41Z</t>
+          <t>2026-09-01T22:43:23Z</t>
         </is>
       </c>
     </row>
@@ -5071,7 +5071,7 @@
       </c>
       <c r="S58" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31T23:58:41Z</t>
+          <t>2026-09-01T22:43:23Z</t>
         </is>
       </c>
     </row>
@@ -5156,7 +5156,7 @@
       </c>
       <c r="S59" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31T23:58:41Z</t>
+          <t>2026-09-01T22:43:23Z</t>
         </is>
       </c>
     </row>
@@ -5241,7 +5241,7 @@
       </c>
       <c r="S60" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31T23:58:41Z</t>
+          <t>2026-09-01T22:43:23Z</t>
         </is>
       </c>
     </row>
@@ -5326,7 +5326,7 @@
       </c>
       <c r="S61" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31T23:58:41Z</t>
+          <t>2026-09-01T22:43:23Z</t>
         </is>
       </c>
     </row>
@@ -5411,7 +5411,7 @@
       </c>
       <c r="S62" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31T23:58:41Z</t>
+          <t>2026-09-01T22:43:23Z</t>
         </is>
       </c>
     </row>
@@ -5496,7 +5496,7 @@
       </c>
       <c r="S63" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31T23:58:41Z</t>
+          <t>2026-09-01T22:43:23Z</t>
         </is>
       </c>
     </row>
@@ -5581,7 +5581,7 @@
       </c>
       <c r="S64" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31T23:58:41Z</t>
+          <t>2026-09-01T22:43:23Z</t>
         </is>
       </c>
     </row>
@@ -5666,7 +5666,7 @@
       </c>
       <c r="S65" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31T23:58:41Z</t>
+          <t>2026-09-01T22:43:23Z</t>
         </is>
       </c>
     </row>
@@ -5751,7 +5751,7 @@
       </c>
       <c r="S66" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31T23:58:41Z</t>
+          <t>2026-09-01T22:43:23Z</t>
         </is>
       </c>
     </row>
@@ -5836,7 +5836,7 @@
       </c>
       <c r="S67" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31T23:58:41Z</t>
+          <t>2026-09-01T22:43:23Z</t>
         </is>
       </c>
     </row>
@@ -5921,7 +5921,7 @@
       </c>
       <c r="S68" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31T23:58:41Z</t>
+          <t>2026-09-01T22:43:23Z</t>
         </is>
       </c>
     </row>
@@ -6006,7 +6006,7 @@
       </c>
       <c r="S69" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31T23:58:41Z</t>
+          <t>2026-09-01T22:43:23Z</t>
         </is>
       </c>
     </row>
@@ -6091,7 +6091,7 @@
       </c>
       <c r="S70" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31T23:58:41Z</t>
+          <t>2026-09-01T22:43:23Z</t>
         </is>
       </c>
     </row>
@@ -6176,7 +6176,7 @@
       </c>
       <c r="S71" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31T23:58:41Z</t>
+          <t>2026-09-01T22:43:23Z</t>
         </is>
       </c>
     </row>
@@ -6261,7 +6261,7 @@
       </c>
       <c r="S72" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31T23:58:41Z</t>
+          <t>2026-09-01T22:43:23Z</t>
         </is>
       </c>
     </row>
@@ -6346,7 +6346,7 @@
       </c>
       <c r="S73" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31T23:58:41Z</t>
+          <t>2026-09-01T22:43:23Z</t>
         </is>
       </c>
     </row>
@@ -6431,7 +6431,7 @@
       </c>
       <c r="S74" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31T23:58:41Z</t>
+          <t>2026-09-01T22:43:23Z</t>
         </is>
       </c>
     </row>
@@ -6516,7 +6516,7 @@
       </c>
       <c r="S75" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31T23:58:41Z</t>
+          <t>2026-09-01T22:43:23Z</t>
         </is>
       </c>
     </row>
@@ -6601,7 +6601,7 @@
       </c>
       <c r="S76" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31T23:58:41Z</t>
+          <t>2026-09-01T22:43:23Z</t>
         </is>
       </c>
     </row>
@@ -6686,7 +6686,7 @@
       </c>
       <c r="S77" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31T23:58:41Z</t>
+          <t>2026-09-01T22:43:23Z</t>
         </is>
       </c>
     </row>
@@ -6771,7 +6771,7 @@
       </c>
       <c r="S78" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31T23:58:41Z</t>
+          <t>2026-09-01T22:43:23Z</t>
         </is>
       </c>
     </row>
@@ -6856,7 +6856,7 @@
       </c>
       <c r="S79" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31T23:58:41Z</t>
+          <t>2026-09-01T22:43:23Z</t>
         </is>
       </c>
     </row>
@@ -6941,7 +6941,7 @@
       </c>
       <c r="S80" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31T23:58:41Z</t>
+          <t>2026-09-01T22:43:23Z</t>
         </is>
       </c>
     </row>
@@ -7026,7 +7026,7 @@
       </c>
       <c r="S81" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31T23:58:41Z</t>
+          <t>2026-09-01T22:43:23Z</t>
         </is>
       </c>
     </row>
@@ -7111,7 +7111,7 @@
       </c>
       <c r="S82" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31T23:58:41Z</t>
+          <t>2026-09-01T22:43:23Z</t>
         </is>
       </c>
     </row>
@@ -7196,7 +7196,7 @@
       </c>
       <c r="S83" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31T23:58:41Z</t>
+          <t>2026-09-01T22:43:23Z</t>
         </is>
       </c>
     </row>
@@ -7281,7 +7281,7 @@
       </c>
       <c r="S84" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31T23:58:41Z</t>
+          <t>2026-09-01T22:43:23Z</t>
         </is>
       </c>
     </row>
@@ -7366,7 +7366,7 @@
       </c>
       <c r="S85" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31T23:58:41Z</t>
+          <t>2026-09-01T22:43:23Z</t>
         </is>
       </c>
     </row>
@@ -7451,7 +7451,7 @@
       </c>
       <c r="S86" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31T23:58:41Z</t>
+          <t>2026-09-01T22:43:23Z</t>
         </is>
       </c>
     </row>
@@ -7536,7 +7536,7 @@
       </c>
       <c r="S87" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31T23:58:41Z</t>
+          <t>2026-09-01T22:43:23Z</t>
         </is>
       </c>
     </row>
@@ -7621,7 +7621,7 @@
       </c>
       <c r="S88" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31T23:58:41Z</t>
+          <t>2026-09-01T22:43:23Z</t>
         </is>
       </c>
     </row>
@@ -7706,7 +7706,7 @@
       </c>
       <c r="S89" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31T23:58:41Z</t>
+          <t>2026-09-01T22:43:23Z</t>
         </is>
       </c>
     </row>
@@ -7791,7 +7791,7 @@
       </c>
       <c r="S90" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31T23:58:41Z</t>
+          <t>2026-09-01T22:43:23Z</t>
         </is>
       </c>
     </row>
@@ -7876,7 +7876,7 @@
       </c>
       <c r="S91" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31T23:58:41Z</t>
+          <t>2026-09-01T22:43:23Z</t>
         </is>
       </c>
     </row>
@@ -7961,7 +7961,7 @@
       </c>
       <c r="S92" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31T23:58:41Z</t>
+          <t>2026-09-01T22:43:23Z</t>
         </is>
       </c>
     </row>
@@ -8046,7 +8046,7 @@
       </c>
       <c r="S93" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31T23:58:41Z</t>
+          <t>2026-09-01T22:43:23Z</t>
         </is>
       </c>
     </row>
@@ -8131,7 +8131,7 @@
       </c>
       <c r="S94" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31T23:58:41Z</t>
+          <t>2026-09-01T22:43:23Z</t>
         </is>
       </c>
     </row>
@@ -8216,7 +8216,7 @@
       </c>
       <c r="S95" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31T23:58:41Z</t>
+          <t>2026-09-01T22:43:23Z</t>
         </is>
       </c>
     </row>
@@ -8301,7 +8301,7 @@
       </c>
       <c r="S96" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31T23:58:41Z</t>
+          <t>2026-09-01T22:43:23Z</t>
         </is>
       </c>
     </row>
@@ -8386,7 +8386,7 @@
       </c>
       <c r="S97" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31T23:58:41Z</t>
+          <t>2026-09-01T22:43:23Z</t>
         </is>
       </c>
     </row>
@@ -8471,7 +8471,7 @@
       </c>
       <c r="S98" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31T23:58:41Z</t>
+          <t>2026-09-01T22:43:23Z</t>
         </is>
       </c>
     </row>
@@ -8556,7 +8556,7 @@
       </c>
       <c r="S99" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31T23:58:41Z</t>
+          <t>2026-09-01T22:43:23Z</t>
         </is>
       </c>
     </row>
@@ -8641,7 +8641,7 @@
       </c>
       <c r="S100" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31T23:58:41Z</t>
+          <t>2026-09-01T22:43:23Z</t>
         </is>
       </c>
     </row>
@@ -8726,7 +8726,7 @@
       </c>
       <c r="S101" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31T23:58:41Z</t>
+          <t>2026-09-01T22:43:23Z</t>
         </is>
       </c>
     </row>
@@ -8811,7 +8811,7 @@
       </c>
       <c r="S102" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31T23:58:41Z</t>
+          <t>2026-09-01T22:43:23Z</t>
         </is>
       </c>
     </row>
@@ -8896,7 +8896,7 @@
       </c>
       <c r="S103" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31T23:58:41Z</t>
+          <t>2026-09-01T22:43:23Z</t>
         </is>
       </c>
     </row>
@@ -8981,7 +8981,7 @@
       </c>
       <c r="S104" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31T23:58:41Z</t>
+          <t>2026-09-01T22:43:23Z</t>
         </is>
       </c>
     </row>
@@ -9066,7 +9066,7 @@
       </c>
       <c r="S105" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31T23:58:41Z</t>
+          <t>2026-09-01T22:43:23Z</t>
         </is>
       </c>
     </row>
@@ -9151,7 +9151,7 @@
       </c>
       <c r="S106" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31T23:58:41Z</t>
+          <t>2026-09-01T22:43:23Z</t>
         </is>
       </c>
     </row>
@@ -9236,7 +9236,7 @@
       </c>
       <c r="S107" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31T23:58:41Z</t>
+          <t>2026-09-01T22:43:23Z</t>
         </is>
       </c>
     </row>
@@ -9321,7 +9321,7 @@
       </c>
       <c r="S108" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31T23:58:41Z</t>
+          <t>2026-09-01T22:43:23Z</t>
         </is>
       </c>
     </row>
@@ -9406,7 +9406,7 @@
       </c>
       <c r="S109" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31T23:58:41Z</t>
+          <t>2026-09-01T22:43:23Z</t>
         </is>
       </c>
     </row>
@@ -9491,7 +9491,7 @@
       </c>
       <c r="S110" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31T23:58:41Z</t>
+          <t>2026-09-01T22:43:23Z</t>
         </is>
       </c>
     </row>
@@ -9576,7 +9576,7 @@
       </c>
       <c r="S111" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31T23:58:41Z</t>
+          <t>2026-09-01T22:43:23Z</t>
         </is>
       </c>
     </row>
@@ -9661,7 +9661,7 @@
       </c>
       <c r="S112" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31T23:58:41Z</t>
+          <t>2026-09-01T22:43:23Z</t>
         </is>
       </c>
     </row>
@@ -9746,7 +9746,7 @@
       </c>
       <c r="S113" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31T23:58:41Z</t>
+          <t>2026-09-01T22:43:23Z</t>
         </is>
       </c>
     </row>
@@ -9831,7 +9831,7 @@
       </c>
       <c r="S114" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31T23:58:41Z</t>
+          <t>2026-09-01T22:43:23Z</t>
         </is>
       </c>
     </row>
@@ -9916,7 +9916,7 @@
       </c>
       <c r="S115" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31T23:58:41Z</t>
+          <t>2026-09-01T22:43:23Z</t>
         </is>
       </c>
     </row>
@@ -10001,7 +10001,7 @@
       </c>
       <c r="S116" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31T23:58:41Z</t>
+          <t>2026-09-01T22:43:23Z</t>
         </is>
       </c>
     </row>
@@ -10086,7 +10086,7 @@
       </c>
       <c r="S117" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31T23:58:41Z</t>
+          <t>2026-09-01T22:43:23Z</t>
         </is>
       </c>
     </row>
@@ -10171,7 +10171,7 @@
       </c>
       <c r="S118" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31T23:58:41Z</t>
+          <t>2026-09-01T22:43:23Z</t>
         </is>
       </c>
     </row>
@@ -10256,7 +10256,7 @@
       </c>
       <c r="S119" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31T23:58:41Z</t>
+          <t>2026-09-01T22:43:23Z</t>
         </is>
       </c>
     </row>
@@ -10341,7 +10341,7 @@
       </c>
       <c r="S120" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31T23:58:41Z</t>
+          <t>2026-09-01T22:43:23Z</t>
         </is>
       </c>
     </row>
@@ -10426,7 +10426,7 @@
       </c>
       <c r="S121" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31T23:58:41Z</t>
+          <t>2026-09-01T22:43:23Z</t>
         </is>
       </c>
     </row>
@@ -10511,7 +10511,7 @@
       </c>
       <c r="S122" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31T23:58:41Z</t>
+          <t>2026-09-01T22:43:23Z</t>
         </is>
       </c>
     </row>
@@ -10596,7 +10596,7 @@
       </c>
       <c r="S123" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31T23:58:41Z</t>
+          <t>2026-09-01T22:43:23Z</t>
         </is>
       </c>
     </row>
@@ -10681,7 +10681,7 @@
       </c>
       <c r="S124" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31T23:58:41Z</t>
+          <t>2026-09-01T22:43:23Z</t>
         </is>
       </c>
     </row>
@@ -10766,7 +10766,7 @@
       </c>
       <c r="S125" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31T23:58:41Z</t>
+          <t>2026-09-01T22:43:23Z</t>
         </is>
       </c>
     </row>
@@ -10851,7 +10851,7 @@
       </c>
       <c r="S126" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31T23:58:41Z</t>
+          <t>2026-09-01T22:43:23Z</t>
         </is>
       </c>
     </row>
@@ -10936,7 +10936,7 @@
       </c>
       <c r="S127" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31T23:58:41Z</t>
+          <t>2026-09-01T22:43:23Z</t>
         </is>
       </c>
     </row>
@@ -11021,7 +11021,7 @@
       </c>
       <c r="S128" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31T23:58:41Z</t>
+          <t>2026-09-01T22:43:23Z</t>
         </is>
       </c>
     </row>
@@ -11106,7 +11106,7 @@
       </c>
       <c r="S129" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31T23:58:41Z</t>
+          <t>2026-09-01T22:43:23Z</t>
         </is>
       </c>
     </row>
@@ -11191,7 +11191,7 @@
       </c>
       <c r="S130" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31T23:58:41Z</t>
+          <t>2026-09-01T22:43:23Z</t>
         </is>
       </c>
     </row>
@@ -11276,7 +11276,7 @@
       </c>
       <c r="S131" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31T23:58:41Z</t>
+          <t>2026-09-01T22:43:23Z</t>
         </is>
       </c>
     </row>
@@ -11361,7 +11361,7 @@
       </c>
       <c r="S132" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31T23:58:41Z</t>
+          <t>2026-09-01T22:43:23Z</t>
         </is>
       </c>
     </row>
@@ -11446,7 +11446,7 @@
       </c>
       <c r="S133" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31T23:58:41Z</t>
+          <t>2026-09-01T22:43:23Z</t>
         </is>
       </c>
     </row>
@@ -11531,7 +11531,7 @@
       </c>
       <c r="S134" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31T23:58:41Z</t>
+          <t>2026-09-01T22:43:23Z</t>
         </is>
       </c>
     </row>
@@ -11616,7 +11616,7 @@
       </c>
       <c r="S135" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31T23:58:41Z</t>
+          <t>2026-09-01T22:43:23Z</t>
         </is>
       </c>
     </row>
@@ -11701,7 +11701,7 @@
       </c>
       <c r="S136" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31T23:58:41Z</t>
+          <t>2026-09-01T22:43:23Z</t>
         </is>
       </c>
     </row>
@@ -11786,7 +11786,7 @@
       </c>
       <c r="S137" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31T23:58:41Z</t>
+          <t>2026-09-01T22:43:23Z</t>
         </is>
       </c>
     </row>
@@ -11871,7 +11871,7 @@
       </c>
       <c r="S138" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31T23:58:41Z</t>
+          <t>2026-09-01T22:43:23Z</t>
         </is>
       </c>
     </row>
@@ -11956,7 +11956,7 @@
       </c>
       <c r="S139" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31T23:58:41Z</t>
+          <t>2026-09-01T22:43:23Z</t>
         </is>
       </c>
     </row>
@@ -12041,7 +12041,7 @@
       </c>
       <c r="S140" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31T23:58:41Z</t>
+          <t>2026-09-01T22:43:23Z</t>
         </is>
       </c>
     </row>
@@ -12126,7 +12126,7 @@
       </c>
       <c r="S141" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31T23:58:41Z</t>
+          <t>2026-09-01T22:43:23Z</t>
         </is>
       </c>
     </row>
@@ -12258,7 +12258,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31T23:58:41Z</t>
+          <t>2026-09-01T22:43:23Z</t>
         </is>
       </c>
     </row>
@@ -12338,7 +12338,7 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>{"dataset_id": "bcv_pib_historico_anual", "title": "Producto interno bruto histórico anual", "table": "PIB histórico anual", "source_file": "7_1_14_anual.xls", "base": "1957/1968/1984/1997", "price_type": "Precios constantes", "measure": "Nivel", "frequency": "Anual", "period": "2017", "year": 2017, "quarter": null, "classification": "Total economía", "component": "Producto interno bruto", "value": 392393.12, "unit": "Millones de bolívares a precios constantes", "status": "", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/7_1_14_anual.xls", "fetched_at": "2026-08-31T23:58:41Z"}</t>
+          <t>{"dataset_id": "bcv_pib_historico_anual", "title": "Producto interno bruto histórico anual", "table": "PIB histórico anual", "source_file": "7_1_14_anual.xls", "base": "1957/1968/1984/1997", "price_type": "Precios constantes", "measure": "Nivel", "frequency": "Anual", "period": "2017", "year": 2017, "quarter": null, "classification": "Total economía", "component": "Producto interno bruto", "value": 392393.12, "unit": "Millones de bolívares a precios constantes", "status": "", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/7_1_14_anual.xls", "fetched_at": "2026-09-01T22:43:23Z"}</t>
         </is>
       </c>
     </row>

--- a/assets/data/bcv/excel/ove_bcv_pib_historico_anual.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_pib_historico_anual.xlsx
@@ -736,7 +736,7 @@
       </c>
       <c r="S7" s="4" t="inlineStr">
         <is>
-          <t>2026-09-01T22:43:23Z</t>
+          <t>2026-09-02T17:10:08Z</t>
         </is>
       </c>
     </row>
@@ -821,7 +821,7 @@
       </c>
       <c r="S8" s="4" t="inlineStr">
         <is>
-          <t>2026-09-01T22:43:23Z</t>
+          <t>2026-09-02T17:10:08Z</t>
         </is>
       </c>
     </row>
@@ -906,7 +906,7 @@
       </c>
       <c r="S9" s="4" t="inlineStr">
         <is>
-          <t>2026-09-01T22:43:23Z</t>
+          <t>2026-09-02T17:10:08Z</t>
         </is>
       </c>
     </row>
@@ -991,7 +991,7 @@
       </c>
       <c r="S10" s="4" t="inlineStr">
         <is>
-          <t>2026-09-01T22:43:23Z</t>
+          <t>2026-09-02T17:10:08Z</t>
         </is>
       </c>
     </row>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="S11" s="4" t="inlineStr">
         <is>
-          <t>2026-09-01T22:43:23Z</t>
+          <t>2026-09-02T17:10:08Z</t>
         </is>
       </c>
     </row>
@@ -1161,7 +1161,7 @@
       </c>
       <c r="S12" s="4" t="inlineStr">
         <is>
-          <t>2026-09-01T22:43:23Z</t>
+          <t>2026-09-02T17:10:08Z</t>
         </is>
       </c>
     </row>
@@ -1246,7 +1246,7 @@
       </c>
       <c r="S13" s="4" t="inlineStr">
         <is>
-          <t>2026-09-01T22:43:23Z</t>
+          <t>2026-09-02T17:10:08Z</t>
         </is>
       </c>
     </row>
@@ -1331,7 +1331,7 @@
       </c>
       <c r="S14" s="4" t="inlineStr">
         <is>
-          <t>2026-09-01T22:43:23Z</t>
+          <t>2026-09-02T17:10:08Z</t>
         </is>
       </c>
     </row>
@@ -1416,7 +1416,7 @@
       </c>
       <c r="S15" s="4" t="inlineStr">
         <is>
-          <t>2026-09-01T22:43:23Z</t>
+          <t>2026-09-02T17:10:08Z</t>
         </is>
       </c>
     </row>
@@ -1501,7 +1501,7 @@
       </c>
       <c r="S16" s="4" t="inlineStr">
         <is>
-          <t>2026-09-01T22:43:23Z</t>
+          <t>2026-09-02T17:10:08Z</t>
         </is>
       </c>
     </row>
@@ -1586,7 +1586,7 @@
       </c>
       <c r="S17" s="4" t="inlineStr">
         <is>
-          <t>2026-09-01T22:43:23Z</t>
+          <t>2026-09-02T17:10:08Z</t>
         </is>
       </c>
     </row>
@@ -1671,7 +1671,7 @@
       </c>
       <c r="S18" s="4" t="inlineStr">
         <is>
-          <t>2026-09-01T22:43:23Z</t>
+          <t>2026-09-02T17:10:08Z</t>
         </is>
       </c>
     </row>
@@ -1756,7 +1756,7 @@
       </c>
       <c r="S19" s="4" t="inlineStr">
         <is>
-          <t>2026-09-01T22:43:23Z</t>
+          <t>2026-09-02T17:10:08Z</t>
         </is>
       </c>
     </row>
@@ -1841,7 +1841,7 @@
       </c>
       <c r="S20" s="4" t="inlineStr">
         <is>
-          <t>2026-09-01T22:43:23Z</t>
+          <t>2026-09-02T17:10:08Z</t>
         </is>
       </c>
     </row>
@@ -1926,7 +1926,7 @@
       </c>
       <c r="S21" s="4" t="inlineStr">
         <is>
-          <t>2026-09-01T22:43:23Z</t>
+          <t>2026-09-02T17:10:08Z</t>
         </is>
       </c>
     </row>
@@ -2011,7 +2011,7 @@
       </c>
       <c r="S22" s="4" t="inlineStr">
         <is>
-          <t>2026-09-01T22:43:23Z</t>
+          <t>2026-09-02T17:10:08Z</t>
         </is>
       </c>
     </row>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="S23" s="4" t="inlineStr">
         <is>
-          <t>2026-09-01T22:43:23Z</t>
+          <t>2026-09-02T17:10:08Z</t>
         </is>
       </c>
     </row>
@@ -2181,7 +2181,7 @@
       </c>
       <c r="S24" s="4" t="inlineStr">
         <is>
-          <t>2026-09-01T22:43:23Z</t>
+          <t>2026-09-02T17:10:08Z</t>
         </is>
       </c>
     </row>
@@ -2266,7 +2266,7 @@
       </c>
       <c r="S25" s="4" t="inlineStr">
         <is>
-          <t>2026-09-01T22:43:23Z</t>
+          <t>2026-09-02T17:10:08Z</t>
         </is>
       </c>
     </row>
@@ -2351,7 +2351,7 @@
       </c>
       <c r="S26" s="4" t="inlineStr">
         <is>
-          <t>2026-09-01T22:43:23Z</t>
+          <t>2026-09-02T17:10:08Z</t>
         </is>
       </c>
     </row>
@@ -2436,7 +2436,7 @@
       </c>
       <c r="S27" s="4" t="inlineStr">
         <is>
-          <t>2026-09-01T22:43:23Z</t>
+          <t>2026-09-02T17:10:08Z</t>
         </is>
       </c>
     </row>
@@ -2521,7 +2521,7 @@
       </c>
       <c r="S28" s="4" t="inlineStr">
         <is>
-          <t>2026-09-01T22:43:23Z</t>
+          <t>2026-09-02T17:10:08Z</t>
         </is>
       </c>
     </row>
@@ -2606,7 +2606,7 @@
       </c>
       <c r="S29" s="4" t="inlineStr">
         <is>
-          <t>2026-09-01T22:43:23Z</t>
+          <t>2026-09-02T17:10:08Z</t>
         </is>
       </c>
     </row>
@@ -2691,7 +2691,7 @@
       </c>
       <c r="S30" s="4" t="inlineStr">
         <is>
-          <t>2026-09-01T22:43:23Z</t>
+          <t>2026-09-02T17:10:08Z</t>
         </is>
       </c>
     </row>
@@ -2776,7 +2776,7 @@
       </c>
       <c r="S31" s="4" t="inlineStr">
         <is>
-          <t>2026-09-01T22:43:23Z</t>
+          <t>2026-09-02T17:10:08Z</t>
         </is>
       </c>
     </row>
@@ -2861,7 +2861,7 @@
       </c>
       <c r="S32" s="4" t="inlineStr">
         <is>
-          <t>2026-09-01T22:43:23Z</t>
+          <t>2026-09-02T17:10:08Z</t>
         </is>
       </c>
     </row>
@@ -2946,7 +2946,7 @@
       </c>
       <c r="S33" s="4" t="inlineStr">
         <is>
-          <t>2026-09-01T22:43:23Z</t>
+          <t>2026-09-02T17:10:08Z</t>
         </is>
       </c>
     </row>
@@ -3031,7 +3031,7 @@
       </c>
       <c r="S34" s="4" t="inlineStr">
         <is>
-          <t>2026-09-01T22:43:23Z</t>
+          <t>2026-09-02T17:10:08Z</t>
         </is>
       </c>
     </row>
@@ -3116,7 +3116,7 @@
       </c>
       <c r="S35" s="4" t="inlineStr">
         <is>
-          <t>2026-09-01T22:43:23Z</t>
+          <t>2026-09-02T17:10:08Z</t>
         </is>
       </c>
     </row>
@@ -3201,7 +3201,7 @@
       </c>
       <c r="S36" s="4" t="inlineStr">
         <is>
-          <t>2026-09-01T22:43:23Z</t>
+          <t>2026-09-02T17:10:08Z</t>
         </is>
       </c>
     </row>
@@ -3286,7 +3286,7 @@
       </c>
       <c r="S37" s="4" t="inlineStr">
         <is>
-          <t>2026-09-01T22:43:23Z</t>
+          <t>2026-09-02T17:10:08Z</t>
         </is>
       </c>
     </row>
@@ -3371,7 +3371,7 @@
       </c>
       <c r="S38" s="4" t="inlineStr">
         <is>
-          <t>2026-09-01T22:43:23Z</t>
+          <t>2026-09-02T17:10:08Z</t>
         </is>
       </c>
     </row>
@@ -3456,7 +3456,7 @@
       </c>
       <c r="S39" s="4" t="inlineStr">
         <is>
-          <t>2026-09-01T22:43:23Z</t>
+          <t>2026-09-02T17:10:08Z</t>
         </is>
       </c>
     </row>
@@ -3541,7 +3541,7 @@
       </c>
       <c r="S40" s="4" t="inlineStr">
         <is>
-          <t>2026-09-01T22:43:23Z</t>
+          <t>2026-09-02T17:10:08Z</t>
         </is>
       </c>
     </row>
@@ -3626,7 +3626,7 @@
       </c>
       <c r="S41" s="4" t="inlineStr">
         <is>
-          <t>2026-09-01T22:43:23Z</t>
+          <t>2026-09-02T17:10:08Z</t>
         </is>
       </c>
     </row>
@@ -3711,7 +3711,7 @@
       </c>
       <c r="S42" s="4" t="inlineStr">
         <is>
-          <t>2026-09-01T22:43:23Z</t>
+          <t>2026-09-02T17:10:08Z</t>
         </is>
       </c>
     </row>
@@ -3796,7 +3796,7 @@
       </c>
       <c r="S43" s="4" t="inlineStr">
         <is>
-          <t>2026-09-01T22:43:23Z</t>
+          <t>2026-09-02T17:10:08Z</t>
         </is>
       </c>
     </row>
@@ -3881,7 +3881,7 @@
       </c>
       <c r="S44" s="4" t="inlineStr">
         <is>
-          <t>2026-09-01T22:43:23Z</t>
+          <t>2026-09-02T17:10:08Z</t>
         </is>
       </c>
     </row>
@@ -3966,7 +3966,7 @@
       </c>
       <c r="S45" s="4" t="inlineStr">
         <is>
-          <t>2026-09-01T22:43:23Z</t>
+          <t>2026-09-02T17:10:08Z</t>
         </is>
       </c>
     </row>
@@ -4051,7 +4051,7 @@
       </c>
       <c r="S46" s="4" t="inlineStr">
         <is>
-          <t>2026-09-01T22:43:23Z</t>
+          <t>2026-09-02T17:10:08Z</t>
         </is>
       </c>
     </row>
@@ -4136,7 +4136,7 @@
       </c>
       <c r="S47" s="4" t="inlineStr">
         <is>
-          <t>2026-09-01T22:43:23Z</t>
+          <t>2026-09-02T17:10:08Z</t>
         </is>
       </c>
     </row>
@@ -4221,7 +4221,7 @@
       </c>
       <c r="S48" s="4" t="inlineStr">
         <is>
-          <t>2026-09-01T22:43:23Z</t>
+          <t>2026-09-02T17:10:08Z</t>
         </is>
       </c>
     </row>
@@ -4306,7 +4306,7 @@
       </c>
       <c r="S49" s="4" t="inlineStr">
         <is>
-          <t>2026-09-01T22:43:23Z</t>
+          <t>2026-09-02T17:10:08Z</t>
         </is>
       </c>
     </row>
@@ -4391,7 +4391,7 @@
       </c>
       <c r="S50" s="4" t="inlineStr">
         <is>
-          <t>2026-09-01T22:43:23Z</t>
+          <t>2026-09-02T17:10:08Z</t>
         </is>
       </c>
     </row>
@@ -4476,7 +4476,7 @@
       </c>
       <c r="S51" s="4" t="inlineStr">
         <is>
-          <t>2026-09-01T22:43:23Z</t>
+          <t>2026-09-02T17:10:08Z</t>
         </is>
       </c>
     </row>
@@ -4561,7 +4561,7 @@
       </c>
       <c r="S52" s="4" t="inlineStr">
         <is>
-          <t>2026-09-01T22:43:23Z</t>
+          <t>2026-09-02T17:10:08Z</t>
         </is>
       </c>
     </row>
@@ -4646,7 +4646,7 @@
       </c>
       <c r="S53" s="4" t="inlineStr">
         <is>
-          <t>2026-09-01T22:43:23Z</t>
+          <t>2026-09-02T17:10:08Z</t>
         </is>
       </c>
     </row>
@@ -4731,7 +4731,7 @@
       </c>
       <c r="S54" s="4" t="inlineStr">
         <is>
-          <t>2026-09-01T22:43:23Z</t>
+          <t>2026-09-02T17:10:08Z</t>
         </is>
       </c>
     </row>
@@ -4816,7 +4816,7 @@
       </c>
       <c r="S55" s="4" t="inlineStr">
         <is>
-          <t>2026-09-01T22:43:23Z</t>
+          <t>2026-09-02T17:10:08Z</t>
         </is>
       </c>
     </row>
@@ -4901,7 +4901,7 @@
       </c>
       <c r="S56" s="4" t="inlineStr">
         <is>
-          <t>2026-09-01T22:43:23Z</t>
+          <t>2026-09-02T17:10:08Z</t>
         </is>
       </c>
     </row>
@@ -4986,7 +4986,7 @@
       </c>
       <c r="S57" s="4" t="inlineStr">
         <is>
-          <t>2026-09-01T22:43:23Z</t>
+          <t>2026-09-02T17:10:08Z</t>
         </is>
       </c>
     </row>
@@ -5071,7 +5071,7 @@
       </c>
       <c r="S58" s="4" t="inlineStr">
         <is>
-          <t>2026-09-01T22:43:23Z</t>
+          <t>2026-09-02T17:10:08Z</t>
         </is>
       </c>
     </row>
@@ -5156,7 +5156,7 @@
       </c>
       <c r="S59" s="4" t="inlineStr">
         <is>
-          <t>2026-09-01T22:43:23Z</t>
+          <t>2026-09-02T17:10:08Z</t>
         </is>
       </c>
     </row>
@@ -5241,7 +5241,7 @@
       </c>
       <c r="S60" s="4" t="inlineStr">
         <is>
-          <t>2026-09-01T22:43:23Z</t>
+          <t>2026-09-02T17:10:08Z</t>
         </is>
       </c>
     </row>
@@ -5326,7 +5326,7 @@
       </c>
       <c r="S61" s="4" t="inlineStr">
         <is>
-          <t>2026-09-01T22:43:23Z</t>
+          <t>2026-09-02T17:10:08Z</t>
         </is>
       </c>
     </row>
@@ -5411,7 +5411,7 @@
       </c>
       <c r="S62" s="4" t="inlineStr">
         <is>
-          <t>2026-09-01T22:43:23Z</t>
+          <t>2026-09-02T17:10:08Z</t>
         </is>
       </c>
     </row>
@@ -5496,7 +5496,7 @@
       </c>
       <c r="S63" s="4" t="inlineStr">
         <is>
-          <t>2026-09-01T22:43:23Z</t>
+          <t>2026-09-02T17:10:08Z</t>
         </is>
       </c>
     </row>
@@ -5581,7 +5581,7 @@
       </c>
       <c r="S64" s="4" t="inlineStr">
         <is>
-          <t>2026-09-01T22:43:23Z</t>
+          <t>2026-09-02T17:10:08Z</t>
         </is>
       </c>
     </row>
@@ -5666,7 +5666,7 @@
       </c>
       <c r="S65" s="4" t="inlineStr">
         <is>
-          <t>2026-09-01T22:43:23Z</t>
+          <t>2026-09-02T17:10:08Z</t>
         </is>
       </c>
     </row>
@@ -5751,7 +5751,7 @@
       </c>
       <c r="S66" s="4" t="inlineStr">
         <is>
-          <t>2026-09-01T22:43:23Z</t>
+          <t>2026-09-02T17:10:08Z</t>
         </is>
       </c>
     </row>
@@ -5836,7 +5836,7 @@
       </c>
       <c r="S67" s="4" t="inlineStr">
         <is>
-          <t>2026-09-01T22:43:23Z</t>
+          <t>2026-09-02T17:10:08Z</t>
         </is>
       </c>
     </row>
@@ -5921,7 +5921,7 @@
       </c>
       <c r="S68" s="4" t="inlineStr">
         <is>
-          <t>2026-09-01T22:43:23Z</t>
+          <t>2026-09-02T17:10:08Z</t>
         </is>
       </c>
     </row>
@@ -6006,7 +6006,7 @@
       </c>
       <c r="S69" s="4" t="inlineStr">
         <is>
-          <t>2026-09-01T22:43:23Z</t>
+          <t>2026-09-02T17:10:08Z</t>
         </is>
       </c>
     </row>
@@ -6091,7 +6091,7 @@
       </c>
       <c r="S70" s="4" t="inlineStr">
         <is>
-          <t>2026-09-01T22:43:23Z</t>
+          <t>2026-09-02T17:10:08Z</t>
         </is>
       </c>
     </row>
@@ -6176,7 +6176,7 @@
       </c>
       <c r="S71" s="4" t="inlineStr">
         <is>
-          <t>2026-09-01T22:43:23Z</t>
+          <t>2026-09-02T17:10:08Z</t>
         </is>
       </c>
     </row>
@@ -6261,7 +6261,7 @@
       </c>
       <c r="S72" s="4" t="inlineStr">
         <is>
-          <t>2026-09-01T22:43:23Z</t>
+          <t>2026-09-02T17:10:08Z</t>
         </is>
       </c>
     </row>
@@ -6346,7 +6346,7 @@
       </c>
       <c r="S73" s="4" t="inlineStr">
         <is>
-          <t>2026-09-01T22:43:23Z</t>
+          <t>2026-09-02T17:10:08Z</t>
         </is>
       </c>
     </row>
@@ -6431,7 +6431,7 @@
       </c>
       <c r="S74" s="4" t="inlineStr">
         <is>
-          <t>2026-09-01T22:43:23Z</t>
+          <t>2026-09-02T17:10:08Z</t>
         </is>
       </c>
     </row>
@@ -6516,7 +6516,7 @@
       </c>
       <c r="S75" s="4" t="inlineStr">
         <is>
-          <t>2026-09-01T22:43:23Z</t>
+          <t>2026-09-02T17:10:08Z</t>
         </is>
       </c>
     </row>
@@ -6601,7 +6601,7 @@
       </c>
       <c r="S76" s="4" t="inlineStr">
         <is>
-          <t>2026-09-01T22:43:23Z</t>
+          <t>2026-09-02T17:10:08Z</t>
         </is>
       </c>
     </row>
@@ -6686,7 +6686,7 @@
       </c>
       <c r="S77" s="4" t="inlineStr">
         <is>
-          <t>2026-09-01T22:43:23Z</t>
+          <t>2026-09-02T17:10:08Z</t>
         </is>
       </c>
     </row>
@@ -6771,7 +6771,7 @@
       </c>
       <c r="S78" s="4" t="inlineStr">
         <is>
-          <t>2026-09-01T22:43:23Z</t>
+          <t>2026-09-02T17:10:08Z</t>
         </is>
       </c>
     </row>
@@ -6856,7 +6856,7 @@
       </c>
       <c r="S79" s="4" t="inlineStr">
         <is>
-          <t>2026-09-01T22:43:23Z</t>
+          <t>2026-09-02T17:10:08Z</t>
         </is>
       </c>
     </row>
@@ -6941,7 +6941,7 @@
       </c>
       <c r="S80" s="4" t="inlineStr">
         <is>
-          <t>2026-09-01T22:43:23Z</t>
+          <t>2026-09-02T17:10:08Z</t>
         </is>
       </c>
     </row>
@@ -7026,7 +7026,7 @@
       </c>
       <c r="S81" s="4" t="inlineStr">
         <is>
-          <t>2026-09-01T22:43:23Z</t>
+          <t>2026-09-02T17:10:08Z</t>
         </is>
       </c>
     </row>
@@ -7111,7 +7111,7 @@
       </c>
       <c r="S82" s="4" t="inlineStr">
         <is>
-          <t>2026-09-01T22:43:23Z</t>
+          <t>2026-09-02T17:10:08Z</t>
         </is>
       </c>
     </row>
@@ -7196,7 +7196,7 @@
       </c>
       <c r="S83" s="4" t="inlineStr">
         <is>
-          <t>2026-09-01T22:43:23Z</t>
+          <t>2026-09-02T17:10:08Z</t>
         </is>
       </c>
     </row>
@@ -7281,7 +7281,7 @@
       </c>
       <c r="S84" s="4" t="inlineStr">
         <is>
-          <t>2026-09-01T22:43:23Z</t>
+          <t>2026-09-02T17:10:08Z</t>
         </is>
       </c>
     </row>
@@ -7366,7 +7366,7 @@
       </c>
       <c r="S85" s="4" t="inlineStr">
         <is>
-          <t>2026-09-01T22:43:23Z</t>
+          <t>2026-09-02T17:10:08Z</t>
         </is>
       </c>
     </row>
@@ -7451,7 +7451,7 @@
       </c>
       <c r="S86" s="4" t="inlineStr">
         <is>
-          <t>2026-09-01T22:43:23Z</t>
+          <t>2026-09-02T17:10:08Z</t>
         </is>
       </c>
     </row>
@@ -7536,7 +7536,7 @@
       </c>
       <c r="S87" s="4" t="inlineStr">
         <is>
-          <t>2026-09-01T22:43:23Z</t>
+          <t>2026-09-02T17:10:08Z</t>
         </is>
       </c>
     </row>
@@ -7621,7 +7621,7 @@
       </c>
       <c r="S88" s="4" t="inlineStr">
         <is>
-          <t>2026-09-01T22:43:23Z</t>
+          <t>2026-09-02T17:10:08Z</t>
         </is>
       </c>
     </row>
@@ -7706,7 +7706,7 @@
       </c>
       <c r="S89" s="4" t="inlineStr">
         <is>
-          <t>2026-09-01T22:43:23Z</t>
+          <t>2026-09-02T17:10:08Z</t>
         </is>
       </c>
     </row>
@@ -7791,7 +7791,7 @@
       </c>
       <c r="S90" s="4" t="inlineStr">
         <is>
-          <t>2026-09-01T22:43:23Z</t>
+          <t>2026-09-02T17:10:08Z</t>
         </is>
       </c>
     </row>
@@ -7876,7 +7876,7 @@
       </c>
       <c r="S91" s="4" t="inlineStr">
         <is>
-          <t>2026-09-01T22:43:23Z</t>
+          <t>2026-09-02T17:10:08Z</t>
         </is>
       </c>
     </row>
@@ -7961,7 +7961,7 @@
       </c>
       <c r="S92" s="4" t="inlineStr">
         <is>
-          <t>2026-09-01T22:43:23Z</t>
+          <t>2026-09-02T17:10:08Z</t>
         </is>
       </c>
     </row>
@@ -8046,7 +8046,7 @@
       </c>
       <c r="S93" s="4" t="inlineStr">
         <is>
-          <t>2026-09-01T22:43:23Z</t>
+          <t>2026-09-02T17:10:08Z</t>
         </is>
       </c>
     </row>
@@ -8131,7 +8131,7 @@
       </c>
       <c r="S94" s="4" t="inlineStr">
         <is>
-          <t>2026-09-01T22:43:23Z</t>
+          <t>2026-09-02T17:10:08Z</t>
         </is>
       </c>
     </row>
@@ -8216,7 +8216,7 @@
       </c>
       <c r="S95" s="4" t="inlineStr">
         <is>
-          <t>2026-09-01T22:43:23Z</t>
+          <t>2026-09-02T17:10:08Z</t>
         </is>
       </c>
     </row>
@@ -8301,7 +8301,7 @@
       </c>
       <c r="S96" s="4" t="inlineStr">
         <is>
-          <t>2026-09-01T22:43:23Z</t>
+          <t>2026-09-02T17:10:08Z</t>
         </is>
       </c>
     </row>
@@ -8386,7 +8386,7 @@
       </c>
       <c r="S97" s="4" t="inlineStr">
         <is>
-          <t>2026-09-01T22:43:23Z</t>
+          <t>2026-09-02T17:10:08Z</t>
         </is>
       </c>
     </row>
@@ -8471,7 +8471,7 @@
       </c>
       <c r="S98" s="4" t="inlineStr">
         <is>
-          <t>2026-09-01T22:43:23Z</t>
+          <t>2026-09-02T17:10:08Z</t>
         </is>
       </c>
     </row>
@@ -8556,7 +8556,7 @@
       </c>
       <c r="S99" s="4" t="inlineStr">
         <is>
-          <t>2026-09-01T22:43:23Z</t>
+          <t>2026-09-02T17:10:08Z</t>
         </is>
       </c>
     </row>
@@ -8641,7 +8641,7 @@
       </c>
       <c r="S100" s="4" t="inlineStr">
         <is>
-          <t>2026-09-01T22:43:23Z</t>
+          <t>2026-09-02T17:10:08Z</t>
         </is>
       </c>
     </row>
@@ -8726,7 +8726,7 @@
       </c>
       <c r="S101" s="4" t="inlineStr">
         <is>
-          <t>2026-09-01T22:43:23Z</t>
+          <t>2026-09-02T17:10:08Z</t>
         </is>
       </c>
     </row>
@@ -8811,7 +8811,7 @@
       </c>
       <c r="S102" s="4" t="inlineStr">
         <is>
-          <t>2026-09-01T22:43:23Z</t>
+          <t>2026-09-02T17:10:08Z</t>
         </is>
       </c>
     </row>
@@ -8896,7 +8896,7 @@
       </c>
       <c r="S103" s="4" t="inlineStr">
         <is>
-          <t>2026-09-01T22:43:23Z</t>
+          <t>2026-09-02T17:10:08Z</t>
         </is>
       </c>
     </row>
@@ -8981,7 +8981,7 @@
       </c>
       <c r="S104" s="4" t="inlineStr">
         <is>
-          <t>2026-09-01T22:43:23Z</t>
+          <t>2026-09-02T17:10:08Z</t>
         </is>
       </c>
     </row>
@@ -9066,7 +9066,7 @@
       </c>
       <c r="S105" s="4" t="inlineStr">
         <is>
-          <t>2026-09-01T22:43:23Z</t>
+          <t>2026-09-02T17:10:08Z</t>
         </is>
       </c>
     </row>
@@ -9151,7 +9151,7 @@
       </c>
       <c r="S106" s="4" t="inlineStr">
         <is>
-          <t>2026-09-01T22:43:23Z</t>
+          <t>2026-09-02T17:10:08Z</t>
         </is>
       </c>
     </row>
@@ -9236,7 +9236,7 @@
       </c>
       <c r="S107" s="4" t="inlineStr">
         <is>
-          <t>2026-09-01T22:43:23Z</t>
+          <t>2026-09-02T17:10:08Z</t>
         </is>
       </c>
     </row>
@@ -9321,7 +9321,7 @@
       </c>
       <c r="S108" s="4" t="inlineStr">
         <is>
-          <t>2026-09-01T22:43:23Z</t>
+          <t>2026-09-02T17:10:08Z</t>
         </is>
       </c>
     </row>
@@ -9406,7 +9406,7 @@
       </c>
       <c r="S109" s="4" t="inlineStr">
         <is>
-          <t>2026-09-01T22:43:23Z</t>
+          <t>2026-09-02T17:10:08Z</t>
         </is>
       </c>
     </row>
@@ -9491,7 +9491,7 @@
       </c>
       <c r="S110" s="4" t="inlineStr">
         <is>
-          <t>2026-09-01T22:43:23Z</t>
+          <t>2026-09-02T17:10:08Z</t>
         </is>
       </c>
     </row>
@@ -9576,7 +9576,7 @@
       </c>
       <c r="S111" s="4" t="inlineStr">
         <is>
-          <t>2026-09-01T22:43:23Z</t>
+          <t>2026-09-02T17:10:08Z</t>
         </is>
       </c>
     </row>
@@ -9661,7 +9661,7 @@
       </c>
       <c r="S112" s="4" t="inlineStr">
         <is>
-          <t>2026-09-01T22:43:23Z</t>
+          <t>2026-09-02T17:10:08Z</t>
         </is>
       </c>
     </row>
@@ -9746,7 +9746,7 @@
       </c>
       <c r="S113" s="4" t="inlineStr">
         <is>
-          <t>2026-09-01T22:43:23Z</t>
+          <t>2026-09-02T17:10:08Z</t>
         </is>
       </c>
     </row>
@@ -9831,7 +9831,7 @@
       </c>
       <c r="S114" s="4" t="inlineStr">
         <is>
-          <t>2026-09-01T22:43:23Z</t>
+          <t>2026-09-02T17:10:08Z</t>
         </is>
       </c>
     </row>
@@ -9916,7 +9916,7 @@
       </c>
       <c r="S115" s="4" t="inlineStr">
         <is>
-          <t>2026-09-01T22:43:23Z</t>
+          <t>2026-09-02T17:10:08Z</t>
         </is>
       </c>
     </row>
@@ -10001,7 +10001,7 @@
       </c>
       <c r="S116" s="4" t="inlineStr">
         <is>
-          <t>2026-09-01T22:43:23Z</t>
+          <t>2026-09-02T17:10:08Z</t>
         </is>
       </c>
     </row>
@@ -10086,7 +10086,7 @@
       </c>
       <c r="S117" s="4" t="inlineStr">
         <is>
-          <t>2026-09-01T22:43:23Z</t>
+          <t>2026-09-02T17:10:08Z</t>
         </is>
       </c>
     </row>
@@ -10171,7 +10171,7 @@
       </c>
       <c r="S118" s="4" t="inlineStr">
         <is>
-          <t>2026-09-01T22:43:23Z</t>
+          <t>2026-09-02T17:10:08Z</t>
         </is>
       </c>
     </row>
@@ -10256,7 +10256,7 @@
       </c>
       <c r="S119" s="4" t="inlineStr">
         <is>
-          <t>2026-09-01T22:43:23Z</t>
+          <t>2026-09-02T17:10:08Z</t>
         </is>
       </c>
     </row>
@@ -10341,7 +10341,7 @@
       </c>
       <c r="S120" s="4" t="inlineStr">
         <is>
-          <t>2026-09-01T22:43:23Z</t>
+          <t>2026-09-02T17:10:08Z</t>
         </is>
       </c>
     </row>
@@ -10426,7 +10426,7 @@
       </c>
       <c r="S121" s="4" t="inlineStr">
         <is>
-          <t>2026-09-01T22:43:23Z</t>
+          <t>2026-09-02T17:10:08Z</t>
         </is>
       </c>
     </row>
@@ -10511,7 +10511,7 @@
       </c>
       <c r="S122" s="4" t="inlineStr">
         <is>
-          <t>2026-09-01T22:43:23Z</t>
+          <t>2026-09-02T17:10:08Z</t>
         </is>
       </c>
     </row>
@@ -10596,7 +10596,7 @@
       </c>
       <c r="S123" s="4" t="inlineStr">
         <is>
-          <t>2026-09-01T22:43:23Z</t>
+          <t>2026-09-02T17:10:08Z</t>
         </is>
       </c>
     </row>
@@ -10681,7 +10681,7 @@
       </c>
       <c r="S124" s="4" t="inlineStr">
         <is>
-          <t>2026-09-01T22:43:23Z</t>
+          <t>2026-09-02T17:10:08Z</t>
         </is>
       </c>
     </row>
@@ -10766,7 +10766,7 @@
       </c>
       <c r="S125" s="4" t="inlineStr">
         <is>
-          <t>2026-09-01T22:43:23Z</t>
+          <t>2026-09-02T17:10:08Z</t>
         </is>
       </c>
     </row>
@@ -10851,7 +10851,7 @@
       </c>
       <c r="S126" s="4" t="inlineStr">
         <is>
-          <t>2026-09-01T22:43:23Z</t>
+          <t>2026-09-02T17:10:08Z</t>
         </is>
       </c>
     </row>
@@ -10936,7 +10936,7 @@
       </c>
       <c r="S127" s="4" t="inlineStr">
         <is>
-          <t>2026-09-01T22:43:23Z</t>
+          <t>2026-09-02T17:10:08Z</t>
         </is>
       </c>
     </row>
@@ -11021,7 +11021,7 @@
       </c>
       <c r="S128" s="4" t="inlineStr">
         <is>
-          <t>2026-09-01T22:43:23Z</t>
+          <t>2026-09-02T17:10:08Z</t>
         </is>
       </c>
     </row>
@@ -11106,7 +11106,7 @@
       </c>
       <c r="S129" s="4" t="inlineStr">
         <is>
-          <t>2026-09-01T22:43:23Z</t>
+          <t>2026-09-02T17:10:08Z</t>
         </is>
       </c>
     </row>
@@ -11191,7 +11191,7 @@
       </c>
       <c r="S130" s="4" t="inlineStr">
         <is>
-          <t>2026-09-01T22:43:23Z</t>
+          <t>2026-09-02T17:10:08Z</t>
         </is>
       </c>
     </row>
@@ -11276,7 +11276,7 @@
       </c>
       <c r="S131" s="4" t="inlineStr">
         <is>
-          <t>2026-09-01T22:43:23Z</t>
+          <t>2026-09-02T17:10:08Z</t>
         </is>
       </c>
     </row>
@@ -11361,7 +11361,7 @@
       </c>
       <c r="S132" s="4" t="inlineStr">
         <is>
-          <t>2026-09-01T22:43:23Z</t>
+          <t>2026-09-02T17:10:08Z</t>
         </is>
       </c>
     </row>
@@ -11446,7 +11446,7 @@
       </c>
       <c r="S133" s="4" t="inlineStr">
         <is>
-          <t>2026-09-01T22:43:23Z</t>
+          <t>2026-09-02T17:10:08Z</t>
         </is>
       </c>
     </row>
@@ -11531,7 +11531,7 @@
       </c>
       <c r="S134" s="4" t="inlineStr">
         <is>
-          <t>2026-09-01T22:43:23Z</t>
+          <t>2026-09-02T17:10:08Z</t>
         </is>
       </c>
     </row>
@@ -11616,7 +11616,7 @@
       </c>
       <c r="S135" s="4" t="inlineStr">
         <is>
-          <t>2026-09-01T22:43:23Z</t>
+          <t>2026-09-02T17:10:08Z</t>
         </is>
       </c>
     </row>
@@ -11701,7 +11701,7 @@
       </c>
       <c r="S136" s="4" t="inlineStr">
         <is>
-          <t>2026-09-01T22:43:23Z</t>
+          <t>2026-09-02T17:10:08Z</t>
         </is>
       </c>
     </row>
@@ -11786,7 +11786,7 @@
       </c>
       <c r="S137" s="4" t="inlineStr">
         <is>
-          <t>2026-09-01T22:43:23Z</t>
+          <t>2026-09-02T17:10:08Z</t>
         </is>
       </c>
     </row>
@@ -11871,7 +11871,7 @@
       </c>
       <c r="S138" s="4" t="inlineStr">
         <is>
-          <t>2026-09-01T22:43:23Z</t>
+          <t>2026-09-02T17:10:08Z</t>
         </is>
       </c>
     </row>
@@ -11956,7 +11956,7 @@
       </c>
       <c r="S139" s="4" t="inlineStr">
         <is>
-          <t>2026-09-01T22:43:23Z</t>
+          <t>2026-09-02T17:10:08Z</t>
         </is>
       </c>
     </row>
@@ -12041,7 +12041,7 @@
       </c>
       <c r="S140" s="4" t="inlineStr">
         <is>
-          <t>2026-09-01T22:43:23Z</t>
+          <t>2026-09-02T17:10:08Z</t>
         </is>
       </c>
     </row>
@@ -12126,7 +12126,7 @@
       </c>
       <c r="S141" s="4" t="inlineStr">
         <is>
-          <t>2026-09-01T22:43:23Z</t>
+          <t>2026-09-02T17:10:08Z</t>
         </is>
       </c>
     </row>
@@ -12258,7 +12258,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>2026-09-01T22:43:23Z</t>
+          <t>2026-09-02T17:10:08Z</t>
         </is>
       </c>
     </row>
@@ -12338,7 +12338,7 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>{"dataset_id": "bcv_pib_historico_anual", "title": "Producto interno bruto histórico anual", "table": "PIB histórico anual", "source_file": "7_1_14_anual.xls", "base": "1957/1968/1984/1997", "price_type": "Precios constantes", "measure": "Nivel", "frequency": "Anual", "period": "2017", "year": 2017, "quarter": null, "classification": "Total economía", "component": "Producto interno bruto", "value": 392393.12, "unit": "Millones de bolívares a precios constantes", "status": "", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/7_1_14_anual.xls", "fetched_at": "2026-09-01T22:43:23Z"}</t>
+          <t>{"dataset_id": "bcv_pib_historico_anual", "title": "Producto interno bruto histórico anual", "table": "PIB histórico anual", "source_file": "7_1_14_anual.xls", "base": "1957/1968/1984/1997", "price_type": "Precios constantes", "measure": "Nivel", "frequency": "Anual", "period": "2017", "year": 2017, "quarter": null, "classification": "Total economía", "component": "Producto interno bruto", "value": 392393.12, "unit": "Millones de bolívares a precios constantes", "status": "", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/7_1_14_anual.xls", "fetched_at": "2026-09-02T17:10:08Z"}</t>
         </is>
       </c>
     </row>

--- a/assets/data/bcv/excel/ove_bcv_pib_historico_anual.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_pib_historico_anual.xlsx
@@ -736,7 +736,7 @@
       </c>
       <c r="S7" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -821,7 +821,7 @@
       </c>
       <c r="S8" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -906,7 +906,7 @@
       </c>
       <c r="S9" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -991,7 +991,7 @@
       </c>
       <c r="S10" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="S11" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -1161,7 +1161,7 @@
       </c>
       <c r="S12" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -1246,7 +1246,7 @@
       </c>
       <c r="S13" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -1331,7 +1331,7 @@
       </c>
       <c r="S14" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -1416,7 +1416,7 @@
       </c>
       <c r="S15" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -1501,7 +1501,7 @@
       </c>
       <c r="S16" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -1586,7 +1586,7 @@
       </c>
       <c r="S17" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -1671,7 +1671,7 @@
       </c>
       <c r="S18" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -1756,7 +1756,7 @@
       </c>
       <c r="S19" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -1841,7 +1841,7 @@
       </c>
       <c r="S20" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -1926,7 +1926,7 @@
       </c>
       <c r="S21" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -2011,7 +2011,7 @@
       </c>
       <c r="S22" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="S23" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -2181,7 +2181,7 @@
       </c>
       <c r="S24" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -2266,7 +2266,7 @@
       </c>
       <c r="S25" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -2351,7 +2351,7 @@
       </c>
       <c r="S26" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -2436,7 +2436,7 @@
       </c>
       <c r="S27" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -2521,7 +2521,7 @@
       </c>
       <c r="S28" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -2606,7 +2606,7 @@
       </c>
       <c r="S29" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -2691,7 +2691,7 @@
       </c>
       <c r="S30" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -2776,7 +2776,7 @@
       </c>
       <c r="S31" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -2861,7 +2861,7 @@
       </c>
       <c r="S32" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -2946,7 +2946,7 @@
       </c>
       <c r="S33" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -3031,7 +3031,7 @@
       </c>
       <c r="S34" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -3116,7 +3116,7 @@
       </c>
       <c r="S35" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -3201,7 +3201,7 @@
       </c>
       <c r="S36" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -3286,7 +3286,7 @@
       </c>
       <c r="S37" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -3371,7 +3371,7 @@
       </c>
       <c r="S38" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -3456,7 +3456,7 @@
       </c>
       <c r="S39" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -3541,7 +3541,7 @@
       </c>
       <c r="S40" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -3626,7 +3626,7 @@
       </c>
       <c r="S41" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -3711,7 +3711,7 @@
       </c>
       <c r="S42" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -3796,7 +3796,7 @@
       </c>
       <c r="S43" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -3881,7 +3881,7 @@
       </c>
       <c r="S44" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -3966,7 +3966,7 @@
       </c>
       <c r="S45" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -4051,7 +4051,7 @@
       </c>
       <c r="S46" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -4136,7 +4136,7 @@
       </c>
       <c r="S47" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -4221,7 +4221,7 @@
       </c>
       <c r="S48" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -4306,7 +4306,7 @@
       </c>
       <c r="S49" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -4391,7 +4391,7 @@
       </c>
       <c r="S50" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -4476,7 +4476,7 @@
       </c>
       <c r="S51" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -4561,7 +4561,7 @@
       </c>
       <c r="S52" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -4646,7 +4646,7 @@
       </c>
       <c r="S53" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -4731,7 +4731,7 @@
       </c>
       <c r="S54" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -4816,7 +4816,7 @@
       </c>
       <c r="S55" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -4901,7 +4901,7 @@
       </c>
       <c r="S56" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -4986,7 +4986,7 @@
       </c>
       <c r="S57" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -5071,7 +5071,7 @@
       </c>
       <c r="S58" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -5156,7 +5156,7 @@
       </c>
       <c r="S59" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -5241,7 +5241,7 @@
       </c>
       <c r="S60" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -5326,7 +5326,7 @@
       </c>
       <c r="S61" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -5411,7 +5411,7 @@
       </c>
       <c r="S62" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -5496,7 +5496,7 @@
       </c>
       <c r="S63" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -5581,7 +5581,7 @@
       </c>
       <c r="S64" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -5666,7 +5666,7 @@
       </c>
       <c r="S65" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -5751,7 +5751,7 @@
       </c>
       <c r="S66" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -5836,7 +5836,7 @@
       </c>
       <c r="S67" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -5921,7 +5921,7 @@
       </c>
       <c r="S68" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -6006,7 +6006,7 @@
       </c>
       <c r="S69" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -6091,7 +6091,7 @@
       </c>
       <c r="S70" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -6176,7 +6176,7 @@
       </c>
       <c r="S71" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -6261,7 +6261,7 @@
       </c>
       <c r="S72" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -6346,7 +6346,7 @@
       </c>
       <c r="S73" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -6431,7 +6431,7 @@
       </c>
       <c r="S74" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -6516,7 +6516,7 @@
       </c>
       <c r="S75" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -6601,7 +6601,7 @@
       </c>
       <c r="S76" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -6686,7 +6686,7 @@
       </c>
       <c r="S77" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -6771,7 +6771,7 @@
       </c>
       <c r="S78" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -6856,7 +6856,7 @@
       </c>
       <c r="S79" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -6941,7 +6941,7 @@
       </c>
       <c r="S80" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -7026,7 +7026,7 @@
       </c>
       <c r="S81" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -7111,7 +7111,7 @@
       </c>
       <c r="S82" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -7196,7 +7196,7 @@
       </c>
       <c r="S83" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -7281,7 +7281,7 @@
       </c>
       <c r="S84" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -7366,7 +7366,7 @@
       </c>
       <c r="S85" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -7451,7 +7451,7 @@
       </c>
       <c r="S86" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -7536,7 +7536,7 @@
       </c>
       <c r="S87" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -7621,7 +7621,7 @@
       </c>
       <c r="S88" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -7706,7 +7706,7 @@
       </c>
       <c r="S89" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -7791,7 +7791,7 @@
       </c>
       <c r="S90" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -7876,7 +7876,7 @@
       </c>
       <c r="S91" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -7961,7 +7961,7 @@
       </c>
       <c r="S92" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -8046,7 +8046,7 @@
       </c>
       <c r="S93" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -8131,7 +8131,7 @@
       </c>
       <c r="S94" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -8216,7 +8216,7 @@
       </c>
       <c r="S95" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -8301,7 +8301,7 @@
       </c>
       <c r="S96" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -8386,7 +8386,7 @@
       </c>
       <c r="S97" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -8471,7 +8471,7 @@
       </c>
       <c r="S98" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -8556,7 +8556,7 @@
       </c>
       <c r="S99" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -8641,7 +8641,7 @@
       </c>
       <c r="S100" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -8726,7 +8726,7 @@
       </c>
       <c r="S101" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -8811,7 +8811,7 @@
       </c>
       <c r="S102" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -8896,7 +8896,7 @@
       </c>
       <c r="S103" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -8981,7 +8981,7 @@
       </c>
       <c r="S104" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -9066,7 +9066,7 @@
       </c>
       <c r="S105" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -9151,7 +9151,7 @@
       </c>
       <c r="S106" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -9236,7 +9236,7 @@
       </c>
       <c r="S107" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -9321,7 +9321,7 @@
       </c>
       <c r="S108" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -9406,7 +9406,7 @@
       </c>
       <c r="S109" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -9491,7 +9491,7 @@
       </c>
       <c r="S110" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -9576,7 +9576,7 @@
       </c>
       <c r="S111" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -9661,7 +9661,7 @@
       </c>
       <c r="S112" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -9746,7 +9746,7 @@
       </c>
       <c r="S113" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -9831,7 +9831,7 @@
       </c>
       <c r="S114" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -9916,7 +9916,7 @@
       </c>
       <c r="S115" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -10001,7 +10001,7 @@
       </c>
       <c r="S116" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -10086,7 +10086,7 @@
       </c>
       <c r="S117" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -10171,7 +10171,7 @@
       </c>
       <c r="S118" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -10256,7 +10256,7 @@
       </c>
       <c r="S119" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -10341,7 +10341,7 @@
       </c>
       <c r="S120" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -10426,7 +10426,7 @@
       </c>
       <c r="S121" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -10511,7 +10511,7 @@
       </c>
       <c r="S122" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -10596,7 +10596,7 @@
       </c>
       <c r="S123" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -10681,7 +10681,7 @@
       </c>
       <c r="S124" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -10766,7 +10766,7 @@
       </c>
       <c r="S125" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -10851,7 +10851,7 @@
       </c>
       <c r="S126" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -10936,7 +10936,7 @@
       </c>
       <c r="S127" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -11021,7 +11021,7 @@
       </c>
       <c r="S128" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -11106,7 +11106,7 @@
       </c>
       <c r="S129" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -11191,7 +11191,7 @@
       </c>
       <c r="S130" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -11276,7 +11276,7 @@
       </c>
       <c r="S131" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -11361,7 +11361,7 @@
       </c>
       <c r="S132" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -11446,7 +11446,7 @@
       </c>
       <c r="S133" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -11531,7 +11531,7 @@
       </c>
       <c r="S134" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -11616,7 +11616,7 @@
       </c>
       <c r="S135" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -11701,7 +11701,7 @@
       </c>
       <c r="S136" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -11786,7 +11786,7 @@
       </c>
       <c r="S137" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -11871,7 +11871,7 @@
       </c>
       <c r="S138" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -11956,7 +11956,7 @@
       </c>
       <c r="S139" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -12041,7 +12041,7 @@
       </c>
       <c r="S140" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -12126,7 +12126,7 @@
       </c>
       <c r="S141" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -12258,7 +12258,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -12338,7 +12338,7 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>{"dataset_id": "bcv_pib_historico_anual", "title": "Producto interno bruto histórico anual", "table": "PIB histórico anual", "source_file": "7_1_14_anual.xls", "base": "1957/1968/1984/1997", "price_type": "Precios constantes", "measure": "Nivel", "frequency": "Anual", "period": "2017", "year": 2017, "quarter": null, "classification": "Total economía", "component": "Producto interno bruto", "value": 392393.12, "unit": "Millones de bolívares a precios constantes", "status": "", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/7_1_14_anual.xls", "fetched_at": "2026-09-02T17:10:08Z"}</t>
+          <t>{"dataset_id": "bcv_pib_historico_anual", "title": "Producto interno bruto histórico anual", "table": "PIB histórico anual", "source_file": "7_1_14_anual.xls", "base": "1957/1968/1984/1997", "price_type": "Precios constantes", "measure": "Nivel", "frequency": "Anual", "period": "2017", "year": 2017, "quarter": null, "classification": "Total economía", "component": "Producto interno bruto", "value": 392393.12, "unit": "Millones de bolívares a precios constantes", "status": "", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/7_1_14_anual.xls", "fetched_at": "2026-09-02T22:45:38Z"}</t>
         </is>
       </c>
     </row>

--- a/assets/data/bcv/excel/ove_bcv_pib_historico_anual.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_pib_historico_anual.xlsx
@@ -736,7 +736,7 @@
       </c>
       <c r="S7" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T22:45:38Z</t>
+          <t>2026-09-03T22:43:49Z</t>
         </is>
       </c>
     </row>
@@ -821,7 +821,7 @@
       </c>
       <c r="S8" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T22:45:38Z</t>
+          <t>2026-09-03T22:43:49Z</t>
         </is>
       </c>
     </row>
@@ -906,7 +906,7 @@
       </c>
       <c r="S9" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T22:45:38Z</t>
+          <t>2026-09-03T22:43:49Z</t>
         </is>
       </c>
     </row>
@@ -991,7 +991,7 @@
       </c>
       <c r="S10" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T22:45:38Z</t>
+          <t>2026-09-03T22:43:49Z</t>
         </is>
       </c>
     </row>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="S11" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T22:45:38Z</t>
+          <t>2026-09-03T22:43:49Z</t>
         </is>
       </c>
     </row>
@@ -1161,7 +1161,7 @@
       </c>
       <c r="S12" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T22:45:38Z</t>
+          <t>2026-09-03T22:43:49Z</t>
         </is>
       </c>
     </row>
@@ -1246,7 +1246,7 @@
       </c>
       <c r="S13" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T22:45:38Z</t>
+          <t>2026-09-03T22:43:49Z</t>
         </is>
       </c>
     </row>
@@ -1331,7 +1331,7 @@
       </c>
       <c r="S14" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T22:45:38Z</t>
+          <t>2026-09-03T22:43:49Z</t>
         </is>
       </c>
     </row>
@@ -1416,7 +1416,7 @@
       </c>
       <c r="S15" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T22:45:38Z</t>
+          <t>2026-09-03T22:43:49Z</t>
         </is>
       </c>
     </row>
@@ -1501,7 +1501,7 @@
       </c>
       <c r="S16" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T22:45:38Z</t>
+          <t>2026-09-03T22:43:49Z</t>
         </is>
       </c>
     </row>
@@ -1586,7 +1586,7 @@
       </c>
       <c r="S17" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T22:45:38Z</t>
+          <t>2026-09-03T22:43:49Z</t>
         </is>
       </c>
     </row>
@@ -1671,7 +1671,7 @@
       </c>
       <c r="S18" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T22:45:38Z</t>
+          <t>2026-09-03T22:43:49Z</t>
         </is>
       </c>
     </row>
@@ -1756,7 +1756,7 @@
       </c>
       <c r="S19" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T22:45:38Z</t>
+          <t>2026-09-03T22:43:49Z</t>
         </is>
       </c>
     </row>
@@ -1841,7 +1841,7 @@
       </c>
       <c r="S20" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T22:45:38Z</t>
+          <t>2026-09-03T22:43:49Z</t>
         </is>
       </c>
     </row>
@@ -1926,7 +1926,7 @@
       </c>
       <c r="S21" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T22:45:38Z</t>
+          <t>2026-09-03T22:43:49Z</t>
         </is>
       </c>
     </row>
@@ -2011,7 +2011,7 @@
       </c>
       <c r="S22" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T22:45:38Z</t>
+          <t>2026-09-03T22:43:49Z</t>
         </is>
       </c>
     </row>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="S23" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T22:45:38Z</t>
+          <t>2026-09-03T22:43:49Z</t>
         </is>
       </c>
     </row>
@@ -2181,7 +2181,7 @@
       </c>
       <c r="S24" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T22:45:38Z</t>
+          <t>2026-09-03T22:43:49Z</t>
         </is>
       </c>
     </row>
@@ -2266,7 +2266,7 @@
       </c>
       <c r="S25" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T22:45:38Z</t>
+          <t>2026-09-03T22:43:49Z</t>
         </is>
       </c>
     </row>
@@ -2351,7 +2351,7 @@
       </c>
       <c r="S26" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T22:45:38Z</t>
+          <t>2026-09-03T22:43:49Z</t>
         </is>
       </c>
     </row>
@@ -2436,7 +2436,7 @@
       </c>
       <c r="S27" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T22:45:38Z</t>
+          <t>2026-09-03T22:43:49Z</t>
         </is>
       </c>
     </row>
@@ -2521,7 +2521,7 @@
       </c>
       <c r="S28" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T22:45:38Z</t>
+          <t>2026-09-03T22:43:49Z</t>
         </is>
       </c>
     </row>
@@ -2606,7 +2606,7 @@
       </c>
       <c r="S29" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T22:45:38Z</t>
+          <t>2026-09-03T22:43:49Z</t>
         </is>
       </c>
     </row>
@@ -2691,7 +2691,7 @@
       </c>
       <c r="S30" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T22:45:38Z</t>
+          <t>2026-09-03T22:43:49Z</t>
         </is>
       </c>
     </row>
@@ -2776,7 +2776,7 @@
       </c>
       <c r="S31" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T22:45:38Z</t>
+          <t>2026-09-03T22:43:49Z</t>
         </is>
       </c>
     </row>
@@ -2861,7 +2861,7 @@
       </c>
       <c r="S32" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T22:45:38Z</t>
+          <t>2026-09-03T22:43:49Z</t>
         </is>
       </c>
     </row>
@@ -2946,7 +2946,7 @@
       </c>
       <c r="S33" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T22:45:38Z</t>
+          <t>2026-09-03T22:43:49Z</t>
         </is>
       </c>
     </row>
@@ -3031,7 +3031,7 @@
       </c>
       <c r="S34" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T22:45:38Z</t>
+          <t>2026-09-03T22:43:49Z</t>
         </is>
       </c>
     </row>
@@ -3116,7 +3116,7 @@
       </c>
       <c r="S35" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T22:45:38Z</t>
+          <t>2026-09-03T22:43:49Z</t>
         </is>
       </c>
     </row>
@@ -3201,7 +3201,7 @@
       </c>
       <c r="S36" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T22:45:38Z</t>
+          <t>2026-09-03T22:43:49Z</t>
         </is>
       </c>
     </row>
@@ -3286,7 +3286,7 @@
       </c>
       <c r="S37" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T22:45:38Z</t>
+          <t>2026-09-03T22:43:49Z</t>
         </is>
       </c>
     </row>
@@ -3371,7 +3371,7 @@
       </c>
       <c r="S38" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T22:45:38Z</t>
+          <t>2026-09-03T22:43:49Z</t>
         </is>
       </c>
     </row>
@@ -3456,7 +3456,7 @@
       </c>
       <c r="S39" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T22:45:38Z</t>
+          <t>2026-09-03T22:43:49Z</t>
         </is>
       </c>
     </row>
@@ -3541,7 +3541,7 @@
       </c>
       <c r="S40" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T22:45:38Z</t>
+          <t>2026-09-03T22:43:49Z</t>
         </is>
       </c>
     </row>
@@ -3626,7 +3626,7 @@
       </c>
       <c r="S41" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T22:45:38Z</t>
+          <t>2026-09-03T22:43:49Z</t>
         </is>
       </c>
     </row>
@@ -3711,7 +3711,7 @@
       </c>
       <c r="S42" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T22:45:38Z</t>
+          <t>2026-09-03T22:43:49Z</t>
         </is>
       </c>
     </row>
@@ -3796,7 +3796,7 @@
       </c>
       <c r="S43" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T22:45:38Z</t>
+          <t>2026-09-03T22:43:49Z</t>
         </is>
       </c>
     </row>
@@ -3881,7 +3881,7 @@
       </c>
       <c r="S44" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T22:45:38Z</t>
+          <t>2026-09-03T22:43:49Z</t>
         </is>
       </c>
     </row>
@@ -3966,7 +3966,7 @@
       </c>
       <c r="S45" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T22:45:38Z</t>
+          <t>2026-09-03T22:43:49Z</t>
         </is>
       </c>
     </row>
@@ -4051,7 +4051,7 @@
       </c>
       <c r="S46" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T22:45:38Z</t>
+          <t>2026-09-03T22:43:49Z</t>
         </is>
       </c>
     </row>
@@ -4136,7 +4136,7 @@
       </c>
       <c r="S47" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T22:45:38Z</t>
+          <t>2026-09-03T22:43:49Z</t>
         </is>
       </c>
     </row>
@@ -4221,7 +4221,7 @@
       </c>
       <c r="S48" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T22:45:38Z</t>
+          <t>2026-09-03T22:43:49Z</t>
         </is>
       </c>
     </row>
@@ -4306,7 +4306,7 @@
       </c>
       <c r="S49" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T22:45:38Z</t>
+          <t>2026-09-03T22:43:49Z</t>
         </is>
       </c>
     </row>
@@ -4391,7 +4391,7 @@
       </c>
       <c r="S50" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T22:45:38Z</t>
+          <t>2026-09-03T22:43:49Z</t>
         </is>
       </c>
     </row>
@@ -4476,7 +4476,7 @@
       </c>
       <c r="S51" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T22:45:38Z</t>
+          <t>2026-09-03T22:43:49Z</t>
         </is>
       </c>
     </row>
@@ -4561,7 +4561,7 @@
       </c>
       <c r="S52" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T22:45:38Z</t>
+          <t>2026-09-03T22:43:49Z</t>
         </is>
       </c>
     </row>
@@ -4646,7 +4646,7 @@
       </c>
       <c r="S53" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T22:45:38Z</t>
+          <t>2026-09-03T22:43:49Z</t>
         </is>
       </c>
     </row>
@@ -4731,7 +4731,7 @@
       </c>
       <c r="S54" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T22:45:38Z</t>
+          <t>2026-09-03T22:43:49Z</t>
         </is>
       </c>
     </row>
@@ -4816,7 +4816,7 @@
       </c>
       <c r="S55" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T22:45:38Z</t>
+          <t>2026-09-03T22:43:49Z</t>
         </is>
       </c>
     </row>
@@ -4901,7 +4901,7 @@
       </c>
       <c r="S56" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T22:45:38Z</t>
+          <t>2026-09-03T22:43:49Z</t>
         </is>
       </c>
     </row>
@@ -4986,7 +4986,7 @@
       </c>
       <c r="S57" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T22:45:38Z</t>
+          <t>2026-09-03T22:43:49Z</t>
         </is>
       </c>
     </row>
@@ -5071,7 +5071,7 @@
       </c>
       <c r="S58" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T22:45:38Z</t>
+          <t>2026-09-03T22:43:49Z</t>
         </is>
       </c>
     </row>
@@ -5156,7 +5156,7 @@
       </c>
       <c r="S59" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T22:45:38Z</t>
+          <t>2026-09-03T22:43:49Z</t>
         </is>
       </c>
     </row>
@@ -5241,7 +5241,7 @@
       </c>
       <c r="S60" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T22:45:38Z</t>
+          <t>2026-09-03T22:43:49Z</t>
         </is>
       </c>
     </row>
@@ -5326,7 +5326,7 @@
       </c>
       <c r="S61" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T22:45:38Z</t>
+          <t>2026-09-03T22:43:49Z</t>
         </is>
       </c>
     </row>
@@ -5411,7 +5411,7 @@
       </c>
       <c r="S62" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T22:45:38Z</t>
+          <t>2026-09-03T22:43:49Z</t>
         </is>
       </c>
     </row>
@@ -5496,7 +5496,7 @@
       </c>
       <c r="S63" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T22:45:38Z</t>
+          <t>2026-09-03T22:43:49Z</t>
         </is>
       </c>
     </row>
@@ -5581,7 +5581,7 @@
       </c>
       <c r="S64" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T22:45:38Z</t>
+          <t>2026-09-03T22:43:49Z</t>
         </is>
       </c>
     </row>
@@ -5666,7 +5666,7 @@
       </c>
       <c r="S65" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T22:45:38Z</t>
+          <t>2026-09-03T22:43:49Z</t>
         </is>
       </c>
     </row>
@@ -5751,7 +5751,7 @@
       </c>
       <c r="S66" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T22:45:38Z</t>
+          <t>2026-09-03T22:43:49Z</t>
         </is>
       </c>
     </row>
@@ -5836,7 +5836,7 @@
       </c>
       <c r="S67" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T22:45:38Z</t>
+          <t>2026-09-03T22:43:49Z</t>
         </is>
       </c>
     </row>
@@ -5921,7 +5921,7 @@
       </c>
       <c r="S68" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T22:45:38Z</t>
+          <t>2026-09-03T22:43:49Z</t>
         </is>
       </c>
     </row>
@@ -6006,7 +6006,7 @@
       </c>
       <c r="S69" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T22:45:38Z</t>
+          <t>2026-09-03T22:43:49Z</t>
         </is>
       </c>
     </row>
@@ -6091,7 +6091,7 @@
       </c>
       <c r="S70" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T22:45:38Z</t>
+          <t>2026-09-03T22:43:49Z</t>
         </is>
       </c>
     </row>
@@ -6176,7 +6176,7 @@
       </c>
       <c r="S71" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T22:45:38Z</t>
+          <t>2026-09-03T22:43:49Z</t>
         </is>
       </c>
     </row>
@@ -6261,7 +6261,7 @@
       </c>
       <c r="S72" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T22:45:38Z</t>
+          <t>2026-09-03T22:43:49Z</t>
         </is>
       </c>
     </row>
@@ -6346,7 +6346,7 @@
       </c>
       <c r="S73" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T22:45:38Z</t>
+          <t>2026-09-03T22:43:49Z</t>
         </is>
       </c>
     </row>
@@ -6431,7 +6431,7 @@
       </c>
       <c r="S74" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T22:45:38Z</t>
+          <t>2026-09-03T22:43:49Z</t>
         </is>
       </c>
     </row>
@@ -6516,7 +6516,7 @@
       </c>
       <c r="S75" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T22:45:38Z</t>
+          <t>2026-09-03T22:43:49Z</t>
         </is>
       </c>
     </row>
@@ -6601,7 +6601,7 @@
       </c>
       <c r="S76" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T22:45:38Z</t>
+          <t>2026-09-03T22:43:49Z</t>
         </is>
       </c>
     </row>
@@ -6686,7 +6686,7 @@
       </c>
       <c r="S77" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T22:45:38Z</t>
+          <t>2026-09-03T22:43:49Z</t>
         </is>
       </c>
     </row>
@@ -6771,7 +6771,7 @@
       </c>
       <c r="S78" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T22:45:38Z</t>
+          <t>2026-09-03T22:43:49Z</t>
         </is>
       </c>
     </row>
@@ -6856,7 +6856,7 @@
       </c>
       <c r="S79" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T22:45:38Z</t>
+          <t>2026-09-03T22:43:49Z</t>
         </is>
       </c>
     </row>
@@ -6941,7 +6941,7 @@
       </c>
       <c r="S80" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T22:45:38Z</t>
+          <t>2026-09-03T22:43:49Z</t>
         </is>
       </c>
     </row>
@@ -7026,7 +7026,7 @@
       </c>
       <c r="S81" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T22:45:38Z</t>
+          <t>2026-09-03T22:43:49Z</t>
         </is>
       </c>
     </row>
@@ -7111,7 +7111,7 @@
       </c>
       <c r="S82" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T22:45:38Z</t>
+          <t>2026-09-03T22:43:49Z</t>
         </is>
       </c>
     </row>
@@ -7196,7 +7196,7 @@
       </c>
       <c r="S83" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T22:45:38Z</t>
+          <t>2026-09-03T22:43:49Z</t>
         </is>
       </c>
     </row>
@@ -7281,7 +7281,7 @@
       </c>
       <c r="S84" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T22:45:38Z</t>
+          <t>2026-09-03T22:43:49Z</t>
         </is>
       </c>
     </row>
@@ -7366,7 +7366,7 @@
       </c>
       <c r="S85" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T22:45:38Z</t>
+          <t>2026-09-03T22:43:49Z</t>
         </is>
       </c>
     </row>
@@ -7451,7 +7451,7 @@
       </c>
       <c r="S86" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T22:45:38Z</t>
+          <t>2026-09-03T22:43:49Z</t>
         </is>
       </c>
     </row>
@@ -7536,7 +7536,7 @@
       </c>
       <c r="S87" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T22:45:38Z</t>
+          <t>2026-09-03T22:43:49Z</t>
         </is>
       </c>
     </row>
@@ -7621,7 +7621,7 @@
       </c>
       <c r="S88" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T22:45:38Z</t>
+          <t>2026-09-03T22:43:49Z</t>
         </is>
       </c>
     </row>
@@ -7706,7 +7706,7 @@
       </c>
       <c r="S89" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T22:45:38Z</t>
+          <t>2026-09-03T22:43:49Z</t>
         </is>
       </c>
     </row>
@@ -7791,7 +7791,7 @@
       </c>
       <c r="S90" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T22:45:38Z</t>
+          <t>2026-09-03T22:43:49Z</t>
         </is>
       </c>
     </row>
@@ -7876,7 +7876,7 @@
       </c>
       <c r="S91" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T22:45:38Z</t>
+          <t>2026-09-03T22:43:49Z</t>
         </is>
       </c>
     </row>
@@ -7961,7 +7961,7 @@
       </c>
       <c r="S92" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T22:45:38Z</t>
+          <t>2026-09-03T22:43:49Z</t>
         </is>
       </c>
     </row>
@@ -8046,7 +8046,7 @@
       </c>
       <c r="S93" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T22:45:38Z</t>
+          <t>2026-09-03T22:43:49Z</t>
         </is>
       </c>
     </row>
@@ -8131,7 +8131,7 @@
       </c>
       <c r="S94" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T22:45:38Z</t>
+          <t>2026-09-03T22:43:49Z</t>
         </is>
       </c>
     </row>
@@ -8216,7 +8216,7 @@
       </c>
       <c r="S95" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T22:45:38Z</t>
+          <t>2026-09-03T22:43:49Z</t>
         </is>
       </c>
     </row>
@@ -8301,7 +8301,7 @@
       </c>
       <c r="S96" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T22:45:38Z</t>
+          <t>2026-09-03T22:43:49Z</t>
         </is>
       </c>
     </row>
@@ -8386,7 +8386,7 @@
       </c>
       <c r="S97" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T22:45:38Z</t>
+          <t>2026-09-03T22:43:49Z</t>
         </is>
       </c>
     </row>
@@ -8471,7 +8471,7 @@
       </c>
       <c r="S98" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T22:45:38Z</t>
+          <t>2026-09-03T22:43:49Z</t>
         </is>
       </c>
     </row>
@@ -8556,7 +8556,7 @@
       </c>
       <c r="S99" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T22:45:38Z</t>
+          <t>2026-09-03T22:43:49Z</t>
         </is>
       </c>
     </row>
@@ -8641,7 +8641,7 @@
       </c>
       <c r="S100" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T22:45:38Z</t>
+          <t>2026-09-03T22:43:49Z</t>
         </is>
       </c>
     </row>
@@ -8726,7 +8726,7 @@
       </c>
       <c r="S101" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T22:45:38Z</t>
+          <t>2026-09-03T22:43:49Z</t>
         </is>
       </c>
     </row>
@@ -8811,7 +8811,7 @@
       </c>
       <c r="S102" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T22:45:38Z</t>
+          <t>2026-09-03T22:43:49Z</t>
         </is>
       </c>
     </row>
@@ -8896,7 +8896,7 @@
       </c>
       <c r="S103" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T22:45:38Z</t>
+          <t>2026-09-03T22:43:49Z</t>
         </is>
       </c>
     </row>
@@ -8981,7 +8981,7 @@
       </c>
       <c r="S104" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T22:45:38Z</t>
+          <t>2026-09-03T22:43:49Z</t>
         </is>
       </c>
     </row>
@@ -9066,7 +9066,7 @@
       </c>
       <c r="S105" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T22:45:38Z</t>
+          <t>2026-09-03T22:43:49Z</t>
         </is>
       </c>
     </row>
@@ -9151,7 +9151,7 @@
       </c>
       <c r="S106" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T22:45:38Z</t>
+          <t>2026-09-03T22:43:49Z</t>
         </is>
       </c>
     </row>
@@ -9236,7 +9236,7 @@
       </c>
       <c r="S107" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T22:45:38Z</t>
+          <t>2026-09-03T22:43:49Z</t>
         </is>
       </c>
     </row>
@@ -9321,7 +9321,7 @@
       </c>
       <c r="S108" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T22:45:38Z</t>
+          <t>2026-09-03T22:43:49Z</t>
         </is>
       </c>
     </row>
@@ -9406,7 +9406,7 @@
       </c>
       <c r="S109" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T22:45:38Z</t>
+          <t>2026-09-03T22:43:49Z</t>
         </is>
       </c>
     </row>
@@ -9491,7 +9491,7 @@
       </c>
       <c r="S110" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T22:45:38Z</t>
+          <t>2026-09-03T22:43:49Z</t>
         </is>
       </c>
     </row>
@@ -9576,7 +9576,7 @@
       </c>
       <c r="S111" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T22:45:38Z</t>
+          <t>2026-09-03T22:43:49Z</t>
         </is>
       </c>
     </row>
@@ -9661,7 +9661,7 @@
       </c>
       <c r="S112" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T22:45:38Z</t>
+          <t>2026-09-03T22:43:49Z</t>
         </is>
       </c>
     </row>
@@ -9746,7 +9746,7 @@
       </c>
       <c r="S113" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T22:45:38Z</t>
+          <t>2026-09-03T22:43:49Z</t>
         </is>
       </c>
     </row>
@@ -9831,7 +9831,7 @@
       </c>
       <c r="S114" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T22:45:38Z</t>
+          <t>2026-09-03T22:43:49Z</t>
         </is>
       </c>
     </row>
@@ -9916,7 +9916,7 @@
       </c>
       <c r="S115" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T22:45:38Z</t>
+          <t>2026-09-03T22:43:49Z</t>
         </is>
       </c>
     </row>
@@ -10001,7 +10001,7 @@
       </c>
       <c r="S116" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T22:45:38Z</t>
+          <t>2026-09-03T22:43:49Z</t>
         </is>
       </c>
     </row>
@@ -10086,7 +10086,7 @@
       </c>
       <c r="S117" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T22:45:38Z</t>
+          <t>2026-09-03T22:43:49Z</t>
         </is>
       </c>
     </row>
@@ -10171,7 +10171,7 @@
       </c>
       <c r="S118" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T22:45:38Z</t>
+          <t>2026-09-03T22:43:49Z</t>
         </is>
       </c>
     </row>
@@ -10256,7 +10256,7 @@
       </c>
       <c r="S119" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T22:45:38Z</t>
+          <t>2026-09-03T22:43:49Z</t>
         </is>
       </c>
     </row>
@@ -10341,7 +10341,7 @@
       </c>
       <c r="S120" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T22:45:38Z</t>
+          <t>2026-09-03T22:43:49Z</t>
         </is>
       </c>
     </row>
@@ -10426,7 +10426,7 @@
       </c>
       <c r="S121" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T22:45:38Z</t>
+          <t>2026-09-03T22:43:49Z</t>
         </is>
       </c>
     </row>
@@ -10511,7 +10511,7 @@
       </c>
       <c r="S122" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T22:45:38Z</t>
+          <t>2026-09-03T22:43:49Z</t>
         </is>
       </c>
     </row>
@@ -10596,7 +10596,7 @@
       </c>
       <c r="S123" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T22:45:38Z</t>
+          <t>2026-09-03T22:43:49Z</t>
         </is>
       </c>
     </row>
@@ -10681,7 +10681,7 @@
       </c>
       <c r="S124" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T22:45:38Z</t>
+          <t>2026-09-03T22:43:49Z</t>
         </is>
       </c>
     </row>
@@ -10766,7 +10766,7 @@
       </c>
       <c r="S125" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T22:45:38Z</t>
+          <t>2026-09-03T22:43:49Z</t>
         </is>
       </c>
     </row>
@@ -10851,7 +10851,7 @@
       </c>
       <c r="S126" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T22:45:38Z</t>
+          <t>2026-09-03T22:43:49Z</t>
         </is>
       </c>
     </row>
@@ -10936,7 +10936,7 @@
       </c>
       <c r="S127" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T22:45:38Z</t>
+          <t>2026-09-03T22:43:49Z</t>
         </is>
       </c>
     </row>
@@ -11021,7 +11021,7 @@
       </c>
       <c r="S128" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T22:45:38Z</t>
+          <t>2026-09-03T22:43:49Z</t>
         </is>
       </c>
     </row>
@@ -11106,7 +11106,7 @@
       </c>
       <c r="S129" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T22:45:38Z</t>
+          <t>2026-09-03T22:43:49Z</t>
         </is>
       </c>
     </row>
@@ -11191,7 +11191,7 @@
       </c>
       <c r="S130" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T22:45:38Z</t>
+          <t>2026-09-03T22:43:49Z</t>
         </is>
       </c>
     </row>
@@ -11276,7 +11276,7 @@
       </c>
       <c r="S131" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T22:45:38Z</t>
+          <t>2026-09-03T22:43:49Z</t>
         </is>
       </c>
     </row>
@@ -11361,7 +11361,7 @@
       </c>
       <c r="S132" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T22:45:38Z</t>
+          <t>2026-09-03T22:43:49Z</t>
         </is>
       </c>
     </row>
@@ -11446,7 +11446,7 @@
       </c>
       <c r="S133" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T22:45:38Z</t>
+          <t>2026-09-03T22:43:49Z</t>
         </is>
       </c>
     </row>
@@ -11531,7 +11531,7 @@
       </c>
       <c r="S134" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T22:45:38Z</t>
+          <t>2026-09-03T22:43:49Z</t>
         </is>
       </c>
     </row>
@@ -11616,7 +11616,7 @@
       </c>
       <c r="S135" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T22:45:38Z</t>
+          <t>2026-09-03T22:43:49Z</t>
         </is>
       </c>
     </row>
@@ -11701,7 +11701,7 @@
       </c>
       <c r="S136" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T22:45:38Z</t>
+          <t>2026-09-03T22:43:49Z</t>
         </is>
       </c>
     </row>
@@ -11786,7 +11786,7 @@
       </c>
       <c r="S137" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T22:45:38Z</t>
+          <t>2026-09-03T22:43:49Z</t>
         </is>
       </c>
     </row>
@@ -11871,7 +11871,7 @@
       </c>
       <c r="S138" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T22:45:38Z</t>
+          <t>2026-09-03T22:43:49Z</t>
         </is>
       </c>
     </row>
@@ -11956,7 +11956,7 @@
       </c>
       <c r="S139" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T22:45:38Z</t>
+          <t>2026-09-03T22:43:49Z</t>
         </is>
       </c>
     </row>
@@ -12041,7 +12041,7 @@
       </c>
       <c r="S140" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T22:45:38Z</t>
+          <t>2026-09-03T22:43:49Z</t>
         </is>
       </c>
     </row>
@@ -12126,7 +12126,7 @@
       </c>
       <c r="S141" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T22:45:38Z</t>
+          <t>2026-09-03T22:43:49Z</t>
         </is>
       </c>
     </row>
@@ -12258,7 +12258,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T22:45:38Z</t>
+          <t>2026-09-03T22:43:49Z</t>
         </is>
       </c>
     </row>
@@ -12338,7 +12338,7 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>{"dataset_id": "bcv_pib_historico_anual", "title": "Producto interno bruto histórico anual", "table": "PIB histórico anual", "source_file": "7_1_14_anual.xls", "base": "1957/1968/1984/1997", "price_type": "Precios constantes", "measure": "Nivel", "frequency": "Anual", "period": "2017", "year": 2017, "quarter": null, "classification": "Total economía", "component": "Producto interno bruto", "value": 392393.12, "unit": "Millones de bolívares a precios constantes", "status": "", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/7_1_14_anual.xls", "fetched_at": "2026-09-02T22:45:38Z"}</t>
+          <t>{"dataset_id": "bcv_pib_historico_anual", "title": "Producto interno bruto histórico anual", "table": "PIB histórico anual", "source_file": "7_1_14_anual.xls", "base": "1957/1968/1984/1997", "price_type": "Precios constantes", "measure": "Nivel", "frequency": "Anual", "period": "2017", "year": 2017, "quarter": null, "classification": "Total economía", "component": "Producto interno bruto", "value": 392393.12, "unit": "Millones de bolívares a precios constantes", "status": "", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/7_1_14_anual.xls", "fetched_at": "2026-09-03T22:43:49Z"}</t>
         </is>
       </c>
     </row>

--- a/assets/data/bcv/excel/ove_bcv_pib_historico_anual.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_pib_historico_anual.xlsx
@@ -736,7 +736,7 @@
       </c>
       <c r="S7" s="4" t="inlineStr">
         <is>
-          <t>2026-09-03T22:43:49Z</t>
+          <t>2026-09-04T22:26:51Z</t>
         </is>
       </c>
     </row>
@@ -821,7 +821,7 @@
       </c>
       <c r="S8" s="4" t="inlineStr">
         <is>
-          <t>2026-09-03T22:43:49Z</t>
+          <t>2026-09-04T22:26:51Z</t>
         </is>
       </c>
     </row>
@@ -906,7 +906,7 @@
       </c>
       <c r="S9" s="4" t="inlineStr">
         <is>
-          <t>2026-09-03T22:43:49Z</t>
+          <t>2026-09-04T22:26:51Z</t>
         </is>
       </c>
     </row>
@@ -991,7 +991,7 @@
       </c>
       <c r="S10" s="4" t="inlineStr">
         <is>
-          <t>2026-09-03T22:43:49Z</t>
+          <t>2026-09-04T22:26:51Z</t>
         </is>
       </c>
     </row>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="S11" s="4" t="inlineStr">
         <is>
-          <t>2026-09-03T22:43:49Z</t>
+          <t>2026-09-04T22:26:51Z</t>
         </is>
       </c>
     </row>
@@ -1161,7 +1161,7 @@
       </c>
       <c r="S12" s="4" t="inlineStr">
         <is>
-          <t>2026-09-03T22:43:49Z</t>
+          <t>2026-09-04T22:26:51Z</t>
         </is>
       </c>
     </row>
@@ -1246,7 +1246,7 @@
       </c>
       <c r="S13" s="4" t="inlineStr">
         <is>
-          <t>2026-09-03T22:43:49Z</t>
+          <t>2026-09-04T22:26:51Z</t>
         </is>
       </c>
     </row>
@@ -1331,7 +1331,7 @@
       </c>
       <c r="S14" s="4" t="inlineStr">
         <is>
-          <t>2026-09-03T22:43:49Z</t>
+          <t>2026-09-04T22:26:51Z</t>
         </is>
       </c>
     </row>
@@ -1416,7 +1416,7 @@
       </c>
       <c r="S15" s="4" t="inlineStr">
         <is>
-          <t>2026-09-03T22:43:49Z</t>
+          <t>2026-09-04T22:26:51Z</t>
         </is>
       </c>
     </row>
@@ -1501,7 +1501,7 @@
       </c>
       <c r="S16" s="4" t="inlineStr">
         <is>
-          <t>2026-09-03T22:43:49Z</t>
+          <t>2026-09-04T22:26:51Z</t>
         </is>
       </c>
     </row>
@@ -1586,7 +1586,7 @@
       </c>
       <c r="S17" s="4" t="inlineStr">
         <is>
-          <t>2026-09-03T22:43:49Z</t>
+          <t>2026-09-04T22:26:51Z</t>
         </is>
       </c>
     </row>
@@ -1671,7 +1671,7 @@
       </c>
       <c r="S18" s="4" t="inlineStr">
         <is>
-          <t>2026-09-03T22:43:49Z</t>
+          <t>2026-09-04T22:26:51Z</t>
         </is>
       </c>
     </row>
@@ -1756,7 +1756,7 @@
       </c>
       <c r="S19" s="4" t="inlineStr">
         <is>
-          <t>2026-09-03T22:43:49Z</t>
+          <t>2026-09-04T22:26:51Z</t>
         </is>
       </c>
     </row>
@@ -1841,7 +1841,7 @@
       </c>
       <c r="S20" s="4" t="inlineStr">
         <is>
-          <t>2026-09-03T22:43:49Z</t>
+          <t>2026-09-04T22:26:51Z</t>
         </is>
       </c>
     </row>
@@ -1926,7 +1926,7 @@
       </c>
       <c r="S21" s="4" t="inlineStr">
         <is>
-          <t>2026-09-03T22:43:49Z</t>
+          <t>2026-09-04T22:26:51Z</t>
         </is>
       </c>
     </row>
@@ -2011,7 +2011,7 @@
       </c>
       <c r="S22" s="4" t="inlineStr">
         <is>
-          <t>2026-09-03T22:43:49Z</t>
+          <t>2026-09-04T22:26:51Z</t>
         </is>
       </c>
     </row>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="S23" s="4" t="inlineStr">
         <is>
-          <t>2026-09-03T22:43:49Z</t>
+          <t>2026-09-04T22:26:51Z</t>
         </is>
       </c>
     </row>
@@ -2181,7 +2181,7 @@
       </c>
       <c r="S24" s="4" t="inlineStr">
         <is>
-          <t>2026-09-03T22:43:49Z</t>
+          <t>2026-09-04T22:26:51Z</t>
         </is>
       </c>
     </row>
@@ -2266,7 +2266,7 @@
       </c>
       <c r="S25" s="4" t="inlineStr">
         <is>
-          <t>2026-09-03T22:43:49Z</t>
+          <t>2026-09-04T22:26:51Z</t>
         </is>
       </c>
     </row>
@@ -2351,7 +2351,7 @@
       </c>
       <c r="S26" s="4" t="inlineStr">
         <is>
-          <t>2026-09-03T22:43:49Z</t>
+          <t>2026-09-04T22:26:51Z</t>
         </is>
       </c>
     </row>
@@ -2436,7 +2436,7 @@
       </c>
       <c r="S27" s="4" t="inlineStr">
         <is>
-          <t>2026-09-03T22:43:49Z</t>
+          <t>2026-09-04T22:26:51Z</t>
         </is>
       </c>
     </row>
@@ -2521,7 +2521,7 @@
       </c>
       <c r="S28" s="4" t="inlineStr">
         <is>
-          <t>2026-09-03T22:43:49Z</t>
+          <t>2026-09-04T22:26:51Z</t>
         </is>
       </c>
     </row>
@@ -2606,7 +2606,7 @@
       </c>
       <c r="S29" s="4" t="inlineStr">
         <is>
-          <t>2026-09-03T22:43:49Z</t>
+          <t>2026-09-04T22:26:51Z</t>
         </is>
       </c>
     </row>
@@ -2691,7 +2691,7 @@
       </c>
       <c r="S30" s="4" t="inlineStr">
         <is>
-          <t>2026-09-03T22:43:49Z</t>
+          <t>2026-09-04T22:26:51Z</t>
         </is>
       </c>
     </row>
@@ -2776,7 +2776,7 @@
       </c>
       <c r="S31" s="4" t="inlineStr">
         <is>
-          <t>2026-09-03T22:43:49Z</t>
+          <t>2026-09-04T22:26:51Z</t>
         </is>
       </c>
     </row>
@@ -2861,7 +2861,7 @@
       </c>
       <c r="S32" s="4" t="inlineStr">
         <is>
-          <t>2026-09-03T22:43:49Z</t>
+          <t>2026-09-04T22:26:51Z</t>
         </is>
       </c>
     </row>
@@ -2946,7 +2946,7 @@
       </c>
       <c r="S33" s="4" t="inlineStr">
         <is>
-          <t>2026-09-03T22:43:49Z</t>
+          <t>2026-09-04T22:26:51Z</t>
         </is>
       </c>
     </row>
@@ -3031,7 +3031,7 @@
       </c>
       <c r="S34" s="4" t="inlineStr">
         <is>
-          <t>2026-09-03T22:43:49Z</t>
+          <t>2026-09-04T22:26:51Z</t>
         </is>
       </c>
     </row>
@@ -3116,7 +3116,7 @@
       </c>
       <c r="S35" s="4" t="inlineStr">
         <is>
-          <t>2026-09-03T22:43:49Z</t>
+          <t>2026-09-04T22:26:51Z</t>
         </is>
       </c>
     </row>
@@ -3201,7 +3201,7 @@
       </c>
       <c r="S36" s="4" t="inlineStr">
         <is>
-          <t>2026-09-03T22:43:49Z</t>
+          <t>2026-09-04T22:26:51Z</t>
         </is>
       </c>
     </row>
@@ -3286,7 +3286,7 @@
       </c>
       <c r="S37" s="4" t="inlineStr">
         <is>
-          <t>2026-09-03T22:43:49Z</t>
+          <t>2026-09-04T22:26:51Z</t>
         </is>
       </c>
     </row>
@@ -3371,7 +3371,7 @@
       </c>
       <c r="S38" s="4" t="inlineStr">
         <is>
-          <t>2026-09-03T22:43:49Z</t>
+          <t>2026-09-04T22:26:51Z</t>
         </is>
       </c>
     </row>
@@ -3456,7 +3456,7 @@
       </c>
       <c r="S39" s="4" t="inlineStr">
         <is>
-          <t>2026-09-03T22:43:49Z</t>
+          <t>2026-09-04T22:26:51Z</t>
         </is>
       </c>
     </row>
@@ -3541,7 +3541,7 @@
       </c>
       <c r="S40" s="4" t="inlineStr">
         <is>
-          <t>2026-09-03T22:43:49Z</t>
+          <t>2026-09-04T22:26:51Z</t>
         </is>
       </c>
     </row>
@@ -3626,7 +3626,7 @@
       </c>
       <c r="S41" s="4" t="inlineStr">
         <is>
-          <t>2026-09-03T22:43:49Z</t>
+          <t>2026-09-04T22:26:51Z</t>
         </is>
       </c>
     </row>
@@ -3711,7 +3711,7 @@
       </c>
       <c r="S42" s="4" t="inlineStr">
         <is>
-          <t>2026-09-03T22:43:49Z</t>
+          <t>2026-09-04T22:26:51Z</t>
         </is>
       </c>
     </row>
@@ -3796,7 +3796,7 @@
       </c>
       <c r="S43" s="4" t="inlineStr">
         <is>
-          <t>2026-09-03T22:43:49Z</t>
+          <t>2026-09-04T22:26:51Z</t>
         </is>
       </c>
     </row>
@@ -3881,7 +3881,7 @@
       </c>
       <c r="S44" s="4" t="inlineStr">
         <is>
-          <t>2026-09-03T22:43:49Z</t>
+          <t>2026-09-04T22:26:51Z</t>
         </is>
       </c>
     </row>
@@ -3966,7 +3966,7 @@
       </c>
       <c r="S45" s="4" t="inlineStr">
         <is>
-          <t>2026-09-03T22:43:49Z</t>
+          <t>2026-09-04T22:26:51Z</t>
         </is>
       </c>
     </row>
@@ -4051,7 +4051,7 @@
       </c>
       <c r="S46" s="4" t="inlineStr">
         <is>
-          <t>2026-09-03T22:43:49Z</t>
+          <t>2026-09-04T22:26:51Z</t>
         </is>
       </c>
     </row>
@@ -4136,7 +4136,7 @@
       </c>
       <c r="S47" s="4" t="inlineStr">
         <is>
-          <t>2026-09-03T22:43:49Z</t>
+          <t>2026-09-04T22:26:51Z</t>
         </is>
       </c>
     </row>
@@ -4221,7 +4221,7 @@
       </c>
       <c r="S48" s="4" t="inlineStr">
         <is>
-          <t>2026-09-03T22:43:49Z</t>
+          <t>2026-09-04T22:26:51Z</t>
         </is>
       </c>
     </row>
@@ -4306,7 +4306,7 @@
       </c>
       <c r="S49" s="4" t="inlineStr">
         <is>
-          <t>2026-09-03T22:43:49Z</t>
+          <t>2026-09-04T22:26:51Z</t>
         </is>
       </c>
     </row>
@@ -4391,7 +4391,7 @@
       </c>
       <c r="S50" s="4" t="inlineStr">
         <is>
-          <t>2026-09-03T22:43:49Z</t>
+          <t>2026-09-04T22:26:51Z</t>
         </is>
       </c>
     </row>
@@ -4476,7 +4476,7 @@
       </c>
       <c r="S51" s="4" t="inlineStr">
         <is>
-          <t>2026-09-03T22:43:49Z</t>
+          <t>2026-09-04T22:26:51Z</t>
         </is>
       </c>
     </row>
@@ -4561,7 +4561,7 @@
       </c>
       <c r="S52" s="4" t="inlineStr">
         <is>
-          <t>2026-09-03T22:43:49Z</t>
+          <t>2026-09-04T22:26:51Z</t>
         </is>
       </c>
     </row>
@@ -4646,7 +4646,7 @@
       </c>
       <c r="S53" s="4" t="inlineStr">
         <is>
-          <t>2026-09-03T22:43:49Z</t>
+          <t>2026-09-04T22:26:51Z</t>
         </is>
       </c>
     </row>
@@ -4731,7 +4731,7 @@
       </c>
       <c r="S54" s="4" t="inlineStr">
         <is>
-          <t>2026-09-03T22:43:49Z</t>
+          <t>2026-09-04T22:26:51Z</t>
         </is>
       </c>
     </row>
@@ -4816,7 +4816,7 @@
       </c>
       <c r="S55" s="4" t="inlineStr">
         <is>
-          <t>2026-09-03T22:43:49Z</t>
+          <t>2026-09-04T22:26:51Z</t>
         </is>
       </c>
     </row>
@@ -4901,7 +4901,7 @@
       </c>
       <c r="S56" s="4" t="inlineStr">
         <is>
-          <t>2026-09-03T22:43:49Z</t>
+          <t>2026-09-04T22:26:51Z</t>
         </is>
       </c>
     </row>
@@ -4986,7 +4986,7 @@
       </c>
       <c r="S57" s="4" t="inlineStr">
         <is>
-          <t>2026-09-03T22:43:49Z</t>
+          <t>2026-09-04T22:26:51Z</t>
         </is>
       </c>
     </row>
@@ -5071,7 +5071,7 @@
       </c>
       <c r="S58" s="4" t="inlineStr">
         <is>
-          <t>2026-09-03T22:43:49Z</t>
+          <t>2026-09-04T22:26:51Z</t>
         </is>
       </c>
     </row>
@@ -5156,7 +5156,7 @@
       </c>
       <c r="S59" s="4" t="inlineStr">
         <is>
-          <t>2026-09-03T22:43:49Z</t>
+          <t>2026-09-04T22:26:51Z</t>
         </is>
       </c>
     </row>
@@ -5241,7 +5241,7 @@
       </c>
       <c r="S60" s="4" t="inlineStr">
         <is>
-          <t>2026-09-03T22:43:49Z</t>
+          <t>2026-09-04T22:26:51Z</t>
         </is>
       </c>
     </row>
@@ -5326,7 +5326,7 @@
       </c>
       <c r="S61" s="4" t="inlineStr">
         <is>
-          <t>2026-09-03T22:43:49Z</t>
+          <t>2026-09-04T22:26:51Z</t>
         </is>
       </c>
     </row>
@@ -5411,7 +5411,7 @@
       </c>
       <c r="S62" s="4" t="inlineStr">
         <is>
-          <t>2026-09-03T22:43:49Z</t>
+          <t>2026-09-04T22:26:51Z</t>
         </is>
       </c>
     </row>
@@ -5496,7 +5496,7 @@
       </c>
       <c r="S63" s="4" t="inlineStr">
         <is>
-          <t>2026-09-03T22:43:49Z</t>
+          <t>2026-09-04T22:26:51Z</t>
         </is>
       </c>
     </row>
@@ -5581,7 +5581,7 @@
       </c>
       <c r="S64" s="4" t="inlineStr">
         <is>
-          <t>2026-09-03T22:43:49Z</t>
+          <t>2026-09-04T22:26:51Z</t>
         </is>
       </c>
     </row>
@@ -5666,7 +5666,7 @@
       </c>
       <c r="S65" s="4" t="inlineStr">
         <is>
-          <t>2026-09-03T22:43:49Z</t>
+          <t>2026-09-04T22:26:51Z</t>
         </is>
       </c>
     </row>
@@ -5751,7 +5751,7 @@
       </c>
       <c r="S66" s="4" t="inlineStr">
         <is>
-          <t>2026-09-03T22:43:49Z</t>
+          <t>2026-09-04T22:26:51Z</t>
         </is>
       </c>
     </row>
@@ -5836,7 +5836,7 @@
       </c>
       <c r="S67" s="4" t="inlineStr">
         <is>
-          <t>2026-09-03T22:43:49Z</t>
+          <t>2026-09-04T22:26:51Z</t>
         </is>
       </c>
     </row>
@@ -5921,7 +5921,7 @@
       </c>
       <c r="S68" s="4" t="inlineStr">
         <is>
-          <t>2026-09-03T22:43:49Z</t>
+          <t>2026-09-04T22:26:51Z</t>
         </is>
       </c>
     </row>
@@ -6006,7 +6006,7 @@
       </c>
       <c r="S69" s="4" t="inlineStr">
         <is>
-          <t>2026-09-03T22:43:49Z</t>
+          <t>2026-09-04T22:26:51Z</t>
         </is>
       </c>
     </row>
@@ -6091,7 +6091,7 @@
       </c>
       <c r="S70" s="4" t="inlineStr">
         <is>
-          <t>2026-09-03T22:43:49Z</t>
+          <t>2026-09-04T22:26:51Z</t>
         </is>
       </c>
     </row>
@@ -6176,7 +6176,7 @@
       </c>
       <c r="S71" s="4" t="inlineStr">
         <is>
-          <t>2026-09-03T22:43:49Z</t>
+          <t>2026-09-04T22:26:51Z</t>
         </is>
       </c>
     </row>
@@ -6261,7 +6261,7 @@
       </c>
       <c r="S72" s="4" t="inlineStr">
         <is>
-          <t>2026-09-03T22:43:49Z</t>
+          <t>2026-09-04T22:26:51Z</t>
         </is>
       </c>
     </row>
@@ -6346,7 +6346,7 @@
       </c>
       <c r="S73" s="4" t="inlineStr">
         <is>
-          <t>2026-09-03T22:43:49Z</t>
+          <t>2026-09-04T22:26:51Z</t>
         </is>
       </c>
     </row>
@@ -6431,7 +6431,7 @@
       </c>
       <c r="S74" s="4" t="inlineStr">
         <is>
-          <t>2026-09-03T22:43:49Z</t>
+          <t>2026-09-04T22:26:51Z</t>
         </is>
       </c>
     </row>
@@ -6516,7 +6516,7 @@
       </c>
       <c r="S75" s="4" t="inlineStr">
         <is>
-          <t>2026-09-03T22:43:49Z</t>
+          <t>2026-09-04T22:26:51Z</t>
         </is>
       </c>
     </row>
@@ -6601,7 +6601,7 @@
       </c>
       <c r="S76" s="4" t="inlineStr">
         <is>
-          <t>2026-09-03T22:43:49Z</t>
+          <t>2026-09-04T22:26:51Z</t>
         </is>
       </c>
     </row>
@@ -6686,7 +6686,7 @@
       </c>
       <c r="S77" s="4" t="inlineStr">
         <is>
-          <t>2026-09-03T22:43:49Z</t>
+          <t>2026-09-04T22:26:51Z</t>
         </is>
       </c>
     </row>
@@ -6771,7 +6771,7 @@
       </c>
       <c r="S78" s="4" t="inlineStr">
         <is>
-          <t>2026-09-03T22:43:49Z</t>
+          <t>2026-09-04T22:26:51Z</t>
         </is>
       </c>
     </row>
@@ -6856,7 +6856,7 @@
       </c>
       <c r="S79" s="4" t="inlineStr">
         <is>
-          <t>2026-09-03T22:43:49Z</t>
+          <t>2026-09-04T22:26:51Z</t>
         </is>
       </c>
     </row>
@@ -6941,7 +6941,7 @@
       </c>
       <c r="S80" s="4" t="inlineStr">
         <is>
-          <t>2026-09-03T22:43:49Z</t>
+          <t>2026-09-04T22:26:51Z</t>
         </is>
       </c>
     </row>
@@ -7026,7 +7026,7 @@
       </c>
       <c r="S81" s="4" t="inlineStr">
         <is>
-          <t>2026-09-03T22:43:49Z</t>
+          <t>2026-09-04T22:26:51Z</t>
         </is>
       </c>
     </row>
@@ -7111,7 +7111,7 @@
       </c>
       <c r="S82" s="4" t="inlineStr">
         <is>
-          <t>2026-09-03T22:43:49Z</t>
+          <t>2026-09-04T22:26:51Z</t>
         </is>
       </c>
     </row>
@@ -7196,7 +7196,7 @@
       </c>
       <c r="S83" s="4" t="inlineStr">
         <is>
-          <t>2026-09-03T22:43:49Z</t>
+          <t>2026-09-04T22:26:51Z</t>
         </is>
       </c>
     </row>
@@ -7281,7 +7281,7 @@
       </c>
       <c r="S84" s="4" t="inlineStr">
         <is>
-          <t>2026-09-03T22:43:49Z</t>
+          <t>2026-09-04T22:26:51Z</t>
         </is>
       </c>
     </row>
@@ -7366,7 +7366,7 @@
       </c>
       <c r="S85" s="4" t="inlineStr">
         <is>
-          <t>2026-09-03T22:43:49Z</t>
+          <t>2026-09-04T22:26:51Z</t>
         </is>
       </c>
     </row>
@@ -7451,7 +7451,7 @@
       </c>
       <c r="S86" s="4" t="inlineStr">
         <is>
-          <t>2026-09-03T22:43:49Z</t>
+          <t>2026-09-04T22:26:51Z</t>
         </is>
       </c>
     </row>
@@ -7536,7 +7536,7 @@
       </c>
       <c r="S87" s="4" t="inlineStr">
         <is>
-          <t>2026-09-03T22:43:49Z</t>
+          <t>2026-09-04T22:26:51Z</t>
         </is>
       </c>
     </row>
@@ -7621,7 +7621,7 @@
       </c>
       <c r="S88" s="4" t="inlineStr">
         <is>
-          <t>2026-09-03T22:43:49Z</t>
+          <t>2026-09-04T22:26:51Z</t>
         </is>
       </c>
     </row>
@@ -7706,7 +7706,7 @@
       </c>
       <c r="S89" s="4" t="inlineStr">
         <is>
-          <t>2026-09-03T22:43:49Z</t>
+          <t>2026-09-04T22:26:51Z</t>
         </is>
       </c>
     </row>
@@ -7791,7 +7791,7 @@
       </c>
       <c r="S90" s="4" t="inlineStr">
         <is>
-          <t>2026-09-03T22:43:49Z</t>
+          <t>2026-09-04T22:26:51Z</t>
         </is>
       </c>
     </row>
@@ -7876,7 +7876,7 @@
       </c>
       <c r="S91" s="4" t="inlineStr">
         <is>
-          <t>2026-09-03T22:43:49Z</t>
+          <t>2026-09-04T22:26:51Z</t>
         </is>
       </c>
     </row>
@@ -7961,7 +7961,7 @@
       </c>
       <c r="S92" s="4" t="inlineStr">
         <is>
-          <t>2026-09-03T22:43:49Z</t>
+          <t>2026-09-04T22:26:51Z</t>
         </is>
       </c>
     </row>
@@ -8046,7 +8046,7 @@
       </c>
       <c r="S93" s="4" t="inlineStr">
         <is>
-          <t>2026-09-03T22:43:49Z</t>
+          <t>2026-09-04T22:26:51Z</t>
         </is>
       </c>
     </row>
@@ -8131,7 +8131,7 @@
       </c>
       <c r="S94" s="4" t="inlineStr">
         <is>
-          <t>2026-09-03T22:43:49Z</t>
+          <t>2026-09-04T22:26:51Z</t>
         </is>
       </c>
     </row>
@@ -8216,7 +8216,7 @@
       </c>
       <c r="S95" s="4" t="inlineStr">
         <is>
-          <t>2026-09-03T22:43:49Z</t>
+          <t>2026-09-04T22:26:51Z</t>
         </is>
       </c>
     </row>
@@ -8301,7 +8301,7 @@
       </c>
       <c r="S96" s="4" t="inlineStr">
         <is>
-          <t>2026-09-03T22:43:49Z</t>
+          <t>2026-09-04T22:26:51Z</t>
         </is>
       </c>
     </row>
@@ -8386,7 +8386,7 @@
       </c>
       <c r="S97" s="4" t="inlineStr">
         <is>
-          <t>2026-09-03T22:43:49Z</t>
+          <t>2026-09-04T22:26:51Z</t>
         </is>
       </c>
     </row>
@@ -8471,7 +8471,7 @@
       </c>
       <c r="S98" s="4" t="inlineStr">
         <is>
-          <t>2026-09-03T22:43:49Z</t>
+          <t>2026-09-04T22:26:51Z</t>
         </is>
       </c>
     </row>
@@ -8556,7 +8556,7 @@
       </c>
       <c r="S99" s="4" t="inlineStr">
         <is>
-          <t>2026-09-03T22:43:49Z</t>
+          <t>2026-09-04T22:26:51Z</t>
         </is>
       </c>
     </row>
@@ -8641,7 +8641,7 @@
       </c>
       <c r="S100" s="4" t="inlineStr">
         <is>
-          <t>2026-09-03T22:43:49Z</t>
+          <t>2026-09-04T22:26:51Z</t>
         </is>
       </c>
     </row>
@@ -8726,7 +8726,7 @@
       </c>
       <c r="S101" s="4" t="inlineStr">
         <is>
-          <t>2026-09-03T22:43:49Z</t>
+          <t>2026-09-04T22:26:51Z</t>
         </is>
       </c>
     </row>
@@ -8811,7 +8811,7 @@
       </c>
       <c r="S102" s="4" t="inlineStr">
         <is>
-          <t>2026-09-03T22:43:49Z</t>
+          <t>2026-09-04T22:26:51Z</t>
         </is>
       </c>
     </row>
@@ -8896,7 +8896,7 @@
       </c>
       <c r="S103" s="4" t="inlineStr">
         <is>
-          <t>2026-09-03T22:43:49Z</t>
+          <t>2026-09-04T22:26:51Z</t>
         </is>
       </c>
     </row>
@@ -8981,7 +8981,7 @@
       </c>
       <c r="S104" s="4" t="inlineStr">
         <is>
-          <t>2026-09-03T22:43:49Z</t>
+          <t>2026-09-04T22:26:51Z</t>
         </is>
       </c>
     </row>
@@ -9066,7 +9066,7 @@
       </c>
       <c r="S105" s="4" t="inlineStr">
         <is>
-          <t>2026-09-03T22:43:49Z</t>
+          <t>2026-09-04T22:26:51Z</t>
         </is>
       </c>
     </row>
@@ -9151,7 +9151,7 @@
       </c>
       <c r="S106" s="4" t="inlineStr">
         <is>
-          <t>2026-09-03T22:43:49Z</t>
+          <t>2026-09-04T22:26:51Z</t>
         </is>
       </c>
     </row>
@@ -9236,7 +9236,7 @@
       </c>
       <c r="S107" s="4" t="inlineStr">
         <is>
-          <t>2026-09-03T22:43:49Z</t>
+          <t>2026-09-04T22:26:51Z</t>
         </is>
       </c>
     </row>
@@ -9321,7 +9321,7 @@
       </c>
       <c r="S108" s="4" t="inlineStr">
         <is>
-          <t>2026-09-03T22:43:49Z</t>
+          <t>2026-09-04T22:26:51Z</t>
         </is>
       </c>
     </row>
@@ -9406,7 +9406,7 @@
       </c>
       <c r="S109" s="4" t="inlineStr">
         <is>
-          <t>2026-09-03T22:43:49Z</t>
+          <t>2026-09-04T22:26:51Z</t>
         </is>
       </c>
     </row>
@@ -9491,7 +9491,7 @@
       </c>
       <c r="S110" s="4" t="inlineStr">
         <is>
-          <t>2026-09-03T22:43:49Z</t>
+          <t>2026-09-04T22:26:51Z</t>
         </is>
       </c>
     </row>
@@ -9576,7 +9576,7 @@
       </c>
       <c r="S111" s="4" t="inlineStr">
         <is>
-          <t>2026-09-03T22:43:49Z</t>
+          <t>2026-09-04T22:26:51Z</t>
         </is>
       </c>
     </row>
@@ -9661,7 +9661,7 @@
       </c>
       <c r="S112" s="4" t="inlineStr">
         <is>
-          <t>2026-09-03T22:43:49Z</t>
+          <t>2026-09-04T22:26:51Z</t>
         </is>
       </c>
     </row>
@@ -9746,7 +9746,7 @@
       </c>
       <c r="S113" s="4" t="inlineStr">
         <is>
-          <t>2026-09-03T22:43:49Z</t>
+          <t>2026-09-04T22:26:51Z</t>
         </is>
       </c>
     </row>
@@ -9831,7 +9831,7 @@
       </c>
       <c r="S114" s="4" t="inlineStr">
         <is>
-          <t>2026-09-03T22:43:49Z</t>
+          <t>2026-09-04T22:26:51Z</t>
         </is>
       </c>
     </row>
@@ -9916,7 +9916,7 @@
       </c>
       <c r="S115" s="4" t="inlineStr">
         <is>
-          <t>2026-09-03T22:43:49Z</t>
+          <t>2026-09-04T22:26:51Z</t>
         </is>
       </c>
     </row>
@@ -10001,7 +10001,7 @@
       </c>
       <c r="S116" s="4" t="inlineStr">
         <is>
-          <t>2026-09-03T22:43:49Z</t>
+          <t>2026-09-04T22:26:51Z</t>
         </is>
       </c>
     </row>
@@ -10086,7 +10086,7 @@
       </c>
       <c r="S117" s="4" t="inlineStr">
         <is>
-          <t>2026-09-03T22:43:49Z</t>
+          <t>2026-09-04T22:26:51Z</t>
         </is>
       </c>
     </row>
@@ -10171,7 +10171,7 @@
       </c>
       <c r="S118" s="4" t="inlineStr">
         <is>
-          <t>2026-09-03T22:43:49Z</t>
+          <t>2026-09-04T22:26:51Z</t>
         </is>
       </c>
     </row>
@@ -10256,7 +10256,7 @@
       </c>
       <c r="S119" s="4" t="inlineStr">
         <is>
-          <t>2026-09-03T22:43:49Z</t>
+          <t>2026-09-04T22:26:51Z</t>
         </is>
       </c>
     </row>
@@ -10341,7 +10341,7 @@
       </c>
       <c r="S120" s="4" t="inlineStr">
         <is>
-          <t>2026-09-03T22:43:49Z</t>
+          <t>2026-09-04T22:26:51Z</t>
         </is>
       </c>
     </row>
@@ -10426,7 +10426,7 @@
       </c>
       <c r="S121" s="4" t="inlineStr">
         <is>
-          <t>2026-09-03T22:43:49Z</t>
+          <t>2026-09-04T22:26:51Z</t>
         </is>
       </c>
     </row>
@@ -10511,7 +10511,7 @@
       </c>
       <c r="S122" s="4" t="inlineStr">
         <is>
-          <t>2026-09-03T22:43:49Z</t>
+          <t>2026-09-04T22:26:51Z</t>
         </is>
       </c>
     </row>
@@ -10596,7 +10596,7 @@
       </c>
       <c r="S123" s="4" t="inlineStr">
         <is>
-          <t>2026-09-03T22:43:49Z</t>
+          <t>2026-09-04T22:26:51Z</t>
         </is>
       </c>
     </row>
@@ -10681,7 +10681,7 @@
       </c>
       <c r="S124" s="4" t="inlineStr">
         <is>
-          <t>2026-09-03T22:43:49Z</t>
+          <t>2026-09-04T22:26:51Z</t>
         </is>
       </c>
     </row>
@@ -10766,7 +10766,7 @@
       </c>
       <c r="S125" s="4" t="inlineStr">
         <is>
-          <t>2026-09-03T22:43:49Z</t>
+          <t>2026-09-04T22:26:51Z</t>
         </is>
       </c>
     </row>
@@ -10851,7 +10851,7 @@
       </c>
       <c r="S126" s="4" t="inlineStr">
         <is>
-          <t>2026-09-03T22:43:49Z</t>
+          <t>2026-09-04T22:26:51Z</t>
         </is>
       </c>
     </row>
@@ -10936,7 +10936,7 @@
       </c>
       <c r="S127" s="4" t="inlineStr">
         <is>
-          <t>2026-09-03T22:43:49Z</t>
+          <t>2026-09-04T22:26:51Z</t>
         </is>
       </c>
     </row>
@@ -11021,7 +11021,7 @@
       </c>
       <c r="S128" s="4" t="inlineStr">
         <is>
-          <t>2026-09-03T22:43:49Z</t>
+          <t>2026-09-04T22:26:51Z</t>
         </is>
       </c>
     </row>
@@ -11106,7 +11106,7 @@
       </c>
       <c r="S129" s="4" t="inlineStr">
         <is>
-          <t>2026-09-03T22:43:49Z</t>
+          <t>2026-09-04T22:26:51Z</t>
         </is>
       </c>
     </row>
@@ -11191,7 +11191,7 @@
       </c>
       <c r="S130" s="4" t="inlineStr">
         <is>
-          <t>2026-09-03T22:43:49Z</t>
+          <t>2026-09-04T22:26:51Z</t>
         </is>
       </c>
     </row>
@@ -11276,7 +11276,7 @@
       </c>
       <c r="S131" s="4" t="inlineStr">
         <is>
-          <t>2026-09-03T22:43:49Z</t>
+          <t>2026-09-04T22:26:51Z</t>
         </is>
       </c>
     </row>
@@ -11361,7 +11361,7 @@
       </c>
       <c r="S132" s="4" t="inlineStr">
         <is>
-          <t>2026-09-03T22:43:49Z</t>
+          <t>2026-09-04T22:26:51Z</t>
         </is>
       </c>
     </row>
@@ -11446,7 +11446,7 @@
       </c>
       <c r="S133" s="4" t="inlineStr">
         <is>
-          <t>2026-09-03T22:43:49Z</t>
+          <t>2026-09-04T22:26:51Z</t>
         </is>
       </c>
     </row>
@@ -11531,7 +11531,7 @@
       </c>
       <c r="S134" s="4" t="inlineStr">
         <is>
-          <t>2026-09-03T22:43:49Z</t>
+          <t>2026-09-04T22:26:51Z</t>
         </is>
       </c>
     </row>
@@ -11616,7 +11616,7 @@
       </c>
       <c r="S135" s="4" t="inlineStr">
         <is>
-          <t>2026-09-03T22:43:49Z</t>
+          <t>2026-09-04T22:26:51Z</t>
         </is>
       </c>
     </row>
@@ -11701,7 +11701,7 @@
       </c>
       <c r="S136" s="4" t="inlineStr">
         <is>
-          <t>2026-09-03T22:43:49Z</t>
+          <t>2026-09-04T22:26:51Z</t>
         </is>
       </c>
     </row>
@@ -11786,7 +11786,7 @@
       </c>
       <c r="S137" s="4" t="inlineStr">
         <is>
-          <t>2026-09-03T22:43:49Z</t>
+          <t>2026-09-04T22:26:51Z</t>
         </is>
       </c>
     </row>
@@ -11871,7 +11871,7 @@
       </c>
       <c r="S138" s="4" t="inlineStr">
         <is>
-          <t>2026-09-03T22:43:49Z</t>
+          <t>2026-09-04T22:26:51Z</t>
         </is>
       </c>
     </row>
@@ -11956,7 +11956,7 @@
       </c>
       <c r="S139" s="4" t="inlineStr">
         <is>
-          <t>2026-09-03T22:43:49Z</t>
+          <t>2026-09-04T22:26:51Z</t>
         </is>
       </c>
     </row>
@@ -12041,7 +12041,7 @@
       </c>
       <c r="S140" s="4" t="inlineStr">
         <is>
-          <t>2026-09-03T22:43:49Z</t>
+          <t>2026-09-04T22:26:51Z</t>
         </is>
       </c>
     </row>
@@ -12126,7 +12126,7 @@
       </c>
       <c r="S141" s="4" t="inlineStr">
         <is>
-          <t>2026-09-03T22:43:49Z</t>
+          <t>2026-09-04T22:26:51Z</t>
         </is>
       </c>
     </row>
@@ -12258,7 +12258,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>2026-09-03T22:43:49Z</t>
+          <t>2026-09-04T22:26:51Z</t>
         </is>
       </c>
     </row>
@@ -12338,7 +12338,7 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>{"dataset_id": "bcv_pib_historico_anual", "title": "Producto interno bruto histórico anual", "table": "PIB histórico anual", "source_file": "7_1_14_anual.xls", "base": "1957/1968/1984/1997", "price_type": "Precios constantes", "measure": "Nivel", "frequency": "Anual", "period": "2017", "year": 2017, "quarter": null, "classification": "Total economía", "component": "Producto interno bruto", "value": 392393.12, "unit": "Millones de bolívares a precios constantes", "status": "", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/7_1_14_anual.xls", "fetched_at": "2026-09-03T22:43:49Z"}</t>
+          <t>{"dataset_id": "bcv_pib_historico_anual", "title": "Producto interno bruto histórico anual", "table": "PIB histórico anual", "source_file": "7_1_14_anual.xls", "base": "1957/1968/1984/1997", "price_type": "Precios constantes", "measure": "Nivel", "frequency": "Anual", "period": "2017", "year": 2017, "quarter": null, "classification": "Total economía", "component": "Producto interno bruto", "value": 392393.12, "unit": "Millones de bolívares a precios constantes", "status": "", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/7_1_14_anual.xls", "fetched_at": "2026-09-04T22:26:51Z"}</t>
         </is>
       </c>
     </row>

--- a/assets/data/bcv/excel/ove_bcv_pib_historico_anual.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_pib_historico_anual.xlsx
@@ -736,7 +736,7 @@
       </c>
       <c r="S7" s="4" t="inlineStr">
         <is>
-          <t>2026-09-04T22:26:51Z</t>
+          <t>2026-09-05T22:09:18Z</t>
         </is>
       </c>
     </row>
@@ -821,7 +821,7 @@
       </c>
       <c r="S8" s="4" t="inlineStr">
         <is>
-          <t>2026-09-04T22:26:51Z</t>
+          <t>2026-09-05T22:09:18Z</t>
         </is>
       </c>
     </row>
@@ -906,7 +906,7 @@
       </c>
       <c r="S9" s="4" t="inlineStr">
         <is>
-          <t>2026-09-04T22:26:51Z</t>
+          <t>2026-09-05T22:09:18Z</t>
         </is>
       </c>
     </row>
@@ -991,7 +991,7 @@
       </c>
       <c r="S10" s="4" t="inlineStr">
         <is>
-          <t>2026-09-04T22:26:51Z</t>
+          <t>2026-09-05T22:09:18Z</t>
         </is>
       </c>
     </row>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="S11" s="4" t="inlineStr">
         <is>
-          <t>2026-09-04T22:26:51Z</t>
+          <t>2026-09-05T22:09:18Z</t>
         </is>
       </c>
     </row>
@@ -1161,7 +1161,7 @@
       </c>
       <c r="S12" s="4" t="inlineStr">
         <is>
-          <t>2026-09-04T22:26:51Z</t>
+          <t>2026-09-05T22:09:18Z</t>
         </is>
       </c>
     </row>
@@ -1246,7 +1246,7 @@
       </c>
       <c r="S13" s="4" t="inlineStr">
         <is>
-          <t>2026-09-04T22:26:51Z</t>
+          <t>2026-09-05T22:09:18Z</t>
         </is>
       </c>
     </row>
@@ -1331,7 +1331,7 @@
       </c>
       <c r="S14" s="4" t="inlineStr">
         <is>
-          <t>2026-09-04T22:26:51Z</t>
+          <t>2026-09-05T22:09:18Z</t>
         </is>
       </c>
     </row>
@@ -1416,7 +1416,7 @@
       </c>
       <c r="S15" s="4" t="inlineStr">
         <is>
-          <t>2026-09-04T22:26:51Z</t>
+          <t>2026-09-05T22:09:18Z</t>
         </is>
       </c>
     </row>
@@ -1501,7 +1501,7 @@
       </c>
       <c r="S16" s="4" t="inlineStr">
         <is>
-          <t>2026-09-04T22:26:51Z</t>
+          <t>2026-09-05T22:09:18Z</t>
         </is>
       </c>
     </row>
@@ -1586,7 +1586,7 @@
       </c>
       <c r="S17" s="4" t="inlineStr">
         <is>
-          <t>2026-09-04T22:26:51Z</t>
+          <t>2026-09-05T22:09:18Z</t>
         </is>
       </c>
     </row>
@@ -1671,7 +1671,7 @@
       </c>
       <c r="S18" s="4" t="inlineStr">
         <is>
-          <t>2026-09-04T22:26:51Z</t>
+          <t>2026-09-05T22:09:18Z</t>
         </is>
       </c>
     </row>
@@ -1756,7 +1756,7 @@
       </c>
       <c r="S19" s="4" t="inlineStr">
         <is>
-          <t>2026-09-04T22:26:51Z</t>
+          <t>2026-09-05T22:09:18Z</t>
         </is>
       </c>
     </row>
@@ -1841,7 +1841,7 @@
       </c>
       <c r="S20" s="4" t="inlineStr">
         <is>
-          <t>2026-09-04T22:26:51Z</t>
+          <t>2026-09-05T22:09:18Z</t>
         </is>
       </c>
     </row>
@@ -1926,7 +1926,7 @@
       </c>
       <c r="S21" s="4" t="inlineStr">
         <is>
-          <t>2026-09-04T22:26:51Z</t>
+          <t>2026-09-05T22:09:18Z</t>
         </is>
       </c>
     </row>
@@ -2011,7 +2011,7 @@
       </c>
       <c r="S22" s="4" t="inlineStr">
         <is>
-          <t>2026-09-04T22:26:51Z</t>
+          <t>2026-09-05T22:09:18Z</t>
         </is>
       </c>
     </row>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="S23" s="4" t="inlineStr">
         <is>
-          <t>2026-09-04T22:26:51Z</t>
+          <t>2026-09-05T22:09:18Z</t>
         </is>
       </c>
     </row>
@@ -2181,7 +2181,7 @@
       </c>
       <c r="S24" s="4" t="inlineStr">
         <is>
-          <t>2026-09-04T22:26:51Z</t>
+          <t>2026-09-05T22:09:18Z</t>
         </is>
       </c>
     </row>
@@ -2266,7 +2266,7 @@
       </c>
       <c r="S25" s="4" t="inlineStr">
         <is>
-          <t>2026-09-04T22:26:51Z</t>
+          <t>2026-09-05T22:09:18Z</t>
         </is>
       </c>
     </row>
@@ -2351,7 +2351,7 @@
       </c>
       <c r="S26" s="4" t="inlineStr">
         <is>
-          <t>2026-09-04T22:26:51Z</t>
+          <t>2026-09-05T22:09:18Z</t>
         </is>
       </c>
     </row>
@@ -2436,7 +2436,7 @@
       </c>
       <c r="S27" s="4" t="inlineStr">
         <is>
-          <t>2026-09-04T22:26:51Z</t>
+          <t>2026-09-05T22:09:18Z</t>
         </is>
       </c>
     </row>
@@ -2521,7 +2521,7 @@
       </c>
       <c r="S28" s="4" t="inlineStr">
         <is>
-          <t>2026-09-04T22:26:51Z</t>
+          <t>2026-09-05T22:09:18Z</t>
         </is>
       </c>
     </row>
@@ -2606,7 +2606,7 @@
       </c>
       <c r="S29" s="4" t="inlineStr">
         <is>
-          <t>2026-09-04T22:26:51Z</t>
+          <t>2026-09-05T22:09:18Z</t>
         </is>
       </c>
     </row>
@@ -2691,7 +2691,7 @@
       </c>
       <c r="S30" s="4" t="inlineStr">
         <is>
-          <t>2026-09-04T22:26:51Z</t>
+          <t>2026-09-05T22:09:18Z</t>
         </is>
       </c>
     </row>
@@ -2776,7 +2776,7 @@
       </c>
       <c r="S31" s="4" t="inlineStr">
         <is>
-          <t>2026-09-04T22:26:51Z</t>
+          <t>2026-09-05T22:09:18Z</t>
         </is>
       </c>
     </row>
@@ -2861,7 +2861,7 @@
       </c>
       <c r="S32" s="4" t="inlineStr">
         <is>
-          <t>2026-09-04T22:26:51Z</t>
+          <t>2026-09-05T22:09:18Z</t>
         </is>
       </c>
     </row>
@@ -2946,7 +2946,7 @@
       </c>
       <c r="S33" s="4" t="inlineStr">
         <is>
-          <t>2026-09-04T22:26:51Z</t>
+          <t>2026-09-05T22:09:18Z</t>
         </is>
       </c>
     </row>
@@ -3031,7 +3031,7 @@
       </c>
       <c r="S34" s="4" t="inlineStr">
         <is>
-          <t>2026-09-04T22:26:51Z</t>
+          <t>2026-09-05T22:09:18Z</t>
         </is>
       </c>
     </row>
@@ -3116,7 +3116,7 @@
       </c>
       <c r="S35" s="4" t="inlineStr">
         <is>
-          <t>2026-09-04T22:26:51Z</t>
+          <t>2026-09-05T22:09:18Z</t>
         </is>
       </c>
     </row>
@@ -3201,7 +3201,7 @@
       </c>
       <c r="S36" s="4" t="inlineStr">
         <is>
-          <t>2026-09-04T22:26:51Z</t>
+          <t>2026-09-05T22:09:18Z</t>
         </is>
       </c>
     </row>
@@ -3286,7 +3286,7 @@
       </c>
       <c r="S37" s="4" t="inlineStr">
         <is>
-          <t>2026-09-04T22:26:51Z</t>
+          <t>2026-09-05T22:09:18Z</t>
         </is>
       </c>
     </row>
@@ -3371,7 +3371,7 @@
       </c>
       <c r="S38" s="4" t="inlineStr">
         <is>
-          <t>2026-09-04T22:26:51Z</t>
+          <t>2026-09-05T22:09:18Z</t>
         </is>
       </c>
     </row>
@@ -3456,7 +3456,7 @@
       </c>
       <c r="S39" s="4" t="inlineStr">
         <is>
-          <t>2026-09-04T22:26:51Z</t>
+          <t>2026-09-05T22:09:18Z</t>
         </is>
       </c>
     </row>
@@ -3541,7 +3541,7 @@
       </c>
       <c r="S40" s="4" t="inlineStr">
         <is>
-          <t>2026-09-04T22:26:51Z</t>
+          <t>2026-09-05T22:09:18Z</t>
         </is>
       </c>
     </row>
@@ -3626,7 +3626,7 @@
       </c>
       <c r="S41" s="4" t="inlineStr">
         <is>
-          <t>2026-09-04T22:26:51Z</t>
+          <t>2026-09-05T22:09:18Z</t>
         </is>
       </c>
     </row>
@@ -3711,7 +3711,7 @@
       </c>
       <c r="S42" s="4" t="inlineStr">
         <is>
-          <t>2026-09-04T22:26:51Z</t>
+          <t>2026-09-05T22:09:18Z</t>
         </is>
       </c>
     </row>
@@ -3796,7 +3796,7 @@
       </c>
       <c r="S43" s="4" t="inlineStr">
         <is>
-          <t>2026-09-04T22:26:51Z</t>
+          <t>2026-09-05T22:09:18Z</t>
         </is>
       </c>
     </row>
@@ -3881,7 +3881,7 @@
       </c>
       <c r="S44" s="4" t="inlineStr">
         <is>
-          <t>2026-09-04T22:26:51Z</t>
+          <t>2026-09-05T22:09:18Z</t>
         </is>
       </c>
     </row>
@@ -3966,7 +3966,7 @@
       </c>
       <c r="S45" s="4" t="inlineStr">
         <is>
-          <t>2026-09-04T22:26:51Z</t>
+          <t>2026-09-05T22:09:18Z</t>
         </is>
       </c>
     </row>
@@ -4051,7 +4051,7 @@
       </c>
       <c r="S46" s="4" t="inlineStr">
         <is>
-          <t>2026-09-04T22:26:51Z</t>
+          <t>2026-09-05T22:09:18Z</t>
         </is>
       </c>
     </row>
@@ -4136,7 +4136,7 @@
       </c>
       <c r="S47" s="4" t="inlineStr">
         <is>
-          <t>2026-09-04T22:26:51Z</t>
+          <t>2026-09-05T22:09:18Z</t>
         </is>
       </c>
     </row>
@@ -4221,7 +4221,7 @@
       </c>
       <c r="S48" s="4" t="inlineStr">
         <is>
-          <t>2026-09-04T22:26:51Z</t>
+          <t>2026-09-05T22:09:18Z</t>
         </is>
       </c>
     </row>
@@ -4306,7 +4306,7 @@
       </c>
       <c r="S49" s="4" t="inlineStr">
         <is>
-          <t>2026-09-04T22:26:51Z</t>
+          <t>2026-09-05T22:09:18Z</t>
         </is>
       </c>
     </row>
@@ -4391,7 +4391,7 @@
       </c>
       <c r="S50" s="4" t="inlineStr">
         <is>
-          <t>2026-09-04T22:26:51Z</t>
+          <t>2026-09-05T22:09:18Z</t>
         </is>
       </c>
     </row>
@@ -4476,7 +4476,7 @@
       </c>
       <c r="S51" s="4" t="inlineStr">
         <is>
-          <t>2026-09-04T22:26:51Z</t>
+          <t>2026-09-05T22:09:18Z</t>
         </is>
       </c>
     </row>
@@ -4561,7 +4561,7 @@
       </c>
       <c r="S52" s="4" t="inlineStr">
         <is>
-          <t>2026-09-04T22:26:51Z</t>
+          <t>2026-09-05T22:09:18Z</t>
         </is>
       </c>
     </row>
@@ -4646,7 +4646,7 @@
       </c>
       <c r="S53" s="4" t="inlineStr">
         <is>
-          <t>2026-09-04T22:26:51Z</t>
+          <t>2026-09-05T22:09:18Z</t>
         </is>
       </c>
     </row>
@@ -4731,7 +4731,7 @@
       </c>
       <c r="S54" s="4" t="inlineStr">
         <is>
-          <t>2026-09-04T22:26:51Z</t>
+          <t>2026-09-05T22:09:18Z</t>
         </is>
       </c>
     </row>
@@ -4816,7 +4816,7 @@
       </c>
       <c r="S55" s="4" t="inlineStr">
         <is>
-          <t>2026-09-04T22:26:51Z</t>
+          <t>2026-09-05T22:09:18Z</t>
         </is>
       </c>
     </row>
@@ -4901,7 +4901,7 @@
       </c>
       <c r="S56" s="4" t="inlineStr">
         <is>
-          <t>2026-09-04T22:26:51Z</t>
+          <t>2026-09-05T22:09:18Z</t>
         </is>
       </c>
     </row>
@@ -4986,7 +4986,7 @@
       </c>
       <c r="S57" s="4" t="inlineStr">
         <is>
-          <t>2026-09-04T22:26:51Z</t>
+          <t>2026-09-05T22:09:18Z</t>
         </is>
       </c>
     </row>
@@ -5071,7 +5071,7 @@
       </c>
       <c r="S58" s="4" t="inlineStr">
         <is>
-          <t>2026-09-04T22:26:51Z</t>
+          <t>2026-09-05T22:09:18Z</t>
         </is>
       </c>
     </row>
@@ -5156,7 +5156,7 @@
       </c>
       <c r="S59" s="4" t="inlineStr">
         <is>
-          <t>2026-09-04T22:26:51Z</t>
+          <t>2026-09-05T22:09:18Z</t>
         </is>
       </c>
     </row>
@@ -5241,7 +5241,7 @@
       </c>
       <c r="S60" s="4" t="inlineStr">
         <is>
-          <t>2026-09-04T22:26:51Z</t>
+          <t>2026-09-05T22:09:18Z</t>
         </is>
       </c>
     </row>
@@ -5326,7 +5326,7 @@
       </c>
       <c r="S61" s="4" t="inlineStr">
         <is>
-          <t>2026-09-04T22:26:51Z</t>
+          <t>2026-09-05T22:09:18Z</t>
         </is>
       </c>
     </row>
@@ -5411,7 +5411,7 @@
       </c>
       <c r="S62" s="4" t="inlineStr">
         <is>
-          <t>2026-09-04T22:26:51Z</t>
+          <t>2026-09-05T22:09:18Z</t>
         </is>
       </c>
     </row>
@@ -5496,7 +5496,7 @@
       </c>
       <c r="S63" s="4" t="inlineStr">
         <is>
-          <t>2026-09-04T22:26:51Z</t>
+          <t>2026-09-05T22:09:18Z</t>
         </is>
       </c>
     </row>
@@ -5581,7 +5581,7 @@
       </c>
       <c r="S64" s="4" t="inlineStr">
         <is>
-          <t>2026-09-04T22:26:51Z</t>
+          <t>2026-09-05T22:09:18Z</t>
         </is>
       </c>
     </row>
@@ -5666,7 +5666,7 @@
       </c>
       <c r="S65" s="4" t="inlineStr">
         <is>
-          <t>2026-09-04T22:26:51Z</t>
+          <t>2026-09-05T22:09:18Z</t>
         </is>
       </c>
     </row>
@@ -5751,7 +5751,7 @@
       </c>
       <c r="S66" s="4" t="inlineStr">
         <is>
-          <t>2026-09-04T22:26:51Z</t>
+          <t>2026-09-05T22:09:18Z</t>
         </is>
       </c>
     </row>
@@ -5836,7 +5836,7 @@
       </c>
       <c r="S67" s="4" t="inlineStr">
         <is>
-          <t>2026-09-04T22:26:51Z</t>
+          <t>2026-09-05T22:09:18Z</t>
         </is>
       </c>
     </row>
@@ -5921,7 +5921,7 @@
       </c>
       <c r="S68" s="4" t="inlineStr">
         <is>
-          <t>2026-09-04T22:26:51Z</t>
+          <t>2026-09-05T22:09:18Z</t>
         </is>
       </c>
     </row>
@@ -6006,7 +6006,7 @@
       </c>
       <c r="S69" s="4" t="inlineStr">
         <is>
-          <t>2026-09-04T22:26:51Z</t>
+          <t>2026-09-05T22:09:18Z</t>
         </is>
       </c>
     </row>
@@ -6091,7 +6091,7 @@
       </c>
       <c r="S70" s="4" t="inlineStr">
         <is>
-          <t>2026-09-04T22:26:51Z</t>
+          <t>2026-09-05T22:09:18Z</t>
         </is>
       </c>
     </row>
@@ -6176,7 +6176,7 @@
       </c>
       <c r="S71" s="4" t="inlineStr">
         <is>
-          <t>2026-09-04T22:26:51Z</t>
+          <t>2026-09-05T22:09:18Z</t>
         </is>
       </c>
     </row>
@@ -6261,7 +6261,7 @@
       </c>
       <c r="S72" s="4" t="inlineStr">
         <is>
-          <t>2026-09-04T22:26:51Z</t>
+          <t>2026-09-05T22:09:18Z</t>
         </is>
       </c>
     </row>
@@ -6346,7 +6346,7 @@
       </c>
       <c r="S73" s="4" t="inlineStr">
         <is>
-          <t>2026-09-04T22:26:51Z</t>
+          <t>2026-09-05T22:09:18Z</t>
         </is>
       </c>
     </row>
@@ -6431,7 +6431,7 @@
       </c>
       <c r="S74" s="4" t="inlineStr">
         <is>
-          <t>2026-09-04T22:26:51Z</t>
+          <t>2026-09-05T22:09:18Z</t>
         </is>
       </c>
     </row>
@@ -6516,7 +6516,7 @@
       </c>
       <c r="S75" s="4" t="inlineStr">
         <is>
-          <t>2026-09-04T22:26:51Z</t>
+          <t>2026-09-05T22:09:18Z</t>
         </is>
       </c>
     </row>
@@ -6601,7 +6601,7 @@
       </c>
       <c r="S76" s="4" t="inlineStr">
         <is>
-          <t>2026-09-04T22:26:51Z</t>
+          <t>2026-09-05T22:09:18Z</t>
         </is>
       </c>
     </row>
@@ -6686,7 +6686,7 @@
       </c>
       <c r="S77" s="4" t="inlineStr">
         <is>
-          <t>2026-09-04T22:26:51Z</t>
+          <t>2026-09-05T22:09:18Z</t>
         </is>
       </c>
     </row>
@@ -6771,7 +6771,7 @@
       </c>
       <c r="S78" s="4" t="inlineStr">
         <is>
-          <t>2026-09-04T22:26:51Z</t>
+          <t>2026-09-05T22:09:18Z</t>
         </is>
       </c>
     </row>
@@ -6856,7 +6856,7 @@
       </c>
       <c r="S79" s="4" t="inlineStr">
         <is>
-          <t>2026-09-04T22:26:51Z</t>
+          <t>2026-09-05T22:09:18Z</t>
         </is>
       </c>
     </row>
@@ -6941,7 +6941,7 @@
       </c>
       <c r="S80" s="4" t="inlineStr">
         <is>
-          <t>2026-09-04T22:26:51Z</t>
+          <t>2026-09-05T22:09:18Z</t>
         </is>
       </c>
     </row>
@@ -7026,7 +7026,7 @@
       </c>
       <c r="S81" s="4" t="inlineStr">
         <is>
-          <t>2026-09-04T22:26:51Z</t>
+          <t>2026-09-05T22:09:18Z</t>
         </is>
       </c>
     </row>
@@ -7111,7 +7111,7 @@
       </c>
       <c r="S82" s="4" t="inlineStr">
         <is>
-          <t>2026-09-04T22:26:51Z</t>
+          <t>2026-09-05T22:09:18Z</t>
         </is>
       </c>
     </row>
@@ -7196,7 +7196,7 @@
       </c>
       <c r="S83" s="4" t="inlineStr">
         <is>
-          <t>2026-09-04T22:26:51Z</t>
+          <t>2026-09-05T22:09:18Z</t>
         </is>
       </c>
     </row>
@@ -7281,7 +7281,7 @@
       </c>
       <c r="S84" s="4" t="inlineStr">
         <is>
-          <t>2026-09-04T22:26:51Z</t>
+          <t>2026-09-05T22:09:18Z</t>
         </is>
       </c>
     </row>
@@ -7366,7 +7366,7 @@
       </c>
       <c r="S85" s="4" t="inlineStr">
         <is>
-          <t>2026-09-04T22:26:51Z</t>
+          <t>2026-09-05T22:09:18Z</t>
         </is>
       </c>
     </row>
@@ -7451,7 +7451,7 @@
       </c>
       <c r="S86" s="4" t="inlineStr">
         <is>
-          <t>2026-09-04T22:26:51Z</t>
+          <t>2026-09-05T22:09:18Z</t>
         </is>
       </c>
     </row>
@@ -7536,7 +7536,7 @@
       </c>
       <c r="S87" s="4" t="inlineStr">
         <is>
-          <t>2026-09-04T22:26:51Z</t>
+          <t>2026-09-05T22:09:18Z</t>
         </is>
       </c>
     </row>
@@ -7621,7 +7621,7 @@
       </c>
       <c r="S88" s="4" t="inlineStr">
         <is>
-          <t>2026-09-04T22:26:51Z</t>
+          <t>2026-09-05T22:09:18Z</t>
         </is>
       </c>
     </row>
@@ -7706,7 +7706,7 @@
       </c>
       <c r="S89" s="4" t="inlineStr">
         <is>
-          <t>2026-09-04T22:26:51Z</t>
+          <t>2026-09-05T22:09:18Z</t>
         </is>
       </c>
     </row>
@@ -7791,7 +7791,7 @@
       </c>
       <c r="S90" s="4" t="inlineStr">
         <is>
-          <t>2026-09-04T22:26:51Z</t>
+          <t>2026-09-05T22:09:18Z</t>
         </is>
       </c>
     </row>
@@ -7876,7 +7876,7 @@
       </c>
       <c r="S91" s="4" t="inlineStr">
         <is>
-          <t>2026-09-04T22:26:51Z</t>
+          <t>2026-09-05T22:09:18Z</t>
         </is>
       </c>
     </row>
@@ -7961,7 +7961,7 @@
       </c>
       <c r="S92" s="4" t="inlineStr">
         <is>
-          <t>2026-09-04T22:26:51Z</t>
+          <t>2026-09-05T22:09:18Z</t>
         </is>
       </c>
     </row>
@@ -8046,7 +8046,7 @@
       </c>
       <c r="S93" s="4" t="inlineStr">
         <is>
-          <t>2026-09-04T22:26:51Z</t>
+          <t>2026-09-05T22:09:18Z</t>
         </is>
       </c>
     </row>
@@ -8131,7 +8131,7 @@
       </c>
       <c r="S94" s="4" t="inlineStr">
         <is>
-          <t>2026-09-04T22:26:51Z</t>
+          <t>2026-09-05T22:09:18Z</t>
         </is>
       </c>
     </row>
@@ -8216,7 +8216,7 @@
       </c>
       <c r="S95" s="4" t="inlineStr">
         <is>
-          <t>2026-09-04T22:26:51Z</t>
+          <t>2026-09-05T22:09:18Z</t>
         </is>
       </c>
     </row>
@@ -8301,7 +8301,7 @@
       </c>
       <c r="S96" s="4" t="inlineStr">
         <is>
-          <t>2026-09-04T22:26:51Z</t>
+          <t>2026-09-05T22:09:18Z</t>
         </is>
       </c>
     </row>
@@ -8386,7 +8386,7 @@
       </c>
       <c r="S97" s="4" t="inlineStr">
         <is>
-          <t>2026-09-04T22:26:51Z</t>
+          <t>2026-09-05T22:09:18Z</t>
         </is>
       </c>
     </row>
@@ -8471,7 +8471,7 @@
       </c>
       <c r="S98" s="4" t="inlineStr">
         <is>
-          <t>2026-09-04T22:26:51Z</t>
+          <t>2026-09-05T22:09:18Z</t>
         </is>
       </c>
     </row>
@@ -8556,7 +8556,7 @@
       </c>
       <c r="S99" s="4" t="inlineStr">
         <is>
-          <t>2026-09-04T22:26:51Z</t>
+          <t>2026-09-05T22:09:18Z</t>
         </is>
       </c>
     </row>
@@ -8641,7 +8641,7 @@
       </c>
       <c r="S100" s="4" t="inlineStr">
         <is>
-          <t>2026-09-04T22:26:51Z</t>
+          <t>2026-09-05T22:09:18Z</t>
         </is>
       </c>
     </row>
@@ -8726,7 +8726,7 @@
       </c>
       <c r="S101" s="4" t="inlineStr">
         <is>
-          <t>2026-09-04T22:26:51Z</t>
+          <t>2026-09-05T22:09:18Z</t>
         </is>
       </c>
     </row>
@@ -8811,7 +8811,7 @@
       </c>
       <c r="S102" s="4" t="inlineStr">
         <is>
-          <t>2026-09-04T22:26:51Z</t>
+          <t>2026-09-05T22:09:18Z</t>
         </is>
       </c>
     </row>
@@ -8896,7 +8896,7 @@
       </c>
       <c r="S103" s="4" t="inlineStr">
         <is>
-          <t>2026-09-04T22:26:51Z</t>
+          <t>2026-09-05T22:09:18Z</t>
         </is>
       </c>
     </row>
@@ -8981,7 +8981,7 @@
       </c>
       <c r="S104" s="4" t="inlineStr">
         <is>
-          <t>2026-09-04T22:26:51Z</t>
+          <t>2026-09-05T22:09:18Z</t>
         </is>
       </c>
     </row>
@@ -9066,7 +9066,7 @@
       </c>
       <c r="S105" s="4" t="inlineStr">
         <is>
-          <t>2026-09-04T22:26:51Z</t>
+          <t>2026-09-05T22:09:18Z</t>
         </is>
       </c>
     </row>
@@ -9151,7 +9151,7 @@
       </c>
       <c r="S106" s="4" t="inlineStr">
         <is>
-          <t>2026-09-04T22:26:51Z</t>
+          <t>2026-09-05T22:09:18Z</t>
         </is>
       </c>
     </row>
@@ -9236,7 +9236,7 @@
       </c>
       <c r="S107" s="4" t="inlineStr">
         <is>
-          <t>2026-09-04T22:26:51Z</t>
+          <t>2026-09-05T22:09:18Z</t>
         </is>
       </c>
     </row>
@@ -9321,7 +9321,7 @@
       </c>
       <c r="S108" s="4" t="inlineStr">
         <is>
-          <t>2026-09-04T22:26:51Z</t>
+          <t>2026-09-05T22:09:18Z</t>
         </is>
       </c>
     </row>
@@ -9406,7 +9406,7 @@
       </c>
       <c r="S109" s="4" t="inlineStr">
         <is>
-          <t>2026-09-04T22:26:51Z</t>
+          <t>2026-09-05T22:09:18Z</t>
         </is>
       </c>
     </row>
@@ -9491,7 +9491,7 @@
       </c>
       <c r="S110" s="4" t="inlineStr">
         <is>
-          <t>2026-09-04T22:26:51Z</t>
+          <t>2026-09-05T22:09:18Z</t>
         </is>
       </c>
     </row>
@@ -9576,7 +9576,7 @@
       </c>
       <c r="S111" s="4" t="inlineStr">
         <is>
-          <t>2026-09-04T22:26:51Z</t>
+          <t>2026-09-05T22:09:18Z</t>
         </is>
       </c>
     </row>
@@ -9661,7 +9661,7 @@
       </c>
       <c r="S112" s="4" t="inlineStr">
         <is>
-          <t>2026-09-04T22:26:51Z</t>
+          <t>2026-09-05T22:09:18Z</t>
         </is>
       </c>
     </row>
@@ -9746,7 +9746,7 @@
       </c>
       <c r="S113" s="4" t="inlineStr">
         <is>
-          <t>2026-09-04T22:26:51Z</t>
+          <t>2026-09-05T22:09:18Z</t>
         </is>
       </c>
     </row>
@@ -9831,7 +9831,7 @@
       </c>
       <c r="S114" s="4" t="inlineStr">
         <is>
-          <t>2026-09-04T22:26:51Z</t>
+          <t>2026-09-05T22:09:18Z</t>
         </is>
       </c>
     </row>
@@ -9916,7 +9916,7 @@
       </c>
       <c r="S115" s="4" t="inlineStr">
         <is>
-          <t>2026-09-04T22:26:51Z</t>
+          <t>2026-09-05T22:09:18Z</t>
         </is>
       </c>
     </row>
@@ -10001,7 +10001,7 @@
       </c>
       <c r="S116" s="4" t="inlineStr">
         <is>
-          <t>2026-09-04T22:26:51Z</t>
+          <t>2026-09-05T22:09:18Z</t>
         </is>
       </c>
     </row>
@@ -10086,7 +10086,7 @@
       </c>
       <c r="S117" s="4" t="inlineStr">
         <is>
-          <t>2026-09-04T22:26:51Z</t>
+          <t>2026-09-05T22:09:18Z</t>
         </is>
       </c>
     </row>
@@ -10171,7 +10171,7 @@
       </c>
       <c r="S118" s="4" t="inlineStr">
         <is>
-          <t>2026-09-04T22:26:51Z</t>
+          <t>2026-09-05T22:09:18Z</t>
         </is>
       </c>
     </row>
@@ -10256,7 +10256,7 @@
       </c>
       <c r="S119" s="4" t="inlineStr">
         <is>
-          <t>2026-09-04T22:26:51Z</t>
+          <t>2026-09-05T22:09:18Z</t>
         </is>
       </c>
     </row>
@@ -10341,7 +10341,7 @@
       </c>
       <c r="S120" s="4" t="inlineStr">
         <is>
-          <t>2026-09-04T22:26:51Z</t>
+          <t>2026-09-05T22:09:18Z</t>
         </is>
       </c>
     </row>
@@ -10426,7 +10426,7 @@
       </c>
       <c r="S121" s="4" t="inlineStr">
         <is>
-          <t>2026-09-04T22:26:51Z</t>
+          <t>2026-09-05T22:09:18Z</t>
         </is>
       </c>
     </row>
@@ -10511,7 +10511,7 @@
       </c>
       <c r="S122" s="4" t="inlineStr">
         <is>
-          <t>2026-09-04T22:26:51Z</t>
+          <t>2026-09-05T22:09:18Z</t>
         </is>
       </c>
     </row>
@@ -10596,7 +10596,7 @@
       </c>
       <c r="S123" s="4" t="inlineStr">
         <is>
-          <t>2026-09-04T22:26:51Z</t>
+          <t>2026-09-05T22:09:18Z</t>
         </is>
       </c>
     </row>
@@ -10681,7 +10681,7 @@
       </c>
       <c r="S124" s="4" t="inlineStr">
         <is>
-          <t>2026-09-04T22:26:51Z</t>
+          <t>2026-09-05T22:09:18Z</t>
         </is>
       </c>
     </row>
@@ -10766,7 +10766,7 @@
       </c>
       <c r="S125" s="4" t="inlineStr">
         <is>
-          <t>2026-09-04T22:26:51Z</t>
+          <t>2026-09-05T22:09:18Z</t>
         </is>
       </c>
     </row>
@@ -10851,7 +10851,7 @@
       </c>
       <c r="S126" s="4" t="inlineStr">
         <is>
-          <t>2026-09-04T22:26:51Z</t>
+          <t>2026-09-05T22:09:18Z</t>
         </is>
       </c>
     </row>
@@ -10936,7 +10936,7 @@
       </c>
       <c r="S127" s="4" t="inlineStr">
         <is>
-          <t>2026-09-04T22:26:51Z</t>
+          <t>2026-09-05T22:09:18Z</t>
         </is>
       </c>
     </row>
@@ -11021,7 +11021,7 @@
       </c>
       <c r="S128" s="4" t="inlineStr">
         <is>
-          <t>2026-09-04T22:26:51Z</t>
+          <t>2026-09-05T22:09:18Z</t>
         </is>
       </c>
     </row>
@@ -11106,7 +11106,7 @@
       </c>
       <c r="S129" s="4" t="inlineStr">
         <is>
-          <t>2026-09-04T22:26:51Z</t>
+          <t>2026-09-05T22:09:18Z</t>
         </is>
       </c>
     </row>
@@ -11191,7 +11191,7 @@
       </c>
       <c r="S130" s="4" t="inlineStr">
         <is>
-          <t>2026-09-04T22:26:51Z</t>
+          <t>2026-09-05T22:09:18Z</t>
         </is>
       </c>
     </row>
@@ -11276,7 +11276,7 @@
       </c>
       <c r="S131" s="4" t="inlineStr">
         <is>
-          <t>2026-09-04T22:26:51Z</t>
+          <t>2026-09-05T22:09:18Z</t>
         </is>
       </c>
     </row>
@@ -11361,7 +11361,7 @@
       </c>
       <c r="S132" s="4" t="inlineStr">
         <is>
-          <t>2026-09-04T22:26:51Z</t>
+          <t>2026-09-05T22:09:18Z</t>
         </is>
       </c>
     </row>
@@ -11446,7 +11446,7 @@
       </c>
       <c r="S133" s="4" t="inlineStr">
         <is>
-          <t>2026-09-04T22:26:51Z</t>
+          <t>2026-09-05T22:09:18Z</t>
         </is>
       </c>
     </row>
@@ -11531,7 +11531,7 @@
       </c>
       <c r="S134" s="4" t="inlineStr">
         <is>
-          <t>2026-09-04T22:26:51Z</t>
+          <t>2026-09-05T22:09:18Z</t>
         </is>
       </c>
     </row>
@@ -11616,7 +11616,7 @@
       </c>
       <c r="S135" s="4" t="inlineStr">
         <is>
-          <t>2026-09-04T22:26:51Z</t>
+          <t>2026-09-05T22:09:18Z</t>
         </is>
       </c>
     </row>
@@ -11701,7 +11701,7 @@
       </c>
       <c r="S136" s="4" t="inlineStr">
         <is>
-          <t>2026-09-04T22:26:51Z</t>
+          <t>2026-09-05T22:09:18Z</t>
         </is>
       </c>
     </row>
@@ -11786,7 +11786,7 @@
       </c>
       <c r="S137" s="4" t="inlineStr">
         <is>
-          <t>2026-09-04T22:26:51Z</t>
+          <t>2026-09-05T22:09:18Z</t>
         </is>
       </c>
     </row>
@@ -11871,7 +11871,7 @@
       </c>
       <c r="S138" s="4" t="inlineStr">
         <is>
-          <t>2026-09-04T22:26:51Z</t>
+          <t>2026-09-05T22:09:18Z</t>
         </is>
       </c>
     </row>
@@ -11956,7 +11956,7 @@
       </c>
       <c r="S139" s="4" t="inlineStr">
         <is>
-          <t>2026-09-04T22:26:51Z</t>
+          <t>2026-09-05T22:09:18Z</t>
         </is>
       </c>
     </row>
@@ -12041,7 +12041,7 @@
       </c>
       <c r="S140" s="4" t="inlineStr">
         <is>
-          <t>2026-09-04T22:26:51Z</t>
+          <t>2026-09-05T22:09:18Z</t>
         </is>
       </c>
     </row>
@@ -12126,7 +12126,7 @@
       </c>
       <c r="S141" s="4" t="inlineStr">
         <is>
-          <t>2026-09-04T22:26:51Z</t>
+          <t>2026-09-05T22:09:18Z</t>
         </is>
       </c>
     </row>
@@ -12258,7 +12258,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>2026-09-04T22:26:51Z</t>
+          <t>2026-09-05T22:09:18Z</t>
         </is>
       </c>
     </row>
@@ -12338,7 +12338,7 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>{"dataset_id": "bcv_pib_historico_anual", "title": "Producto interno bruto histórico anual", "table": "PIB histórico anual", "source_file": "7_1_14_anual.xls", "base": "1957/1968/1984/1997", "price_type": "Precios constantes", "measure": "Nivel", "frequency": "Anual", "period": "2017", "year": 2017, "quarter": null, "classification": "Total economía", "component": "Producto interno bruto", "value": 392393.12, "unit": "Millones de bolívares a precios constantes", "status": "", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/7_1_14_anual.xls", "fetched_at": "2026-09-04T22:26:51Z"}</t>
+          <t>{"dataset_id": "bcv_pib_historico_anual", "title": "Producto interno bruto histórico anual", "table": "PIB histórico anual", "source_file": "7_1_14_anual.xls", "base": "1957/1968/1984/1997", "price_type": "Precios constantes", "measure": "Nivel", "frequency": "Anual", "period": "2017", "year": 2017, "quarter": null, "classification": "Total economía", "component": "Producto interno bruto", "value": 392393.12, "unit": "Millones de bolívares a precios constantes", "status": "", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/7_1_14_anual.xls", "fetched_at": "2026-09-05T22:09:18Z"}</t>
         </is>
       </c>
     </row>

--- a/assets/data/bcv/excel/ove_bcv_pib_historico_anual.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_pib_historico_anual.xlsx
@@ -736,7 +736,7 @@
       </c>
       <c r="S7" s="4" t="inlineStr">
         <is>
-          <t>2026-09-05T22:09:18Z</t>
+          <t>2026-09-06T22:12:31Z</t>
         </is>
       </c>
     </row>
@@ -821,7 +821,7 @@
       </c>
       <c r="S8" s="4" t="inlineStr">
         <is>
-          <t>2026-09-05T22:09:18Z</t>
+          <t>2026-09-06T22:12:31Z</t>
         </is>
       </c>
     </row>
@@ -906,7 +906,7 @@
       </c>
       <c r="S9" s="4" t="inlineStr">
         <is>
-          <t>2026-09-05T22:09:18Z</t>
+          <t>2026-09-06T22:12:31Z</t>
         </is>
       </c>
     </row>
@@ -991,7 +991,7 @@
       </c>
       <c r="S10" s="4" t="inlineStr">
         <is>
-          <t>2026-09-05T22:09:18Z</t>
+          <t>2026-09-06T22:12:31Z</t>
         </is>
       </c>
     </row>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="S11" s="4" t="inlineStr">
         <is>
-          <t>2026-09-05T22:09:18Z</t>
+          <t>2026-09-06T22:12:31Z</t>
         </is>
       </c>
     </row>
@@ -1161,7 +1161,7 @@
       </c>
       <c r="S12" s="4" t="inlineStr">
         <is>
-          <t>2026-09-05T22:09:18Z</t>
+          <t>2026-09-06T22:12:31Z</t>
         </is>
       </c>
     </row>
@@ -1246,7 +1246,7 @@
       </c>
       <c r="S13" s="4" t="inlineStr">
         <is>
-          <t>2026-09-05T22:09:18Z</t>
+          <t>2026-09-06T22:12:31Z</t>
         </is>
       </c>
     </row>
@@ -1331,7 +1331,7 @@
       </c>
       <c r="S14" s="4" t="inlineStr">
         <is>
-          <t>2026-09-05T22:09:18Z</t>
+          <t>2026-09-06T22:12:31Z</t>
         </is>
       </c>
     </row>
@@ -1416,7 +1416,7 @@
       </c>
       <c r="S15" s="4" t="inlineStr">
         <is>
-          <t>2026-09-05T22:09:18Z</t>
+          <t>2026-09-06T22:12:31Z</t>
         </is>
       </c>
     </row>
@@ -1501,7 +1501,7 @@
       </c>
       <c r="S16" s="4" t="inlineStr">
         <is>
-          <t>2026-09-05T22:09:18Z</t>
+          <t>2026-09-06T22:12:31Z</t>
         </is>
       </c>
     </row>
@@ -1586,7 +1586,7 @@
       </c>
       <c r="S17" s="4" t="inlineStr">
         <is>
-          <t>2026-09-05T22:09:18Z</t>
+          <t>2026-09-06T22:12:31Z</t>
         </is>
       </c>
     </row>
@@ -1671,7 +1671,7 @@
       </c>
       <c r="S18" s="4" t="inlineStr">
         <is>
-          <t>2026-09-05T22:09:18Z</t>
+          <t>2026-09-06T22:12:31Z</t>
         </is>
       </c>
     </row>
@@ -1756,7 +1756,7 @@
       </c>
       <c r="S19" s="4" t="inlineStr">
         <is>
-          <t>2026-09-05T22:09:18Z</t>
+          <t>2026-09-06T22:12:31Z</t>
         </is>
       </c>
     </row>
@@ -1841,7 +1841,7 @@
       </c>
       <c r="S20" s="4" t="inlineStr">
         <is>
-          <t>2026-09-05T22:09:18Z</t>
+          <t>2026-09-06T22:12:31Z</t>
         </is>
       </c>
     </row>
@@ -1926,7 +1926,7 @@
       </c>
       <c r="S21" s="4" t="inlineStr">
         <is>
-          <t>2026-09-05T22:09:18Z</t>
+          <t>2026-09-06T22:12:31Z</t>
         </is>
       </c>
     </row>
@@ -2011,7 +2011,7 @@
       </c>
       <c r="S22" s="4" t="inlineStr">
         <is>
-          <t>2026-09-05T22:09:18Z</t>
+          <t>2026-09-06T22:12:31Z</t>
         </is>
       </c>
     </row>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="S23" s="4" t="inlineStr">
         <is>
-          <t>2026-09-05T22:09:18Z</t>
+          <t>2026-09-06T22:12:31Z</t>
         </is>
       </c>
     </row>
@@ -2181,7 +2181,7 @@
       </c>
       <c r="S24" s="4" t="inlineStr">
         <is>
-          <t>2026-09-05T22:09:18Z</t>
+          <t>2026-09-06T22:12:31Z</t>
         </is>
       </c>
     </row>
@@ -2266,7 +2266,7 @@
       </c>
       <c r="S25" s="4" t="inlineStr">
         <is>
-          <t>2026-09-05T22:09:18Z</t>
+          <t>2026-09-06T22:12:31Z</t>
         </is>
       </c>
     </row>
@@ -2351,7 +2351,7 @@
       </c>
       <c r="S26" s="4" t="inlineStr">
         <is>
-          <t>2026-09-05T22:09:18Z</t>
+          <t>2026-09-06T22:12:31Z</t>
         </is>
       </c>
     </row>
@@ -2436,7 +2436,7 @@
       </c>
       <c r="S27" s="4" t="inlineStr">
         <is>
-          <t>2026-09-05T22:09:18Z</t>
+          <t>2026-09-06T22:12:31Z</t>
         </is>
       </c>
     </row>
@@ -2521,7 +2521,7 @@
       </c>
       <c r="S28" s="4" t="inlineStr">
         <is>
-          <t>2026-09-05T22:09:18Z</t>
+          <t>2026-09-06T22:12:31Z</t>
         </is>
       </c>
     </row>
@@ -2606,7 +2606,7 @@
       </c>
       <c r="S29" s="4" t="inlineStr">
         <is>
-          <t>2026-09-05T22:09:18Z</t>
+          <t>2026-09-06T22:12:31Z</t>
         </is>
       </c>
     </row>
@@ -2691,7 +2691,7 @@
       </c>
       <c r="S30" s="4" t="inlineStr">
         <is>
-          <t>2026-09-05T22:09:18Z</t>
+          <t>2026-09-06T22:12:31Z</t>
         </is>
       </c>
     </row>
@@ -2776,7 +2776,7 @@
       </c>
       <c r="S31" s="4" t="inlineStr">
         <is>
-          <t>2026-09-05T22:09:18Z</t>
+          <t>2026-09-06T22:12:31Z</t>
         </is>
       </c>
     </row>
@@ -2861,7 +2861,7 @@
       </c>
       <c r="S32" s="4" t="inlineStr">
         <is>
-          <t>2026-09-05T22:09:18Z</t>
+          <t>2026-09-06T22:12:31Z</t>
         </is>
       </c>
     </row>
@@ -2946,7 +2946,7 @@
       </c>
       <c r="S33" s="4" t="inlineStr">
         <is>
-          <t>2026-09-05T22:09:18Z</t>
+          <t>2026-09-06T22:12:31Z</t>
         </is>
       </c>
     </row>
@@ -3031,7 +3031,7 @@
       </c>
       <c r="S34" s="4" t="inlineStr">
         <is>
-          <t>2026-09-05T22:09:18Z</t>
+          <t>2026-09-06T22:12:31Z</t>
         </is>
       </c>
     </row>
@@ -3116,7 +3116,7 @@
       </c>
       <c r="S35" s="4" t="inlineStr">
         <is>
-          <t>2026-09-05T22:09:18Z</t>
+          <t>2026-09-06T22:12:31Z</t>
         </is>
       </c>
     </row>
@@ -3201,7 +3201,7 @@
       </c>
       <c r="S36" s="4" t="inlineStr">
         <is>
-          <t>2026-09-05T22:09:18Z</t>
+          <t>2026-09-06T22:12:31Z</t>
         </is>
       </c>
     </row>
@@ -3286,7 +3286,7 @@
       </c>
       <c r="S37" s="4" t="inlineStr">
         <is>
-          <t>2026-09-05T22:09:18Z</t>
+          <t>2026-09-06T22:12:31Z</t>
         </is>
       </c>
     </row>
@@ -3371,7 +3371,7 @@
       </c>
       <c r="S38" s="4" t="inlineStr">
         <is>
-          <t>2026-09-05T22:09:18Z</t>
+          <t>2026-09-06T22:12:31Z</t>
         </is>
       </c>
     </row>
@@ -3456,7 +3456,7 @@
       </c>
       <c r="S39" s="4" t="inlineStr">
         <is>
-          <t>2026-09-05T22:09:18Z</t>
+          <t>2026-09-06T22:12:31Z</t>
         </is>
       </c>
     </row>
@@ -3541,7 +3541,7 @@
       </c>
       <c r="S40" s="4" t="inlineStr">
         <is>
-          <t>2026-09-05T22:09:18Z</t>
+          <t>2026-09-06T22:12:31Z</t>
         </is>
       </c>
     </row>
@@ -3626,7 +3626,7 @@
       </c>
       <c r="S41" s="4" t="inlineStr">
         <is>
-          <t>2026-09-05T22:09:18Z</t>
+          <t>2026-09-06T22:12:31Z</t>
         </is>
       </c>
     </row>
@@ -3711,7 +3711,7 @@
       </c>
       <c r="S42" s="4" t="inlineStr">
         <is>
-          <t>2026-09-05T22:09:18Z</t>
+          <t>2026-09-06T22:12:31Z</t>
         </is>
       </c>
     </row>
@@ -3796,7 +3796,7 @@
       </c>
       <c r="S43" s="4" t="inlineStr">
         <is>
-          <t>2026-09-05T22:09:18Z</t>
+          <t>2026-09-06T22:12:31Z</t>
         </is>
       </c>
     </row>
@@ -3881,7 +3881,7 @@
       </c>
       <c r="S44" s="4" t="inlineStr">
         <is>
-          <t>2026-09-05T22:09:18Z</t>
+          <t>2026-09-06T22:12:31Z</t>
         </is>
       </c>
     </row>
@@ -3966,7 +3966,7 @@
       </c>
       <c r="S45" s="4" t="inlineStr">
         <is>
-          <t>2026-09-05T22:09:18Z</t>
+          <t>2026-09-06T22:12:31Z</t>
         </is>
       </c>
     </row>
@@ -4051,7 +4051,7 @@
       </c>
       <c r="S46" s="4" t="inlineStr">
         <is>
-          <t>2026-09-05T22:09:18Z</t>
+          <t>2026-09-06T22:12:31Z</t>
         </is>
       </c>
     </row>
@@ -4136,7 +4136,7 @@
       </c>
       <c r="S47" s="4" t="inlineStr">
         <is>
-          <t>2026-09-05T22:09:18Z</t>
+          <t>2026-09-06T22:12:31Z</t>
         </is>
       </c>
     </row>
@@ -4221,7 +4221,7 @@
       </c>
       <c r="S48" s="4" t="inlineStr">
         <is>
-          <t>2026-09-05T22:09:18Z</t>
+          <t>2026-09-06T22:12:31Z</t>
         </is>
       </c>
     </row>
@@ -4306,7 +4306,7 @@
       </c>
       <c r="S49" s="4" t="inlineStr">
         <is>
-          <t>2026-09-05T22:09:18Z</t>
+          <t>2026-09-06T22:12:31Z</t>
         </is>
       </c>
     </row>
@@ -4391,7 +4391,7 @@
       </c>
       <c r="S50" s="4" t="inlineStr">
         <is>
-          <t>2026-09-05T22:09:18Z</t>
+          <t>2026-09-06T22:12:31Z</t>
         </is>
       </c>
     </row>
@@ -4476,7 +4476,7 @@
       </c>
       <c r="S51" s="4" t="inlineStr">
         <is>
-          <t>2026-09-05T22:09:18Z</t>
+          <t>2026-09-06T22:12:31Z</t>
         </is>
       </c>
     </row>
@@ -4561,7 +4561,7 @@
       </c>
       <c r="S52" s="4" t="inlineStr">
         <is>
-          <t>2026-09-05T22:09:18Z</t>
+          <t>2026-09-06T22:12:31Z</t>
         </is>
       </c>
     </row>
@@ -4646,7 +4646,7 @@
       </c>
       <c r="S53" s="4" t="inlineStr">
         <is>
-          <t>2026-09-05T22:09:18Z</t>
+          <t>2026-09-06T22:12:31Z</t>
         </is>
       </c>
     </row>
@@ -4731,7 +4731,7 @@
       </c>
       <c r="S54" s="4" t="inlineStr">
         <is>
-          <t>2026-09-05T22:09:18Z</t>
+          <t>2026-09-06T22:12:31Z</t>
         </is>
       </c>
     </row>
@@ -4816,7 +4816,7 @@
       </c>
       <c r="S55" s="4" t="inlineStr">
         <is>
-          <t>2026-09-05T22:09:18Z</t>
+          <t>2026-09-06T22:12:31Z</t>
         </is>
       </c>
     </row>
@@ -4901,7 +4901,7 @@
       </c>
       <c r="S56" s="4" t="inlineStr">
         <is>
-          <t>2026-09-05T22:09:18Z</t>
+          <t>2026-09-06T22:12:31Z</t>
         </is>
       </c>
     </row>
@@ -4986,7 +4986,7 @@
       </c>
       <c r="S57" s="4" t="inlineStr">
         <is>
-          <t>2026-09-05T22:09:18Z</t>
+          <t>2026-09-06T22:12:31Z</t>
         </is>
       </c>
     </row>
@@ -5071,7 +5071,7 @@
       </c>
       <c r="S58" s="4" t="inlineStr">
         <is>
-          <t>2026-09-05T22:09:18Z</t>
+          <t>2026-09-06T22:12:31Z</t>
         </is>
       </c>
     </row>
@@ -5156,7 +5156,7 @@
       </c>
       <c r="S59" s="4" t="inlineStr">
         <is>
-          <t>2026-09-05T22:09:18Z</t>
+          <t>2026-09-06T22:12:31Z</t>
         </is>
       </c>
     </row>
@@ -5241,7 +5241,7 @@
       </c>
       <c r="S60" s="4" t="inlineStr">
         <is>
-          <t>2026-09-05T22:09:18Z</t>
+          <t>2026-09-06T22:12:31Z</t>
         </is>
       </c>
     </row>
@@ -5326,7 +5326,7 @@
       </c>
       <c r="S61" s="4" t="inlineStr">
         <is>
-          <t>2026-09-05T22:09:18Z</t>
+          <t>2026-09-06T22:12:31Z</t>
         </is>
       </c>
     </row>
@@ -5411,7 +5411,7 @@
       </c>
       <c r="S62" s="4" t="inlineStr">
         <is>
-          <t>2026-09-05T22:09:18Z</t>
+          <t>2026-09-06T22:12:31Z</t>
         </is>
       </c>
     </row>
@@ -5496,7 +5496,7 @@
       </c>
       <c r="S63" s="4" t="inlineStr">
         <is>
-          <t>2026-09-05T22:09:18Z</t>
+          <t>2026-09-06T22:12:31Z</t>
         </is>
       </c>
     </row>
@@ -5581,7 +5581,7 @@
       </c>
       <c r="S64" s="4" t="inlineStr">
         <is>
-          <t>2026-09-05T22:09:18Z</t>
+          <t>2026-09-06T22:12:31Z</t>
         </is>
       </c>
     </row>
@@ -5666,7 +5666,7 @@
       </c>
       <c r="S65" s="4" t="inlineStr">
         <is>
-          <t>2026-09-05T22:09:18Z</t>
+          <t>2026-09-06T22:12:31Z</t>
         </is>
       </c>
     </row>
@@ -5751,7 +5751,7 @@
       </c>
       <c r="S66" s="4" t="inlineStr">
         <is>
-          <t>2026-09-05T22:09:18Z</t>
+          <t>2026-09-06T22:12:31Z</t>
         </is>
       </c>
     </row>
@@ -5836,7 +5836,7 @@
       </c>
       <c r="S67" s="4" t="inlineStr">
         <is>
-          <t>2026-09-05T22:09:18Z</t>
+          <t>2026-09-06T22:12:31Z</t>
         </is>
       </c>
     </row>
@@ -5921,7 +5921,7 @@
       </c>
       <c r="S68" s="4" t="inlineStr">
         <is>
-          <t>2026-09-05T22:09:18Z</t>
+          <t>2026-09-06T22:12:31Z</t>
         </is>
       </c>
     </row>
@@ -6006,7 +6006,7 @@
       </c>
       <c r="S69" s="4" t="inlineStr">
         <is>
-          <t>2026-09-05T22:09:18Z</t>
+          <t>2026-09-06T22:12:31Z</t>
         </is>
       </c>
     </row>
@@ -6091,7 +6091,7 @@
       </c>
       <c r="S70" s="4" t="inlineStr">
         <is>
-          <t>2026-09-05T22:09:18Z</t>
+          <t>2026-09-06T22:12:31Z</t>
         </is>
       </c>
     </row>
@@ -6176,7 +6176,7 @@
       </c>
       <c r="S71" s="4" t="inlineStr">
         <is>
-          <t>2026-09-05T22:09:18Z</t>
+          <t>2026-09-06T22:12:31Z</t>
         </is>
       </c>
     </row>
@@ -6261,7 +6261,7 @@
       </c>
       <c r="S72" s="4" t="inlineStr">
         <is>
-          <t>2026-09-05T22:09:18Z</t>
+          <t>2026-09-06T22:12:31Z</t>
         </is>
       </c>
     </row>
@@ -6346,7 +6346,7 @@
       </c>
       <c r="S73" s="4" t="inlineStr">
         <is>
-          <t>2026-09-05T22:09:18Z</t>
+          <t>2026-09-06T22:12:31Z</t>
         </is>
       </c>
     </row>
@@ -6431,7 +6431,7 @@
       </c>
       <c r="S74" s="4" t="inlineStr">
         <is>
-          <t>2026-09-05T22:09:18Z</t>
+          <t>2026-09-06T22:12:31Z</t>
         </is>
       </c>
     </row>
@@ -6516,7 +6516,7 @@
       </c>
       <c r="S75" s="4" t="inlineStr">
         <is>
-          <t>2026-09-05T22:09:18Z</t>
+          <t>2026-09-06T22:12:31Z</t>
         </is>
       </c>
     </row>
@@ -6601,7 +6601,7 @@
       </c>
       <c r="S76" s="4" t="inlineStr">
         <is>
-          <t>2026-09-05T22:09:18Z</t>
+          <t>2026-09-06T22:12:31Z</t>
         </is>
       </c>
     </row>
@@ -6686,7 +6686,7 @@
       </c>
       <c r="S77" s="4" t="inlineStr">
         <is>
-          <t>2026-09-05T22:09:18Z</t>
+          <t>2026-09-06T22:12:31Z</t>
         </is>
       </c>
     </row>
@@ -6771,7 +6771,7 @@
       </c>
       <c r="S78" s="4" t="inlineStr">
         <is>
-          <t>2026-09-05T22:09:18Z</t>
+          <t>2026-09-06T22:12:31Z</t>
         </is>
       </c>
     </row>
@@ -6856,7 +6856,7 @@
       </c>
       <c r="S79" s="4" t="inlineStr">
         <is>
-          <t>2026-09-05T22:09:18Z</t>
+          <t>2026-09-06T22:12:31Z</t>
         </is>
       </c>
     </row>
@@ -6941,7 +6941,7 @@
       </c>
       <c r="S80" s="4" t="inlineStr">
         <is>
-          <t>2026-09-05T22:09:18Z</t>
+          <t>2026-09-06T22:12:31Z</t>
         </is>
       </c>
     </row>
@@ -7026,7 +7026,7 @@
       </c>
       <c r="S81" s="4" t="inlineStr">
         <is>
-          <t>2026-09-05T22:09:18Z</t>
+          <t>2026-09-06T22:12:31Z</t>
         </is>
       </c>
     </row>
@@ -7111,7 +7111,7 @@
       </c>
       <c r="S82" s="4" t="inlineStr">
         <is>
-          <t>2026-09-05T22:09:18Z</t>
+          <t>2026-09-06T22:12:31Z</t>
         </is>
       </c>
     </row>
@@ -7196,7 +7196,7 @@
       </c>
       <c r="S83" s="4" t="inlineStr">
         <is>
-          <t>2026-09-05T22:09:18Z</t>
+          <t>2026-09-06T22:12:31Z</t>
         </is>
       </c>
     </row>
@@ -7281,7 +7281,7 @@
       </c>
       <c r="S84" s="4" t="inlineStr">
         <is>
-          <t>2026-09-05T22:09:18Z</t>
+          <t>2026-09-06T22:12:31Z</t>
         </is>
       </c>
     </row>
@@ -7366,7 +7366,7 @@
       </c>
       <c r="S85" s="4" t="inlineStr">
         <is>
-          <t>2026-09-05T22:09:18Z</t>
+          <t>2026-09-06T22:12:31Z</t>
         </is>
       </c>
     </row>
@@ -7451,7 +7451,7 @@
       </c>
       <c r="S86" s="4" t="inlineStr">
         <is>
-          <t>2026-09-05T22:09:18Z</t>
+          <t>2026-09-06T22:12:31Z</t>
         </is>
       </c>
     </row>
@@ -7536,7 +7536,7 @@
       </c>
       <c r="S87" s="4" t="inlineStr">
         <is>
-          <t>2026-09-05T22:09:18Z</t>
+          <t>2026-09-06T22:12:31Z</t>
         </is>
       </c>
     </row>
@@ -7621,7 +7621,7 @@
       </c>
       <c r="S88" s="4" t="inlineStr">
         <is>
-          <t>2026-09-05T22:09:18Z</t>
+          <t>2026-09-06T22:12:31Z</t>
         </is>
       </c>
     </row>
@@ -7706,7 +7706,7 @@
       </c>
       <c r="S89" s="4" t="inlineStr">
         <is>
-          <t>2026-09-05T22:09:18Z</t>
+          <t>2026-09-06T22:12:31Z</t>
         </is>
       </c>
     </row>
@@ -7791,7 +7791,7 @@
       </c>
       <c r="S90" s="4" t="inlineStr">
         <is>
-          <t>2026-09-05T22:09:18Z</t>
+          <t>2026-09-06T22:12:31Z</t>
         </is>
       </c>
     </row>
@@ -7876,7 +7876,7 @@
       </c>
       <c r="S91" s="4" t="inlineStr">
         <is>
-          <t>2026-09-05T22:09:18Z</t>
+          <t>2026-09-06T22:12:31Z</t>
         </is>
       </c>
     </row>
@@ -7961,7 +7961,7 @@
       </c>
       <c r="S92" s="4" t="inlineStr">
         <is>
-          <t>2026-09-05T22:09:18Z</t>
+          <t>2026-09-06T22:12:31Z</t>
         </is>
       </c>
     </row>
@@ -8046,7 +8046,7 @@
       </c>
       <c r="S93" s="4" t="inlineStr">
         <is>
-          <t>2026-09-05T22:09:18Z</t>
+          <t>2026-09-06T22:12:31Z</t>
         </is>
       </c>
     </row>
@@ -8131,7 +8131,7 @@
       </c>
       <c r="S94" s="4" t="inlineStr">
         <is>
-          <t>2026-09-05T22:09:18Z</t>
+          <t>2026-09-06T22:12:31Z</t>
         </is>
       </c>
     </row>
@@ -8216,7 +8216,7 @@
       </c>
       <c r="S95" s="4" t="inlineStr">
         <is>
-          <t>2026-09-05T22:09:18Z</t>
+          <t>2026-09-06T22:12:31Z</t>
         </is>
       </c>
     </row>
@@ -8301,7 +8301,7 @@
       </c>
       <c r="S96" s="4" t="inlineStr">
         <is>
-          <t>2026-09-05T22:09:18Z</t>
+          <t>2026-09-06T22:12:31Z</t>
         </is>
       </c>
     </row>
@@ -8386,7 +8386,7 @@
       </c>
       <c r="S97" s="4" t="inlineStr">
         <is>
-          <t>2026-09-05T22:09:18Z</t>
+          <t>2026-09-06T22:12:31Z</t>
         </is>
       </c>
     </row>
@@ -8471,7 +8471,7 @@
       </c>
       <c r="S98" s="4" t="inlineStr">
         <is>
-          <t>2026-09-05T22:09:18Z</t>
+          <t>2026-09-06T22:12:31Z</t>
         </is>
       </c>
     </row>
@@ -8556,7 +8556,7 @@
       </c>
       <c r="S99" s="4" t="inlineStr">
         <is>
-          <t>2026-09-05T22:09:18Z</t>
+          <t>2026-09-06T22:12:31Z</t>
         </is>
       </c>
     </row>
@@ -8641,7 +8641,7 @@
       </c>
       <c r="S100" s="4" t="inlineStr">
         <is>
-          <t>2026-09-05T22:09:18Z</t>
+          <t>2026-09-06T22:12:31Z</t>
         </is>
       </c>
     </row>
@@ -8726,7 +8726,7 @@
       </c>
       <c r="S101" s="4" t="inlineStr">
         <is>
-          <t>2026-09-05T22:09:18Z</t>
+          <t>2026-09-06T22:12:31Z</t>
         </is>
       </c>
     </row>
@@ -8811,7 +8811,7 @@
       </c>
       <c r="S102" s="4" t="inlineStr">
         <is>
-          <t>2026-09-05T22:09:18Z</t>
+          <t>2026-09-06T22:12:31Z</t>
         </is>
       </c>
     </row>
@@ -8896,7 +8896,7 @@
       </c>
       <c r="S103" s="4" t="inlineStr">
         <is>
-          <t>2026-09-05T22:09:18Z</t>
+          <t>2026-09-06T22:12:31Z</t>
         </is>
       </c>
     </row>
@@ -8981,7 +8981,7 @@
       </c>
       <c r="S104" s="4" t="inlineStr">
         <is>
-          <t>2026-09-05T22:09:18Z</t>
+          <t>2026-09-06T22:12:31Z</t>
         </is>
       </c>
     </row>
@@ -9066,7 +9066,7 @@
       </c>
       <c r="S105" s="4" t="inlineStr">
         <is>
-          <t>2026-09-05T22:09:18Z</t>
+          <t>2026-09-06T22:12:31Z</t>
         </is>
       </c>
     </row>
@@ -9151,7 +9151,7 @@
       </c>
       <c r="S106" s="4" t="inlineStr">
         <is>
-          <t>2026-09-05T22:09:18Z</t>
+          <t>2026-09-06T22:12:31Z</t>
         </is>
       </c>
     </row>
@@ -9236,7 +9236,7 @@
       </c>
       <c r="S107" s="4" t="inlineStr">
         <is>
-          <t>2026-09-05T22:09:18Z</t>
+          <t>2026-09-06T22:12:31Z</t>
         </is>
       </c>
     </row>
@@ -9321,7 +9321,7 @@
       </c>
       <c r="S108" s="4" t="inlineStr">
         <is>
-          <t>2026-09-05T22:09:18Z</t>
+          <t>2026-09-06T22:12:31Z</t>
         </is>
       </c>
     </row>
@@ -9406,7 +9406,7 @@
       </c>
       <c r="S109" s="4" t="inlineStr">
         <is>
-          <t>2026-09-05T22:09:18Z</t>
+          <t>2026-09-06T22:12:31Z</t>
         </is>
       </c>
     </row>
@@ -9491,7 +9491,7 @@
       </c>
       <c r="S110" s="4" t="inlineStr">
         <is>
-          <t>2026-09-05T22:09:18Z</t>
+          <t>2026-09-06T22:12:31Z</t>
         </is>
       </c>
     </row>
@@ -9576,7 +9576,7 @@
       </c>
       <c r="S111" s="4" t="inlineStr">
         <is>
-          <t>2026-09-05T22:09:18Z</t>
+          <t>2026-09-06T22:12:31Z</t>
         </is>
       </c>
     </row>
@@ -9661,7 +9661,7 @@
       </c>
       <c r="S112" s="4" t="inlineStr">
         <is>
-          <t>2026-09-05T22:09:18Z</t>
+          <t>2026-09-06T22:12:31Z</t>
         </is>
       </c>
     </row>
@@ -9746,7 +9746,7 @@
       </c>
       <c r="S113" s="4" t="inlineStr">
         <is>
-          <t>2026-09-05T22:09:18Z</t>
+          <t>2026-09-06T22:12:31Z</t>
         </is>
       </c>
     </row>
@@ -9831,7 +9831,7 @@
       </c>
       <c r="S114" s="4" t="inlineStr">
         <is>
-          <t>2026-09-05T22:09:18Z</t>
+          <t>2026-09-06T22:12:31Z</t>
         </is>
       </c>
     </row>
@@ -9916,7 +9916,7 @@
       </c>
       <c r="S115" s="4" t="inlineStr">
         <is>
-          <t>2026-09-05T22:09:18Z</t>
+          <t>2026-09-06T22:12:31Z</t>
         </is>
       </c>
     </row>
@@ -10001,7 +10001,7 @@
       </c>
       <c r="S116" s="4" t="inlineStr">
         <is>
-          <t>2026-09-05T22:09:18Z</t>
+          <t>2026-09-06T22:12:31Z</t>
         </is>
       </c>
     </row>
@@ -10086,7 +10086,7 @@
       </c>
       <c r="S117" s="4" t="inlineStr">
         <is>
-          <t>2026-09-05T22:09:18Z</t>
+          <t>2026-09-06T22:12:31Z</t>
         </is>
       </c>
     </row>
@@ -10171,7 +10171,7 @@
       </c>
       <c r="S118" s="4" t="inlineStr">
         <is>
-          <t>2026-09-05T22:09:18Z</t>
+          <t>2026-09-06T22:12:31Z</t>
         </is>
       </c>
     </row>
@@ -10256,7 +10256,7 @@
       </c>
       <c r="S119" s="4" t="inlineStr">
         <is>
-          <t>2026-09-05T22:09:18Z</t>
+          <t>2026-09-06T22:12:31Z</t>
         </is>
       </c>
     </row>
@@ -10341,7 +10341,7 @@
       </c>
       <c r="S120" s="4" t="inlineStr">
         <is>
-          <t>2026-09-05T22:09:18Z</t>
+          <t>2026-09-06T22:12:31Z</t>
         </is>
       </c>
     </row>
@@ -10426,7 +10426,7 @@
       </c>
       <c r="S121" s="4" t="inlineStr">
         <is>
-          <t>2026-09-05T22:09:18Z</t>
+          <t>2026-09-06T22:12:31Z</t>
         </is>
       </c>
     </row>
@@ -10511,7 +10511,7 @@
       </c>
       <c r="S122" s="4" t="inlineStr">
         <is>
-          <t>2026-09-05T22:09:18Z</t>
+          <t>2026-09-06T22:12:31Z</t>
         </is>
       </c>
     </row>
@@ -10596,7 +10596,7 @@
       </c>
       <c r="S123" s="4" t="inlineStr">
         <is>
-          <t>2026-09-05T22:09:18Z</t>
+          <t>2026-09-06T22:12:31Z</t>
         </is>
       </c>
     </row>
@@ -10681,7 +10681,7 @@
       </c>
       <c r="S124" s="4" t="inlineStr">
         <is>
-          <t>2026-09-05T22:09:18Z</t>
+          <t>2026-09-06T22:12:31Z</t>
         </is>
       </c>
     </row>
@@ -10766,7 +10766,7 @@
       </c>
       <c r="S125" s="4" t="inlineStr">
         <is>
-          <t>2026-09-05T22:09:18Z</t>
+          <t>2026-09-06T22:12:31Z</t>
         </is>
       </c>
     </row>
@@ -10851,7 +10851,7 @@
       </c>
       <c r="S126" s="4" t="inlineStr">
         <is>
-          <t>2026-09-05T22:09:18Z</t>
+          <t>2026-09-06T22:12:31Z</t>
         </is>
       </c>
     </row>
@@ -10936,7 +10936,7 @@
       </c>
       <c r="S127" s="4" t="inlineStr">
         <is>
-          <t>2026-09-05T22:09:18Z</t>
+          <t>2026-09-06T22:12:31Z</t>
         </is>
       </c>
     </row>
@@ -11021,7 +11021,7 @@
       </c>
       <c r="S128" s="4" t="inlineStr">
         <is>
-          <t>2026-09-05T22:09:18Z</t>
+          <t>2026-09-06T22:12:31Z</t>
         </is>
       </c>
     </row>
@@ -11106,7 +11106,7 @@
       </c>
       <c r="S129" s="4" t="inlineStr">
         <is>
-          <t>2026-09-05T22:09:18Z</t>
+          <t>2026-09-06T22:12:31Z</t>
         </is>
       </c>
     </row>
@@ -11191,7 +11191,7 @@
       </c>
       <c r="S130" s="4" t="inlineStr">
         <is>
-          <t>2026-09-05T22:09:18Z</t>
+          <t>2026-09-06T22:12:31Z</t>
         </is>
       </c>
     </row>
@@ -11276,7 +11276,7 @@
       </c>
       <c r="S131" s="4" t="inlineStr">
         <is>
-          <t>2026-09-05T22:09:18Z</t>
+          <t>2026-09-06T22:12:31Z</t>
         </is>
       </c>
     </row>
@@ -11361,7 +11361,7 @@
       </c>
       <c r="S132" s="4" t="inlineStr">
         <is>
-          <t>2026-09-05T22:09:18Z</t>
+          <t>2026-09-06T22:12:31Z</t>
         </is>
       </c>
     </row>
@@ -11446,7 +11446,7 @@
       </c>
       <c r="S133" s="4" t="inlineStr">
         <is>
-          <t>2026-09-05T22:09:18Z</t>
+          <t>2026-09-06T22:12:31Z</t>
         </is>
       </c>
     </row>
@@ -11531,7 +11531,7 @@
       </c>
       <c r="S134" s="4" t="inlineStr">
         <is>
-          <t>2026-09-05T22:09:18Z</t>
+          <t>2026-09-06T22:12:31Z</t>
         </is>
       </c>
     </row>
@@ -11616,7 +11616,7 @@
       </c>
       <c r="S135" s="4" t="inlineStr">
         <is>
-          <t>2026-09-05T22:09:18Z</t>
+          <t>2026-09-06T22:12:31Z</t>
         </is>
       </c>
     </row>
@@ -11701,7 +11701,7 @@
       </c>
       <c r="S136" s="4" t="inlineStr">
         <is>
-          <t>2026-09-05T22:09:18Z</t>
+          <t>2026-09-06T22:12:31Z</t>
         </is>
       </c>
     </row>
@@ -11786,7 +11786,7 @@
       </c>
       <c r="S137" s="4" t="inlineStr">
         <is>
-          <t>2026-09-05T22:09:18Z</t>
+          <t>2026-09-06T22:12:31Z</t>
         </is>
       </c>
     </row>
@@ -11871,7 +11871,7 @@
       </c>
       <c r="S138" s="4" t="inlineStr">
         <is>
-          <t>2026-09-05T22:09:18Z</t>
+          <t>2026-09-06T22:12:31Z</t>
         </is>
       </c>
     </row>
@@ -11956,7 +11956,7 @@
       </c>
       <c r="S139" s="4" t="inlineStr">
         <is>
-          <t>2026-09-05T22:09:18Z</t>
+          <t>2026-09-06T22:12:31Z</t>
         </is>
       </c>
     </row>
@@ -12041,7 +12041,7 @@
       </c>
       <c r="S140" s="4" t="inlineStr">
         <is>
-          <t>2026-09-05T22:09:18Z</t>
+          <t>2026-09-06T22:12:31Z</t>
         </is>
       </c>
     </row>
@@ -12126,7 +12126,7 @@
       </c>
       <c r="S141" s="4" t="inlineStr">
         <is>
-          <t>2026-09-05T22:09:18Z</t>
+          <t>2026-09-06T22:12:31Z</t>
         </is>
       </c>
     </row>
@@ -12258,7 +12258,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>2026-09-05T22:09:18Z</t>
+          <t>2026-09-06T22:12:31Z</t>
         </is>
       </c>
     </row>
@@ -12338,7 +12338,7 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>{"dataset_id": "bcv_pib_historico_anual", "title": "Producto interno bruto histórico anual", "table": "PIB histórico anual", "source_file": "7_1_14_anual.xls", "base": "1957/1968/1984/1997", "price_type": "Precios constantes", "measure": "Nivel", "frequency": "Anual", "period": "2017", "year": 2017, "quarter": null, "classification": "Total economía", "component": "Producto interno bruto", "value": 392393.12, "unit": "Millones de bolívares a precios constantes", "status": "", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/7_1_14_anual.xls", "fetched_at": "2026-09-05T22:09:18Z"}</t>
+          <t>{"dataset_id": "bcv_pib_historico_anual", "title": "Producto interno bruto histórico anual", "table": "PIB histórico anual", "source_file": "7_1_14_anual.xls", "base": "1957/1968/1984/1997", "price_type": "Precios constantes", "measure": "Nivel", "frequency": "Anual", "period": "2017", "year": 2017, "quarter": null, "classification": "Total economía", "component": "Producto interno bruto", "value": 392393.12, "unit": "Millones de bolívares a precios constantes", "status": "", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/7_1_14_anual.xls", "fetched_at": "2026-09-06T22:12:31Z"}</t>
         </is>
       </c>
     </row>

--- a/assets/data/bcv/excel/ove_bcv_pib_historico_anual.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_pib_historico_anual.xlsx
@@ -736,7 +736,7 @@
       </c>
       <c r="S7" s="4" t="inlineStr">
         <is>
-          <t>2026-09-06T22:12:31Z</t>
+          <t>2026-09-07T18:15:18Z</t>
         </is>
       </c>
     </row>
@@ -821,7 +821,7 @@
       </c>
       <c r="S8" s="4" t="inlineStr">
         <is>
-          <t>2026-09-06T22:12:31Z</t>
+          <t>2026-09-07T18:15:18Z</t>
         </is>
       </c>
     </row>
@@ -906,7 +906,7 @@
       </c>
       <c r="S9" s="4" t="inlineStr">
         <is>
-          <t>2026-09-06T22:12:31Z</t>
+          <t>2026-09-07T18:15:18Z</t>
         </is>
       </c>
     </row>
@@ -991,7 +991,7 @@
       </c>
       <c r="S10" s="4" t="inlineStr">
         <is>
-          <t>2026-09-06T22:12:31Z</t>
+          <t>2026-09-07T18:15:18Z</t>
         </is>
       </c>
     </row>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="S11" s="4" t="inlineStr">
         <is>
-          <t>2026-09-06T22:12:31Z</t>
+          <t>2026-09-07T18:15:18Z</t>
         </is>
       </c>
     </row>
@@ -1161,7 +1161,7 @@
       </c>
       <c r="S12" s="4" t="inlineStr">
         <is>
-          <t>2026-09-06T22:12:31Z</t>
+          <t>2026-09-07T18:15:18Z</t>
         </is>
       </c>
     </row>
@@ -1246,7 +1246,7 @@
       </c>
       <c r="S13" s="4" t="inlineStr">
         <is>
-          <t>2026-09-06T22:12:31Z</t>
+          <t>2026-09-07T18:15:18Z</t>
         </is>
       </c>
     </row>
@@ -1331,7 +1331,7 @@
       </c>
       <c r="S14" s="4" t="inlineStr">
         <is>
-          <t>2026-09-06T22:12:31Z</t>
+          <t>2026-09-07T18:15:18Z</t>
         </is>
       </c>
     </row>
@@ -1416,7 +1416,7 @@
       </c>
       <c r="S15" s="4" t="inlineStr">
         <is>
-          <t>2026-09-06T22:12:31Z</t>
+          <t>2026-09-07T18:15:18Z</t>
         </is>
       </c>
     </row>
@@ -1501,7 +1501,7 @@
       </c>
       <c r="S16" s="4" t="inlineStr">
         <is>
-          <t>2026-09-06T22:12:31Z</t>
+          <t>2026-09-07T18:15:18Z</t>
         </is>
       </c>
     </row>
@@ -1586,7 +1586,7 @@
       </c>
       <c r="S17" s="4" t="inlineStr">
         <is>
-          <t>2026-09-06T22:12:31Z</t>
+          <t>2026-09-07T18:15:18Z</t>
         </is>
       </c>
     </row>
@@ -1671,7 +1671,7 @@
       </c>
       <c r="S18" s="4" t="inlineStr">
         <is>
-          <t>2026-09-06T22:12:31Z</t>
+          <t>2026-09-07T18:15:18Z</t>
         </is>
       </c>
     </row>
@@ -1756,7 +1756,7 @@
       </c>
       <c r="S19" s="4" t="inlineStr">
         <is>
-          <t>2026-09-06T22:12:31Z</t>
+          <t>2026-09-07T18:15:18Z</t>
         </is>
       </c>
     </row>
@@ -1841,7 +1841,7 @@
       </c>
       <c r="S20" s="4" t="inlineStr">
         <is>
-          <t>2026-09-06T22:12:31Z</t>
+          <t>2026-09-07T18:15:18Z</t>
         </is>
       </c>
     </row>
@@ -1926,7 +1926,7 @@
       </c>
       <c r="S21" s="4" t="inlineStr">
         <is>
-          <t>2026-09-06T22:12:31Z</t>
+          <t>2026-09-07T18:15:18Z</t>
         </is>
       </c>
     </row>
@@ -2011,7 +2011,7 @@
       </c>
       <c r="S22" s="4" t="inlineStr">
         <is>
-          <t>2026-09-06T22:12:31Z</t>
+          <t>2026-09-07T18:15:18Z</t>
         </is>
       </c>
     </row>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="S23" s="4" t="inlineStr">
         <is>
-          <t>2026-09-06T22:12:31Z</t>
+          <t>2026-09-07T18:15:18Z</t>
         </is>
       </c>
     </row>
@@ -2181,7 +2181,7 @@
       </c>
       <c r="S24" s="4" t="inlineStr">
         <is>
-          <t>2026-09-06T22:12:31Z</t>
+          <t>2026-09-07T18:15:18Z</t>
         </is>
       </c>
     </row>
@@ -2266,7 +2266,7 @@
       </c>
       <c r="S25" s="4" t="inlineStr">
         <is>
-          <t>2026-09-06T22:12:31Z</t>
+          <t>2026-09-07T18:15:18Z</t>
         </is>
       </c>
     </row>
@@ -2351,7 +2351,7 @@
       </c>
       <c r="S26" s="4" t="inlineStr">
         <is>
-          <t>2026-09-06T22:12:31Z</t>
+          <t>2026-09-07T18:15:18Z</t>
         </is>
       </c>
     </row>
@@ -2436,7 +2436,7 @@
       </c>
       <c r="S27" s="4" t="inlineStr">
         <is>
-          <t>2026-09-06T22:12:31Z</t>
+          <t>2026-09-07T18:15:18Z</t>
         </is>
       </c>
     </row>
@@ -2521,7 +2521,7 @@
       </c>
       <c r="S28" s="4" t="inlineStr">
         <is>
-          <t>2026-09-06T22:12:31Z</t>
+          <t>2026-09-07T18:15:18Z</t>
         </is>
       </c>
     </row>
@@ -2606,7 +2606,7 @@
       </c>
       <c r="S29" s="4" t="inlineStr">
         <is>
-          <t>2026-09-06T22:12:31Z</t>
+          <t>2026-09-07T18:15:18Z</t>
         </is>
       </c>
     </row>
@@ -2691,7 +2691,7 @@
       </c>
       <c r="S30" s="4" t="inlineStr">
         <is>
-          <t>2026-09-06T22:12:31Z</t>
+          <t>2026-09-07T18:15:18Z</t>
         </is>
       </c>
     </row>
@@ -2776,7 +2776,7 @@
       </c>
       <c r="S31" s="4" t="inlineStr">
         <is>
-          <t>2026-09-06T22:12:31Z</t>
+          <t>2026-09-07T18:15:18Z</t>
         </is>
       </c>
     </row>
@@ -2861,7 +2861,7 @@
       </c>
       <c r="S32" s="4" t="inlineStr">
         <is>
-          <t>2026-09-06T22:12:31Z</t>
+          <t>2026-09-07T18:15:18Z</t>
         </is>
       </c>
     </row>
@@ -2946,7 +2946,7 @@
       </c>
       <c r="S33" s="4" t="inlineStr">
         <is>
-          <t>2026-09-06T22:12:31Z</t>
+          <t>2026-09-07T18:15:18Z</t>
         </is>
       </c>
     </row>
@@ -3031,7 +3031,7 @@
       </c>
       <c r="S34" s="4" t="inlineStr">
         <is>
-          <t>2026-09-06T22:12:31Z</t>
+          <t>2026-09-07T18:15:18Z</t>
         </is>
       </c>
     </row>
@@ -3116,7 +3116,7 @@
       </c>
       <c r="S35" s="4" t="inlineStr">
         <is>
-          <t>2026-09-06T22:12:31Z</t>
+          <t>2026-09-07T18:15:18Z</t>
         </is>
       </c>
     </row>
@@ -3201,7 +3201,7 @@
       </c>
       <c r="S36" s="4" t="inlineStr">
         <is>
-          <t>2026-09-06T22:12:31Z</t>
+          <t>2026-09-07T18:15:18Z</t>
         </is>
       </c>
     </row>
@@ -3286,7 +3286,7 @@
       </c>
       <c r="S37" s="4" t="inlineStr">
         <is>
-          <t>2026-09-06T22:12:31Z</t>
+          <t>2026-09-07T18:15:18Z</t>
         </is>
       </c>
     </row>
@@ -3371,7 +3371,7 @@
       </c>
       <c r="S38" s="4" t="inlineStr">
         <is>
-          <t>2026-09-06T22:12:31Z</t>
+          <t>2026-09-07T18:15:18Z</t>
         </is>
       </c>
     </row>
@@ -3456,7 +3456,7 @@
       </c>
       <c r="S39" s="4" t="inlineStr">
         <is>
-          <t>2026-09-06T22:12:31Z</t>
+          <t>2026-09-07T18:15:18Z</t>
         </is>
       </c>
     </row>
@@ -3541,7 +3541,7 @@
       </c>
       <c r="S40" s="4" t="inlineStr">
         <is>
-          <t>2026-09-06T22:12:31Z</t>
+          <t>2026-09-07T18:15:18Z</t>
         </is>
       </c>
     </row>
@@ -3626,7 +3626,7 @@
       </c>
       <c r="S41" s="4" t="inlineStr">
         <is>
-          <t>2026-09-06T22:12:31Z</t>
+          <t>2026-09-07T18:15:18Z</t>
         </is>
       </c>
     </row>
@@ -3711,7 +3711,7 @@
       </c>
       <c r="S42" s="4" t="inlineStr">
         <is>
-          <t>2026-09-06T22:12:31Z</t>
+          <t>2026-09-07T18:15:18Z</t>
         </is>
       </c>
     </row>
@@ -3796,7 +3796,7 @@
       </c>
       <c r="S43" s="4" t="inlineStr">
         <is>
-          <t>2026-09-06T22:12:31Z</t>
+          <t>2026-09-07T18:15:18Z</t>
         </is>
       </c>
     </row>
@@ -3881,7 +3881,7 @@
       </c>
       <c r="S44" s="4" t="inlineStr">
         <is>
-          <t>2026-09-06T22:12:31Z</t>
+          <t>2026-09-07T18:15:18Z</t>
         </is>
       </c>
     </row>
@@ -3966,7 +3966,7 @@
       </c>
       <c r="S45" s="4" t="inlineStr">
         <is>
-          <t>2026-09-06T22:12:31Z</t>
+          <t>2026-09-07T18:15:18Z</t>
         </is>
       </c>
     </row>
@@ -4051,7 +4051,7 @@
       </c>
       <c r="S46" s="4" t="inlineStr">
         <is>
-          <t>2026-09-06T22:12:31Z</t>
+          <t>2026-09-07T18:15:18Z</t>
         </is>
       </c>
     </row>
@@ -4136,7 +4136,7 @@
       </c>
       <c r="S47" s="4" t="inlineStr">
         <is>
-          <t>2026-09-06T22:12:31Z</t>
+          <t>2026-09-07T18:15:18Z</t>
         </is>
       </c>
     </row>
@@ -4221,7 +4221,7 @@
       </c>
       <c r="S48" s="4" t="inlineStr">
         <is>
-          <t>2026-09-06T22:12:31Z</t>
+          <t>2026-09-07T18:15:18Z</t>
         </is>
       </c>
     </row>
@@ -4306,7 +4306,7 @@
       </c>
       <c r="S49" s="4" t="inlineStr">
         <is>
-          <t>2026-09-06T22:12:31Z</t>
+          <t>2026-09-07T18:15:18Z</t>
         </is>
       </c>
     </row>
@@ -4391,7 +4391,7 @@
       </c>
       <c r="S50" s="4" t="inlineStr">
         <is>
-          <t>2026-09-06T22:12:31Z</t>
+          <t>2026-09-07T18:15:18Z</t>
         </is>
       </c>
     </row>
@@ -4476,7 +4476,7 @@
       </c>
       <c r="S51" s="4" t="inlineStr">
         <is>
-          <t>2026-09-06T22:12:31Z</t>
+          <t>2026-09-07T18:15:18Z</t>
         </is>
       </c>
     </row>
@@ -4561,7 +4561,7 @@
       </c>
       <c r="S52" s="4" t="inlineStr">
         <is>
-          <t>2026-09-06T22:12:31Z</t>
+          <t>2026-09-07T18:15:18Z</t>
         </is>
       </c>
     </row>
@@ -4646,7 +4646,7 @@
       </c>
       <c r="S53" s="4" t="inlineStr">
         <is>
-          <t>2026-09-06T22:12:31Z</t>
+          <t>2026-09-07T18:15:18Z</t>
         </is>
       </c>
     </row>
@@ -4731,7 +4731,7 @@
       </c>
       <c r="S54" s="4" t="inlineStr">
         <is>
-          <t>2026-09-06T22:12:31Z</t>
+          <t>2026-09-07T18:15:18Z</t>
         </is>
       </c>
     </row>
@@ -4816,7 +4816,7 @@
       </c>
       <c r="S55" s="4" t="inlineStr">
         <is>
-          <t>2026-09-06T22:12:31Z</t>
+          <t>2026-09-07T18:15:18Z</t>
         </is>
       </c>
     </row>
@@ -4901,7 +4901,7 @@
       </c>
       <c r="S56" s="4" t="inlineStr">
         <is>
-          <t>2026-09-06T22:12:31Z</t>
+          <t>2026-09-07T18:15:18Z</t>
         </is>
       </c>
     </row>
@@ -4986,7 +4986,7 @@
       </c>
       <c r="S57" s="4" t="inlineStr">
         <is>
-          <t>2026-09-06T22:12:31Z</t>
+          <t>2026-09-07T18:15:18Z</t>
         </is>
       </c>
     </row>
@@ -5071,7 +5071,7 @@
       </c>
       <c r="S58" s="4" t="inlineStr">
         <is>
-          <t>2026-09-06T22:12:31Z</t>
+          <t>2026-09-07T18:15:18Z</t>
         </is>
       </c>
     </row>
@@ -5156,7 +5156,7 @@
       </c>
       <c r="S59" s="4" t="inlineStr">
         <is>
-          <t>2026-09-06T22:12:31Z</t>
+          <t>2026-09-07T18:15:18Z</t>
         </is>
       </c>
     </row>
@@ -5241,7 +5241,7 @@
       </c>
       <c r="S60" s="4" t="inlineStr">
         <is>
-          <t>2026-09-06T22:12:31Z</t>
+          <t>2026-09-07T18:15:18Z</t>
         </is>
       </c>
     </row>
@@ -5326,7 +5326,7 @@
       </c>
       <c r="S61" s="4" t="inlineStr">
         <is>
-          <t>2026-09-06T22:12:31Z</t>
+          <t>2026-09-07T18:15:18Z</t>
         </is>
       </c>
     </row>
@@ -5411,7 +5411,7 @@
       </c>
       <c r="S62" s="4" t="inlineStr">
         <is>
-          <t>2026-09-06T22:12:31Z</t>
+          <t>2026-09-07T18:15:18Z</t>
         </is>
       </c>
     </row>
@@ -5496,7 +5496,7 @@
       </c>
       <c r="S63" s="4" t="inlineStr">
         <is>
-          <t>2026-09-06T22:12:31Z</t>
+          <t>2026-09-07T18:15:18Z</t>
         </is>
       </c>
     </row>
@@ -5581,7 +5581,7 @@
       </c>
       <c r="S64" s="4" t="inlineStr">
         <is>
-          <t>2026-09-06T22:12:31Z</t>
+          <t>2026-09-07T18:15:18Z</t>
         </is>
       </c>
     </row>
@@ -5666,7 +5666,7 @@
       </c>
       <c r="S65" s="4" t="inlineStr">
         <is>
-          <t>2026-09-06T22:12:31Z</t>
+          <t>2026-09-07T18:15:18Z</t>
         </is>
       </c>
     </row>
@@ -5751,7 +5751,7 @@
       </c>
       <c r="S66" s="4" t="inlineStr">
         <is>
-          <t>2026-09-06T22:12:31Z</t>
+          <t>2026-09-07T18:15:18Z</t>
         </is>
       </c>
     </row>
@@ -5836,7 +5836,7 @@
       </c>
       <c r="S67" s="4" t="inlineStr">
         <is>
-          <t>2026-09-06T22:12:31Z</t>
+          <t>2026-09-07T18:15:18Z</t>
         </is>
       </c>
     </row>
@@ -5921,7 +5921,7 @@
       </c>
       <c r="S68" s="4" t="inlineStr">
         <is>
-          <t>2026-09-06T22:12:31Z</t>
+          <t>2026-09-07T18:15:18Z</t>
         </is>
       </c>
     </row>
@@ -6006,7 +6006,7 @@
       </c>
       <c r="S69" s="4" t="inlineStr">
         <is>
-          <t>2026-09-06T22:12:31Z</t>
+          <t>2026-09-07T18:15:18Z</t>
         </is>
       </c>
     </row>
@@ -6091,7 +6091,7 @@
       </c>
       <c r="S70" s="4" t="inlineStr">
         <is>
-          <t>2026-09-06T22:12:31Z</t>
+          <t>2026-09-07T18:15:18Z</t>
         </is>
       </c>
     </row>
@@ -6176,7 +6176,7 @@
       </c>
       <c r="S71" s="4" t="inlineStr">
         <is>
-          <t>2026-09-06T22:12:31Z</t>
+          <t>2026-09-07T18:15:18Z</t>
         </is>
       </c>
     </row>
@@ -6261,7 +6261,7 @@
       </c>
       <c r="S72" s="4" t="inlineStr">
         <is>
-          <t>2026-09-06T22:12:31Z</t>
+          <t>2026-09-07T18:15:18Z</t>
         </is>
       </c>
     </row>
@@ -6346,7 +6346,7 @@
       </c>
       <c r="S73" s="4" t="inlineStr">
         <is>
-          <t>2026-09-06T22:12:31Z</t>
+          <t>2026-09-07T18:15:18Z</t>
         </is>
       </c>
     </row>
@@ -6431,7 +6431,7 @@
       </c>
       <c r="S74" s="4" t="inlineStr">
         <is>
-          <t>2026-09-06T22:12:31Z</t>
+          <t>2026-09-07T18:15:18Z</t>
         </is>
       </c>
     </row>
@@ -6516,7 +6516,7 @@
       </c>
       <c r="S75" s="4" t="inlineStr">
         <is>
-          <t>2026-09-06T22:12:31Z</t>
+          <t>2026-09-07T18:15:18Z</t>
         </is>
       </c>
     </row>
@@ -6601,7 +6601,7 @@
       </c>
       <c r="S76" s="4" t="inlineStr">
         <is>
-          <t>2026-09-06T22:12:31Z</t>
+          <t>2026-09-07T18:15:18Z</t>
         </is>
       </c>
     </row>
@@ -6686,7 +6686,7 @@
       </c>
       <c r="S77" s="4" t="inlineStr">
         <is>
-          <t>2026-09-06T22:12:31Z</t>
+          <t>2026-09-07T18:15:18Z</t>
         </is>
       </c>
     </row>
@@ -6771,7 +6771,7 @@
       </c>
       <c r="S78" s="4" t="inlineStr">
         <is>
-          <t>2026-09-06T22:12:31Z</t>
+          <t>2026-09-07T18:15:18Z</t>
         </is>
       </c>
     </row>
@@ -6856,7 +6856,7 @@
       </c>
       <c r="S79" s="4" t="inlineStr">
         <is>
-          <t>2026-09-06T22:12:31Z</t>
+          <t>2026-09-07T18:15:18Z</t>
         </is>
       </c>
     </row>
@@ -6941,7 +6941,7 @@
       </c>
       <c r="S80" s="4" t="inlineStr">
         <is>
-          <t>2026-09-06T22:12:31Z</t>
+          <t>2026-09-07T18:15:18Z</t>
         </is>
       </c>
     </row>
@@ -7026,7 +7026,7 @@
       </c>
       <c r="S81" s="4" t="inlineStr">
         <is>
-          <t>2026-09-06T22:12:31Z</t>
+          <t>2026-09-07T18:15:18Z</t>
         </is>
       </c>
     </row>
@@ -7111,7 +7111,7 @@
       </c>
       <c r="S82" s="4" t="inlineStr">
         <is>
-          <t>2026-09-06T22:12:31Z</t>
+          <t>2026-09-07T18:15:18Z</t>
         </is>
       </c>
     </row>
@@ -7196,7 +7196,7 @@
       </c>
       <c r="S83" s="4" t="inlineStr">
         <is>
-          <t>2026-09-06T22:12:31Z</t>
+          <t>2026-09-07T18:15:18Z</t>
         </is>
       </c>
     </row>
@@ -7281,7 +7281,7 @@
       </c>
       <c r="S84" s="4" t="inlineStr">
         <is>
-          <t>2026-09-06T22:12:31Z</t>
+          <t>2026-09-07T18:15:18Z</t>
         </is>
       </c>
     </row>
@@ -7366,7 +7366,7 @@
       </c>
       <c r="S85" s="4" t="inlineStr">
         <is>
-          <t>2026-09-06T22:12:31Z</t>
+          <t>2026-09-07T18:15:18Z</t>
         </is>
       </c>
     </row>
@@ -7451,7 +7451,7 @@
       </c>
       <c r="S86" s="4" t="inlineStr">
         <is>
-          <t>2026-09-06T22:12:31Z</t>
+          <t>2026-09-07T18:15:18Z</t>
         </is>
       </c>
     </row>
@@ -7536,7 +7536,7 @@
       </c>
       <c r="S87" s="4" t="inlineStr">
         <is>
-          <t>2026-09-06T22:12:31Z</t>
+          <t>2026-09-07T18:15:18Z</t>
         </is>
       </c>
     </row>
@@ -7621,7 +7621,7 @@
       </c>
       <c r="S88" s="4" t="inlineStr">
         <is>
-          <t>2026-09-06T22:12:31Z</t>
+          <t>2026-09-07T18:15:18Z</t>
         </is>
       </c>
     </row>
@@ -7706,7 +7706,7 @@
       </c>
       <c r="S89" s="4" t="inlineStr">
         <is>
-          <t>2026-09-06T22:12:31Z</t>
+          <t>2026-09-07T18:15:18Z</t>
         </is>
       </c>
     </row>
@@ -7791,7 +7791,7 @@
       </c>
       <c r="S90" s="4" t="inlineStr">
         <is>
-          <t>2026-09-06T22:12:31Z</t>
+          <t>2026-09-07T18:15:18Z</t>
         </is>
       </c>
     </row>
@@ -7876,7 +7876,7 @@
       </c>
       <c r="S91" s="4" t="inlineStr">
         <is>
-          <t>2026-09-06T22:12:31Z</t>
+          <t>2026-09-07T18:15:18Z</t>
         </is>
       </c>
     </row>
@@ -7961,7 +7961,7 @@
       </c>
       <c r="S92" s="4" t="inlineStr">
         <is>
-          <t>2026-09-06T22:12:31Z</t>
+          <t>2026-09-07T18:15:18Z</t>
         </is>
       </c>
     </row>
@@ -8046,7 +8046,7 @@
       </c>
       <c r="S93" s="4" t="inlineStr">
         <is>
-          <t>2026-09-06T22:12:31Z</t>
+          <t>2026-09-07T18:15:18Z</t>
         </is>
       </c>
     </row>
@@ -8131,7 +8131,7 @@
       </c>
       <c r="S94" s="4" t="inlineStr">
         <is>
-          <t>2026-09-06T22:12:31Z</t>
+          <t>2026-09-07T18:15:18Z</t>
         </is>
       </c>
     </row>
@@ -8216,7 +8216,7 @@
       </c>
       <c r="S95" s="4" t="inlineStr">
         <is>
-          <t>2026-09-06T22:12:31Z</t>
+          <t>2026-09-07T18:15:18Z</t>
         </is>
       </c>
     </row>
@@ -8301,7 +8301,7 @@
       </c>
       <c r="S96" s="4" t="inlineStr">
         <is>
-          <t>2026-09-06T22:12:31Z</t>
+          <t>2026-09-07T18:15:18Z</t>
         </is>
       </c>
     </row>
@@ -8386,7 +8386,7 @@
       </c>
       <c r="S97" s="4" t="inlineStr">
         <is>
-          <t>2026-09-06T22:12:31Z</t>
+          <t>2026-09-07T18:15:18Z</t>
         </is>
       </c>
     </row>
@@ -8471,7 +8471,7 @@
       </c>
       <c r="S98" s="4" t="inlineStr">
         <is>
-          <t>2026-09-06T22:12:31Z</t>
+          <t>2026-09-07T18:15:18Z</t>
         </is>
       </c>
     </row>
@@ -8556,7 +8556,7 @@
       </c>
       <c r="S99" s="4" t="inlineStr">
         <is>
-          <t>2026-09-06T22:12:31Z</t>
+          <t>2026-09-07T18:15:18Z</t>
         </is>
       </c>
     </row>
@@ -8641,7 +8641,7 @@
       </c>
       <c r="S100" s="4" t="inlineStr">
         <is>
-          <t>2026-09-06T22:12:31Z</t>
+          <t>2026-09-07T18:15:18Z</t>
         </is>
       </c>
     </row>
@@ -8726,7 +8726,7 @@
       </c>
       <c r="S101" s="4" t="inlineStr">
         <is>
-          <t>2026-09-06T22:12:31Z</t>
+          <t>2026-09-07T18:15:18Z</t>
         </is>
       </c>
     </row>
@@ -8811,7 +8811,7 @@
       </c>
       <c r="S102" s="4" t="inlineStr">
         <is>
-          <t>2026-09-06T22:12:31Z</t>
+          <t>2026-09-07T18:15:18Z</t>
         </is>
       </c>
     </row>
@@ -8896,7 +8896,7 @@
       </c>
       <c r="S103" s="4" t="inlineStr">
         <is>
-          <t>2026-09-06T22:12:31Z</t>
+          <t>2026-09-07T18:15:18Z</t>
         </is>
       </c>
     </row>
@@ -8981,7 +8981,7 @@
       </c>
       <c r="S104" s="4" t="inlineStr">
         <is>
-          <t>2026-09-06T22:12:31Z</t>
+          <t>2026-09-07T18:15:18Z</t>
         </is>
       </c>
     </row>
@@ -9066,7 +9066,7 @@
       </c>
       <c r="S105" s="4" t="inlineStr">
         <is>
-          <t>2026-09-06T22:12:31Z</t>
+          <t>2026-09-07T18:15:18Z</t>
         </is>
       </c>
     </row>
@@ -9151,7 +9151,7 @@
       </c>
       <c r="S106" s="4" t="inlineStr">
         <is>
-          <t>2026-09-06T22:12:31Z</t>
+          <t>2026-09-07T18:15:18Z</t>
         </is>
       </c>
     </row>
@@ -9236,7 +9236,7 @@
       </c>
       <c r="S107" s="4" t="inlineStr">
         <is>
-          <t>2026-09-06T22:12:31Z</t>
+          <t>2026-09-07T18:15:18Z</t>
         </is>
       </c>
     </row>
@@ -9321,7 +9321,7 @@
       </c>
       <c r="S108" s="4" t="inlineStr">
         <is>
-          <t>2026-09-06T22:12:31Z</t>
+          <t>2026-09-07T18:15:18Z</t>
         </is>
       </c>
     </row>
@@ -9406,7 +9406,7 @@
       </c>
       <c r="S109" s="4" t="inlineStr">
         <is>
-          <t>2026-09-06T22:12:31Z</t>
+          <t>2026-09-07T18:15:18Z</t>
         </is>
       </c>
     </row>
@@ -9491,7 +9491,7 @@
       </c>
       <c r="S110" s="4" t="inlineStr">
         <is>
-          <t>2026-09-06T22:12:31Z</t>
+          <t>2026-09-07T18:15:18Z</t>
         </is>
       </c>
     </row>
@@ -9576,7 +9576,7 @@
       </c>
       <c r="S111" s="4" t="inlineStr">
         <is>
-          <t>2026-09-06T22:12:31Z</t>
+          <t>2026-09-07T18:15:18Z</t>
         </is>
       </c>
     </row>
@@ -9661,7 +9661,7 @@
       </c>
       <c r="S112" s="4" t="inlineStr">
         <is>
-          <t>2026-09-06T22:12:31Z</t>
+          <t>2026-09-07T18:15:18Z</t>
         </is>
       </c>
     </row>
@@ -9746,7 +9746,7 @@
       </c>
       <c r="S113" s="4" t="inlineStr">
         <is>
-          <t>2026-09-06T22:12:31Z</t>
+          <t>2026-09-07T18:15:18Z</t>
         </is>
       </c>
     </row>
@@ -9831,7 +9831,7 @@
       </c>
       <c r="S114" s="4" t="inlineStr">
         <is>
-          <t>2026-09-06T22:12:31Z</t>
+          <t>2026-09-07T18:15:18Z</t>
         </is>
       </c>
     </row>
@@ -9916,7 +9916,7 @@
       </c>
       <c r="S115" s="4" t="inlineStr">
         <is>
-          <t>2026-09-06T22:12:31Z</t>
+          <t>2026-09-07T18:15:18Z</t>
         </is>
       </c>
     </row>
@@ -10001,7 +10001,7 @@
       </c>
       <c r="S116" s="4" t="inlineStr">
         <is>
-          <t>2026-09-06T22:12:31Z</t>
+          <t>2026-09-07T18:15:18Z</t>
         </is>
       </c>
     </row>
@@ -10086,7 +10086,7 @@
       </c>
       <c r="S117" s="4" t="inlineStr">
         <is>
-          <t>2026-09-06T22:12:31Z</t>
+          <t>2026-09-07T18:15:18Z</t>
         </is>
       </c>
     </row>
@@ -10171,7 +10171,7 @@
       </c>
       <c r="S118" s="4" t="inlineStr">
         <is>
-          <t>2026-09-06T22:12:31Z</t>
+          <t>2026-09-07T18:15:18Z</t>
         </is>
       </c>
     </row>
@@ -10256,7 +10256,7 @@
       </c>
       <c r="S119" s="4" t="inlineStr">
         <is>
-          <t>2026-09-06T22:12:31Z</t>
+          <t>2026-09-07T18:15:18Z</t>
         </is>
       </c>
     </row>
@@ -10341,7 +10341,7 @@
       </c>
       <c r="S120" s="4" t="inlineStr">
         <is>
-          <t>2026-09-06T22:12:31Z</t>
+          <t>2026-09-07T18:15:18Z</t>
         </is>
       </c>
     </row>
@@ -10426,7 +10426,7 @@
       </c>
       <c r="S121" s="4" t="inlineStr">
         <is>
-          <t>2026-09-06T22:12:31Z</t>
+          <t>2026-09-07T18:15:18Z</t>
         </is>
       </c>
     </row>
@@ -10511,7 +10511,7 @@
       </c>
       <c r="S122" s="4" t="inlineStr">
         <is>
-          <t>2026-09-06T22:12:31Z</t>
+          <t>2026-09-07T18:15:18Z</t>
         </is>
       </c>
     </row>
@@ -10596,7 +10596,7 @@
       </c>
       <c r="S123" s="4" t="inlineStr">
         <is>
-          <t>2026-09-06T22:12:31Z</t>
+          <t>2026-09-07T18:15:18Z</t>
         </is>
       </c>
     </row>
@@ -10681,7 +10681,7 @@
       </c>
       <c r="S124" s="4" t="inlineStr">
         <is>
-          <t>2026-09-06T22:12:31Z</t>
+          <t>2026-09-07T18:15:18Z</t>
         </is>
       </c>
     </row>
@@ -10766,7 +10766,7 @@
       </c>
       <c r="S125" s="4" t="inlineStr">
         <is>
-          <t>2026-09-06T22:12:31Z</t>
+          <t>2026-09-07T18:15:18Z</t>
         </is>
       </c>
     </row>
@@ -10851,7 +10851,7 @@
       </c>
       <c r="S126" s="4" t="inlineStr">
         <is>
-          <t>2026-09-06T22:12:31Z</t>
+          <t>2026-09-07T18:15:18Z</t>
         </is>
       </c>
     </row>
@@ -10936,7 +10936,7 @@
       </c>
       <c r="S127" s="4" t="inlineStr">
         <is>
-          <t>2026-09-06T22:12:31Z</t>
+          <t>2026-09-07T18:15:18Z</t>
         </is>
       </c>
     </row>
@@ -11021,7 +11021,7 @@
       </c>
       <c r="S128" s="4" t="inlineStr">
         <is>
-          <t>2026-09-06T22:12:31Z</t>
+          <t>2026-09-07T18:15:18Z</t>
         </is>
       </c>
     </row>
@@ -11106,7 +11106,7 @@
       </c>
       <c r="S129" s="4" t="inlineStr">
         <is>
-          <t>2026-09-06T22:12:31Z</t>
+          <t>2026-09-07T18:15:18Z</t>
         </is>
       </c>
     </row>
@@ -11191,7 +11191,7 @@
       </c>
       <c r="S130" s="4" t="inlineStr">
         <is>
-          <t>2026-09-06T22:12:31Z</t>
+          <t>2026-09-07T18:15:18Z</t>
         </is>
       </c>
     </row>
@@ -11276,7 +11276,7 @@
       </c>
       <c r="S131" s="4" t="inlineStr">
         <is>
-          <t>2026-09-06T22:12:31Z</t>
+          <t>2026-09-07T18:15:18Z</t>
         </is>
       </c>
     </row>
@@ -11361,7 +11361,7 @@
       </c>
       <c r="S132" s="4" t="inlineStr">
         <is>
-          <t>2026-09-06T22:12:31Z</t>
+          <t>2026-09-07T18:15:18Z</t>
         </is>
       </c>
     </row>
@@ -11446,7 +11446,7 @@
       </c>
       <c r="S133" s="4" t="inlineStr">
         <is>
-          <t>2026-09-06T22:12:31Z</t>
+          <t>2026-09-07T18:15:18Z</t>
         </is>
       </c>
     </row>
@@ -11531,7 +11531,7 @@
       </c>
       <c r="S134" s="4" t="inlineStr">
         <is>
-          <t>2026-09-06T22:12:31Z</t>
+          <t>2026-09-07T18:15:18Z</t>
         </is>
       </c>
     </row>
@@ -11616,7 +11616,7 @@
       </c>
       <c r="S135" s="4" t="inlineStr">
         <is>
-          <t>2026-09-06T22:12:31Z</t>
+          <t>2026-09-07T18:15:18Z</t>
         </is>
       </c>
     </row>
@@ -11701,7 +11701,7 @@
       </c>
       <c r="S136" s="4" t="inlineStr">
         <is>
-          <t>2026-09-06T22:12:31Z</t>
+          <t>2026-09-07T18:15:18Z</t>
         </is>
       </c>
     </row>
@@ -11786,7 +11786,7 @@
       </c>
       <c r="S137" s="4" t="inlineStr">
         <is>
-          <t>2026-09-06T22:12:31Z</t>
+          <t>2026-09-07T18:15:18Z</t>
         </is>
       </c>
     </row>
@@ -11871,7 +11871,7 @@
       </c>
       <c r="S138" s="4" t="inlineStr">
         <is>
-          <t>2026-09-06T22:12:31Z</t>
+          <t>2026-09-07T18:15:18Z</t>
         </is>
       </c>
     </row>
@@ -11956,7 +11956,7 @@
       </c>
       <c r="S139" s="4" t="inlineStr">
         <is>
-          <t>2026-09-06T22:12:31Z</t>
+          <t>2026-09-07T18:15:18Z</t>
         </is>
       </c>
     </row>
@@ -12041,7 +12041,7 @@
       </c>
       <c r="S140" s="4" t="inlineStr">
         <is>
-          <t>2026-09-06T22:12:31Z</t>
+          <t>2026-09-07T18:15:18Z</t>
         </is>
       </c>
     </row>
@@ -12126,7 +12126,7 @@
       </c>
       <c r="S141" s="4" t="inlineStr">
         <is>
-          <t>2026-09-06T22:12:31Z</t>
+          <t>2026-09-07T18:15:18Z</t>
         </is>
       </c>
     </row>
@@ -12258,7 +12258,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>2026-09-06T22:12:31Z</t>
+          <t>2026-09-07T18:15:18Z</t>
         </is>
       </c>
     </row>
@@ -12338,7 +12338,7 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>{"dataset_id": "bcv_pib_historico_anual", "title": "Producto interno bruto histórico anual", "table": "PIB histórico anual", "source_file": "7_1_14_anual.xls", "base": "1957/1968/1984/1997", "price_type": "Precios constantes", "measure": "Nivel", "frequency": "Anual", "period": "2017", "year": 2017, "quarter": null, "classification": "Total economía", "component": "Producto interno bruto", "value": 392393.12, "unit": "Millones de bolívares a precios constantes", "status": "", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/7_1_14_anual.xls", "fetched_at": "2026-09-06T22:12:31Z"}</t>
+          <t>{"dataset_id": "bcv_pib_historico_anual", "title": "Producto interno bruto histórico anual", "table": "PIB histórico anual", "source_file": "7_1_14_anual.xls", "base": "1957/1968/1984/1997", "price_type": "Precios constantes", "measure": "Nivel", "frequency": "Anual", "period": "2017", "year": 2017, "quarter": null, "classification": "Total economía", "component": "Producto interno bruto", "value": 392393.12, "unit": "Millones de bolívares a precios constantes", "status": "", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/7_1_14_anual.xls", "fetched_at": "2026-09-07T18:15:18Z"}</t>
         </is>
       </c>
     </row>

--- a/assets/data/bcv/excel/ove_bcv_pib_historico_anual.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_pib_historico_anual.xlsx
@@ -736,7 +736,7 @@
       </c>
       <c r="S7" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07T18:15:18Z</t>
+          <t>2026-09-07T22:56:44Z</t>
         </is>
       </c>
     </row>
@@ -821,7 +821,7 @@
       </c>
       <c r="S8" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07T18:15:18Z</t>
+          <t>2026-09-07T22:56:44Z</t>
         </is>
       </c>
     </row>
@@ -906,7 +906,7 @@
       </c>
       <c r="S9" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07T18:15:18Z</t>
+          <t>2026-09-07T22:56:44Z</t>
         </is>
       </c>
     </row>
@@ -991,7 +991,7 @@
       </c>
       <c r="S10" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07T18:15:18Z</t>
+          <t>2026-09-07T22:56:44Z</t>
         </is>
       </c>
     </row>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="S11" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07T18:15:18Z</t>
+          <t>2026-09-07T22:56:44Z</t>
         </is>
       </c>
     </row>
@@ -1161,7 +1161,7 @@
       </c>
       <c r="S12" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07T18:15:18Z</t>
+          <t>2026-09-07T22:56:44Z</t>
         </is>
       </c>
     </row>
@@ -1246,7 +1246,7 @@
       </c>
       <c r="S13" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07T18:15:18Z</t>
+          <t>2026-09-07T22:56:44Z</t>
         </is>
       </c>
     </row>
@@ -1331,7 +1331,7 @@
       </c>
       <c r="S14" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07T18:15:18Z</t>
+          <t>2026-09-07T22:56:44Z</t>
         </is>
       </c>
     </row>
@@ -1416,7 +1416,7 @@
       </c>
       <c r="S15" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07T18:15:18Z</t>
+          <t>2026-09-07T22:56:44Z</t>
         </is>
       </c>
     </row>
@@ -1501,7 +1501,7 @@
       </c>
       <c r="S16" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07T18:15:18Z</t>
+          <t>2026-09-07T22:56:44Z</t>
         </is>
       </c>
     </row>
@@ -1586,7 +1586,7 @@
       </c>
       <c r="S17" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07T18:15:18Z</t>
+          <t>2026-09-07T22:56:44Z</t>
         </is>
       </c>
     </row>
@@ -1671,7 +1671,7 @@
       </c>
       <c r="S18" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07T18:15:18Z</t>
+          <t>2026-09-07T22:56:44Z</t>
         </is>
       </c>
     </row>
@@ -1756,7 +1756,7 @@
       </c>
       <c r="S19" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07T18:15:18Z</t>
+          <t>2026-09-07T22:56:44Z</t>
         </is>
       </c>
     </row>
@@ -1841,7 +1841,7 @@
       </c>
       <c r="S20" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07T18:15:18Z</t>
+          <t>2026-09-07T22:56:44Z</t>
         </is>
       </c>
     </row>
@@ -1926,7 +1926,7 @@
       </c>
       <c r="S21" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07T18:15:18Z</t>
+          <t>2026-09-07T22:56:44Z</t>
         </is>
       </c>
     </row>
@@ -2011,7 +2011,7 @@
       </c>
       <c r="S22" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07T18:15:18Z</t>
+          <t>2026-09-07T22:56:44Z</t>
         </is>
       </c>
     </row>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="S23" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07T18:15:18Z</t>
+          <t>2026-09-07T22:56:44Z</t>
         </is>
       </c>
     </row>
@@ -2181,7 +2181,7 @@
       </c>
       <c r="S24" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07T18:15:18Z</t>
+          <t>2026-09-07T22:56:44Z</t>
         </is>
       </c>
     </row>
@@ -2266,7 +2266,7 @@
       </c>
       <c r="S25" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07T18:15:18Z</t>
+          <t>2026-09-07T22:56:44Z</t>
         </is>
       </c>
     </row>
@@ -2351,7 +2351,7 @@
       </c>
       <c r="S26" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07T18:15:18Z</t>
+          <t>2026-09-07T22:56:44Z</t>
         </is>
       </c>
     </row>
@@ -2436,7 +2436,7 @@
       </c>
       <c r="S27" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07T18:15:18Z</t>
+          <t>2026-09-07T22:56:44Z</t>
         </is>
       </c>
     </row>
@@ -2521,7 +2521,7 @@
       </c>
       <c r="S28" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07T18:15:18Z</t>
+          <t>2026-09-07T22:56:44Z</t>
         </is>
       </c>
     </row>
@@ -2606,7 +2606,7 @@
       </c>
       <c r="S29" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07T18:15:18Z</t>
+          <t>2026-09-07T22:56:44Z</t>
         </is>
       </c>
     </row>
@@ -2691,7 +2691,7 @@
       </c>
       <c r="S30" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07T18:15:18Z</t>
+          <t>2026-09-07T22:56:44Z</t>
         </is>
       </c>
     </row>
@@ -2776,7 +2776,7 @@
       </c>
       <c r="S31" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07T18:15:18Z</t>
+          <t>2026-09-07T22:56:44Z</t>
         </is>
       </c>
     </row>
@@ -2861,7 +2861,7 @@
       </c>
       <c r="S32" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07T18:15:18Z</t>
+          <t>2026-09-07T22:56:44Z</t>
         </is>
       </c>
     </row>
@@ -2946,7 +2946,7 @@
       </c>
       <c r="S33" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07T18:15:18Z</t>
+          <t>2026-09-07T22:56:44Z</t>
         </is>
       </c>
     </row>
@@ -3031,7 +3031,7 @@
       </c>
       <c r="S34" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07T18:15:18Z</t>
+          <t>2026-09-07T22:56:44Z</t>
         </is>
       </c>
     </row>
@@ -3116,7 +3116,7 @@
       </c>
       <c r="S35" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07T18:15:18Z</t>
+          <t>2026-09-07T22:56:44Z</t>
         </is>
       </c>
     </row>
@@ -3201,7 +3201,7 @@
       </c>
       <c r="S36" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07T18:15:18Z</t>
+          <t>2026-09-07T22:56:44Z</t>
         </is>
       </c>
     </row>
@@ -3286,7 +3286,7 @@
       </c>
       <c r="S37" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07T18:15:18Z</t>
+          <t>2026-09-07T22:56:44Z</t>
         </is>
       </c>
     </row>
@@ -3371,7 +3371,7 @@
       </c>
       <c r="S38" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07T18:15:18Z</t>
+          <t>2026-09-07T22:56:44Z</t>
         </is>
       </c>
     </row>
@@ -3456,7 +3456,7 @@
       </c>
       <c r="S39" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07T18:15:18Z</t>
+          <t>2026-09-07T22:56:44Z</t>
         </is>
       </c>
     </row>
@@ -3541,7 +3541,7 @@
       </c>
       <c r="S40" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07T18:15:18Z</t>
+          <t>2026-09-07T22:56:44Z</t>
         </is>
       </c>
     </row>
@@ -3626,7 +3626,7 @@
       </c>
       <c r="S41" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07T18:15:18Z</t>
+          <t>2026-09-07T22:56:44Z</t>
         </is>
       </c>
     </row>
@@ -3711,7 +3711,7 @@
       </c>
       <c r="S42" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07T18:15:18Z</t>
+          <t>2026-09-07T22:56:44Z</t>
         </is>
       </c>
     </row>
@@ -3796,7 +3796,7 @@
       </c>
       <c r="S43" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07T18:15:18Z</t>
+          <t>2026-09-07T22:56:44Z</t>
         </is>
       </c>
     </row>
@@ -3881,7 +3881,7 @@
       </c>
       <c r="S44" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07T18:15:18Z</t>
+          <t>2026-09-07T22:56:44Z</t>
         </is>
       </c>
     </row>
@@ -3966,7 +3966,7 @@
       </c>
       <c r="S45" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07T18:15:18Z</t>
+          <t>2026-09-07T22:56:44Z</t>
         </is>
       </c>
     </row>
@@ -4051,7 +4051,7 @@
       </c>
       <c r="S46" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07T18:15:18Z</t>
+          <t>2026-09-07T22:56:44Z</t>
         </is>
       </c>
     </row>
@@ -4136,7 +4136,7 @@
       </c>
       <c r="S47" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07T18:15:18Z</t>
+          <t>2026-09-07T22:56:44Z</t>
         </is>
       </c>
     </row>
@@ -4221,7 +4221,7 @@
       </c>
       <c r="S48" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07T18:15:18Z</t>
+          <t>2026-09-07T22:56:44Z</t>
         </is>
       </c>
     </row>
@@ -4306,7 +4306,7 @@
       </c>
       <c r="S49" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07T18:15:18Z</t>
+          <t>2026-09-07T22:56:44Z</t>
         </is>
       </c>
     </row>
@@ -4391,7 +4391,7 @@
       </c>
       <c r="S50" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07T18:15:18Z</t>
+          <t>2026-09-07T22:56:44Z</t>
         </is>
       </c>
     </row>
@@ -4476,7 +4476,7 @@
       </c>
       <c r="S51" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07T18:15:18Z</t>
+          <t>2026-09-07T22:56:44Z</t>
         </is>
       </c>
     </row>
@@ -4561,7 +4561,7 @@
       </c>
       <c r="S52" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07T18:15:18Z</t>
+          <t>2026-09-07T22:56:44Z</t>
         </is>
       </c>
     </row>
@@ -4646,7 +4646,7 @@
       </c>
       <c r="S53" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07T18:15:18Z</t>
+          <t>2026-09-07T22:56:44Z</t>
         </is>
       </c>
     </row>
@@ -4731,7 +4731,7 @@
       </c>
       <c r="S54" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07T18:15:18Z</t>
+          <t>2026-09-07T22:56:44Z</t>
         </is>
       </c>
     </row>
@@ -4816,7 +4816,7 @@
       </c>
       <c r="S55" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07T18:15:18Z</t>
+          <t>2026-09-07T22:56:44Z</t>
         </is>
       </c>
     </row>
@@ -4901,7 +4901,7 @@
       </c>
       <c r="S56" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07T18:15:18Z</t>
+          <t>2026-09-07T22:56:44Z</t>
         </is>
       </c>
     </row>
@@ -4986,7 +4986,7 @@
       </c>
       <c r="S57" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07T18:15:18Z</t>
+          <t>2026-09-07T22:56:44Z</t>
         </is>
       </c>
     </row>
@@ -5071,7 +5071,7 @@
       </c>
       <c r="S58" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07T18:15:18Z</t>
+          <t>2026-09-07T22:56:44Z</t>
         </is>
       </c>
     </row>
@@ -5156,7 +5156,7 @@
       </c>
       <c r="S59" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07T18:15:18Z</t>
+          <t>2026-09-07T22:56:44Z</t>
         </is>
       </c>
     </row>
@@ -5241,7 +5241,7 @@
       </c>
       <c r="S60" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07T18:15:18Z</t>
+          <t>2026-09-07T22:56:44Z</t>
         </is>
       </c>
     </row>
@@ -5326,7 +5326,7 @@
       </c>
       <c r="S61" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07T18:15:18Z</t>
+          <t>2026-09-07T22:56:44Z</t>
         </is>
       </c>
     </row>
@@ -5411,7 +5411,7 @@
       </c>
       <c r="S62" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07T18:15:18Z</t>
+          <t>2026-09-07T22:56:44Z</t>
         </is>
       </c>
     </row>
@@ -5496,7 +5496,7 @@
       </c>
       <c r="S63" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07T18:15:18Z</t>
+          <t>2026-09-07T22:56:44Z</t>
         </is>
       </c>
     </row>
@@ -5581,7 +5581,7 @@
       </c>
       <c r="S64" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07T18:15:18Z</t>
+          <t>2026-09-07T22:56:44Z</t>
         </is>
       </c>
     </row>
@@ -5666,7 +5666,7 @@
       </c>
       <c r="S65" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07T18:15:18Z</t>
+          <t>2026-09-07T22:56:44Z</t>
         </is>
       </c>
     </row>
@@ -5751,7 +5751,7 @@
       </c>
       <c r="S66" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07T18:15:18Z</t>
+          <t>2026-09-07T22:56:44Z</t>
         </is>
       </c>
     </row>
@@ -5836,7 +5836,7 @@
       </c>
       <c r="S67" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07T18:15:18Z</t>
+          <t>2026-09-07T22:56:44Z</t>
         </is>
       </c>
     </row>
@@ -5921,7 +5921,7 @@
       </c>
       <c r="S68" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07T18:15:18Z</t>
+          <t>2026-09-07T22:56:44Z</t>
         </is>
       </c>
     </row>
@@ -6006,7 +6006,7 @@
       </c>
       <c r="S69" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07T18:15:18Z</t>
+          <t>2026-09-07T22:56:44Z</t>
         </is>
       </c>
     </row>
@@ -6091,7 +6091,7 @@
       </c>
       <c r="S70" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07T18:15:18Z</t>
+          <t>2026-09-07T22:56:44Z</t>
         </is>
       </c>
     </row>
@@ -6176,7 +6176,7 @@
       </c>
       <c r="S71" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07T18:15:18Z</t>
+          <t>2026-09-07T22:56:44Z</t>
         </is>
       </c>
     </row>
@@ -6261,7 +6261,7 @@
       </c>
       <c r="S72" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07T18:15:18Z</t>
+          <t>2026-09-07T22:56:44Z</t>
         </is>
       </c>
     </row>
@@ -6346,7 +6346,7 @@
       </c>
       <c r="S73" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07T18:15:18Z</t>
+          <t>2026-09-07T22:56:44Z</t>
         </is>
       </c>
     </row>
@@ -6431,7 +6431,7 @@
       </c>
       <c r="S74" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07T18:15:18Z</t>
+          <t>2026-09-07T22:56:44Z</t>
         </is>
       </c>
     </row>
@@ -6516,7 +6516,7 @@
       </c>
       <c r="S75" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07T18:15:18Z</t>
+          <t>2026-09-07T22:56:44Z</t>
         </is>
       </c>
     </row>
@@ -6601,7 +6601,7 @@
       </c>
       <c r="S76" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07T18:15:18Z</t>
+          <t>2026-09-07T22:56:44Z</t>
         </is>
       </c>
     </row>
@@ -6686,7 +6686,7 @@
       </c>
       <c r="S77" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07T18:15:18Z</t>
+          <t>2026-09-07T22:56:44Z</t>
         </is>
       </c>
     </row>
@@ -6771,7 +6771,7 @@
       </c>
       <c r="S78" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07T18:15:18Z</t>
+          <t>2026-09-07T22:56:44Z</t>
         </is>
       </c>
     </row>
@@ -6856,7 +6856,7 @@
       </c>
       <c r="S79" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07T18:15:18Z</t>
+          <t>2026-09-07T22:56:44Z</t>
         </is>
       </c>
     </row>
@@ -6941,7 +6941,7 @@
       </c>
       <c r="S80" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07T18:15:18Z</t>
+          <t>2026-09-07T22:56:44Z</t>
         </is>
       </c>
     </row>
@@ -7026,7 +7026,7 @@
       </c>
       <c r="S81" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07T18:15:18Z</t>
+          <t>2026-09-07T22:56:44Z</t>
         </is>
       </c>
     </row>
@@ -7111,7 +7111,7 @@
       </c>
       <c r="S82" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07T18:15:18Z</t>
+          <t>2026-09-07T22:56:44Z</t>
         </is>
       </c>
     </row>
@@ -7196,7 +7196,7 @@
       </c>
       <c r="S83" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07T18:15:18Z</t>
+          <t>2026-09-07T22:56:44Z</t>
         </is>
       </c>
     </row>
@@ -7281,7 +7281,7 @@
       </c>
       <c r="S84" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07T18:15:18Z</t>
+          <t>2026-09-07T22:56:44Z</t>
         </is>
       </c>
     </row>
@@ -7366,7 +7366,7 @@
       </c>
       <c r="S85" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07T18:15:18Z</t>
+          <t>2026-09-07T22:56:44Z</t>
         </is>
       </c>
     </row>
@@ -7451,7 +7451,7 @@
       </c>
       <c r="S86" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07T18:15:18Z</t>
+          <t>2026-09-07T22:56:44Z</t>
         </is>
       </c>
     </row>
@@ -7536,7 +7536,7 @@
       </c>
       <c r="S87" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07T18:15:18Z</t>
+          <t>2026-09-07T22:56:44Z</t>
         </is>
       </c>
     </row>
@@ -7621,7 +7621,7 @@
       </c>
       <c r="S88" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07T18:15:18Z</t>
+          <t>2026-09-07T22:56:44Z</t>
         </is>
       </c>
     </row>
@@ -7706,7 +7706,7 @@
       </c>
       <c r="S89" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07T18:15:18Z</t>
+          <t>2026-09-07T22:56:44Z</t>
         </is>
       </c>
     </row>
@@ -7791,7 +7791,7 @@
       </c>
       <c r="S90" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07T18:15:18Z</t>
+          <t>2026-09-07T22:56:44Z</t>
         </is>
       </c>
     </row>
@@ -7876,7 +7876,7 @@
       </c>
       <c r="S91" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07T18:15:18Z</t>
+          <t>2026-09-07T22:56:44Z</t>
         </is>
       </c>
     </row>
@@ -7961,7 +7961,7 @@
       </c>
       <c r="S92" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07T18:15:18Z</t>
+          <t>2026-09-07T22:56:44Z</t>
         </is>
       </c>
     </row>
@@ -8046,7 +8046,7 @@
       </c>
       <c r="S93" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07T18:15:18Z</t>
+          <t>2026-09-07T22:56:44Z</t>
         </is>
       </c>
     </row>
@@ -8131,7 +8131,7 @@
       </c>
       <c r="S94" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07T18:15:18Z</t>
+          <t>2026-09-07T22:56:44Z</t>
         </is>
       </c>
     </row>
@@ -8216,7 +8216,7 @@
       </c>
       <c r="S95" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07T18:15:18Z</t>
+          <t>2026-09-07T22:56:44Z</t>
         </is>
       </c>
     </row>
@@ -8301,7 +8301,7 @@
       </c>
       <c r="S96" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07T18:15:18Z</t>
+          <t>2026-09-07T22:56:44Z</t>
         </is>
       </c>
     </row>
@@ -8386,7 +8386,7 @@
       </c>
       <c r="S97" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07T18:15:18Z</t>
+          <t>2026-09-07T22:56:44Z</t>
         </is>
       </c>
     </row>
@@ -8471,7 +8471,7 @@
       </c>
       <c r="S98" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07T18:15:18Z</t>
+          <t>2026-09-07T22:56:44Z</t>
         </is>
       </c>
     </row>
@@ -8556,7 +8556,7 @@
       </c>
       <c r="S99" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07T18:15:18Z</t>
+          <t>2026-09-07T22:56:44Z</t>
         </is>
       </c>
     </row>
@@ -8641,7 +8641,7 @@
       </c>
       <c r="S100" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07T18:15:18Z</t>
+          <t>2026-09-07T22:56:44Z</t>
         </is>
       </c>
     </row>
@@ -8726,7 +8726,7 @@
       </c>
       <c r="S101" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07T18:15:18Z</t>
+          <t>2026-09-07T22:56:44Z</t>
         </is>
       </c>
     </row>
@@ -8811,7 +8811,7 @@
       </c>
       <c r="S102" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07T18:15:18Z</t>
+          <t>2026-09-07T22:56:44Z</t>
         </is>
       </c>
     </row>
@@ -8896,7 +8896,7 @@
       </c>
       <c r="S103" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07T18:15:18Z</t>
+          <t>2026-09-07T22:56:44Z</t>
         </is>
       </c>
     </row>
@@ -8981,7 +8981,7 @@
       </c>
       <c r="S104" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07T18:15:18Z</t>
+          <t>2026-09-07T22:56:44Z</t>
         </is>
       </c>
     </row>
@@ -9066,7 +9066,7 @@
       </c>
       <c r="S105" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07T18:15:18Z</t>
+          <t>2026-09-07T22:56:44Z</t>
         </is>
       </c>
     </row>
@@ -9151,7 +9151,7 @@
       </c>
       <c r="S106" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07T18:15:18Z</t>
+          <t>2026-09-07T22:56:44Z</t>
         </is>
       </c>
     </row>
@@ -9236,7 +9236,7 @@
       </c>
       <c r="S107" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07T18:15:18Z</t>
+          <t>2026-09-07T22:56:44Z</t>
         </is>
       </c>
     </row>
@@ -9321,7 +9321,7 @@
       </c>
       <c r="S108" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07T18:15:18Z</t>
+          <t>2026-09-07T22:56:44Z</t>
         </is>
       </c>
     </row>
@@ -9406,7 +9406,7 @@
       </c>
       <c r="S109" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07T18:15:18Z</t>
+          <t>2026-09-07T22:56:44Z</t>
         </is>
       </c>
     </row>
@@ -9491,7 +9491,7 @@
       </c>
       <c r="S110" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07T18:15:18Z</t>
+          <t>2026-09-07T22:56:44Z</t>
         </is>
       </c>
     </row>
@@ -9576,7 +9576,7 @@
       </c>
       <c r="S111" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07T18:15:18Z</t>
+          <t>2026-09-07T22:56:44Z</t>
         </is>
       </c>
     </row>
@@ -9661,7 +9661,7 @@
       </c>
       <c r="S112" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07T18:15:18Z</t>
+          <t>2026-09-07T22:56:44Z</t>
         </is>
       </c>
     </row>
@@ -9746,7 +9746,7 @@
       </c>
       <c r="S113" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07T18:15:18Z</t>
+          <t>2026-09-07T22:56:44Z</t>
         </is>
       </c>
     </row>
@@ -9831,7 +9831,7 @@
       </c>
       <c r="S114" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07T18:15:18Z</t>
+          <t>2026-09-07T22:56:44Z</t>
         </is>
       </c>
     </row>
@@ -9916,7 +9916,7 @@
       </c>
       <c r="S115" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07T18:15:18Z</t>
+          <t>2026-09-07T22:56:44Z</t>
         </is>
       </c>
     </row>
@@ -10001,7 +10001,7 @@
       </c>
       <c r="S116" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07T18:15:18Z</t>
+          <t>2026-09-07T22:56:44Z</t>
         </is>
       </c>
     </row>
@@ -10086,7 +10086,7 @@
       </c>
       <c r="S117" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07T18:15:18Z</t>
+          <t>2026-09-07T22:56:44Z</t>
         </is>
       </c>
     </row>
@@ -10171,7 +10171,7 @@
       </c>
       <c r="S118" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07T18:15:18Z</t>
+          <t>2026-09-07T22:56:44Z</t>
         </is>
       </c>
     </row>
@@ -10256,7 +10256,7 @@
       </c>
       <c r="S119" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07T18:15:18Z</t>
+          <t>2026-09-07T22:56:44Z</t>
         </is>
       </c>
     </row>
@@ -10341,7 +10341,7 @@
       </c>
       <c r="S120" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07T18:15:18Z</t>
+          <t>2026-09-07T22:56:44Z</t>
         </is>
       </c>
     </row>
@@ -10426,7 +10426,7 @@
       </c>
       <c r="S121" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07T18:15:18Z</t>
+          <t>2026-09-07T22:56:44Z</t>
         </is>
       </c>
     </row>
@@ -10511,7 +10511,7 @@
       </c>
       <c r="S122" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07T18:15:18Z</t>
+          <t>2026-09-07T22:56:44Z</t>
         </is>
       </c>
     </row>
@@ -10596,7 +10596,7 @@
       </c>
       <c r="S123" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07T18:15:18Z</t>
+          <t>2026-09-07T22:56:44Z</t>
         </is>
       </c>
     </row>
@@ -10681,7 +10681,7 @@
       </c>
       <c r="S124" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07T18:15:18Z</t>
+          <t>2026-09-07T22:56:44Z</t>
         </is>
       </c>
     </row>
@@ -10766,7 +10766,7 @@
       </c>
       <c r="S125" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07T18:15:18Z</t>
+          <t>2026-09-07T22:56:44Z</t>
         </is>
       </c>
     </row>
@@ -10851,7 +10851,7 @@
       </c>
       <c r="S126" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07T18:15:18Z</t>
+          <t>2026-09-07T22:56:44Z</t>
         </is>
       </c>
     </row>
@@ -10936,7 +10936,7 @@
       </c>
       <c r="S127" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07T18:15:18Z</t>
+          <t>2026-09-07T22:56:44Z</t>
         </is>
       </c>
     </row>
@@ -11021,7 +11021,7 @@
       </c>
       <c r="S128" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07T18:15:18Z</t>
+          <t>2026-09-07T22:56:44Z</t>
         </is>
       </c>
     </row>
@@ -11106,7 +11106,7 @@
       </c>
       <c r="S129" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07T18:15:18Z</t>
+          <t>2026-09-07T22:56:44Z</t>
         </is>
       </c>
     </row>
@@ -11191,7 +11191,7 @@
       </c>
       <c r="S130" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07T18:15:18Z</t>
+          <t>2026-09-07T22:56:44Z</t>
         </is>
       </c>
     </row>
@@ -11276,7 +11276,7 @@
       </c>
       <c r="S131" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07T18:15:18Z</t>
+          <t>2026-09-07T22:56:44Z</t>
         </is>
       </c>
     </row>
@@ -11361,7 +11361,7 @@
       </c>
       <c r="S132" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07T18:15:18Z</t>
+          <t>2026-09-07T22:56:44Z</t>
         </is>
       </c>
     </row>
@@ -11446,7 +11446,7 @@
       </c>
       <c r="S133" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07T18:15:18Z</t>
+          <t>2026-09-07T22:56:44Z</t>
         </is>
       </c>
     </row>
@@ -11531,7 +11531,7 @@
       </c>
       <c r="S134" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07T18:15:18Z</t>
+          <t>2026-09-07T22:56:44Z</t>
         </is>
       </c>
     </row>
@@ -11616,7 +11616,7 @@
       </c>
       <c r="S135" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07T18:15:18Z</t>
+          <t>2026-09-07T22:56:44Z</t>
         </is>
       </c>
     </row>
@@ -11701,7 +11701,7 @@
       </c>
       <c r="S136" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07T18:15:18Z</t>
+          <t>2026-09-07T22:56:44Z</t>
         </is>
       </c>
     </row>
@@ -11786,7 +11786,7 @@
       </c>
       <c r="S137" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07T18:15:18Z</t>
+          <t>2026-09-07T22:56:44Z</t>
         </is>
       </c>
     </row>
@@ -11871,7 +11871,7 @@
       </c>
       <c r="S138" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07T18:15:18Z</t>
+          <t>2026-09-07T22:56:44Z</t>
         </is>
       </c>
     </row>
@@ -11956,7 +11956,7 @@
       </c>
       <c r="S139" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07T18:15:18Z</t>
+          <t>2026-09-07T22:56:44Z</t>
         </is>
       </c>
     </row>
@@ -12041,7 +12041,7 @@
       </c>
       <c r="S140" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07T18:15:18Z</t>
+          <t>2026-09-07T22:56:44Z</t>
         </is>
       </c>
     </row>
@@ -12126,7 +12126,7 @@
       </c>
       <c r="S141" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07T18:15:18Z</t>
+          <t>2026-09-07T22:56:44Z</t>
         </is>
       </c>
     </row>
@@ -12258,7 +12258,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07T18:15:18Z</t>
+          <t>2026-09-07T22:56:44Z</t>
         </is>
       </c>
     </row>
@@ -12338,7 +12338,7 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>{"dataset_id": "bcv_pib_historico_anual", "title": "Producto interno bruto histórico anual", "table": "PIB histórico anual", "source_file": "7_1_14_anual.xls", "base": "1957/1968/1984/1997", "price_type": "Precios constantes", "measure": "Nivel", "frequency": "Anual", "period": "2017", "year": 2017, "quarter": null, "classification": "Total economía", "component": "Producto interno bruto", "value": 392393.12, "unit": "Millones de bolívares a precios constantes", "status": "", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/7_1_14_anual.xls", "fetched_at": "2026-09-07T18:15:18Z"}</t>
+          <t>{"dataset_id": "bcv_pib_historico_anual", "title": "Producto interno bruto histórico anual", "table": "PIB histórico anual", "source_file": "7_1_14_anual.xls", "base": "1957/1968/1984/1997", "price_type": "Precios constantes", "measure": "Nivel", "frequency": "Anual", "period": "2017", "year": 2017, "quarter": null, "classification": "Total economía", "component": "Producto interno bruto", "value": 392393.12, "unit": "Millones de bolívares a precios constantes", "status": "", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/7_1_14_anual.xls", "fetched_at": "2026-09-07T22:56:44Z"}</t>
         </is>
       </c>
     </row>

--- a/assets/data/bcv/excel/ove_bcv_pib_historico_anual.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_pib_historico_anual.xlsx
@@ -736,7 +736,7 @@
       </c>
       <c r="S7" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07T22:56:44Z</t>
+          <t>2026-09-08T22:51:30Z</t>
         </is>
       </c>
     </row>
@@ -821,7 +821,7 @@
       </c>
       <c r="S8" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07T22:56:44Z</t>
+          <t>2026-09-08T22:51:30Z</t>
         </is>
       </c>
     </row>
@@ -906,7 +906,7 @@
       </c>
       <c r="S9" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07T22:56:44Z</t>
+          <t>2026-09-08T22:51:30Z</t>
         </is>
       </c>
     </row>
@@ -991,7 +991,7 @@
       </c>
       <c r="S10" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07T22:56:44Z</t>
+          <t>2026-09-08T22:51:30Z</t>
         </is>
       </c>
     </row>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="S11" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07T22:56:44Z</t>
+          <t>2026-09-08T22:51:30Z</t>
         </is>
       </c>
     </row>
@@ -1161,7 +1161,7 @@
       </c>
       <c r="S12" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07T22:56:44Z</t>
+          <t>2026-09-08T22:51:30Z</t>
         </is>
       </c>
     </row>
@@ -1246,7 +1246,7 @@
       </c>
       <c r="S13" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07T22:56:44Z</t>
+          <t>2026-09-08T22:51:30Z</t>
         </is>
       </c>
     </row>
@@ -1331,7 +1331,7 @@
       </c>
       <c r="S14" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07T22:56:44Z</t>
+          <t>2026-09-08T22:51:30Z</t>
         </is>
       </c>
     </row>
@@ -1416,7 +1416,7 @@
       </c>
       <c r="S15" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07T22:56:44Z</t>
+          <t>2026-09-08T22:51:30Z</t>
         </is>
       </c>
     </row>
@@ -1501,7 +1501,7 @@
       </c>
       <c r="S16" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07T22:56:44Z</t>
+          <t>2026-09-08T22:51:30Z</t>
         </is>
       </c>
     </row>
@@ -1586,7 +1586,7 @@
       </c>
       <c r="S17" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07T22:56:44Z</t>
+          <t>2026-09-08T22:51:30Z</t>
         </is>
       </c>
     </row>
@@ -1671,7 +1671,7 @@
       </c>
       <c r="S18" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07T22:56:44Z</t>
+          <t>2026-09-08T22:51:30Z</t>
         </is>
       </c>
     </row>
@@ -1756,7 +1756,7 @@
       </c>
       <c r="S19" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07T22:56:44Z</t>
+          <t>2026-09-08T22:51:30Z</t>
         </is>
       </c>
     </row>
@@ -1841,7 +1841,7 @@
       </c>
       <c r="S20" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07T22:56:44Z</t>
+          <t>2026-09-08T22:51:30Z</t>
         </is>
       </c>
     </row>
@@ -1926,7 +1926,7 @@
       </c>
       <c r="S21" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07T22:56:44Z</t>
+          <t>2026-09-08T22:51:30Z</t>
         </is>
       </c>
     </row>
@@ -2011,7 +2011,7 @@
       </c>
       <c r="S22" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07T22:56:44Z</t>
+          <t>2026-09-08T22:51:30Z</t>
         </is>
       </c>
     </row>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="S23" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07T22:56:44Z</t>
+          <t>2026-09-08T22:51:30Z</t>
         </is>
       </c>
     </row>
@@ -2181,7 +2181,7 @@
       </c>
       <c r="S24" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07T22:56:44Z</t>
+          <t>2026-09-08T22:51:30Z</t>
         </is>
       </c>
     </row>
@@ -2266,7 +2266,7 @@
       </c>
       <c r="S25" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07T22:56:44Z</t>
+          <t>2026-09-08T22:51:30Z</t>
         </is>
       </c>
     </row>
@@ -2351,7 +2351,7 @@
       </c>
       <c r="S26" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07T22:56:44Z</t>
+          <t>2026-09-08T22:51:30Z</t>
         </is>
       </c>
     </row>
@@ -2436,7 +2436,7 @@
       </c>
       <c r="S27" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07T22:56:44Z</t>
+          <t>2026-09-08T22:51:30Z</t>
         </is>
       </c>
     </row>
@@ -2521,7 +2521,7 @@
       </c>
       <c r="S28" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07T22:56:44Z</t>
+          <t>2026-09-08T22:51:30Z</t>
         </is>
       </c>
     </row>
@@ -2606,7 +2606,7 @@
       </c>
       <c r="S29" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07T22:56:44Z</t>
+          <t>2026-09-08T22:51:30Z</t>
         </is>
       </c>
     </row>
@@ -2691,7 +2691,7 @@
       </c>
       <c r="S30" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07T22:56:44Z</t>
+          <t>2026-09-08T22:51:30Z</t>
         </is>
       </c>
     </row>
@@ -2776,7 +2776,7 @@
       </c>
       <c r="S31" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07T22:56:44Z</t>
+          <t>2026-09-08T22:51:30Z</t>
         </is>
       </c>
     </row>
@@ -2861,7 +2861,7 @@
       </c>
       <c r="S32" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07T22:56:44Z</t>
+          <t>2026-09-08T22:51:30Z</t>
         </is>
       </c>
     </row>
@@ -2946,7 +2946,7 @@
       </c>
       <c r="S33" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07T22:56:44Z</t>
+          <t>2026-09-08T22:51:30Z</t>
         </is>
       </c>
     </row>
@@ -3031,7 +3031,7 @@
       </c>
       <c r="S34" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07T22:56:44Z</t>
+          <t>2026-09-08T22:51:30Z</t>
         </is>
       </c>
     </row>
@@ -3116,7 +3116,7 @@
       </c>
       <c r="S35" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07T22:56:44Z</t>
+          <t>2026-09-08T22:51:30Z</t>
         </is>
       </c>
     </row>
@@ -3201,7 +3201,7 @@
       </c>
       <c r="S36" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07T22:56:44Z</t>
+          <t>2026-09-08T22:51:30Z</t>
         </is>
       </c>
     </row>
@@ -3286,7 +3286,7 @@
       </c>
       <c r="S37" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07T22:56:44Z</t>
+          <t>2026-09-08T22:51:30Z</t>
         </is>
       </c>
     </row>
@@ -3371,7 +3371,7 @@
       </c>
       <c r="S38" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07T22:56:44Z</t>
+          <t>2026-09-08T22:51:30Z</t>
         </is>
       </c>
     </row>
@@ -3456,7 +3456,7 @@
       </c>
       <c r="S39" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07T22:56:44Z</t>
+          <t>2026-09-08T22:51:30Z</t>
         </is>
       </c>
     </row>
@@ -3541,7 +3541,7 @@
       </c>
       <c r="S40" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07T22:56:44Z</t>
+          <t>2026-09-08T22:51:30Z</t>
         </is>
       </c>
     </row>
@@ -3626,7 +3626,7 @@
       </c>
       <c r="S41" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07T22:56:44Z</t>
+          <t>2026-09-08T22:51:30Z</t>
         </is>
       </c>
     </row>
@@ -3711,7 +3711,7 @@
       </c>
       <c r="S42" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07T22:56:44Z</t>
+          <t>2026-09-08T22:51:30Z</t>
         </is>
       </c>
     </row>
@@ -3796,7 +3796,7 @@
       </c>
       <c r="S43" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07T22:56:44Z</t>
+          <t>2026-09-08T22:51:30Z</t>
         </is>
       </c>
     </row>
@@ -3881,7 +3881,7 @@
       </c>
       <c r="S44" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07T22:56:44Z</t>
+          <t>2026-09-08T22:51:30Z</t>
         </is>
       </c>
     </row>
@@ -3966,7 +3966,7 @@
       </c>
       <c r="S45" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07T22:56:44Z</t>
+          <t>2026-09-08T22:51:30Z</t>
         </is>
       </c>
     </row>
@@ -4051,7 +4051,7 @@
       </c>
       <c r="S46" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07T22:56:44Z</t>
+          <t>2026-09-08T22:51:30Z</t>
         </is>
       </c>
     </row>
@@ -4136,7 +4136,7 @@
       </c>
       <c r="S47" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07T22:56:44Z</t>
+          <t>2026-09-08T22:51:30Z</t>
         </is>
       </c>
     </row>
@@ -4221,7 +4221,7 @@
       </c>
       <c r="S48" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07T22:56:44Z</t>
+          <t>2026-09-08T22:51:30Z</t>
         </is>
       </c>
     </row>
@@ -4306,7 +4306,7 @@
       </c>
       <c r="S49" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07T22:56:44Z</t>
+          <t>2026-09-08T22:51:30Z</t>
         </is>
       </c>
     </row>
@@ -4391,7 +4391,7 @@
       </c>
       <c r="S50" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07T22:56:44Z</t>
+          <t>2026-09-08T22:51:30Z</t>
         </is>
       </c>
     </row>
@@ -4476,7 +4476,7 @@
       </c>
       <c r="S51" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07T22:56:44Z</t>
+          <t>2026-09-08T22:51:30Z</t>
         </is>
       </c>
     </row>
@@ -4561,7 +4561,7 @@
       </c>
       <c r="S52" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07T22:56:44Z</t>
+          <t>2026-09-08T22:51:30Z</t>
         </is>
       </c>
     </row>
@@ -4646,7 +4646,7 @@
       </c>
       <c r="S53" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07T22:56:44Z</t>
+          <t>2026-09-08T22:51:30Z</t>
         </is>
       </c>
     </row>
@@ -4731,7 +4731,7 @@
       </c>
       <c r="S54" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07T22:56:44Z</t>
+          <t>2026-09-08T22:51:30Z</t>
         </is>
       </c>
     </row>
@@ -4816,7 +4816,7 @@
       </c>
       <c r="S55" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07T22:56:44Z</t>
+          <t>2026-09-08T22:51:30Z</t>
         </is>
       </c>
     </row>
@@ -4901,7 +4901,7 @@
       </c>
       <c r="S56" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07T22:56:44Z</t>
+          <t>2026-09-08T22:51:30Z</t>
         </is>
       </c>
     </row>
@@ -4986,7 +4986,7 @@
       </c>
       <c r="S57" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07T22:56:44Z</t>
+          <t>2026-09-08T22:51:30Z</t>
         </is>
       </c>
     </row>
@@ -5071,7 +5071,7 @@
       </c>
       <c r="S58" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07T22:56:44Z</t>
+          <t>2026-09-08T22:51:30Z</t>
         </is>
       </c>
     </row>
@@ -5156,7 +5156,7 @@
       </c>
       <c r="S59" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07T22:56:44Z</t>
+          <t>2026-09-08T22:51:30Z</t>
         </is>
       </c>
     </row>
@@ -5241,7 +5241,7 @@
       </c>
       <c r="S60" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07T22:56:44Z</t>
+          <t>2026-09-08T22:51:30Z</t>
         </is>
       </c>
     </row>
@@ -5326,7 +5326,7 @@
       </c>
       <c r="S61" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07T22:56:44Z</t>
+          <t>2026-09-08T22:51:30Z</t>
         </is>
       </c>
     </row>
@@ -5411,7 +5411,7 @@
       </c>
       <c r="S62" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07T22:56:44Z</t>
+          <t>2026-09-08T22:51:30Z</t>
         </is>
       </c>
     </row>
@@ -5496,7 +5496,7 @@
       </c>
       <c r="S63" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07T22:56:44Z</t>
+          <t>2026-09-08T22:51:30Z</t>
         </is>
       </c>
     </row>
@@ -5581,7 +5581,7 @@
       </c>
       <c r="S64" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07T22:56:44Z</t>
+          <t>2026-09-08T22:51:30Z</t>
         </is>
       </c>
     </row>
@@ -5666,7 +5666,7 @@
       </c>
       <c r="S65" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07T22:56:44Z</t>
+          <t>2026-09-08T22:51:30Z</t>
         </is>
       </c>
     </row>
@@ -5751,7 +5751,7 @@
       </c>
       <c r="S66" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07T22:56:44Z</t>
+          <t>2026-09-08T22:51:30Z</t>
         </is>
       </c>
     </row>
@@ -5836,7 +5836,7 @@
       </c>
       <c r="S67" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07T22:56:44Z</t>
+          <t>2026-09-08T22:51:30Z</t>
         </is>
       </c>
     </row>
@@ -5921,7 +5921,7 @@
       </c>
       <c r="S68" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07T22:56:44Z</t>
+          <t>2026-09-08T22:51:30Z</t>
         </is>
       </c>
     </row>
@@ -6006,7 +6006,7 @@
       </c>
       <c r="S69" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07T22:56:44Z</t>
+          <t>2026-09-08T22:51:30Z</t>
         </is>
       </c>
     </row>
@@ -6091,7 +6091,7 @@
       </c>
       <c r="S70" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07T22:56:44Z</t>
+          <t>2026-09-08T22:51:30Z</t>
         </is>
       </c>
     </row>
@@ -6176,7 +6176,7 @@
       </c>
       <c r="S71" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07T22:56:44Z</t>
+          <t>2026-09-08T22:51:30Z</t>
         </is>
       </c>
     </row>
@@ -6261,7 +6261,7 @@
       </c>
       <c r="S72" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07T22:56:44Z</t>
+          <t>2026-09-08T22:51:30Z</t>
         </is>
       </c>
     </row>
@@ -6346,7 +6346,7 @@
       </c>
       <c r="S73" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07T22:56:44Z</t>
+          <t>2026-09-08T22:51:30Z</t>
         </is>
       </c>
     </row>
@@ -6431,7 +6431,7 @@
       </c>
       <c r="S74" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07T22:56:44Z</t>
+          <t>2026-09-08T22:51:30Z</t>
         </is>
       </c>
     </row>
@@ -6516,7 +6516,7 @@
       </c>
       <c r="S75" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07T22:56:44Z</t>
+          <t>2026-09-08T22:51:30Z</t>
         </is>
       </c>
     </row>
@@ -6601,7 +6601,7 @@
       </c>
       <c r="S76" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07T22:56:44Z</t>
+          <t>2026-09-08T22:51:30Z</t>
         </is>
       </c>
     </row>
@@ -6686,7 +6686,7 @@
       </c>
       <c r="S77" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07T22:56:44Z</t>
+          <t>2026-09-08T22:51:30Z</t>
         </is>
       </c>
     </row>
@@ -6771,7 +6771,7 @@
       </c>
       <c r="S78" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07T22:56:44Z</t>
+          <t>2026-09-08T22:51:30Z</t>
         </is>
       </c>
     </row>
@@ -6856,7 +6856,7 @@
       </c>
       <c r="S79" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07T22:56:44Z</t>
+          <t>2026-09-08T22:51:30Z</t>
         </is>
       </c>
     </row>
@@ -6941,7 +6941,7 @@
       </c>
       <c r="S80" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07T22:56:44Z</t>
+          <t>2026-09-08T22:51:30Z</t>
         </is>
       </c>
     </row>
@@ -7026,7 +7026,7 @@
       </c>
       <c r="S81" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07T22:56:44Z</t>
+          <t>2026-09-08T22:51:30Z</t>
         </is>
       </c>
     </row>
@@ -7111,7 +7111,7 @@
       </c>
       <c r="S82" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07T22:56:44Z</t>
+          <t>2026-09-08T22:51:30Z</t>
         </is>
       </c>
     </row>
@@ -7196,7 +7196,7 @@
       </c>
       <c r="S83" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07T22:56:44Z</t>
+          <t>2026-09-08T22:51:30Z</t>
         </is>
       </c>
     </row>
@@ -7281,7 +7281,7 @@
       </c>
       <c r="S84" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07T22:56:44Z</t>
+          <t>2026-09-08T22:51:30Z</t>
         </is>
       </c>
     </row>
@@ -7366,7 +7366,7 @@
       </c>
       <c r="S85" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07T22:56:44Z</t>
+          <t>2026-09-08T22:51:30Z</t>
         </is>
       </c>
     </row>
@@ -7451,7 +7451,7 @@
       </c>
       <c r="S86" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07T22:56:44Z</t>
+          <t>2026-09-08T22:51:30Z</t>
         </is>
       </c>
     </row>
@@ -7536,7 +7536,7 @@
       </c>
       <c r="S87" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07T22:56:44Z</t>
+          <t>2026-09-08T22:51:30Z</t>
         </is>
       </c>
     </row>
@@ -7621,7 +7621,7 @@
       </c>
       <c r="S88" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07T22:56:44Z</t>
+          <t>2026-09-08T22:51:30Z</t>
         </is>
       </c>
     </row>
@@ -7706,7 +7706,7 @@
       </c>
       <c r="S89" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07T22:56:44Z</t>
+          <t>2026-09-08T22:51:30Z</t>
         </is>
       </c>
     </row>
@@ -7791,7 +7791,7 @@
       </c>
       <c r="S90" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07T22:56:44Z</t>
+          <t>2026-09-08T22:51:30Z</t>
         </is>
       </c>
     </row>
@@ -7876,7 +7876,7 @@
       </c>
       <c r="S91" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07T22:56:44Z</t>
+          <t>2026-09-08T22:51:30Z</t>
         </is>
       </c>
     </row>
@@ -7961,7 +7961,7 @@
       </c>
       <c r="S92" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07T22:56:44Z</t>
+          <t>2026-09-08T22:51:30Z</t>
         </is>
       </c>
     </row>
@@ -8046,7 +8046,7 @@
       </c>
       <c r="S93" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07T22:56:44Z</t>
+          <t>2026-09-08T22:51:30Z</t>
         </is>
       </c>
     </row>
@@ -8131,7 +8131,7 @@
       </c>
       <c r="S94" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07T22:56:44Z</t>
+          <t>2026-09-08T22:51:30Z</t>
         </is>
       </c>
     </row>
@@ -8216,7 +8216,7 @@
       </c>
       <c r="S95" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07T22:56:44Z</t>
+          <t>2026-09-08T22:51:30Z</t>
         </is>
       </c>
     </row>
@@ -8301,7 +8301,7 @@
       </c>
       <c r="S96" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07T22:56:44Z</t>
+          <t>2026-09-08T22:51:30Z</t>
         </is>
       </c>
     </row>
@@ -8386,7 +8386,7 @@
       </c>
       <c r="S97" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07T22:56:44Z</t>
+          <t>2026-09-08T22:51:30Z</t>
         </is>
       </c>
     </row>
@@ -8471,7 +8471,7 @@
       </c>
       <c r="S98" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07T22:56:44Z</t>
+          <t>2026-09-08T22:51:30Z</t>
         </is>
       </c>
     </row>
@@ -8556,7 +8556,7 @@
       </c>
       <c r="S99" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07T22:56:44Z</t>
+          <t>2026-09-08T22:51:30Z</t>
         </is>
       </c>
     </row>
@@ -8641,7 +8641,7 @@
       </c>
       <c r="S100" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07T22:56:44Z</t>
+          <t>2026-09-08T22:51:30Z</t>
         </is>
       </c>
     </row>
@@ -8726,7 +8726,7 @@
       </c>
       <c r="S101" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07T22:56:44Z</t>
+          <t>2026-09-08T22:51:30Z</t>
         </is>
       </c>
     </row>
@@ -8811,7 +8811,7 @@
       </c>
       <c r="S102" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07T22:56:44Z</t>
+          <t>2026-09-08T22:51:30Z</t>
         </is>
       </c>
     </row>
@@ -8896,7 +8896,7 @@
       </c>
       <c r="S103" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07T22:56:44Z</t>
+          <t>2026-09-08T22:51:30Z</t>
         </is>
       </c>
     </row>
@@ -8981,7 +8981,7 @@
       </c>
       <c r="S104" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07T22:56:44Z</t>
+          <t>2026-09-08T22:51:30Z</t>
         </is>
       </c>
     </row>
@@ -9066,7 +9066,7 @@
       </c>
       <c r="S105" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07T22:56:44Z</t>
+          <t>2026-09-08T22:51:30Z</t>
         </is>
       </c>
     </row>
@@ -9151,7 +9151,7 @@
       </c>
       <c r="S106" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07T22:56:44Z</t>
+          <t>2026-09-08T22:51:30Z</t>
         </is>
       </c>
     </row>
@@ -9236,7 +9236,7 @@
       </c>
       <c r="S107" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07T22:56:44Z</t>
+          <t>2026-09-08T22:51:30Z</t>
         </is>
       </c>
     </row>
@@ -9321,7 +9321,7 @@
       </c>
       <c r="S108" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07T22:56:44Z</t>
+          <t>2026-09-08T22:51:30Z</t>
         </is>
       </c>
     </row>
@@ -9406,7 +9406,7 @@
       </c>
       <c r="S109" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07T22:56:44Z</t>
+          <t>2026-09-08T22:51:30Z</t>
         </is>
       </c>
     </row>
@@ -9491,7 +9491,7 @@
       </c>
       <c r="S110" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07T22:56:44Z</t>
+          <t>2026-09-08T22:51:30Z</t>
         </is>
       </c>
     </row>
@@ -9576,7 +9576,7 @@
       </c>
       <c r="S111" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07T22:56:44Z</t>
+          <t>2026-09-08T22:51:30Z</t>
         </is>
       </c>
     </row>
@@ -9661,7 +9661,7 @@
       </c>
       <c r="S112" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07T22:56:44Z</t>
+          <t>2026-09-08T22:51:30Z</t>
         </is>
       </c>
     </row>
@@ -9746,7 +9746,7 @@
       </c>
       <c r="S113" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07T22:56:44Z</t>
+          <t>2026-09-08T22:51:30Z</t>
         </is>
       </c>
     </row>
@@ -9831,7 +9831,7 @@
       </c>
       <c r="S114" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07T22:56:44Z</t>
+          <t>2026-09-08T22:51:30Z</t>
         </is>
       </c>
     </row>
@@ -9916,7 +9916,7 @@
       </c>
       <c r="S115" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07T22:56:44Z</t>
+          <t>2026-09-08T22:51:30Z</t>
         </is>
       </c>
     </row>
@@ -10001,7 +10001,7 @@
       </c>
       <c r="S116" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07T22:56:44Z</t>
+          <t>2026-09-08T22:51:30Z</t>
         </is>
       </c>
     </row>
@@ -10086,7 +10086,7 @@
       </c>
       <c r="S117" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07T22:56:44Z</t>
+          <t>2026-09-08T22:51:30Z</t>
         </is>
       </c>
     </row>
@@ -10171,7 +10171,7 @@
       </c>
       <c r="S118" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07T22:56:44Z</t>
+          <t>2026-09-08T22:51:30Z</t>
         </is>
       </c>
     </row>
@@ -10256,7 +10256,7 @@
       </c>
       <c r="S119" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07T22:56:44Z</t>
+          <t>2026-09-08T22:51:30Z</t>
         </is>
       </c>
     </row>
@@ -10341,7 +10341,7 @@
       </c>
       <c r="S120" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07T22:56:44Z</t>
+          <t>2026-09-08T22:51:30Z</t>
         </is>
       </c>
     </row>
@@ -10426,7 +10426,7 @@
       </c>
       <c r="S121" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07T22:56:44Z</t>
+          <t>2026-09-08T22:51:30Z</t>
         </is>
       </c>
     </row>
@@ -10511,7 +10511,7 @@
       </c>
       <c r="S122" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07T22:56:44Z</t>
+          <t>2026-09-08T22:51:30Z</t>
         </is>
       </c>
     </row>
@@ -10596,7 +10596,7 @@
       </c>
       <c r="S123" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07T22:56:44Z</t>
+          <t>2026-09-08T22:51:30Z</t>
         </is>
       </c>
     </row>
@@ -10681,7 +10681,7 @@
       </c>
       <c r="S124" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07T22:56:44Z</t>
+          <t>2026-09-08T22:51:30Z</t>
         </is>
       </c>
     </row>
@@ -10766,7 +10766,7 @@
       </c>
       <c r="S125" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07T22:56:44Z</t>
+          <t>2026-09-08T22:51:30Z</t>
         </is>
       </c>
     </row>
@@ -10851,7 +10851,7 @@
       </c>
       <c r="S126" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07T22:56:44Z</t>
+          <t>2026-09-08T22:51:30Z</t>
         </is>
       </c>
     </row>
@@ -10936,7 +10936,7 @@
       </c>
       <c r="S127" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07T22:56:44Z</t>
+          <t>2026-09-08T22:51:30Z</t>
         </is>
       </c>
     </row>
@@ -11021,7 +11021,7 @@
       </c>
       <c r="S128" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07T22:56:44Z</t>
+          <t>2026-09-08T22:51:30Z</t>
         </is>
       </c>
     </row>
@@ -11106,7 +11106,7 @@
       </c>
       <c r="S129" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07T22:56:44Z</t>
+          <t>2026-09-08T22:51:30Z</t>
         </is>
       </c>
     </row>
@@ -11191,7 +11191,7 @@
       </c>
       <c r="S130" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07T22:56:44Z</t>
+          <t>2026-09-08T22:51:30Z</t>
         </is>
       </c>
     </row>
@@ -11276,7 +11276,7 @@
       </c>
       <c r="S131" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07T22:56:44Z</t>
+          <t>2026-09-08T22:51:30Z</t>
         </is>
       </c>
     </row>
@@ -11361,7 +11361,7 @@
       </c>
       <c r="S132" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07T22:56:44Z</t>
+          <t>2026-09-08T22:51:30Z</t>
         </is>
       </c>
     </row>
@@ -11446,7 +11446,7 @@
       </c>
       <c r="S133" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07T22:56:44Z</t>
+          <t>2026-09-08T22:51:30Z</t>
         </is>
       </c>
     </row>
@@ -11531,7 +11531,7 @@
       </c>
       <c r="S134" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07T22:56:44Z</t>
+          <t>2026-09-08T22:51:30Z</t>
         </is>
       </c>
     </row>
@@ -11616,7 +11616,7 @@
       </c>
       <c r="S135" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07T22:56:44Z</t>
+          <t>2026-09-08T22:51:30Z</t>
         </is>
       </c>
     </row>
@@ -11701,7 +11701,7 @@
       </c>
       <c r="S136" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07T22:56:44Z</t>
+          <t>2026-09-08T22:51:30Z</t>
         </is>
       </c>
     </row>
@@ -11786,7 +11786,7 @@
       </c>
       <c r="S137" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07T22:56:44Z</t>
+          <t>2026-09-08T22:51:30Z</t>
         </is>
       </c>
     </row>
@@ -11871,7 +11871,7 @@
       </c>
       <c r="S138" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07T22:56:44Z</t>
+          <t>2026-09-08T22:51:30Z</t>
         </is>
       </c>
     </row>
@@ -11956,7 +11956,7 @@
       </c>
       <c r="S139" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07T22:56:44Z</t>
+          <t>2026-09-08T22:51:30Z</t>
         </is>
       </c>
     </row>
@@ -12041,7 +12041,7 @@
       </c>
       <c r="S140" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07T22:56:44Z</t>
+          <t>2026-09-08T22:51:30Z</t>
         </is>
       </c>
     </row>
@@ -12126,7 +12126,7 @@
       </c>
       <c r="S141" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07T22:56:44Z</t>
+          <t>2026-09-08T22:51:30Z</t>
         </is>
       </c>
     </row>
@@ -12258,7 +12258,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07T22:56:44Z</t>
+          <t>2026-09-08T22:51:30Z</t>
         </is>
       </c>
     </row>
@@ -12338,7 +12338,7 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>{"dataset_id": "bcv_pib_historico_anual", "title": "Producto interno bruto histórico anual", "table": "PIB histórico anual", "source_file": "7_1_14_anual.xls", "base": "1957/1968/1984/1997", "price_type": "Precios constantes", "measure": "Nivel", "frequency": "Anual", "period": "2017", "year": 2017, "quarter": null, "classification": "Total economía", "component": "Producto interno bruto", "value": 392393.12, "unit": "Millones de bolívares a precios constantes", "status": "", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/7_1_14_anual.xls", "fetched_at": "2026-09-07T22:56:44Z"}</t>
+          <t>{"dataset_id": "bcv_pib_historico_anual", "title": "Producto interno bruto histórico anual", "table": "PIB histórico anual", "source_file": "7_1_14_anual.xls", "base": "1957/1968/1984/1997", "price_type": "Precios constantes", "measure": "Nivel", "frequency": "Anual", "period": "2017", "year": 2017, "quarter": null, "classification": "Total economía", "component": "Producto interno bruto", "value": 392393.12, "unit": "Millones de bolívares a precios constantes", "status": "", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/7_1_14_anual.xls", "fetched_at": "2026-09-08T22:51:30Z"}</t>
         </is>
       </c>
     </row>

--- a/assets/data/bcv/excel/ove_bcv_pib_historico_anual.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_pib_historico_anual.xlsx
@@ -736,7 +736,7 @@
       </c>
       <c r="S7" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -821,7 +821,7 @@
       </c>
       <c r="S8" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -906,7 +906,7 @@
       </c>
       <c r="S9" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -991,7 +991,7 @@
       </c>
       <c r="S10" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="S11" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -1161,7 +1161,7 @@
       </c>
       <c r="S12" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -1246,7 +1246,7 @@
       </c>
       <c r="S13" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -1331,7 +1331,7 @@
       </c>
       <c r="S14" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -1416,7 +1416,7 @@
       </c>
       <c r="S15" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -1501,7 +1501,7 @@
       </c>
       <c r="S16" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -1586,7 +1586,7 @@
       </c>
       <c r="S17" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -1671,7 +1671,7 @@
       </c>
       <c r="S18" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -1756,7 +1756,7 @@
       </c>
       <c r="S19" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -1841,7 +1841,7 @@
       </c>
       <c r="S20" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -1926,7 +1926,7 @@
       </c>
       <c r="S21" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -2011,7 +2011,7 @@
       </c>
       <c r="S22" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="S23" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -2181,7 +2181,7 @@
       </c>
       <c r="S24" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -2266,7 +2266,7 @@
       </c>
       <c r="S25" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -2351,7 +2351,7 @@
       </c>
       <c r="S26" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -2436,7 +2436,7 @@
       </c>
       <c r="S27" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -2521,7 +2521,7 @@
       </c>
       <c r="S28" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -2606,7 +2606,7 @@
       </c>
       <c r="S29" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -2691,7 +2691,7 @@
       </c>
       <c r="S30" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -2776,7 +2776,7 @@
       </c>
       <c r="S31" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -2861,7 +2861,7 @@
       </c>
       <c r="S32" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -2946,7 +2946,7 @@
       </c>
       <c r="S33" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -3031,7 +3031,7 @@
       </c>
       <c r="S34" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -3116,7 +3116,7 @@
       </c>
       <c r="S35" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -3201,7 +3201,7 @@
       </c>
       <c r="S36" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -3286,7 +3286,7 @@
       </c>
       <c r="S37" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -3371,7 +3371,7 @@
       </c>
       <c r="S38" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -3456,7 +3456,7 @@
       </c>
       <c r="S39" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -3541,7 +3541,7 @@
       </c>
       <c r="S40" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -3626,7 +3626,7 @@
       </c>
       <c r="S41" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -3711,7 +3711,7 @@
       </c>
       <c r="S42" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -3796,7 +3796,7 @@
       </c>
       <c r="S43" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -3881,7 +3881,7 @@
       </c>
       <c r="S44" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -3966,7 +3966,7 @@
       </c>
       <c r="S45" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -4051,7 +4051,7 @@
       </c>
       <c r="S46" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -4136,7 +4136,7 @@
       </c>
       <c r="S47" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -4221,7 +4221,7 @@
       </c>
       <c r="S48" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -4306,7 +4306,7 @@
       </c>
       <c r="S49" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -4391,7 +4391,7 @@
       </c>
       <c r="S50" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -4476,7 +4476,7 @@
       </c>
       <c r="S51" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -4561,7 +4561,7 @@
       </c>
       <c r="S52" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -4646,7 +4646,7 @@
       </c>
       <c r="S53" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -4731,7 +4731,7 @@
       </c>
       <c r="S54" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -4816,7 +4816,7 @@
       </c>
       <c r="S55" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -4901,7 +4901,7 @@
       </c>
       <c r="S56" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -4986,7 +4986,7 @@
       </c>
       <c r="S57" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -5071,7 +5071,7 @@
       </c>
       <c r="S58" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -5156,7 +5156,7 @@
       </c>
       <c r="S59" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -5241,7 +5241,7 @@
       </c>
       <c r="S60" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -5326,7 +5326,7 @@
       </c>
       <c r="S61" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -5411,7 +5411,7 @@
       </c>
       <c r="S62" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -5496,7 +5496,7 @@
       </c>
       <c r="S63" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -5581,7 +5581,7 @@
       </c>
       <c r="S64" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -5666,7 +5666,7 @@
       </c>
       <c r="S65" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -5751,7 +5751,7 @@
       </c>
       <c r="S66" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -5836,7 +5836,7 @@
       </c>
       <c r="S67" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -5921,7 +5921,7 @@
       </c>
       <c r="S68" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -6006,7 +6006,7 @@
       </c>
       <c r="S69" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -6091,7 +6091,7 @@
       </c>
       <c r="S70" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -6176,7 +6176,7 @@
       </c>
       <c r="S71" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -6261,7 +6261,7 @@
       </c>
       <c r="S72" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -6346,7 +6346,7 @@
       </c>
       <c r="S73" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -6431,7 +6431,7 @@
       </c>
       <c r="S74" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -6516,7 +6516,7 @@
       </c>
       <c r="S75" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -6601,7 +6601,7 @@
       </c>
       <c r="S76" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -6686,7 +6686,7 @@
       </c>
       <c r="S77" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -6771,7 +6771,7 @@
       </c>
       <c r="S78" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -6856,7 +6856,7 @@
       </c>
       <c r="S79" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -6941,7 +6941,7 @@
       </c>
       <c r="S80" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -7026,7 +7026,7 @@
       </c>
       <c r="S81" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -7111,7 +7111,7 @@
       </c>
       <c r="S82" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -7196,7 +7196,7 @@
       </c>
       <c r="S83" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -7281,7 +7281,7 @@
       </c>
       <c r="S84" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -7366,7 +7366,7 @@
       </c>
       <c r="S85" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -7451,7 +7451,7 @@
       </c>
       <c r="S86" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -7536,7 +7536,7 @@
       </c>
       <c r="S87" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -7621,7 +7621,7 @@
       </c>
       <c r="S88" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -7706,7 +7706,7 @@
       </c>
       <c r="S89" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -7791,7 +7791,7 @@
       </c>
       <c r="S90" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -7876,7 +7876,7 @@
       </c>
       <c r="S91" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -7961,7 +7961,7 @@
       </c>
       <c r="S92" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -8046,7 +8046,7 @@
       </c>
       <c r="S93" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -8131,7 +8131,7 @@
       </c>
       <c r="S94" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -8216,7 +8216,7 @@
       </c>
       <c r="S95" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -8301,7 +8301,7 @@
       </c>
       <c r="S96" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -8386,7 +8386,7 @@
       </c>
       <c r="S97" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -8471,7 +8471,7 @@
       </c>
       <c r="S98" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -8556,7 +8556,7 @@
       </c>
       <c r="S99" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -8641,7 +8641,7 @@
       </c>
       <c r="S100" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -8726,7 +8726,7 @@
       </c>
       <c r="S101" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -8811,7 +8811,7 @@
       </c>
       <c r="S102" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -8896,7 +8896,7 @@
       </c>
       <c r="S103" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -8981,7 +8981,7 @@
       </c>
       <c r="S104" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -9066,7 +9066,7 @@
       </c>
       <c r="S105" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -9151,7 +9151,7 @@
       </c>
       <c r="S106" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -9236,7 +9236,7 @@
       </c>
       <c r="S107" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -9321,7 +9321,7 @@
       </c>
       <c r="S108" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -9406,7 +9406,7 @@
       </c>
       <c r="S109" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -9491,7 +9491,7 @@
       </c>
       <c r="S110" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -9576,7 +9576,7 @@
       </c>
       <c r="S111" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -9661,7 +9661,7 @@
       </c>
       <c r="S112" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -9746,7 +9746,7 @@
       </c>
       <c r="S113" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -9831,7 +9831,7 @@
       </c>
       <c r="S114" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -9916,7 +9916,7 @@
       </c>
       <c r="S115" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -10001,7 +10001,7 @@
       </c>
       <c r="S116" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -10086,7 +10086,7 @@
       </c>
       <c r="S117" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -10171,7 +10171,7 @@
       </c>
       <c r="S118" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -10256,7 +10256,7 @@
       </c>
       <c r="S119" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -10341,7 +10341,7 @@
       </c>
       <c r="S120" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -10426,7 +10426,7 @@
       </c>
       <c r="S121" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -10511,7 +10511,7 @@
       </c>
       <c r="S122" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -10596,7 +10596,7 @@
       </c>
       <c r="S123" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -10681,7 +10681,7 @@
       </c>
       <c r="S124" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -10766,7 +10766,7 @@
       </c>
       <c r="S125" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -10851,7 +10851,7 @@
       </c>
       <c r="S126" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -10936,7 +10936,7 @@
       </c>
       <c r="S127" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -11021,7 +11021,7 @@
       </c>
       <c r="S128" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -11106,7 +11106,7 @@
       </c>
       <c r="S129" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -11191,7 +11191,7 @@
       </c>
       <c r="S130" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -11276,7 +11276,7 @@
       </c>
       <c r="S131" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -11361,7 +11361,7 @@
       </c>
       <c r="S132" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -11446,7 +11446,7 @@
       </c>
       <c r="S133" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -11531,7 +11531,7 @@
       </c>
       <c r="S134" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -11616,7 +11616,7 @@
       </c>
       <c r="S135" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -11701,7 +11701,7 @@
       </c>
       <c r="S136" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -11786,7 +11786,7 @@
       </c>
       <c r="S137" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -11871,7 +11871,7 @@
       </c>
       <c r="S138" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -11956,7 +11956,7 @@
       </c>
       <c r="S139" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -12041,7 +12041,7 @@
       </c>
       <c r="S140" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -12126,7 +12126,7 @@
       </c>
       <c r="S141" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -12258,7 +12258,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -12338,7 +12338,7 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>{"dataset_id": "bcv_pib_historico_anual", "title": "Producto interno bruto histórico anual", "table": "PIB histórico anual", "source_file": "7_1_14_anual.xls", "base": "1957/1968/1984/1997", "price_type": "Precios constantes", "measure": "Nivel", "frequency": "Anual", "period": "2017", "year": 2017, "quarter": null, "classification": "Total economía", "component": "Producto interno bruto", "value": 392393.12, "unit": "Millones de bolívares a precios constantes", "status": "", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/7_1_14_anual.xls", "fetched_at": "2026-09-08T22:51:30Z"}</t>
+          <t>{"dataset_id": "bcv_pib_historico_anual", "title": "Producto interno bruto histórico anual", "table": "PIB histórico anual", "source_file": "7_1_14_anual.xls", "base": "1957/1968/1984/1997", "price_type": "Precios constantes", "measure": "Nivel", "frequency": "Anual", "period": "2017", "year": 2017, "quarter": null, "classification": "Total economía", "component": "Producto interno bruto", "value": 392393.12, "unit": "Millones de bolívares a precios constantes", "status": "", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/7_1_14_anual.xls", "fetched_at": "2026-09-09T22:40:34Z"}</t>
         </is>
       </c>
     </row>

--- a/assets/data/bcv/excel/ove_bcv_pib_historico_anual.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_pib_historico_anual.xlsx
@@ -736,7 +736,7 @@
       </c>
       <c r="S7" s="4" t="inlineStr">
         <is>
-          <t>2026-09-09T22:40:34Z</t>
+          <t>2026-09-10T22:42:29Z</t>
         </is>
       </c>
     </row>
@@ -821,7 +821,7 @@
       </c>
       <c r="S8" s="4" t="inlineStr">
         <is>
-          <t>2026-09-09T22:40:34Z</t>
+          <t>2026-09-10T22:42:29Z</t>
         </is>
       </c>
     </row>
@@ -906,7 +906,7 @@
       </c>
       <c r="S9" s="4" t="inlineStr">
         <is>
-          <t>2026-09-09T22:40:34Z</t>
+          <t>2026-09-10T22:42:29Z</t>
         </is>
       </c>
     </row>
@@ -991,7 +991,7 @@
       </c>
       <c r="S10" s="4" t="inlineStr">
         <is>
-          <t>2026-09-09T22:40:34Z</t>
+          <t>2026-09-10T22:42:29Z</t>
         </is>
       </c>
     </row>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="S11" s="4" t="inlineStr">
         <is>
-          <t>2026-09-09T22:40:34Z</t>
+          <t>2026-09-10T22:42:29Z</t>
         </is>
       </c>
     </row>
@@ -1161,7 +1161,7 @@
       </c>
       <c r="S12" s="4" t="inlineStr">
         <is>
-          <t>2026-09-09T22:40:34Z</t>
+          <t>2026-09-10T22:42:29Z</t>
         </is>
       </c>
     </row>
@@ -1246,7 +1246,7 @@
       </c>
       <c r="S13" s="4" t="inlineStr">
         <is>
-          <t>2026-09-09T22:40:34Z</t>
+          <t>2026-09-10T22:42:29Z</t>
         </is>
       </c>
     </row>
@@ -1331,7 +1331,7 @@
       </c>
       <c r="S14" s="4" t="inlineStr">
         <is>
-          <t>2026-09-09T22:40:34Z</t>
+          <t>2026-09-10T22:42:29Z</t>
         </is>
       </c>
     </row>
@@ -1416,7 +1416,7 @@
       </c>
       <c r="S15" s="4" t="inlineStr">
         <is>
-          <t>2026-09-09T22:40:34Z</t>
+          <t>2026-09-10T22:42:29Z</t>
         </is>
       </c>
     </row>
@@ -1501,7 +1501,7 @@
       </c>
       <c r="S16" s="4" t="inlineStr">
         <is>
-          <t>2026-09-09T22:40:34Z</t>
+          <t>2026-09-10T22:42:29Z</t>
         </is>
       </c>
     </row>
@@ -1586,7 +1586,7 @@
       </c>
       <c r="S17" s="4" t="inlineStr">
         <is>
-          <t>2026-09-09T22:40:34Z</t>
+          <t>2026-09-10T22:42:29Z</t>
         </is>
       </c>
     </row>
@@ -1671,7 +1671,7 @@
       </c>
       <c r="S18" s="4" t="inlineStr">
         <is>
-          <t>2026-09-09T22:40:34Z</t>
+          <t>2026-09-10T22:42:29Z</t>
         </is>
       </c>
     </row>
@@ -1756,7 +1756,7 @@
       </c>
       <c r="S19" s="4" t="inlineStr">
         <is>
-          <t>2026-09-09T22:40:34Z</t>
+          <t>2026-09-10T22:42:29Z</t>
         </is>
       </c>
     </row>
@@ -1841,7 +1841,7 @@
       </c>
       <c r="S20" s="4" t="inlineStr">
         <is>
-          <t>2026-09-09T22:40:34Z</t>
+          <t>2026-09-10T22:42:29Z</t>
         </is>
       </c>
     </row>
@@ -1926,7 +1926,7 @@
       </c>
       <c r="S21" s="4" t="inlineStr">
         <is>
-          <t>2026-09-09T22:40:34Z</t>
+          <t>2026-09-10T22:42:29Z</t>
         </is>
       </c>
     </row>
@@ -2011,7 +2011,7 @@
       </c>
       <c r="S22" s="4" t="inlineStr">
         <is>
-          <t>2026-09-09T22:40:34Z</t>
+          <t>2026-09-10T22:42:29Z</t>
         </is>
       </c>
     </row>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="S23" s="4" t="inlineStr">
         <is>
-          <t>2026-09-09T22:40:34Z</t>
+          <t>2026-09-10T22:42:29Z</t>
         </is>
       </c>
     </row>
@@ -2181,7 +2181,7 @@
       </c>
       <c r="S24" s="4" t="inlineStr">
         <is>
-          <t>2026-09-09T22:40:34Z</t>
+          <t>2026-09-10T22:42:29Z</t>
         </is>
       </c>
     </row>
@@ -2266,7 +2266,7 @@
       </c>
       <c r="S25" s="4" t="inlineStr">
         <is>
-          <t>2026-09-09T22:40:34Z</t>
+          <t>2026-09-10T22:42:29Z</t>
         </is>
       </c>
     </row>
@@ -2351,7 +2351,7 @@
       </c>
       <c r="S26" s="4" t="inlineStr">
         <is>
-          <t>2026-09-09T22:40:34Z</t>
+          <t>2026-09-10T22:42:29Z</t>
         </is>
       </c>
     </row>
@@ -2436,7 +2436,7 @@
       </c>
       <c r="S27" s="4" t="inlineStr">
         <is>
-          <t>2026-09-09T22:40:34Z</t>
+          <t>2026-09-10T22:42:29Z</t>
         </is>
       </c>
     </row>
@@ -2521,7 +2521,7 @@
       </c>
       <c r="S28" s="4" t="inlineStr">
         <is>
-          <t>2026-09-09T22:40:34Z</t>
+          <t>2026-09-10T22:42:29Z</t>
         </is>
       </c>
     </row>
@@ -2606,7 +2606,7 @@
       </c>
       <c r="S29" s="4" t="inlineStr">
         <is>
-          <t>2026-09-09T22:40:34Z</t>
+          <t>2026-09-10T22:42:29Z</t>
         </is>
       </c>
     </row>
@@ -2691,7 +2691,7 @@
       </c>
       <c r="S30" s="4" t="inlineStr">
         <is>
-          <t>2026-09-09T22:40:34Z</t>
+          <t>2026-09-10T22:42:29Z</t>
         </is>
       </c>
     </row>
@@ -2776,7 +2776,7 @@
       </c>
       <c r="S31" s="4" t="inlineStr">
         <is>
-          <t>2026-09-09T22:40:34Z</t>
+          <t>2026-09-10T22:42:29Z</t>
         </is>
       </c>
     </row>
@@ -2861,7 +2861,7 @@
       </c>
       <c r="S32" s="4" t="inlineStr">
         <is>
-          <t>2026-09-09T22:40:34Z</t>
+          <t>2026-09-10T22:42:29Z</t>
         </is>
       </c>
     </row>
@@ -2946,7 +2946,7 @@
       </c>
       <c r="S33" s="4" t="inlineStr">
         <is>
-          <t>2026-09-09T22:40:34Z</t>
+          <t>2026-09-10T22:42:29Z</t>
         </is>
       </c>
     </row>
@@ -3031,7 +3031,7 @@
       </c>
       <c r="S34" s="4" t="inlineStr">
         <is>
-          <t>2026-09-09T22:40:34Z</t>
+          <t>2026-09-10T22:42:29Z</t>
         </is>
       </c>
     </row>
@@ -3116,7 +3116,7 @@
       </c>
       <c r="S35" s="4" t="inlineStr">
         <is>
-          <t>2026-09-09T22:40:34Z</t>
+          <t>2026-09-10T22:42:29Z</t>
         </is>
       </c>
     </row>
@@ -3201,7 +3201,7 @@
       </c>
       <c r="S36" s="4" t="inlineStr">
         <is>
-          <t>2026-09-09T22:40:34Z</t>
+          <t>2026-09-10T22:42:29Z</t>
         </is>
       </c>
     </row>
@@ -3286,7 +3286,7 @@
       </c>
       <c r="S37" s="4" t="inlineStr">
         <is>
-          <t>2026-09-09T22:40:34Z</t>
+          <t>2026-09-10T22:42:29Z</t>
         </is>
       </c>
     </row>
@@ -3371,7 +3371,7 @@
       </c>
       <c r="S38" s="4" t="inlineStr">
         <is>
-          <t>2026-09-09T22:40:34Z</t>
+          <t>2026-09-10T22:42:29Z</t>
         </is>
       </c>
     </row>
@@ -3456,7 +3456,7 @@
       </c>
       <c r="S39" s="4" t="inlineStr">
         <is>
-          <t>2026-09-09T22:40:34Z</t>
+          <t>2026-09-10T22:42:29Z</t>
         </is>
       </c>
     </row>
@@ -3541,7 +3541,7 @@
       </c>
       <c r="S40" s="4" t="inlineStr">
         <is>
-          <t>2026-09-09T22:40:34Z</t>
+          <t>2026-09-10T22:42:29Z</t>
         </is>
       </c>
     </row>
@@ -3626,7 +3626,7 @@
       </c>
       <c r="S41" s="4" t="inlineStr">
         <is>
-          <t>2026-09-09T22:40:34Z</t>
+          <t>2026-09-10T22:42:29Z</t>
         </is>
       </c>
     </row>
@@ -3711,7 +3711,7 @@
       </c>
       <c r="S42" s="4" t="inlineStr">
         <is>
-          <t>2026-09-09T22:40:34Z</t>
+          <t>2026-09-10T22:42:29Z</t>
         </is>
       </c>
     </row>
@@ -3796,7 +3796,7 @@
       </c>
       <c r="S43" s="4" t="inlineStr">
         <is>
-          <t>2026-09-09T22:40:34Z</t>
+          <t>2026-09-10T22:42:29Z</t>
         </is>
       </c>
     </row>
@@ -3881,7 +3881,7 @@
       </c>
       <c r="S44" s="4" t="inlineStr">
         <is>
-          <t>2026-09-09T22:40:34Z</t>
+          <t>2026-09-10T22:42:29Z</t>
         </is>
       </c>
     </row>
@@ -3966,7 +3966,7 @@
       </c>
       <c r="S45" s="4" t="inlineStr">
         <is>
-          <t>2026-09-09T22:40:34Z</t>
+          <t>2026-09-10T22:42:29Z</t>
         </is>
       </c>
     </row>
@@ -4051,7 +4051,7 @@
       </c>
       <c r="S46" s="4" t="inlineStr">
         <is>
-          <t>2026-09-09T22:40:34Z</t>
+          <t>2026-09-10T22:42:29Z</t>
         </is>
       </c>
     </row>
@@ -4136,7 +4136,7 @@
       </c>
       <c r="S47" s="4" t="inlineStr">
         <is>
-          <t>2026-09-09T22:40:34Z</t>
+          <t>2026-09-10T22:42:29Z</t>
         </is>
       </c>
     </row>
@@ -4221,7 +4221,7 @@
       </c>
       <c r="S48" s="4" t="inlineStr">
         <is>
-          <t>2026-09-09T22:40:34Z</t>
+          <t>2026-09-10T22:42:29Z</t>
         </is>
       </c>
     </row>
@@ -4306,7 +4306,7 @@
       </c>
       <c r="S49" s="4" t="inlineStr">
         <is>
-          <t>2026-09-09T22:40:34Z</t>
+          <t>2026-09-10T22:42:29Z</t>
         </is>
       </c>
     </row>
@@ -4391,7 +4391,7 @@
       </c>
       <c r="S50" s="4" t="inlineStr">
         <is>
-          <t>2026-09-09T22:40:34Z</t>
+          <t>2026-09-10T22:42:29Z</t>
         </is>
       </c>
     </row>
@@ -4476,7 +4476,7 @@
       </c>
       <c r="S51" s="4" t="inlineStr">
         <is>
-          <t>2026-09-09T22:40:34Z</t>
+          <t>2026-09-10T22:42:29Z</t>
         </is>
       </c>
     </row>
@@ -4561,7 +4561,7 @@
       </c>
       <c r="S52" s="4" t="inlineStr">
         <is>
-          <t>2026-09-09T22:40:34Z</t>
+          <t>2026-09-10T22:42:29Z</t>
         </is>
       </c>
     </row>
@@ -4646,7 +4646,7 @@
       </c>
       <c r="S53" s="4" t="inlineStr">
         <is>
-          <t>2026-09-09T22:40:34Z</t>
+          <t>2026-09-10T22:42:29Z</t>
         </is>
       </c>
     </row>
@@ -4731,7 +4731,7 @@
       </c>
       <c r="S54" s="4" t="inlineStr">
         <is>
-          <t>2026-09-09T22:40:34Z</t>
+          <t>2026-09-10T22:42:29Z</t>
         </is>
       </c>
     </row>
@@ -4816,7 +4816,7 @@
       </c>
       <c r="S55" s="4" t="inlineStr">
         <is>
-          <t>2026-09-09T22:40:34Z</t>
+          <t>2026-09-10T22:42:29Z</t>
         </is>
       </c>
     </row>
@@ -4901,7 +4901,7 @@
       </c>
       <c r="S56" s="4" t="inlineStr">
         <is>
-          <t>2026-09-09T22:40:34Z</t>
+          <t>2026-09-10T22:42:29Z</t>
         </is>
       </c>
     </row>
@@ -4986,7 +4986,7 @@
       </c>
       <c r="S57" s="4" t="inlineStr">
         <is>
-          <t>2026-09-09T22:40:34Z</t>
+          <t>2026-09-10T22:42:29Z</t>
         </is>
       </c>
     </row>
@@ -5071,7 +5071,7 @@
       </c>
       <c r="S58" s="4" t="inlineStr">
         <is>
-          <t>2026-09-09T22:40:34Z</t>
+          <t>2026-09-10T22:42:29Z</t>
         </is>
       </c>
     </row>
@@ -5156,7 +5156,7 @@
       </c>
       <c r="S59" s="4" t="inlineStr">
         <is>
-          <t>2026-09-09T22:40:34Z</t>
+          <t>2026-09-10T22:42:29Z</t>
         </is>
       </c>
     </row>
@@ -5241,7 +5241,7 @@
       </c>
       <c r="S60" s="4" t="inlineStr">
         <is>
-          <t>2026-09-09T22:40:34Z</t>
+          <t>2026-09-10T22:42:29Z</t>
         </is>
       </c>
     </row>
@@ -5326,7 +5326,7 @@
       </c>
       <c r="S61" s="4" t="inlineStr">
         <is>
-          <t>2026-09-09T22:40:34Z</t>
+          <t>2026-09-10T22:42:29Z</t>
         </is>
       </c>
     </row>
@@ -5411,7 +5411,7 @@
       </c>
       <c r="S62" s="4" t="inlineStr">
         <is>
-          <t>2026-09-09T22:40:34Z</t>
+          <t>2026-09-10T22:42:29Z</t>
         </is>
       </c>
     </row>
@@ -5496,7 +5496,7 @@
       </c>
       <c r="S63" s="4" t="inlineStr">
         <is>
-          <t>2026-09-09T22:40:34Z</t>
+          <t>2026-09-10T22:42:29Z</t>
         </is>
       </c>
     </row>
@@ -5581,7 +5581,7 @@
       </c>
       <c r="S64" s="4" t="inlineStr">
         <is>
-          <t>2026-09-09T22:40:34Z</t>
+          <t>2026-09-10T22:42:29Z</t>
         </is>
       </c>
     </row>
@@ -5666,7 +5666,7 @@
       </c>
       <c r="S65" s="4" t="inlineStr">
         <is>
-          <t>2026-09-09T22:40:34Z</t>
+          <t>2026-09-10T22:42:29Z</t>
         </is>
       </c>
     </row>
@@ -5751,7 +5751,7 @@
       </c>
       <c r="S66" s="4" t="inlineStr">
         <is>
-          <t>2026-09-09T22:40:34Z</t>
+          <t>2026-09-10T22:42:29Z</t>
         </is>
       </c>
     </row>
@@ -5836,7 +5836,7 @@
       </c>
       <c r="S67" s="4" t="inlineStr">
         <is>
-          <t>2026-09-09T22:40:34Z</t>
+          <t>2026-09-10T22:42:29Z</t>
         </is>
       </c>
     </row>
@@ -5921,7 +5921,7 @@
       </c>
       <c r="S68" s="4" t="inlineStr">
         <is>
-          <t>2026-09-09T22:40:34Z</t>
+          <t>2026-09-10T22:42:29Z</t>
         </is>
       </c>
     </row>
@@ -6006,7 +6006,7 @@
       </c>
       <c r="S69" s="4" t="inlineStr">
         <is>
-          <t>2026-09-09T22:40:34Z</t>
+          <t>2026-09-10T22:42:29Z</t>
         </is>
       </c>
     </row>
@@ -6091,7 +6091,7 @@
       </c>
       <c r="S70" s="4" t="inlineStr">
         <is>
-          <t>2026-09-09T22:40:34Z</t>
+          <t>2026-09-10T22:42:29Z</t>
         </is>
       </c>
     </row>
@@ -6176,7 +6176,7 @@
       </c>
       <c r="S71" s="4" t="inlineStr">
         <is>
-          <t>2026-09-09T22:40:34Z</t>
+          <t>2026-09-10T22:42:29Z</t>
         </is>
       </c>
     </row>
@@ -6261,7 +6261,7 @@
       </c>
       <c r="S72" s="4" t="inlineStr">
         <is>
-          <t>2026-09-09T22:40:34Z</t>
+          <t>2026-09-10T22:42:29Z</t>
         </is>
       </c>
     </row>
@@ -6346,7 +6346,7 @@
       </c>
       <c r="S73" s="4" t="inlineStr">
         <is>
-          <t>2026-09-09T22:40:34Z</t>
+          <t>2026-09-10T22:42:29Z</t>
         </is>
       </c>
     </row>
@@ -6431,7 +6431,7 @@
       </c>
       <c r="S74" s="4" t="inlineStr">
         <is>
-          <t>2026-09-09T22:40:34Z</t>
+          <t>2026-09-10T22:42:29Z</t>
         </is>
       </c>
     </row>
@@ -6516,7 +6516,7 @@
       </c>
       <c r="S75" s="4" t="inlineStr">
         <is>
-          <t>2026-09-09T22:40:34Z</t>
+          <t>2026-09-10T22:42:29Z</t>
         </is>
       </c>
     </row>
@@ -6601,7 +6601,7 @@
       </c>
       <c r="S76" s="4" t="inlineStr">
         <is>
-          <t>2026-09-09T22:40:34Z</t>
+          <t>2026-09-10T22:42:29Z</t>
         </is>
       </c>
     </row>
@@ -6686,7 +6686,7 @@
       </c>
       <c r="S77" s="4" t="inlineStr">
         <is>
-          <t>2026-09-09T22:40:34Z</t>
+          <t>2026-09-10T22:42:29Z</t>
         </is>
       </c>
     </row>
@@ -6771,7 +6771,7 @@
       </c>
       <c r="S78" s="4" t="inlineStr">
         <is>
-          <t>2026-09-09T22:40:34Z</t>
+          <t>2026-09-10T22:42:29Z</t>
         </is>
       </c>
     </row>
@@ -6856,7 +6856,7 @@
       </c>
       <c r="S79" s="4" t="inlineStr">
         <is>
-          <t>2026-09-09T22:40:34Z</t>
+          <t>2026-09-10T22:42:29Z</t>
         </is>
       </c>
     </row>
@@ -6941,7 +6941,7 @@
       </c>
       <c r="S80" s="4" t="inlineStr">
         <is>
-          <t>2026-09-09T22:40:34Z</t>
+          <t>2026-09-10T22:42:29Z</t>
         </is>
       </c>
     </row>
@@ -7026,7 +7026,7 @@
       </c>
       <c r="S81" s="4" t="inlineStr">
         <is>
-          <t>2026-09-09T22:40:34Z</t>
+          <t>2026-09-10T22:42:29Z</t>
         </is>
       </c>
     </row>
@@ -7111,7 +7111,7 @@
       </c>
       <c r="S82" s="4" t="inlineStr">
         <is>
-          <t>2026-09-09T22:40:34Z</t>
+          <t>2026-09-10T22:42:29Z</t>
         </is>
       </c>
     </row>
@@ -7196,7 +7196,7 @@
       </c>
       <c r="S83" s="4" t="inlineStr">
         <is>
-          <t>2026-09-09T22:40:34Z</t>
+          <t>2026-09-10T22:42:29Z</t>
         </is>
       </c>
     </row>
@@ -7281,7 +7281,7 @@
       </c>
       <c r="S84" s="4" t="inlineStr">
         <is>
-          <t>2026-09-09T22:40:34Z</t>
+          <t>2026-09-10T22:42:29Z</t>
         </is>
       </c>
     </row>
@@ -7366,7 +7366,7 @@
       </c>
       <c r="S85" s="4" t="inlineStr">
         <is>
-          <t>2026-09-09T22:40:34Z</t>
+          <t>2026-09-10T22:42:29Z</t>
         </is>
       </c>
     </row>
@@ -7451,7 +7451,7 @@
       </c>
       <c r="S86" s="4" t="inlineStr">
         <is>
-          <t>2026-09-09T22:40:34Z</t>
+          <t>2026-09-10T22:42:29Z</t>
         </is>
       </c>
     </row>
@@ -7536,7 +7536,7 @@
       </c>
       <c r="S87" s="4" t="inlineStr">
         <is>
-          <t>2026-09-09T22:40:34Z</t>
+          <t>2026-09-10T22:42:29Z</t>
         </is>
       </c>
     </row>
@@ -7621,7 +7621,7 @@
       </c>
       <c r="S88" s="4" t="inlineStr">
         <is>
-          <t>2026-09-09T22:40:34Z</t>
+          <t>2026-09-10T22:42:29Z</t>
         </is>
       </c>
     </row>
@@ -7706,7 +7706,7 @@
       </c>
       <c r="S89" s="4" t="inlineStr">
         <is>
-          <t>2026-09-09T22:40:34Z</t>
+          <t>2026-09-10T22:42:29Z</t>
         </is>
       </c>
     </row>
@@ -7791,7 +7791,7 @@
       </c>
       <c r="S90" s="4" t="inlineStr">
         <is>
-          <t>2026-09-09T22:40:34Z</t>
+          <t>2026-09-10T22:42:29Z</t>
         </is>
       </c>
     </row>
@@ -7876,7 +7876,7 @@
       </c>
       <c r="S91" s="4" t="inlineStr">
         <is>
-          <t>2026-09-09T22:40:34Z</t>
+          <t>2026-09-10T22:42:29Z</t>
         </is>
       </c>
     </row>
@@ -7961,7 +7961,7 @@
       </c>
       <c r="S92" s="4" t="inlineStr">
         <is>
-          <t>2026-09-09T22:40:34Z</t>
+          <t>2026-09-10T22:42:29Z</t>
         </is>
       </c>
     </row>
@@ -8046,7 +8046,7 @@
       </c>
       <c r="S93" s="4" t="inlineStr">
         <is>
-          <t>2026-09-09T22:40:34Z</t>
+          <t>2026-09-10T22:42:29Z</t>
         </is>
       </c>
     </row>
@@ -8131,7 +8131,7 @@
       </c>
       <c r="S94" s="4" t="inlineStr">
         <is>
-          <t>2026-09-09T22:40:34Z</t>
+          <t>2026-09-10T22:42:29Z</t>
         </is>
       </c>
     </row>
@@ -8216,7 +8216,7 @@
       </c>
       <c r="S95" s="4" t="inlineStr">
         <is>
-          <t>2026-09-09T22:40:34Z</t>
+          <t>2026-09-10T22:42:29Z</t>
         </is>
       </c>
     </row>
@@ -8301,7 +8301,7 @@
       </c>
       <c r="S96" s="4" t="inlineStr">
         <is>
-          <t>2026-09-09T22:40:34Z</t>
+          <t>2026-09-10T22:42:29Z</t>
         </is>
       </c>
     </row>
@@ -8386,7 +8386,7 @@
       </c>
       <c r="S97" s="4" t="inlineStr">
         <is>
-          <t>2026-09-09T22:40:34Z</t>
+          <t>2026-09-10T22:42:29Z</t>
         </is>
       </c>
     </row>
@@ -8471,7 +8471,7 @@
       </c>
       <c r="S98" s="4" t="inlineStr">
         <is>
-          <t>2026-09-09T22:40:34Z</t>
+          <t>2026-09-10T22:42:29Z</t>
         </is>
       </c>
     </row>
@@ -8556,7 +8556,7 @@
       </c>
       <c r="S99" s="4" t="inlineStr">
         <is>
-          <t>2026-09-09T22:40:34Z</t>
+          <t>2026-09-10T22:42:29Z</t>
         </is>
       </c>
     </row>
@@ -8641,7 +8641,7 @@
       </c>
       <c r="S100" s="4" t="inlineStr">
         <is>
-          <t>2026-09-09T22:40:34Z</t>
+          <t>2026-09-10T22:42:29Z</t>
         </is>
       </c>
     </row>
@@ -8726,7 +8726,7 @@
       </c>
       <c r="S101" s="4" t="inlineStr">
         <is>
-          <t>2026-09-09T22:40:34Z</t>
+          <t>2026-09-10T22:42:29Z</t>
         </is>
       </c>
     </row>
@@ -8811,7 +8811,7 @@
       </c>
       <c r="S102" s="4" t="inlineStr">
         <is>
-          <t>2026-09-09T22:40:34Z</t>
+          <t>2026-09-10T22:42:29Z</t>
         </is>
       </c>
     </row>
@@ -8896,7 +8896,7 @@
       </c>
       <c r="S103" s="4" t="inlineStr">
         <is>
-          <t>2026-09-09T22:40:34Z</t>
+          <t>2026-09-10T22:42:29Z</t>
         </is>
       </c>
     </row>
@@ -8981,7 +8981,7 @@
       </c>
       <c r="S104" s="4" t="inlineStr">
         <is>
-          <t>2026-09-09T22:40:34Z</t>
+          <t>2026-09-10T22:42:29Z</t>
         </is>
       </c>
     </row>
@@ -9066,7 +9066,7 @@
       </c>
       <c r="S105" s="4" t="inlineStr">
         <is>
-          <t>2026-09-09T22:40:34Z</t>
+          <t>2026-09-10T22:42:29Z</t>
         </is>
       </c>
     </row>
@@ -9151,7 +9151,7 @@
       </c>
       <c r="S106" s="4" t="inlineStr">
         <is>
-          <t>2026-09-09T22:40:34Z</t>
+          <t>2026-09-10T22:42:29Z</t>
         </is>
       </c>
     </row>
@@ -9236,7 +9236,7 @@
       </c>
       <c r="S107" s="4" t="inlineStr">
         <is>
-          <t>2026-09-09T22:40:34Z</t>
+          <t>2026-09-10T22:42:29Z</t>
         </is>
       </c>
     </row>
@@ -9321,7 +9321,7 @@
       </c>
       <c r="S108" s="4" t="inlineStr">
         <is>
-          <t>2026-09-09T22:40:34Z</t>
+          <t>2026-09-10T22:42:29Z</t>
         </is>
       </c>
     </row>
@@ -9406,7 +9406,7 @@
       </c>
       <c r="S109" s="4" t="inlineStr">
         <is>
-          <t>2026-09-09T22:40:34Z</t>
+          <t>2026-09-10T22:42:29Z</t>
         </is>
       </c>
     </row>
@@ -9491,7 +9491,7 @@
       </c>
       <c r="S110" s="4" t="inlineStr">
         <is>
-          <t>2026-09-09T22:40:34Z</t>
+          <t>2026-09-10T22:42:29Z</t>
         </is>
       </c>
     </row>
@@ -9576,7 +9576,7 @@
       </c>
       <c r="S111" s="4" t="inlineStr">
         <is>
-          <t>2026-09-09T22:40:34Z</t>
+          <t>2026-09-10T22:42:29Z</t>
         </is>
       </c>
     </row>
@@ -9661,7 +9661,7 @@
       </c>
       <c r="S112" s="4" t="inlineStr">
         <is>
-          <t>2026-09-09T22:40:34Z</t>
+          <t>2026-09-10T22:42:29Z</t>
         </is>
       </c>
     </row>
@@ -9746,7 +9746,7 @@
       </c>
       <c r="S113" s="4" t="inlineStr">
         <is>
-          <t>2026-09-09T22:40:34Z</t>
+          <t>2026-09-10T22:42:29Z</t>
         </is>
       </c>
     </row>
@@ -9831,7 +9831,7 @@
       </c>
       <c r="S114" s="4" t="inlineStr">
         <is>
-          <t>2026-09-09T22:40:34Z</t>
+          <t>2026-09-10T22:42:29Z</t>
         </is>
       </c>
     </row>
@@ -9916,7 +9916,7 @@
       </c>
       <c r="S115" s="4" t="inlineStr">
         <is>
-          <t>2026-09-09T22:40:34Z</t>
+          <t>2026-09-10T22:42:29Z</t>
         </is>
       </c>
     </row>
@@ -10001,7 +10001,7 @@
       </c>
       <c r="S116" s="4" t="inlineStr">
         <is>
-          <t>2026-09-09T22:40:34Z</t>
+          <t>2026-09-10T22:42:29Z</t>
         </is>
       </c>
     </row>
@@ -10086,7 +10086,7 @@
       </c>
       <c r="S117" s="4" t="inlineStr">
         <is>
-          <t>2026-09-09T22:40:34Z</t>
+          <t>2026-09-10T22:42:29Z</t>
         </is>
       </c>
     </row>
@@ -10171,7 +10171,7 @@
       </c>
       <c r="S118" s="4" t="inlineStr">
         <is>
-          <t>2026-09-09T22:40:34Z</t>
+          <t>2026-09-10T22:42:29Z</t>
         </is>
       </c>
     </row>
@@ -10256,7 +10256,7 @@
       </c>
       <c r="S119" s="4" t="inlineStr">
         <is>
-          <t>2026-09-09T22:40:34Z</t>
+          <t>2026-09-10T22:42:29Z</t>
         </is>
       </c>
     </row>
@@ -10341,7 +10341,7 @@
       </c>
       <c r="S120" s="4" t="inlineStr">
         <is>
-          <t>2026-09-09T22:40:34Z</t>
+          <t>2026-09-10T22:42:29Z</t>
         </is>
       </c>
     </row>
@@ -10426,7 +10426,7 @@
       </c>
       <c r="S121" s="4" t="inlineStr">
         <is>
-          <t>2026-09-09T22:40:34Z</t>
+          <t>2026-09-10T22:42:29Z</t>
         </is>
       </c>
     </row>
@@ -10511,7 +10511,7 @@
       </c>
       <c r="S122" s="4" t="inlineStr">
         <is>
-          <t>2026-09-09T22:40:34Z</t>
+          <t>2026-09-10T22:42:29Z</t>
         </is>
       </c>
     </row>
@@ -10596,7 +10596,7 @@
       </c>
       <c r="S123" s="4" t="inlineStr">
         <is>
-          <t>2026-09-09T22:40:34Z</t>
+          <t>2026-09-10T22:42:29Z</t>
         </is>
       </c>
     </row>
@@ -10681,7 +10681,7 @@
       </c>
       <c r="S124" s="4" t="inlineStr">
         <is>
-          <t>2026-09-09T22:40:34Z</t>
+          <t>2026-09-10T22:42:29Z</t>
         </is>
       </c>
     </row>
@@ -10766,7 +10766,7 @@
       </c>
       <c r="S125" s="4" t="inlineStr">
         <is>
-          <t>2026-09-09T22:40:34Z</t>
+          <t>2026-09-10T22:42:29Z</t>
         </is>
       </c>
     </row>
@@ -10851,7 +10851,7 @@
       </c>
       <c r="S126" s="4" t="inlineStr">
         <is>
-          <t>2026-09-09T22:40:34Z</t>
+          <t>2026-09-10T22:42:29Z</t>
         </is>
       </c>
     </row>
@@ -10936,7 +10936,7 @@
       </c>
       <c r="S127" s="4" t="inlineStr">
         <is>
-          <t>2026-09-09T22:40:34Z</t>
+          <t>2026-09-10T22:42:29Z</t>
         </is>
       </c>
     </row>
@@ -11021,7 +11021,7 @@
       </c>
       <c r="S128" s="4" t="inlineStr">
         <is>
-          <t>2026-09-09T22:40:34Z</t>
+          <t>2026-09-10T22:42:29Z</t>
         </is>
       </c>
     </row>
@@ -11106,7 +11106,7 @@
       </c>
       <c r="S129" s="4" t="inlineStr">
         <is>
-          <t>2026-09-09T22:40:34Z</t>
+          <t>2026-09-10T22:42:29Z</t>
         </is>
       </c>
     </row>
@@ -11191,7 +11191,7 @@
       </c>
       <c r="S130" s="4" t="inlineStr">
         <is>
-          <t>2026-09-09T22:40:34Z</t>
+          <t>2026-09-10T22:42:29Z</t>
         </is>
       </c>
     </row>
@@ -11276,7 +11276,7 @@
       </c>
       <c r="S131" s="4" t="inlineStr">
         <is>
-          <t>2026-09-09T22:40:34Z</t>
+          <t>2026-09-10T22:42:29Z</t>
         </is>
       </c>
     </row>
@@ -11361,7 +11361,7 @@
       </c>
       <c r="S132" s="4" t="inlineStr">
         <is>
-          <t>2026-09-09T22:40:34Z</t>
+          <t>2026-09-10T22:42:29Z</t>
         </is>
       </c>
     </row>
@@ -11446,7 +11446,7 @@
       </c>
       <c r="S133" s="4" t="inlineStr">
         <is>
-          <t>2026-09-09T22:40:34Z</t>
+          <t>2026-09-10T22:42:29Z</t>
         </is>
       </c>
     </row>
@@ -11531,7 +11531,7 @@
       </c>
       <c r="S134" s="4" t="inlineStr">
         <is>
-          <t>2026-09-09T22:40:34Z</t>
+          <t>2026-09-10T22:42:29Z</t>
         </is>
       </c>
     </row>
@@ -11616,7 +11616,7 @@
       </c>
       <c r="S135" s="4" t="inlineStr">
         <is>
-          <t>2026-09-09T22:40:34Z</t>
+          <t>2026-09-10T22:42:29Z</t>
         </is>
       </c>
     </row>
@@ -11701,7 +11701,7 @@
       </c>
       <c r="S136" s="4" t="inlineStr">
         <is>
-          <t>2026-09-09T22:40:34Z</t>
+          <t>2026-09-10T22:42:29Z</t>
         </is>
       </c>
     </row>
@@ -11786,7 +11786,7 @@
       </c>
       <c r="S137" s="4" t="inlineStr">
         <is>
-          <t>2026-09-09T22:40:34Z</t>
+          <t>2026-09-10T22:42:29Z</t>
         </is>
       </c>
     </row>
@@ -11871,7 +11871,7 @@
       </c>
       <c r="S138" s="4" t="inlineStr">
         <is>
-          <t>2026-09-09T22:40:34Z</t>
+          <t>2026-09-10T22:42:29Z</t>
         </is>
       </c>
     </row>
@@ -11956,7 +11956,7 @@
       </c>
       <c r="S139" s="4" t="inlineStr">
         <is>
-          <t>2026-09-09T22:40:34Z</t>
+          <t>2026-09-10T22:42:29Z</t>
         </is>
       </c>
     </row>
@@ -12041,7 +12041,7 @@
       </c>
       <c r="S140" s="4" t="inlineStr">
         <is>
-          <t>2026-09-09T22:40:34Z</t>
+          <t>2026-09-10T22:42:29Z</t>
         </is>
       </c>
     </row>
@@ -12126,7 +12126,7 @@
       </c>
       <c r="S141" s="4" t="inlineStr">
         <is>
-          <t>2026-09-09T22:40:34Z</t>
+          <t>2026-09-10T22:42:29Z</t>
         </is>
       </c>
     </row>
@@ -12258,7 +12258,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>2026-09-09T22:40:34Z</t>
+          <t>2026-09-10T22:42:29Z</t>
         </is>
       </c>
     </row>
@@ -12338,7 +12338,7 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>{"dataset_id": "bcv_pib_historico_anual", "title": "Producto interno bruto histórico anual", "table": "PIB histórico anual", "source_file": "7_1_14_anual.xls", "base": "1957/1968/1984/1997", "price_type": "Precios constantes", "measure": "Nivel", "frequency": "Anual", "period": "2017", "year": 2017, "quarter": null, "classification": "Total economía", "component": "Producto interno bruto", "value": 392393.12, "unit": "Millones de bolívares a precios constantes", "status": "", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/7_1_14_anual.xls", "fetched_at": "2026-09-09T22:40:34Z"}</t>
+          <t>{"dataset_id": "bcv_pib_historico_anual", "title": "Producto interno bruto histórico anual", "table": "PIB histórico anual", "source_file": "7_1_14_anual.xls", "base": "1957/1968/1984/1997", "price_type": "Precios constantes", "measure": "Nivel", "frequency": "Anual", "period": "2017", "year": 2017, "quarter": null, "classification": "Total economía", "component": "Producto interno bruto", "value": 392393.12, "unit": "Millones de bolívares a precios constantes", "status": "", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/7_1_14_anual.xls", "fetched_at": "2026-09-10T22:42:29Z"}</t>
         </is>
       </c>
     </row>

--- a/assets/data/bcv/excel/ove_bcv_pib_historico_anual.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_pib_historico_anual.xlsx
@@ -736,7 +736,7 @@
       </c>
       <c r="S7" s="4" t="inlineStr">
         <is>
-          <t>2026-09-10T22:42:29Z</t>
+          <t>2026-09-11T22:42:45Z</t>
         </is>
       </c>
     </row>
@@ -821,7 +821,7 @@
       </c>
       <c r="S8" s="4" t="inlineStr">
         <is>
-          <t>2026-09-10T22:42:29Z</t>
+          <t>2026-09-11T22:42:45Z</t>
         </is>
       </c>
     </row>
@@ -906,7 +906,7 @@
       </c>
       <c r="S9" s="4" t="inlineStr">
         <is>
-          <t>2026-09-10T22:42:29Z</t>
+          <t>2026-09-11T22:42:45Z</t>
         </is>
       </c>
     </row>
@@ -991,7 +991,7 @@
       </c>
       <c r="S10" s="4" t="inlineStr">
         <is>
-          <t>2026-09-10T22:42:29Z</t>
+          <t>2026-09-11T22:42:45Z</t>
         </is>
       </c>
     </row>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="S11" s="4" t="inlineStr">
         <is>
-          <t>2026-09-10T22:42:29Z</t>
+          <t>2026-09-11T22:42:45Z</t>
         </is>
       </c>
     </row>
@@ -1161,7 +1161,7 @@
       </c>
       <c r="S12" s="4" t="inlineStr">
         <is>
-          <t>2026-09-10T22:42:29Z</t>
+          <t>2026-09-11T22:42:45Z</t>
         </is>
       </c>
     </row>
@@ -1246,7 +1246,7 @@
       </c>
       <c r="S13" s="4" t="inlineStr">
         <is>
-          <t>2026-09-10T22:42:29Z</t>
+          <t>2026-09-11T22:42:45Z</t>
         </is>
       </c>
     </row>
@@ -1331,7 +1331,7 @@
       </c>
       <c r="S14" s="4" t="inlineStr">
         <is>
-          <t>2026-09-10T22:42:29Z</t>
+          <t>2026-09-11T22:42:45Z</t>
         </is>
       </c>
     </row>
@@ -1416,7 +1416,7 @@
       </c>
       <c r="S15" s="4" t="inlineStr">
         <is>
-          <t>2026-09-10T22:42:29Z</t>
+          <t>2026-09-11T22:42:45Z</t>
         </is>
       </c>
     </row>
@@ -1501,7 +1501,7 @@
       </c>
       <c r="S16" s="4" t="inlineStr">
         <is>
-          <t>2026-09-10T22:42:29Z</t>
+          <t>2026-09-11T22:42:45Z</t>
         </is>
       </c>
     </row>
@@ -1586,7 +1586,7 @@
       </c>
       <c r="S17" s="4" t="inlineStr">
         <is>
-          <t>2026-09-10T22:42:29Z</t>
+          <t>2026-09-11T22:42:45Z</t>
         </is>
       </c>
     </row>
@@ -1671,7 +1671,7 @@
       </c>
       <c r="S18" s="4" t="inlineStr">
         <is>
-          <t>2026-09-10T22:42:29Z</t>
+          <t>2026-09-11T22:42:45Z</t>
         </is>
       </c>
     </row>
@@ -1756,7 +1756,7 @@
       </c>
       <c r="S19" s="4" t="inlineStr">
         <is>
-          <t>2026-09-10T22:42:29Z</t>
+          <t>2026-09-11T22:42:45Z</t>
         </is>
       </c>
     </row>
@@ -1841,7 +1841,7 @@
       </c>
       <c r="S20" s="4" t="inlineStr">
         <is>
-          <t>2026-09-10T22:42:29Z</t>
+          <t>2026-09-11T22:42:45Z</t>
         </is>
       </c>
     </row>
@@ -1926,7 +1926,7 @@
       </c>
       <c r="S21" s="4" t="inlineStr">
         <is>
-          <t>2026-09-10T22:42:29Z</t>
+          <t>2026-09-11T22:42:45Z</t>
         </is>
       </c>
     </row>
@@ -2011,7 +2011,7 @@
       </c>
       <c r="S22" s="4" t="inlineStr">
         <is>
-          <t>2026-09-10T22:42:29Z</t>
+          <t>2026-09-11T22:42:45Z</t>
         </is>
       </c>
     </row>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="S23" s="4" t="inlineStr">
         <is>
-          <t>2026-09-10T22:42:29Z</t>
+          <t>2026-09-11T22:42:45Z</t>
         </is>
       </c>
     </row>
@@ -2181,7 +2181,7 @@
       </c>
       <c r="S24" s="4" t="inlineStr">
         <is>
-          <t>2026-09-10T22:42:29Z</t>
+          <t>2026-09-11T22:42:45Z</t>
         </is>
       </c>
     </row>
@@ -2266,7 +2266,7 @@
       </c>
       <c r="S25" s="4" t="inlineStr">
         <is>
-          <t>2026-09-10T22:42:29Z</t>
+          <t>2026-09-11T22:42:45Z</t>
         </is>
       </c>
     </row>
@@ -2351,7 +2351,7 @@
       </c>
       <c r="S26" s="4" t="inlineStr">
         <is>
-          <t>2026-09-10T22:42:29Z</t>
+          <t>2026-09-11T22:42:45Z</t>
         </is>
       </c>
     </row>
@@ -2436,7 +2436,7 @@
       </c>
       <c r="S27" s="4" t="inlineStr">
         <is>
-          <t>2026-09-10T22:42:29Z</t>
+          <t>2026-09-11T22:42:45Z</t>
         </is>
       </c>
     </row>
@@ -2521,7 +2521,7 @@
       </c>
       <c r="S28" s="4" t="inlineStr">
         <is>
-          <t>2026-09-10T22:42:29Z</t>
+          <t>2026-09-11T22:42:45Z</t>
         </is>
       </c>
     </row>
@@ -2606,7 +2606,7 @@
       </c>
       <c r="S29" s="4" t="inlineStr">
         <is>
-          <t>2026-09-10T22:42:29Z</t>
+          <t>2026-09-11T22:42:45Z</t>
         </is>
       </c>
     </row>
@@ -2691,7 +2691,7 @@
       </c>
       <c r="S30" s="4" t="inlineStr">
         <is>
-          <t>2026-09-10T22:42:29Z</t>
+          <t>2026-09-11T22:42:45Z</t>
         </is>
       </c>
     </row>
@@ -2776,7 +2776,7 @@
       </c>
       <c r="S31" s="4" t="inlineStr">
         <is>
-          <t>2026-09-10T22:42:29Z</t>
+          <t>2026-09-11T22:42:45Z</t>
         </is>
       </c>
     </row>
@@ -2861,7 +2861,7 @@
       </c>
       <c r="S32" s="4" t="inlineStr">
         <is>
-          <t>2026-09-10T22:42:29Z</t>
+          <t>2026-09-11T22:42:45Z</t>
         </is>
       </c>
     </row>
@@ -2946,7 +2946,7 @@
       </c>
       <c r="S33" s="4" t="inlineStr">
         <is>
-          <t>2026-09-10T22:42:29Z</t>
+          <t>2026-09-11T22:42:45Z</t>
         </is>
       </c>
     </row>
@@ -3031,7 +3031,7 @@
       </c>
       <c r="S34" s="4" t="inlineStr">
         <is>
-          <t>2026-09-10T22:42:29Z</t>
+          <t>2026-09-11T22:42:45Z</t>
         </is>
       </c>
     </row>
@@ -3116,7 +3116,7 @@
       </c>
       <c r="S35" s="4" t="inlineStr">
         <is>
-          <t>2026-09-10T22:42:29Z</t>
+          <t>2026-09-11T22:42:45Z</t>
         </is>
       </c>
     </row>
@@ -3201,7 +3201,7 @@
       </c>
       <c r="S36" s="4" t="inlineStr">
         <is>
-          <t>2026-09-10T22:42:29Z</t>
+          <t>2026-09-11T22:42:45Z</t>
         </is>
       </c>
     </row>
@@ -3286,7 +3286,7 @@
       </c>
       <c r="S37" s="4" t="inlineStr">
         <is>
-          <t>2026-09-10T22:42:29Z</t>
+          <t>2026-09-11T22:42:45Z</t>
         </is>
       </c>
     </row>
@@ -3371,7 +3371,7 @@
       </c>
       <c r="S38" s="4" t="inlineStr">
         <is>
-          <t>2026-09-10T22:42:29Z</t>
+          <t>2026-09-11T22:42:45Z</t>
         </is>
       </c>
     </row>
@@ -3456,7 +3456,7 @@
       </c>
       <c r="S39" s="4" t="inlineStr">
         <is>
-          <t>2026-09-10T22:42:29Z</t>
+          <t>2026-09-11T22:42:45Z</t>
         </is>
       </c>
     </row>
@@ -3541,7 +3541,7 @@
       </c>
       <c r="S40" s="4" t="inlineStr">
         <is>
-          <t>2026-09-10T22:42:29Z</t>
+          <t>2026-09-11T22:42:45Z</t>
         </is>
       </c>
     </row>
@@ -3626,7 +3626,7 @@
       </c>
       <c r="S41" s="4" t="inlineStr">
         <is>
-          <t>2026-09-10T22:42:29Z</t>
+          <t>2026-09-11T22:42:45Z</t>
         </is>
       </c>
     </row>
@@ -3711,7 +3711,7 @@
       </c>
       <c r="S42" s="4" t="inlineStr">
         <is>
-          <t>2026-09-10T22:42:29Z</t>
+          <t>2026-09-11T22:42:45Z</t>
         </is>
       </c>
     </row>
@@ -3796,7 +3796,7 @@
       </c>
       <c r="S43" s="4" t="inlineStr">
         <is>
-          <t>2026-09-10T22:42:29Z</t>
+          <t>2026-09-11T22:42:45Z</t>
         </is>
       </c>
     </row>
@@ -3881,7 +3881,7 @@
       </c>
       <c r="S44" s="4" t="inlineStr">
         <is>
-          <t>2026-09-10T22:42:29Z</t>
+          <t>2026-09-11T22:42:45Z</t>
         </is>
       </c>
     </row>
@@ -3966,7 +3966,7 @@
       </c>
       <c r="S45" s="4" t="inlineStr">
         <is>
-          <t>2026-09-10T22:42:29Z</t>
+          <t>2026-09-11T22:42:45Z</t>
         </is>
       </c>
     </row>
@@ -4051,7 +4051,7 @@
       </c>
       <c r="S46" s="4" t="inlineStr">
         <is>
-          <t>2026-09-10T22:42:29Z</t>
+          <t>2026-09-11T22:42:45Z</t>
         </is>
       </c>
     </row>
@@ -4136,7 +4136,7 @@
       </c>
       <c r="S47" s="4" t="inlineStr">
         <is>
-          <t>2026-09-10T22:42:29Z</t>
+          <t>2026-09-11T22:42:45Z</t>
         </is>
       </c>
     </row>
@@ -4221,7 +4221,7 @@
       </c>
       <c r="S48" s="4" t="inlineStr">
         <is>
-          <t>2026-09-10T22:42:29Z</t>
+          <t>2026-09-11T22:42:45Z</t>
         </is>
       </c>
     </row>
@@ -4306,7 +4306,7 @@
       </c>
       <c r="S49" s="4" t="inlineStr">
         <is>
-          <t>2026-09-10T22:42:29Z</t>
+          <t>2026-09-11T22:42:45Z</t>
         </is>
       </c>
     </row>
@@ -4391,7 +4391,7 @@
       </c>
       <c r="S50" s="4" t="inlineStr">
         <is>
-          <t>2026-09-10T22:42:29Z</t>
+          <t>2026-09-11T22:42:45Z</t>
         </is>
       </c>
     </row>
@@ -4476,7 +4476,7 @@
       </c>
       <c r="S51" s="4" t="inlineStr">
         <is>
-          <t>2026-09-10T22:42:29Z</t>
+          <t>2026-09-11T22:42:45Z</t>
         </is>
       </c>
     </row>
@@ -4561,7 +4561,7 @@
       </c>
       <c r="S52" s="4" t="inlineStr">
         <is>
-          <t>2026-09-10T22:42:29Z</t>
+          <t>2026-09-11T22:42:45Z</t>
         </is>
       </c>
     </row>
@@ -4646,7 +4646,7 @@
       </c>
       <c r="S53" s="4" t="inlineStr">
         <is>
-          <t>2026-09-10T22:42:29Z</t>
+          <t>2026-09-11T22:42:45Z</t>
         </is>
       </c>
     </row>
@@ -4731,7 +4731,7 @@
       </c>
       <c r="S54" s="4" t="inlineStr">
         <is>
-          <t>2026-09-10T22:42:29Z</t>
+          <t>2026-09-11T22:42:45Z</t>
         </is>
       </c>
     </row>
@@ -4816,7 +4816,7 @@
       </c>
       <c r="S55" s="4" t="inlineStr">
         <is>
-          <t>2026-09-10T22:42:29Z</t>
+          <t>2026-09-11T22:42:45Z</t>
         </is>
       </c>
     </row>
@@ -4901,7 +4901,7 @@
       </c>
       <c r="S56" s="4" t="inlineStr">
         <is>
-          <t>2026-09-10T22:42:29Z</t>
+          <t>2026-09-11T22:42:45Z</t>
         </is>
       </c>
     </row>
@@ -4986,7 +4986,7 @@
       </c>
       <c r="S57" s="4" t="inlineStr">
         <is>
-          <t>2026-09-10T22:42:29Z</t>
+          <t>2026-09-11T22:42:45Z</t>
         </is>
       </c>
     </row>
@@ -5071,7 +5071,7 @@
       </c>
       <c r="S58" s="4" t="inlineStr">
         <is>
-          <t>2026-09-10T22:42:29Z</t>
+          <t>2026-09-11T22:42:45Z</t>
         </is>
       </c>
     </row>
@@ -5156,7 +5156,7 @@
       </c>
       <c r="S59" s="4" t="inlineStr">
         <is>
-          <t>2026-09-10T22:42:29Z</t>
+          <t>2026-09-11T22:42:45Z</t>
         </is>
       </c>
     </row>
@@ -5241,7 +5241,7 @@
       </c>
       <c r="S60" s="4" t="inlineStr">
         <is>
-          <t>2026-09-10T22:42:29Z</t>
+          <t>2026-09-11T22:42:45Z</t>
         </is>
       </c>
     </row>
@@ -5326,7 +5326,7 @@
       </c>
       <c r="S61" s="4" t="inlineStr">
         <is>
-          <t>2026-09-10T22:42:29Z</t>
+          <t>2026-09-11T22:42:45Z</t>
         </is>
       </c>
     </row>
@@ -5411,7 +5411,7 @@
       </c>
       <c r="S62" s="4" t="inlineStr">
         <is>
-          <t>2026-09-10T22:42:29Z</t>
+          <t>2026-09-11T22:42:45Z</t>
         </is>
       </c>
     </row>
@@ -5496,7 +5496,7 @@
       </c>
       <c r="S63" s="4" t="inlineStr">
         <is>
-          <t>2026-09-10T22:42:29Z</t>
+          <t>2026-09-11T22:42:45Z</t>
         </is>
       </c>
     </row>
@@ -5581,7 +5581,7 @@
       </c>
       <c r="S64" s="4" t="inlineStr">
         <is>
-          <t>2026-09-10T22:42:29Z</t>
+          <t>2026-09-11T22:42:45Z</t>
         </is>
       </c>
     </row>
@@ -5666,7 +5666,7 @@
       </c>
       <c r="S65" s="4" t="inlineStr">
         <is>
-          <t>2026-09-10T22:42:29Z</t>
+          <t>2026-09-11T22:42:45Z</t>
         </is>
       </c>
     </row>
@@ -5751,7 +5751,7 @@
       </c>
       <c r="S66" s="4" t="inlineStr">
         <is>
-          <t>2026-09-10T22:42:29Z</t>
+          <t>2026-09-11T22:42:45Z</t>
         </is>
       </c>
     </row>
@@ -5836,7 +5836,7 @@
       </c>
       <c r="S67" s="4" t="inlineStr">
         <is>
-          <t>2026-09-10T22:42:29Z</t>
+          <t>2026-09-11T22:42:45Z</t>
         </is>
       </c>
     </row>
@@ -5921,7 +5921,7 @@
       </c>
       <c r="S68" s="4" t="inlineStr">
         <is>
-          <t>2026-09-10T22:42:29Z</t>
+          <t>2026-09-11T22:42:45Z</t>
         </is>
       </c>
     </row>
@@ -6006,7 +6006,7 @@
       </c>
       <c r="S69" s="4" t="inlineStr">
         <is>
-          <t>2026-09-10T22:42:29Z</t>
+          <t>2026-09-11T22:42:45Z</t>
         </is>
       </c>
     </row>
@@ -6091,7 +6091,7 @@
       </c>
       <c r="S70" s="4" t="inlineStr">
         <is>
-          <t>2026-09-10T22:42:29Z</t>
+          <t>2026-09-11T22:42:45Z</t>
         </is>
       </c>
     </row>
@@ -6176,7 +6176,7 @@
       </c>
       <c r="S71" s="4" t="inlineStr">
         <is>
-          <t>2026-09-10T22:42:29Z</t>
+          <t>2026-09-11T22:42:45Z</t>
         </is>
       </c>
     </row>
@@ -6261,7 +6261,7 @@
       </c>
       <c r="S72" s="4" t="inlineStr">
         <is>
-          <t>2026-09-10T22:42:29Z</t>
+          <t>2026-09-11T22:42:45Z</t>
         </is>
       </c>
     </row>
@@ -6346,7 +6346,7 @@
       </c>
       <c r="S73" s="4" t="inlineStr">
         <is>
-          <t>2026-09-10T22:42:29Z</t>
+          <t>2026-09-11T22:42:45Z</t>
         </is>
       </c>
     </row>
@@ -6431,7 +6431,7 @@
       </c>
       <c r="S74" s="4" t="inlineStr">
         <is>
-          <t>2026-09-10T22:42:29Z</t>
+          <t>2026-09-11T22:42:45Z</t>
         </is>
       </c>
     </row>
@@ -6516,7 +6516,7 @@
       </c>
       <c r="S75" s="4" t="inlineStr">
         <is>
-          <t>2026-09-10T22:42:29Z</t>
+          <t>2026-09-11T22:42:45Z</t>
         </is>
       </c>
     </row>
@@ -6601,7 +6601,7 @@
       </c>
       <c r="S76" s="4" t="inlineStr">
         <is>
-          <t>2026-09-10T22:42:29Z</t>
+          <t>2026-09-11T22:42:45Z</t>
         </is>
       </c>
     </row>
@@ -6686,7 +6686,7 @@
       </c>
       <c r="S77" s="4" t="inlineStr">
         <is>
-          <t>2026-09-10T22:42:29Z</t>
+          <t>2026-09-11T22:42:45Z</t>
         </is>
       </c>
     </row>
@@ -6771,7 +6771,7 @@
       </c>
       <c r="S78" s="4" t="inlineStr">
         <is>
-          <t>2026-09-10T22:42:29Z</t>
+          <t>2026-09-11T22:42:45Z</t>
         </is>
       </c>
     </row>
@@ -6856,7 +6856,7 @@
       </c>
       <c r="S79" s="4" t="inlineStr">
         <is>
-          <t>2026-09-10T22:42:29Z</t>
+          <t>2026-09-11T22:42:45Z</t>
         </is>
       </c>
     </row>
@@ -6941,7 +6941,7 @@
       </c>
       <c r="S80" s="4" t="inlineStr">
         <is>
-          <t>2026-09-10T22:42:29Z</t>
+          <t>2026-09-11T22:42:45Z</t>
         </is>
       </c>
     </row>
@@ -7026,7 +7026,7 @@
       </c>
       <c r="S81" s="4" t="inlineStr">
         <is>
-          <t>2026-09-10T22:42:29Z</t>
+          <t>2026-09-11T22:42:45Z</t>
         </is>
       </c>
     </row>
@@ -7111,7 +7111,7 @@
       </c>
       <c r="S82" s="4" t="inlineStr">
         <is>
-          <t>2026-09-10T22:42:29Z</t>
+          <t>2026-09-11T22:42:45Z</t>
         </is>
       </c>
     </row>
@@ -7196,7 +7196,7 @@
       </c>
       <c r="S83" s="4" t="inlineStr">
         <is>
-          <t>2026-09-10T22:42:29Z</t>
+          <t>2026-09-11T22:42:45Z</t>
         </is>
       </c>
     </row>
@@ -7281,7 +7281,7 @@
       </c>
       <c r="S84" s="4" t="inlineStr">
         <is>
-          <t>2026-09-10T22:42:29Z</t>
+          <t>2026-09-11T22:42:45Z</t>
         </is>
       </c>
     </row>
@@ -7366,7 +7366,7 @@
       </c>
       <c r="S85" s="4" t="inlineStr">
         <is>
-          <t>2026-09-10T22:42:29Z</t>
+          <t>2026-09-11T22:42:45Z</t>
         </is>
       </c>
     </row>
@@ -7451,7 +7451,7 @@
       </c>
       <c r="S86" s="4" t="inlineStr">
         <is>
-          <t>2026-09-10T22:42:29Z</t>
+          <t>2026-09-11T22:42:45Z</t>
         </is>
       </c>
     </row>
@@ -7536,7 +7536,7 @@
       </c>
       <c r="S87" s="4" t="inlineStr">
         <is>
-          <t>2026-09-10T22:42:29Z</t>
+          <t>2026-09-11T22:42:45Z</t>
         </is>
       </c>
     </row>
@@ -7621,7 +7621,7 @@
       </c>
       <c r="S88" s="4" t="inlineStr">
         <is>
-          <t>2026-09-10T22:42:29Z</t>
+          <t>2026-09-11T22:42:45Z</t>
         </is>
       </c>
     </row>
@@ -7706,7 +7706,7 @@
       </c>
       <c r="S89" s="4" t="inlineStr">
         <is>
-          <t>2026-09-10T22:42:29Z</t>
+          <t>2026-09-11T22:42:45Z</t>
         </is>
       </c>
     </row>
@@ -7791,7 +7791,7 @@
       </c>
       <c r="S90" s="4" t="inlineStr">
         <is>
-          <t>2026-09-10T22:42:29Z</t>
+          <t>2026-09-11T22:42:45Z</t>
         </is>
       </c>
     </row>
@@ -7876,7 +7876,7 @@
       </c>
       <c r="S91" s="4" t="inlineStr">
         <is>
-          <t>2026-09-10T22:42:29Z</t>
+          <t>2026-09-11T22:42:45Z</t>
         </is>
       </c>
     </row>
@@ -7961,7 +7961,7 @@
       </c>
       <c r="S92" s="4" t="inlineStr">
         <is>
-          <t>2026-09-10T22:42:29Z</t>
+          <t>2026-09-11T22:42:45Z</t>
         </is>
       </c>
     </row>
@@ -8046,7 +8046,7 @@
       </c>
       <c r="S93" s="4" t="inlineStr">
         <is>
-          <t>2026-09-10T22:42:29Z</t>
+          <t>2026-09-11T22:42:45Z</t>
         </is>
       </c>
     </row>
@@ -8131,7 +8131,7 @@
       </c>
       <c r="S94" s="4" t="inlineStr">
         <is>
-          <t>2026-09-10T22:42:29Z</t>
+          <t>2026-09-11T22:42:45Z</t>
         </is>
       </c>
     </row>
@@ -8216,7 +8216,7 @@
       </c>
       <c r="S95" s="4" t="inlineStr">
         <is>
-          <t>2026-09-10T22:42:29Z</t>
+          <t>2026-09-11T22:42:45Z</t>
         </is>
       </c>
     </row>
@@ -8301,7 +8301,7 @@
       </c>
       <c r="S96" s="4" t="inlineStr">
         <is>
-          <t>2026-09-10T22:42:29Z</t>
+          <t>2026-09-11T22:42:45Z</t>
         </is>
       </c>
     </row>
@@ -8386,7 +8386,7 @@
       </c>
       <c r="S97" s="4" t="inlineStr">
         <is>
-          <t>2026-09-10T22:42:29Z</t>
+          <t>2026-09-11T22:42:45Z</t>
         </is>
       </c>
     </row>
@@ -8471,7 +8471,7 @@
       </c>
       <c r="S98" s="4" t="inlineStr">
         <is>
-          <t>2026-09-10T22:42:29Z</t>
+          <t>2026-09-11T22:42:45Z</t>
         </is>
       </c>
     </row>
@@ -8556,7 +8556,7 @@
       </c>
       <c r="S99" s="4" t="inlineStr">
         <is>
-          <t>2026-09-10T22:42:29Z</t>
+          <t>2026-09-11T22:42:45Z</t>
         </is>
       </c>
     </row>
@@ -8641,7 +8641,7 @@
       </c>
       <c r="S100" s="4" t="inlineStr">
         <is>
-          <t>2026-09-10T22:42:29Z</t>
+          <t>2026-09-11T22:42:45Z</t>
         </is>
       </c>
     </row>
@@ -8726,7 +8726,7 @@
       </c>
       <c r="S101" s="4" t="inlineStr">
         <is>
-          <t>2026-09-10T22:42:29Z</t>
+          <t>2026-09-11T22:42:45Z</t>
         </is>
       </c>
     </row>
@@ -8811,7 +8811,7 @@
       </c>
       <c r="S102" s="4" t="inlineStr">
         <is>
-          <t>2026-09-10T22:42:29Z</t>
+          <t>2026-09-11T22:42:45Z</t>
         </is>
       </c>
     </row>
@@ -8896,7 +8896,7 @@
       </c>
       <c r="S103" s="4" t="inlineStr">
         <is>
-          <t>2026-09-10T22:42:29Z</t>
+          <t>2026-09-11T22:42:45Z</t>
         </is>
       </c>
     </row>
@@ -8981,7 +8981,7 @@
       </c>
       <c r="S104" s="4" t="inlineStr">
         <is>
-          <t>2026-09-10T22:42:29Z</t>
+          <t>2026-09-11T22:42:45Z</t>
         </is>
       </c>
     </row>
@@ -9066,7 +9066,7 @@
       </c>
       <c r="S105" s="4" t="inlineStr">
         <is>
-          <t>2026-09-10T22:42:29Z</t>
+          <t>2026-09-11T22:42:45Z</t>
         </is>
       </c>
     </row>
@@ -9151,7 +9151,7 @@
       </c>
       <c r="S106" s="4" t="inlineStr">
         <is>
-          <t>2026-09-10T22:42:29Z</t>
+          <t>2026-09-11T22:42:45Z</t>
         </is>
       </c>
     </row>
@@ -9236,7 +9236,7 @@
       </c>
       <c r="S107" s="4" t="inlineStr">
         <is>
-          <t>2026-09-10T22:42:29Z</t>
+          <t>2026-09-11T22:42:45Z</t>
         </is>
       </c>
     </row>
@@ -9321,7 +9321,7 @@
       </c>
       <c r="S108" s="4" t="inlineStr">
         <is>
-          <t>2026-09-10T22:42:29Z</t>
+          <t>2026-09-11T22:42:45Z</t>
         </is>
       </c>
     </row>
@@ -9406,7 +9406,7 @@
       </c>
       <c r="S109" s="4" t="inlineStr">
         <is>
-          <t>2026-09-10T22:42:29Z</t>
+          <t>2026-09-11T22:42:45Z</t>
         </is>
       </c>
     </row>
@@ -9491,7 +9491,7 @@
       </c>
       <c r="S110" s="4" t="inlineStr">
         <is>
-          <t>2026-09-10T22:42:29Z</t>
+          <t>2026-09-11T22:42:45Z</t>
         </is>
       </c>
     </row>
@@ -9576,7 +9576,7 @@
       </c>
       <c r="S111" s="4" t="inlineStr">
         <is>
-          <t>2026-09-10T22:42:29Z</t>
+          <t>2026-09-11T22:42:45Z</t>
         </is>
       </c>
     </row>
@@ -9661,7 +9661,7 @@
       </c>
       <c r="S112" s="4" t="inlineStr">
         <is>
-          <t>2026-09-10T22:42:29Z</t>
+          <t>2026-09-11T22:42:45Z</t>
         </is>
       </c>
     </row>
@@ -9746,7 +9746,7 @@
       </c>
       <c r="S113" s="4" t="inlineStr">
         <is>
-          <t>2026-09-10T22:42:29Z</t>
+          <t>2026-09-11T22:42:45Z</t>
         </is>
       </c>
     </row>
@@ -9831,7 +9831,7 @@
       </c>
       <c r="S114" s="4" t="inlineStr">
         <is>
-          <t>2026-09-10T22:42:29Z</t>
+          <t>2026-09-11T22:42:45Z</t>
         </is>
       </c>
     </row>
@@ -9916,7 +9916,7 @@
       </c>
       <c r="S115" s="4" t="inlineStr">
         <is>
-          <t>2026-09-10T22:42:29Z</t>
+          <t>2026-09-11T22:42:45Z</t>
         </is>
       </c>
     </row>
@@ -10001,7 +10001,7 @@
       </c>
       <c r="S116" s="4" t="inlineStr">
         <is>
-          <t>2026-09-10T22:42:29Z</t>
+          <t>2026-09-11T22:42:45Z</t>
         </is>
       </c>
     </row>
@@ -10086,7 +10086,7 @@
       </c>
       <c r="S117" s="4" t="inlineStr">
         <is>
-          <t>2026-09-10T22:42:29Z</t>
+          <t>2026-09-11T22:42:45Z</t>
         </is>
       </c>
     </row>
@@ -10171,7 +10171,7 @@
       </c>
       <c r="S118" s="4" t="inlineStr">
         <is>
-          <t>2026-09-10T22:42:29Z</t>
+          <t>2026-09-11T22:42:45Z</t>
         </is>
       </c>
     </row>
@@ -10256,7 +10256,7 @@
       </c>
       <c r="S119" s="4" t="inlineStr">
         <is>
-          <t>2026-09-10T22:42:29Z</t>
+          <t>2026-09-11T22:42:45Z</t>
         </is>
       </c>
     </row>
@@ -10341,7 +10341,7 @@
       </c>
       <c r="S120" s="4" t="inlineStr">
         <is>
-          <t>2026-09-10T22:42:29Z</t>
+          <t>2026-09-11T22:42:45Z</t>
         </is>
       </c>
     </row>
@@ -10426,7 +10426,7 @@
       </c>
       <c r="S121" s="4" t="inlineStr">
         <is>
-          <t>2026-09-10T22:42:29Z</t>
+          <t>2026-09-11T22:42:45Z</t>
         </is>
       </c>
     </row>
@@ -10511,7 +10511,7 @@
       </c>
       <c r="S122" s="4" t="inlineStr">
         <is>
-          <t>2026-09-10T22:42:29Z</t>
+          <t>2026-09-11T22:42:45Z</t>
         </is>
       </c>
     </row>
@@ -10596,7 +10596,7 @@
       </c>
       <c r="S123" s="4" t="inlineStr">
         <is>
-          <t>2026-09-10T22:42:29Z</t>
+          <t>2026-09-11T22:42:45Z</t>
         </is>
       </c>
     </row>
@@ -10681,7 +10681,7 @@
       </c>
       <c r="S124" s="4" t="inlineStr">
         <is>
-          <t>2026-09-10T22:42:29Z</t>
+          <t>2026-09-11T22:42:45Z</t>
         </is>
       </c>
     </row>
@@ -10766,7 +10766,7 @@
       </c>
       <c r="S125" s="4" t="inlineStr">
         <is>
-          <t>2026-09-10T22:42:29Z</t>
+          <t>2026-09-11T22:42:45Z</t>
         </is>
       </c>
     </row>
@@ -10851,7 +10851,7 @@
       </c>
       <c r="S126" s="4" t="inlineStr">
         <is>
-          <t>2026-09-10T22:42:29Z</t>
+          <t>2026-09-11T22:42:45Z</t>
         </is>
       </c>
     </row>
@@ -10936,7 +10936,7 @@
       </c>
       <c r="S127" s="4" t="inlineStr">
         <is>
-          <t>2026-09-10T22:42:29Z</t>
+          <t>2026-09-11T22:42:45Z</t>
         </is>
       </c>
     </row>
@@ -11021,7 +11021,7 @@
       </c>
       <c r="S128" s="4" t="inlineStr">
         <is>
-          <t>2026-09-10T22:42:29Z</t>
+          <t>2026-09-11T22:42:45Z</t>
         </is>
       </c>
     </row>
@@ -11106,7 +11106,7 @@
       </c>
       <c r="S129" s="4" t="inlineStr">
         <is>
-          <t>2026-09-10T22:42:29Z</t>
+          <t>2026-09-11T22:42:45Z</t>
         </is>
       </c>
     </row>
@@ -11191,7 +11191,7 @@
       </c>
       <c r="S130" s="4" t="inlineStr">
         <is>
-          <t>2026-09-10T22:42:29Z</t>
+          <t>2026-09-11T22:42:45Z</t>
         </is>
       </c>
     </row>
@@ -11276,7 +11276,7 @@
       </c>
       <c r="S131" s="4" t="inlineStr">
         <is>
-          <t>2026-09-10T22:42:29Z</t>
+          <t>2026-09-11T22:42:45Z</t>
         </is>
       </c>
     </row>
@@ -11361,7 +11361,7 @@
       </c>
       <c r="S132" s="4" t="inlineStr">
         <is>
-          <t>2026-09-10T22:42:29Z</t>
+          <t>2026-09-11T22:42:45Z</t>
         </is>
       </c>
     </row>
@@ -11446,7 +11446,7 @@
       </c>
       <c r="S133" s="4" t="inlineStr">
         <is>
-          <t>2026-09-10T22:42:29Z</t>
+          <t>2026-09-11T22:42:45Z</t>
         </is>
       </c>
     </row>
@@ -11531,7 +11531,7 @@
       </c>
       <c r="S134" s="4" t="inlineStr">
         <is>
-          <t>2026-09-10T22:42:29Z</t>
+          <t>2026-09-11T22:42:45Z</t>
         </is>
       </c>
     </row>
@@ -11616,7 +11616,7 @@
       </c>
       <c r="S135" s="4" t="inlineStr">
         <is>
-          <t>2026-09-10T22:42:29Z</t>
+          <t>2026-09-11T22:42:45Z</t>
         </is>
       </c>
     </row>
@@ -11701,7 +11701,7 @@
       </c>
       <c r="S136" s="4" t="inlineStr">
         <is>
-          <t>2026-09-10T22:42:29Z</t>
+          <t>2026-09-11T22:42:45Z</t>
         </is>
       </c>
     </row>
@@ -11786,7 +11786,7 @@
       </c>
       <c r="S137" s="4" t="inlineStr">
         <is>
-          <t>2026-09-10T22:42:29Z</t>
+          <t>2026-09-11T22:42:45Z</t>
         </is>
       </c>
     </row>
@@ -11871,7 +11871,7 @@
       </c>
       <c r="S138" s="4" t="inlineStr">
         <is>
-          <t>2026-09-10T22:42:29Z</t>
+          <t>2026-09-11T22:42:45Z</t>
         </is>
       </c>
     </row>
@@ -11956,7 +11956,7 @@
       </c>
       <c r="S139" s="4" t="inlineStr">
         <is>
-          <t>2026-09-10T22:42:29Z</t>
+          <t>2026-09-11T22:42:45Z</t>
         </is>
       </c>
     </row>
@@ -12041,7 +12041,7 @@
       </c>
       <c r="S140" s="4" t="inlineStr">
         <is>
-          <t>2026-09-10T22:42:29Z</t>
+          <t>2026-09-11T22:42:45Z</t>
         </is>
       </c>
     </row>
@@ -12126,7 +12126,7 @@
       </c>
       <c r="S141" s="4" t="inlineStr">
         <is>
-          <t>2026-09-10T22:42:29Z</t>
+          <t>2026-09-11T22:42:45Z</t>
         </is>
       </c>
     </row>
@@ -12258,7 +12258,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>2026-09-10T22:42:29Z</t>
+          <t>2026-09-11T22:42:45Z</t>
         </is>
       </c>
     </row>
@@ -12338,7 +12338,7 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>{"dataset_id": "bcv_pib_historico_anual", "title": "Producto interno bruto histórico anual", "table": "PIB histórico anual", "source_file": "7_1_14_anual.xls", "base": "1957/1968/1984/1997", "price_type": "Precios constantes", "measure": "Nivel", "frequency": "Anual", "period": "2017", "year": 2017, "quarter": null, "classification": "Total economía", "component": "Producto interno bruto", "value": 392393.12, "unit": "Millones de bolívares a precios constantes", "status": "", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/7_1_14_anual.xls", "fetched_at": "2026-09-10T22:42:29Z"}</t>
+          <t>{"dataset_id": "bcv_pib_historico_anual", "title": "Producto interno bruto histórico anual", "table": "PIB histórico anual", "source_file": "7_1_14_anual.xls", "base": "1957/1968/1984/1997", "price_type": "Precios constantes", "measure": "Nivel", "frequency": "Anual", "period": "2017", "year": 2017, "quarter": null, "classification": "Total economía", "component": "Producto interno bruto", "value": 392393.12, "unit": "Millones de bolívares a precios constantes", "status": "", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/7_1_14_anual.xls", "fetched_at": "2026-09-11T22:42:45Z"}</t>
         </is>
       </c>
     </row>

--- a/assets/data/bcv/excel/ove_bcv_pib_historico_anual.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_pib_historico_anual.xlsx
@@ -736,7 +736,7 @@
       </c>
       <c r="S7" s="4" t="inlineStr">
         <is>
-          <t>2026-09-11T22:42:45Z</t>
+          <t>2026-09-12T16:18:28Z</t>
         </is>
       </c>
     </row>
@@ -821,7 +821,7 @@
       </c>
       <c r="S8" s="4" t="inlineStr">
         <is>
-          <t>2026-09-11T22:42:45Z</t>
+          <t>2026-09-12T16:18:28Z</t>
         </is>
       </c>
     </row>
@@ -906,7 +906,7 @@
       </c>
       <c r="S9" s="4" t="inlineStr">
         <is>
-          <t>2026-09-11T22:42:45Z</t>
+          <t>2026-09-12T16:18:28Z</t>
         </is>
       </c>
     </row>
@@ -991,7 +991,7 @@
       </c>
       <c r="S10" s="4" t="inlineStr">
         <is>
-          <t>2026-09-11T22:42:45Z</t>
+          <t>2026-09-12T16:18:28Z</t>
         </is>
       </c>
     </row>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="S11" s="4" t="inlineStr">
         <is>
-          <t>2026-09-11T22:42:45Z</t>
+          <t>2026-09-12T16:18:28Z</t>
         </is>
       </c>
     </row>
@@ -1161,7 +1161,7 @@
       </c>
       <c r="S12" s="4" t="inlineStr">
         <is>
-          <t>2026-09-11T22:42:45Z</t>
+          <t>2026-09-12T16:18:28Z</t>
         </is>
       </c>
     </row>
@@ -1246,7 +1246,7 @@
       </c>
       <c r="S13" s="4" t="inlineStr">
         <is>
-          <t>2026-09-11T22:42:45Z</t>
+          <t>2026-09-12T16:18:28Z</t>
         </is>
       </c>
     </row>
@@ -1331,7 +1331,7 @@
       </c>
       <c r="S14" s="4" t="inlineStr">
         <is>
-          <t>2026-09-11T22:42:45Z</t>
+          <t>2026-09-12T16:18:28Z</t>
         </is>
       </c>
     </row>
@@ -1416,7 +1416,7 @@
       </c>
       <c r="S15" s="4" t="inlineStr">
         <is>
-          <t>2026-09-11T22:42:45Z</t>
+          <t>2026-09-12T16:18:28Z</t>
         </is>
       </c>
     </row>
@@ -1501,7 +1501,7 @@
       </c>
       <c r="S16" s="4" t="inlineStr">
         <is>
-          <t>2026-09-11T22:42:45Z</t>
+          <t>2026-09-12T16:18:28Z</t>
         </is>
       </c>
     </row>
@@ -1586,7 +1586,7 @@
       </c>
       <c r="S17" s="4" t="inlineStr">
         <is>
-          <t>2026-09-11T22:42:45Z</t>
+          <t>2026-09-12T16:18:28Z</t>
         </is>
       </c>
     </row>
@@ -1671,7 +1671,7 @@
       </c>
       <c r="S18" s="4" t="inlineStr">
         <is>
-          <t>2026-09-11T22:42:45Z</t>
+          <t>2026-09-12T16:18:28Z</t>
         </is>
       </c>
     </row>
@@ -1756,7 +1756,7 @@
       </c>
       <c r="S19" s="4" t="inlineStr">
         <is>
-          <t>2026-09-11T22:42:45Z</t>
+          <t>2026-09-12T16:18:28Z</t>
         </is>
       </c>
     </row>
@@ -1841,7 +1841,7 @@
       </c>
       <c r="S20" s="4" t="inlineStr">
         <is>
-          <t>2026-09-11T22:42:45Z</t>
+          <t>2026-09-12T16:18:28Z</t>
         </is>
       </c>
     </row>
@@ -1926,7 +1926,7 @@
       </c>
       <c r="S21" s="4" t="inlineStr">
         <is>
-          <t>2026-09-11T22:42:45Z</t>
+          <t>2026-09-12T16:18:28Z</t>
         </is>
       </c>
     </row>
@@ -2011,7 +2011,7 @@
       </c>
       <c r="S22" s="4" t="inlineStr">
         <is>
-          <t>2026-09-11T22:42:45Z</t>
+          <t>2026-09-12T16:18:28Z</t>
         </is>
       </c>
     </row>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="S23" s="4" t="inlineStr">
         <is>
-          <t>2026-09-11T22:42:45Z</t>
+          <t>2026-09-12T16:18:28Z</t>
         </is>
       </c>
     </row>
@@ -2181,7 +2181,7 @@
       </c>
       <c r="S24" s="4" t="inlineStr">
         <is>
-          <t>2026-09-11T22:42:45Z</t>
+          <t>2026-09-12T16:18:28Z</t>
         </is>
       </c>
     </row>
@@ -2266,7 +2266,7 @@
       </c>
       <c r="S25" s="4" t="inlineStr">
         <is>
-          <t>2026-09-11T22:42:45Z</t>
+          <t>2026-09-12T16:18:28Z</t>
         </is>
       </c>
     </row>
@@ -2351,7 +2351,7 @@
       </c>
       <c r="S26" s="4" t="inlineStr">
         <is>
-          <t>2026-09-11T22:42:45Z</t>
+          <t>2026-09-12T16:18:28Z</t>
         </is>
       </c>
     </row>
@@ -2436,7 +2436,7 @@
       </c>
       <c r="S27" s="4" t="inlineStr">
         <is>
-          <t>2026-09-11T22:42:45Z</t>
+          <t>2026-09-12T16:18:28Z</t>
         </is>
       </c>
     </row>
@@ -2521,7 +2521,7 @@
       </c>
       <c r="S28" s="4" t="inlineStr">
         <is>
-          <t>2026-09-11T22:42:45Z</t>
+          <t>2026-09-12T16:18:28Z</t>
         </is>
       </c>
     </row>
@@ -2606,7 +2606,7 @@
       </c>
       <c r="S29" s="4" t="inlineStr">
         <is>
-          <t>2026-09-11T22:42:45Z</t>
+          <t>2026-09-12T16:18:28Z</t>
         </is>
       </c>
     </row>
@@ -2691,7 +2691,7 @@
       </c>
       <c r="S30" s="4" t="inlineStr">
         <is>
-          <t>2026-09-11T22:42:45Z</t>
+          <t>2026-09-12T16:18:28Z</t>
         </is>
       </c>
     </row>
@@ -2776,7 +2776,7 @@
       </c>
       <c r="S31" s="4" t="inlineStr">
         <is>
-          <t>2026-09-11T22:42:45Z</t>
+          <t>2026-09-12T16:18:28Z</t>
         </is>
       </c>
     </row>
@@ -2861,7 +2861,7 @@
       </c>
       <c r="S32" s="4" t="inlineStr">
         <is>
-          <t>2026-09-11T22:42:45Z</t>
+          <t>2026-09-12T16:18:28Z</t>
         </is>
       </c>
     </row>
@@ -2946,7 +2946,7 @@
       </c>
       <c r="S33" s="4" t="inlineStr">
         <is>
-          <t>2026-09-11T22:42:45Z</t>
+          <t>2026-09-12T16:18:28Z</t>
         </is>
       </c>
     </row>
@@ -3031,7 +3031,7 @@
       </c>
       <c r="S34" s="4" t="inlineStr">
         <is>
-          <t>2026-09-11T22:42:45Z</t>
+          <t>2026-09-12T16:18:28Z</t>
         </is>
       </c>
     </row>
@@ -3116,7 +3116,7 @@
       </c>
       <c r="S35" s="4" t="inlineStr">
         <is>
-          <t>2026-09-11T22:42:45Z</t>
+          <t>2026-09-12T16:18:28Z</t>
         </is>
       </c>
     </row>
@@ -3201,7 +3201,7 @@
       </c>
       <c r="S36" s="4" t="inlineStr">
         <is>
-          <t>2026-09-11T22:42:45Z</t>
+          <t>2026-09-12T16:18:28Z</t>
         </is>
       </c>
     </row>
@@ -3286,7 +3286,7 @@
       </c>
       <c r="S37" s="4" t="inlineStr">
         <is>
-          <t>2026-09-11T22:42:45Z</t>
+          <t>2026-09-12T16:18:28Z</t>
         </is>
       </c>
     </row>
@@ -3371,7 +3371,7 @@
       </c>
       <c r="S38" s="4" t="inlineStr">
         <is>
-          <t>2026-09-11T22:42:45Z</t>
+          <t>2026-09-12T16:18:28Z</t>
         </is>
       </c>
     </row>
@@ -3456,7 +3456,7 @@
       </c>
       <c r="S39" s="4" t="inlineStr">
         <is>
-          <t>2026-09-11T22:42:45Z</t>
+          <t>2026-09-12T16:18:28Z</t>
         </is>
       </c>
     </row>
@@ -3541,7 +3541,7 @@
       </c>
       <c r="S40" s="4" t="inlineStr">
         <is>
-          <t>2026-09-11T22:42:45Z</t>
+          <t>2026-09-12T16:18:28Z</t>
         </is>
       </c>
     </row>
@@ -3626,7 +3626,7 @@
       </c>
       <c r="S41" s="4" t="inlineStr">
         <is>
-          <t>2026-09-11T22:42:45Z</t>
+          <t>2026-09-12T16:18:28Z</t>
         </is>
       </c>
     </row>
@@ -3711,7 +3711,7 @@
       </c>
       <c r="S42" s="4" t="inlineStr">
         <is>
-          <t>2026-09-11T22:42:45Z</t>
+          <t>2026-09-12T16:18:28Z</t>
         </is>
       </c>
     </row>
@@ -3796,7 +3796,7 @@
       </c>
       <c r="S43" s="4" t="inlineStr">
         <is>
-          <t>2026-09-11T22:42:45Z</t>
+          <t>2026-09-12T16:18:28Z</t>
         </is>
       </c>
     </row>
@@ -3881,7 +3881,7 @@
       </c>
       <c r="S44" s="4" t="inlineStr">
         <is>
-          <t>2026-09-11T22:42:45Z</t>
+          <t>2026-09-12T16:18:28Z</t>
         </is>
       </c>
     </row>
@@ -3966,7 +3966,7 @@
       </c>
       <c r="S45" s="4" t="inlineStr">
         <is>
-          <t>2026-09-11T22:42:45Z</t>
+          <t>2026-09-12T16:18:28Z</t>
         </is>
       </c>
     </row>
@@ -4051,7 +4051,7 @@
       </c>
       <c r="S46" s="4" t="inlineStr">
         <is>
-          <t>2026-09-11T22:42:45Z</t>
+          <t>2026-09-12T16:18:28Z</t>
         </is>
       </c>
     </row>
@@ -4136,7 +4136,7 @@
       </c>
       <c r="S47" s="4" t="inlineStr">
         <is>
-          <t>2026-09-11T22:42:45Z</t>
+          <t>2026-09-12T16:18:28Z</t>
         </is>
       </c>
     </row>
@@ -4221,7 +4221,7 @@
       </c>
       <c r="S48" s="4" t="inlineStr">
         <is>
-          <t>2026-09-11T22:42:45Z</t>
+          <t>2026-09-12T16:18:28Z</t>
         </is>
       </c>
     </row>
@@ -4306,7 +4306,7 @@
       </c>
       <c r="S49" s="4" t="inlineStr">
         <is>
-          <t>2026-09-11T22:42:45Z</t>
+          <t>2026-09-12T16:18:28Z</t>
         </is>
       </c>
     </row>
@@ -4391,7 +4391,7 @@
       </c>
       <c r="S50" s="4" t="inlineStr">
         <is>
-          <t>2026-09-11T22:42:45Z</t>
+          <t>2026-09-12T16:18:28Z</t>
         </is>
       </c>
     </row>
@@ -4476,7 +4476,7 @@
       </c>
       <c r="S51" s="4" t="inlineStr">
         <is>
-          <t>2026-09-11T22:42:45Z</t>
+          <t>2026-09-12T16:18:28Z</t>
         </is>
       </c>
     </row>
@@ -4561,7 +4561,7 @@
       </c>
       <c r="S52" s="4" t="inlineStr">
         <is>
-          <t>2026-09-11T22:42:45Z</t>
+          <t>2026-09-12T16:18:28Z</t>
         </is>
       </c>
     </row>
@@ -4646,7 +4646,7 @@
       </c>
       <c r="S53" s="4" t="inlineStr">
         <is>
-          <t>2026-09-11T22:42:45Z</t>
+          <t>2026-09-12T16:18:28Z</t>
         </is>
       </c>
     </row>
@@ -4731,7 +4731,7 @@
       </c>
       <c r="S54" s="4" t="inlineStr">
         <is>
-          <t>2026-09-11T22:42:45Z</t>
+          <t>2026-09-12T16:18:28Z</t>
         </is>
       </c>
     </row>
@@ -4816,7 +4816,7 @@
       </c>
       <c r="S55" s="4" t="inlineStr">
         <is>
-          <t>2026-09-11T22:42:45Z</t>
+          <t>2026-09-12T16:18:28Z</t>
         </is>
       </c>
     </row>
@@ -4901,7 +4901,7 @@
       </c>
       <c r="S56" s="4" t="inlineStr">
         <is>
-          <t>2026-09-11T22:42:45Z</t>
+          <t>2026-09-12T16:18:28Z</t>
         </is>
       </c>
     </row>
@@ -4986,7 +4986,7 @@
       </c>
       <c r="S57" s="4" t="inlineStr">
         <is>
-          <t>2026-09-11T22:42:45Z</t>
+          <t>2026-09-12T16:18:28Z</t>
         </is>
       </c>
     </row>
@@ -5071,7 +5071,7 @@
       </c>
       <c r="S58" s="4" t="inlineStr">
         <is>
-          <t>2026-09-11T22:42:45Z</t>
+          <t>2026-09-12T16:18:28Z</t>
         </is>
       </c>
     </row>
@@ -5156,7 +5156,7 @@
       </c>
       <c r="S59" s="4" t="inlineStr">
         <is>
-          <t>2026-09-11T22:42:45Z</t>
+          <t>2026-09-12T16:18:28Z</t>
         </is>
       </c>
     </row>
@@ -5241,7 +5241,7 @@
       </c>
       <c r="S60" s="4" t="inlineStr">
         <is>
-          <t>2026-09-11T22:42:45Z</t>
+          <t>2026-09-12T16:18:28Z</t>
         </is>
       </c>
     </row>
@@ -5326,7 +5326,7 @@
       </c>
       <c r="S61" s="4" t="inlineStr">
         <is>
-          <t>2026-09-11T22:42:45Z</t>
+          <t>2026-09-12T16:18:28Z</t>
         </is>
       </c>
     </row>
@@ -5411,7 +5411,7 @@
       </c>
       <c r="S62" s="4" t="inlineStr">
         <is>
-          <t>2026-09-11T22:42:45Z</t>
+          <t>2026-09-12T16:18:28Z</t>
         </is>
       </c>
     </row>
@@ -5496,7 +5496,7 @@
       </c>
       <c r="S63" s="4" t="inlineStr">
         <is>
-          <t>2026-09-11T22:42:45Z</t>
+          <t>2026-09-12T16:18:28Z</t>
         </is>
       </c>
     </row>
@@ -5581,7 +5581,7 @@
       </c>
       <c r="S64" s="4" t="inlineStr">
         <is>
-          <t>2026-09-11T22:42:45Z</t>
+          <t>2026-09-12T16:18:28Z</t>
         </is>
       </c>
     </row>
@@ -5666,7 +5666,7 @@
       </c>
       <c r="S65" s="4" t="inlineStr">
         <is>
-          <t>2026-09-11T22:42:45Z</t>
+          <t>2026-09-12T16:18:28Z</t>
         </is>
       </c>
     </row>
@@ -5751,7 +5751,7 @@
       </c>
       <c r="S66" s="4" t="inlineStr">
         <is>
-          <t>2026-09-11T22:42:45Z</t>
+          <t>2026-09-12T16:18:28Z</t>
         </is>
       </c>
     </row>
@@ -5836,7 +5836,7 @@
       </c>
       <c r="S67" s="4" t="inlineStr">
         <is>
-          <t>2026-09-11T22:42:45Z</t>
+          <t>2026-09-12T16:18:28Z</t>
         </is>
       </c>
     </row>
@@ -5921,7 +5921,7 @@
       </c>
       <c r="S68" s="4" t="inlineStr">
         <is>
-          <t>2026-09-11T22:42:45Z</t>
+          <t>2026-09-12T16:18:28Z</t>
         </is>
       </c>
     </row>
@@ -6006,7 +6006,7 @@
       </c>
       <c r="S69" s="4" t="inlineStr">
         <is>
-          <t>2026-09-11T22:42:45Z</t>
+          <t>2026-09-12T16:18:28Z</t>
         </is>
       </c>
     </row>
@@ -6091,7 +6091,7 @@
       </c>
       <c r="S70" s="4" t="inlineStr">
         <is>
-          <t>2026-09-11T22:42:45Z</t>
+          <t>2026-09-12T16:18:28Z</t>
         </is>
       </c>
     </row>
@@ -6176,7 +6176,7 @@
       </c>
       <c r="S71" s="4" t="inlineStr">
         <is>
-          <t>2026-09-11T22:42:45Z</t>
+          <t>2026-09-12T16:18:28Z</t>
         </is>
       </c>
     </row>
@@ -6261,7 +6261,7 @@
       </c>
       <c r="S72" s="4" t="inlineStr">
         <is>
-          <t>2026-09-11T22:42:45Z</t>
+          <t>2026-09-12T16:18:28Z</t>
         </is>
       </c>
     </row>
@@ -6346,7 +6346,7 @@
       </c>
       <c r="S73" s="4" t="inlineStr">
         <is>
-          <t>2026-09-11T22:42:45Z</t>
+          <t>2026-09-12T16:18:28Z</t>
         </is>
       </c>
     </row>
@@ -6431,7 +6431,7 @@
       </c>
       <c r="S74" s="4" t="inlineStr">
         <is>
-          <t>2026-09-11T22:42:45Z</t>
+          <t>2026-09-12T16:18:28Z</t>
         </is>
       </c>
     </row>
@@ -6516,7 +6516,7 @@
       </c>
       <c r="S75" s="4" t="inlineStr">
         <is>
-          <t>2026-09-11T22:42:45Z</t>
+          <t>2026-09-12T16:18:28Z</t>
         </is>
       </c>
     </row>
@@ -6601,7 +6601,7 @@
       </c>
       <c r="S76" s="4" t="inlineStr">
         <is>
-          <t>2026-09-11T22:42:45Z</t>
+          <t>2026-09-12T16:18:28Z</t>
         </is>
       </c>
     </row>
@@ -6686,7 +6686,7 @@
       </c>
       <c r="S77" s="4" t="inlineStr">
         <is>
-          <t>2026-09-11T22:42:45Z</t>
+          <t>2026-09-12T16:18:28Z</t>
         </is>
       </c>
     </row>
@@ -6771,7 +6771,7 @@
       </c>
       <c r="S78" s="4" t="inlineStr">
         <is>
-          <t>2026-09-11T22:42:45Z</t>
+          <t>2026-09-12T16:18:28Z</t>
         </is>
       </c>
     </row>
@@ -6856,7 +6856,7 @@
       </c>
       <c r="S79" s="4" t="inlineStr">
         <is>
-          <t>2026-09-11T22:42:45Z</t>
+          <t>2026-09-12T16:18:28Z</t>
         </is>
       </c>
     </row>
@@ -6941,7 +6941,7 @@
       </c>
       <c r="S80" s="4" t="inlineStr">
         <is>
-          <t>2026-09-11T22:42:45Z</t>
+          <t>2026-09-12T16:18:28Z</t>
         </is>
       </c>
     </row>
@@ -7026,7 +7026,7 @@
       </c>
       <c r="S81" s="4" t="inlineStr">
         <is>
-          <t>2026-09-11T22:42:45Z</t>
+          <t>2026-09-12T16:18:28Z</t>
         </is>
       </c>
     </row>
@@ -7111,7 +7111,7 @@
       </c>
       <c r="S82" s="4" t="inlineStr">
         <is>
-          <t>2026-09-11T22:42:45Z</t>
+          <t>2026-09-12T16:18:28Z</t>
         </is>
       </c>
     </row>
@@ -7196,7 +7196,7 @@
       </c>
       <c r="S83" s="4" t="inlineStr">
         <is>
-          <t>2026-09-11T22:42:45Z</t>
+          <t>2026-09-12T16:18:28Z</t>
         </is>
       </c>
     </row>
@@ -7281,7 +7281,7 @@
       </c>
       <c r="S84" s="4" t="inlineStr">
         <is>
-          <t>2026-09-11T22:42:45Z</t>
+          <t>2026-09-12T16:18:28Z</t>
         </is>
       </c>
     </row>
@@ -7366,7 +7366,7 @@
       </c>
       <c r="S85" s="4" t="inlineStr">
         <is>
-          <t>2026-09-11T22:42:45Z</t>
+          <t>2026-09-12T16:18:28Z</t>
         </is>
       </c>
     </row>
@@ -7451,7 +7451,7 @@
       </c>
       <c r="S86" s="4" t="inlineStr">
         <is>
-          <t>2026-09-11T22:42:45Z</t>
+          <t>2026-09-12T16:18:28Z</t>
         </is>
       </c>
     </row>
@@ -7536,7 +7536,7 @@
       </c>
       <c r="S87" s="4" t="inlineStr">
         <is>
-          <t>2026-09-11T22:42:45Z</t>
+          <t>2026-09-12T16:18:28Z</t>
         </is>
       </c>
     </row>
@@ -7621,7 +7621,7 @@
       </c>
       <c r="S88" s="4" t="inlineStr">
         <is>
-          <t>2026-09-11T22:42:45Z</t>
+          <t>2026-09-12T16:18:28Z</t>
         </is>
       </c>
     </row>
@@ -7706,7 +7706,7 @@
       </c>
       <c r="S89" s="4" t="inlineStr">
         <is>
-          <t>2026-09-11T22:42:45Z</t>
+          <t>2026-09-12T16:18:28Z</t>
         </is>
       </c>
     </row>
@@ -7791,7 +7791,7 @@
       </c>
       <c r="S90" s="4" t="inlineStr">
         <is>
-          <t>2026-09-11T22:42:45Z</t>
+          <t>2026-09-12T16:18:28Z</t>
         </is>
       </c>
     </row>
@@ -7876,7 +7876,7 @@
       </c>
       <c r="S91" s="4" t="inlineStr">
         <is>
-          <t>2026-09-11T22:42:45Z</t>
+          <t>2026-09-12T16:18:28Z</t>
         </is>
       </c>
     </row>
@@ -7961,7 +7961,7 @@
       </c>
       <c r="S92" s="4" t="inlineStr">
         <is>
-          <t>2026-09-11T22:42:45Z</t>
+          <t>2026-09-12T16:18:28Z</t>
         </is>
       </c>
     </row>
@@ -8046,7 +8046,7 @@
       </c>
       <c r="S93" s="4" t="inlineStr">
         <is>
-          <t>2026-09-11T22:42:45Z</t>
+          <t>2026-09-12T16:18:28Z</t>
         </is>
       </c>
     </row>
@@ -8131,7 +8131,7 @@
       </c>
       <c r="S94" s="4" t="inlineStr">
         <is>
-          <t>2026-09-11T22:42:45Z</t>
+          <t>2026-09-12T16:18:28Z</t>
         </is>
       </c>
     </row>
@@ -8216,7 +8216,7 @@
       </c>
       <c r="S95" s="4" t="inlineStr">
         <is>
-          <t>2026-09-11T22:42:45Z</t>
+          <t>2026-09-12T16:18:28Z</t>
         </is>
       </c>
     </row>
@@ -8301,7 +8301,7 @@
       </c>
       <c r="S96" s="4" t="inlineStr">
         <is>
-          <t>2026-09-11T22:42:45Z</t>
+          <t>2026-09-12T16:18:28Z</t>
         </is>
       </c>
     </row>
@@ -8386,7 +8386,7 @@
       </c>
       <c r="S97" s="4" t="inlineStr">
         <is>
-          <t>2026-09-11T22:42:45Z</t>
+          <t>2026-09-12T16:18:28Z</t>
         </is>
       </c>
     </row>
@@ -8471,7 +8471,7 @@
       </c>
       <c r="S98" s="4" t="inlineStr">
         <is>
-          <t>2026-09-11T22:42:45Z</t>
+          <t>2026-09-12T16:18:28Z</t>
         </is>
       </c>
     </row>
@@ -8556,7 +8556,7 @@
       </c>
       <c r="S99" s="4" t="inlineStr">
         <is>
-          <t>2026-09-11T22:42:45Z</t>
+          <t>2026-09-12T16:18:28Z</t>
         </is>
       </c>
     </row>
@@ -8641,7 +8641,7 @@
       </c>
       <c r="S100" s="4" t="inlineStr">
         <is>
-          <t>2026-09-11T22:42:45Z</t>
+          <t>2026-09-12T16:18:28Z</t>
         </is>
       </c>
     </row>
@@ -8726,7 +8726,7 @@
       </c>
       <c r="S101" s="4" t="inlineStr">
         <is>
-          <t>2026-09-11T22:42:45Z</t>
+          <t>2026-09-12T16:18:28Z</t>
         </is>
       </c>
     </row>
@@ -8811,7 +8811,7 @@
       </c>
       <c r="S102" s="4" t="inlineStr">
         <is>
-          <t>2026-09-11T22:42:45Z</t>
+          <t>2026-09-12T16:18:28Z</t>
         </is>
       </c>
     </row>
@@ -8896,7 +8896,7 @@
       </c>
       <c r="S103" s="4" t="inlineStr">
         <is>
-          <t>2026-09-11T22:42:45Z</t>
+          <t>2026-09-12T16:18:28Z</t>
         </is>
       </c>
     </row>
@@ -8981,7 +8981,7 @@
       </c>
       <c r="S104" s="4" t="inlineStr">
         <is>
-          <t>2026-09-11T22:42:45Z</t>
+          <t>2026-09-12T16:18:28Z</t>
         </is>
       </c>
     </row>
@@ -9066,7 +9066,7 @@
       </c>
       <c r="S105" s="4" t="inlineStr">
         <is>
-          <t>2026-09-11T22:42:45Z</t>
+          <t>2026-09-12T16:18:28Z</t>
         </is>
       </c>
     </row>
@@ -9151,7 +9151,7 @@
       </c>
       <c r="S106" s="4" t="inlineStr">
         <is>
-          <t>2026-09-11T22:42:45Z</t>
+          <t>2026-09-12T16:18:28Z</t>
         </is>
       </c>
     </row>
@@ -9236,7 +9236,7 @@
       </c>
       <c r="S107" s="4" t="inlineStr">
         <is>
-          <t>2026-09-11T22:42:45Z</t>
+          <t>2026-09-12T16:18:28Z</t>
         </is>
       </c>
     </row>
@@ -9321,7 +9321,7 @@
       </c>
       <c r="S108" s="4" t="inlineStr">
         <is>
-          <t>2026-09-11T22:42:45Z</t>
+          <t>2026-09-12T16:18:28Z</t>
         </is>
       </c>
     </row>
@@ -9406,7 +9406,7 @@
       </c>
       <c r="S109" s="4" t="inlineStr">
         <is>
-          <t>2026-09-11T22:42:45Z</t>
+          <t>2026-09-12T16:18:28Z</t>
         </is>
       </c>
     </row>
@@ -9491,7 +9491,7 @@
       </c>
       <c r="S110" s="4" t="inlineStr">
         <is>
-          <t>2026-09-11T22:42:45Z</t>
+          <t>2026-09-12T16:18:28Z</t>
         </is>
       </c>
     </row>
@@ -9576,7 +9576,7 @@
       </c>
       <c r="S111" s="4" t="inlineStr">
         <is>
-          <t>2026-09-11T22:42:45Z</t>
+          <t>2026-09-12T16:18:28Z</t>
         </is>
       </c>
     </row>
@@ -9661,7 +9661,7 @@
       </c>
       <c r="S112" s="4" t="inlineStr">
         <is>
-          <t>2026-09-11T22:42:45Z</t>
+          <t>2026-09-12T16:18:28Z</t>
         </is>
       </c>
     </row>
@@ -9746,7 +9746,7 @@
       </c>
       <c r="S113" s="4" t="inlineStr">
         <is>
-          <t>2026-09-11T22:42:45Z</t>
+          <t>2026-09-12T16:18:28Z</t>
         </is>
       </c>
     </row>
@@ -9831,7 +9831,7 @@
       </c>
       <c r="S114" s="4" t="inlineStr">
         <is>
-          <t>2026-09-11T22:42:45Z</t>
+          <t>2026-09-12T16:18:28Z</t>
         </is>
       </c>
     </row>
@@ -9916,7 +9916,7 @@
       </c>
       <c r="S115" s="4" t="inlineStr">
         <is>
-          <t>2026-09-11T22:42:45Z</t>
+          <t>2026-09-12T16:18:28Z</t>
         </is>
       </c>
     </row>
@@ -10001,7 +10001,7 @@
       </c>
       <c r="S116" s="4" t="inlineStr">
         <is>
-          <t>2026-09-11T22:42:45Z</t>
+          <t>2026-09-12T16:18:28Z</t>
         </is>
       </c>
     </row>
@@ -10086,7 +10086,7 @@
       </c>
       <c r="S117" s="4" t="inlineStr">
         <is>
-          <t>2026-09-11T22:42:45Z</t>
+          <t>2026-09-12T16:18:28Z</t>
         </is>
       </c>
     </row>
@@ -10171,7 +10171,7 @@
       </c>
       <c r="S118" s="4" t="inlineStr">
         <is>
-          <t>2026-09-11T22:42:45Z</t>
+          <t>2026-09-12T16:18:28Z</t>
         </is>
       </c>
     </row>
@@ -10256,7 +10256,7 @@
       </c>
       <c r="S119" s="4" t="inlineStr">
         <is>
-          <t>2026-09-11T22:42:45Z</t>
+          <t>2026-09-12T16:18:28Z</t>
         </is>
       </c>
     </row>
@@ -10341,7 +10341,7 @@
       </c>
       <c r="S120" s="4" t="inlineStr">
         <is>
-          <t>2026-09-11T22:42:45Z</t>
+          <t>2026-09-12T16:18:28Z</t>
         </is>
       </c>
     </row>
@@ -10426,7 +10426,7 @@
       </c>
       <c r="S121" s="4" t="inlineStr">
         <is>
-          <t>2026-09-11T22:42:45Z</t>
+          <t>2026-09-12T16:18:28Z</t>
         </is>
       </c>
     </row>
@@ -10511,7 +10511,7 @@
       </c>
       <c r="S122" s="4" t="inlineStr">
         <is>
-          <t>2026-09-11T22:42:45Z</t>
+          <t>2026-09-12T16:18:28Z</t>
         </is>
       </c>
     </row>
@@ -10596,7 +10596,7 @@
       </c>
       <c r="S123" s="4" t="inlineStr">
         <is>
-          <t>2026-09-11T22:42:45Z</t>
+          <t>2026-09-12T16:18:28Z</t>
         </is>
       </c>
     </row>
@@ -10681,7 +10681,7 @@
       </c>
       <c r="S124" s="4" t="inlineStr">
         <is>
-          <t>2026-09-11T22:42:45Z</t>
+          <t>2026-09-12T16:18:28Z</t>
         </is>
       </c>
     </row>
@@ -10766,7 +10766,7 @@
       </c>
       <c r="S125" s="4" t="inlineStr">
         <is>
-          <t>2026-09-11T22:42:45Z</t>
+          <t>2026-09-12T16:18:28Z</t>
         </is>
       </c>
     </row>
@@ -10851,7 +10851,7 @@
       </c>
       <c r="S126" s="4" t="inlineStr">
         <is>
-          <t>2026-09-11T22:42:45Z</t>
+          <t>2026-09-12T16:18:28Z</t>
         </is>
       </c>
     </row>
@@ -10936,7 +10936,7 @@
       </c>
       <c r="S127" s="4" t="inlineStr">
         <is>
-          <t>2026-09-11T22:42:45Z</t>
+          <t>2026-09-12T16:18:28Z</t>
         </is>
       </c>
     </row>
@@ -11021,7 +11021,7 @@
       </c>
       <c r="S128" s="4" t="inlineStr">
         <is>
-          <t>2026-09-11T22:42:45Z</t>
+          <t>2026-09-12T16:18:28Z</t>
         </is>
       </c>
     </row>
@@ -11106,7 +11106,7 @@
       </c>
       <c r="S129" s="4" t="inlineStr">
         <is>
-          <t>2026-09-11T22:42:45Z</t>
+          <t>2026-09-12T16:18:28Z</t>
         </is>
       </c>
     </row>
@@ -11191,7 +11191,7 @@
       </c>
       <c r="S130" s="4" t="inlineStr">
         <is>
-          <t>2026-09-11T22:42:45Z</t>
+          <t>2026-09-12T16:18:28Z</t>
         </is>
       </c>
     </row>
@@ -11276,7 +11276,7 @@
       </c>
       <c r="S131" s="4" t="inlineStr">
         <is>
-          <t>2026-09-11T22:42:45Z</t>
+          <t>2026-09-12T16:18:28Z</t>
         </is>
       </c>
     </row>
@@ -11361,7 +11361,7 @@
       </c>
       <c r="S132" s="4" t="inlineStr">
         <is>
-          <t>2026-09-11T22:42:45Z</t>
+          <t>2026-09-12T16:18:28Z</t>
         </is>
       </c>
     </row>
@@ -11446,7 +11446,7 @@
       </c>
       <c r="S133" s="4" t="inlineStr">
         <is>
-          <t>2026-09-11T22:42:45Z</t>
+          <t>2026-09-12T16:18:28Z</t>
         </is>
       </c>
     </row>
@@ -11531,7 +11531,7 @@
       </c>
       <c r="S134" s="4" t="inlineStr">
         <is>
-          <t>2026-09-11T22:42:45Z</t>
+          <t>2026-09-12T16:18:28Z</t>
         </is>
       </c>
     </row>
@@ -11616,7 +11616,7 @@
       </c>
       <c r="S135" s="4" t="inlineStr">
         <is>
-          <t>2026-09-11T22:42:45Z</t>
+          <t>2026-09-12T16:18:28Z</t>
         </is>
       </c>
     </row>
@@ -11701,7 +11701,7 @@
       </c>
       <c r="S136" s="4" t="inlineStr">
         <is>
-          <t>2026-09-11T22:42:45Z</t>
+          <t>2026-09-12T16:18:28Z</t>
         </is>
       </c>
     </row>
@@ -11786,7 +11786,7 @@
       </c>
       <c r="S137" s="4" t="inlineStr">
         <is>
-          <t>2026-09-11T22:42:45Z</t>
+          <t>2026-09-12T16:18:28Z</t>
         </is>
       </c>
     </row>
@@ -11871,7 +11871,7 @@
       </c>
       <c r="S138" s="4" t="inlineStr">
         <is>
-          <t>2026-09-11T22:42:45Z</t>
+          <t>2026-09-12T16:18:28Z</t>
         </is>
       </c>
     </row>
@@ -11956,7 +11956,7 @@
       </c>
       <c r="S139" s="4" t="inlineStr">
         <is>
-          <t>2026-09-11T22:42:45Z</t>
+          <t>2026-09-12T16:18:28Z</t>
         </is>
       </c>
     </row>
@@ -12041,7 +12041,7 @@
       </c>
       <c r="S140" s="4" t="inlineStr">
         <is>
-          <t>2026-09-11T22:42:45Z</t>
+          <t>2026-09-12T16:18:28Z</t>
         </is>
       </c>
     </row>
@@ -12126,7 +12126,7 @@
       </c>
       <c r="S141" s="4" t="inlineStr">
         <is>
-          <t>2026-09-11T22:42:45Z</t>
+          <t>2026-09-12T16:18:28Z</t>
         </is>
       </c>
     </row>
@@ -12258,7 +12258,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>2026-09-11T22:42:45Z</t>
+          <t>2026-09-12T16:18:28Z</t>
         </is>
       </c>
     </row>
@@ -12338,7 +12338,7 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>{"dataset_id": "bcv_pib_historico_anual", "title": "Producto interno bruto histórico anual", "table": "PIB histórico anual", "source_file": "7_1_14_anual.xls", "base": "1957/1968/1984/1997", "price_type": "Precios constantes", "measure": "Nivel", "frequency": "Anual", "period": "2017", "year": 2017, "quarter": null, "classification": "Total economía", "component": "Producto interno bruto", "value": 392393.12, "unit": "Millones de bolívares a precios constantes", "status": "", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/7_1_14_anual.xls", "fetched_at": "2026-09-11T22:42:45Z"}</t>
+          <t>{"dataset_id": "bcv_pib_historico_anual", "title": "Producto interno bruto histórico anual", "table": "PIB histórico anual", "source_file": "7_1_14_anual.xls", "base": "1957/1968/1984/1997", "price_type": "Precios constantes", "measure": "Nivel", "frequency": "Anual", "period": "2017", "year": 2017, "quarter": null, "classification": "Total economía", "component": "Producto interno bruto", "value": 392393.12, "unit": "Millones de bolívares a precios constantes", "status": "", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/7_1_14_anual.xls", "fetched_at": "2026-09-12T16:18:28Z"}</t>
         </is>
       </c>
     </row>

--- a/assets/data/bcv/excel/ove_bcv_pib_historico_anual.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_pib_historico_anual.xlsx
@@ -736,7 +736,7 @@
       </c>
       <c r="S7" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T16:18:28Z</t>
+          <t>2026-09-12T22:27:02Z</t>
         </is>
       </c>
     </row>
@@ -821,7 +821,7 @@
       </c>
       <c r="S8" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T16:18:28Z</t>
+          <t>2026-09-12T22:27:02Z</t>
         </is>
       </c>
     </row>
@@ -906,7 +906,7 @@
       </c>
       <c r="S9" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T16:18:28Z</t>
+          <t>2026-09-12T22:27:02Z</t>
         </is>
       </c>
     </row>
@@ -991,7 +991,7 @@
       </c>
       <c r="S10" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T16:18:28Z</t>
+          <t>2026-09-12T22:27:02Z</t>
         </is>
       </c>
     </row>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="S11" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T16:18:28Z</t>
+          <t>2026-09-12T22:27:02Z</t>
         </is>
       </c>
     </row>
@@ -1161,7 +1161,7 @@
       </c>
       <c r="S12" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T16:18:28Z</t>
+          <t>2026-09-12T22:27:02Z</t>
         </is>
       </c>
     </row>
@@ -1246,7 +1246,7 @@
       </c>
       <c r="S13" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T16:18:28Z</t>
+          <t>2026-09-12T22:27:02Z</t>
         </is>
       </c>
     </row>
@@ -1331,7 +1331,7 @@
       </c>
       <c r="S14" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T16:18:28Z</t>
+          <t>2026-09-12T22:27:02Z</t>
         </is>
       </c>
     </row>
@@ -1416,7 +1416,7 @@
       </c>
       <c r="S15" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T16:18:28Z</t>
+          <t>2026-09-12T22:27:02Z</t>
         </is>
       </c>
     </row>
@@ -1501,7 +1501,7 @@
       </c>
       <c r="S16" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T16:18:28Z</t>
+          <t>2026-09-12T22:27:02Z</t>
         </is>
       </c>
     </row>
@@ -1586,7 +1586,7 @@
       </c>
       <c r="S17" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T16:18:28Z</t>
+          <t>2026-09-12T22:27:02Z</t>
         </is>
       </c>
     </row>
@@ -1671,7 +1671,7 @@
       </c>
       <c r="S18" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T16:18:28Z</t>
+          <t>2026-09-12T22:27:02Z</t>
         </is>
       </c>
     </row>
@@ -1756,7 +1756,7 @@
       </c>
       <c r="S19" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T16:18:28Z</t>
+          <t>2026-09-12T22:27:02Z</t>
         </is>
       </c>
     </row>
@@ -1841,7 +1841,7 @@
       </c>
       <c r="S20" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T16:18:28Z</t>
+          <t>2026-09-12T22:27:02Z</t>
         </is>
       </c>
     </row>
@@ -1926,7 +1926,7 @@
       </c>
       <c r="S21" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T16:18:28Z</t>
+          <t>2026-09-12T22:27:02Z</t>
         </is>
       </c>
     </row>
@@ -2011,7 +2011,7 @@
       </c>
       <c r="S22" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T16:18:28Z</t>
+          <t>2026-09-12T22:27:02Z</t>
         </is>
       </c>
     </row>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="S23" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T16:18:28Z</t>
+          <t>2026-09-12T22:27:02Z</t>
         </is>
       </c>
     </row>
@@ -2181,7 +2181,7 @@
       </c>
       <c r="S24" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T16:18:28Z</t>
+          <t>2026-09-12T22:27:02Z</t>
         </is>
       </c>
     </row>
@@ -2266,7 +2266,7 @@
       </c>
       <c r="S25" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T16:18:28Z</t>
+          <t>2026-09-12T22:27:02Z</t>
         </is>
       </c>
     </row>
@@ -2351,7 +2351,7 @@
       </c>
       <c r="S26" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T16:18:28Z</t>
+          <t>2026-09-12T22:27:02Z</t>
         </is>
       </c>
     </row>
@@ -2436,7 +2436,7 @@
       </c>
       <c r="S27" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T16:18:28Z</t>
+          <t>2026-09-12T22:27:02Z</t>
         </is>
       </c>
     </row>
@@ -2521,7 +2521,7 @@
       </c>
       <c r="S28" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T16:18:28Z</t>
+          <t>2026-09-12T22:27:02Z</t>
         </is>
       </c>
     </row>
@@ -2606,7 +2606,7 @@
       </c>
       <c r="S29" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T16:18:28Z</t>
+          <t>2026-09-12T22:27:02Z</t>
         </is>
       </c>
     </row>
@@ -2691,7 +2691,7 @@
       </c>
       <c r="S30" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T16:18:28Z</t>
+          <t>2026-09-12T22:27:02Z</t>
         </is>
       </c>
     </row>
@@ -2776,7 +2776,7 @@
       </c>
       <c r="S31" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T16:18:28Z</t>
+          <t>2026-09-12T22:27:02Z</t>
         </is>
       </c>
     </row>
@@ -2861,7 +2861,7 @@
       </c>
       <c r="S32" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T16:18:28Z</t>
+          <t>2026-09-12T22:27:02Z</t>
         </is>
       </c>
     </row>
@@ -2946,7 +2946,7 @@
       </c>
       <c r="S33" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T16:18:28Z</t>
+          <t>2026-09-12T22:27:02Z</t>
         </is>
       </c>
     </row>
@@ -3031,7 +3031,7 @@
       </c>
       <c r="S34" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T16:18:28Z</t>
+          <t>2026-09-12T22:27:02Z</t>
         </is>
       </c>
     </row>
@@ -3116,7 +3116,7 @@
       </c>
       <c r="S35" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T16:18:28Z</t>
+          <t>2026-09-12T22:27:02Z</t>
         </is>
       </c>
     </row>
@@ -3201,7 +3201,7 @@
       </c>
       <c r="S36" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T16:18:28Z</t>
+          <t>2026-09-12T22:27:02Z</t>
         </is>
       </c>
     </row>
@@ -3286,7 +3286,7 @@
       </c>
       <c r="S37" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T16:18:28Z</t>
+          <t>2026-09-12T22:27:02Z</t>
         </is>
       </c>
     </row>
@@ -3371,7 +3371,7 @@
       </c>
       <c r="S38" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T16:18:28Z</t>
+          <t>2026-09-12T22:27:02Z</t>
         </is>
       </c>
     </row>
@@ -3456,7 +3456,7 @@
       </c>
       <c r="S39" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T16:18:28Z</t>
+          <t>2026-09-12T22:27:02Z</t>
         </is>
       </c>
     </row>
@@ -3541,7 +3541,7 @@
       </c>
       <c r="S40" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T16:18:28Z</t>
+          <t>2026-09-12T22:27:02Z</t>
         </is>
       </c>
     </row>
@@ -3626,7 +3626,7 @@
       </c>
       <c r="S41" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T16:18:28Z</t>
+          <t>2026-09-12T22:27:02Z</t>
         </is>
       </c>
     </row>
@@ -3711,7 +3711,7 @@
       </c>
       <c r="S42" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T16:18:28Z</t>
+          <t>2026-09-12T22:27:02Z</t>
         </is>
       </c>
     </row>
@@ -3796,7 +3796,7 @@
       </c>
       <c r="S43" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T16:18:28Z</t>
+          <t>2026-09-12T22:27:02Z</t>
         </is>
       </c>
     </row>
@@ -3881,7 +3881,7 @@
       </c>
       <c r="S44" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T16:18:28Z</t>
+          <t>2026-09-12T22:27:02Z</t>
         </is>
       </c>
     </row>
@@ -3966,7 +3966,7 @@
       </c>
       <c r="S45" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T16:18:28Z</t>
+          <t>2026-09-12T22:27:02Z</t>
         </is>
       </c>
     </row>
@@ -4051,7 +4051,7 @@
       </c>
       <c r="S46" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T16:18:28Z</t>
+          <t>2026-09-12T22:27:02Z</t>
         </is>
       </c>
     </row>
@@ -4136,7 +4136,7 @@
       </c>
       <c r="S47" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T16:18:28Z</t>
+          <t>2026-09-12T22:27:02Z</t>
         </is>
       </c>
     </row>
@@ -4221,7 +4221,7 @@
       </c>
       <c r="S48" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T16:18:28Z</t>
+          <t>2026-09-12T22:27:02Z</t>
         </is>
       </c>
     </row>
@@ -4306,7 +4306,7 @@
       </c>
       <c r="S49" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T16:18:28Z</t>
+          <t>2026-09-12T22:27:02Z</t>
         </is>
       </c>
     </row>
@@ -4391,7 +4391,7 @@
       </c>
       <c r="S50" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T16:18:28Z</t>
+          <t>2026-09-12T22:27:02Z</t>
         </is>
       </c>
     </row>
@@ -4476,7 +4476,7 @@
       </c>
       <c r="S51" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T16:18:28Z</t>
+          <t>2026-09-12T22:27:02Z</t>
         </is>
       </c>
     </row>
@@ -4561,7 +4561,7 @@
       </c>
       <c r="S52" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T16:18:28Z</t>
+          <t>2026-09-12T22:27:02Z</t>
         </is>
       </c>
     </row>
@@ -4646,7 +4646,7 @@
       </c>
       <c r="S53" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T16:18:28Z</t>
+          <t>2026-09-12T22:27:02Z</t>
         </is>
       </c>
     </row>
@@ -4731,7 +4731,7 @@
       </c>
       <c r="S54" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T16:18:28Z</t>
+          <t>2026-09-12T22:27:02Z</t>
         </is>
       </c>
     </row>
@@ -4816,7 +4816,7 @@
       </c>
       <c r="S55" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T16:18:28Z</t>
+          <t>2026-09-12T22:27:02Z</t>
         </is>
       </c>
     </row>
@@ -4901,7 +4901,7 @@
       </c>
       <c r="S56" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T16:18:28Z</t>
+          <t>2026-09-12T22:27:02Z</t>
         </is>
       </c>
     </row>
@@ -4986,7 +4986,7 @@
       </c>
       <c r="S57" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T16:18:28Z</t>
+          <t>2026-09-12T22:27:02Z</t>
         </is>
       </c>
     </row>
@@ -5071,7 +5071,7 @@
       </c>
       <c r="S58" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T16:18:28Z</t>
+          <t>2026-09-12T22:27:02Z</t>
         </is>
       </c>
     </row>
@@ -5156,7 +5156,7 @@
       </c>
       <c r="S59" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T16:18:28Z</t>
+          <t>2026-09-12T22:27:02Z</t>
         </is>
       </c>
     </row>
@@ -5241,7 +5241,7 @@
       </c>
       <c r="S60" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T16:18:28Z</t>
+          <t>2026-09-12T22:27:02Z</t>
         </is>
       </c>
     </row>
@@ -5326,7 +5326,7 @@
       </c>
       <c r="S61" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T16:18:28Z</t>
+          <t>2026-09-12T22:27:02Z</t>
         </is>
       </c>
     </row>
@@ -5411,7 +5411,7 @@
       </c>
       <c r="S62" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T16:18:28Z</t>
+          <t>2026-09-12T22:27:02Z</t>
         </is>
       </c>
     </row>
@@ -5496,7 +5496,7 @@
       </c>
       <c r="S63" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T16:18:28Z</t>
+          <t>2026-09-12T22:27:02Z</t>
         </is>
       </c>
     </row>
@@ -5581,7 +5581,7 @@
       </c>
       <c r="S64" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T16:18:28Z</t>
+          <t>2026-09-12T22:27:02Z</t>
         </is>
       </c>
     </row>
@@ -5666,7 +5666,7 @@
       </c>
       <c r="S65" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T16:18:28Z</t>
+          <t>2026-09-12T22:27:02Z</t>
         </is>
       </c>
     </row>
@@ -5751,7 +5751,7 @@
       </c>
       <c r="S66" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T16:18:28Z</t>
+          <t>2026-09-12T22:27:02Z</t>
         </is>
       </c>
     </row>
@@ -5836,7 +5836,7 @@
       </c>
       <c r="S67" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T16:18:28Z</t>
+          <t>2026-09-12T22:27:02Z</t>
         </is>
       </c>
     </row>
@@ -5921,7 +5921,7 @@
       </c>
       <c r="S68" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T16:18:28Z</t>
+          <t>2026-09-12T22:27:02Z</t>
         </is>
       </c>
     </row>
@@ -6006,7 +6006,7 @@
       </c>
       <c r="S69" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T16:18:28Z</t>
+          <t>2026-09-12T22:27:02Z</t>
         </is>
       </c>
     </row>
@@ -6091,7 +6091,7 @@
       </c>
       <c r="S70" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T16:18:28Z</t>
+          <t>2026-09-12T22:27:02Z</t>
         </is>
       </c>
     </row>
@@ -6176,7 +6176,7 @@
       </c>
       <c r="S71" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T16:18:28Z</t>
+          <t>2026-09-12T22:27:02Z</t>
         </is>
       </c>
     </row>
@@ -6261,7 +6261,7 @@
       </c>
       <c r="S72" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T16:18:28Z</t>
+          <t>2026-09-12T22:27:02Z</t>
         </is>
       </c>
     </row>
@@ -6346,7 +6346,7 @@
       </c>
       <c r="S73" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T16:18:28Z</t>
+          <t>2026-09-12T22:27:02Z</t>
         </is>
       </c>
     </row>
@@ -6431,7 +6431,7 @@
       </c>
       <c r="S74" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T16:18:28Z</t>
+          <t>2026-09-12T22:27:02Z</t>
         </is>
       </c>
     </row>
@@ -6516,7 +6516,7 @@
       </c>
       <c r="S75" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T16:18:28Z</t>
+          <t>2026-09-12T22:27:02Z</t>
         </is>
       </c>
     </row>
@@ -6601,7 +6601,7 @@
       </c>
       <c r="S76" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T16:18:28Z</t>
+          <t>2026-09-12T22:27:02Z</t>
         </is>
       </c>
     </row>
@@ -6686,7 +6686,7 @@
       </c>
       <c r="S77" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T16:18:28Z</t>
+          <t>2026-09-12T22:27:02Z</t>
         </is>
       </c>
     </row>
@@ -6771,7 +6771,7 @@
       </c>
       <c r="S78" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T16:18:28Z</t>
+          <t>2026-09-12T22:27:02Z</t>
         </is>
       </c>
     </row>
@@ -6856,7 +6856,7 @@
       </c>
       <c r="S79" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T16:18:28Z</t>
+          <t>2026-09-12T22:27:02Z</t>
         </is>
       </c>
     </row>
@@ -6941,7 +6941,7 @@
       </c>
       <c r="S80" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T16:18:28Z</t>
+          <t>2026-09-12T22:27:02Z</t>
         </is>
       </c>
     </row>
@@ -7026,7 +7026,7 @@
       </c>
       <c r="S81" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T16:18:28Z</t>
+          <t>2026-09-12T22:27:02Z</t>
         </is>
       </c>
     </row>
@@ -7111,7 +7111,7 @@
       </c>
       <c r="S82" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T16:18:28Z</t>
+          <t>2026-09-12T22:27:02Z</t>
         </is>
       </c>
     </row>
@@ -7196,7 +7196,7 @@
       </c>
       <c r="S83" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T16:18:28Z</t>
+          <t>2026-09-12T22:27:02Z</t>
         </is>
       </c>
     </row>
@@ -7281,7 +7281,7 @@
       </c>
       <c r="S84" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T16:18:28Z</t>
+          <t>2026-09-12T22:27:02Z</t>
         </is>
       </c>
     </row>
@@ -7366,7 +7366,7 @@
       </c>
       <c r="S85" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T16:18:28Z</t>
+          <t>2026-09-12T22:27:02Z</t>
         </is>
       </c>
     </row>
@@ -7451,7 +7451,7 @@
       </c>
       <c r="S86" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T16:18:28Z</t>
+          <t>2026-09-12T22:27:02Z</t>
         </is>
       </c>
     </row>
@@ -7536,7 +7536,7 @@
       </c>
       <c r="S87" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T16:18:28Z</t>
+          <t>2026-09-12T22:27:02Z</t>
         </is>
       </c>
     </row>
@@ -7621,7 +7621,7 @@
       </c>
       <c r="S88" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T16:18:28Z</t>
+          <t>2026-09-12T22:27:02Z</t>
         </is>
       </c>
     </row>
@@ -7706,7 +7706,7 @@
       </c>
       <c r="S89" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T16:18:28Z</t>
+          <t>2026-09-12T22:27:02Z</t>
         </is>
       </c>
     </row>
@@ -7791,7 +7791,7 @@
       </c>
       <c r="S90" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T16:18:28Z</t>
+          <t>2026-09-12T22:27:02Z</t>
         </is>
       </c>
     </row>
@@ -7876,7 +7876,7 @@
       </c>
       <c r="S91" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T16:18:28Z</t>
+          <t>2026-09-12T22:27:02Z</t>
         </is>
       </c>
     </row>
@@ -7961,7 +7961,7 @@
       </c>
       <c r="S92" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T16:18:28Z</t>
+          <t>2026-09-12T22:27:02Z</t>
         </is>
       </c>
     </row>
@@ -8046,7 +8046,7 @@
       </c>
       <c r="S93" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T16:18:28Z</t>
+          <t>2026-09-12T22:27:02Z</t>
         </is>
       </c>
     </row>
@@ -8131,7 +8131,7 @@
       </c>
       <c r="S94" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T16:18:28Z</t>
+          <t>2026-09-12T22:27:02Z</t>
         </is>
       </c>
     </row>
@@ -8216,7 +8216,7 @@
       </c>
       <c r="S95" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T16:18:28Z</t>
+          <t>2026-09-12T22:27:02Z</t>
         </is>
       </c>
     </row>
@@ -8301,7 +8301,7 @@
       </c>
       <c r="S96" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T16:18:28Z</t>
+          <t>2026-09-12T22:27:02Z</t>
         </is>
       </c>
     </row>
@@ -8386,7 +8386,7 @@
       </c>
       <c r="S97" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T16:18:28Z</t>
+          <t>2026-09-12T22:27:02Z</t>
         </is>
       </c>
     </row>
@@ -8471,7 +8471,7 @@
       </c>
       <c r="S98" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T16:18:28Z</t>
+          <t>2026-09-12T22:27:02Z</t>
         </is>
       </c>
     </row>
@@ -8556,7 +8556,7 @@
       </c>
       <c r="S99" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T16:18:28Z</t>
+          <t>2026-09-12T22:27:02Z</t>
         </is>
       </c>
     </row>
@@ -8641,7 +8641,7 @@
       </c>
       <c r="S100" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T16:18:28Z</t>
+          <t>2026-09-12T22:27:02Z</t>
         </is>
       </c>
     </row>
@@ -8726,7 +8726,7 @@
       </c>
       <c r="S101" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T16:18:28Z</t>
+          <t>2026-09-12T22:27:02Z</t>
         </is>
       </c>
     </row>
@@ -8811,7 +8811,7 @@
       </c>
       <c r="S102" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T16:18:28Z</t>
+          <t>2026-09-12T22:27:02Z</t>
         </is>
       </c>
     </row>
@@ -8896,7 +8896,7 @@
       </c>
       <c r="S103" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T16:18:28Z</t>
+          <t>2026-09-12T22:27:02Z</t>
         </is>
       </c>
     </row>
@@ -8981,7 +8981,7 @@
       </c>
       <c r="S104" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T16:18:28Z</t>
+          <t>2026-09-12T22:27:02Z</t>
         </is>
       </c>
     </row>
@@ -9066,7 +9066,7 @@
       </c>
       <c r="S105" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T16:18:28Z</t>
+          <t>2026-09-12T22:27:02Z</t>
         </is>
       </c>
     </row>
@@ -9151,7 +9151,7 @@
       </c>
       <c r="S106" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T16:18:28Z</t>
+          <t>2026-09-12T22:27:02Z</t>
         </is>
       </c>
     </row>
@@ -9236,7 +9236,7 @@
       </c>
       <c r="S107" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T16:18:28Z</t>
+          <t>2026-09-12T22:27:02Z</t>
         </is>
       </c>
     </row>
@@ -9321,7 +9321,7 @@
       </c>
       <c r="S108" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T16:18:28Z</t>
+          <t>2026-09-12T22:27:02Z</t>
         </is>
       </c>
     </row>
@@ -9406,7 +9406,7 @@
       </c>
       <c r="S109" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T16:18:28Z</t>
+          <t>2026-09-12T22:27:02Z</t>
         </is>
       </c>
     </row>
@@ -9491,7 +9491,7 @@
       </c>
       <c r="S110" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T16:18:28Z</t>
+          <t>2026-09-12T22:27:02Z</t>
         </is>
       </c>
     </row>
@@ -9576,7 +9576,7 @@
       </c>
       <c r="S111" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T16:18:28Z</t>
+          <t>2026-09-12T22:27:02Z</t>
         </is>
       </c>
     </row>
@@ -9661,7 +9661,7 @@
       </c>
       <c r="S112" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T16:18:28Z</t>
+          <t>2026-09-12T22:27:02Z</t>
         </is>
       </c>
     </row>
@@ -9746,7 +9746,7 @@
       </c>
       <c r="S113" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T16:18:28Z</t>
+          <t>2026-09-12T22:27:02Z</t>
         </is>
       </c>
     </row>
@@ -9831,7 +9831,7 @@
       </c>
       <c r="S114" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T16:18:28Z</t>
+          <t>2026-09-12T22:27:02Z</t>
         </is>
       </c>
     </row>
@@ -9916,7 +9916,7 @@
       </c>
       <c r="S115" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T16:18:28Z</t>
+          <t>2026-09-12T22:27:02Z</t>
         </is>
       </c>
     </row>
@@ -10001,7 +10001,7 @@
       </c>
       <c r="S116" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T16:18:28Z</t>
+          <t>2026-09-12T22:27:02Z</t>
         </is>
       </c>
     </row>
@@ -10086,7 +10086,7 @@
       </c>
       <c r="S117" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T16:18:28Z</t>
+          <t>2026-09-12T22:27:02Z</t>
         </is>
       </c>
     </row>
@@ -10171,7 +10171,7 @@
       </c>
       <c r="S118" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T16:18:28Z</t>
+          <t>2026-09-12T22:27:02Z</t>
         </is>
       </c>
     </row>
@@ -10256,7 +10256,7 @@
       </c>
       <c r="S119" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T16:18:28Z</t>
+          <t>2026-09-12T22:27:02Z</t>
         </is>
       </c>
     </row>
@@ -10341,7 +10341,7 @@
       </c>
       <c r="S120" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T16:18:28Z</t>
+          <t>2026-09-12T22:27:02Z</t>
         </is>
       </c>
     </row>
@@ -10426,7 +10426,7 @@
       </c>
       <c r="S121" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T16:18:28Z</t>
+          <t>2026-09-12T22:27:02Z</t>
         </is>
       </c>
     </row>
@@ -10511,7 +10511,7 @@
       </c>
       <c r="S122" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T16:18:28Z</t>
+          <t>2026-09-12T22:27:02Z</t>
         </is>
       </c>
     </row>
@@ -10596,7 +10596,7 @@
       </c>
       <c r="S123" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T16:18:28Z</t>
+          <t>2026-09-12T22:27:02Z</t>
         </is>
       </c>
     </row>
@@ -10681,7 +10681,7 @@
       </c>
       <c r="S124" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T16:18:28Z</t>
+          <t>2026-09-12T22:27:02Z</t>
         </is>
       </c>
     </row>
@@ -10766,7 +10766,7 @@
       </c>
       <c r="S125" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T16:18:28Z</t>
+          <t>2026-09-12T22:27:02Z</t>
         </is>
       </c>
     </row>
@@ -10851,7 +10851,7 @@
       </c>
       <c r="S126" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T16:18:28Z</t>
+          <t>2026-09-12T22:27:02Z</t>
         </is>
       </c>
     </row>
@@ -10936,7 +10936,7 @@
       </c>
       <c r="S127" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T16:18:28Z</t>
+          <t>2026-09-12T22:27:02Z</t>
         </is>
       </c>
     </row>
@@ -11021,7 +11021,7 @@
       </c>
       <c r="S128" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T16:18:28Z</t>
+          <t>2026-09-12T22:27:02Z</t>
         </is>
       </c>
     </row>
@@ -11106,7 +11106,7 @@
       </c>
       <c r="S129" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T16:18:28Z</t>
+          <t>2026-09-12T22:27:02Z</t>
         </is>
       </c>
     </row>
@@ -11191,7 +11191,7 @@
       </c>
       <c r="S130" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T16:18:28Z</t>
+          <t>2026-09-12T22:27:02Z</t>
         </is>
       </c>
     </row>
@@ -11276,7 +11276,7 @@
       </c>
       <c r="S131" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T16:18:28Z</t>
+          <t>2026-09-12T22:27:02Z</t>
         </is>
       </c>
     </row>
@@ -11361,7 +11361,7 @@
       </c>
       <c r="S132" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T16:18:28Z</t>
+          <t>2026-09-12T22:27:02Z</t>
         </is>
       </c>
     </row>
@@ -11446,7 +11446,7 @@
       </c>
       <c r="S133" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T16:18:28Z</t>
+          <t>2026-09-12T22:27:02Z</t>
         </is>
       </c>
     </row>
@@ -11531,7 +11531,7 @@
       </c>
       <c r="S134" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T16:18:28Z</t>
+          <t>2026-09-12T22:27:02Z</t>
         </is>
       </c>
     </row>
@@ -11616,7 +11616,7 @@
       </c>
       <c r="S135" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T16:18:28Z</t>
+          <t>2026-09-12T22:27:02Z</t>
         </is>
       </c>
     </row>
@@ -11701,7 +11701,7 @@
       </c>
       <c r="S136" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T16:18:28Z</t>
+          <t>2026-09-12T22:27:02Z</t>
         </is>
       </c>
     </row>
@@ -11786,7 +11786,7 @@
       </c>
       <c r="S137" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T16:18:28Z</t>
+          <t>2026-09-12T22:27:02Z</t>
         </is>
       </c>
     </row>
@@ -11871,7 +11871,7 @@
       </c>
       <c r="S138" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T16:18:28Z</t>
+          <t>2026-09-12T22:27:02Z</t>
         </is>
       </c>
     </row>
@@ -11956,7 +11956,7 @@
       </c>
       <c r="S139" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T16:18:28Z</t>
+          <t>2026-09-12T22:27:02Z</t>
         </is>
       </c>
     </row>
@@ -12041,7 +12041,7 @@
       </c>
       <c r="S140" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T16:18:28Z</t>
+          <t>2026-09-12T22:27:02Z</t>
         </is>
       </c>
     </row>
@@ -12126,7 +12126,7 @@
       </c>
       <c r="S141" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T16:18:28Z</t>
+          <t>2026-09-12T22:27:02Z</t>
         </is>
       </c>
     </row>
@@ -12258,7 +12258,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T16:18:28Z</t>
+          <t>2026-09-12T22:27:02Z</t>
         </is>
       </c>
     </row>
@@ -12338,7 +12338,7 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>{"dataset_id": "bcv_pib_historico_anual", "title": "Producto interno bruto histórico anual", "table": "PIB histórico anual", "source_file": "7_1_14_anual.xls", "base": "1957/1968/1984/1997", "price_type": "Precios constantes", "measure": "Nivel", "frequency": "Anual", "period": "2017", "year": 2017, "quarter": null, "classification": "Total economía", "component": "Producto interno bruto", "value": 392393.12, "unit": "Millones de bolívares a precios constantes", "status": "", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/7_1_14_anual.xls", "fetched_at": "2026-09-12T16:18:28Z"}</t>
+          <t>{"dataset_id": "bcv_pib_historico_anual", "title": "Producto interno bruto histórico anual", "table": "PIB histórico anual", "source_file": "7_1_14_anual.xls", "base": "1957/1968/1984/1997", "price_type": "Precios constantes", "measure": "Nivel", "frequency": "Anual", "period": "2017", "year": 2017, "quarter": null, "classification": "Total economía", "component": "Producto interno bruto", "value": 392393.12, "unit": "Millones de bolívares a precios constantes", "status": "", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/7_1_14_anual.xls", "fetched_at": "2026-09-12T22:27:02Z"}</t>
         </is>
       </c>
     </row>
